--- a/data/freight/US Rail Traffic.xlsx
+++ b/data/freight/US Rail Traffic.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm12\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAC6BABE-21A2-45A1-B818-986EE25408AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F86E7320-A39F-4E3D-866D-A73825E87169}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-5790" windowWidth="29040" windowHeight="15720" xr2:uid="{55EF15CE-83DB-4E42-B75D-C3DAE3AA4C48}"/>
   </bookViews>
@@ -93,7 +93,7 @@
     <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="178" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="181" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="179" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
@@ -255,16 +255,16 @@
     <xf numFmtId="178" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5708,6 +5708,9 @@
                 </c:pt>
                 <c:pt idx="885">
                   <c:v>515921</c:v>
+                </c:pt>
+                <c:pt idx="886">
+                  <c:v>501328</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -23124,6 +23127,9 @@
 )</f>
         <v>UTC-4</v>
       </c>
+      <c r="E888" s="17">
+        <v>501328</v>
+      </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E876">

--- a/data/freight/US Rail Traffic.xlsx
+++ b/data/freight/US Rail Traffic.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm12\PycharmProjects\AlternativeData\data\freight\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F86E7320-A39F-4E3D-866D-A73825E87169}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{951197DF-26FF-4E53-B6D9-FFB5794A92CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-5790" windowWidth="29040" windowHeight="15720" xr2:uid="{55EF15CE-83DB-4E42-B75D-C3DAE3AA4C48}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{55EF15CE-83DB-4E42-B75D-C3DAE3AA4C48}"/>
   </bookViews>
   <sheets>
     <sheet name="USRT" sheetId="1" r:id="rId1"/>
@@ -30,9 +30,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -3042,6 +3039,9 @@
                 <c:pt idx="886">
                   <c:v>46120</c:v>
                 </c:pt>
+                <c:pt idx="887">
+                  <c:v>46127</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5856,6 +5856,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -5863,7 +5864,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -6792,18 +6792,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83FCC8DB-37A0-4531-B65E-34C65BAF4830}">
-  <dimension ref="A1:E888"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E889"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="12.6" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.28515625" style="21" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.33203125" style="21" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.42578125" style="17" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="5"/>
+    <col min="5" max="5" width="12.44140625" style="17" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -6820,7 +6820,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="6">
         <v>39823</v>
       </c>
@@ -6853,7 +6853,7 @@
         <v>474565</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="6">
         <v>39830</v>
       </c>
@@ -6871,7 +6871,7 @@
         <v>465386</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="6">
         <v>39837</v>
       </c>
@@ -6889,7 +6889,7 @@
         <v>462128</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="6">
         <v>39844</v>
       </c>
@@ -6907,7 +6907,7 @@
         <v>449966</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="6">
         <v>39851</v>
       </c>
@@ -6925,7 +6925,7 @@
         <v>455757</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="6">
         <v>39858</v>
       </c>
@@ -6943,7 +6943,7 @@
         <v>471961</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="6">
         <v>39865</v>
       </c>
@@ -6961,7 +6961,7 @@
         <v>446575</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="6">
         <v>39872</v>
       </c>
@@ -6979,7 +6979,7 @@
         <v>458242</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="6">
         <v>39879</v>
       </c>
@@ -6997,7 +6997,7 @@
         <v>455041</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="6">
         <v>39886</v>
       </c>
@@ -7015,7 +7015,7 @@
         <v>455686</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="6">
         <v>39893</v>
       </c>
@@ -7033,7 +7033,7 @@
         <v>459547</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="6">
         <v>39900</v>
       </c>
@@ -7051,7 +7051,7 @@
         <v>439844</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="6">
         <v>39907</v>
       </c>
@@ -7069,7 +7069,7 @@
         <v>447103</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" s="6">
         <v>39914</v>
       </c>
@@ -7087,7 +7087,7 @@
         <v>426107</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="6">
         <v>39921</v>
       </c>
@@ -7105,7 +7105,7 @@
         <v>438602</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" s="6">
         <v>39928</v>
       </c>
@@ -7123,7 +7123,7 @@
         <v>444794</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" s="6">
         <v>39935</v>
       </c>
@@ -7141,7 +7141,7 @@
         <v>442378</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" s="6">
         <v>39942</v>
       </c>
@@ -7159,7 +7159,7 @@
         <v>435052</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" s="6">
         <v>39949</v>
       </c>
@@ -7177,7 +7177,7 @@
         <v>438329</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" s="6">
         <v>39956</v>
       </c>
@@ -7195,7 +7195,7 @@
         <v>451355</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" s="6">
         <v>39963</v>
       </c>
@@ -7213,7 +7213,7 @@
         <v>401248</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" s="6">
         <v>39970</v>
       </c>
@@ -7231,7 +7231,7 @@
         <v>448743</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" s="6">
         <v>39977</v>
       </c>
@@ -7249,7 +7249,7 @@
         <v>451065</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" s="6">
         <v>39984</v>
       </c>
@@ -7267,7 +7267,7 @@
         <v>449103</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" s="6">
         <v>39991</v>
       </c>
@@ -7285,7 +7285,7 @@
         <v>444212</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" s="6">
         <v>39998</v>
       </c>
@@ -7303,7 +7303,7 @@
         <v>410661</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" s="6">
         <v>40005</v>
       </c>
@@ -7321,7 +7321,7 @@
         <v>439041</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" s="6">
         <v>40012</v>
       </c>
@@ -7339,7 +7339,7 @@
         <v>456926</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" s="6">
         <v>40019</v>
       </c>
@@ -7357,7 +7357,7 @@
         <v>467395</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" s="6">
         <v>40026</v>
       </c>
@@ -7375,7 +7375,7 @@
         <v>468150</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" s="6">
         <v>40033</v>
       </c>
@@ -7393,7 +7393,7 @@
         <v>469814</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" s="6">
         <v>40040</v>
       </c>
@@ -7411,7 +7411,7 @@
         <v>469727</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" s="6">
         <v>40047</v>
       </c>
@@ -7429,7 +7429,7 @@
         <v>472644</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" s="6">
         <v>40054</v>
       </c>
@@ -7447,7 +7447,7 @@
         <v>488273</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" s="6">
         <v>40061</v>
       </c>
@@ -7465,7 +7465,7 @@
         <v>486009</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" s="6">
         <v>40068</v>
       </c>
@@ -7483,7 +7483,7 @@
         <v>439238</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" s="6">
         <v>40075</v>
       </c>
@@ -7501,7 +7501,7 @@
         <v>487236</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" s="6">
         <v>40082</v>
       </c>
@@ -7519,7 +7519,7 @@
         <v>477434</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" s="6">
         <v>40089</v>
       </c>
@@ -7537,7 +7537,7 @@
         <v>484157</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" s="6">
         <v>40096</v>
       </c>
@@ -7555,7 +7555,7 @@
         <v>481944</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" s="6">
         <v>40103</v>
       </c>
@@ -7573,7 +7573,7 @@
         <v>481827</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" s="6">
         <v>40110</v>
       </c>
@@ -7591,7 +7591,7 @@
         <v>483850</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" s="6">
         <v>40117</v>
       </c>
@@ -7609,7 +7609,7 @@
         <v>479450</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" s="6">
         <v>40124</v>
       </c>
@@ -7627,7 +7627,7 @@
         <v>481493</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" s="6">
         <v>40131</v>
       </c>
@@ -7645,7 +7645,7 @@
         <v>489073</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" s="6">
         <v>40138</v>
       </c>
@@ -7663,7 +7663,7 @@
         <v>500284</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" s="6">
         <v>40145</v>
       </c>
@@ -7681,7 +7681,7 @@
         <v>412036</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" s="6">
         <v>40152</v>
       </c>
@@ -7699,7 +7699,7 @@
         <v>491440</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" s="6">
         <v>40159</v>
       </c>
@@ -7717,7 +7717,7 @@
         <v>464948</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" s="6">
         <v>40166</v>
       </c>
@@ -7735,7 +7735,7 @@
         <v>481426</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52" s="6">
         <v>40173</v>
       </c>
@@ -7753,7 +7753,7 @@
         <v>339702</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53" s="6">
         <v>40180</v>
       </c>
@@ -7771,7 +7771,7 @@
         <v>376455</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" s="6">
         <v>40187</v>
       </c>
@@ -7789,7 +7789,7 @@
         <v>433584</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55" s="6">
         <v>40194</v>
       </c>
@@ -7807,7 +7807,7 @@
         <v>465758</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56" s="6">
         <v>40201</v>
       </c>
@@ -7825,7 +7825,7 @@
         <v>478227</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57" s="6">
         <v>40208</v>
       </c>
@@ -7843,7 +7843,7 @@
         <v>482390</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58" s="6">
         <v>40215</v>
       </c>
@@ -7861,7 +7861,7 @@
         <v>469221</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59" s="6">
         <v>40222</v>
       </c>
@@ -7879,7 +7879,7 @@
         <v>450177</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60" s="6">
         <v>40229</v>
       </c>
@@ -7897,7 +7897,7 @@
         <v>474203</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61" s="6">
         <v>40236</v>
       </c>
@@ -7915,7 +7915,7 @@
         <v>496078</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62" s="6">
         <v>40243</v>
       </c>
@@ -7933,7 +7933,7 @@
         <v>497456</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63" s="6">
         <v>40250</v>
       </c>
@@ -7951,7 +7951,7 @@
         <v>491463</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64" s="6">
         <v>40257</v>
       </c>
@@ -7969,7 +7969,7 @@
         <v>488939</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A65" s="6">
         <v>40264</v>
       </c>
@@ -7987,7 +7987,7 @@
         <v>504028</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66" s="6">
         <v>40271</v>
       </c>
@@ -8020,7 +8020,7 @@
         <v>486474</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67" s="6">
         <v>40278</v>
       </c>
@@ -8038,7 +8038,7 @@
         <v>492044</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68" s="6">
         <v>40285</v>
       </c>
@@ -8056,7 +8056,7 @@
         <v>506502</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A69" s="6">
         <v>40292</v>
       </c>
@@ -8074,7 +8074,7 @@
         <v>510565</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A70" s="6">
         <v>40299</v>
       </c>
@@ -8092,7 +8092,7 @@
         <v>508731</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A71" s="6">
         <v>40306</v>
       </c>
@@ -8110,7 +8110,7 @@
         <v>497714</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A72" s="6">
         <v>40313</v>
       </c>
@@ -8128,7 +8128,7 @@
         <v>508469</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A73" s="6">
         <v>40320</v>
       </c>
@@ -8146,7 +8146,7 @@
         <v>503232</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74" s="6">
         <v>40327</v>
       </c>
@@ -8164,7 +8164,7 @@
         <v>511776</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75" s="6">
         <v>40334</v>
       </c>
@@ -8182,7 +8182,7 @@
         <v>462009</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A76" s="6">
         <v>40341</v>
       </c>
@@ -8200,7 +8200,7 @@
         <v>512048</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A77" s="6">
         <v>40348</v>
       </c>
@@ -8218,7 +8218,7 @@
         <v>512898</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A78" s="6">
         <v>40355</v>
       </c>
@@ -8236,7 +8236,7 @@
         <v>511945</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A79" s="6">
         <v>40362</v>
       </c>
@@ -8254,7 +8254,7 @@
         <v>518063</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A80" s="6">
         <v>40369</v>
       </c>
@@ -8272,7 +8272,7 @@
         <v>445917</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A81" s="6">
         <v>40376</v>
       </c>
@@ -8290,7 +8290,7 @@
         <v>509860</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A82" s="6">
         <v>40383</v>
       </c>
@@ -8308,7 +8308,7 @@
         <v>517297</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A83" s="6">
         <v>40390</v>
       </c>
@@ -8326,7 +8326,7 @@
         <v>533187</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A84" s="6">
         <v>40397</v>
       </c>
@@ -8344,7 +8344,7 @@
         <v>515715</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A85" s="6">
         <v>40404</v>
       </c>
@@ -8362,7 +8362,7 @@
         <v>529715</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A86" s="6">
         <v>40411</v>
       </c>
@@ -8380,7 +8380,7 @@
         <v>533038</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A87" s="6">
         <v>40418</v>
       </c>
@@ -8398,7 +8398,7 @@
         <v>539552</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A88" s="6">
         <v>40425</v>
       </c>
@@ -8416,7 +8416,7 @@
         <v>542006</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A89" s="6">
         <v>40432</v>
       </c>
@@ -8434,7 +8434,7 @@
         <v>484380</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A90" s="6">
         <v>40439</v>
       </c>
@@ -8452,7 +8452,7 @@
         <v>544692</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A91" s="6">
         <v>40446</v>
       </c>
@@ -8470,7 +8470,7 @@
         <v>542075</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A92" s="6">
         <v>40453</v>
       </c>
@@ -8488,7 +8488,7 @@
         <v>539646</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A93" s="6">
         <v>40460</v>
       </c>
@@ -8506,7 +8506,7 @@
         <v>533301</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A94" s="6">
         <v>40467</v>
       </c>
@@ -8524,7 +8524,7 @@
         <v>540844</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A95" s="6">
         <v>40474</v>
       </c>
@@ -8542,7 +8542,7 @@
         <v>538461</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A96" s="6">
         <v>40481</v>
       </c>
@@ -8560,7 +8560,7 @@
         <v>525601</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A97" s="6">
         <v>40488</v>
       </c>
@@ -8578,7 +8578,7 @@
         <v>519134</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A98" s="6">
         <v>40495</v>
       </c>
@@ -8596,7 +8596,7 @@
         <v>530157</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A99" s="6">
         <v>40502</v>
       </c>
@@ -8614,7 +8614,7 @@
         <v>533989</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A100" s="6">
         <v>40509</v>
       </c>
@@ -8632,7 +8632,7 @@
         <v>437911</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A101" s="6">
         <v>40516</v>
       </c>
@@ -8650,7 +8650,7 @@
         <v>539405</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A102" s="9">
         <v>40523</v>
       </c>
@@ -8668,7 +8668,7 @@
         <v>520326</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A103" s="9">
         <v>40530</v>
       </c>
@@ -8686,7 +8686,7 @@
         <v>491896</v>
       </c>
     </row>
-    <row r="104" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A104" s="9">
         <v>40537</v>
       </c>
@@ -8704,7 +8704,7 @@
         <v>433347</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A105" s="9">
         <v>40544</v>
       </c>
@@ -8722,7 +8722,7 @@
         <v>406967</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A106" s="9">
         <v>40551</v>
       </c>
@@ -8740,7 +8740,7 @@
         <v>498773</v>
       </c>
     </row>
-    <row r="107" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A107" s="9">
         <v>40558</v>
       </c>
@@ -8758,7 +8758,7 @@
         <v>496473</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A108" s="9">
         <v>40565</v>
       </c>
@@ -8776,7 +8776,7 @@
         <v>496043</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A109" s="9">
         <v>40572</v>
       </c>
@@ -8794,7 +8794,7 @@
         <v>513889</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A110" s="9">
         <v>40579</v>
       </c>
@@ -8812,7 +8812,7 @@
         <v>465931</v>
       </c>
     </row>
-    <row r="111" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A111" s="9">
         <v>40586</v>
       </c>
@@ -8830,7 +8830,7 @@
         <v>502078</v>
       </c>
     </row>
-    <row r="112" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A112" s="9">
         <v>40593</v>
       </c>
@@ -8848,7 +8848,7 @@
         <v>530973</v>
       </c>
     </row>
-    <row r="113" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A113" s="9">
         <v>40600</v>
       </c>
@@ -8866,7 +8866,7 @@
         <v>516841</v>
       </c>
     </row>
-    <row r="114" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A114" s="9">
         <v>40607</v>
       </c>
@@ -8884,7 +8884,7 @@
         <v>515296</v>
       </c>
     </row>
-    <row r="115" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A115" s="9">
         <v>40614</v>
       </c>
@@ -8902,7 +8902,7 @@
         <v>508992</v>
       </c>
     </row>
-    <row r="116" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A116" s="9">
         <v>40621</v>
       </c>
@@ -8920,7 +8920,7 @@
         <v>516560</v>
       </c>
     </row>
-    <row r="117" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A117" s="9">
         <v>40628</v>
       </c>
@@ -8938,7 +8938,7 @@
         <v>522937</v>
       </c>
     </row>
-    <row r="118" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A118" s="9">
         <v>40635</v>
       </c>
@@ -8956,7 +8956,7 @@
         <v>540213</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A119" s="9">
         <v>40642</v>
       </c>
@@ -8974,7 +8974,7 @@
         <v>522511</v>
       </c>
     </row>
-    <row r="120" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A120" s="9">
         <v>40649</v>
       </c>
@@ -8992,7 +8992,7 @@
         <v>525886</v>
       </c>
     </row>
-    <row r="121" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A121" s="9">
         <v>40656</v>
       </c>
@@ -9010,7 +9010,7 @@
         <v>518374</v>
       </c>
     </row>
-    <row r="122" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A122" s="9">
         <v>40663</v>
       </c>
@@ -9028,7 +9028,7 @@
         <v>525024</v>
       </c>
     </row>
-    <row r="123" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A123" s="9">
         <v>40670</v>
       </c>
@@ -9046,7 +9046,7 @@
         <v>514038</v>
       </c>
     </row>
-    <row r="124" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A124" s="9">
         <v>40677</v>
       </c>
@@ -9064,7 +9064,7 @@
         <v>526146</v>
       </c>
     </row>
-    <row r="125" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A125" s="9">
         <v>40684</v>
       </c>
@@ -9082,7 +9082,7 @@
         <v>529383</v>
       </c>
     </row>
-    <row r="126" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A126" s="11">
         <v>40691</v>
       </c>
@@ -9100,7 +9100,7 @@
         <v>522717</v>
       </c>
     </row>
-    <row r="127" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A127" s="9">
         <v>40698</v>
       </c>
@@ -9118,7 +9118,7 @@
         <v>479149</v>
       </c>
     </row>
-    <row r="128" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A128" s="9">
         <v>40705</v>
       </c>
@@ -9136,7 +9136,7 @@
         <v>527603</v>
       </c>
     </row>
-    <row r="129" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A129" s="9">
         <v>40712</v>
       </c>
@@ -9154,7 +9154,7 @@
         <v>531992</v>
       </c>
     </row>
-    <row r="130" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A130" s="9">
         <v>40719</v>
       </c>
@@ -9187,7 +9187,7 @@
         <v>519337</v>
       </c>
     </row>
-    <row r="131" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A131" s="9">
         <v>40726</v>
       </c>
@@ -9205,7 +9205,7 @@
         <v>522931</v>
       </c>
     </row>
-    <row r="132" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A132" s="9">
         <v>40733</v>
       </c>
@@ -9223,7 +9223,7 @@
         <v>438193</v>
       </c>
     </row>
-    <row r="133" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A133" s="9">
         <v>40740</v>
       </c>
@@ -9241,7 +9241,7 @@
         <v>511711</v>
       </c>
     </row>
-    <row r="134" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A134" s="9">
         <v>40747</v>
       </c>
@@ -9259,7 +9259,7 @@
         <v>524090</v>
       </c>
     </row>
-    <row r="135" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A135" s="9">
         <v>40754</v>
       </c>
@@ -9277,7 +9277,7 @@
         <v>533337</v>
       </c>
     </row>
-    <row r="136" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A136" s="9">
         <v>40761</v>
       </c>
@@ -9295,7 +9295,7 @@
         <v>522889</v>
       </c>
     </row>
-    <row r="137" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A137" s="9">
         <v>40768</v>
       </c>
@@ -9313,7 +9313,7 @@
         <v>527864</v>
       </c>
     </row>
-    <row r="138" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A138" s="9">
         <v>40775</v>
       </c>
@@ -9331,7 +9331,7 @@
         <v>539201</v>
       </c>
     </row>
-    <row r="139" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A139" s="9">
         <v>40782</v>
       </c>
@@ -9349,7 +9349,7 @@
         <v>535994</v>
       </c>
     </row>
-    <row r="140" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A140" s="9">
         <v>40789</v>
       </c>
@@ -9367,7 +9367,7 @@
         <v>537201</v>
       </c>
     </row>
-    <row r="141" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A141" s="9">
         <v>40796</v>
       </c>
@@ -9385,7 +9385,7 @@
         <v>486472</v>
       </c>
     </row>
-    <row r="142" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A142" s="9">
         <v>40803</v>
       </c>
@@ -9403,7 +9403,7 @@
         <v>542164</v>
       </c>
     </row>
-    <row r="143" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A143" s="9">
         <v>40810</v>
       </c>
@@ -9421,7 +9421,7 @@
         <v>553535</v>
       </c>
     </row>
-    <row r="144" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A144" s="9">
         <v>40817</v>
       </c>
@@ -9439,7 +9439,7 @@
         <v>563034</v>
       </c>
     </row>
-    <row r="145" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A145" s="9">
         <v>40824</v>
       </c>
@@ -9457,7 +9457,7 @@
         <v>544499</v>
       </c>
     </row>
-    <row r="146" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A146" s="9">
         <v>40831</v>
       </c>
@@ -9475,7 +9475,7 @@
         <v>547752</v>
       </c>
     </row>
-    <row r="147" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A147" s="9">
         <v>40838</v>
       </c>
@@ -9493,7 +9493,7 @@
         <v>547268</v>
       </c>
     </row>
-    <row r="148" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A148" s="9">
         <v>40845</v>
       </c>
@@ -9511,7 +9511,7 @@
         <v>551674</v>
       </c>
     </row>
-    <row r="149" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A149" s="9">
         <v>40852</v>
       </c>
@@ -9529,7 +9529,7 @@
         <v>537645</v>
       </c>
     </row>
-    <row r="150" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A150" s="9">
         <v>40859</v>
       </c>
@@ -9547,7 +9547,7 @@
         <v>544563</v>
       </c>
     </row>
-    <row r="151" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A151" s="11">
         <v>40866</v>
       </c>
@@ -9565,7 +9565,7 @@
         <v>545153</v>
       </c>
     </row>
-    <row r="152" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A152" s="9">
         <v>40873</v>
       </c>
@@ -9583,7 +9583,7 @@
         <v>456170</v>
       </c>
     </row>
-    <row r="153" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A153" s="9">
         <v>40880</v>
       </c>
@@ -9601,7 +9601,7 @@
         <v>555353</v>
       </c>
     </row>
-    <row r="154" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A154" s="9">
         <v>40887</v>
       </c>
@@ -9619,7 +9619,7 @@
         <v>538299</v>
       </c>
     </row>
-    <row r="155" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A155" s="9">
         <v>40894</v>
       </c>
@@ -9637,7 +9637,7 @@
         <v>537699</v>
       </c>
     </row>
-    <row r="156" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A156" s="9">
         <v>40901</v>
       </c>
@@ -9655,7 +9655,7 @@
         <v>505089</v>
       </c>
     </row>
-    <row r="157" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A157" s="9">
         <v>40908</v>
       </c>
@@ -9673,7 +9673,7 @@
         <v>426883</v>
       </c>
     </row>
-    <row r="158" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A158" s="9">
         <v>40915</v>
       </c>
@@ -9691,7 +9691,7 @@
         <v>468674</v>
       </c>
     </row>
-    <row r="159" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A159" s="9">
         <v>40922</v>
       </c>
@@ -9709,7 +9709,7 @@
         <v>527651</v>
       </c>
     </row>
-    <row r="160" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A160" s="9">
         <v>40929</v>
       </c>
@@ -9727,7 +9727,7 @@
         <v>507440</v>
       </c>
     </row>
-    <row r="161" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A161" s="9">
         <v>40936</v>
       </c>
@@ -9745,7 +9745,7 @@
         <v>518682</v>
       </c>
     </row>
-    <row r="162" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A162" s="9">
         <v>40943</v>
       </c>
@@ -9763,7 +9763,7 @@
         <v>517136</v>
       </c>
     </row>
-    <row r="163" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A163" s="9">
         <v>40950</v>
       </c>
@@ -9781,7 +9781,7 @@
         <v>506708</v>
       </c>
     </row>
-    <row r="164" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A164" s="9">
         <v>40957</v>
       </c>
@@ -9799,7 +9799,7 @@
         <v>502992</v>
       </c>
     </row>
-    <row r="165" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A165" s="9">
         <v>40964</v>
       </c>
@@ -9817,7 +9817,7 @@
         <v>496046</v>
       </c>
     </row>
-    <row r="166" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A166" s="9">
         <v>40971</v>
       </c>
@@ -9835,7 +9835,7 @@
         <v>510568</v>
       </c>
     </row>
-    <row r="167" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A167" s="9">
         <v>40978</v>
       </c>
@@ -9853,7 +9853,7 @@
         <v>504767</v>
       </c>
     </row>
-    <row r="168" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A168" s="9">
         <v>40985</v>
       </c>
@@ -9871,7 +9871,7 @@
         <v>505558</v>
       </c>
     </row>
-    <row r="169" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A169" s="9">
         <v>40992</v>
       </c>
@@ -9889,7 +9889,7 @@
         <v>510794</v>
       </c>
     </row>
-    <row r="170" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A170" s="9">
         <v>40999</v>
       </c>
@@ -9907,7 +9907,7 @@
         <v>529734</v>
       </c>
     </row>
-    <row r="171" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A171" s="9">
         <v>41006</v>
       </c>
@@ -9925,7 +9925,7 @@
         <v>502127</v>
       </c>
     </row>
-    <row r="172" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A172" s="9">
         <v>41013</v>
       </c>
@@ -9943,7 +9943,7 @@
         <v>510946</v>
       </c>
     </row>
-    <row r="173" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A173" s="9">
         <v>41020</v>
       </c>
@@ -9961,7 +9961,7 @@
         <v>521538</v>
       </c>
     </row>
-    <row r="174" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A174" s="9">
         <v>41027</v>
       </c>
@@ -9979,7 +9979,7 @@
         <v>525445</v>
       </c>
     </row>
-    <row r="175" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A175" s="9">
         <v>41034</v>
       </c>
@@ -9997,7 +9997,7 @@
         <v>515167</v>
       </c>
     </row>
-    <row r="176" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A176" s="11">
         <v>41041</v>
       </c>
@@ -10015,7 +10015,7 @@
         <v>518043</v>
       </c>
     </row>
-    <row r="177" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A177" s="9">
         <v>41048</v>
       </c>
@@ -10033,7 +10033,7 @@
         <v>522229</v>
       </c>
     </row>
-    <row r="178" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A178" s="9">
         <v>41055</v>
       </c>
@@ -10051,7 +10051,7 @@
         <v>536107</v>
       </c>
     </row>
-    <row r="179" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A179" s="9">
         <v>41062</v>
       </c>
@@ -10069,7 +10069,7 @@
         <v>479118</v>
       </c>
     </row>
-    <row r="180" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A180" s="9">
         <v>41069</v>
       </c>
@@ -10087,7 +10087,7 @@
         <v>531835</v>
       </c>
     </row>
-    <row r="181" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A181" s="9">
         <v>41076</v>
       </c>
@@ -10105,7 +10105,7 @@
         <v>537011</v>
       </c>
     </row>
-    <row r="182" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A182" s="9">
         <v>41083</v>
       </c>
@@ -10123,7 +10123,7 @@
         <v>534858</v>
       </c>
     </row>
-    <row r="183" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A183" s="9">
         <v>41090</v>
       </c>
@@ -10141,7 +10141,7 @@
         <v>532131</v>
       </c>
     </row>
-    <row r="184" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A184" s="9">
         <v>41097</v>
       </c>
@@ -10159,7 +10159,7 @@
         <v>446518</v>
       </c>
     </row>
-    <row r="185" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A185" s="9">
         <v>41104</v>
       </c>
@@ -10177,7 +10177,7 @@
         <v>532071</v>
       </c>
     </row>
-    <row r="186" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A186" s="9">
         <v>41111</v>
       </c>
@@ -10195,7 +10195,7 @@
         <v>532729</v>
       </c>
     </row>
-    <row r="187" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A187" s="9">
         <v>41118</v>
       </c>
@@ -10213,7 +10213,7 @@
         <v>538486</v>
       </c>
     </row>
-    <row r="188" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A188" s="9">
         <v>41125</v>
       </c>
@@ -10231,7 +10231,7 @@
         <v>531490</v>
       </c>
     </row>
-    <row r="189" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A189" s="9">
         <v>41132</v>
       </c>
@@ -10249,7 +10249,7 @@
         <v>532202</v>
       </c>
     </row>
-    <row r="190" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A190" s="9">
         <v>41139</v>
       </c>
@@ -10267,7 +10267,7 @@
         <v>541140</v>
       </c>
     </row>
-    <row r="191" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A191" s="9">
         <v>41146</v>
       </c>
@@ -10285,7 +10285,7 @@
         <v>545406</v>
       </c>
     </row>
-    <row r="192" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A192" s="9">
         <v>41153</v>
       </c>
@@ -10303,7 +10303,7 @@
         <v>541845</v>
       </c>
     </row>
-    <row r="193" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A193" s="9">
         <v>41160</v>
       </c>
@@ -10321,7 +10321,7 @@
         <v>486818</v>
       </c>
     </row>
-    <row r="194" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A194" s="9">
         <v>41167</v>
       </c>
@@ -10354,7 +10354,7 @@
         <v>543250</v>
       </c>
     </row>
-    <row r="195" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A195" s="9">
         <v>41174</v>
       </c>
@@ -10372,7 +10372,7 @@
         <v>542897</v>
       </c>
     </row>
-    <row r="196" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A196" s="9">
         <v>41181</v>
       </c>
@@ -10390,7 +10390,7 @@
         <v>552468</v>
       </c>
     </row>
-    <row r="197" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A197" s="9">
         <v>41188</v>
       </c>
@@ -10408,7 +10408,7 @@
         <v>534553</v>
       </c>
     </row>
-    <row r="198" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A198" s="9">
         <v>41195</v>
       </c>
@@ -10426,7 +10426,7 @@
         <v>535915</v>
       </c>
     </row>
-    <row r="199" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A199" s="9">
         <v>41202</v>
       </c>
@@ -10444,7 +10444,7 @@
         <v>542674</v>
       </c>
     </row>
-    <row r="200" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A200" s="9">
         <v>41209</v>
       </c>
@@ -10462,7 +10462,7 @@
         <v>540290</v>
       </c>
     </row>
-    <row r="201" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A201" s="11">
         <v>41216</v>
       </c>
@@ -10480,7 +10480,7 @@
         <v>502697</v>
       </c>
     </row>
-    <row r="202" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A202" s="9">
         <v>41223</v>
       </c>
@@ -10498,7 +10498,7 @@
         <v>532945</v>
       </c>
     </row>
-    <row r="203" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A203" s="9">
         <v>41230</v>
       </c>
@@ -10516,7 +10516,7 @@
         <v>537832</v>
       </c>
     </row>
-    <row r="204" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A204" s="9">
         <v>41237</v>
       </c>
@@ -10534,7 +10534,7 @@
         <v>447469</v>
       </c>
     </row>
-    <row r="205" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A205" s="9">
         <v>41244</v>
       </c>
@@ -10552,7 +10552,7 @@
         <v>547119</v>
       </c>
     </row>
-    <row r="206" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A206" s="9">
         <v>41251</v>
       </c>
@@ -10570,7 +10570,7 @@
         <v>532304</v>
       </c>
     </row>
-    <row r="207" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A207" s="9">
         <v>41258</v>
       </c>
@@ -10588,7 +10588,7 @@
         <v>544625</v>
       </c>
     </row>
-    <row r="208" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A208" s="9">
         <v>41265</v>
       </c>
@@ -10606,7 +10606,7 @@
         <v>530342</v>
       </c>
     </row>
-    <row r="209" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A209" s="9">
         <v>41272</v>
       </c>
@@ -10624,7 +10624,7 @@
         <v>367721</v>
       </c>
     </row>
-    <row r="210" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A210" s="9">
         <v>41279</v>
       </c>
@@ -10642,7 +10642,7 @@
         <v>419999</v>
       </c>
     </row>
-    <row r="211" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A211" s="9">
         <v>41286</v>
       </c>
@@ -10660,7 +10660,7 @@
         <v>532789</v>
       </c>
     </row>
-    <row r="212" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A212" s="9">
         <v>41293</v>
       </c>
@@ -10678,7 +10678,7 @@
         <v>526887</v>
       </c>
     </row>
-    <row r="213" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A213" s="9">
         <v>41300</v>
       </c>
@@ -10696,7 +10696,7 @@
         <v>504628</v>
       </c>
     </row>
-    <row r="214" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A214" s="9">
         <v>41307</v>
       </c>
@@ -10714,7 +10714,7 @@
         <v>523931</v>
       </c>
     </row>
-    <row r="215" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A215" s="9">
         <v>41314</v>
       </c>
@@ -10732,7 +10732,7 @@
         <v>518048</v>
       </c>
     </row>
-    <row r="216" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A216" s="9">
         <v>41321</v>
       </c>
@@ -10750,7 +10750,7 @@
         <v>529674</v>
       </c>
     </row>
-    <row r="217" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A217" s="9">
         <v>41328</v>
       </c>
@@ -10768,7 +10768,7 @@
         <v>516142</v>
       </c>
     </row>
-    <row r="218" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A218" s="9">
         <v>41335</v>
       </c>
@@ -10786,7 +10786,7 @@
         <v>533057</v>
       </c>
     </row>
-    <row r="219" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A219" s="9">
         <v>41342</v>
       </c>
@@ -10804,7 +10804,7 @@
         <v>511872</v>
       </c>
     </row>
-    <row r="220" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A220" s="9">
         <v>41349</v>
       </c>
@@ -10822,7 +10822,7 @@
         <v>509430</v>
       </c>
     </row>
-    <row r="221" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A221" s="9">
         <v>41356</v>
       </c>
@@ -10840,7 +10840,7 @@
         <v>514379</v>
       </c>
     </row>
-    <row r="222" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A222" s="9">
         <v>41363</v>
       </c>
@@ -10858,7 +10858,7 @@
         <v>514954</v>
       </c>
     </row>
-    <row r="223" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A223" s="9">
         <v>41370</v>
       </c>
@@ -10876,7 +10876,7 @@
         <v>512396</v>
       </c>
     </row>
-    <row r="224" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A224" s="9">
         <v>41377</v>
       </c>
@@ -10894,7 +10894,7 @@
         <v>517662</v>
       </c>
     </row>
-    <row r="225" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A225" s="9">
         <v>41384</v>
       </c>
@@ -10912,7 +10912,7 @@
         <v>517360</v>
       </c>
     </row>
-    <row r="226" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A226" s="11">
         <v>41391</v>
       </c>
@@ -10930,7 +10930,7 @@
         <v>523207</v>
       </c>
     </row>
-    <row r="227" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A227" s="9">
         <v>41398</v>
       </c>
@@ -10948,7 +10948,7 @@
         <v>529594</v>
       </c>
     </row>
-    <row r="228" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A228" s="9">
         <v>41405</v>
       </c>
@@ -10966,7 +10966,7 @@
         <v>529252</v>
       </c>
     </row>
-    <row r="229" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A229" s="9">
         <v>41412</v>
       </c>
@@ -10984,7 +10984,7 @@
         <v>535835</v>
       </c>
     </row>
-    <row r="230" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A230" s="9">
         <v>41419</v>
       </c>
@@ -11002,7 +11002,7 @@
         <v>529937</v>
       </c>
     </row>
-    <row r="231" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A231" s="9">
         <v>41426</v>
       </c>
@@ -11020,7 +11020,7 @@
         <v>491082</v>
       </c>
     </row>
-    <row r="232" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A232" s="9">
         <v>41433</v>
       </c>
@@ -11038,7 +11038,7 @@
         <v>530890</v>
       </c>
     </row>
-    <row r="233" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A233" s="9">
         <v>41440</v>
       </c>
@@ -11056,7 +11056,7 @@
         <v>543145</v>
       </c>
     </row>
-    <row r="234" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A234" s="9">
         <v>41447</v>
       </c>
@@ -11074,7 +11074,7 @@
         <v>541031</v>
       </c>
     </row>
-    <row r="235" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A235" s="9">
         <v>41454</v>
       </c>
@@ -11092,7 +11092,7 @@
         <v>531040</v>
       </c>
     </row>
-    <row r="236" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A236" s="9">
         <v>41461</v>
       </c>
@@ -11110,7 +11110,7 @@
         <v>453493</v>
       </c>
     </row>
-    <row r="237" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A237" s="9">
         <v>41468</v>
       </c>
@@ -11128,7 +11128,7 @@
         <v>525333</v>
       </c>
     </row>
-    <row r="238" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A238" s="9">
         <v>41475</v>
       </c>
@@ -11146,7 +11146,7 @@
         <v>531357</v>
       </c>
     </row>
-    <row r="239" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A239" s="9">
         <v>41482</v>
       </c>
@@ -11164,7 +11164,7 @@
         <v>551911</v>
       </c>
     </row>
-    <row r="240" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A240" s="9">
         <v>41489</v>
       </c>
@@ -11182,7 +11182,7 @@
         <v>542396</v>
       </c>
     </row>
-    <row r="241" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A241" s="9">
         <v>41496</v>
       </c>
@@ -11200,7 +11200,7 @@
         <v>546772</v>
       </c>
     </row>
-    <row r="242" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A242" s="9">
         <v>41503</v>
       </c>
@@ -11218,7 +11218,7 @@
         <v>552359</v>
       </c>
     </row>
-    <row r="243" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A243" s="9">
         <v>41510</v>
       </c>
@@ -11236,7 +11236,7 @@
         <v>548969</v>
       </c>
     </row>
-    <row r="244" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A244" s="9">
         <v>41517</v>
       </c>
@@ -11254,7 +11254,7 @@
         <v>561698</v>
       </c>
     </row>
-    <row r="245" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A245" s="9">
         <v>41524</v>
       </c>
@@ -11272,7 +11272,7 @@
         <v>507493</v>
       </c>
     </row>
-    <row r="246" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A246" s="9">
         <v>41531</v>
       </c>
@@ -11290,7 +11290,7 @@
         <v>562094</v>
       </c>
     </row>
-    <row r="247" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A247" s="9">
         <v>41538</v>
       </c>
@@ -11308,7 +11308,7 @@
         <v>551057</v>
       </c>
     </row>
-    <row r="248" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A248" s="9">
         <v>41545</v>
       </c>
@@ -11326,7 +11326,7 @@
         <v>566662</v>
       </c>
     </row>
-    <row r="249" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A249" s="9">
         <v>41552</v>
       </c>
@@ -11344,7 +11344,7 @@
         <v>545708</v>
       </c>
     </row>
-    <row r="250" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A250" s="9">
         <v>41559</v>
       </c>
@@ -11362,7 +11362,7 @@
         <v>546211</v>
       </c>
     </row>
-    <row r="251" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A251" s="11">
         <v>41566</v>
       </c>
@@ -11380,7 +11380,7 @@
         <v>553943</v>
       </c>
     </row>
-    <row r="252" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A252" s="9">
         <v>41573</v>
       </c>
@@ -11398,7 +11398,7 @@
         <v>558686</v>
       </c>
     </row>
-    <row r="253" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A253" s="9">
         <v>41580</v>
       </c>
@@ -11416,7 +11416,7 @@
         <v>556662</v>
       </c>
     </row>
-    <row r="254" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A254" s="9">
         <v>41587</v>
       </c>
@@ -11434,7 +11434,7 @@
         <v>562840</v>
       </c>
     </row>
-    <row r="255" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A255" s="9">
         <v>41594</v>
       </c>
@@ -11452,7 +11452,7 @@
         <v>562206</v>
       </c>
     </row>
-    <row r="256" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A256" s="9">
         <v>41601</v>
       </c>
@@ -11470,7 +11470,7 @@
         <v>564340</v>
       </c>
     </row>
-    <row r="257" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A257" s="9">
         <v>41608</v>
       </c>
@@ -11488,7 +11488,7 @@
         <v>463516</v>
       </c>
     </row>
-    <row r="258" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A258" s="9">
         <v>41615</v>
       </c>
@@ -11521,7 +11521,7 @@
         <v>541978</v>
       </c>
     </row>
-    <row r="259" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A259" s="9">
         <v>41622</v>
       </c>
@@ -11539,7 +11539,7 @@
         <v>546825</v>
       </c>
     </row>
-    <row r="260" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A260" s="9">
         <v>41629</v>
       </c>
@@ -11557,7 +11557,7 @@
         <v>544984</v>
       </c>
     </row>
-    <row r="261" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A261" s="9">
         <v>41636</v>
       </c>
@@ -11575,7 +11575,7 @@
         <v>403329</v>
       </c>
     </row>
-    <row r="262" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A262" s="9">
         <v>41643</v>
       </c>
@@ -11593,7 +11593,7 @@
         <v>433724</v>
       </c>
     </row>
-    <row r="263" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A263" s="9">
         <v>41650</v>
       </c>
@@ -11611,7 +11611,7 @@
         <v>492836</v>
       </c>
     </row>
-    <row r="264" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A264" s="9">
         <v>41657</v>
       </c>
@@ -11629,7 +11629,7 @@
         <v>557253</v>
       </c>
     </row>
-    <row r="265" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A265" s="9">
         <v>41664</v>
       </c>
@@ -11647,7 +11647,7 @@
         <v>526644</v>
       </c>
     </row>
-    <row r="266" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A266" s="9">
         <v>41671</v>
       </c>
@@ -11665,7 +11665,7 @@
         <v>518012</v>
       </c>
     </row>
-    <row r="267" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A267" s="9">
         <v>41678</v>
       </c>
@@ -11683,7 +11683,7 @@
         <v>507368</v>
       </c>
     </row>
-    <row r="268" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A268" s="9">
         <v>41685</v>
       </c>
@@ -11701,7 +11701,7 @@
         <v>507257</v>
       </c>
     </row>
-    <row r="269" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A269" s="9">
         <v>41692</v>
       </c>
@@ -11719,7 +11719,7 @@
         <v>535036</v>
       </c>
     </row>
-    <row r="270" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A270" s="9">
         <v>41699</v>
       </c>
@@ -11737,7 +11737,7 @@
         <v>545004</v>
       </c>
     </row>
-    <row r="271" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A271" s="9">
         <v>41706</v>
       </c>
@@ -11755,7 +11755,7 @@
         <v>518495</v>
       </c>
     </row>
-    <row r="272" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A272" s="9">
         <v>41713</v>
       </c>
@@ -11773,7 +11773,7 @@
         <v>545366</v>
       </c>
     </row>
-    <row r="273" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A273" s="9">
         <v>41720</v>
       </c>
@@ -11791,7 +11791,7 @@
         <v>552238</v>
       </c>
     </row>
-    <row r="274" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A274" s="9">
         <v>41727</v>
       </c>
@@ -11809,7 +11809,7 @@
         <v>566505</v>
       </c>
     </row>
-    <row r="275" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A275" s="9">
         <v>41734</v>
       </c>
@@ -11827,7 +11827,7 @@
         <v>557123</v>
       </c>
     </row>
-    <row r="276" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A276" s="11">
         <v>41741</v>
       </c>
@@ -11845,7 +11845,7 @@
         <v>559676</v>
       </c>
     </row>
-    <row r="277" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A277" s="9">
         <v>41748</v>
       </c>
@@ -11863,7 +11863,7 @@
         <v>549826</v>
       </c>
     </row>
-    <row r="278" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A278" s="9">
         <v>41755</v>
       </c>
@@ -11881,7 +11881,7 @@
         <v>566336</v>
       </c>
     </row>
-    <row r="279" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A279" s="9">
         <v>41762</v>
       </c>
@@ -11899,7 +11899,7 @@
         <v>564801</v>
       </c>
     </row>
-    <row r="280" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A280" s="9">
         <v>41769</v>
       </c>
@@ -11917,7 +11917,7 @@
         <v>564096</v>
       </c>
     </row>
-    <row r="281" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A281" s="9">
         <v>41783</v>
       </c>
@@ -11935,7 +11935,7 @@
         <v>570380</v>
       </c>
     </row>
-    <row r="282" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A282" s="9">
         <v>41790</v>
       </c>
@@ -11953,7 +11953,7 @@
         <v>531725</v>
       </c>
     </row>
-    <row r="283" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A283" s="9">
         <v>41797</v>
       </c>
@@ -11971,7 +11971,7 @@
         <v>562747</v>
       </c>
     </row>
-    <row r="284" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A284" s="9">
         <v>41804</v>
       </c>
@@ -11989,7 +11989,7 @@
         <v>565375</v>
       </c>
     </row>
-    <row r="285" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A285" s="9">
         <v>41811</v>
       </c>
@@ -12007,7 +12007,7 @@
         <v>563695</v>
       </c>
     </row>
-    <row r="286" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A286" s="9">
         <v>41818</v>
       </c>
@@ -12025,7 +12025,7 @@
         <v>563223</v>
       </c>
     </row>
-    <row r="287" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A287" s="9">
         <v>41825</v>
       </c>
@@ -12043,7 +12043,7 @@
         <v>497828</v>
       </c>
     </row>
-    <row r="288" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A288" s="9">
         <v>41832</v>
       </c>
@@ -12061,7 +12061,7 @@
         <v>546863</v>
       </c>
     </row>
-    <row r="289" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A289" s="9">
         <v>41839</v>
       </c>
@@ -12079,7 +12079,7 @@
         <v>566931</v>
       </c>
     </row>
-    <row r="290" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A290" s="9">
         <v>41846</v>
       </c>
@@ -12097,7 +12097,7 @@
         <v>571797</v>
       </c>
     </row>
-    <row r="291" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A291" s="9">
         <v>41853</v>
       </c>
@@ -12115,7 +12115,7 @@
         <v>574552</v>
       </c>
     </row>
-    <row r="292" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A292" s="9">
         <v>41860</v>
       </c>
@@ -12133,7 +12133,7 @@
         <v>567908</v>
       </c>
     </row>
-    <row r="293" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A293" s="9">
         <v>41867</v>
       </c>
@@ -12151,7 +12151,7 @@
         <v>574592</v>
       </c>
     </row>
-    <row r="294" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A294" s="9">
         <v>41874</v>
       </c>
@@ -12169,7 +12169,7 @@
         <v>566266</v>
       </c>
     </row>
-    <row r="295" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A295" s="9">
         <v>41881</v>
       </c>
@@ -12187,7 +12187,7 @@
         <v>579209</v>
       </c>
     </row>
-    <row r="296" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A296" s="9">
         <v>41888</v>
       </c>
@@ -12205,7 +12205,7 @@
         <v>525144</v>
       </c>
     </row>
-    <row r="297" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A297" s="9">
         <v>41895</v>
       </c>
@@ -12223,7 +12223,7 @@
         <v>579440</v>
       </c>
     </row>
-    <row r="298" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A298" s="9">
         <v>41902</v>
       </c>
@@ -12241,7 +12241,7 @@
         <v>581955</v>
       </c>
     </row>
-    <row r="299" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A299" s="9">
         <v>41909</v>
       </c>
@@ -12259,7 +12259,7 @@
         <v>576934</v>
       </c>
     </row>
-    <row r="300" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A300" s="9">
         <v>41916</v>
       </c>
@@ -12277,7 +12277,7 @@
         <v>576356</v>
       </c>
     </row>
-    <row r="301" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A301" s="11">
         <v>41923</v>
       </c>
@@ -12295,7 +12295,7 @@
         <v>571812</v>
       </c>
     </row>
-    <row r="302" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A302" s="9">
         <v>41930</v>
       </c>
@@ -12313,7 +12313,7 @@
         <v>569684</v>
       </c>
     </row>
-    <row r="303" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A303" s="9">
         <v>41937</v>
       </c>
@@ -12331,7 +12331,7 @@
         <v>586115</v>
       </c>
     </row>
-    <row r="304" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A304" s="9">
         <v>41944</v>
       </c>
@@ -12349,7 +12349,7 @@
         <v>585208</v>
       </c>
     </row>
-    <row r="305" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A305" s="9">
         <v>41951</v>
       </c>
@@ -12367,7 +12367,7 @@
         <v>568807</v>
       </c>
     </row>
-    <row r="306" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A306" s="9">
         <v>41958</v>
       </c>
@@ -12385,7 +12385,7 @@
         <v>570350</v>
       </c>
     </row>
-    <row r="307" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A307" s="9">
         <v>41965</v>
       </c>
@@ -12403,7 +12403,7 @@
         <v>565185</v>
       </c>
     </row>
-    <row r="308" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A308" s="9">
         <v>41972</v>
       </c>
@@ -12421,7 +12421,7 @@
         <v>492532</v>
       </c>
     </row>
-    <row r="309" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A309" s="9">
         <v>41979</v>
       </c>
@@ -12439,7 +12439,7 @@
         <v>580108</v>
       </c>
     </row>
-    <row r="310" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A310" s="9">
         <v>41986</v>
       </c>
@@ -12457,7 +12457,7 @@
         <v>592608</v>
       </c>
     </row>
-    <row r="311" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A311" s="9">
         <v>41993</v>
       </c>
@@ -12475,7 +12475,7 @@
         <v>580559</v>
       </c>
     </row>
-    <row r="312" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A312" s="9">
         <v>42000</v>
       </c>
@@ -12493,7 +12493,7 @@
         <v>433338</v>
       </c>
     </row>
-    <row r="313" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A313" s="9">
         <v>42007</v>
       </c>
@@ -12511,7 +12511,7 @@
         <v>446201</v>
       </c>
     </row>
-    <row r="314" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A314" s="9">
         <v>42014</v>
       </c>
@@ -12529,7 +12529,7 @@
         <v>517520</v>
       </c>
     </row>
-    <row r="315" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A315" s="9">
         <v>42021</v>
       </c>
@@ -12547,7 +12547,7 @@
         <v>551856</v>
       </c>
     </row>
-    <row r="316" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A316" s="9">
         <v>42028</v>
       </c>
@@ -12565,7 +12565,7 @@
         <v>548055</v>
       </c>
     </row>
-    <row r="317" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A317" s="9">
         <v>42035</v>
       </c>
@@ -12583,7 +12583,7 @@
         <v>548478</v>
       </c>
     </row>
-    <row r="318" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A318" s="9">
         <v>42042</v>
       </c>
@@ -12601,7 +12601,7 @@
         <v>511563</v>
       </c>
     </row>
-    <row r="319" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A319" s="9">
         <v>42049</v>
       </c>
@@ -12619,7 +12619,7 @@
         <v>525224</v>
       </c>
     </row>
-    <row r="320" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A320" s="9">
         <v>42056</v>
       </c>
@@ -12637,7 +12637,7 @@
         <v>473161</v>
       </c>
     </row>
-    <row r="321" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A321" s="9">
         <v>42063</v>
       </c>
@@ -12655,7 +12655,7 @@
         <v>508658</v>
       </c>
     </row>
-    <row r="322" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A322" s="9">
         <v>42070</v>
       </c>
@@ -12688,7 +12688,7 @@
         <v>522382</v>
       </c>
     </row>
-    <row r="323" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A323" s="9">
         <v>42077</v>
       </c>
@@ -12706,7 +12706,7 @@
         <v>553031</v>
       </c>
     </row>
-    <row r="324" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A324" s="9">
         <v>42084</v>
       </c>
@@ -12724,7 +12724,7 @@
         <v>562472</v>
       </c>
     </row>
-    <row r="325" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A325" s="9">
         <v>42091</v>
       </c>
@@ -12742,7 +12742,7 @@
         <v>563280</v>
       </c>
     </row>
-    <row r="326" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A326" s="11">
         <v>42098</v>
       </c>
@@ -12760,7 +12760,7 @@
         <v>549021</v>
       </c>
     </row>
-    <row r="327" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A327" s="9">
         <v>42105</v>
       </c>
@@ -12778,7 +12778,7 @@
         <v>557812</v>
       </c>
     </row>
-    <row r="328" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A328" s="9">
         <v>42112</v>
       </c>
@@ -12796,7 +12796,7 @@
         <v>556432</v>
       </c>
     </row>
-    <row r="329" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A329" s="9">
         <v>42119</v>
       </c>
@@ -12814,7 +12814,7 @@
         <v>557306</v>
       </c>
     </row>
-    <row r="330" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A330" s="9">
         <v>42126</v>
       </c>
@@ -12832,7 +12832,7 @@
         <v>565787</v>
       </c>
     </row>
-    <row r="331" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A331" s="9">
         <v>42133</v>
       </c>
@@ -12850,7 +12850,7 @@
         <v>551034</v>
       </c>
     </row>
-    <row r="332" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A332" s="9">
         <v>42140</v>
       </c>
@@ -12868,7 +12868,7 @@
         <v>549199</v>
       </c>
     </row>
-    <row r="333" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A333" s="9">
         <v>42147</v>
       </c>
@@ -12886,7 +12886,7 @@
         <v>554477</v>
       </c>
     </row>
-    <row r="334" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A334" s="9">
         <v>42154</v>
       </c>
@@ -12904,7 +12904,7 @@
         <v>505543</v>
       </c>
     </row>
-    <row r="335" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A335" s="9">
         <v>42161</v>
       </c>
@@ -12922,7 +12922,7 @@
         <v>550037</v>
       </c>
     </row>
-    <row r="336" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A336" s="9">
         <v>42168</v>
       </c>
@@ -12940,7 +12940,7 @@
         <v>554461</v>
       </c>
     </row>
-    <row r="337" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A337" s="9">
         <v>42175</v>
       </c>
@@ -12958,7 +12958,7 @@
         <v>550839</v>
       </c>
     </row>
-    <row r="338" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A338" s="9">
         <v>42182</v>
       </c>
@@ -12976,7 +12976,7 @@
         <v>547969</v>
       </c>
     </row>
-    <row r="339" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A339" s="9">
         <v>42189</v>
       </c>
@@ -12994,7 +12994,7 @@
         <v>506284</v>
       </c>
     </row>
-    <row r="340" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A340" s="9">
         <v>42196</v>
       </c>
@@ -13012,7 +13012,7 @@
         <v>534097</v>
       </c>
     </row>
-    <row r="341" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A341" s="9">
         <v>42203</v>
       </c>
@@ -13030,7 +13030,7 @@
         <v>551181</v>
       </c>
     </row>
-    <row r="342" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A342" s="9">
         <v>42210</v>
       </c>
@@ -13048,7 +13048,7 @@
         <v>557612</v>
       </c>
     </row>
-    <row r="343" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A343" s="9">
         <v>42217</v>
       </c>
@@ -13066,7 +13066,7 @@
         <v>559125</v>
       </c>
     </row>
-    <row r="344" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A344" s="9">
         <v>42224</v>
       </c>
@@ -13084,7 +13084,7 @@
         <v>562884</v>
       </c>
     </row>
-    <row r="345" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A345" s="9">
         <v>42238</v>
       </c>
@@ -13102,7 +13102,7 @@
         <v>567943</v>
       </c>
     </row>
-    <row r="346" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A346" s="9">
         <v>42245</v>
       </c>
@@ -13120,7 +13120,7 @@
         <v>575323</v>
       </c>
     </row>
-    <row r="347" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A347" s="9">
         <v>42252</v>
       </c>
@@ -13138,7 +13138,7 @@
         <v>567206</v>
       </c>
     </row>
-    <row r="348" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A348" s="9">
         <v>42259</v>
       </c>
@@ -13156,7 +13156,7 @@
         <v>510797</v>
       </c>
     </row>
-    <row r="349" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A349" s="9">
         <v>42266</v>
       </c>
@@ -13174,7 +13174,7 @@
         <v>566734</v>
       </c>
     </row>
-    <row r="350" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A350" s="9">
         <v>42273</v>
       </c>
@@ -13192,7 +13192,7 @@
         <v>566700</v>
       </c>
     </row>
-    <row r="351" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A351" s="11">
         <v>42280</v>
       </c>
@@ -13210,7 +13210,7 @@
         <v>572293</v>
       </c>
     </row>
-    <row r="352" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A352" s="9">
         <v>42287</v>
       </c>
@@ -13228,7 +13228,7 @@
         <v>556233</v>
       </c>
     </row>
-    <row r="353" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A353" s="9">
         <v>42294</v>
       </c>
@@ -13246,7 +13246,7 @@
         <v>554696</v>
       </c>
     </row>
-    <row r="354" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A354" s="9">
         <v>42301</v>
       </c>
@@ -13264,7 +13264,7 @@
         <v>553144</v>
       </c>
     </row>
-    <row r="355" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A355" s="9">
         <v>42308</v>
       </c>
@@ -13282,7 +13282,7 @@
         <v>549707</v>
       </c>
     </row>
-    <row r="356" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A356" s="9">
         <v>42315</v>
       </c>
@@ -13300,7 +13300,7 @@
         <v>539165</v>
       </c>
     </row>
-    <row r="357" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A357" s="9">
         <v>42322</v>
       </c>
@@ -13318,7 +13318,7 @@
         <v>543681</v>
       </c>
     </row>
-    <row r="358" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A358" s="9">
         <v>42336</v>
       </c>
@@ -13336,7 +13336,7 @@
         <v>450389</v>
       </c>
     </row>
-    <row r="359" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A359" s="9">
         <v>42343</v>
       </c>
@@ -13354,7 +13354,7 @@
         <v>542050</v>
       </c>
     </row>
-    <row r="360" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A360" s="9">
         <v>42350</v>
       </c>
@@ -13372,7 +13372,7 @@
         <v>544975</v>
       </c>
     </row>
-    <row r="361" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A361" s="9">
         <v>42357</v>
       </c>
@@ -13390,7 +13390,7 @@
         <v>525555</v>
       </c>
     </row>
-    <row r="362" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A362" s="9">
         <v>42364</v>
       </c>
@@ -13408,7 +13408,7 @@
         <v>391107</v>
       </c>
     </row>
-    <row r="363" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A363" s="9">
         <v>42371</v>
       </c>
@@ -13426,7 +13426,7 @@
         <v>395663</v>
       </c>
     </row>
-    <row r="364" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A364" s="9">
         <v>42378</v>
       </c>
@@ -13444,7 +13444,7 @@
         <v>498160</v>
       </c>
     </row>
-    <row r="365" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A365" s="9">
         <v>42385</v>
       </c>
@@ -13462,7 +13462,7 @@
         <v>506433</v>
       </c>
     </row>
-    <row r="366" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A366" s="9">
         <v>42392</v>
       </c>
@@ -13480,7 +13480,7 @@
         <v>490324</v>
       </c>
     </row>
-    <row r="367" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A367" s="9">
         <v>42399</v>
       </c>
@@ -13498,7 +13498,7 @@
         <v>512746</v>
       </c>
     </row>
-    <row r="368" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A368" s="9">
         <v>42406</v>
       </c>
@@ -13516,7 +13516,7 @@
         <v>504510</v>
       </c>
     </row>
-    <row r="369" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A369" s="9">
         <v>42413</v>
       </c>
@@ -13534,7 +13534,7 @@
         <v>505148</v>
       </c>
     </row>
-    <row r="370" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A370" s="9">
         <v>42420</v>
       </c>
@@ -13552,7 +13552,7 @@
         <v>497210</v>
       </c>
     </row>
-    <row r="371" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A371" s="9">
         <v>42427</v>
       </c>
@@ -13570,7 +13570,7 @@
         <v>521300</v>
       </c>
     </row>
-    <row r="372" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A372" s="9">
         <v>42434</v>
       </c>
@@ -13588,7 +13588,7 @@
         <v>512202</v>
       </c>
     </row>
-    <row r="373" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A373" s="9">
         <v>42441</v>
       </c>
@@ -13606,7 +13606,7 @@
         <v>489177</v>
       </c>
     </row>
-    <row r="374" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A374" s="9">
         <v>42448</v>
       </c>
@@ -13624,7 +13624,7 @@
         <v>483463</v>
       </c>
     </row>
-    <row r="375" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A375" s="9">
         <v>42455</v>
       </c>
@@ -13642,7 +13642,7 @@
         <v>470271</v>
       </c>
     </row>
-    <row r="376" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A376" s="11">
         <v>42462</v>
       </c>
@@ -13660,7 +13660,7 @@
         <v>491979</v>
       </c>
     </row>
-    <row r="377" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A377" s="9">
         <v>42469</v>
       </c>
@@ -13678,7 +13678,7 @@
         <v>479059</v>
       </c>
     </row>
-    <row r="378" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A378" s="9">
         <v>42476</v>
       </c>
@@ -13696,7 +13696,7 @@
         <v>499779</v>
       </c>
     </row>
-    <row r="379" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A379" s="9">
         <v>42483</v>
       </c>
@@ -13714,7 +13714,7 @@
         <v>491946</v>
       </c>
     </row>
-    <row r="380" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A380" s="9">
         <v>42490</v>
       </c>
@@ -13732,7 +13732,7 @@
         <v>502045</v>
       </c>
     </row>
-    <row r="381" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A381" s="9">
         <v>42497</v>
       </c>
@@ -13750,7 +13750,7 @@
         <v>492923</v>
       </c>
     </row>
-    <row r="382" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A382" s="9">
         <v>42504</v>
       </c>
@@ -13768,7 +13768,7 @@
         <v>498379</v>
       </c>
     </row>
-    <row r="383" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A383" s="9">
         <v>42511</v>
       </c>
@@ -13786,7 +13786,7 @@
         <v>506983</v>
       </c>
     </row>
-    <row r="384" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A384" s="9">
         <v>42518</v>
       </c>
@@ -13804,7 +13804,7 @@
         <v>513917</v>
       </c>
     </row>
-    <row r="385" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A385" s="9">
         <v>42525</v>
       </c>
@@ -13822,7 +13822,7 @@
         <v>455346</v>
       </c>
     </row>
-    <row r="386" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A386" s="9">
         <v>42532</v>
       </c>
@@ -13855,7 +13855,7 @@
         <v>513471</v>
       </c>
     </row>
-    <row r="387" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A387" s="9">
         <v>42539</v>
       </c>
@@ -13873,7 +13873,7 @@
         <v>516096</v>
       </c>
     </row>
-    <row r="388" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A388" s="9">
         <v>42546</v>
       </c>
@@ -13891,7 +13891,7 @@
         <v>526161</v>
       </c>
     </row>
-    <row r="389" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A389" s="9">
         <v>42553</v>
       </c>
@@ -13909,7 +13909,7 @@
         <v>529191</v>
       </c>
     </row>
-    <row r="390" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A390" s="9">
         <v>42560</v>
       </c>
@@ -13927,7 +13927,7 @@
         <v>442113</v>
       </c>
     </row>
-    <row r="391" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A391" s="9">
         <v>42567</v>
       </c>
@@ -13945,7 +13945,7 @@
         <v>520222</v>
       </c>
     </row>
-    <row r="392" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A392" s="9">
         <v>42574</v>
       </c>
@@ -13963,7 +13963,7 @@
         <v>528070</v>
       </c>
     </row>
-    <row r="393" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A393" s="9">
         <v>42581</v>
       </c>
@@ -13981,7 +13981,7 @@
         <v>536916</v>
       </c>
     </row>
-    <row r="394" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A394" s="9">
         <v>42588</v>
       </c>
@@ -13999,7 +13999,7 @@
         <v>531595</v>
       </c>
     </row>
-    <row r="395" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A395" s="9">
         <v>42595</v>
       </c>
@@ -14017,7 +14017,7 @@
         <v>534533</v>
       </c>
     </row>
-    <row r="396" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A396" s="9">
         <v>42602</v>
       </c>
@@ -14035,7 +14035,7 @@
         <v>531484</v>
       </c>
     </row>
-    <row r="397" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A397" s="9">
         <v>42609</v>
       </c>
@@ -14053,7 +14053,7 @@
         <v>539657</v>
       </c>
     </row>
-    <row r="398" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A398" s="9">
         <v>42616</v>
       </c>
@@ -14071,7 +14071,7 @@
         <v>538826</v>
       </c>
     </row>
-    <row r="399" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A399" s="9">
         <v>42623</v>
       </c>
@@ -14089,7 +14089,7 @@
         <v>482894</v>
       </c>
     </row>
-    <row r="400" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A400" s="9">
         <v>42630</v>
       </c>
@@ -14107,7 +14107,7 @@
         <v>537904</v>
       </c>
     </row>
-    <row r="401" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A401" s="11">
         <v>42637</v>
       </c>
@@ -14125,7 +14125,7 @@
         <v>539609</v>
       </c>
     </row>
-    <row r="402" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A402" s="9">
         <v>42644</v>
       </c>
@@ -14143,7 +14143,7 @@
         <v>549171</v>
       </c>
     </row>
-    <row r="403" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A403" s="9">
         <v>42651</v>
       </c>
@@ -14161,7 +14161,7 @@
         <v>521789</v>
       </c>
     </row>
-    <row r="404" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A404" s="9">
         <v>42658</v>
       </c>
@@ -14179,7 +14179,7 @@
         <v>531936</v>
       </c>
     </row>
-    <row r="405" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A405" s="9">
         <v>42665</v>
       </c>
@@ -14197,7 +14197,7 @@
         <v>544092</v>
       </c>
     </row>
-    <row r="406" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A406" s="9">
         <v>42672</v>
       </c>
@@ -14215,7 +14215,7 @@
         <v>544997</v>
       </c>
     </row>
-    <row r="407" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A407" s="9">
         <v>42679</v>
       </c>
@@ -14233,7 +14233,7 @@
         <v>543377</v>
       </c>
     </row>
-    <row r="408" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A408" s="9">
         <v>42686</v>
       </c>
@@ -14251,7 +14251,7 @@
         <v>541127</v>
       </c>
     </row>
-    <row r="409" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A409" s="9">
         <v>42693</v>
       </c>
@@ -14269,7 +14269,7 @@
         <v>547804</v>
       </c>
     </row>
-    <row r="410" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A410" s="9">
         <v>42700</v>
       </c>
@@ -14287,7 +14287,7 @@
         <v>452759</v>
       </c>
     </row>
-    <row r="411" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A411" s="9">
         <v>42707</v>
       </c>
@@ -14305,7 +14305,7 @@
         <v>553130</v>
       </c>
     </row>
-    <row r="412" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A412" s="9">
         <v>42714</v>
       </c>
@@ -14323,7 +14323,7 @@
         <v>538932</v>
       </c>
     </row>
-    <row r="413" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A413" s="9">
         <v>42721</v>
       </c>
@@ -14341,7 +14341,7 @@
         <v>523949</v>
       </c>
     </row>
-    <row r="414" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A414" s="9">
         <v>42728</v>
       </c>
@@ -14359,7 +14359,7 @@
         <v>496633</v>
       </c>
     </row>
-    <row r="415" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A415" s="9">
         <v>42735</v>
       </c>
@@ -14377,7 +14377,7 @@
         <v>425998</v>
       </c>
     </row>
-    <row r="416" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A416" s="9">
         <v>42742</v>
       </c>
@@ -14395,7 +14395,7 @@
         <v>441417</v>
       </c>
     </row>
-    <row r="417" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A417" s="9">
         <v>42749</v>
       </c>
@@ -14413,7 +14413,7 @@
         <v>516229</v>
       </c>
     </row>
-    <row r="418" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A418" s="9">
         <v>42756</v>
       </c>
@@ -14431,7 +14431,7 @@
         <v>530299</v>
       </c>
     </row>
-    <row r="419" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A419" s="9">
         <v>42763</v>
       </c>
@@ -14449,7 +14449,7 @@
         <v>529696</v>
       </c>
     </row>
-    <row r="420" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A420" s="9">
         <v>42770</v>
       </c>
@@ -14467,7 +14467,7 @@
         <v>541474</v>
       </c>
     </row>
-    <row r="421" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A421" s="9">
         <v>42777</v>
       </c>
@@ -14485,7 +14485,7 @@
         <v>518431</v>
       </c>
     </row>
-    <row r="422" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A422" s="9">
         <v>42784</v>
       </c>
@@ -14503,7 +14503,7 @@
         <v>531123</v>
       </c>
     </row>
-    <row r="423" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A423" s="9">
         <v>42791</v>
       </c>
@@ -14521,7 +14521,7 @@
         <v>521451</v>
       </c>
     </row>
-    <row r="424" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A424" s="9">
         <v>42798</v>
       </c>
@@ -14539,7 +14539,7 @@
         <v>521607</v>
       </c>
     </row>
-    <row r="425" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A425" s="9">
         <v>42805</v>
       </c>
@@ -14557,7 +14557,7 @@
         <v>510638</v>
       </c>
     </row>
-    <row r="426" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A426" s="11">
         <v>42812</v>
       </c>
@@ -14575,7 +14575,7 @@
         <v>495281</v>
       </c>
     </row>
-    <row r="427" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A427" s="9">
         <v>42819</v>
       </c>
@@ -14593,7 +14593,7 @@
         <v>526471</v>
       </c>
     </row>
-    <row r="428" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A428" s="9">
         <v>42826</v>
       </c>
@@ -14611,7 +14611,7 @@
         <v>527665</v>
       </c>
     </row>
-    <row r="429" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A429" s="9">
         <v>42833</v>
       </c>
@@ -14629,7 +14629,7 @@
         <v>513022</v>
       </c>
     </row>
-    <row r="430" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A430" s="9">
         <v>42840</v>
       </c>
@@ -14647,7 +14647,7 @@
         <v>519318</v>
       </c>
     </row>
-    <row r="431" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A431" s="9">
         <v>42847</v>
       </c>
@@ -14665,7 +14665,7 @@
         <v>515131</v>
       </c>
     </row>
-    <row r="432" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A432" s="9">
         <v>42854</v>
       </c>
@@ -14683,7 +14683,7 @@
         <v>527830</v>
       </c>
     </row>
-    <row r="433" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A433" s="9">
         <v>42861</v>
       </c>
@@ -14701,7 +14701,7 @@
         <v>515305</v>
       </c>
     </row>
-    <row r="434" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A434" s="9">
         <v>42868</v>
       </c>
@@ -14719,7 +14719,7 @@
         <v>526970</v>
       </c>
     </row>
-    <row r="435" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A435" s="9">
         <v>42875</v>
       </c>
@@ -14737,7 +14737,7 @@
         <v>534922</v>
       </c>
     </row>
-    <row r="436" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A436" s="9">
         <v>42882</v>
       </c>
@@ -14755,7 +14755,7 @@
         <v>548103</v>
       </c>
     </row>
-    <row r="437" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A437" s="9">
         <v>42889</v>
       </c>
@@ -14773,7 +14773,7 @@
         <v>500192</v>
       </c>
     </row>
-    <row r="438" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A438" s="9">
         <v>42896</v>
       </c>
@@ -14791,7 +14791,7 @@
         <v>545317</v>
       </c>
     </row>
-    <row r="439" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A439" s="9">
         <v>42903</v>
       </c>
@@ -14809,7 +14809,7 @@
         <v>543179</v>
       </c>
     </row>
-    <row r="440" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A440" s="9">
         <v>42910</v>
       </c>
@@ -14827,7 +14827,7 @@
         <v>544694</v>
       </c>
     </row>
-    <row r="441" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A441" s="9">
         <v>42917</v>
       </c>
@@ -14845,7 +14845,7 @@
         <v>546361</v>
       </c>
     </row>
-    <row r="442" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A442" s="9">
         <v>42924</v>
       </c>
@@ -14863,7 +14863,7 @@
         <v>453080</v>
       </c>
     </row>
-    <row r="443" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A443" s="9">
         <v>42931</v>
       </c>
@@ -14881,7 +14881,7 @@
         <v>540005</v>
       </c>
     </row>
-    <row r="444" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A444" s="9">
         <v>42938</v>
       </c>
@@ -14899,7 +14899,7 @@
         <v>534152</v>
       </c>
     </row>
-    <row r="445" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A445" s="9">
         <v>42945</v>
       </c>
@@ -14917,7 +14917,7 @@
         <v>550356</v>
       </c>
     </row>
-    <row r="446" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A446" s="9">
         <v>42952</v>
       </c>
@@ -14935,7 +14935,7 @@
         <v>554822</v>
       </c>
     </row>
-    <row r="447" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A447" s="9">
         <v>42959</v>
       </c>
@@ -14953,7 +14953,7 @@
         <v>548790</v>
       </c>
     </row>
-    <row r="448" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A448" s="9">
         <v>42966</v>
       </c>
@@ -14971,7 +14971,7 @@
         <v>554021</v>
       </c>
     </row>
-    <row r="449" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A449" s="9">
         <v>42973</v>
       </c>
@@ -14989,7 +14989,7 @@
         <v>551776</v>
       </c>
     </row>
-    <row r="450" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A450" s="9">
         <v>42980</v>
       </c>
@@ -15022,7 +15022,7 @@
         <v>534140</v>
       </c>
     </row>
-    <row r="451" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A451" s="11">
         <v>42987</v>
       </c>
@@ -15040,7 +15040,7 @@
         <v>486474</v>
       </c>
     </row>
-    <row r="452" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A452" s="9">
         <v>42994</v>
       </c>
@@ -15058,7 +15058,7 @@
         <v>530774</v>
       </c>
     </row>
-    <row r="453" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A453" s="9">
         <v>43001</v>
       </c>
@@ -15076,7 +15076,7 @@
         <v>548204</v>
       </c>
     </row>
-    <row r="454" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A454" s="9">
         <v>43008</v>
       </c>
@@ -15094,7 +15094,7 @@
         <v>559555</v>
       </c>
     </row>
-    <row r="455" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A455" s="9">
         <v>43015</v>
       </c>
@@ -15112,7 +15112,7 @@
         <v>554826</v>
       </c>
     </row>
-    <row r="456" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A456" s="9">
         <v>43022</v>
       </c>
@@ -15130,7 +15130,7 @@
         <v>548264</v>
       </c>
     </row>
-    <row r="457" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A457" s="9">
         <v>43029</v>
       </c>
@@ -15148,7 +15148,7 @@
         <v>559989</v>
       </c>
     </row>
-    <row r="458" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A458" s="9">
         <v>43036</v>
       </c>
@@ -15166,7 +15166,7 @@
         <v>546582</v>
       </c>
     </row>
-    <row r="459" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A459" s="9">
         <v>43043</v>
       </c>
@@ -15184,7 +15184,7 @@
         <v>538739</v>
       </c>
     </row>
-    <row r="460" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A460" s="9">
         <v>43050</v>
       </c>
@@ -15202,7 +15202,7 @@
         <v>547480</v>
       </c>
     </row>
-    <row r="461" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A461" s="9">
         <v>43057</v>
       </c>
@@ -15220,7 +15220,7 @@
         <v>554066</v>
       </c>
     </row>
-    <row r="462" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A462" s="9">
         <v>43064</v>
       </c>
@@ -15238,7 +15238,7 @@
         <v>463602</v>
       </c>
     </row>
-    <row r="463" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A463" s="9">
         <v>43071</v>
       </c>
@@ -15256,7 +15256,7 @@
         <v>572794</v>
       </c>
     </row>
-    <row r="464" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A464" s="9">
         <v>43078</v>
       </c>
@@ -15274,7 +15274,7 @@
         <v>560756</v>
       </c>
     </row>
-    <row r="465" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A465" s="9">
         <v>43085</v>
       </c>
@@ -15292,7 +15292,7 @@
         <v>554779</v>
       </c>
     </row>
-    <row r="466" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A466" s="9">
         <v>43092</v>
       </c>
@@ -15310,7 +15310,7 @@
         <v>551566</v>
       </c>
     </row>
-    <row r="467" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A467" s="9">
         <v>43099</v>
       </c>
@@ -15328,7 +15328,7 @@
         <v>397032</v>
       </c>
     </row>
-    <row r="468" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A468" s="9">
         <v>43113</v>
       </c>
@@ -15346,7 +15346,7 @@
         <v>511937</v>
       </c>
     </row>
-    <row r="469" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A469" s="9">
         <v>43120</v>
       </c>
@@ -15364,7 +15364,7 @@
         <v>508239</v>
       </c>
     </row>
-    <row r="470" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A470" s="9">
         <v>43127</v>
       </c>
@@ -15382,7 +15382,7 @@
         <v>543515</v>
       </c>
     </row>
-    <row r="471" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A471" s="9">
         <v>43134</v>
       </c>
@@ -15400,7 +15400,7 @@
         <v>547993</v>
       </c>
     </row>
-    <row r="472" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A472" s="9">
         <v>43141</v>
       </c>
@@ -15418,7 +15418,7 @@
         <v>519545</v>
       </c>
     </row>
-    <row r="473" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A473" s="9">
         <v>43148</v>
       </c>
@@ -15436,7 +15436,7 @@
         <v>539963</v>
       </c>
     </row>
-    <row r="474" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A474" s="9">
         <v>43155</v>
       </c>
@@ -15454,7 +15454,7 @@
         <v>528440</v>
       </c>
     </row>
-    <row r="475" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A475" s="9">
         <v>43162</v>
       </c>
@@ -15472,7 +15472,7 @@
         <v>544194</v>
       </c>
     </row>
-    <row r="476" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A476" s="11">
         <v>43169</v>
       </c>
@@ -15490,7 +15490,7 @@
         <v>534282</v>
       </c>
     </row>
-    <row r="477" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A477" s="9">
         <v>43176</v>
       </c>
@@ -15508,7 +15508,7 @@
         <v>537338</v>
       </c>
     </row>
-    <row r="478" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A478" s="9">
         <v>43183</v>
       </c>
@@ -15526,7 +15526,7 @@
         <v>526521</v>
       </c>
     </row>
-    <row r="479" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A479" s="9">
         <v>43190</v>
       </c>
@@ -15544,7 +15544,7 @@
         <v>534751</v>
       </c>
     </row>
-    <row r="480" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A480" s="9">
         <v>43197</v>
       </c>
@@ -15562,7 +15562,7 @@
         <v>524905</v>
       </c>
     </row>
-    <row r="481" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A481" s="9">
         <v>43204</v>
       </c>
@@ -15580,7 +15580,7 @@
         <v>534198</v>
       </c>
     </row>
-    <row r="482" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A482" s="9">
         <v>43211</v>
       </c>
@@ -15598,7 +15598,7 @@
         <v>539425</v>
       </c>
     </row>
-    <row r="483" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A483" s="9">
         <v>43218</v>
       </c>
@@ -15616,7 +15616,7 @@
         <v>551498</v>
       </c>
     </row>
-    <row r="484" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A484" s="9">
         <v>43225</v>
       </c>
@@ -15634,7 +15634,7 @@
         <v>545937</v>
       </c>
     </row>
-    <row r="485" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A485" s="9">
         <v>43232</v>
       </c>
@@ -15652,7 +15652,7 @@
         <v>550029</v>
       </c>
     </row>
-    <row r="486" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A486" s="9">
         <v>43239</v>
       </c>
@@ -15670,7 +15670,7 @@
         <v>546415</v>
       </c>
     </row>
-    <row r="487" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A487" s="9">
         <v>43246</v>
       </c>
@@ -15688,7 +15688,7 @@
         <v>565502</v>
       </c>
     </row>
-    <row r="488" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A488" s="9">
         <v>43253</v>
       </c>
@@ -15706,7 +15706,7 @@
         <v>509740</v>
       </c>
     </row>
-    <row r="489" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A489" s="9">
         <v>43260</v>
       </c>
@@ -15724,7 +15724,7 @@
         <v>561061</v>
       </c>
     </row>
-    <row r="490" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A490" s="9">
         <v>43267</v>
       </c>
@@ -15742,7 +15742,7 @@
         <v>558098</v>
       </c>
     </row>
-    <row r="491" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A491" s="9">
         <v>43274</v>
       </c>
@@ -15760,7 +15760,7 @@
         <v>557340</v>
       </c>
     </row>
-    <row r="492" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A492" s="9">
         <v>43281</v>
       </c>
@@ -15778,7 +15778,7 @@
         <v>564243</v>
       </c>
     </row>
-    <row r="493" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A493" s="9">
         <v>43288</v>
       </c>
@@ -15796,7 +15796,7 @@
         <v>485193</v>
       </c>
     </row>
-    <row r="494" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A494" s="9">
         <v>43295</v>
       </c>
@@ -15814,7 +15814,7 @@
         <v>559064</v>
       </c>
     </row>
-    <row r="495" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A495" s="9">
         <v>43302</v>
       </c>
@@ -15832,7 +15832,7 @@
         <v>553024</v>
       </c>
     </row>
-    <row r="496" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A496" s="9">
         <v>43309</v>
       </c>
@@ -15850,7 +15850,7 @@
         <v>559154</v>
       </c>
     </row>
-    <row r="497" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A497" s="9">
         <v>43316</v>
       </c>
@@ -15868,7 +15868,7 @@
         <v>570995</v>
       </c>
     </row>
-    <row r="498" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A498" s="9">
         <v>43323</v>
       </c>
@@ -15886,7 +15886,7 @@
         <v>556887</v>
       </c>
     </row>
-    <row r="499" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A499" s="9">
         <v>43330</v>
       </c>
@@ -15904,7 +15904,7 @@
         <v>567477</v>
       </c>
     </row>
-    <row r="500" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A500" s="9">
         <v>43337</v>
       </c>
@@ -15922,7 +15922,7 @@
         <v>565706</v>
       </c>
     </row>
-    <row r="501" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A501" s="11">
         <v>43344</v>
       </c>
@@ -15940,7 +15940,7 @@
         <v>567881</v>
       </c>
     </row>
-    <row r="502" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A502" s="9">
         <v>43351</v>
       </c>
@@ -15958,7 +15958,7 @@
         <v>502208</v>
       </c>
     </row>
-    <row r="503" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A503" s="9">
         <v>43358</v>
       </c>
@@ -15976,7 +15976,7 @@
         <v>553003</v>
       </c>
     </row>
-    <row r="504" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A504" s="9">
         <v>43365</v>
       </c>
@@ -15994,7 +15994,7 @@
         <v>567078</v>
       </c>
     </row>
-    <row r="505" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A505" s="9">
         <v>43372</v>
       </c>
@@ -16012,7 +16012,7 @@
         <v>571922</v>
       </c>
     </row>
-    <row r="506" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A506" s="9">
         <v>43379</v>
       </c>
@@ -16030,7 +16030,7 @@
         <v>554238</v>
       </c>
     </row>
-    <row r="507" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A507" s="9">
         <v>43386</v>
       </c>
@@ -16048,7 +16048,7 @@
         <v>549757</v>
       </c>
     </row>
-    <row r="508" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A508" s="9">
         <v>43393</v>
       </c>
@@ -16066,7 +16066,7 @@
         <v>555106</v>
       </c>
     </row>
-    <row r="509" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A509" s="9">
         <v>43400</v>
       </c>
@@ -16084,7 +16084,7 @@
         <v>562804</v>
       </c>
     </row>
-    <row r="510" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A510" s="9">
         <v>43407</v>
       </c>
@@ -16102,7 +16102,7 @@
         <v>560046</v>
       </c>
     </row>
-    <row r="511" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A511" s="9">
         <v>43414</v>
       </c>
@@ -16120,7 +16120,7 @@
         <v>547236</v>
       </c>
     </row>
-    <row r="512" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A512" s="9">
         <v>43421</v>
       </c>
@@ -16138,7 +16138,7 @@
         <v>546541</v>
       </c>
     </row>
-    <row r="513" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A513" s="9">
         <v>43428</v>
       </c>
@@ -16156,7 +16156,7 @@
         <v>470851</v>
       </c>
     </row>
-    <row r="514" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A514" s="9">
         <v>43435</v>
       </c>
@@ -16189,7 +16189,7 @@
         <v>567282</v>
       </c>
     </row>
-    <row r="515" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A515" s="9">
         <v>43442</v>
       </c>
@@ -16207,7 +16207,7 @@
         <v>570225</v>
       </c>
     </row>
-    <row r="516" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A516" s="9">
         <v>43449</v>
       </c>
@@ -16225,7 +16225,7 @@
         <v>568941</v>
       </c>
     </row>
-    <row r="517" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A517" s="9">
         <v>43456</v>
       </c>
@@ -16243,7 +16243,7 @@
         <v>567252</v>
       </c>
     </row>
-    <row r="518" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A518" s="9">
         <v>43463</v>
       </c>
@@ -16261,7 +16261,7 @@
         <v>411676</v>
       </c>
     </row>
-    <row r="519" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A519" s="9">
         <v>43470</v>
       </c>
@@ -16279,7 +16279,7 @@
         <v>436103</v>
       </c>
     </row>
-    <row r="520" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A520" s="9">
         <v>43477</v>
       </c>
@@ -16297,7 +16297,7 @@
         <v>555127</v>
       </c>
     </row>
-    <row r="521" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A521" s="9">
         <v>43484</v>
       </c>
@@ -16315,7 +16315,7 @@
         <v>543111</v>
       </c>
     </row>
-    <row r="522" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A522" s="9">
         <v>43491</v>
       </c>
@@ -16333,7 +16333,7 @@
         <v>522026</v>
       </c>
     </row>
-    <row r="523" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A523" s="9">
         <v>43498</v>
       </c>
@@ -16351,7 +16351,7 @@
         <v>498288</v>
       </c>
     </row>
-    <row r="524" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A524" s="9">
         <v>43505</v>
       </c>
@@ -16369,7 +16369,7 @@
         <v>519779</v>
       </c>
     </row>
-    <row r="525" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A525" s="9">
         <v>43512</v>
       </c>
@@ -16387,7 +16387,7 @@
         <v>523915</v>
       </c>
     </row>
-    <row r="526" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A526" s="11">
         <v>43519</v>
       </c>
@@ -16405,7 +16405,7 @@
         <v>522630</v>
       </c>
     </row>
-    <row r="527" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A527" s="9">
         <v>43526</v>
       </c>
@@ -16423,7 +16423,7 @@
         <v>528153</v>
       </c>
     </row>
-    <row r="528" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A528" s="9">
         <v>43533</v>
       </c>
@@ -16441,7 +16441,7 @@
         <v>508958</v>
       </c>
     </row>
-    <row r="529" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A529" s="9">
         <v>43540</v>
       </c>
@@ -16459,7 +16459,7 @@
         <v>501001</v>
       </c>
     </row>
-    <row r="530" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A530" s="9">
         <v>43547</v>
       </c>
@@ -16477,7 +16477,7 @@
         <v>503017</v>
       </c>
     </row>
-    <row r="531" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A531" s="9">
         <v>43554</v>
       </c>
@@ -16495,7 +16495,7 @@
         <v>509958</v>
       </c>
     </row>
-    <row r="532" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A532" s="9">
         <v>43561</v>
       </c>
@@ -16513,7 +16513,7 @@
         <v>510192</v>
       </c>
     </row>
-    <row r="533" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A533" s="9">
         <v>43568</v>
       </c>
@@ -16531,7 +16531,7 @@
         <v>528167</v>
       </c>
     </row>
-    <row r="534" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A534" s="9">
         <v>43575</v>
       </c>
@@ -16549,7 +16549,7 @@
         <v>526141</v>
       </c>
     </row>
-    <row r="535" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A535" s="9">
         <v>43582</v>
       </c>
@@ -16567,7 +16567,7 @@
         <v>533190</v>
       </c>
     </row>
-    <row r="536" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A536" s="9">
         <v>43589</v>
       </c>
@@ -16585,7 +16585,7 @@
         <v>535089</v>
       </c>
     </row>
-    <row r="537" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A537" s="9">
         <v>43596</v>
       </c>
@@ -16603,7 +16603,7 @@
         <v>529263</v>
       </c>
     </row>
-    <row r="538" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A538" s="9">
         <v>43603</v>
       </c>
@@ -16621,7 +16621,7 @@
         <v>536358</v>
       </c>
     </row>
-    <row r="539" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A539" s="9">
         <v>43610</v>
       </c>
@@ -16639,7 +16639,7 @@
         <v>527966</v>
       </c>
     </row>
-    <row r="540" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A540" s="9">
         <v>43617</v>
       </c>
@@ -16657,7 +16657,7 @@
         <v>478679</v>
       </c>
     </row>
-    <row r="541" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A541" s="9">
         <v>43624</v>
       </c>
@@ -16675,7 +16675,7 @@
         <v>513099</v>
       </c>
     </row>
-    <row r="542" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A542" s="9">
         <v>43631</v>
       </c>
@@ -16693,7 +16693,7 @@
         <v>527989</v>
       </c>
     </row>
-    <row r="543" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A543" s="9">
         <v>43638</v>
       </c>
@@ -16711,7 +16711,7 @@
         <v>525116</v>
       </c>
     </row>
-    <row r="544" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A544" s="9">
         <v>43645</v>
       </c>
@@ -16729,7 +16729,7 @@
         <v>533164</v>
       </c>
     </row>
-    <row r="545" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A545" s="9">
         <v>43652</v>
       </c>
@@ -16747,7 +16747,7 @@
         <v>448459</v>
       </c>
     </row>
-    <row r="546" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A546" s="9">
         <v>43659</v>
       </c>
@@ -16765,7 +16765,7 @@
         <v>527908</v>
       </c>
     </row>
-    <row r="547" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A547" s="9">
         <v>43666</v>
       </c>
@@ -16783,7 +16783,7 @@
         <v>526010</v>
       </c>
     </row>
-    <row r="548" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A548" s="9">
         <v>43673</v>
       </c>
@@ -16801,7 +16801,7 @@
         <v>534498</v>
       </c>
     </row>
-    <row r="549" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A549" s="9">
         <v>43680</v>
       </c>
@@ -16819,7 +16819,7 @@
         <v>541558</v>
       </c>
     </row>
-    <row r="550" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A550" s="9">
         <v>43687</v>
       </c>
@@ -16837,7 +16837,7 @@
         <v>533190</v>
       </c>
     </row>
-    <row r="551" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A551" s="11">
         <v>43694</v>
       </c>
@@ -16855,7 +16855,7 @@
         <v>537617</v>
       </c>
     </row>
-    <row r="552" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A552" s="9">
         <v>43701</v>
       </c>
@@ -16873,7 +16873,7 @@
         <v>532483</v>
       </c>
     </row>
-    <row r="553" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A553" s="9">
         <v>43708</v>
       </c>
@@ -16891,7 +16891,7 @@
         <v>541945</v>
       </c>
     </row>
-    <row r="554" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A554" s="9">
         <v>43715</v>
       </c>
@@ -16909,7 +16909,7 @@
         <v>469285</v>
       </c>
     </row>
-    <row r="555" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A555" s="9">
         <v>43722</v>
       </c>
@@ -16927,7 +16927,7 @@
         <v>526734</v>
       </c>
     </row>
-    <row r="556" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A556" s="9">
         <v>43729</v>
       </c>
@@ -16945,7 +16945,7 @@
         <v>528670</v>
       </c>
     </row>
-    <row r="557" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A557" s="9">
         <v>43736</v>
       </c>
@@ -16963,7 +16963,7 @@
         <v>529336</v>
       </c>
     </row>
-    <row r="558" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A558" s="9">
         <v>43743</v>
       </c>
@@ -16981,7 +16981,7 @@
         <v>515061</v>
       </c>
     </row>
-    <row r="559" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A559" s="9">
         <v>43750</v>
       </c>
@@ -16999,7 +16999,7 @@
         <v>510820</v>
       </c>
     </row>
-    <row r="560" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A560" s="9">
         <v>43757</v>
       </c>
@@ -17017,7 +17017,7 @@
         <v>507381</v>
       </c>
     </row>
-    <row r="561" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A561" s="9">
         <v>43764</v>
       </c>
@@ -17035,7 +17035,7 @@
         <v>513147</v>
       </c>
     </row>
-    <row r="562" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A562" s="9">
         <v>43771</v>
       </c>
@@ -17053,7 +17053,7 @@
         <v>510012</v>
       </c>
     </row>
-    <row r="563" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A563" s="9">
         <v>43778</v>
       </c>
@@ -17071,7 +17071,7 @@
         <v>515269</v>
       </c>
     </row>
-    <row r="564" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A564" s="9">
         <v>43785</v>
       </c>
@@ -17089,7 +17089,7 @@
         <v>501249</v>
       </c>
     </row>
-    <row r="565" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A565" s="9">
         <v>43792</v>
       </c>
@@ -17107,7 +17107,7 @@
         <v>521927</v>
       </c>
     </row>
-    <row r="566" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A566" s="9">
         <v>43813</v>
       </c>
@@ -17125,7 +17125,7 @@
         <v>520589</v>
       </c>
     </row>
-    <row r="567" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A567" s="9">
         <v>43820</v>
       </c>
@@ -17143,7 +17143,7 @@
         <v>507589</v>
       </c>
     </row>
-    <row r="568" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A568" s="9">
         <v>43827</v>
       </c>
@@ -17161,7 +17161,7 @@
         <v>373728</v>
       </c>
     </row>
-    <row r="569" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A569" s="9">
         <v>43834</v>
       </c>
@@ -17179,7 +17179,7 @@
         <v>414014</v>
       </c>
     </row>
-    <row r="570" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A570" s="9">
         <v>43841</v>
       </c>
@@ -17197,7 +17197,7 @@
         <v>501624</v>
       </c>
     </row>
-    <row r="571" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A571" s="9">
         <v>43848</v>
       </c>
@@ -17215,7 +17215,7 @@
         <v>499732</v>
       </c>
     </row>
-    <row r="572" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A572" s="9">
         <v>43855</v>
       </c>
@@ -17233,7 +17233,7 @@
         <v>485282</v>
       </c>
     </row>
-    <row r="573" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A573" s="9">
         <v>43862</v>
       </c>
@@ -17251,7 +17251,7 @@
         <v>510161</v>
       </c>
     </row>
-    <row r="574" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A574" s="9">
         <v>43869</v>
       </c>
@@ -17269,7 +17269,7 @@
         <v>485329</v>
       </c>
     </row>
-    <row r="575" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A575" s="9">
         <v>43876</v>
       </c>
@@ -17287,7 +17287,7 @@
         <v>479137</v>
       </c>
     </row>
-    <row r="576" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A576" s="11">
         <v>43883</v>
       </c>
@@ -17305,7 +17305,7 @@
         <v>482690</v>
       </c>
     </row>
-    <row r="577" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A577" s="9">
         <v>43890</v>
       </c>
@@ -17323,7 +17323,7 @@
         <v>477611</v>
       </c>
     </row>
-    <row r="578" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A578" s="9">
         <v>43897</v>
       </c>
@@ -17356,7 +17356,7 @@
         <v>462303</v>
       </c>
     </row>
-    <row r="579" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A579" s="9">
         <v>43904</v>
       </c>
@@ -17374,7 +17374,7 @@
         <v>463017</v>
       </c>
     </row>
-    <row r="580" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A580" s="9">
         <v>43911</v>
       </c>
@@ -17392,7 +17392,7 @@
         <v>459966</v>
       </c>
     </row>
-    <row r="581" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A581" s="9">
         <v>43918</v>
       </c>
@@ -17410,7 +17410,7 @@
         <v>449767</v>
       </c>
     </row>
-    <row r="582" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A582" s="9">
         <v>43925</v>
       </c>
@@ -17428,7 +17428,7 @@
         <v>429095</v>
       </c>
     </row>
-    <row r="583" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A583" s="9">
         <v>43932</v>
       </c>
@@ -17446,7 +17446,7 @@
         <v>412503</v>
       </c>
     </row>
-    <row r="584" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A584" s="9">
         <v>43939</v>
       </c>
@@ -17464,7 +17464,7 @@
         <v>403283</v>
       </c>
     </row>
-    <row r="585" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A585" s="9">
         <v>43946</v>
       </c>
@@ -17482,7 +17482,7 @@
         <v>414123</v>
       </c>
     </row>
-    <row r="586" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A586" s="9">
         <v>43953</v>
       </c>
@@ -17500,7 +17500,7 @@
         <v>416954</v>
       </c>
     </row>
-    <row r="587" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A587" s="9">
         <v>43960</v>
       </c>
@@ -17518,7 +17518,7 @@
         <v>412549</v>
       </c>
     </row>
-    <row r="588" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A588" s="9">
         <v>43967</v>
       </c>
@@ -17536,7 +17536,7 @@
         <v>416115</v>
       </c>
     </row>
-    <row r="589" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A589" s="9">
         <v>43974</v>
       </c>
@@ -17554,7 +17554,7 @@
         <v>428715</v>
       </c>
     </row>
-    <row r="590" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A590" s="9">
         <v>43981</v>
       </c>
@@ -17572,7 +17572,7 @@
         <v>395714</v>
       </c>
     </row>
-    <row r="591" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A591" s="9">
         <v>43988</v>
       </c>
@@ -17590,7 +17590,7 @@
         <v>433171</v>
       </c>
     </row>
-    <row r="592" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A592" s="9">
         <v>43995</v>
       </c>
@@ -17608,7 +17608,7 @@
         <v>449291</v>
       </c>
     </row>
-    <row r="593" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A593" s="9">
         <v>44002</v>
       </c>
@@ -17626,7 +17626,7 @@
         <v>457278</v>
       </c>
     </row>
-    <row r="594" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A594" s="9">
         <v>44009</v>
       </c>
@@ -17644,7 +17644,7 @@
         <v>459449</v>
       </c>
     </row>
-    <row r="595" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A595" s="9">
         <v>44016</v>
       </c>
@@ -17662,7 +17662,7 @@
         <v>437989</v>
       </c>
     </row>
-    <row r="596" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A596" s="9">
         <v>44023</v>
       </c>
@@ -17680,7 +17680,7 @@
         <v>449092</v>
       </c>
     </row>
-    <row r="597" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A597" s="9">
         <v>44030</v>
       </c>
@@ -17698,7 +17698,7 @@
         <v>481597</v>
       </c>
     </row>
-    <row r="598" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A598" s="9">
         <v>44037</v>
       </c>
@@ -17716,7 +17716,7 @@
         <v>481331</v>
       </c>
     </row>
-    <row r="599" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A599" s="9">
         <v>44044</v>
       </c>
@@ -17734,7 +17734,7 @@
         <v>487968</v>
       </c>
     </row>
-    <row r="600" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A600" s="9">
         <v>44051</v>
       </c>
@@ -17752,7 +17752,7 @@
         <v>497397</v>
       </c>
     </row>
-    <row r="601" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A601" s="11">
         <v>44058</v>
       </c>
@@ -17770,7 +17770,7 @@
         <v>500563</v>
       </c>
     </row>
-    <row r="602" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A602" s="9">
         <v>44072</v>
       </c>
@@ -17788,7 +17788,7 @@
         <v>508307</v>
       </c>
     </row>
-    <row r="603" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A603" s="9">
         <v>44079</v>
       </c>
@@ -17806,7 +17806,7 @@
         <v>509637</v>
       </c>
     </row>
-    <row r="604" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A604" s="9">
         <v>44086</v>
       </c>
@@ -17824,7 +17824,7 @@
         <v>474785</v>
       </c>
     </row>
-    <row r="605" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A605" s="9">
         <v>44093</v>
       </c>
@@ -17842,7 +17842,7 @@
         <v>521956</v>
       </c>
     </row>
-    <row r="606" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A606" s="9">
         <v>44100</v>
       </c>
@@ -17860,7 +17860,7 @@
         <v>518290</v>
       </c>
     </row>
-    <row r="607" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A607" s="9">
         <v>44107</v>
       </c>
@@ -17878,7 +17878,7 @@
         <v>518761</v>
       </c>
     </row>
-    <row r="608" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A608" s="9">
         <v>44114</v>
       </c>
@@ -17896,7 +17896,7 @@
         <v>520452</v>
       </c>
     </row>
-    <row r="609" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A609" s="9">
         <v>44121</v>
       </c>
@@ -17914,7 +17914,7 @@
         <v>518763</v>
       </c>
     </row>
-    <row r="610" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A610" s="9">
         <v>44128</v>
       </c>
@@ -17932,7 +17932,7 @@
         <v>522653</v>
       </c>
     </row>
-    <row r="611" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A611" s="9">
         <v>44135</v>
       </c>
@@ -17950,7 +17950,7 @@
         <v>520778</v>
       </c>
     </row>
-    <row r="612" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A612" s="9">
         <v>44142</v>
       </c>
@@ -17968,7 +17968,7 @@
         <v>522028</v>
       </c>
     </row>
-    <row r="613" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A613" s="9">
         <v>44149</v>
       </c>
@@ -17986,7 +17986,7 @@
         <v>527462</v>
       </c>
     </row>
-    <row r="614" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A614" s="9">
         <v>44156</v>
       </c>
@@ -18004,7 +18004,7 @@
         <v>534607</v>
       </c>
     </row>
-    <row r="615" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A615" s="9">
         <v>44163</v>
       </c>
@@ -18022,7 +18022,7 @@
         <v>452792</v>
       </c>
     </row>
-    <row r="616" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A616" s="9">
         <v>44170</v>
       </c>
@@ -18040,7 +18040,7 @@
         <v>542203</v>
       </c>
     </row>
-    <row r="617" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A617" s="9">
         <v>44177</v>
       </c>
@@ -18058,7 +18058,7 @@
         <v>546209</v>
       </c>
     </row>
-    <row r="618" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A618" s="9">
         <v>44191</v>
       </c>
@@ -18076,7 +18076,7 @@
         <v>405111</v>
       </c>
     </row>
-    <row r="619" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A619" s="9">
         <v>44198</v>
       </c>
@@ -18094,7 +18094,7 @@
         <v>421991</v>
       </c>
     </row>
-    <row r="620" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A620" s="9">
         <v>44205</v>
       </c>
@@ -18112,7 +18112,7 @@
         <v>525253</v>
       </c>
     </row>
-    <row r="621" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A621" s="9">
         <v>44212</v>
       </c>
@@ -18130,7 +18130,7 @@
         <v>528547</v>
       </c>
     </row>
-    <row r="622" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A622" s="9">
         <v>44219</v>
       </c>
@@ -18148,7 +18148,7 @@
         <v>529030</v>
       </c>
     </row>
-    <row r="623" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="623" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A623" s="9">
         <v>44226</v>
       </c>
@@ -18166,7 +18166,7 @@
         <v>520693</v>
       </c>
     </row>
-    <row r="624" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A624" s="9">
         <v>44233</v>
       </c>
@@ -18184,7 +18184,7 @@
         <v>495815</v>
       </c>
     </row>
-    <row r="625" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="625" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A625" s="9">
         <v>44240</v>
       </c>
@@ -18202,7 +18202,7 @@
         <v>480483</v>
       </c>
     </row>
-    <row r="626" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A626" s="11">
         <v>44247</v>
       </c>
@@ -18220,7 +18220,7 @@
         <v>377904</v>
       </c>
     </row>
-    <row r="627" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="627" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A627" s="9">
         <v>44254</v>
       </c>
@@ -18238,7 +18238,7 @@
         <v>486429</v>
       </c>
     </row>
-    <row r="628" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="628" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A628" s="9">
         <v>44261</v>
       </c>
@@ -18256,7 +18256,7 @@
         <v>515135</v>
       </c>
     </row>
-    <row r="629" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="629" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A629" s="9">
         <v>44268</v>
       </c>
@@ -18274,7 +18274,7 @@
         <v>520736</v>
       </c>
     </row>
-    <row r="630" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A630" s="9">
         <v>44275</v>
       </c>
@@ -18292,7 +18292,7 @@
         <v>513325</v>
       </c>
     </row>
-    <row r="631" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="631" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A631" s="9">
         <v>44282</v>
       </c>
@@ -18310,7 +18310,7 @@
         <v>521731</v>
       </c>
     </row>
-    <row r="632" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="632" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A632" s="9">
         <v>44289</v>
       </c>
@@ -18328,7 +18328,7 @@
         <v>515562</v>
       </c>
     </row>
-    <row r="633" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="633" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A633" s="9">
         <v>44296</v>
       </c>
@@ -18346,7 +18346,7 @@
         <v>513724</v>
       </c>
     </row>
-    <row r="634" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="634" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A634" s="9">
         <v>44303</v>
       </c>
@@ -18364,7 +18364,7 @@
         <v>533217</v>
       </c>
     </row>
-    <row r="635" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="635" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A635" s="9">
         <v>44310</v>
       </c>
@@ -18382,7 +18382,7 @@
         <v>538184</v>
       </c>
     </row>
-    <row r="636" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="636" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A636" s="9">
         <v>44317</v>
       </c>
@@ -18400,7 +18400,7 @@
         <v>540667</v>
       </c>
     </row>
-    <row r="637" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="637" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A637" s="9">
         <v>44324</v>
       </c>
@@ -18418,7 +18418,7 @@
         <v>523309</v>
       </c>
     </row>
-    <row r="638" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="638" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A638" s="9">
         <v>44331</v>
       </c>
@@ -18436,7 +18436,7 @@
         <v>533872</v>
       </c>
     </row>
-    <row r="639" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="639" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A639" s="9">
         <v>44338</v>
       </c>
@@ -18454,7 +18454,7 @@
         <v>528774</v>
       </c>
     </row>
-    <row r="640" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="640" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A640" s="9">
         <v>44345</v>
       </c>
@@ -18472,7 +18472,7 @@
         <v>530225</v>
       </c>
     </row>
-    <row r="641" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="641" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A641" s="9">
         <v>44352</v>
       </c>
@@ -18490,7 +18490,7 @@
         <v>489144</v>
       </c>
     </row>
-    <row r="642" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="642" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A642" s="9">
         <v>44359</v>
       </c>
@@ -18523,7 +18523,7 @@
         <v>529635</v>
       </c>
     </row>
-    <row r="643" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="643" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A643" s="9">
         <v>44366</v>
       </c>
@@ -18541,7 +18541,7 @@
         <v>514112</v>
       </c>
     </row>
-    <row r="644" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="644" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A644" s="9">
         <v>44373</v>
       </c>
@@ -18559,7 +18559,7 @@
         <v>516167</v>
       </c>
     </row>
-    <row r="645" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="645" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A645" s="9">
         <v>44380</v>
       </c>
@@ -18577,7 +18577,7 @@
         <v>512919</v>
       </c>
     </row>
-    <row r="646" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="646" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A646" s="9">
         <v>44387</v>
       </c>
@@ -18595,7 +18595,7 @@
         <v>451825</v>
       </c>
     </row>
-    <row r="647" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="647" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A647" s="9">
         <v>44394</v>
       </c>
@@ -18613,7 +18613,7 @@
         <v>513255</v>
       </c>
     </row>
-    <row r="648" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="648" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A648" s="9">
         <v>44401</v>
       </c>
@@ -18631,7 +18631,7 @@
         <v>503219</v>
       </c>
     </row>
-    <row r="649" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="649" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A649" s="9">
         <v>44408</v>
       </c>
@@ -18649,7 +18649,7 @@
         <v>502540</v>
       </c>
     </row>
-    <row r="650" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="650" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A650" s="9">
         <v>44415</v>
       </c>
@@ -18667,7 +18667,7 @@
         <v>509607</v>
       </c>
     </row>
-    <row r="651" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="651" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A651" s="11">
         <v>44422</v>
       </c>
@@ -18685,7 +18685,7 @@
         <v>504810</v>
       </c>
     </row>
-    <row r="652" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="652" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A652" s="9">
         <v>44429</v>
       </c>
@@ -18703,7 +18703,7 @@
         <v>501273</v>
       </c>
     </row>
-    <row r="653" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="653" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A653" s="9">
         <v>44436</v>
       </c>
@@ -18721,7 +18721,7 @@
         <v>504417</v>
       </c>
     </row>
-    <row r="654" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="654" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A654" s="9">
         <v>44443</v>
       </c>
@@ -18739,7 +18739,7 @@
         <v>494415</v>
       </c>
     </row>
-    <row r="655" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="655" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A655" s="9">
         <v>44450</v>
       </c>
@@ -18757,7 +18757,7 @@
         <v>468610</v>
       </c>
     </row>
-    <row r="656" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="656" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A656" s="9">
         <v>44457</v>
       </c>
@@ -18775,7 +18775,7 @@
         <v>505622</v>
       </c>
     </row>
-    <row r="657" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="657" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A657" s="9">
         <v>44464</v>
       </c>
@@ -18793,7 +18793,7 @@
         <v>511713</v>
       </c>
     </row>
-    <row r="658" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="658" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A658" s="9">
         <v>44471</v>
       </c>
@@ -18811,7 +18811,7 @@
         <v>515849</v>
       </c>
     </row>
-    <row r="659" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="659" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A659" s="9">
         <v>44478</v>
       </c>
@@ -18829,7 +18829,7 @@
         <v>506642</v>
       </c>
     </row>
-    <row r="660" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="660" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A660" s="9">
         <v>44485</v>
       </c>
@@ -18847,7 +18847,7 @@
         <v>496983</v>
       </c>
     </row>
-    <row r="661" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="661" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A661" s="9">
         <v>44492</v>
       </c>
@@ -18865,7 +18865,7 @@
         <v>510762</v>
       </c>
     </row>
-    <row r="662" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="662" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A662" s="9">
         <v>44499</v>
       </c>
@@ -18883,7 +18883,7 @@
         <v>510141</v>
       </c>
     </row>
-    <row r="663" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="663" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A663" s="9">
         <v>44506</v>
       </c>
@@ -18901,7 +18901,7 @@
         <v>504111</v>
       </c>
     </row>
-    <row r="664" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="664" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A664" s="9">
         <v>44513</v>
       </c>
@@ -18919,7 +18919,7 @@
         <v>502613</v>
       </c>
     </row>
-    <row r="665" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="665" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A665" s="9">
         <v>44520</v>
       </c>
@@ -18937,7 +18937,7 @@
         <v>508309</v>
       </c>
     </row>
-    <row r="666" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="666" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A666" s="9">
         <v>44527</v>
       </c>
@@ -18955,7 +18955,7 @@
         <v>430793</v>
       </c>
     </row>
-    <row r="667" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="667" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A667" s="9">
         <v>44534</v>
       </c>
@@ -18973,7 +18973,7 @@
         <v>527406</v>
       </c>
     </row>
-    <row r="668" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="668" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A668" s="9">
         <v>44541</v>
       </c>
@@ -18991,7 +18991,7 @@
         <v>513366</v>
       </c>
     </row>
-    <row r="669" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="669" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A669" s="9">
         <v>44548</v>
       </c>
@@ -19009,7 +19009,7 @@
         <v>504099</v>
       </c>
     </row>
-    <row r="670" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="670" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A670" s="9">
         <v>44555</v>
       </c>
@@ -19027,7 +19027,7 @@
         <v>420373</v>
       </c>
     </row>
-    <row r="671" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="671" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A671" s="9">
         <v>44562</v>
       </c>
@@ -19045,7 +19045,7 @@
         <v>395371</v>
       </c>
     </row>
-    <row r="672" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="672" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A672" s="9">
         <v>44569</v>
       </c>
@@ -19063,7 +19063,7 @@
         <v>440761</v>
       </c>
     </row>
-    <row r="673" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="673" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A673" s="9">
         <v>44576</v>
       </c>
@@ -19081,7 +19081,7 @@
         <v>493617</v>
       </c>
     </row>
-    <row r="674" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="674" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A674" s="9">
         <v>44583</v>
       </c>
@@ -19099,7 +19099,7 @@
         <v>477462</v>
       </c>
     </row>
-    <row r="675" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="675" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A675" s="9">
         <v>44590</v>
       </c>
@@ -19117,7 +19117,7 @@
         <v>491868</v>
       </c>
     </row>
-    <row r="676" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="676" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A676" s="11">
         <v>44597</v>
       </c>
@@ -19135,7 +19135,7 @@
         <v>458152</v>
       </c>
     </row>
-    <row r="677" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="677" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A677" s="9">
         <v>44604</v>
       </c>
@@ -19153,7 +19153,7 @@
         <v>504482</v>
       </c>
     </row>
-    <row r="678" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="678" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A678" s="9">
         <v>44611</v>
       </c>
@@ -19171,7 +19171,7 @@
         <v>497822</v>
       </c>
     </row>
-    <row r="679" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="679" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A679" s="9">
         <v>44625</v>
       </c>
@@ -19189,7 +19189,7 @@
         <v>505177</v>
       </c>
     </row>
-    <row r="680" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="680" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A680" s="9">
         <v>44632</v>
       </c>
@@ -19207,7 +19207,7 @@
         <v>496134</v>
       </c>
     </row>
-    <row r="681" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="681" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A681" s="9">
         <v>44639</v>
       </c>
@@ -19225,7 +19225,7 @@
         <v>499362</v>
       </c>
     </row>
-    <row r="682" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="682" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A682" s="9">
         <v>44646</v>
       </c>
@@ -19243,7 +19243,7 @@
         <v>504817</v>
       </c>
     </row>
-    <row r="683" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="683" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A683" s="9">
         <v>44653</v>
       </c>
@@ -19261,7 +19261,7 @@
         <v>502194</v>
       </c>
     </row>
-    <row r="684" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="684" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A684" s="9">
         <v>44660</v>
       </c>
@@ -19279,7 +19279,7 @@
         <v>508343</v>
       </c>
     </row>
-    <row r="685" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="685" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A685" s="9">
         <v>44667</v>
       </c>
@@ -19297,7 +19297,7 @@
         <v>489801</v>
       </c>
     </row>
-    <row r="686" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="686" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A686" s="9">
         <v>44674</v>
       </c>
@@ -19315,7 +19315,7 @@
         <v>498011</v>
       </c>
     </row>
-    <row r="687" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="687" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A687" s="9">
         <v>44681</v>
       </c>
@@ -19333,7 +19333,7 @@
         <v>506699</v>
       </c>
     </row>
-    <row r="688" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="688" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A688" s="9">
         <v>44688</v>
       </c>
@@ -19351,7 +19351,7 @@
         <v>504927</v>
       </c>
     </row>
-    <row r="689" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="689" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A689" s="9">
         <v>44695</v>
       </c>
@@ -19369,7 +19369,7 @@
         <v>505120</v>
       </c>
     </row>
-    <row r="690" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="690" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A690" s="9">
         <v>44702</v>
       </c>
@@ -19387,7 +19387,7 @@
         <v>506976</v>
       </c>
     </row>
-    <row r="691" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="691" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A691" s="9">
         <v>44709</v>
       </c>
@@ -19405,7 +19405,7 @@
         <v>514277</v>
       </c>
     </row>
-    <row r="692" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="692" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A692" s="9">
         <v>44716</v>
       </c>
@@ -19423,7 +19423,7 @@
         <v>475513</v>
       </c>
     </row>
-    <row r="693" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="693" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A693" s="9">
         <v>44723</v>
       </c>
@@ -19441,7 +19441,7 @@
         <v>510295</v>
       </c>
     </row>
-    <row r="694" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="694" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A694" s="9">
         <v>44730</v>
       </c>
@@ -19459,7 +19459,7 @@
         <v>501207</v>
       </c>
     </row>
-    <row r="695" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="695" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A695" s="9">
         <v>44737</v>
       </c>
@@ -19477,7 +19477,7 @@
         <v>493374</v>
       </c>
     </row>
-    <row r="696" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="696" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A696" s="9">
         <v>44744</v>
       </c>
@@ -19495,7 +19495,7 @@
         <v>500285</v>
       </c>
     </row>
-    <row r="697" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="697" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A697" s="9">
         <v>44751</v>
       </c>
@@ -19513,7 +19513,7 @@
         <v>437600</v>
       </c>
     </row>
-    <row r="698" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="698" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A698" s="9">
         <v>44758</v>
       </c>
@@ -19531,7 +19531,7 @@
         <v>498899</v>
       </c>
     </row>
-    <row r="699" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="699" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A699" s="9">
         <v>44765</v>
       </c>
@@ -19549,7 +19549,7 @@
         <v>498901</v>
       </c>
     </row>
-    <row r="700" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="700" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A700" s="9">
         <v>44772</v>
       </c>
@@ -19567,7 +19567,7 @@
         <v>505409</v>
       </c>
     </row>
-    <row r="701" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="701" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A701" s="11">
         <v>44779</v>
       </c>
@@ -19585,7 +19585,7 @@
         <v>496526</v>
       </c>
     </row>
-    <row r="702" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="702" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A702" s="9">
         <v>44786</v>
       </c>
@@ -19603,7 +19603,7 @@
         <v>502775</v>
       </c>
     </row>
-    <row r="703" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="703" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A703" s="9">
         <v>44793</v>
       </c>
@@ -19621,7 +19621,7 @@
         <v>501548</v>
       </c>
     </row>
-    <row r="704" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="704" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A704" s="9">
         <v>44800</v>
       </c>
@@ -19639,7 +19639,7 @@
         <v>511574</v>
       </c>
     </row>
-    <row r="705" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="705" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A705" s="9">
         <v>44807</v>
       </c>
@@ -19657,7 +19657,7 @@
         <v>513087</v>
       </c>
     </row>
-    <row r="706" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="706" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A706" s="9">
         <v>44814</v>
       </c>
@@ -19690,7 +19690,7 @@
         <v>464261</v>
       </c>
     </row>
-    <row r="707" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="707" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A707" s="9">
         <v>44821</v>
       </c>
@@ -19708,7 +19708,7 @@
         <v>490654</v>
       </c>
     </row>
-    <row r="708" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="708" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A708" s="9">
         <v>44828</v>
       </c>
@@ -19726,7 +19726,7 @@
         <v>489111</v>
       </c>
     </row>
-    <row r="709" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="709" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A709" s="9">
         <v>44835</v>
       </c>
@@ -19744,7 +19744,7 @@
         <v>495868</v>
       </c>
     </row>
-    <row r="710" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="710" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A710" s="9">
         <v>44842</v>
       </c>
@@ -19762,7 +19762,7 @@
         <v>494413</v>
       </c>
     </row>
-    <row r="711" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="711" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A711" s="9">
         <v>44849</v>
       </c>
@@ -19780,7 +19780,7 @@
         <v>500304</v>
       </c>
     </row>
-    <row r="712" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="712" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A712" s="9">
         <v>44856</v>
       </c>
@@ -19798,7 +19798,7 @@
         <v>505322</v>
       </c>
     </row>
-    <row r="713" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="713" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A713" s="9">
         <v>44863</v>
       </c>
@@ -19816,7 +19816,7 @@
         <v>514457</v>
       </c>
     </row>
-    <row r="714" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="714" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A714" s="9">
         <v>44870</v>
       </c>
@@ -19834,7 +19834,7 @@
         <v>502106</v>
       </c>
     </row>
-    <row r="715" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="715" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A715" s="9">
         <v>44877</v>
       </c>
@@ -19852,7 +19852,7 @@
         <v>490350</v>
       </c>
     </row>
-    <row r="716" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="716" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A716" s="9">
         <v>44884</v>
       </c>
@@ -19870,7 +19870,7 @@
         <v>491794</v>
       </c>
     </row>
-    <row r="717" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="717" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A717" s="9">
         <v>44891</v>
       </c>
@@ -19888,7 +19888,7 @@
         <v>413305</v>
       </c>
     </row>
-    <row r="718" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="718" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A718" s="9">
         <v>44898</v>
       </c>
@@ -19906,7 +19906,7 @@
         <v>495472</v>
       </c>
     </row>
-    <row r="719" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="719" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A719" s="9">
         <v>44905</v>
       </c>
@@ -19924,7 +19924,7 @@
         <v>500310</v>
       </c>
     </row>
-    <row r="720" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="720" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A720" s="9">
         <v>44912</v>
       </c>
@@ -19942,7 +19942,7 @@
         <v>476232</v>
       </c>
     </row>
-    <row r="721" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="721" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A721" s="9">
         <v>44919</v>
       </c>
@@ -19960,7 +19960,7 @@
         <v>400289</v>
       </c>
     </row>
-    <row r="722" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="722" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A722" s="9">
         <v>44926</v>
       </c>
@@ -19978,7 +19978,7 @@
         <v>365553</v>
       </c>
     </row>
-    <row r="723" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="723" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A723" s="9">
         <v>44933</v>
       </c>
@@ -19996,7 +19996,7 @@
         <v>416489</v>
       </c>
     </row>
-    <row r="724" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="724" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A724" s="9">
         <v>44940</v>
       </c>
@@ -20014,7 +20014,7 @@
         <v>486000</v>
       </c>
     </row>
-    <row r="725" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="725" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A725" s="9">
         <v>44947</v>
       </c>
@@ -20032,7 +20032,7 @@
         <v>467485</v>
       </c>
     </row>
-    <row r="726" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="726" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A726" s="11">
         <v>44954</v>
       </c>
@@ -20050,7 +20050,7 @@
         <v>473650</v>
       </c>
     </row>
-    <row r="727" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="727" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A727" s="9">
         <v>44961</v>
       </c>
@@ -20068,7 +20068,7 @@
         <v>449586</v>
       </c>
     </row>
-    <row r="728" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="728" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A728" s="9">
         <v>44968</v>
       </c>
@@ -20086,7 +20086,7 @@
         <v>473972</v>
       </c>
     </row>
-    <row r="729" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="729" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A729" s="9">
         <v>44975</v>
       </c>
@@ -20104,7 +20104,7 @@
         <v>466932</v>
       </c>
     </row>
-    <row r="730" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="730" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A730" s="9">
         <v>44982</v>
       </c>
@@ -20122,7 +20122,7 @@
         <v>459233</v>
       </c>
     </row>
-    <row r="731" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="731" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A731" s="9">
         <v>44989</v>
       </c>
@@ -20140,7 +20140,7 @@
         <v>474191</v>
       </c>
     </row>
-    <row r="732" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="732" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A732" s="9">
         <v>44996</v>
       </c>
@@ -20158,7 +20158,7 @@
         <v>458629</v>
       </c>
     </row>
-    <row r="733" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="733" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A733" s="9">
         <v>45003</v>
       </c>
@@ -20176,7 +20176,7 @@
         <v>453500</v>
       </c>
     </row>
-    <row r="734" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="734" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A734" s="9">
         <v>45010</v>
       </c>
@@ -20194,7 +20194,7 @@
         <v>469958</v>
       </c>
     </row>
-    <row r="735" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="735" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A735" s="9">
         <v>45017</v>
       </c>
@@ -20212,7 +20212,7 @@
         <v>467430</v>
       </c>
     </row>
-    <row r="736" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="736" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A736" s="9">
         <v>45024</v>
       </c>
@@ -20230,7 +20230,7 @@
         <v>451336</v>
       </c>
     </row>
-    <row r="737" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="737" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A737" s="9">
         <v>45031</v>
       </c>
@@ -20248,7 +20248,7 @@
         <v>468197</v>
       </c>
     </row>
-    <row r="738" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="738" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A738" s="9">
         <v>45038</v>
       </c>
@@ -20266,7 +20266,7 @@
         <v>480457</v>
       </c>
     </row>
-    <row r="739" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="739" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A739" s="9">
         <v>45045</v>
       </c>
@@ -20284,7 +20284,7 @@
         <v>481960</v>
       </c>
     </row>
-    <row r="740" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="740" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A740" s="9">
         <v>45052</v>
       </c>
@@ -20302,7 +20302,7 @@
         <v>471859</v>
       </c>
     </row>
-    <row r="741" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="741" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A741" s="9">
         <v>45059</v>
       </c>
@@ -20320,7 +20320,7 @@
         <v>466381</v>
       </c>
     </row>
-    <row r="742" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="742" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A742" s="9">
         <v>45066</v>
       </c>
@@ -20338,7 +20338,7 @@
         <v>470694</v>
       </c>
     </row>
-    <row r="743" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="743" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A743" s="9">
         <v>45073</v>
       </c>
@@ -20356,7 +20356,7 @@
         <v>480998</v>
       </c>
     </row>
-    <row r="744" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="744" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A744" s="9">
         <v>45080</v>
       </c>
@@ -20374,7 +20374,7 @@
         <v>439601</v>
       </c>
     </row>
-    <row r="745" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="745" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A745" s="9">
         <v>45087</v>
       </c>
@@ -20392,7 +20392,7 @@
         <v>471141</v>
       </c>
     </row>
-    <row r="746" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="746" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A746" s="9">
         <v>45094</v>
       </c>
@@ -20410,7 +20410,7 @@
         <v>477126</v>
       </c>
     </row>
-    <row r="747" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="747" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A747" s="9">
         <v>45101</v>
       </c>
@@ -20428,7 +20428,7 @@
         <v>469453</v>
       </c>
     </row>
-    <row r="748" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="748" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A748" s="9">
         <v>45108</v>
       </c>
@@ -20446,7 +20446,7 @@
         <v>474443</v>
       </c>
     </row>
-    <row r="749" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="749" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A749" s="9">
         <v>45115</v>
       </c>
@@ -20464,7 +20464,7 @@
         <v>407843</v>
       </c>
     </row>
-    <row r="750" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="750" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A750" s="9">
         <v>45122</v>
       </c>
@@ -20482,7 +20482,7 @@
         <v>478153</v>
       </c>
     </row>
-    <row r="751" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="751" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A751" s="11">
         <v>45129</v>
       </c>
@@ -20500,7 +20500,7 @@
         <v>473736</v>
       </c>
     </row>
-    <row r="752" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="752" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A752" s="9">
         <v>45136</v>
       </c>
@@ -20518,7 +20518,7 @@
         <v>483481</v>
       </c>
     </row>
-    <row r="753" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="753" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A753" s="9">
         <v>45143</v>
       </c>
@@ -20536,7 +20536,7 @@
         <v>471938</v>
       </c>
     </row>
-    <row r="754" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="754" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A754" s="9">
         <v>45150</v>
       </c>
@@ -20554,7 +20554,7 @@
         <v>472498</v>
       </c>
     </row>
-    <row r="755" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="755" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A755" s="9">
         <v>45157</v>
       </c>
@@ -20572,7 +20572,7 @@
         <v>478853</v>
       </c>
     </row>
-    <row r="756" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="756" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A756" s="9">
         <v>45164</v>
       </c>
@@ -20590,7 +20590,7 @@
         <v>472525</v>
       </c>
     </row>
-    <row r="757" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="757" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A757" s="9">
         <v>45171</v>
       </c>
@@ -20608,7 +20608,7 @@
         <v>476851</v>
       </c>
     </row>
-    <row r="758" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="758" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A758" s="9">
         <v>45178</v>
       </c>
@@ -20626,7 +20626,7 @@
         <v>447345</v>
       </c>
     </row>
-    <row r="759" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="759" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A759" s="9">
         <v>45185</v>
       </c>
@@ -20644,7 +20644,7 @@
         <v>489790</v>
       </c>
     </row>
-    <row r="760" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="760" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A760" s="9">
         <v>45192</v>
       </c>
@@ -20662,7 +20662,7 @@
         <v>493323</v>
       </c>
     </row>
-    <row r="761" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="761" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A761" s="9">
         <v>45199</v>
       </c>
@@ -20680,7 +20680,7 @@
         <v>500154</v>
       </c>
     </row>
-    <row r="762" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="762" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A762" s="9">
         <v>45206</v>
       </c>
@@ -20698,7 +20698,7 @@
         <v>499217</v>
       </c>
     </row>
-    <row r="763" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="763" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A763" s="9">
         <v>45213</v>
       </c>
@@ -20716,7 +20716,7 @@
         <v>492781</v>
       </c>
     </row>
-    <row r="764" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="764" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A764" s="9">
         <v>45220</v>
       </c>
@@ -20734,7 +20734,7 @@
         <v>505985</v>
       </c>
     </row>
-    <row r="765" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="765" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A765" s="9">
         <v>45227</v>
       </c>
@@ -20752,7 +20752,7 @@
         <v>499389</v>
       </c>
     </row>
-    <row r="766" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="766" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A766" s="9">
         <v>45234</v>
       </c>
@@ -20770,7 +20770,7 @@
         <v>484757</v>
       </c>
     </row>
-    <row r="767" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="767" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A767" s="9">
         <v>45241</v>
       </c>
@@ -20788,7 +20788,7 @@
         <v>497348</v>
       </c>
     </row>
-    <row r="768" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="768" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A768" s="9">
         <v>45248</v>
       </c>
@@ -20806,7 +20806,7 @@
         <v>501416</v>
       </c>
     </row>
-    <row r="769" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="769" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A769" s="9">
         <v>45255</v>
       </c>
@@ -20824,7 +20824,7 @@
         <v>415332</v>
       </c>
     </row>
-    <row r="770" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="770" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A770" s="9">
         <v>45262</v>
       </c>
@@ -20857,7 +20857,7 @@
         <v>509626</v>
       </c>
     </row>
-    <row r="771" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="771" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A771" s="9">
         <v>45269</v>
       </c>
@@ -20875,7 +20875,7 @@
         <v>499094</v>
       </c>
     </row>
-    <row r="772" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="772" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A772" s="9">
         <v>45276</v>
       </c>
@@ -20893,7 +20893,7 @@
         <v>502583</v>
       </c>
     </row>
-    <row r="773" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="773" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A773" s="9">
         <v>45283</v>
       </c>
@@ -20911,7 +20911,7 @@
         <v>486787</v>
       </c>
     </row>
-    <row r="774" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="774" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A774" s="9">
         <v>45297</v>
       </c>
@@ -20929,7 +20929,7 @@
         <v>417257</v>
       </c>
     </row>
-    <row r="775" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="775" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A775" s="9">
         <v>45304</v>
       </c>
@@ -20947,7 +20947,7 @@
         <v>457453</v>
       </c>
     </row>
-    <row r="776" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="776" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A776" s="13">
         <v>45311</v>
       </c>
@@ -20965,7 +20965,7 @@
         <v>397553</v>
       </c>
     </row>
-    <row r="777" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="777" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A777" s="15">
         <v>45318</v>
       </c>
@@ -20983,7 +20983,7 @@
         <v>467222</v>
       </c>
     </row>
-    <row r="778" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="778" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A778" s="15">
         <v>45325</v>
       </c>
@@ -21001,7 +21001,7 @@
         <v>491697</v>
       </c>
     </row>
-    <row r="779" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="779" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A779" s="15">
         <v>45332</v>
       </c>
@@ -21019,7 +21019,7 @@
         <v>484840</v>
       </c>
     </row>
-    <row r="780" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="780" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A780" s="15">
         <v>45339</v>
       </c>
@@ -21037,7 +21037,7 @@
         <v>474226</v>
       </c>
     </row>
-    <row r="781" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="781" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A781" s="15">
         <v>45346</v>
       </c>
@@ -21055,7 +21055,7 @@
         <v>483656</v>
       </c>
     </row>
-    <row r="782" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="782" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A782" s="15">
         <v>45353</v>
       </c>
@@ -21073,7 +21073,7 @@
         <v>483138</v>
       </c>
     </row>
-    <row r="783" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="783" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A783" s="15">
         <v>45360</v>
       </c>
@@ -21091,7 +21091,7 @@
         <v>472662</v>
       </c>
     </row>
-    <row r="784" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="784" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A784" s="15">
         <v>45367</v>
       </c>
@@ -21109,7 +21109,7 @@
         <v>474596</v>
       </c>
     </row>
-    <row r="785" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="785" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A785" s="15">
         <v>45374</v>
       </c>
@@ -21127,7 +21127,7 @@
         <v>470593</v>
       </c>
     </row>
-    <row r="786" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="786" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A786" s="15">
         <v>45381</v>
       </c>
@@ -21145,7 +21145,7 @@
         <v>472651</v>
       </c>
     </row>
-    <row r="787" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="787" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A787" s="15">
         <v>45388</v>
       </c>
@@ -21163,7 +21163,7 @@
         <v>450142</v>
       </c>
     </row>
-    <row r="788" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="788" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A788" s="15">
         <v>45395</v>
       </c>
@@ -21181,7 +21181,7 @@
         <v>466463</v>
       </c>
     </row>
-    <row r="789" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="789" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A789" s="15">
         <v>45402</v>
       </c>
@@ -21199,7 +21199,7 @@
         <v>474544</v>
       </c>
     </row>
-    <row r="790" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="790" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A790" s="15">
         <v>45409</v>
       </c>
@@ -21217,7 +21217,7 @@
         <v>476302</v>
       </c>
     </row>
-    <row r="791" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="791" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A791" s="15">
         <v>45416</v>
       </c>
@@ -21235,7 +21235,7 @@
         <v>463106</v>
       </c>
     </row>
-    <row r="792" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="792" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A792" s="15">
         <v>45423</v>
       </c>
@@ -21253,7 +21253,7 @@
         <v>468748</v>
       </c>
     </row>
-    <row r="793" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="793" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A793" s="15">
         <v>45430</v>
       </c>
@@ -21271,7 +21271,7 @@
         <v>474886</v>
       </c>
     </row>
-    <row r="794" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="794" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A794" s="15">
         <v>45437</v>
       </c>
@@ -21289,7 +21289,7 @@
         <v>485232</v>
       </c>
     </row>
-    <row r="795" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="795" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A795" s="15">
         <v>45444</v>
       </c>
@@ -21307,7 +21307,7 @@
         <v>450077</v>
       </c>
     </row>
-    <row r="796" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="796" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A796" s="15">
         <v>45451</v>
       </c>
@@ -21325,7 +21325,7 @@
         <v>489916</v>
       </c>
     </row>
-    <row r="797" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="797" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A797" s="15">
         <v>45458</v>
       </c>
@@ -21343,7 +21343,7 @@
         <v>493138</v>
       </c>
     </row>
-    <row r="798" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="798" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A798" s="15">
         <v>45465</v>
       </c>
@@ -21361,7 +21361,7 @@
         <v>485557</v>
       </c>
     </row>
-    <row r="799" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="799" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A799" s="15">
         <v>45472</v>
       </c>
@@ -21379,7 +21379,7 @@
         <v>491899</v>
       </c>
     </row>
-    <row r="800" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="800" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A800" s="15">
         <v>45479</v>
       </c>
@@ -21397,7 +21397,7 @@
         <v>421817</v>
       </c>
     </row>
-    <row r="801" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="801" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A801" s="13">
         <v>45486</v>
       </c>
@@ -21415,7 +21415,7 @@
         <v>483806</v>
       </c>
     </row>
-    <row r="802" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="802" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A802" s="15">
         <v>45493</v>
       </c>
@@ -21433,7 +21433,7 @@
         <v>480083</v>
       </c>
     </row>
-    <row r="803" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="803" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A803" s="15">
         <v>45500</v>
       </c>
@@ -21451,7 +21451,7 @@
         <v>508496</v>
       </c>
     </row>
-    <row r="804" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="804" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A804" s="15">
         <v>45507</v>
       </c>
@@ -21469,7 +21469,7 @@
         <v>498807</v>
       </c>
     </row>
-    <row r="805" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="805" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A805" s="15">
         <v>45514</v>
       </c>
@@ -21487,7 +21487,7 @@
         <v>496509</v>
       </c>
     </row>
-    <row r="806" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="806" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A806" s="15">
         <v>45521</v>
       </c>
@@ -21505,7 +21505,7 @@
         <v>516819</v>
       </c>
     </row>
-    <row r="807" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="807" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A807" s="15">
         <v>45528</v>
       </c>
@@ -21523,7 +21523,7 @@
         <v>516807</v>
       </c>
     </row>
-    <row r="808" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="808" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A808" s="15">
         <v>45535</v>
       </c>
@@ -21541,7 +21541,7 @@
         <v>516632</v>
       </c>
     </row>
-    <row r="809" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="809" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A809" s="15">
         <v>45542</v>
       </c>
@@ -21559,7 +21559,7 @@
         <v>479179</v>
       </c>
     </row>
-    <row r="810" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="810" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A810" s="15">
         <v>45549</v>
       </c>
@@ -21577,7 +21577,7 @@
         <v>522557</v>
       </c>
     </row>
-    <row r="811" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="811" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A811" s="15">
         <v>45556</v>
       </c>
@@ -21595,7 +21595,7 @@
         <v>522112</v>
       </c>
     </row>
-    <row r="812" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="812" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A812" s="15">
         <v>45563</v>
       </c>
@@ -21613,7 +21613,7 @@
         <v>507537</v>
       </c>
     </row>
-    <row r="813" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="813" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A813" s="15">
         <v>45570</v>
       </c>
@@ -21631,7 +21631,7 @@
         <v>486187</v>
       </c>
     </row>
-    <row r="814" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="814" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A814" s="15">
         <v>45577</v>
       </c>
@@ -21649,7 +21649,7 @@
         <v>505033</v>
       </c>
     </row>
-    <row r="815" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="815" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A815" s="15">
         <v>45584</v>
       </c>
@@ -21667,7 +21667,7 @@
         <v>510730</v>
       </c>
     </row>
-    <row r="816" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="816" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A816" s="15">
         <v>45591</v>
       </c>
@@ -21685,7 +21685,7 @@
         <v>519415</v>
       </c>
     </row>
-    <row r="817" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="817" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A817" s="15">
         <v>45598</v>
       </c>
@@ -21703,7 +21703,7 @@
         <v>516743</v>
       </c>
     </row>
-    <row r="818" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="818" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A818" s="15">
         <v>45612</v>
       </c>
@@ -21721,7 +21721,7 @@
         <v>516886</v>
       </c>
     </row>
-    <row r="819" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="819" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A819" s="15">
         <v>45619</v>
       </c>
@@ -21739,7 +21739,7 @@
         <v>520798</v>
       </c>
     </row>
-    <row r="820" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="820" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A820" s="15">
         <v>45626</v>
       </c>
@@ -21757,7 +21757,7 @@
         <v>439362</v>
       </c>
     </row>
-    <row r="821" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="821" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A821" s="15">
         <v>45633</v>
       </c>
@@ -21775,7 +21775,7 @@
         <v>520894</v>
       </c>
     </row>
-    <row r="822" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="822" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A822" s="15">
         <v>45640</v>
       </c>
@@ -21793,7 +21793,7 @@
         <v>526166</v>
       </c>
     </row>
-    <row r="823" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="823" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A823" s="15">
         <v>45647</v>
       </c>
@@ -21811,7 +21811,7 @@
         <v>523912</v>
       </c>
     </row>
-    <row r="824" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="824" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A824" s="15">
         <v>45654</v>
       </c>
@@ -21829,7 +21829,7 @@
         <v>389700</v>
       </c>
     </row>
-    <row r="825" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="825" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A825" s="15">
         <v>45661</v>
       </c>
@@ -21847,7 +21847,7 @@
         <v>421410</v>
       </c>
     </row>
-    <row r="826" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="826" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A826" s="13">
         <v>45668</v>
       </c>
@@ -21865,7 +21865,7 @@
         <v>465390</v>
       </c>
     </row>
-    <row r="827" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="827" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A827" s="15">
         <v>45675</v>
       </c>
@@ -21883,7 +21883,7 @@
         <v>500160</v>
       </c>
     </row>
-    <row r="828" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="828" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A828" s="15">
         <v>45682</v>
       </c>
@@ -21901,7 +21901,7 @@
         <v>454797</v>
       </c>
     </row>
-    <row r="829" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="829" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A829" s="15">
         <v>45689</v>
       </c>
@@ -21919,7 +21919,7 @@
         <v>513622</v>
       </c>
     </row>
-    <row r="830" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="830" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A830" s="15">
         <v>45696</v>
       </c>
@@ -21937,7 +21937,7 @@
         <v>502449</v>
       </c>
     </row>
-    <row r="831" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="831" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A831" s="15">
         <v>45703</v>
       </c>
@@ -21955,7 +21955,7 @@
         <v>480740</v>
       </c>
     </row>
-    <row r="832" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="832" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A832" s="15">
         <v>45710</v>
       </c>
@@ -21973,7 +21973,7 @@
         <v>458513</v>
       </c>
     </row>
-    <row r="833" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="833" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A833" s="15">
         <v>45717</v>
       </c>
@@ -21991,7 +21991,7 @@
         <v>508531</v>
       </c>
     </row>
-    <row r="834" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="834" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A834" s="15">
         <v>45724</v>
       </c>
@@ -22024,7 +22024,7 @@
         <v>497412</v>
       </c>
     </row>
-    <row r="835" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="835" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A835" s="15">
         <v>45731</v>
       </c>
@@ -22042,7 +22042,7 @@
         <v>503473</v>
       </c>
     </row>
-    <row r="836" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="836" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A836" s="15">
         <v>45738</v>
       </c>
@@ -22060,7 +22060,7 @@
         <v>496214</v>
       </c>
     </row>
-    <row r="837" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="837" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A837" s="15">
         <v>45745</v>
       </c>
@@ -22078,7 +22078,7 @@
         <v>513553</v>
       </c>
     </row>
-    <row r="838" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="838" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A838" s="15">
         <v>45752</v>
       </c>
@@ -22096,7 +22096,7 @@
         <v>500584</v>
       </c>
     </row>
-    <row r="839" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="839" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A839" s="15">
         <v>45759</v>
       </c>
@@ -22114,7 +22114,7 @@
         <v>491908</v>
       </c>
     </row>
-    <row r="840" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="840" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A840" s="15">
         <v>45766</v>
       </c>
@@ -22132,7 +22132,7 @@
         <v>496053</v>
       </c>
     </row>
-    <row r="841" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="841" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A841" s="15">
         <v>45773</v>
       </c>
@@ -22150,7 +22150,7 @@
         <v>502105</v>
       </c>
     </row>
-    <row r="842" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="842" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A842" s="15">
         <v>45780</v>
       </c>
@@ -22168,7 +22168,7 @@
         <v>498693</v>
       </c>
     </row>
-    <row r="843" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="843" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A843" s="15">
         <v>45787</v>
       </c>
@@ -22186,7 +22186,7 @@
         <v>495552</v>
       </c>
     </row>
-    <row r="844" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="844" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A844" s="15">
         <v>45794</v>
       </c>
@@ -22204,7 +22204,7 @@
         <v>490775</v>
       </c>
     </row>
-    <row r="845" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="845" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A845" s="15">
         <v>45801</v>
       </c>
@@ -22222,7 +22222,7 @@
         <v>488709</v>
       </c>
     </row>
-    <row r="846" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="846" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A846" s="15">
         <v>45808</v>
       </c>
@@ -22240,7 +22240,7 @@
         <v>459884</v>
       </c>
     </row>
-    <row r="847" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="847" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A847" s="15">
         <v>45815</v>
       </c>
@@ -22258,7 +22258,7 @@
         <v>483807</v>
       </c>
     </row>
-    <row r="848" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="848" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A848" s="15">
         <v>45822</v>
       </c>
@@ -22276,7 +22276,7 @@
         <v>485810</v>
       </c>
     </row>
-    <row r="849" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="849" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A849" s="15">
         <v>45829</v>
       </c>
@@ -22294,7 +22294,7 @@
         <v>487328</v>
       </c>
     </row>
-    <row r="850" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="850" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A850" s="15">
         <v>45836</v>
       </c>
@@ -22312,7 +22312,7 @@
         <v>491424</v>
       </c>
     </row>
-    <row r="851" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="851" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A851" s="13">
         <v>45843</v>
       </c>
@@ -22330,7 +22330,7 @@
         <v>443049</v>
       </c>
     </row>
-    <row r="852" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="852" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A852" s="15">
         <v>45850</v>
       </c>
@@ -22348,7 +22348,7 @@
         <v>496188</v>
       </c>
     </row>
-    <row r="853" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="853" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A853" s="15">
         <v>45857</v>
       </c>
@@ -22366,7 +22366,7 @@
         <v>506882</v>
       </c>
     </row>
-    <row r="854" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="854" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A854" s="15">
         <v>45864</v>
       </c>
@@ -22384,7 +22384,7 @@
         <v>514279</v>
       </c>
     </row>
-    <row r="855" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="855" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A855" s="15">
         <v>45871</v>
       </c>
@@ -22402,7 +22402,7 @@
         <v>513529</v>
       </c>
     </row>
-    <row r="856" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="856" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A856" s="15">
         <v>45878</v>
       </c>
@@ -22420,7 +22420,7 @@
         <v>511194</v>
       </c>
     </row>
-    <row r="857" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="857" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A857" s="15">
         <v>45885</v>
       </c>
@@ -22438,7 +22438,7 @@
         <v>512970</v>
       </c>
     </row>
-    <row r="858" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="858" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A858" s="15">
         <v>45892</v>
       </c>
@@ -22456,7 +22456,7 @@
         <v>512333</v>
       </c>
     </row>
-    <row r="859" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="859" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A859" s="15">
         <v>45899</v>
       </c>
@@ -22474,7 +22474,7 @@
         <v>521502</v>
       </c>
     </row>
-    <row r="860" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="860" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A860" s="15">
         <v>45906</v>
       </c>
@@ -22492,7 +22492,7 @@
         <v>467880</v>
       </c>
     </row>
-    <row r="861" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="861" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A861" s="15">
         <v>45913</v>
       </c>
@@ -22510,7 +22510,7 @@
         <v>514167</v>
       </c>
     </row>
-    <row r="862" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="862" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A862" s="15">
         <v>45920</v>
       </c>
@@ -22528,7 +22528,7 @@
         <v>510677</v>
       </c>
     </row>
-    <row r="863" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="863" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A863" s="13">
         <v>45927</v>
       </c>
@@ -22546,7 +22546,7 @@
         <v>512642</v>
       </c>
     </row>
-    <row r="864" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="864" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A864" s="15">
         <v>45934</v>
       </c>
@@ -22564,7 +22564,7 @@
         <v>503538</v>
       </c>
     </row>
-    <row r="865" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="865" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A865" s="15">
         <v>45941</v>
       </c>
@@ -22582,7 +22582,7 @@
         <v>498462</v>
       </c>
     </row>
-    <row r="866" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="866" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A866" s="15">
         <v>45948</v>
       </c>
@@ -22600,7 +22600,7 @@
         <v>497854</v>
       </c>
     </row>
-    <row r="867" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="867" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A867" s="15">
         <v>45955</v>
       </c>
@@ -22618,7 +22618,7 @@
         <v>499688</v>
       </c>
     </row>
-    <row r="868" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="868" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A868" s="15">
         <v>45962</v>
       </c>
@@ -22636,7 +22636,7 @@
         <v>496928</v>
       </c>
     </row>
-    <row r="869" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="869" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A869" s="15">
         <v>45969</v>
       </c>
@@ -22654,7 +22654,7 @@
         <v>493493</v>
       </c>
     </row>
-    <row r="870" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="870" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A870" s="15">
         <v>45976</v>
       </c>
@@ -22672,7 +22672,7 @@
         <v>493880</v>
       </c>
     </row>
-    <row r="871" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="871" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A871" s="15">
         <v>45983</v>
       </c>
@@ -22690,7 +22690,7 @@
         <v>516110</v>
       </c>
     </row>
-    <row r="872" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="872" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A872" s="15">
         <v>45990</v>
       </c>
@@ -22708,7 +22708,7 @@
         <v>431435</v>
       </c>
     </row>
-    <row r="873" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="873" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A873" s="15">
         <v>45997</v>
       </c>
@@ -22726,7 +22726,7 @@
         <v>508999</v>
       </c>
     </row>
-    <row r="874" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="874" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A874" s="15">
         <v>46004</v>
       </c>
@@ -22744,7 +22744,7 @@
         <v>518904</v>
       </c>
     </row>
-    <row r="875" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="875" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A875" s="13">
         <v>46018</v>
       </c>
@@ -22762,7 +22762,7 @@
         <v>392295</v>
       </c>
     </row>
-    <row r="876" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="876" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A876" s="7">
         <v>46025</v>
       </c>
@@ -22780,7 +22780,7 @@
         <v>404293</v>
       </c>
     </row>
-    <row r="877" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="877" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A877" s="13">
         <v>46032</v>
       </c>
@@ -22798,7 +22798,7 @@
         <v>510457</v>
       </c>
     </row>
-    <row r="878" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="878" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A878" s="7">
         <v>46039</v>
       </c>
@@ -22831,7 +22831,7 @@
         <v>505385</v>
       </c>
     </row>
-    <row r="879" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="879" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A879" s="13">
         <v>46046</v>
       </c>
@@ -22864,7 +22864,7 @@
         <v>481708</v>
       </c>
     </row>
-    <row r="880" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="880" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A880" s="13">
         <v>46053</v>
       </c>
@@ -22897,7 +22897,7 @@
         <v>434361</v>
       </c>
     </row>
-    <row r="881" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="881" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A881" s="13">
         <v>46060</v>
       </c>
@@ -22915,7 +22915,7 @@
         <v>486854</v>
       </c>
     </row>
-    <row r="882" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="882" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A882" s="7">
         <v>46067</v>
       </c>
@@ -22948,7 +22948,7 @@
         <v>510399</v>
       </c>
     </row>
-    <row r="883" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="883" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A883" s="13">
         <v>46074</v>
       </c>
@@ -22981,7 +22981,7 @@
         <v>507712</v>
       </c>
     </row>
-    <row r="884" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="884" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A884" s="7">
         <v>46081</v>
       </c>
@@ -22999,7 +22999,7 @@
         <v>516729</v>
       </c>
     </row>
-    <row r="885" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="885" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A885" s="13">
         <v>46088</v>
       </c>
@@ -23032,7 +23032,7 @@
         <v>514996</v>
       </c>
     </row>
-    <row r="886" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="886" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A886" s="7">
         <v>46102</v>
       </c>
@@ -23065,7 +23065,7 @@
         <v>502252</v>
       </c>
     </row>
-    <row r="887" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="887" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A887" s="7">
         <v>46109</v>
       </c>
@@ -23098,7 +23098,7 @@
         <v>515921</v>
       </c>
     </row>
-    <row r="888" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="888" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A888" s="7">
         <v>46116</v>
       </c>
@@ -23131,6 +23131,36 @@
         <v>501328</v>
       </c>
     </row>
+    <row r="889" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A889" s="7">
+        <v>46123</v>
+      </c>
+      <c r="B889" s="7">
+        <v>46127</v>
+      </c>
+      <c r="C889" s="21">
+        <v>0.500694444444444</v>
+      </c>
+      <c r="D889" s="6" t="str">
+        <f>IF(
+ AND(
+  A889 &gt;= IF(
+         YEAR(A889)&gt;=2007,
+         DATE(YEAR(A889),3,14)-WEEKDAY(DATE(YEAR(A889),3,14),1)+1 + TIME(2,0,0),
+         DATE(YEAR(A889),4,7)-WEEKDAY(DATE(YEAR(A889),4,7),1)+1 + TIME(2,0,0)
+       ),
+  A889 &lt;  IF(
+         YEAR(A889)&gt;=2007,
+         DATE(YEAR(A889),11,7)-WEEKDAY(DATE(YEAR(A889),11,7),1)+1 + TIME(2,0,0),
+         DATE(YEAR(A889),10,31)-WEEKDAY(DATE(YEAR(A889),10,31),1) + TIME(2,0,0)
+       )
+ ),
+ "UTC-4",
+ "UTC-5"
+)</f>
+        <v>UTC-4</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E876">
     <sortCondition ref="B2:B876"/>
@@ -23144,7 +23174,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{300947AE-C9E8-48BA-99BA-AA00E1AFF02E}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -23155,12 +23185,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFF96248-4EFB-4252-A059-6D65AEEDC293}">
   <dimension ref="B2:C4"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15.6" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
@@ -23168,7 +23198,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
@@ -23176,7 +23206,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>

--- a/data/freight/US Rail Traffic.xlsx
+++ b/data/freight/US Rail Traffic.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBEE92D5-7C67-4D94-8836-CED26B96F48D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{590EDCE9-680D-4174-9F77-09AC26B98199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{55EF15CE-83DB-4E42-B75D-C3DAE3AA4C48}"/>
   </bookViews>
@@ -5729,6 +5729,9 @@
                 </c:pt>
                 <c:pt idx="889">
                   <c:v>511616</c:v>
+                </c:pt>
+                <c:pt idx="890">
+                  <c:v>518773</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -23151,11 +23154,14 @@
         <v>46148</v>
       </c>
       <c r="C892" s="21">
-        <v>0.50069444444444444</v>
+        <v>0.51388888888888884</v>
       </c>
       <c r="D892" s="6" t="str">
         <f t="shared" si="15"/>
         <v>UTC-4</v>
+      </c>
+      <c r="E892" s="17">
+        <v>518773</v>
       </c>
     </row>
   </sheetData>

--- a/data/freight/US Rail Traffic.xlsx
+++ b/data/freight/US Rail Traffic.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FC9258F-8986-44A3-903D-90C4C103DDA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4776DF8F-3CAF-4A22-BB7B-5B77173D17C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{55EF15CE-83DB-4E42-B75D-C3DAE3AA4C48}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{55EF15CE-83DB-4E42-B75D-C3DAE3AA4C48}"/>
   </bookViews>
   <sheets>
     <sheet name="USRT" sheetId="1" r:id="rId1"/>
@@ -79,7 +79,6 @@
   </si>
   <si>
     <t>https://ycharts.com/indicators/us_weekly_rail_traffic</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -297,37 +296,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-              <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="ko-KR"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
+    <c:autoTitleDeleted val="1"/>
     <c:plotArea>
       <c:layout/>
       <c:lineChart>
@@ -337,13 +306,25 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>USRT</c:v>
+            <c:strRef>
+              <c:f>USRT!$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v> USRT </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="25400" cap="rnd">
+            <a:ln w="22225" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent1"/>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
               </a:solidFill>
+              <a:prstDash val="sysDot"/>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -351,33 +332,27 @@
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
-          <c:dPt>
-            <c:idx val="757"/>
-            <c:marker>
-              <c:symbol val="none"/>
-            </c:marker>
-            <c:bubble3D val="0"/>
+          <c:trendline>
             <c:spPr>
               <a:ln w="25400" cap="rnd">
                 <a:solidFill>
                   <a:schemeClr val="accent1"/>
                 </a:solidFill>
-                <a:round/>
+                <a:prstDash val="solid"/>
               </a:ln>
               <a:effectLst/>
             </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-EA16-44AC-9102-B33C30064F60}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
+            <c:trendlineType val="movingAvg"/>
+            <c:period val="12"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
           <c:cat>
             <c:numRef>
-              <c:f>USRT!$B$2:$B$11885</c:f>
+              <c:f>USRT!$B$2:$B$894</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="11884"/>
+                <c:ptCount val="893"/>
                 <c:pt idx="0">
                   <c:v>39827</c:v>
                 </c:pt>
@@ -3062,10 +3037,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>USRT!$E$2:$E$11885</c:f>
+              <c:f>USRT!$E$2:$E$894</c:f>
               <c:numCache>
                 <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"??_);_(@_)</c:formatCode>
-                <c:ptCount val="11884"/>
+                <c:ptCount val="893"/>
                 <c:pt idx="0">
                   <c:v>474565</c:v>
                 </c:pt>
@@ -5741,6 +5716,9 @@
                 </c:pt>
                 <c:pt idx="891">
                   <c:v>513755</c:v>
+                </c:pt>
+                <c:pt idx="892">
+                  <c:v>511216</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5748,7 +5726,7 @@
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-EA16-44AC-9102-B33C30064F60}"/>
+              <c16:uniqueId val="{00000001-0C31-4DD5-B01F-36685A417BA4}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -5761,11 +5739,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="323398112"/>
-        <c:axId val="317933392"/>
+        <c:axId val="1507289439"/>
+        <c:axId val="1507269279"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="323398112"/>
+        <c:axId val="1507289439"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="46387"/>
@@ -5807,10 +5785,10 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="ko-KR"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="317933392"/>
+        <c:crossAx val="1507269279"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -5819,11 +5797,10 @@
         <c:majorTimeUnit val="years"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="317933392"/>
+        <c:axId val="1507269279"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="610000"/>
-          <c:min val="350000"/>
+          <c:min val="300000"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -5869,10 +5846,10 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="ko-KR"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="323398112"/>
+        <c:crossAx val="1507289439"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5884,6 +5861,37 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr rtl="0">
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
@@ -5915,7 +5923,7 @@
           <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="ko-KR"/>
+      <a:endParaRPr lang="en-US"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -6489,20 +6497,20 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>1904</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>571500</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>138113</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>190499</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="차트 1">
+        <xdr:cNvPr id="3" name="차트 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7C2212F3-3128-48CB-B97E-F9B83099017B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{468310C7-20E0-4D73-9C72-53AA4A8B9AE3}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6829,7 +6837,7 @@
     <col min="2" max="2" width="16.109375" style="7" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.33203125" style="21" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.44140625" style="17" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.44140625" style="17" customWidth="1"/>
     <col min="6" max="16384" width="9.109375" style="5"/>
   </cols>
   <sheetData>
@@ -23214,11 +23222,14 @@
         <v>46162</v>
       </c>
       <c r="C894" s="21">
-        <v>0.52222222222222225</v>
+        <v>0.50347222222222221</v>
       </c>
       <c r="D894" s="6" t="str">
         <f t="shared" si="16"/>
         <v>UTC-4</v>
+      </c>
+      <c r="E894" s="17">
+        <v>511216</v>
       </c>
     </row>
   </sheetData>

--- a/data/freight/US Rail Traffic.xlsx
+++ b/data/freight/US Rail Traffic.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2A94987-9107-44BC-B992-F8762E3FA7F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB4EA763-B32F-4CEB-AC5E-3ECE54A931E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{55EF15CE-83DB-4E42-B75D-C3DAE3AA4C48}"/>
   </bookViews>
@@ -6830,7 +6830,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83FCC8DB-37A0-4531-B65E-34C65BAF4830}">
-  <dimension ref="A1:E896"/>
+  <dimension ref="A1:E897"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="12.6" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.109375" style="7" bestFit="1" customWidth="1"/>
@@ -23261,7 +23261,7 @@
         <v>0.5</v>
       </c>
       <c r="D896" s="6" t="str">
-        <f t="shared" ref="D896" si="17">IF(
+        <f t="shared" ref="D896:D897" si="17">IF(
  AND(
   A896 &gt;= IF(
          YEAR(A896)&gt;=2007,
@@ -23281,6 +23281,21 @@
       </c>
       <c r="E896" s="17">
         <v>492795</v>
+      </c>
+    </row>
+    <row r="897" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A897" s="7">
+        <v>46179</v>
+      </c>
+      <c r="B897" s="7">
+        <v>46183</v>
+      </c>
+      <c r="C897" s="21">
+        <v>0.50347222222222221</v>
+      </c>
+      <c r="D897" s="6" t="str">
+        <f t="shared" si="17"/>
+        <v>UTC-4</v>
       </c>
     </row>
   </sheetData>

--- a/data/freight/US Rail Traffic.xlsx
+++ b/data/freight/US Rail Traffic.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D34E4C66-39F2-432E-8003-3C3B0D494AA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BE7669D-C908-4B04-95FF-F3543A847F21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{55EF15CE-83DB-4E42-B75D-C3DAE3AA4C48}"/>
   </bookViews>
@@ -6833,14 +6833,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83FCC8DB-37A0-4531-B65E-34C65BAF4830}">
-  <dimension ref="A1:E897"/>
+  <dimension ref="A1:E898"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.33203125" style="21" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.44140625" style="20" customWidth="1"/>
+    <col min="1" max="1" width="10.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.21875" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.33203125" style="21" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.77734375" style="20" bestFit="1" customWidth="1"/>
     <col min="6" max="16384" width="9.109375" style="6"/>
   </cols>
   <sheetData>
@@ -23264,7 +23264,7 @@
         <v>0.5</v>
       </c>
       <c r="D896" s="7" t="str">
-        <f t="shared" ref="D896:D897" si="17">IF(
+        <f t="shared" ref="D896:D898" si="17">IF(
  AND(
   A896 &gt;= IF(
          YEAR(A896)&gt;=2007,
@@ -23302,6 +23302,21 @@
       </c>
       <c r="E897" s="20">
         <v>521804</v>
+      </c>
+    </row>
+    <row r="898" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A898" s="8">
+        <v>46186</v>
+      </c>
+      <c r="B898" s="8">
+        <v>46190</v>
+      </c>
+      <c r="C898" s="21">
+        <v>0.51388888888888884</v>
+      </c>
+      <c r="D898" s="7" t="str">
+        <f t="shared" si="17"/>
+        <v>UTC-4</v>
       </c>
     </row>
   </sheetData>

--- a/data/freight/US Rail Traffic.xlsx
+++ b/data/freight/US Rail Traffic.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\freight\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tommy/Desktop/Pycharm/FinancialData/data/freight/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BE7669D-C908-4B04-95FF-F3543A847F21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7F58D89-9EED-7F4C-BBB2-83419F8101A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{55EF15CE-83DB-4E42-B75D-C3DAE3AA4C48}"/>
+    <workbookView xWindow="22160" yWindow="600" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{55EF15CE-83DB-4E42-B75D-C3DAE3AA4C48}"/>
   </bookViews>
   <sheets>
     <sheet name="USRT" sheetId="1" r:id="rId1"/>
@@ -91,7 +91,7 @@
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="166" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -268,9 +268,9 @@
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="쉼표" xfId="1" builtinId="3"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -288,7 +288,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -6537,9 +6537,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -6577,7 +6577,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -6683,7 +6683,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -6825,7 +6825,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -6834,17 +6834,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83FCC8DB-37A0-4531-B65E-34C65BAF4830}">
   <dimension ref="A1:E898"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.21875" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.33203125" style="21" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.77734375" style="20" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="6"/>
+    <col min="5" max="5" width="8.83203125" style="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.1640625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -6861,7 +6861,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" ht="16">
       <c r="A2" s="7">
         <v>39823</v>
       </c>
@@ -6894,7 +6894,7 @@
         <v>474565</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="16">
       <c r="A3" s="7">
         <v>39830</v>
       </c>
@@ -6912,7 +6912,7 @@
         <v>465386</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" ht="16">
       <c r="A4" s="7">
         <v>39837</v>
       </c>
@@ -6930,7 +6930,7 @@
         <v>462128</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="16">
       <c r="A5" s="7">
         <v>39844</v>
       </c>
@@ -6948,7 +6948,7 @@
         <v>449966</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="16">
       <c r="A6" s="7">
         <v>39851</v>
       </c>
@@ -6966,7 +6966,7 @@
         <v>455757</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" ht="16">
       <c r="A7" s="7">
         <v>39858</v>
       </c>
@@ -6984,7 +6984,7 @@
         <v>471961</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" ht="16">
       <c r="A8" s="7">
         <v>39865</v>
       </c>
@@ -7002,7 +7002,7 @@
         <v>446575</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" ht="16">
       <c r="A9" s="7">
         <v>39872</v>
       </c>
@@ -7020,7 +7020,7 @@
         <v>458242</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" ht="16">
       <c r="A10" s="7">
         <v>39879</v>
       </c>
@@ -7038,7 +7038,7 @@
         <v>455041</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" ht="16">
       <c r="A11" s="7">
         <v>39886</v>
       </c>
@@ -7056,7 +7056,7 @@
         <v>455686</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" ht="16">
       <c r="A12" s="7">
         <v>39893</v>
       </c>
@@ -7074,7 +7074,7 @@
         <v>459547</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" ht="16">
       <c r="A13" s="7">
         <v>39900</v>
       </c>
@@ -7092,7 +7092,7 @@
         <v>439844</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" ht="16">
       <c r="A14" s="7">
         <v>39907</v>
       </c>
@@ -7110,7 +7110,7 @@
         <v>447103</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" ht="16">
       <c r="A15" s="7">
         <v>39914</v>
       </c>
@@ -7128,7 +7128,7 @@
         <v>426107</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" ht="16">
       <c r="A16" s="7">
         <v>39921</v>
       </c>
@@ -7146,7 +7146,7 @@
         <v>438602</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" ht="16">
       <c r="A17" s="7">
         <v>39928</v>
       </c>
@@ -7164,7 +7164,7 @@
         <v>444794</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" ht="16">
       <c r="A18" s="7">
         <v>39935</v>
       </c>
@@ -7182,7 +7182,7 @@
         <v>442378</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" ht="16">
       <c r="A19" s="7">
         <v>39942</v>
       </c>
@@ -7200,7 +7200,7 @@
         <v>435052</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" ht="16">
       <c r="A20" s="7">
         <v>39949</v>
       </c>
@@ -7218,7 +7218,7 @@
         <v>438329</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" ht="16">
       <c r="A21" s="7">
         <v>39956</v>
       </c>
@@ -7236,7 +7236,7 @@
         <v>451355</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" ht="16">
       <c r="A22" s="7">
         <v>39963</v>
       </c>
@@ -7254,7 +7254,7 @@
         <v>401248</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" ht="16">
       <c r="A23" s="7">
         <v>39970</v>
       </c>
@@ -7272,7 +7272,7 @@
         <v>448743</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" ht="16">
       <c r="A24" s="7">
         <v>39977</v>
       </c>
@@ -7290,7 +7290,7 @@
         <v>451065</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" ht="16">
       <c r="A25" s="7">
         <v>39984</v>
       </c>
@@ -7308,7 +7308,7 @@
         <v>449103</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5" ht="16">
       <c r="A26" s="7">
         <v>39991</v>
       </c>
@@ -7326,7 +7326,7 @@
         <v>444212</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" ht="16">
       <c r="A27" s="7">
         <v>39998</v>
       </c>
@@ -7344,7 +7344,7 @@
         <v>410661</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5" ht="16">
       <c r="A28" s="7">
         <v>40005</v>
       </c>
@@ -7362,7 +7362,7 @@
         <v>439041</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5" ht="16">
       <c r="A29" s="7">
         <v>40012</v>
       </c>
@@ -7380,7 +7380,7 @@
         <v>456926</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:5" ht="16">
       <c r="A30" s="7">
         <v>40019</v>
       </c>
@@ -7398,7 +7398,7 @@
         <v>467395</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:5" ht="16">
       <c r="A31" s="7">
         <v>40026</v>
       </c>
@@ -7416,7 +7416,7 @@
         <v>468150</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:5" ht="16">
       <c r="A32" s="7">
         <v>40033</v>
       </c>
@@ -7434,7 +7434,7 @@
         <v>469814</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:5" ht="16">
       <c r="A33" s="7">
         <v>40040</v>
       </c>
@@ -7452,7 +7452,7 @@
         <v>469727</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:5" ht="16">
       <c r="A34" s="7">
         <v>40047</v>
       </c>
@@ -7470,7 +7470,7 @@
         <v>472644</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:5" ht="16">
       <c r="A35" s="7">
         <v>40054</v>
       </c>
@@ -7488,7 +7488,7 @@
         <v>488273</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:5" ht="16">
       <c r="A36" s="7">
         <v>40061</v>
       </c>
@@ -7506,7 +7506,7 @@
         <v>486009</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:5" ht="16">
       <c r="A37" s="7">
         <v>40068</v>
       </c>
@@ -7524,7 +7524,7 @@
         <v>439238</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:5" ht="16">
       <c r="A38" s="7">
         <v>40075</v>
       </c>
@@ -7542,7 +7542,7 @@
         <v>487236</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:5" ht="16">
       <c r="A39" s="7">
         <v>40082</v>
       </c>
@@ -7560,7 +7560,7 @@
         <v>477434</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:5" ht="16">
       <c r="A40" s="7">
         <v>40089</v>
       </c>
@@ -7578,7 +7578,7 @@
         <v>484157</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:5" ht="16">
       <c r="A41" s="7">
         <v>40096</v>
       </c>
@@ -7596,7 +7596,7 @@
         <v>481944</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:5" ht="16">
       <c r="A42" s="7">
         <v>40103</v>
       </c>
@@ -7614,7 +7614,7 @@
         <v>481827</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:5" ht="16">
       <c r="A43" s="7">
         <v>40110</v>
       </c>
@@ -7632,7 +7632,7 @@
         <v>483850</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:5" ht="16">
       <c r="A44" s="7">
         <v>40117</v>
       </c>
@@ -7650,7 +7650,7 @@
         <v>479450</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:5" ht="16">
       <c r="A45" s="7">
         <v>40124</v>
       </c>
@@ -7668,7 +7668,7 @@
         <v>481493</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:5" ht="16">
       <c r="A46" s="7">
         <v>40131</v>
       </c>
@@ -7686,7 +7686,7 @@
         <v>489073</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:5" ht="16">
       <c r="A47" s="7">
         <v>40138</v>
       </c>
@@ -7704,7 +7704,7 @@
         <v>500284</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:5" ht="16">
       <c r="A48" s="7">
         <v>40145</v>
       </c>
@@ -7722,7 +7722,7 @@
         <v>412036</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:5" ht="16">
       <c r="A49" s="7">
         <v>40152</v>
       </c>
@@ -7740,7 +7740,7 @@
         <v>491440</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:5" ht="16">
       <c r="A50" s="7">
         <v>40159</v>
       </c>
@@ -7758,7 +7758,7 @@
         <v>464948</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:5" ht="16">
       <c r="A51" s="7">
         <v>40166</v>
       </c>
@@ -7776,7 +7776,7 @@
         <v>481426</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:5" ht="16">
       <c r="A52" s="7">
         <v>40173</v>
       </c>
@@ -7794,7 +7794,7 @@
         <v>339702</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:5" ht="16">
       <c r="A53" s="7">
         <v>40180</v>
       </c>
@@ -7812,7 +7812,7 @@
         <v>376455</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:5" ht="16">
       <c r="A54" s="7">
         <v>40187</v>
       </c>
@@ -7830,7 +7830,7 @@
         <v>433584</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:5" ht="16">
       <c r="A55" s="7">
         <v>40194</v>
       </c>
@@ -7848,7 +7848,7 @@
         <v>465758</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:5" ht="16">
       <c r="A56" s="7">
         <v>40201</v>
       </c>
@@ -7866,7 +7866,7 @@
         <v>478227</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:5" ht="16">
       <c r="A57" s="7">
         <v>40208</v>
       </c>
@@ -7884,7 +7884,7 @@
         <v>482390</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:5" ht="16">
       <c r="A58" s="7">
         <v>40215</v>
       </c>
@@ -7902,7 +7902,7 @@
         <v>469221</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:5" ht="16">
       <c r="A59" s="7">
         <v>40222</v>
       </c>
@@ -7920,7 +7920,7 @@
         <v>450177</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:5" ht="16">
       <c r="A60" s="7">
         <v>40229</v>
       </c>
@@ -7938,7 +7938,7 @@
         <v>474203</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:5" ht="16">
       <c r="A61" s="7">
         <v>40236</v>
       </c>
@@ -7956,7 +7956,7 @@
         <v>496078</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:5" ht="16">
       <c r="A62" s="7">
         <v>40243</v>
       </c>
@@ -7974,7 +7974,7 @@
         <v>497456</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:5" ht="16">
       <c r="A63" s="7">
         <v>40250</v>
       </c>
@@ -7992,7 +7992,7 @@
         <v>491463</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:5" ht="16">
       <c r="A64" s="7">
         <v>40257</v>
       </c>
@@ -8010,7 +8010,7 @@
         <v>488939</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:5" ht="16">
       <c r="A65" s="7">
         <v>40264</v>
       </c>
@@ -8028,7 +8028,7 @@
         <v>504028</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:5" ht="16">
       <c r="A66" s="7">
         <v>40271</v>
       </c>
@@ -8061,7 +8061,7 @@
         <v>486474</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:5" ht="16">
       <c r="A67" s="7">
         <v>40278</v>
       </c>
@@ -8079,7 +8079,7 @@
         <v>492044</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:5" ht="16">
       <c r="A68" s="7">
         <v>40285</v>
       </c>
@@ -8097,7 +8097,7 @@
         <v>506502</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:5" ht="16">
       <c r="A69" s="7">
         <v>40292</v>
       </c>
@@ -8115,7 +8115,7 @@
         <v>510565</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:5" ht="16">
       <c r="A70" s="7">
         <v>40299</v>
       </c>
@@ -8133,7 +8133,7 @@
         <v>508731</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:5" ht="16">
       <c r="A71" s="7">
         <v>40306</v>
       </c>
@@ -8151,7 +8151,7 @@
         <v>497714</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:5" ht="16">
       <c r="A72" s="7">
         <v>40313</v>
       </c>
@@ -8169,7 +8169,7 @@
         <v>508469</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:5" ht="16">
       <c r="A73" s="7">
         <v>40320</v>
       </c>
@@ -8187,7 +8187,7 @@
         <v>503232</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:5" ht="16">
       <c r="A74" s="7">
         <v>40327</v>
       </c>
@@ -8205,7 +8205,7 @@
         <v>511776</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:5" ht="16">
       <c r="A75" s="7">
         <v>40334</v>
       </c>
@@ -8223,7 +8223,7 @@
         <v>462009</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:5" ht="16">
       <c r="A76" s="7">
         <v>40341</v>
       </c>
@@ -8241,7 +8241,7 @@
         <v>512048</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:5" ht="16">
       <c r="A77" s="7">
         <v>40348</v>
       </c>
@@ -8259,7 +8259,7 @@
         <v>512898</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:5" ht="16">
       <c r="A78" s="7">
         <v>40355</v>
       </c>
@@ -8277,7 +8277,7 @@
         <v>511945</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:5" ht="16">
       <c r="A79" s="7">
         <v>40362</v>
       </c>
@@ -8295,7 +8295,7 @@
         <v>518063</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:5" ht="16">
       <c r="A80" s="7">
         <v>40369</v>
       </c>
@@ -8313,7 +8313,7 @@
         <v>445917</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:5" ht="16">
       <c r="A81" s="7">
         <v>40376</v>
       </c>
@@ -8331,7 +8331,7 @@
         <v>509860</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:5" ht="16">
       <c r="A82" s="7">
         <v>40383</v>
       </c>
@@ -8349,7 +8349,7 @@
         <v>517297</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:5" ht="16">
       <c r="A83" s="7">
         <v>40390</v>
       </c>
@@ -8367,7 +8367,7 @@
         <v>533187</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:5" ht="16">
       <c r="A84" s="7">
         <v>40397</v>
       </c>
@@ -8385,7 +8385,7 @@
         <v>515715</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:5" ht="16">
       <c r="A85" s="7">
         <v>40404</v>
       </c>
@@ -8403,7 +8403,7 @@
         <v>529715</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:5" ht="16">
       <c r="A86" s="7">
         <v>40411</v>
       </c>
@@ -8421,7 +8421,7 @@
         <v>533038</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:5" ht="16">
       <c r="A87" s="7">
         <v>40418</v>
       </c>
@@ -8439,7 +8439,7 @@
         <v>539552</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:5" ht="16">
       <c r="A88" s="7">
         <v>40425</v>
       </c>
@@ -8457,7 +8457,7 @@
         <v>542006</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:5" ht="16">
       <c r="A89" s="7">
         <v>40432</v>
       </c>
@@ -8475,7 +8475,7 @@
         <v>484380</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:5" ht="16">
       <c r="A90" s="7">
         <v>40439</v>
       </c>
@@ -8493,7 +8493,7 @@
         <v>544692</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:5" ht="16">
       <c r="A91" s="7">
         <v>40446</v>
       </c>
@@ -8511,7 +8511,7 @@
         <v>542075</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:5" ht="16">
       <c r="A92" s="7">
         <v>40453</v>
       </c>
@@ -8529,7 +8529,7 @@
         <v>539646</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:5" ht="16">
       <c r="A93" s="7">
         <v>40460</v>
       </c>
@@ -8547,7 +8547,7 @@
         <v>533301</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:5" ht="16">
       <c r="A94" s="7">
         <v>40467</v>
       </c>
@@ -8565,7 +8565,7 @@
         <v>540844</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:5" ht="16">
       <c r="A95" s="7">
         <v>40474</v>
       </c>
@@ -8583,7 +8583,7 @@
         <v>538461</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:5" ht="16">
       <c r="A96" s="7">
         <v>40481</v>
       </c>
@@ -8601,7 +8601,7 @@
         <v>525601</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:5" ht="16">
       <c r="A97" s="7">
         <v>40488</v>
       </c>
@@ -8619,7 +8619,7 @@
         <v>519134</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:5" ht="16">
       <c r="A98" s="7">
         <v>40495</v>
       </c>
@@ -8637,7 +8637,7 @@
         <v>530157</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:5" ht="16">
       <c r="A99" s="7">
         <v>40502</v>
       </c>
@@ -8655,7 +8655,7 @@
         <v>533989</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:5" ht="16">
       <c r="A100" s="7">
         <v>40509</v>
       </c>
@@ -8673,7 +8673,7 @@
         <v>437911</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:5" ht="17" thickBot="1">
       <c r="A101" s="7">
         <v>40516</v>
       </c>
@@ -8691,7 +8691,7 @@
         <v>539405</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:5" ht="17" thickBot="1">
       <c r="A102" s="11">
         <v>40523</v>
       </c>
@@ -8709,7 +8709,7 @@
         <v>520326</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:5" ht="17" thickBot="1">
       <c r="A103" s="11">
         <v>40530</v>
       </c>
@@ -8727,7 +8727,7 @@
         <v>491896</v>
       </c>
     </row>
-    <row r="104" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:5" ht="17" thickBot="1">
       <c r="A104" s="11">
         <v>40537</v>
       </c>
@@ -8745,7 +8745,7 @@
         <v>433347</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:5" ht="17" thickBot="1">
       <c r="A105" s="11">
         <v>40544</v>
       </c>
@@ -8763,7 +8763,7 @@
         <v>406967</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:5" ht="17" thickBot="1">
       <c r="A106" s="11">
         <v>40551</v>
       </c>
@@ -8781,7 +8781,7 @@
         <v>498773</v>
       </c>
     </row>
-    <row r="107" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:5" ht="17" thickBot="1">
       <c r="A107" s="11">
         <v>40558</v>
       </c>
@@ -8799,7 +8799,7 @@
         <v>496473</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:5" ht="17" thickBot="1">
       <c r="A108" s="11">
         <v>40565</v>
       </c>
@@ -8817,7 +8817,7 @@
         <v>496043</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:5" ht="17" thickBot="1">
       <c r="A109" s="11">
         <v>40572</v>
       </c>
@@ -8835,7 +8835,7 @@
         <v>513889</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:5" ht="17" thickBot="1">
       <c r="A110" s="11">
         <v>40579</v>
       </c>
@@ -8853,7 +8853,7 @@
         <v>465931</v>
       </c>
     </row>
-    <row r="111" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:5" ht="17" thickBot="1">
       <c r="A111" s="11">
         <v>40586</v>
       </c>
@@ -8871,7 +8871,7 @@
         <v>502078</v>
       </c>
     </row>
-    <row r="112" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:5" ht="17" thickBot="1">
       <c r="A112" s="11">
         <v>40593</v>
       </c>
@@ -8889,7 +8889,7 @@
         <v>530973</v>
       </c>
     </row>
-    <row r="113" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:5" ht="17" thickBot="1">
       <c r="A113" s="11">
         <v>40600</v>
       </c>
@@ -8907,7 +8907,7 @@
         <v>516841</v>
       </c>
     </row>
-    <row r="114" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:5" ht="17" thickBot="1">
       <c r="A114" s="11">
         <v>40607</v>
       </c>
@@ -8925,7 +8925,7 @@
         <v>515296</v>
       </c>
     </row>
-    <row r="115" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:5" ht="17" thickBot="1">
       <c r="A115" s="11">
         <v>40614</v>
       </c>
@@ -8943,7 +8943,7 @@
         <v>508992</v>
       </c>
     </row>
-    <row r="116" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:5" ht="17" thickBot="1">
       <c r="A116" s="11">
         <v>40621</v>
       </c>
@@ -8961,7 +8961,7 @@
         <v>516560</v>
       </c>
     </row>
-    <row r="117" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:5" ht="17" thickBot="1">
       <c r="A117" s="11">
         <v>40628</v>
       </c>
@@ -8979,7 +8979,7 @@
         <v>522937</v>
       </c>
     </row>
-    <row r="118" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:5" ht="17" thickBot="1">
       <c r="A118" s="11">
         <v>40635</v>
       </c>
@@ -8997,7 +8997,7 @@
         <v>540213</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:5" ht="17" thickBot="1">
       <c r="A119" s="11">
         <v>40642</v>
       </c>
@@ -9015,7 +9015,7 @@
         <v>522511</v>
       </c>
     </row>
-    <row r="120" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:5" ht="17" thickBot="1">
       <c r="A120" s="11">
         <v>40649</v>
       </c>
@@ -9033,7 +9033,7 @@
         <v>525886</v>
       </c>
     </row>
-    <row r="121" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:5" ht="17" thickBot="1">
       <c r="A121" s="11">
         <v>40656</v>
       </c>
@@ -9051,7 +9051,7 @@
         <v>518374</v>
       </c>
     </row>
-    <row r="122" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:5" ht="17" thickBot="1">
       <c r="A122" s="11">
         <v>40663</v>
       </c>
@@ -9069,7 +9069,7 @@
         <v>525024</v>
       </c>
     </row>
-    <row r="123" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:5" ht="17" thickBot="1">
       <c r="A123" s="11">
         <v>40670</v>
       </c>
@@ -9087,7 +9087,7 @@
         <v>514038</v>
       </c>
     </row>
-    <row r="124" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:5" ht="17" thickBot="1">
       <c r="A124" s="11">
         <v>40677</v>
       </c>
@@ -9105,7 +9105,7 @@
         <v>526146</v>
       </c>
     </row>
-    <row r="125" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:5" ht="17" thickBot="1">
       <c r="A125" s="11">
         <v>40684</v>
       </c>
@@ -9123,7 +9123,7 @@
         <v>529383</v>
       </c>
     </row>
-    <row r="126" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:5" ht="17" thickBot="1">
       <c r="A126" s="13">
         <v>40691</v>
       </c>
@@ -9141,7 +9141,7 @@
         <v>522717</v>
       </c>
     </row>
-    <row r="127" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:5" ht="17" thickBot="1">
       <c r="A127" s="11">
         <v>40698</v>
       </c>
@@ -9159,7 +9159,7 @@
         <v>479149</v>
       </c>
     </row>
-    <row r="128" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:5" ht="17" thickBot="1">
       <c r="A128" s="11">
         <v>40705</v>
       </c>
@@ -9177,7 +9177,7 @@
         <v>527603</v>
       </c>
     </row>
-    <row r="129" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:5" ht="17" thickBot="1">
       <c r="A129" s="11">
         <v>40712</v>
       </c>
@@ -9195,7 +9195,7 @@
         <v>531992</v>
       </c>
     </row>
-    <row r="130" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:5" ht="17" thickBot="1">
       <c r="A130" s="11">
         <v>40719</v>
       </c>
@@ -9228,7 +9228,7 @@
         <v>519337</v>
       </c>
     </row>
-    <row r="131" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:5" ht="17" thickBot="1">
       <c r="A131" s="11">
         <v>40726</v>
       </c>
@@ -9246,7 +9246,7 @@
         <v>522931</v>
       </c>
     </row>
-    <row r="132" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:5" ht="17" thickBot="1">
       <c r="A132" s="11">
         <v>40733</v>
       </c>
@@ -9264,7 +9264,7 @@
         <v>438193</v>
       </c>
     </row>
-    <row r="133" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:5" ht="17" thickBot="1">
       <c r="A133" s="11">
         <v>40740</v>
       </c>
@@ -9282,7 +9282,7 @@
         <v>511711</v>
       </c>
     </row>
-    <row r="134" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:5" ht="17" thickBot="1">
       <c r="A134" s="11">
         <v>40747</v>
       </c>
@@ -9300,7 +9300,7 @@
         <v>524090</v>
       </c>
     </row>
-    <row r="135" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:5" ht="17" thickBot="1">
       <c r="A135" s="11">
         <v>40754</v>
       </c>
@@ -9318,7 +9318,7 @@
         <v>533337</v>
       </c>
     </row>
-    <row r="136" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:5" ht="17" thickBot="1">
       <c r="A136" s="11">
         <v>40761</v>
       </c>
@@ -9336,7 +9336,7 @@
         <v>522889</v>
       </c>
     </row>
-    <row r="137" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:5" ht="17" thickBot="1">
       <c r="A137" s="11">
         <v>40768</v>
       </c>
@@ -9354,7 +9354,7 @@
         <v>527864</v>
       </c>
     </row>
-    <row r="138" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:5" ht="17" thickBot="1">
       <c r="A138" s="11">
         <v>40775</v>
       </c>
@@ -9372,7 +9372,7 @@
         <v>539201</v>
       </c>
     </row>
-    <row r="139" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:5" ht="17" thickBot="1">
       <c r="A139" s="11">
         <v>40782</v>
       </c>
@@ -9390,7 +9390,7 @@
         <v>535994</v>
       </c>
     </row>
-    <row r="140" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:5" ht="17" thickBot="1">
       <c r="A140" s="11">
         <v>40789</v>
       </c>
@@ -9408,7 +9408,7 @@
         <v>537201</v>
       </c>
     </row>
-    <row r="141" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:5" ht="17" thickBot="1">
       <c r="A141" s="11">
         <v>40796</v>
       </c>
@@ -9426,7 +9426,7 @@
         <v>486472</v>
       </c>
     </row>
-    <row r="142" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:5" ht="17" thickBot="1">
       <c r="A142" s="11">
         <v>40803</v>
       </c>
@@ -9444,7 +9444,7 @@
         <v>542164</v>
       </c>
     </row>
-    <row r="143" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:5" ht="17" thickBot="1">
       <c r="A143" s="11">
         <v>40810</v>
       </c>
@@ -9462,7 +9462,7 @@
         <v>553535</v>
       </c>
     </row>
-    <row r="144" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:5" ht="17" thickBot="1">
       <c r="A144" s="11">
         <v>40817</v>
       </c>
@@ -9480,7 +9480,7 @@
         <v>563034</v>
       </c>
     </row>
-    <row r="145" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="145" spans="1:5" ht="17" thickBot="1">
       <c r="A145" s="11">
         <v>40824</v>
       </c>
@@ -9498,7 +9498,7 @@
         <v>544499</v>
       </c>
     </row>
-    <row r="146" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="146" spans="1:5" ht="17" thickBot="1">
       <c r="A146" s="11">
         <v>40831</v>
       </c>
@@ -9516,7 +9516,7 @@
         <v>547752</v>
       </c>
     </row>
-    <row r="147" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:5" ht="17" thickBot="1">
       <c r="A147" s="11">
         <v>40838</v>
       </c>
@@ -9534,7 +9534,7 @@
         <v>547268</v>
       </c>
     </row>
-    <row r="148" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="148" spans="1:5" ht="17" thickBot="1">
       <c r="A148" s="11">
         <v>40845</v>
       </c>
@@ -9552,7 +9552,7 @@
         <v>551674</v>
       </c>
     </row>
-    <row r="149" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:5" ht="17" thickBot="1">
       <c r="A149" s="11">
         <v>40852</v>
       </c>
@@ -9570,7 +9570,7 @@
         <v>537645</v>
       </c>
     </row>
-    <row r="150" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:5" ht="17" thickBot="1">
       <c r="A150" s="11">
         <v>40859</v>
       </c>
@@ -9588,7 +9588,7 @@
         <v>544563</v>
       </c>
     </row>
-    <row r="151" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:5" ht="17" thickBot="1">
       <c r="A151" s="13">
         <v>40866</v>
       </c>
@@ -9606,7 +9606,7 @@
         <v>545153</v>
       </c>
     </row>
-    <row r="152" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:5" ht="17" thickBot="1">
       <c r="A152" s="11">
         <v>40873</v>
       </c>
@@ -9624,7 +9624,7 @@
         <v>456170</v>
       </c>
     </row>
-    <row r="153" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:5" ht="17" thickBot="1">
       <c r="A153" s="11">
         <v>40880</v>
       </c>
@@ -9642,7 +9642,7 @@
         <v>555353</v>
       </c>
     </row>
-    <row r="154" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:5" ht="17" thickBot="1">
       <c r="A154" s="11">
         <v>40887</v>
       </c>
@@ -9660,7 +9660,7 @@
         <v>538299</v>
       </c>
     </row>
-    <row r="155" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:5" ht="17" thickBot="1">
       <c r="A155" s="11">
         <v>40894</v>
       </c>
@@ -9678,7 +9678,7 @@
         <v>537699</v>
       </c>
     </row>
-    <row r="156" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:5" ht="17" thickBot="1">
       <c r="A156" s="11">
         <v>40901</v>
       </c>
@@ -9696,7 +9696,7 @@
         <v>505089</v>
       </c>
     </row>
-    <row r="157" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="157" spans="1:5" ht="17" thickBot="1">
       <c r="A157" s="11">
         <v>40908</v>
       </c>
@@ -9714,7 +9714,7 @@
         <v>426883</v>
       </c>
     </row>
-    <row r="158" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="158" spans="1:5" ht="17" thickBot="1">
       <c r="A158" s="11">
         <v>40915</v>
       </c>
@@ -9732,7 +9732,7 @@
         <v>468674</v>
       </c>
     </row>
-    <row r="159" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="159" spans="1:5" ht="17" thickBot="1">
       <c r="A159" s="11">
         <v>40922</v>
       </c>
@@ -9750,7 +9750,7 @@
         <v>527651</v>
       </c>
     </row>
-    <row r="160" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="160" spans="1:5" ht="17" thickBot="1">
       <c r="A160" s="11">
         <v>40929</v>
       </c>
@@ -9768,7 +9768,7 @@
         <v>507440</v>
       </c>
     </row>
-    <row r="161" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="161" spans="1:5" ht="17" thickBot="1">
       <c r="A161" s="11">
         <v>40936</v>
       </c>
@@ -9786,7 +9786,7 @@
         <v>518682</v>
       </c>
     </row>
-    <row r="162" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:5" ht="17" thickBot="1">
       <c r="A162" s="11">
         <v>40943</v>
       </c>
@@ -9804,7 +9804,7 @@
         <v>517136</v>
       </c>
     </row>
-    <row r="163" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="163" spans="1:5" ht="17" thickBot="1">
       <c r="A163" s="11">
         <v>40950</v>
       </c>
@@ -9822,7 +9822,7 @@
         <v>506708</v>
       </c>
     </row>
-    <row r="164" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="164" spans="1:5" ht="17" thickBot="1">
       <c r="A164" s="11">
         <v>40957</v>
       </c>
@@ -9840,7 +9840,7 @@
         <v>502992</v>
       </c>
     </row>
-    <row r="165" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="165" spans="1:5" ht="17" thickBot="1">
       <c r="A165" s="11">
         <v>40964</v>
       </c>
@@ -9858,7 +9858,7 @@
         <v>496046</v>
       </c>
     </row>
-    <row r="166" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="166" spans="1:5" ht="17" thickBot="1">
       <c r="A166" s="11">
         <v>40971</v>
       </c>
@@ -9876,7 +9876,7 @@
         <v>510568</v>
       </c>
     </row>
-    <row r="167" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="167" spans="1:5" ht="17" thickBot="1">
       <c r="A167" s="11">
         <v>40978</v>
       </c>
@@ -9894,7 +9894,7 @@
         <v>504767</v>
       </c>
     </row>
-    <row r="168" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="168" spans="1:5" ht="17" thickBot="1">
       <c r="A168" s="11">
         <v>40985</v>
       </c>
@@ -9912,7 +9912,7 @@
         <v>505558</v>
       </c>
     </row>
-    <row r="169" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="169" spans="1:5" ht="17" thickBot="1">
       <c r="A169" s="11">
         <v>40992</v>
       </c>
@@ -9930,7 +9930,7 @@
         <v>510794</v>
       </c>
     </row>
-    <row r="170" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="170" spans="1:5" ht="17" thickBot="1">
       <c r="A170" s="11">
         <v>40999</v>
       </c>
@@ -9948,7 +9948,7 @@
         <v>529734</v>
       </c>
     </row>
-    <row r="171" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="171" spans="1:5" ht="17" thickBot="1">
       <c r="A171" s="11">
         <v>41006</v>
       </c>
@@ -9966,7 +9966,7 @@
         <v>502127</v>
       </c>
     </row>
-    <row r="172" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="172" spans="1:5" ht="17" thickBot="1">
       <c r="A172" s="11">
         <v>41013</v>
       </c>
@@ -9984,7 +9984,7 @@
         <v>510946</v>
       </c>
     </row>
-    <row r="173" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="173" spans="1:5" ht="17" thickBot="1">
       <c r="A173" s="11">
         <v>41020</v>
       </c>
@@ -10002,7 +10002,7 @@
         <v>521538</v>
       </c>
     </row>
-    <row r="174" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="174" spans="1:5" ht="17" thickBot="1">
       <c r="A174" s="11">
         <v>41027</v>
       </c>
@@ -10020,7 +10020,7 @@
         <v>525445</v>
       </c>
     </row>
-    <row r="175" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="175" spans="1:5" ht="17" thickBot="1">
       <c r="A175" s="11">
         <v>41034</v>
       </c>
@@ -10038,7 +10038,7 @@
         <v>515167</v>
       </c>
     </row>
-    <row r="176" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="176" spans="1:5" ht="17" thickBot="1">
       <c r="A176" s="13">
         <v>41041</v>
       </c>
@@ -10056,7 +10056,7 @@
         <v>518043</v>
       </c>
     </row>
-    <row r="177" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="177" spans="1:5" ht="17" thickBot="1">
       <c r="A177" s="11">
         <v>41048</v>
       </c>
@@ -10074,7 +10074,7 @@
         <v>522229</v>
       </c>
     </row>
-    <row r="178" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="178" spans="1:5" ht="17" thickBot="1">
       <c r="A178" s="11">
         <v>41055</v>
       </c>
@@ -10092,7 +10092,7 @@
         <v>536107</v>
       </c>
     </row>
-    <row r="179" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="179" spans="1:5" ht="17" thickBot="1">
       <c r="A179" s="11">
         <v>41062</v>
       </c>
@@ -10110,7 +10110,7 @@
         <v>479118</v>
       </c>
     </row>
-    <row r="180" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="180" spans="1:5" ht="17" thickBot="1">
       <c r="A180" s="11">
         <v>41069</v>
       </c>
@@ -10128,7 +10128,7 @@
         <v>531835</v>
       </c>
     </row>
-    <row r="181" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="181" spans="1:5" ht="17" thickBot="1">
       <c r="A181" s="11">
         <v>41076</v>
       </c>
@@ -10146,7 +10146,7 @@
         <v>537011</v>
       </c>
     </row>
-    <row r="182" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="182" spans="1:5" ht="17" thickBot="1">
       <c r="A182" s="11">
         <v>41083</v>
       </c>
@@ -10164,7 +10164,7 @@
         <v>534858</v>
       </c>
     </row>
-    <row r="183" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="183" spans="1:5" ht="17" thickBot="1">
       <c r="A183" s="11">
         <v>41090</v>
       </c>
@@ -10182,7 +10182,7 @@
         <v>532131</v>
       </c>
     </row>
-    <row r="184" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="184" spans="1:5" ht="17" thickBot="1">
       <c r="A184" s="11">
         <v>41097</v>
       </c>
@@ -10200,7 +10200,7 @@
         <v>446518</v>
       </c>
     </row>
-    <row r="185" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="185" spans="1:5" ht="17" thickBot="1">
       <c r="A185" s="11">
         <v>41104</v>
       </c>
@@ -10218,7 +10218,7 @@
         <v>532071</v>
       </c>
     </row>
-    <row r="186" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="186" spans="1:5" ht="17" thickBot="1">
       <c r="A186" s="11">
         <v>41111</v>
       </c>
@@ -10236,7 +10236,7 @@
         <v>532729</v>
       </c>
     </row>
-    <row r="187" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="187" spans="1:5" ht="17" thickBot="1">
       <c r="A187" s="11">
         <v>41118</v>
       </c>
@@ -10254,7 +10254,7 @@
         <v>538486</v>
       </c>
     </row>
-    <row r="188" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="188" spans="1:5" ht="17" thickBot="1">
       <c r="A188" s="11">
         <v>41125</v>
       </c>
@@ -10272,7 +10272,7 @@
         <v>531490</v>
       </c>
     </row>
-    <row r="189" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="189" spans="1:5" ht="17" thickBot="1">
       <c r="A189" s="11">
         <v>41132</v>
       </c>
@@ -10290,7 +10290,7 @@
         <v>532202</v>
       </c>
     </row>
-    <row r="190" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="190" spans="1:5" ht="17" thickBot="1">
       <c r="A190" s="11">
         <v>41139</v>
       </c>
@@ -10308,7 +10308,7 @@
         <v>541140</v>
       </c>
     </row>
-    <row r="191" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="191" spans="1:5" ht="17" thickBot="1">
       <c r="A191" s="11">
         <v>41146</v>
       </c>
@@ -10326,7 +10326,7 @@
         <v>545406</v>
       </c>
     </row>
-    <row r="192" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="192" spans="1:5" ht="17" thickBot="1">
       <c r="A192" s="11">
         <v>41153</v>
       </c>
@@ -10344,7 +10344,7 @@
         <v>541845</v>
       </c>
     </row>
-    <row r="193" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="193" spans="1:5" ht="17" thickBot="1">
       <c r="A193" s="11">
         <v>41160</v>
       </c>
@@ -10362,7 +10362,7 @@
         <v>486818</v>
       </c>
     </row>
-    <row r="194" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="194" spans="1:5" ht="17" thickBot="1">
       <c r="A194" s="11">
         <v>41167</v>
       </c>
@@ -10395,7 +10395,7 @@
         <v>543250</v>
       </c>
     </row>
-    <row r="195" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="195" spans="1:5" ht="17" thickBot="1">
       <c r="A195" s="11">
         <v>41174</v>
       </c>
@@ -10413,7 +10413,7 @@
         <v>542897</v>
       </c>
     </row>
-    <row r="196" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="196" spans="1:5" ht="17" thickBot="1">
       <c r="A196" s="11">
         <v>41181</v>
       </c>
@@ -10431,7 +10431,7 @@
         <v>552468</v>
       </c>
     </row>
-    <row r="197" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="197" spans="1:5" ht="17" thickBot="1">
       <c r="A197" s="11">
         <v>41188</v>
       </c>
@@ -10449,7 +10449,7 @@
         <v>534553</v>
       </c>
     </row>
-    <row r="198" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="198" spans="1:5" ht="17" thickBot="1">
       <c r="A198" s="11">
         <v>41195</v>
       </c>
@@ -10467,7 +10467,7 @@
         <v>535915</v>
       </c>
     </row>
-    <row r="199" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="199" spans="1:5" ht="17" thickBot="1">
       <c r="A199" s="11">
         <v>41202</v>
       </c>
@@ -10485,7 +10485,7 @@
         <v>542674</v>
       </c>
     </row>
-    <row r="200" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="200" spans="1:5" ht="17" thickBot="1">
       <c r="A200" s="11">
         <v>41209</v>
       </c>
@@ -10503,7 +10503,7 @@
         <v>540290</v>
       </c>
     </row>
-    <row r="201" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="201" spans="1:5" ht="17" thickBot="1">
       <c r="A201" s="13">
         <v>41216</v>
       </c>
@@ -10521,7 +10521,7 @@
         <v>502697</v>
       </c>
     </row>
-    <row r="202" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="202" spans="1:5" ht="17" thickBot="1">
       <c r="A202" s="11">
         <v>41223</v>
       </c>
@@ -10539,7 +10539,7 @@
         <v>532945</v>
       </c>
     </row>
-    <row r="203" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="203" spans="1:5" ht="17" thickBot="1">
       <c r="A203" s="11">
         <v>41230</v>
       </c>
@@ -10557,7 +10557,7 @@
         <v>537832</v>
       </c>
     </row>
-    <row r="204" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="204" spans="1:5" ht="17" thickBot="1">
       <c r="A204" s="11">
         <v>41237</v>
       </c>
@@ -10575,7 +10575,7 @@
         <v>447469</v>
       </c>
     </row>
-    <row r="205" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="205" spans="1:5" ht="17" thickBot="1">
       <c r="A205" s="11">
         <v>41244</v>
       </c>
@@ -10593,7 +10593,7 @@
         <v>547119</v>
       </c>
     </row>
-    <row r="206" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="206" spans="1:5" ht="17" thickBot="1">
       <c r="A206" s="11">
         <v>41251</v>
       </c>
@@ -10611,7 +10611,7 @@
         <v>532304</v>
       </c>
     </row>
-    <row r="207" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="207" spans="1:5" ht="17" thickBot="1">
       <c r="A207" s="11">
         <v>41258</v>
       </c>
@@ -10629,7 +10629,7 @@
         <v>544625</v>
       </c>
     </row>
-    <row r="208" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="208" spans="1:5" ht="17" thickBot="1">
       <c r="A208" s="11">
         <v>41265</v>
       </c>
@@ -10647,7 +10647,7 @@
         <v>530342</v>
       </c>
     </row>
-    <row r="209" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="209" spans="1:5" ht="17" thickBot="1">
       <c r="A209" s="11">
         <v>41272</v>
       </c>
@@ -10665,7 +10665,7 @@
         <v>367721</v>
       </c>
     </row>
-    <row r="210" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="210" spans="1:5" ht="17" thickBot="1">
       <c r="A210" s="11">
         <v>41279</v>
       </c>
@@ -10683,7 +10683,7 @@
         <v>419999</v>
       </c>
     </row>
-    <row r="211" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="211" spans="1:5" ht="17" thickBot="1">
       <c r="A211" s="11">
         <v>41286</v>
       </c>
@@ -10701,7 +10701,7 @@
         <v>532789</v>
       </c>
     </row>
-    <row r="212" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="212" spans="1:5" ht="17" thickBot="1">
       <c r="A212" s="11">
         <v>41293</v>
       </c>
@@ -10719,7 +10719,7 @@
         <v>526887</v>
       </c>
     </row>
-    <row r="213" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="213" spans="1:5" ht="17" thickBot="1">
       <c r="A213" s="11">
         <v>41300</v>
       </c>
@@ -10737,7 +10737,7 @@
         <v>504628</v>
       </c>
     </row>
-    <row r="214" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="214" spans="1:5" ht="17" thickBot="1">
       <c r="A214" s="11">
         <v>41307</v>
       </c>
@@ -10755,7 +10755,7 @@
         <v>523931</v>
       </c>
     </row>
-    <row r="215" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="215" spans="1:5" ht="17" thickBot="1">
       <c r="A215" s="11">
         <v>41314</v>
       </c>
@@ -10773,7 +10773,7 @@
         <v>518048</v>
       </c>
     </row>
-    <row r="216" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="216" spans="1:5" ht="17" thickBot="1">
       <c r="A216" s="11">
         <v>41321</v>
       </c>
@@ -10791,7 +10791,7 @@
         <v>529674</v>
       </c>
     </row>
-    <row r="217" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="217" spans="1:5" ht="17" thickBot="1">
       <c r="A217" s="11">
         <v>41328</v>
       </c>
@@ -10809,7 +10809,7 @@
         <v>516142</v>
       </c>
     </row>
-    <row r="218" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="218" spans="1:5" ht="17" thickBot="1">
       <c r="A218" s="11">
         <v>41335</v>
       </c>
@@ -10827,7 +10827,7 @@
         <v>533057</v>
       </c>
     </row>
-    <row r="219" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="219" spans="1:5" ht="17" thickBot="1">
       <c r="A219" s="11">
         <v>41342</v>
       </c>
@@ -10845,7 +10845,7 @@
         <v>511872</v>
       </c>
     </row>
-    <row r="220" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="220" spans="1:5" ht="17" thickBot="1">
       <c r="A220" s="11">
         <v>41349</v>
       </c>
@@ -10863,7 +10863,7 @@
         <v>509430</v>
       </c>
     </row>
-    <row r="221" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="221" spans="1:5" ht="17" thickBot="1">
       <c r="A221" s="11">
         <v>41356</v>
       </c>
@@ -10881,7 +10881,7 @@
         <v>514379</v>
       </c>
     </row>
-    <row r="222" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="222" spans="1:5" ht="17" thickBot="1">
       <c r="A222" s="11">
         <v>41363</v>
       </c>
@@ -10899,7 +10899,7 @@
         <v>514954</v>
       </c>
     </row>
-    <row r="223" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="223" spans="1:5" ht="17" thickBot="1">
       <c r="A223" s="11">
         <v>41370</v>
       </c>
@@ -10917,7 +10917,7 @@
         <v>512396</v>
       </c>
     </row>
-    <row r="224" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="224" spans="1:5" ht="17" thickBot="1">
       <c r="A224" s="11">
         <v>41377</v>
       </c>
@@ -10935,7 +10935,7 @@
         <v>517662</v>
       </c>
     </row>
-    <row r="225" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="225" spans="1:5" ht="17" thickBot="1">
       <c r="A225" s="11">
         <v>41384</v>
       </c>
@@ -10953,7 +10953,7 @@
         <v>517360</v>
       </c>
     </row>
-    <row r="226" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="226" spans="1:5" ht="17" thickBot="1">
       <c r="A226" s="13">
         <v>41391</v>
       </c>
@@ -10971,7 +10971,7 @@
         <v>523207</v>
       </c>
     </row>
-    <row r="227" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="227" spans="1:5" ht="17" thickBot="1">
       <c r="A227" s="11">
         <v>41398</v>
       </c>
@@ -10989,7 +10989,7 @@
         <v>529594</v>
       </c>
     </row>
-    <row r="228" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="228" spans="1:5" ht="17" thickBot="1">
       <c r="A228" s="11">
         <v>41405</v>
       </c>
@@ -11007,7 +11007,7 @@
         <v>529252</v>
       </c>
     </row>
-    <row r="229" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="229" spans="1:5" ht="17" thickBot="1">
       <c r="A229" s="11">
         <v>41412</v>
       </c>
@@ -11025,7 +11025,7 @@
         <v>535835</v>
       </c>
     </row>
-    <row r="230" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="230" spans="1:5" ht="17" thickBot="1">
       <c r="A230" s="11">
         <v>41419</v>
       </c>
@@ -11043,7 +11043,7 @@
         <v>529937</v>
       </c>
     </row>
-    <row r="231" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="231" spans="1:5" ht="17" thickBot="1">
       <c r="A231" s="11">
         <v>41426</v>
       </c>
@@ -11061,7 +11061,7 @@
         <v>491082</v>
       </c>
     </row>
-    <row r="232" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="232" spans="1:5" ht="17" thickBot="1">
       <c r="A232" s="11">
         <v>41433</v>
       </c>
@@ -11079,7 +11079,7 @@
         <v>530890</v>
       </c>
     </row>
-    <row r="233" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="233" spans="1:5" ht="17" thickBot="1">
       <c r="A233" s="11">
         <v>41440</v>
       </c>
@@ -11097,7 +11097,7 @@
         <v>543145</v>
       </c>
     </row>
-    <row r="234" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="234" spans="1:5" ht="17" thickBot="1">
       <c r="A234" s="11">
         <v>41447</v>
       </c>
@@ -11115,7 +11115,7 @@
         <v>541031</v>
       </c>
     </row>
-    <row r="235" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="235" spans="1:5" ht="17" thickBot="1">
       <c r="A235" s="11">
         <v>41454</v>
       </c>
@@ -11133,7 +11133,7 @@
         <v>531040</v>
       </c>
     </row>
-    <row r="236" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="236" spans="1:5" ht="17" thickBot="1">
       <c r="A236" s="11">
         <v>41461</v>
       </c>
@@ -11151,7 +11151,7 @@
         <v>453493</v>
       </c>
     </row>
-    <row r="237" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="237" spans="1:5" ht="17" thickBot="1">
       <c r="A237" s="11">
         <v>41468</v>
       </c>
@@ -11169,7 +11169,7 @@
         <v>525333</v>
       </c>
     </row>
-    <row r="238" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="238" spans="1:5" ht="17" thickBot="1">
       <c r="A238" s="11">
         <v>41475</v>
       </c>
@@ -11187,7 +11187,7 @@
         <v>531357</v>
       </c>
     </row>
-    <row r="239" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="239" spans="1:5" ht="17" thickBot="1">
       <c r="A239" s="11">
         <v>41482</v>
       </c>
@@ -11205,7 +11205,7 @@
         <v>551911</v>
       </c>
     </row>
-    <row r="240" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="240" spans="1:5" ht="17" thickBot="1">
       <c r="A240" s="11">
         <v>41489</v>
       </c>
@@ -11223,7 +11223,7 @@
         <v>542396</v>
       </c>
     </row>
-    <row r="241" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="241" spans="1:5" ht="17" thickBot="1">
       <c r="A241" s="11">
         <v>41496</v>
       </c>
@@ -11241,7 +11241,7 @@
         <v>546772</v>
       </c>
     </row>
-    <row r="242" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="242" spans="1:5" ht="17" thickBot="1">
       <c r="A242" s="11">
         <v>41503</v>
       </c>
@@ -11259,7 +11259,7 @@
         <v>552359</v>
       </c>
     </row>
-    <row r="243" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="243" spans="1:5" ht="17" thickBot="1">
       <c r="A243" s="11">
         <v>41510</v>
       </c>
@@ -11277,7 +11277,7 @@
         <v>548969</v>
       </c>
     </row>
-    <row r="244" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="244" spans="1:5" ht="17" thickBot="1">
       <c r="A244" s="11">
         <v>41517</v>
       </c>
@@ -11295,7 +11295,7 @@
         <v>561698</v>
       </c>
     </row>
-    <row r="245" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="245" spans="1:5" ht="17" thickBot="1">
       <c r="A245" s="11">
         <v>41524</v>
       </c>
@@ -11313,7 +11313,7 @@
         <v>507493</v>
       </c>
     </row>
-    <row r="246" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="246" spans="1:5" ht="17" thickBot="1">
       <c r="A246" s="11">
         <v>41531</v>
       </c>
@@ -11331,7 +11331,7 @@
         <v>562094</v>
       </c>
     </row>
-    <row r="247" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="247" spans="1:5" ht="17" thickBot="1">
       <c r="A247" s="11">
         <v>41538</v>
       </c>
@@ -11349,7 +11349,7 @@
         <v>551057</v>
       </c>
     </row>
-    <row r="248" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="248" spans="1:5" ht="17" thickBot="1">
       <c r="A248" s="11">
         <v>41545</v>
       </c>
@@ -11367,7 +11367,7 @@
         <v>566662</v>
       </c>
     </row>
-    <row r="249" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="249" spans="1:5" ht="17" thickBot="1">
       <c r="A249" s="11">
         <v>41552</v>
       </c>
@@ -11385,7 +11385,7 @@
         <v>545708</v>
       </c>
     </row>
-    <row r="250" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="250" spans="1:5" ht="17" thickBot="1">
       <c r="A250" s="11">
         <v>41559</v>
       </c>
@@ -11403,7 +11403,7 @@
         <v>546211</v>
       </c>
     </row>
-    <row r="251" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="251" spans="1:5" ht="17" thickBot="1">
       <c r="A251" s="13">
         <v>41566</v>
       </c>
@@ -11421,7 +11421,7 @@
         <v>553943</v>
       </c>
     </row>
-    <row r="252" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="252" spans="1:5" ht="17" thickBot="1">
       <c r="A252" s="11">
         <v>41573</v>
       </c>
@@ -11439,7 +11439,7 @@
         <v>558686</v>
       </c>
     </row>
-    <row r="253" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="253" spans="1:5" ht="17" thickBot="1">
       <c r="A253" s="11">
         <v>41580</v>
       </c>
@@ -11457,7 +11457,7 @@
         <v>556662</v>
       </c>
     </row>
-    <row r="254" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="254" spans="1:5" ht="17" thickBot="1">
       <c r="A254" s="11">
         <v>41587</v>
       </c>
@@ -11475,7 +11475,7 @@
         <v>562840</v>
       </c>
     </row>
-    <row r="255" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="255" spans="1:5" ht="17" thickBot="1">
       <c r="A255" s="11">
         <v>41594</v>
       </c>
@@ -11493,7 +11493,7 @@
         <v>562206</v>
       </c>
     </row>
-    <row r="256" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="256" spans="1:5" ht="17" thickBot="1">
       <c r="A256" s="11">
         <v>41601</v>
       </c>
@@ -11511,7 +11511,7 @@
         <v>564340</v>
       </c>
     </row>
-    <row r="257" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="257" spans="1:5" ht="17" thickBot="1">
       <c r="A257" s="11">
         <v>41608</v>
       </c>
@@ -11529,7 +11529,7 @@
         <v>463516</v>
       </c>
     </row>
-    <row r="258" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="258" spans="1:5" ht="17" thickBot="1">
       <c r="A258" s="11">
         <v>41615</v>
       </c>
@@ -11562,7 +11562,7 @@
         <v>541978</v>
       </c>
     </row>
-    <row r="259" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="259" spans="1:5" ht="17" thickBot="1">
       <c r="A259" s="11">
         <v>41622</v>
       </c>
@@ -11580,7 +11580,7 @@
         <v>546825</v>
       </c>
     </row>
-    <row r="260" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="260" spans="1:5" ht="17" thickBot="1">
       <c r="A260" s="11">
         <v>41629</v>
       </c>
@@ -11598,7 +11598,7 @@
         <v>544984</v>
       </c>
     </row>
-    <row r="261" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="261" spans="1:5" ht="17" thickBot="1">
       <c r="A261" s="11">
         <v>41636</v>
       </c>
@@ -11616,7 +11616,7 @@
         <v>403329</v>
       </c>
     </row>
-    <row r="262" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="262" spans="1:5" ht="17" thickBot="1">
       <c r="A262" s="11">
         <v>41643</v>
       </c>
@@ -11634,7 +11634,7 @@
         <v>433724</v>
       </c>
     </row>
-    <row r="263" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="263" spans="1:5" ht="17" thickBot="1">
       <c r="A263" s="11">
         <v>41650</v>
       </c>
@@ -11652,7 +11652,7 @@
         <v>492836</v>
       </c>
     </row>
-    <row r="264" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="264" spans="1:5" ht="17" thickBot="1">
       <c r="A264" s="11">
         <v>41657</v>
       </c>
@@ -11670,7 +11670,7 @@
         <v>557253</v>
       </c>
     </row>
-    <row r="265" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="265" spans="1:5" ht="17" thickBot="1">
       <c r="A265" s="11">
         <v>41664</v>
       </c>
@@ -11688,7 +11688,7 @@
         <v>526644</v>
       </c>
     </row>
-    <row r="266" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="266" spans="1:5" ht="17" thickBot="1">
       <c r="A266" s="11">
         <v>41671</v>
       </c>
@@ -11706,7 +11706,7 @@
         <v>518012</v>
       </c>
     </row>
-    <row r="267" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="267" spans="1:5" ht="17" thickBot="1">
       <c r="A267" s="11">
         <v>41678</v>
       </c>
@@ -11724,7 +11724,7 @@
         <v>507368</v>
       </c>
     </row>
-    <row r="268" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="268" spans="1:5" ht="17" thickBot="1">
       <c r="A268" s="11">
         <v>41685</v>
       </c>
@@ -11742,7 +11742,7 @@
         <v>507257</v>
       </c>
     </row>
-    <row r="269" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="269" spans="1:5" ht="17" thickBot="1">
       <c r="A269" s="11">
         <v>41692</v>
       </c>
@@ -11760,7 +11760,7 @@
         <v>535036</v>
       </c>
     </row>
-    <row r="270" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="270" spans="1:5" ht="17" thickBot="1">
       <c r="A270" s="11">
         <v>41699</v>
       </c>
@@ -11778,7 +11778,7 @@
         <v>545004</v>
       </c>
     </row>
-    <row r="271" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="271" spans="1:5" ht="17" thickBot="1">
       <c r="A271" s="11">
         <v>41706</v>
       </c>
@@ -11796,7 +11796,7 @@
         <v>518495</v>
       </c>
     </row>
-    <row r="272" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="272" spans="1:5" ht="17" thickBot="1">
       <c r="A272" s="11">
         <v>41713</v>
       </c>
@@ -11814,7 +11814,7 @@
         <v>545366</v>
       </c>
     </row>
-    <row r="273" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="273" spans="1:5" ht="17" thickBot="1">
       <c r="A273" s="11">
         <v>41720</v>
       </c>
@@ -11832,7 +11832,7 @@
         <v>552238</v>
       </c>
     </row>
-    <row r="274" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="274" spans="1:5" ht="17" thickBot="1">
       <c r="A274" s="11">
         <v>41727</v>
       </c>
@@ -11850,7 +11850,7 @@
         <v>566505</v>
       </c>
     </row>
-    <row r="275" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="275" spans="1:5" ht="17" thickBot="1">
       <c r="A275" s="11">
         <v>41734</v>
       </c>
@@ -11868,7 +11868,7 @@
         <v>557123</v>
       </c>
     </row>
-    <row r="276" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="276" spans="1:5" ht="17" thickBot="1">
       <c r="A276" s="13">
         <v>41741</v>
       </c>
@@ -11886,7 +11886,7 @@
         <v>559676</v>
       </c>
     </row>
-    <row r="277" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="277" spans="1:5" ht="17" thickBot="1">
       <c r="A277" s="11">
         <v>41748</v>
       </c>
@@ -11904,7 +11904,7 @@
         <v>549826</v>
       </c>
     </row>
-    <row r="278" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="278" spans="1:5" ht="17" thickBot="1">
       <c r="A278" s="11">
         <v>41755</v>
       </c>
@@ -11922,7 +11922,7 @@
         <v>566336</v>
       </c>
     </row>
-    <row r="279" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="279" spans="1:5" ht="17" thickBot="1">
       <c r="A279" s="11">
         <v>41762</v>
       </c>
@@ -11940,7 +11940,7 @@
         <v>564801</v>
       </c>
     </row>
-    <row r="280" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="280" spans="1:5" ht="17" thickBot="1">
       <c r="A280" s="11">
         <v>41769</v>
       </c>
@@ -11958,7 +11958,7 @@
         <v>564096</v>
       </c>
     </row>
-    <row r="281" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="281" spans="1:5" ht="17" thickBot="1">
       <c r="A281" s="11">
         <v>41783</v>
       </c>
@@ -11976,7 +11976,7 @@
         <v>570380</v>
       </c>
     </row>
-    <row r="282" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="282" spans="1:5" ht="17" thickBot="1">
       <c r="A282" s="11">
         <v>41790</v>
       </c>
@@ -11994,7 +11994,7 @@
         <v>531725</v>
       </c>
     </row>
-    <row r="283" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="283" spans="1:5" ht="17" thickBot="1">
       <c r="A283" s="11">
         <v>41797</v>
       </c>
@@ -12012,7 +12012,7 @@
         <v>562747</v>
       </c>
     </row>
-    <row r="284" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="284" spans="1:5" ht="17" thickBot="1">
       <c r="A284" s="11">
         <v>41804</v>
       </c>
@@ -12030,7 +12030,7 @@
         <v>565375</v>
       </c>
     </row>
-    <row r="285" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="285" spans="1:5" ht="17" thickBot="1">
       <c r="A285" s="11">
         <v>41811</v>
       </c>
@@ -12048,7 +12048,7 @@
         <v>563695</v>
       </c>
     </row>
-    <row r="286" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="286" spans="1:5" ht="17" thickBot="1">
       <c r="A286" s="11">
         <v>41818</v>
       </c>
@@ -12066,7 +12066,7 @@
         <v>563223</v>
       </c>
     </row>
-    <row r="287" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="287" spans="1:5" ht="17" thickBot="1">
       <c r="A287" s="11">
         <v>41825</v>
       </c>
@@ -12084,7 +12084,7 @@
         <v>497828</v>
       </c>
     </row>
-    <row r="288" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="288" spans="1:5" ht="17" thickBot="1">
       <c r="A288" s="11">
         <v>41832</v>
       </c>
@@ -12102,7 +12102,7 @@
         <v>546863</v>
       </c>
     </row>
-    <row r="289" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="289" spans="1:5" ht="17" thickBot="1">
       <c r="A289" s="11">
         <v>41839</v>
       </c>
@@ -12120,7 +12120,7 @@
         <v>566931</v>
       </c>
     </row>
-    <row r="290" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="290" spans="1:5" ht="17" thickBot="1">
       <c r="A290" s="11">
         <v>41846</v>
       </c>
@@ -12138,7 +12138,7 @@
         <v>571797</v>
       </c>
     </row>
-    <row r="291" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="291" spans="1:5" ht="17" thickBot="1">
       <c r="A291" s="11">
         <v>41853</v>
       </c>
@@ -12156,7 +12156,7 @@
         <v>574552</v>
       </c>
     </row>
-    <row r="292" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="292" spans="1:5" ht="17" thickBot="1">
       <c r="A292" s="11">
         <v>41860</v>
       </c>
@@ -12174,7 +12174,7 @@
         <v>567908</v>
       </c>
     </row>
-    <row r="293" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="293" spans="1:5" ht="17" thickBot="1">
       <c r="A293" s="11">
         <v>41867</v>
       </c>
@@ -12192,7 +12192,7 @@
         <v>574592</v>
       </c>
     </row>
-    <row r="294" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="294" spans="1:5" ht="17" thickBot="1">
       <c r="A294" s="11">
         <v>41874</v>
       </c>
@@ -12210,7 +12210,7 @@
         <v>566266</v>
       </c>
     </row>
-    <row r="295" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="295" spans="1:5" ht="17" thickBot="1">
       <c r="A295" s="11">
         <v>41881</v>
       </c>
@@ -12228,7 +12228,7 @@
         <v>579209</v>
       </c>
     </row>
-    <row r="296" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="296" spans="1:5" ht="17" thickBot="1">
       <c r="A296" s="11">
         <v>41888</v>
       </c>
@@ -12246,7 +12246,7 @@
         <v>525144</v>
       </c>
     </row>
-    <row r="297" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="297" spans="1:5" ht="17" thickBot="1">
       <c r="A297" s="11">
         <v>41895</v>
       </c>
@@ -12264,7 +12264,7 @@
         <v>579440</v>
       </c>
     </row>
-    <row r="298" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="298" spans="1:5" ht="17" thickBot="1">
       <c r="A298" s="11">
         <v>41902</v>
       </c>
@@ -12282,7 +12282,7 @@
         <v>581955</v>
       </c>
     </row>
-    <row r="299" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="299" spans="1:5" ht="17" thickBot="1">
       <c r="A299" s="11">
         <v>41909</v>
       </c>
@@ -12300,7 +12300,7 @@
         <v>576934</v>
       </c>
     </row>
-    <row r="300" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="300" spans="1:5" ht="17" thickBot="1">
       <c r="A300" s="11">
         <v>41916</v>
       </c>
@@ -12318,7 +12318,7 @@
         <v>576356</v>
       </c>
     </row>
-    <row r="301" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="301" spans="1:5" ht="17" thickBot="1">
       <c r="A301" s="13">
         <v>41923</v>
       </c>
@@ -12336,7 +12336,7 @@
         <v>571812</v>
       </c>
     </row>
-    <row r="302" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="302" spans="1:5" ht="17" thickBot="1">
       <c r="A302" s="11">
         <v>41930</v>
       </c>
@@ -12354,7 +12354,7 @@
         <v>569684</v>
       </c>
     </row>
-    <row r="303" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="303" spans="1:5" ht="17" thickBot="1">
       <c r="A303" s="11">
         <v>41937</v>
       </c>
@@ -12372,7 +12372,7 @@
         <v>586115</v>
       </c>
     </row>
-    <row r="304" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="304" spans="1:5" ht="17" thickBot="1">
       <c r="A304" s="11">
         <v>41944</v>
       </c>
@@ -12390,7 +12390,7 @@
         <v>585208</v>
       </c>
     </row>
-    <row r="305" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="305" spans="1:5" ht="17" thickBot="1">
       <c r="A305" s="11">
         <v>41951</v>
       </c>
@@ -12408,7 +12408,7 @@
         <v>568807</v>
       </c>
     </row>
-    <row r="306" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="306" spans="1:5" ht="17" thickBot="1">
       <c r="A306" s="11">
         <v>41958</v>
       </c>
@@ -12426,7 +12426,7 @@
         <v>570350</v>
       </c>
     </row>
-    <row r="307" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="307" spans="1:5" ht="17" thickBot="1">
       <c r="A307" s="11">
         <v>41965</v>
       </c>
@@ -12444,7 +12444,7 @@
         <v>565185</v>
       </c>
     </row>
-    <row r="308" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="308" spans="1:5" ht="17" thickBot="1">
       <c r="A308" s="11">
         <v>41972</v>
       </c>
@@ -12462,7 +12462,7 @@
         <v>492532</v>
       </c>
     </row>
-    <row r="309" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="309" spans="1:5" ht="17" thickBot="1">
       <c r="A309" s="11">
         <v>41979</v>
       </c>
@@ -12480,7 +12480,7 @@
         <v>580108</v>
       </c>
     </row>
-    <row r="310" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="310" spans="1:5" ht="17" thickBot="1">
       <c r="A310" s="11">
         <v>41986</v>
       </c>
@@ -12498,7 +12498,7 @@
         <v>592608</v>
       </c>
     </row>
-    <row r="311" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="311" spans="1:5" ht="17" thickBot="1">
       <c r="A311" s="11">
         <v>41993</v>
       </c>
@@ -12516,7 +12516,7 @@
         <v>580559</v>
       </c>
     </row>
-    <row r="312" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="312" spans="1:5" ht="17" thickBot="1">
       <c r="A312" s="11">
         <v>42000</v>
       </c>
@@ -12534,7 +12534,7 @@
         <v>433338</v>
       </c>
     </row>
-    <row r="313" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="313" spans="1:5" ht="17" thickBot="1">
       <c r="A313" s="11">
         <v>42007</v>
       </c>
@@ -12552,7 +12552,7 @@
         <v>446201</v>
       </c>
     </row>
-    <row r="314" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="314" spans="1:5" ht="17" thickBot="1">
       <c r="A314" s="11">
         <v>42014</v>
       </c>
@@ -12570,7 +12570,7 @@
         <v>517520</v>
       </c>
     </row>
-    <row r="315" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="315" spans="1:5" ht="17" thickBot="1">
       <c r="A315" s="11">
         <v>42021</v>
       </c>
@@ -12588,7 +12588,7 @@
         <v>551856</v>
       </c>
     </row>
-    <row r="316" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="316" spans="1:5" ht="17" thickBot="1">
       <c r="A316" s="11">
         <v>42028</v>
       </c>
@@ -12606,7 +12606,7 @@
         <v>548055</v>
       </c>
     </row>
-    <row r="317" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="317" spans="1:5" ht="17" thickBot="1">
       <c r="A317" s="11">
         <v>42035</v>
       </c>
@@ -12624,7 +12624,7 @@
         <v>548478</v>
       </c>
     </row>
-    <row r="318" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="318" spans="1:5" ht="17" thickBot="1">
       <c r="A318" s="11">
         <v>42042</v>
       </c>
@@ -12642,7 +12642,7 @@
         <v>511563</v>
       </c>
     </row>
-    <row r="319" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="319" spans="1:5" ht="17" thickBot="1">
       <c r="A319" s="11">
         <v>42049</v>
       </c>
@@ -12660,7 +12660,7 @@
         <v>525224</v>
       </c>
     </row>
-    <row r="320" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="320" spans="1:5" ht="17" thickBot="1">
       <c r="A320" s="11">
         <v>42056</v>
       </c>
@@ -12678,7 +12678,7 @@
         <v>473161</v>
       </c>
     </row>
-    <row r="321" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="321" spans="1:5" ht="17" thickBot="1">
       <c r="A321" s="11">
         <v>42063</v>
       </c>
@@ -12696,7 +12696,7 @@
         <v>508658</v>
       </c>
     </row>
-    <row r="322" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="322" spans="1:5" ht="17" thickBot="1">
       <c r="A322" s="11">
         <v>42070</v>
       </c>
@@ -12729,7 +12729,7 @@
         <v>522382</v>
       </c>
     </row>
-    <row r="323" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="323" spans="1:5" ht="17" thickBot="1">
       <c r="A323" s="11">
         <v>42077</v>
       </c>
@@ -12747,7 +12747,7 @@
         <v>553031</v>
       </c>
     </row>
-    <row r="324" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="324" spans="1:5" ht="17" thickBot="1">
       <c r="A324" s="11">
         <v>42084</v>
       </c>
@@ -12765,7 +12765,7 @@
         <v>562472</v>
       </c>
     </row>
-    <row r="325" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="325" spans="1:5" ht="17" thickBot="1">
       <c r="A325" s="11">
         <v>42091</v>
       </c>
@@ -12783,7 +12783,7 @@
         <v>563280</v>
       </c>
     </row>
-    <row r="326" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="326" spans="1:5" ht="17" thickBot="1">
       <c r="A326" s="13">
         <v>42098</v>
       </c>
@@ -12801,7 +12801,7 @@
         <v>549021</v>
       </c>
     </row>
-    <row r="327" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="327" spans="1:5" ht="17" thickBot="1">
       <c r="A327" s="11">
         <v>42105</v>
       </c>
@@ -12819,7 +12819,7 @@
         <v>557812</v>
       </c>
     </row>
-    <row r="328" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="328" spans="1:5" ht="17" thickBot="1">
       <c r="A328" s="11">
         <v>42112</v>
       </c>
@@ -12837,7 +12837,7 @@
         <v>556432</v>
       </c>
     </row>
-    <row r="329" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="329" spans="1:5" ht="17" thickBot="1">
       <c r="A329" s="11">
         <v>42119</v>
       </c>
@@ -12855,7 +12855,7 @@
         <v>557306</v>
       </c>
     </row>
-    <row r="330" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="330" spans="1:5" ht="17" thickBot="1">
       <c r="A330" s="11">
         <v>42126</v>
       </c>
@@ -12873,7 +12873,7 @@
         <v>565787</v>
       </c>
     </row>
-    <row r="331" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="331" spans="1:5" ht="17" thickBot="1">
       <c r="A331" s="11">
         <v>42133</v>
       </c>
@@ -12891,7 +12891,7 @@
         <v>551034</v>
       </c>
     </row>
-    <row r="332" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="332" spans="1:5" ht="17" thickBot="1">
       <c r="A332" s="11">
         <v>42140</v>
       </c>
@@ -12909,7 +12909,7 @@
         <v>549199</v>
       </c>
     </row>
-    <row r="333" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="333" spans="1:5" ht="17" thickBot="1">
       <c r="A333" s="11">
         <v>42147</v>
       </c>
@@ -12927,7 +12927,7 @@
         <v>554477</v>
       </c>
     </row>
-    <row r="334" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="334" spans="1:5" ht="17" thickBot="1">
       <c r="A334" s="11">
         <v>42154</v>
       </c>
@@ -12945,7 +12945,7 @@
         <v>505543</v>
       </c>
     </row>
-    <row r="335" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="335" spans="1:5" ht="17" thickBot="1">
       <c r="A335" s="11">
         <v>42161</v>
       </c>
@@ -12963,7 +12963,7 @@
         <v>550037</v>
       </c>
     </row>
-    <row r="336" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="336" spans="1:5" ht="17" thickBot="1">
       <c r="A336" s="11">
         <v>42168</v>
       </c>
@@ -12981,7 +12981,7 @@
         <v>554461</v>
       </c>
     </row>
-    <row r="337" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="337" spans="1:5" ht="17" thickBot="1">
       <c r="A337" s="11">
         <v>42175</v>
       </c>
@@ -12999,7 +12999,7 @@
         <v>550839</v>
       </c>
     </row>
-    <row r="338" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="338" spans="1:5" ht="17" thickBot="1">
       <c r="A338" s="11">
         <v>42182</v>
       </c>
@@ -13017,7 +13017,7 @@
         <v>547969</v>
       </c>
     </row>
-    <row r="339" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="339" spans="1:5" ht="17" thickBot="1">
       <c r="A339" s="11">
         <v>42189</v>
       </c>
@@ -13035,7 +13035,7 @@
         <v>506284</v>
       </c>
     </row>
-    <row r="340" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="340" spans="1:5" ht="17" thickBot="1">
       <c r="A340" s="11">
         <v>42196</v>
       </c>
@@ -13053,7 +13053,7 @@
         <v>534097</v>
       </c>
     </row>
-    <row r="341" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="341" spans="1:5" ht="17" thickBot="1">
       <c r="A341" s="11">
         <v>42203</v>
       </c>
@@ -13071,7 +13071,7 @@
         <v>551181</v>
       </c>
     </row>
-    <row r="342" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="342" spans="1:5" ht="17" thickBot="1">
       <c r="A342" s="11">
         <v>42210</v>
       </c>
@@ -13089,7 +13089,7 @@
         <v>557612</v>
       </c>
     </row>
-    <row r="343" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="343" spans="1:5" ht="17" thickBot="1">
       <c r="A343" s="11">
         <v>42217</v>
       </c>
@@ -13107,7 +13107,7 @@
         <v>559125</v>
       </c>
     </row>
-    <row r="344" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="344" spans="1:5" ht="17" thickBot="1">
       <c r="A344" s="11">
         <v>42224</v>
       </c>
@@ -13125,7 +13125,7 @@
         <v>562884</v>
       </c>
     </row>
-    <row r="345" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="345" spans="1:5" ht="17" thickBot="1">
       <c r="A345" s="11">
         <v>42238</v>
       </c>
@@ -13143,7 +13143,7 @@
         <v>567943</v>
       </c>
     </row>
-    <row r="346" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="346" spans="1:5" ht="17" thickBot="1">
       <c r="A346" s="11">
         <v>42245</v>
       </c>
@@ -13161,7 +13161,7 @@
         <v>575323</v>
       </c>
     </row>
-    <row r="347" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="347" spans="1:5" ht="17" thickBot="1">
       <c r="A347" s="11">
         <v>42252</v>
       </c>
@@ -13179,7 +13179,7 @@
         <v>567206</v>
       </c>
     </row>
-    <row r="348" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="348" spans="1:5" ht="17" thickBot="1">
       <c r="A348" s="11">
         <v>42259</v>
       </c>
@@ -13197,7 +13197,7 @@
         <v>510797</v>
       </c>
     </row>
-    <row r="349" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="349" spans="1:5" ht="17" thickBot="1">
       <c r="A349" s="11">
         <v>42266</v>
       </c>
@@ -13215,7 +13215,7 @@
         <v>566734</v>
       </c>
     </row>
-    <row r="350" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="350" spans="1:5" ht="17" thickBot="1">
       <c r="A350" s="11">
         <v>42273</v>
       </c>
@@ -13233,7 +13233,7 @@
         <v>566700</v>
       </c>
     </row>
-    <row r="351" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="351" spans="1:5" ht="17" thickBot="1">
       <c r="A351" s="13">
         <v>42280</v>
       </c>
@@ -13251,7 +13251,7 @@
         <v>572293</v>
       </c>
     </row>
-    <row r="352" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="352" spans="1:5" ht="17" thickBot="1">
       <c r="A352" s="11">
         <v>42287</v>
       </c>
@@ -13269,7 +13269,7 @@
         <v>556233</v>
       </c>
     </row>
-    <row r="353" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="353" spans="1:5" ht="17" thickBot="1">
       <c r="A353" s="11">
         <v>42294</v>
       </c>
@@ -13287,7 +13287,7 @@
         <v>554696</v>
       </c>
     </row>
-    <row r="354" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="354" spans="1:5" ht="17" thickBot="1">
       <c r="A354" s="11">
         <v>42301</v>
       </c>
@@ -13305,7 +13305,7 @@
         <v>553144</v>
       </c>
     </row>
-    <row r="355" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="355" spans="1:5" ht="17" thickBot="1">
       <c r="A355" s="11">
         <v>42308</v>
       </c>
@@ -13323,7 +13323,7 @@
         <v>549707</v>
       </c>
     </row>
-    <row r="356" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="356" spans="1:5" ht="17" thickBot="1">
       <c r="A356" s="11">
         <v>42315</v>
       </c>
@@ -13341,7 +13341,7 @@
         <v>539165</v>
       </c>
     </row>
-    <row r="357" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="357" spans="1:5" ht="17" thickBot="1">
       <c r="A357" s="11">
         <v>42322</v>
       </c>
@@ -13359,7 +13359,7 @@
         <v>543681</v>
       </c>
     </row>
-    <row r="358" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="358" spans="1:5" ht="17" thickBot="1">
       <c r="A358" s="11">
         <v>42336</v>
       </c>
@@ -13377,7 +13377,7 @@
         <v>450389</v>
       </c>
     </row>
-    <row r="359" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="359" spans="1:5" ht="17" thickBot="1">
       <c r="A359" s="11">
         <v>42343</v>
       </c>
@@ -13395,7 +13395,7 @@
         <v>542050</v>
       </c>
     </row>
-    <row r="360" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="360" spans="1:5" ht="17" thickBot="1">
       <c r="A360" s="11">
         <v>42350</v>
       </c>
@@ -13413,7 +13413,7 @@
         <v>544975</v>
       </c>
     </row>
-    <row r="361" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="361" spans="1:5" ht="17" thickBot="1">
       <c r="A361" s="11">
         <v>42357</v>
       </c>
@@ -13431,7 +13431,7 @@
         <v>525555</v>
       </c>
     </row>
-    <row r="362" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="362" spans="1:5" ht="17" thickBot="1">
       <c r="A362" s="11">
         <v>42364</v>
       </c>
@@ -13449,7 +13449,7 @@
         <v>391107</v>
       </c>
     </row>
-    <row r="363" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="363" spans="1:5" ht="17" thickBot="1">
       <c r="A363" s="11">
         <v>42371</v>
       </c>
@@ -13467,7 +13467,7 @@
         <v>395663</v>
       </c>
     </row>
-    <row r="364" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="364" spans="1:5" ht="17" thickBot="1">
       <c r="A364" s="11">
         <v>42378</v>
       </c>
@@ -13485,7 +13485,7 @@
         <v>498160</v>
       </c>
     </row>
-    <row r="365" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="365" spans="1:5" ht="17" thickBot="1">
       <c r="A365" s="11">
         <v>42385</v>
       </c>
@@ -13503,7 +13503,7 @@
         <v>506433</v>
       </c>
     </row>
-    <row r="366" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="366" spans="1:5" ht="17" thickBot="1">
       <c r="A366" s="11">
         <v>42392</v>
       </c>
@@ -13521,7 +13521,7 @@
         <v>490324</v>
       </c>
     </row>
-    <row r="367" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="367" spans="1:5" ht="17" thickBot="1">
       <c r="A367" s="11">
         <v>42399</v>
       </c>
@@ -13539,7 +13539,7 @@
         <v>512746</v>
       </c>
     </row>
-    <row r="368" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="368" spans="1:5" ht="17" thickBot="1">
       <c r="A368" s="11">
         <v>42406</v>
       </c>
@@ -13557,7 +13557,7 @@
         <v>504510</v>
       </c>
     </row>
-    <row r="369" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="369" spans="1:5" ht="17" thickBot="1">
       <c r="A369" s="11">
         <v>42413</v>
       </c>
@@ -13575,7 +13575,7 @@
         <v>505148</v>
       </c>
     </row>
-    <row r="370" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="370" spans="1:5" ht="17" thickBot="1">
       <c r="A370" s="11">
         <v>42420</v>
       </c>
@@ -13593,7 +13593,7 @@
         <v>497210</v>
       </c>
     </row>
-    <row r="371" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="371" spans="1:5" ht="17" thickBot="1">
       <c r="A371" s="11">
         <v>42427</v>
       </c>
@@ -13611,7 +13611,7 @@
         <v>521300</v>
       </c>
     </row>
-    <row r="372" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="372" spans="1:5" ht="17" thickBot="1">
       <c r="A372" s="11">
         <v>42434</v>
       </c>
@@ -13629,7 +13629,7 @@
         <v>512202</v>
       </c>
     </row>
-    <row r="373" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="373" spans="1:5" ht="17" thickBot="1">
       <c r="A373" s="11">
         <v>42441</v>
       </c>
@@ -13647,7 +13647,7 @@
         <v>489177</v>
       </c>
     </row>
-    <row r="374" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="374" spans="1:5" ht="17" thickBot="1">
       <c r="A374" s="11">
         <v>42448</v>
       </c>
@@ -13665,7 +13665,7 @@
         <v>483463</v>
       </c>
     </row>
-    <row r="375" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="375" spans="1:5" ht="17" thickBot="1">
       <c r="A375" s="11">
         <v>42455</v>
       </c>
@@ -13683,7 +13683,7 @@
         <v>470271</v>
       </c>
     </row>
-    <row r="376" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="376" spans="1:5" ht="17" thickBot="1">
       <c r="A376" s="13">
         <v>42462</v>
       </c>
@@ -13701,7 +13701,7 @@
         <v>491979</v>
       </c>
     </row>
-    <row r="377" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="377" spans="1:5" ht="17" thickBot="1">
       <c r="A377" s="11">
         <v>42469</v>
       </c>
@@ -13719,7 +13719,7 @@
         <v>479059</v>
       </c>
     </row>
-    <row r="378" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="378" spans="1:5" ht="17" thickBot="1">
       <c r="A378" s="11">
         <v>42476</v>
       </c>
@@ -13737,7 +13737,7 @@
         <v>499779</v>
       </c>
     </row>
-    <row r="379" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="379" spans="1:5" ht="17" thickBot="1">
       <c r="A379" s="11">
         <v>42483</v>
       </c>
@@ -13755,7 +13755,7 @@
         <v>491946</v>
       </c>
     </row>
-    <row r="380" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="380" spans="1:5" ht="17" thickBot="1">
       <c r="A380" s="11">
         <v>42490</v>
       </c>
@@ -13773,7 +13773,7 @@
         <v>502045</v>
       </c>
     </row>
-    <row r="381" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="381" spans="1:5" ht="17" thickBot="1">
       <c r="A381" s="11">
         <v>42497</v>
       </c>
@@ -13791,7 +13791,7 @@
         <v>492923</v>
       </c>
     </row>
-    <row r="382" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="382" spans="1:5" ht="17" thickBot="1">
       <c r="A382" s="11">
         <v>42504</v>
       </c>
@@ -13809,7 +13809,7 @@
         <v>498379</v>
       </c>
     </row>
-    <row r="383" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="383" spans="1:5" ht="17" thickBot="1">
       <c r="A383" s="11">
         <v>42511</v>
       </c>
@@ -13827,7 +13827,7 @@
         <v>506983</v>
       </c>
     </row>
-    <row r="384" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="384" spans="1:5" ht="17" thickBot="1">
       <c r="A384" s="11">
         <v>42518</v>
       </c>
@@ -13845,7 +13845,7 @@
         <v>513917</v>
       </c>
     </row>
-    <row r="385" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="385" spans="1:5" ht="17" thickBot="1">
       <c r="A385" s="11">
         <v>42525</v>
       </c>
@@ -13863,7 +13863,7 @@
         <v>455346</v>
       </c>
     </row>
-    <row r="386" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="386" spans="1:5" ht="17" thickBot="1">
       <c r="A386" s="11">
         <v>42532</v>
       </c>
@@ -13896,7 +13896,7 @@
         <v>513471</v>
       </c>
     </row>
-    <row r="387" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="387" spans="1:5" ht="17" thickBot="1">
       <c r="A387" s="11">
         <v>42539</v>
       </c>
@@ -13914,7 +13914,7 @@
         <v>516096</v>
       </c>
     </row>
-    <row r="388" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="388" spans="1:5" ht="17" thickBot="1">
       <c r="A388" s="11">
         <v>42546</v>
       </c>
@@ -13932,7 +13932,7 @@
         <v>526161</v>
       </c>
     </row>
-    <row r="389" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="389" spans="1:5" ht="17" thickBot="1">
       <c r="A389" s="11">
         <v>42553</v>
       </c>
@@ -13950,7 +13950,7 @@
         <v>529191</v>
       </c>
     </row>
-    <row r="390" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="390" spans="1:5" ht="17" thickBot="1">
       <c r="A390" s="11">
         <v>42560</v>
       </c>
@@ -13968,7 +13968,7 @@
         <v>442113</v>
       </c>
     </row>
-    <row r="391" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="391" spans="1:5" ht="17" thickBot="1">
       <c r="A391" s="11">
         <v>42567</v>
       </c>
@@ -13986,7 +13986,7 @@
         <v>520222</v>
       </c>
     </row>
-    <row r="392" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="392" spans="1:5" ht="17" thickBot="1">
       <c r="A392" s="11">
         <v>42574</v>
       </c>
@@ -14004,7 +14004,7 @@
         <v>528070</v>
       </c>
     </row>
-    <row r="393" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="393" spans="1:5" ht="17" thickBot="1">
       <c r="A393" s="11">
         <v>42581</v>
       </c>
@@ -14022,7 +14022,7 @@
         <v>536916</v>
       </c>
     </row>
-    <row r="394" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="394" spans="1:5" ht="17" thickBot="1">
       <c r="A394" s="11">
         <v>42588</v>
       </c>
@@ -14040,7 +14040,7 @@
         <v>531595</v>
       </c>
     </row>
-    <row r="395" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="395" spans="1:5" ht="17" thickBot="1">
       <c r="A395" s="11">
         <v>42595</v>
       </c>
@@ -14058,7 +14058,7 @@
         <v>534533</v>
       </c>
     </row>
-    <row r="396" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="396" spans="1:5" ht="17" thickBot="1">
       <c r="A396" s="11">
         <v>42602</v>
       </c>
@@ -14076,7 +14076,7 @@
         <v>531484</v>
       </c>
     </row>
-    <row r="397" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="397" spans="1:5" ht="17" thickBot="1">
       <c r="A397" s="11">
         <v>42609</v>
       </c>
@@ -14094,7 +14094,7 @@
         <v>539657</v>
       </c>
     </row>
-    <row r="398" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="398" spans="1:5" ht="17" thickBot="1">
       <c r="A398" s="11">
         <v>42616</v>
       </c>
@@ -14112,7 +14112,7 @@
         <v>538826</v>
       </c>
     </row>
-    <row r="399" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="399" spans="1:5" ht="17" thickBot="1">
       <c r="A399" s="11">
         <v>42623</v>
       </c>
@@ -14130,7 +14130,7 @@
         <v>482894</v>
       </c>
     </row>
-    <row r="400" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="400" spans="1:5" ht="17" thickBot="1">
       <c r="A400" s="11">
         <v>42630</v>
       </c>
@@ -14148,7 +14148,7 @@
         <v>537904</v>
       </c>
     </row>
-    <row r="401" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="401" spans="1:5" ht="17" thickBot="1">
       <c r="A401" s="13">
         <v>42637</v>
       </c>
@@ -14166,7 +14166,7 @@
         <v>539609</v>
       </c>
     </row>
-    <row r="402" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="402" spans="1:5" ht="17" thickBot="1">
       <c r="A402" s="11">
         <v>42644</v>
       </c>
@@ -14184,7 +14184,7 @@
         <v>549171</v>
       </c>
     </row>
-    <row r="403" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="403" spans="1:5" ht="17" thickBot="1">
       <c r="A403" s="11">
         <v>42651</v>
       </c>
@@ -14202,7 +14202,7 @@
         <v>521789</v>
       </c>
     </row>
-    <row r="404" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="404" spans="1:5" ht="17" thickBot="1">
       <c r="A404" s="11">
         <v>42658</v>
       </c>
@@ -14220,7 +14220,7 @@
         <v>531936</v>
       </c>
     </row>
-    <row r="405" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="405" spans="1:5" ht="17" thickBot="1">
       <c r="A405" s="11">
         <v>42665</v>
       </c>
@@ -14238,7 +14238,7 @@
         <v>544092</v>
       </c>
     </row>
-    <row r="406" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="406" spans="1:5" ht="17" thickBot="1">
       <c r="A406" s="11">
         <v>42672</v>
       </c>
@@ -14256,7 +14256,7 @@
         <v>544997</v>
       </c>
     </row>
-    <row r="407" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="407" spans="1:5" ht="17" thickBot="1">
       <c r="A407" s="11">
         <v>42679</v>
       </c>
@@ -14274,7 +14274,7 @@
         <v>543377</v>
       </c>
     </row>
-    <row r="408" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="408" spans="1:5" ht="17" thickBot="1">
       <c r="A408" s="11">
         <v>42686</v>
       </c>
@@ -14292,7 +14292,7 @@
         <v>541127</v>
       </c>
     </row>
-    <row r="409" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="409" spans="1:5" ht="17" thickBot="1">
       <c r="A409" s="11">
         <v>42693</v>
       </c>
@@ -14310,7 +14310,7 @@
         <v>547804</v>
       </c>
     </row>
-    <row r="410" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="410" spans="1:5" ht="17" thickBot="1">
       <c r="A410" s="11">
         <v>42700</v>
       </c>
@@ -14328,7 +14328,7 @@
         <v>452759</v>
       </c>
     </row>
-    <row r="411" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="411" spans="1:5" ht="17" thickBot="1">
       <c r="A411" s="11">
         <v>42707</v>
       </c>
@@ -14346,7 +14346,7 @@
         <v>553130</v>
       </c>
     </row>
-    <row r="412" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="412" spans="1:5" ht="17" thickBot="1">
       <c r="A412" s="11">
         <v>42714</v>
       </c>
@@ -14364,7 +14364,7 @@
         <v>538932</v>
       </c>
     </row>
-    <row r="413" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="413" spans="1:5" ht="17" thickBot="1">
       <c r="A413" s="11">
         <v>42721</v>
       </c>
@@ -14382,7 +14382,7 @@
         <v>523949</v>
       </c>
     </row>
-    <row r="414" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="414" spans="1:5" ht="17" thickBot="1">
       <c r="A414" s="11">
         <v>42728</v>
       </c>
@@ -14400,7 +14400,7 @@
         <v>496633</v>
       </c>
     </row>
-    <row r="415" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="415" spans="1:5" ht="17" thickBot="1">
       <c r="A415" s="11">
         <v>42735</v>
       </c>
@@ -14418,7 +14418,7 @@
         <v>425998</v>
       </c>
     </row>
-    <row r="416" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="416" spans="1:5" ht="17" thickBot="1">
       <c r="A416" s="11">
         <v>42742</v>
       </c>
@@ -14436,7 +14436,7 @@
         <v>441417</v>
       </c>
     </row>
-    <row r="417" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="417" spans="1:5" ht="17" thickBot="1">
       <c r="A417" s="11">
         <v>42749</v>
       </c>
@@ -14454,7 +14454,7 @@
         <v>516229</v>
       </c>
     </row>
-    <row r="418" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="418" spans="1:5" ht="17" thickBot="1">
       <c r="A418" s="11">
         <v>42756</v>
       </c>
@@ -14472,7 +14472,7 @@
         <v>530299</v>
       </c>
     </row>
-    <row r="419" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="419" spans="1:5" ht="17" thickBot="1">
       <c r="A419" s="11">
         <v>42763</v>
       </c>
@@ -14490,7 +14490,7 @@
         <v>529696</v>
       </c>
     </row>
-    <row r="420" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="420" spans="1:5" ht="17" thickBot="1">
       <c r="A420" s="11">
         <v>42770</v>
       </c>
@@ -14508,7 +14508,7 @@
         <v>541474</v>
       </c>
     </row>
-    <row r="421" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="421" spans="1:5" ht="17" thickBot="1">
       <c r="A421" s="11">
         <v>42777</v>
       </c>
@@ -14526,7 +14526,7 @@
         <v>518431</v>
       </c>
     </row>
-    <row r="422" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="422" spans="1:5" ht="17" thickBot="1">
       <c r="A422" s="11">
         <v>42784</v>
       </c>
@@ -14544,7 +14544,7 @@
         <v>531123</v>
       </c>
     </row>
-    <row r="423" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="423" spans="1:5" ht="17" thickBot="1">
       <c r="A423" s="11">
         <v>42791</v>
       </c>
@@ -14562,7 +14562,7 @@
         <v>521451</v>
       </c>
     </row>
-    <row r="424" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="424" spans="1:5" ht="17" thickBot="1">
       <c r="A424" s="11">
         <v>42798</v>
       </c>
@@ -14580,7 +14580,7 @@
         <v>521607</v>
       </c>
     </row>
-    <row r="425" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="425" spans="1:5" ht="17" thickBot="1">
       <c r="A425" s="11">
         <v>42805</v>
       </c>
@@ -14598,7 +14598,7 @@
         <v>510638</v>
       </c>
     </row>
-    <row r="426" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="426" spans="1:5" ht="17" thickBot="1">
       <c r="A426" s="13">
         <v>42812</v>
       </c>
@@ -14616,7 +14616,7 @@
         <v>495281</v>
       </c>
     </row>
-    <row r="427" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="427" spans="1:5" ht="17" thickBot="1">
       <c r="A427" s="11">
         <v>42819</v>
       </c>
@@ -14634,7 +14634,7 @@
         <v>526471</v>
       </c>
     </row>
-    <row r="428" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="428" spans="1:5" ht="17" thickBot="1">
       <c r="A428" s="11">
         <v>42826</v>
       </c>
@@ -14652,7 +14652,7 @@
         <v>527665</v>
       </c>
     </row>
-    <row r="429" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="429" spans="1:5" ht="17" thickBot="1">
       <c r="A429" s="11">
         <v>42833</v>
       </c>
@@ -14670,7 +14670,7 @@
         <v>513022</v>
       </c>
     </row>
-    <row r="430" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="430" spans="1:5" ht="17" thickBot="1">
       <c r="A430" s="11">
         <v>42840</v>
       </c>
@@ -14688,7 +14688,7 @@
         <v>519318</v>
       </c>
     </row>
-    <row r="431" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="431" spans="1:5" ht="17" thickBot="1">
       <c r="A431" s="11">
         <v>42847</v>
       </c>
@@ -14706,7 +14706,7 @@
         <v>515131</v>
       </c>
     </row>
-    <row r="432" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="432" spans="1:5" ht="17" thickBot="1">
       <c r="A432" s="11">
         <v>42854</v>
       </c>
@@ -14724,7 +14724,7 @@
         <v>527830</v>
       </c>
     </row>
-    <row r="433" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="433" spans="1:5" ht="17" thickBot="1">
       <c r="A433" s="11">
         <v>42861</v>
       </c>
@@ -14742,7 +14742,7 @@
         <v>515305</v>
       </c>
     </row>
-    <row r="434" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="434" spans="1:5" ht="17" thickBot="1">
       <c r="A434" s="11">
         <v>42868</v>
       </c>
@@ -14760,7 +14760,7 @@
         <v>526970</v>
       </c>
     </row>
-    <row r="435" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="435" spans="1:5" ht="17" thickBot="1">
       <c r="A435" s="11">
         <v>42875</v>
       </c>
@@ -14778,7 +14778,7 @@
         <v>534922</v>
       </c>
     </row>
-    <row r="436" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="436" spans="1:5" ht="17" thickBot="1">
       <c r="A436" s="11">
         <v>42882</v>
       </c>
@@ -14796,7 +14796,7 @@
         <v>548103</v>
       </c>
     </row>
-    <row r="437" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="437" spans="1:5" ht="17" thickBot="1">
       <c r="A437" s="11">
         <v>42889</v>
       </c>
@@ -14814,7 +14814,7 @@
         <v>500192</v>
       </c>
     </row>
-    <row r="438" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="438" spans="1:5" ht="17" thickBot="1">
       <c r="A438" s="11">
         <v>42896</v>
       </c>
@@ -14832,7 +14832,7 @@
         <v>545317</v>
       </c>
     </row>
-    <row r="439" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="439" spans="1:5" ht="17" thickBot="1">
       <c r="A439" s="11">
         <v>42903</v>
       </c>
@@ -14850,7 +14850,7 @@
         <v>543179</v>
       </c>
     </row>
-    <row r="440" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="440" spans="1:5" ht="17" thickBot="1">
       <c r="A440" s="11">
         <v>42910</v>
       </c>
@@ -14868,7 +14868,7 @@
         <v>544694</v>
       </c>
     </row>
-    <row r="441" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="441" spans="1:5" ht="17" thickBot="1">
       <c r="A441" s="11">
         <v>42917</v>
       </c>
@@ -14886,7 +14886,7 @@
         <v>546361</v>
       </c>
     </row>
-    <row r="442" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="442" spans="1:5" ht="17" thickBot="1">
       <c r="A442" s="11">
         <v>42924</v>
       </c>
@@ -14904,7 +14904,7 @@
         <v>453080</v>
       </c>
     </row>
-    <row r="443" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="443" spans="1:5" ht="17" thickBot="1">
       <c r="A443" s="11">
         <v>42931</v>
       </c>
@@ -14922,7 +14922,7 @@
         <v>540005</v>
       </c>
     </row>
-    <row r="444" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="444" spans="1:5" ht="17" thickBot="1">
       <c r="A444" s="11">
         <v>42938</v>
       </c>
@@ -14940,7 +14940,7 @@
         <v>534152</v>
       </c>
     </row>
-    <row r="445" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="445" spans="1:5" ht="17" thickBot="1">
       <c r="A445" s="11">
         <v>42945</v>
       </c>
@@ -14958,7 +14958,7 @@
         <v>550356</v>
       </c>
     </row>
-    <row r="446" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="446" spans="1:5" ht="17" thickBot="1">
       <c r="A446" s="11">
         <v>42952</v>
       </c>
@@ -14976,7 +14976,7 @@
         <v>554822</v>
       </c>
     </row>
-    <row r="447" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="447" spans="1:5" ht="17" thickBot="1">
       <c r="A447" s="11">
         <v>42959</v>
       </c>
@@ -14994,7 +14994,7 @@
         <v>548790</v>
       </c>
     </row>
-    <row r="448" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="448" spans="1:5" ht="17" thickBot="1">
       <c r="A448" s="11">
         <v>42966</v>
       </c>
@@ -15012,7 +15012,7 @@
         <v>554021</v>
       </c>
     </row>
-    <row r="449" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="449" spans="1:5" ht="17" thickBot="1">
       <c r="A449" s="11">
         <v>42973</v>
       </c>
@@ -15030,7 +15030,7 @@
         <v>551776</v>
       </c>
     </row>
-    <row r="450" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="450" spans="1:5" ht="17" thickBot="1">
       <c r="A450" s="11">
         <v>42980</v>
       </c>
@@ -15063,7 +15063,7 @@
         <v>534140</v>
       </c>
     </row>
-    <row r="451" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="451" spans="1:5" ht="17" thickBot="1">
       <c r="A451" s="13">
         <v>42987</v>
       </c>
@@ -15081,7 +15081,7 @@
         <v>486474</v>
       </c>
     </row>
-    <row r="452" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="452" spans="1:5" ht="17" thickBot="1">
       <c r="A452" s="11">
         <v>42994</v>
       </c>
@@ -15099,7 +15099,7 @@
         <v>530774</v>
       </c>
     </row>
-    <row r="453" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="453" spans="1:5" ht="17" thickBot="1">
       <c r="A453" s="11">
         <v>43001</v>
       </c>
@@ -15117,7 +15117,7 @@
         <v>548204</v>
       </c>
     </row>
-    <row r="454" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="454" spans="1:5" ht="17" thickBot="1">
       <c r="A454" s="11">
         <v>43008</v>
       </c>
@@ -15135,7 +15135,7 @@
         <v>559555</v>
       </c>
     </row>
-    <row r="455" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="455" spans="1:5" ht="17" thickBot="1">
       <c r="A455" s="11">
         <v>43015</v>
       </c>
@@ -15153,7 +15153,7 @@
         <v>554826</v>
       </c>
     </row>
-    <row r="456" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="456" spans="1:5" ht="17" thickBot="1">
       <c r="A456" s="11">
         <v>43022</v>
       </c>
@@ -15171,7 +15171,7 @@
         <v>548264</v>
       </c>
     </row>
-    <row r="457" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="457" spans="1:5" ht="17" thickBot="1">
       <c r="A457" s="11">
         <v>43029</v>
       </c>
@@ -15189,7 +15189,7 @@
         <v>559989</v>
       </c>
     </row>
-    <row r="458" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="458" spans="1:5" ht="17" thickBot="1">
       <c r="A458" s="11">
         <v>43036</v>
       </c>
@@ -15207,7 +15207,7 @@
         <v>546582</v>
       </c>
     </row>
-    <row r="459" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="459" spans="1:5" ht="17" thickBot="1">
       <c r="A459" s="11">
         <v>43043</v>
       </c>
@@ -15225,7 +15225,7 @@
         <v>538739</v>
       </c>
     </row>
-    <row r="460" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="460" spans="1:5" ht="17" thickBot="1">
       <c r="A460" s="11">
         <v>43050</v>
       </c>
@@ -15243,7 +15243,7 @@
         <v>547480</v>
       </c>
     </row>
-    <row r="461" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="461" spans="1:5" ht="17" thickBot="1">
       <c r="A461" s="11">
         <v>43057</v>
       </c>
@@ -15261,7 +15261,7 @@
         <v>554066</v>
       </c>
     </row>
-    <row r="462" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="462" spans="1:5" ht="17" thickBot="1">
       <c r="A462" s="11">
         <v>43064</v>
       </c>
@@ -15279,7 +15279,7 @@
         <v>463602</v>
       </c>
     </row>
-    <row r="463" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="463" spans="1:5" ht="17" thickBot="1">
       <c r="A463" s="11">
         <v>43071</v>
       </c>
@@ -15297,7 +15297,7 @@
         <v>572794</v>
       </c>
     </row>
-    <row r="464" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="464" spans="1:5" ht="17" thickBot="1">
       <c r="A464" s="11">
         <v>43078</v>
       </c>
@@ -15315,7 +15315,7 @@
         <v>560756</v>
       </c>
     </row>
-    <row r="465" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="465" spans="1:5" ht="17" thickBot="1">
       <c r="A465" s="11">
         <v>43085</v>
       </c>
@@ -15333,7 +15333,7 @@
         <v>554779</v>
       </c>
     </row>
-    <row r="466" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="466" spans="1:5" ht="17" thickBot="1">
       <c r="A466" s="11">
         <v>43092</v>
       </c>
@@ -15351,7 +15351,7 @@
         <v>551566</v>
       </c>
     </row>
-    <row r="467" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="467" spans="1:5" ht="17" thickBot="1">
       <c r="A467" s="11">
         <v>43099</v>
       </c>
@@ -15369,7 +15369,7 @@
         <v>397032</v>
       </c>
     </row>
-    <row r="468" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="468" spans="1:5" ht="17" thickBot="1">
       <c r="A468" s="11">
         <v>43113</v>
       </c>
@@ -15387,7 +15387,7 @@
         <v>511937</v>
       </c>
     </row>
-    <row r="469" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="469" spans="1:5" ht="17" thickBot="1">
       <c r="A469" s="11">
         <v>43120</v>
       </c>
@@ -15405,7 +15405,7 @@
         <v>508239</v>
       </c>
     </row>
-    <row r="470" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="470" spans="1:5" ht="17" thickBot="1">
       <c r="A470" s="11">
         <v>43127</v>
       </c>
@@ -15423,7 +15423,7 @@
         <v>543515</v>
       </c>
     </row>
-    <row r="471" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="471" spans="1:5" ht="17" thickBot="1">
       <c r="A471" s="11">
         <v>43134</v>
       </c>
@@ -15441,7 +15441,7 @@
         <v>547993</v>
       </c>
     </row>
-    <row r="472" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="472" spans="1:5" ht="17" thickBot="1">
       <c r="A472" s="11">
         <v>43141</v>
       </c>
@@ -15459,7 +15459,7 @@
         <v>519545</v>
       </c>
     </row>
-    <row r="473" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="473" spans="1:5" ht="17" thickBot="1">
       <c r="A473" s="11">
         <v>43148</v>
       </c>
@@ -15477,7 +15477,7 @@
         <v>539963</v>
       </c>
     </row>
-    <row r="474" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="474" spans="1:5" ht="17" thickBot="1">
       <c r="A474" s="11">
         <v>43155</v>
       </c>
@@ -15495,7 +15495,7 @@
         <v>528440</v>
       </c>
     </row>
-    <row r="475" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="475" spans="1:5" ht="17" thickBot="1">
       <c r="A475" s="11">
         <v>43162</v>
       </c>
@@ -15513,7 +15513,7 @@
         <v>544194</v>
       </c>
     </row>
-    <row r="476" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="476" spans="1:5" ht="17" thickBot="1">
       <c r="A476" s="13">
         <v>43169</v>
       </c>
@@ -15531,7 +15531,7 @@
         <v>534282</v>
       </c>
     </row>
-    <row r="477" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="477" spans="1:5" ht="17" thickBot="1">
       <c r="A477" s="11">
         <v>43176</v>
       </c>
@@ -15549,7 +15549,7 @@
         <v>537338</v>
       </c>
     </row>
-    <row r="478" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="478" spans="1:5" ht="17" thickBot="1">
       <c r="A478" s="11">
         <v>43183</v>
       </c>
@@ -15567,7 +15567,7 @@
         <v>526521</v>
       </c>
     </row>
-    <row r="479" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="479" spans="1:5" ht="17" thickBot="1">
       <c r="A479" s="11">
         <v>43190</v>
       </c>
@@ -15585,7 +15585,7 @@
         <v>534751</v>
       </c>
     </row>
-    <row r="480" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="480" spans="1:5" ht="17" thickBot="1">
       <c r="A480" s="11">
         <v>43197</v>
       </c>
@@ -15603,7 +15603,7 @@
         <v>524905</v>
       </c>
     </row>
-    <row r="481" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="481" spans="1:5" ht="17" thickBot="1">
       <c r="A481" s="11">
         <v>43204</v>
       </c>
@@ -15621,7 +15621,7 @@
         <v>534198</v>
       </c>
     </row>
-    <row r="482" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="482" spans="1:5" ht="17" thickBot="1">
       <c r="A482" s="11">
         <v>43211</v>
       </c>
@@ -15639,7 +15639,7 @@
         <v>539425</v>
       </c>
     </row>
-    <row r="483" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="483" spans="1:5" ht="17" thickBot="1">
       <c r="A483" s="11">
         <v>43218</v>
       </c>
@@ -15657,7 +15657,7 @@
         <v>551498</v>
       </c>
     </row>
-    <row r="484" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="484" spans="1:5" ht="17" thickBot="1">
       <c r="A484" s="11">
         <v>43225</v>
       </c>
@@ -15675,7 +15675,7 @@
         <v>545937</v>
       </c>
     </row>
-    <row r="485" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="485" spans="1:5" ht="17" thickBot="1">
       <c r="A485" s="11">
         <v>43232</v>
       </c>
@@ -15693,7 +15693,7 @@
         <v>550029</v>
       </c>
     </row>
-    <row r="486" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="486" spans="1:5" ht="17" thickBot="1">
       <c r="A486" s="11">
         <v>43239</v>
       </c>
@@ -15711,7 +15711,7 @@
         <v>546415</v>
       </c>
     </row>
-    <row r="487" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="487" spans="1:5" ht="17" thickBot="1">
       <c r="A487" s="11">
         <v>43246</v>
       </c>
@@ -15729,7 +15729,7 @@
         <v>565502</v>
       </c>
     </row>
-    <row r="488" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="488" spans="1:5" ht="17" thickBot="1">
       <c r="A488" s="11">
         <v>43253</v>
       </c>
@@ -15747,7 +15747,7 @@
         <v>509740</v>
       </c>
     </row>
-    <row r="489" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="489" spans="1:5" ht="17" thickBot="1">
       <c r="A489" s="11">
         <v>43260</v>
       </c>
@@ -15765,7 +15765,7 @@
         <v>561061</v>
       </c>
     </row>
-    <row r="490" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="490" spans="1:5" ht="17" thickBot="1">
       <c r="A490" s="11">
         <v>43267</v>
       </c>
@@ -15783,7 +15783,7 @@
         <v>558098</v>
       </c>
     </row>
-    <row r="491" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="491" spans="1:5" ht="17" thickBot="1">
       <c r="A491" s="11">
         <v>43274</v>
       </c>
@@ -15801,7 +15801,7 @@
         <v>557340</v>
       </c>
     </row>
-    <row r="492" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="492" spans="1:5" ht="17" thickBot="1">
       <c r="A492" s="11">
         <v>43281</v>
       </c>
@@ -15819,7 +15819,7 @@
         <v>564243</v>
       </c>
     </row>
-    <row r="493" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="493" spans="1:5" ht="17" thickBot="1">
       <c r="A493" s="11">
         <v>43288</v>
       </c>
@@ -15837,7 +15837,7 @@
         <v>485193</v>
       </c>
     </row>
-    <row r="494" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="494" spans="1:5" ht="17" thickBot="1">
       <c r="A494" s="11">
         <v>43295</v>
       </c>
@@ -15855,7 +15855,7 @@
         <v>559064</v>
       </c>
     </row>
-    <row r="495" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="495" spans="1:5" ht="17" thickBot="1">
       <c r="A495" s="11">
         <v>43302</v>
       </c>
@@ -15873,7 +15873,7 @@
         <v>553024</v>
       </c>
     </row>
-    <row r="496" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="496" spans="1:5" ht="17" thickBot="1">
       <c r="A496" s="11">
         <v>43309</v>
       </c>
@@ -15891,7 +15891,7 @@
         <v>559154</v>
       </c>
     </row>
-    <row r="497" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="497" spans="1:5" ht="17" thickBot="1">
       <c r="A497" s="11">
         <v>43316</v>
       </c>
@@ -15909,7 +15909,7 @@
         <v>570995</v>
       </c>
     </row>
-    <row r="498" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="498" spans="1:5" ht="17" thickBot="1">
       <c r="A498" s="11">
         <v>43323</v>
       </c>
@@ -15927,7 +15927,7 @@
         <v>556887</v>
       </c>
     </row>
-    <row r="499" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="499" spans="1:5" ht="17" thickBot="1">
       <c r="A499" s="11">
         <v>43330</v>
       </c>
@@ -15945,7 +15945,7 @@
         <v>567477</v>
       </c>
     </row>
-    <row r="500" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="500" spans="1:5" ht="17" thickBot="1">
       <c r="A500" s="11">
         <v>43337</v>
       </c>
@@ -15963,7 +15963,7 @@
         <v>565706</v>
       </c>
     </row>
-    <row r="501" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="501" spans="1:5" ht="17" thickBot="1">
       <c r="A501" s="13">
         <v>43344</v>
       </c>
@@ -15981,7 +15981,7 @@
         <v>567881</v>
       </c>
     </row>
-    <row r="502" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="502" spans="1:5" ht="17" thickBot="1">
       <c r="A502" s="11">
         <v>43351</v>
       </c>
@@ -15999,7 +15999,7 @@
         <v>502208</v>
       </c>
     </row>
-    <row r="503" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="503" spans="1:5" ht="17" thickBot="1">
       <c r="A503" s="11">
         <v>43358</v>
       </c>
@@ -16017,7 +16017,7 @@
         <v>553003</v>
       </c>
     </row>
-    <row r="504" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="504" spans="1:5" ht="17" thickBot="1">
       <c r="A504" s="11">
         <v>43365</v>
       </c>
@@ -16035,7 +16035,7 @@
         <v>567078</v>
       </c>
     </row>
-    <row r="505" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="505" spans="1:5" ht="17" thickBot="1">
       <c r="A505" s="11">
         <v>43372</v>
       </c>
@@ -16053,7 +16053,7 @@
         <v>571922</v>
       </c>
     </row>
-    <row r="506" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="506" spans="1:5" ht="17" thickBot="1">
       <c r="A506" s="11">
         <v>43379</v>
       </c>
@@ -16071,7 +16071,7 @@
         <v>554238</v>
       </c>
     </row>
-    <row r="507" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="507" spans="1:5" ht="17" thickBot="1">
       <c r="A507" s="11">
         <v>43386</v>
       </c>
@@ -16089,7 +16089,7 @@
         <v>549757</v>
       </c>
     </row>
-    <row r="508" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="508" spans="1:5" ht="17" thickBot="1">
       <c r="A508" s="11">
         <v>43393</v>
       </c>
@@ -16107,7 +16107,7 @@
         <v>555106</v>
       </c>
     </row>
-    <row r="509" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="509" spans="1:5" ht="17" thickBot="1">
       <c r="A509" s="11">
         <v>43400</v>
       </c>
@@ -16125,7 +16125,7 @@
         <v>562804</v>
       </c>
     </row>
-    <row r="510" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="510" spans="1:5" ht="17" thickBot="1">
       <c r="A510" s="11">
         <v>43407</v>
       </c>
@@ -16143,7 +16143,7 @@
         <v>560046</v>
       </c>
     </row>
-    <row r="511" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="511" spans="1:5" ht="17" thickBot="1">
       <c r="A511" s="11">
         <v>43414</v>
       </c>
@@ -16161,7 +16161,7 @@
         <v>547236</v>
       </c>
     </row>
-    <row r="512" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="512" spans="1:5" ht="17" thickBot="1">
       <c r="A512" s="11">
         <v>43421</v>
       </c>
@@ -16179,7 +16179,7 @@
         <v>546541</v>
       </c>
     </row>
-    <row r="513" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="513" spans="1:5" ht="17" thickBot="1">
       <c r="A513" s="11">
         <v>43428</v>
       </c>
@@ -16197,7 +16197,7 @@
         <v>470851</v>
       </c>
     </row>
-    <row r="514" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="514" spans="1:5" ht="17" thickBot="1">
       <c r="A514" s="11">
         <v>43435</v>
       </c>
@@ -16230,7 +16230,7 @@
         <v>567282</v>
       </c>
     </row>
-    <row r="515" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="515" spans="1:5" ht="17" thickBot="1">
       <c r="A515" s="11">
         <v>43442</v>
       </c>
@@ -16248,7 +16248,7 @@
         <v>570225</v>
       </c>
     </row>
-    <row r="516" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="516" spans="1:5" ht="17" thickBot="1">
       <c r="A516" s="11">
         <v>43449</v>
       </c>
@@ -16266,7 +16266,7 @@
         <v>568941</v>
       </c>
     </row>
-    <row r="517" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="517" spans="1:5" ht="17" thickBot="1">
       <c r="A517" s="11">
         <v>43456</v>
       </c>
@@ -16284,7 +16284,7 @@
         <v>567252</v>
       </c>
     </row>
-    <row r="518" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="518" spans="1:5" ht="17" thickBot="1">
       <c r="A518" s="11">
         <v>43463</v>
       </c>
@@ -16302,7 +16302,7 @@
         <v>411676</v>
       </c>
     </row>
-    <row r="519" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="519" spans="1:5" ht="17" thickBot="1">
       <c r="A519" s="11">
         <v>43470</v>
       </c>
@@ -16320,7 +16320,7 @@
         <v>436103</v>
       </c>
     </row>
-    <row r="520" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="520" spans="1:5" ht="17" thickBot="1">
       <c r="A520" s="11">
         <v>43477</v>
       </c>
@@ -16338,7 +16338,7 @@
         <v>555127</v>
       </c>
     </row>
-    <row r="521" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="521" spans="1:5" ht="17" thickBot="1">
       <c r="A521" s="11">
         <v>43484</v>
       </c>
@@ -16356,7 +16356,7 @@
         <v>543111</v>
       </c>
     </row>
-    <row r="522" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="522" spans="1:5" ht="17" thickBot="1">
       <c r="A522" s="11">
         <v>43491</v>
       </c>
@@ -16374,7 +16374,7 @@
         <v>522026</v>
       </c>
     </row>
-    <row r="523" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="523" spans="1:5" ht="17" thickBot="1">
       <c r="A523" s="11">
         <v>43498</v>
       </c>
@@ -16392,7 +16392,7 @@
         <v>498288</v>
       </c>
     </row>
-    <row r="524" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="524" spans="1:5" ht="17" thickBot="1">
       <c r="A524" s="11">
         <v>43505</v>
       </c>
@@ -16410,7 +16410,7 @@
         <v>519779</v>
       </c>
     </row>
-    <row r="525" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="525" spans="1:5" ht="17" thickBot="1">
       <c r="A525" s="11">
         <v>43512</v>
       </c>
@@ -16428,7 +16428,7 @@
         <v>523915</v>
       </c>
     </row>
-    <row r="526" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="526" spans="1:5" ht="17" thickBot="1">
       <c r="A526" s="13">
         <v>43519</v>
       </c>
@@ -16446,7 +16446,7 @@
         <v>522630</v>
       </c>
     </row>
-    <row r="527" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="527" spans="1:5" ht="17" thickBot="1">
       <c r="A527" s="11">
         <v>43526</v>
       </c>
@@ -16464,7 +16464,7 @@
         <v>528153</v>
       </c>
     </row>
-    <row r="528" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="528" spans="1:5" ht="17" thickBot="1">
       <c r="A528" s="11">
         <v>43533</v>
       </c>
@@ -16482,7 +16482,7 @@
         <v>508958</v>
       </c>
     </row>
-    <row r="529" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="529" spans="1:5" ht="17" thickBot="1">
       <c r="A529" s="11">
         <v>43540</v>
       </c>
@@ -16500,7 +16500,7 @@
         <v>501001</v>
       </c>
     </row>
-    <row r="530" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="530" spans="1:5" ht="17" thickBot="1">
       <c r="A530" s="11">
         <v>43547</v>
       </c>
@@ -16518,7 +16518,7 @@
         <v>503017</v>
       </c>
     </row>
-    <row r="531" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="531" spans="1:5" ht="17" thickBot="1">
       <c r="A531" s="11">
         <v>43554</v>
       </c>
@@ -16536,7 +16536,7 @@
         <v>509958</v>
       </c>
     </row>
-    <row r="532" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="532" spans="1:5" ht="17" thickBot="1">
       <c r="A532" s="11">
         <v>43561</v>
       </c>
@@ -16554,7 +16554,7 @@
         <v>510192</v>
       </c>
     </row>
-    <row r="533" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="533" spans="1:5" ht="17" thickBot="1">
       <c r="A533" s="11">
         <v>43568</v>
       </c>
@@ -16572,7 +16572,7 @@
         <v>528167</v>
       </c>
     </row>
-    <row r="534" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="534" spans="1:5" ht="17" thickBot="1">
       <c r="A534" s="11">
         <v>43575</v>
       </c>
@@ -16590,7 +16590,7 @@
         <v>526141</v>
       </c>
     </row>
-    <row r="535" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="535" spans="1:5" ht="17" thickBot="1">
       <c r="A535" s="11">
         <v>43582</v>
       </c>
@@ -16608,7 +16608,7 @@
         <v>533190</v>
       </c>
     </row>
-    <row r="536" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="536" spans="1:5" ht="17" thickBot="1">
       <c r="A536" s="11">
         <v>43589</v>
       </c>
@@ -16626,7 +16626,7 @@
         <v>535089</v>
       </c>
     </row>
-    <row r="537" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="537" spans="1:5" ht="17" thickBot="1">
       <c r="A537" s="11">
         <v>43596</v>
       </c>
@@ -16644,7 +16644,7 @@
         <v>529263</v>
       </c>
     </row>
-    <row r="538" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="538" spans="1:5" ht="17" thickBot="1">
       <c r="A538" s="11">
         <v>43603</v>
       </c>
@@ -16662,7 +16662,7 @@
         <v>536358</v>
       </c>
     </row>
-    <row r="539" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="539" spans="1:5" ht="17" thickBot="1">
       <c r="A539" s="11">
         <v>43610</v>
       </c>
@@ -16680,7 +16680,7 @@
         <v>527966</v>
       </c>
     </row>
-    <row r="540" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="540" spans="1:5" ht="17" thickBot="1">
       <c r="A540" s="11">
         <v>43617</v>
       </c>
@@ -16698,7 +16698,7 @@
         <v>478679</v>
       </c>
     </row>
-    <row r="541" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="541" spans="1:5" ht="17" thickBot="1">
       <c r="A541" s="11">
         <v>43624</v>
       </c>
@@ -16716,7 +16716,7 @@
         <v>513099</v>
       </c>
     </row>
-    <row r="542" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="542" spans="1:5" ht="17" thickBot="1">
       <c r="A542" s="11">
         <v>43631</v>
       </c>
@@ -16734,7 +16734,7 @@
         <v>527989</v>
       </c>
     </row>
-    <row r="543" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="543" spans="1:5" ht="17" thickBot="1">
       <c r="A543" s="11">
         <v>43638</v>
       </c>
@@ -16752,7 +16752,7 @@
         <v>525116</v>
       </c>
     </row>
-    <row r="544" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="544" spans="1:5" ht="17" thickBot="1">
       <c r="A544" s="11">
         <v>43645</v>
       </c>
@@ -16770,7 +16770,7 @@
         <v>533164</v>
       </c>
     </row>
-    <row r="545" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="545" spans="1:5" ht="17" thickBot="1">
       <c r="A545" s="11">
         <v>43652</v>
       </c>
@@ -16788,7 +16788,7 @@
         <v>448459</v>
       </c>
     </row>
-    <row r="546" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="546" spans="1:5" ht="17" thickBot="1">
       <c r="A546" s="11">
         <v>43659</v>
       </c>
@@ -16806,7 +16806,7 @@
         <v>527908</v>
       </c>
     </row>
-    <row r="547" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="547" spans="1:5" ht="17" thickBot="1">
       <c r="A547" s="11">
         <v>43666</v>
       </c>
@@ -16824,7 +16824,7 @@
         <v>526010</v>
       </c>
     </row>
-    <row r="548" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="548" spans="1:5" ht="17" thickBot="1">
       <c r="A548" s="11">
         <v>43673</v>
       </c>
@@ -16842,7 +16842,7 @@
         <v>534498</v>
       </c>
     </row>
-    <row r="549" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="549" spans="1:5" ht="17" thickBot="1">
       <c r="A549" s="11">
         <v>43680</v>
       </c>
@@ -16860,7 +16860,7 @@
         <v>541558</v>
       </c>
     </row>
-    <row r="550" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="550" spans="1:5" ht="17" thickBot="1">
       <c r="A550" s="11">
         <v>43687</v>
       </c>
@@ -16878,7 +16878,7 @@
         <v>533190</v>
       </c>
     </row>
-    <row r="551" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="551" spans="1:5" ht="17" thickBot="1">
       <c r="A551" s="13">
         <v>43694</v>
       </c>
@@ -16896,7 +16896,7 @@
         <v>537617</v>
       </c>
     </row>
-    <row r="552" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="552" spans="1:5" ht="17" thickBot="1">
       <c r="A552" s="11">
         <v>43701</v>
       </c>
@@ -16914,7 +16914,7 @@
         <v>532483</v>
       </c>
     </row>
-    <row r="553" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="553" spans="1:5" ht="17" thickBot="1">
       <c r="A553" s="11">
         <v>43708</v>
       </c>
@@ -16932,7 +16932,7 @@
         <v>541945</v>
       </c>
     </row>
-    <row r="554" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="554" spans="1:5" ht="17" thickBot="1">
       <c r="A554" s="11">
         <v>43715</v>
       </c>
@@ -16950,7 +16950,7 @@
         <v>469285</v>
       </c>
     </row>
-    <row r="555" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="555" spans="1:5" ht="17" thickBot="1">
       <c r="A555" s="11">
         <v>43722</v>
       </c>
@@ -16968,7 +16968,7 @@
         <v>526734</v>
       </c>
     </row>
-    <row r="556" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="556" spans="1:5" ht="17" thickBot="1">
       <c r="A556" s="11">
         <v>43729</v>
       </c>
@@ -16986,7 +16986,7 @@
         <v>528670</v>
       </c>
     </row>
-    <row r="557" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="557" spans="1:5" ht="17" thickBot="1">
       <c r="A557" s="11">
         <v>43736</v>
       </c>
@@ -17004,7 +17004,7 @@
         <v>529336</v>
       </c>
     </row>
-    <row r="558" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="558" spans="1:5" ht="17" thickBot="1">
       <c r="A558" s="11">
         <v>43743</v>
       </c>
@@ -17022,7 +17022,7 @@
         <v>515061</v>
       </c>
     </row>
-    <row r="559" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="559" spans="1:5" ht="17" thickBot="1">
       <c r="A559" s="11">
         <v>43750</v>
       </c>
@@ -17040,7 +17040,7 @@
         <v>510820</v>
       </c>
     </row>
-    <row r="560" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="560" spans="1:5" ht="17" thickBot="1">
       <c r="A560" s="11">
         <v>43757</v>
       </c>
@@ -17058,7 +17058,7 @@
         <v>507381</v>
       </c>
     </row>
-    <row r="561" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="561" spans="1:5" ht="17" thickBot="1">
       <c r="A561" s="11">
         <v>43764</v>
       </c>
@@ -17076,7 +17076,7 @@
         <v>513147</v>
       </c>
     </row>
-    <row r="562" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="562" spans="1:5" ht="17" thickBot="1">
       <c r="A562" s="11">
         <v>43771</v>
       </c>
@@ -17094,7 +17094,7 @@
         <v>510012</v>
       </c>
     </row>
-    <row r="563" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="563" spans="1:5" ht="17" thickBot="1">
       <c r="A563" s="11">
         <v>43778</v>
       </c>
@@ -17112,7 +17112,7 @@
         <v>515269</v>
       </c>
     </row>
-    <row r="564" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="564" spans="1:5" ht="17" thickBot="1">
       <c r="A564" s="11">
         <v>43785</v>
       </c>
@@ -17130,7 +17130,7 @@
         <v>501249</v>
       </c>
     </row>
-    <row r="565" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="565" spans="1:5" ht="17" thickBot="1">
       <c r="A565" s="11">
         <v>43792</v>
       </c>
@@ -17148,7 +17148,7 @@
         <v>521927</v>
       </c>
     </row>
-    <row r="566" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="566" spans="1:5" ht="17" thickBot="1">
       <c r="A566" s="11">
         <v>43813</v>
       </c>
@@ -17166,7 +17166,7 @@
         <v>520589</v>
       </c>
     </row>
-    <row r="567" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="567" spans="1:5" ht="17" thickBot="1">
       <c r="A567" s="11">
         <v>43820</v>
       </c>
@@ -17184,7 +17184,7 @@
         <v>507589</v>
       </c>
     </row>
-    <row r="568" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="568" spans="1:5" ht="17" thickBot="1">
       <c r="A568" s="11">
         <v>43827</v>
       </c>
@@ -17202,7 +17202,7 @@
         <v>373728</v>
       </c>
     </row>
-    <row r="569" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="569" spans="1:5" ht="17" thickBot="1">
       <c r="A569" s="11">
         <v>43834</v>
       </c>
@@ -17220,7 +17220,7 @@
         <v>414014</v>
       </c>
     </row>
-    <row r="570" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="570" spans="1:5" ht="17" thickBot="1">
       <c r="A570" s="11">
         <v>43841</v>
       </c>
@@ -17238,7 +17238,7 @@
         <v>501624</v>
       </c>
     </row>
-    <row r="571" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="571" spans="1:5" ht="17" thickBot="1">
       <c r="A571" s="11">
         <v>43848</v>
       </c>
@@ -17256,7 +17256,7 @@
         <v>499732</v>
       </c>
     </row>
-    <row r="572" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="572" spans="1:5" ht="17" thickBot="1">
       <c r="A572" s="11">
         <v>43855</v>
       </c>
@@ -17274,7 +17274,7 @@
         <v>485282</v>
       </c>
     </row>
-    <row r="573" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="573" spans="1:5" ht="17" thickBot="1">
       <c r="A573" s="11">
         <v>43862</v>
       </c>
@@ -17292,7 +17292,7 @@
         <v>510161</v>
       </c>
     </row>
-    <row r="574" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="574" spans="1:5" ht="17" thickBot="1">
       <c r="A574" s="11">
         <v>43869</v>
       </c>
@@ -17310,7 +17310,7 @@
         <v>485329</v>
       </c>
     </row>
-    <row r="575" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="575" spans="1:5" ht="17" thickBot="1">
       <c r="A575" s="11">
         <v>43876</v>
       </c>
@@ -17328,7 +17328,7 @@
         <v>479137</v>
       </c>
     </row>
-    <row r="576" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="576" spans="1:5" ht="17" thickBot="1">
       <c r="A576" s="13">
         <v>43883</v>
       </c>
@@ -17346,7 +17346,7 @@
         <v>482690</v>
       </c>
     </row>
-    <row r="577" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="577" spans="1:5" ht="17" thickBot="1">
       <c r="A577" s="11">
         <v>43890</v>
       </c>
@@ -17364,7 +17364,7 @@
         <v>477611</v>
       </c>
     </row>
-    <row r="578" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="578" spans="1:5" ht="17" thickBot="1">
       <c r="A578" s="11">
         <v>43897</v>
       </c>
@@ -17397,7 +17397,7 @@
         <v>462303</v>
       </c>
     </row>
-    <row r="579" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="579" spans="1:5" ht="17" thickBot="1">
       <c r="A579" s="11">
         <v>43904</v>
       </c>
@@ -17415,7 +17415,7 @@
         <v>463017</v>
       </c>
     </row>
-    <row r="580" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="580" spans="1:5" ht="17" thickBot="1">
       <c r="A580" s="11">
         <v>43911</v>
       </c>
@@ -17433,7 +17433,7 @@
         <v>459966</v>
       </c>
     </row>
-    <row r="581" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="581" spans="1:5" ht="17" thickBot="1">
       <c r="A581" s="11">
         <v>43918</v>
       </c>
@@ -17451,7 +17451,7 @@
         <v>449767</v>
       </c>
     </row>
-    <row r="582" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="582" spans="1:5" ht="17" thickBot="1">
       <c r="A582" s="11">
         <v>43925</v>
       </c>
@@ -17469,7 +17469,7 @@
         <v>429095</v>
       </c>
     </row>
-    <row r="583" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="583" spans="1:5" ht="17" thickBot="1">
       <c r="A583" s="11">
         <v>43932</v>
       </c>
@@ -17487,7 +17487,7 @@
         <v>412503</v>
       </c>
     </row>
-    <row r="584" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="584" spans="1:5" ht="17" thickBot="1">
       <c r="A584" s="11">
         <v>43939</v>
       </c>
@@ -17505,7 +17505,7 @@
         <v>403283</v>
       </c>
     </row>
-    <row r="585" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="585" spans="1:5" ht="17" thickBot="1">
       <c r="A585" s="11">
         <v>43946</v>
       </c>
@@ -17523,7 +17523,7 @@
         <v>414123</v>
       </c>
     </row>
-    <row r="586" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="586" spans="1:5" ht="17" thickBot="1">
       <c r="A586" s="11">
         <v>43953</v>
       </c>
@@ -17541,7 +17541,7 @@
         <v>416954</v>
       </c>
     </row>
-    <row r="587" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="587" spans="1:5" ht="17" thickBot="1">
       <c r="A587" s="11">
         <v>43960</v>
       </c>
@@ -17559,7 +17559,7 @@
         <v>412549</v>
       </c>
     </row>
-    <row r="588" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="588" spans="1:5" ht="17" thickBot="1">
       <c r="A588" s="11">
         <v>43967</v>
       </c>
@@ -17577,7 +17577,7 @@
         <v>416115</v>
       </c>
     </row>
-    <row r="589" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="589" spans="1:5" ht="17" thickBot="1">
       <c r="A589" s="11">
         <v>43974</v>
       </c>
@@ -17595,7 +17595,7 @@
         <v>428715</v>
       </c>
     </row>
-    <row r="590" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="590" spans="1:5" ht="17" thickBot="1">
       <c r="A590" s="11">
         <v>43981</v>
       </c>
@@ -17613,7 +17613,7 @@
         <v>395714</v>
       </c>
     </row>
-    <row r="591" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="591" spans="1:5" ht="17" thickBot="1">
       <c r="A591" s="11">
         <v>43988</v>
       </c>
@@ -17631,7 +17631,7 @@
         <v>433171</v>
       </c>
     </row>
-    <row r="592" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="592" spans="1:5" ht="17" thickBot="1">
       <c r="A592" s="11">
         <v>43995</v>
       </c>
@@ -17649,7 +17649,7 @@
         <v>449291</v>
       </c>
     </row>
-    <row r="593" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="593" spans="1:5" ht="17" thickBot="1">
       <c r="A593" s="11">
         <v>44002</v>
       </c>
@@ -17667,7 +17667,7 @@
         <v>457278</v>
       </c>
     </row>
-    <row r="594" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="594" spans="1:5" ht="17" thickBot="1">
       <c r="A594" s="11">
         <v>44009</v>
       </c>
@@ -17685,7 +17685,7 @@
         <v>459449</v>
       </c>
     </row>
-    <row r="595" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="595" spans="1:5" ht="17" thickBot="1">
       <c r="A595" s="11">
         <v>44016</v>
       </c>
@@ -17703,7 +17703,7 @@
         <v>437989</v>
       </c>
     </row>
-    <row r="596" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="596" spans="1:5" ht="17" thickBot="1">
       <c r="A596" s="11">
         <v>44023</v>
       </c>
@@ -17721,7 +17721,7 @@
         <v>449092</v>
       </c>
     </row>
-    <row r="597" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="597" spans="1:5" ht="17" thickBot="1">
       <c r="A597" s="11">
         <v>44030</v>
       </c>
@@ -17739,7 +17739,7 @@
         <v>481597</v>
       </c>
     </row>
-    <row r="598" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="598" spans="1:5" ht="17" thickBot="1">
       <c r="A598" s="11">
         <v>44037</v>
       </c>
@@ -17757,7 +17757,7 @@
         <v>481331</v>
       </c>
     </row>
-    <row r="599" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="599" spans="1:5" ht="17" thickBot="1">
       <c r="A599" s="11">
         <v>44044</v>
       </c>
@@ -17775,7 +17775,7 @@
         <v>487968</v>
       </c>
     </row>
-    <row r="600" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="600" spans="1:5" ht="17" thickBot="1">
       <c r="A600" s="11">
         <v>44051</v>
       </c>
@@ -17793,7 +17793,7 @@
         <v>497397</v>
       </c>
     </row>
-    <row r="601" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="601" spans="1:5" ht="17" thickBot="1">
       <c r="A601" s="13">
         <v>44058</v>
       </c>
@@ -17811,7 +17811,7 @@
         <v>500563</v>
       </c>
     </row>
-    <row r="602" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="602" spans="1:5" ht="17" thickBot="1">
       <c r="A602" s="11">
         <v>44072</v>
       </c>
@@ -17829,7 +17829,7 @@
         <v>508307</v>
       </c>
     </row>
-    <row r="603" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="603" spans="1:5" ht="17" thickBot="1">
       <c r="A603" s="11">
         <v>44079</v>
       </c>
@@ -17847,7 +17847,7 @@
         <v>509637</v>
       </c>
     </row>
-    <row r="604" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="604" spans="1:5" ht="17" thickBot="1">
       <c r="A604" s="11">
         <v>44086</v>
       </c>
@@ -17865,7 +17865,7 @@
         <v>474785</v>
       </c>
     </row>
-    <row r="605" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="605" spans="1:5" ht="17" thickBot="1">
       <c r="A605" s="11">
         <v>44093</v>
       </c>
@@ -17883,7 +17883,7 @@
         <v>521956</v>
       </c>
     </row>
-    <row r="606" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="606" spans="1:5" ht="17" thickBot="1">
       <c r="A606" s="11">
         <v>44100</v>
       </c>
@@ -17901,7 +17901,7 @@
         <v>518290</v>
       </c>
     </row>
-    <row r="607" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="607" spans="1:5" ht="17" thickBot="1">
       <c r="A607" s="11">
         <v>44107</v>
       </c>
@@ -17919,7 +17919,7 @@
         <v>518761</v>
       </c>
     </row>
-    <row r="608" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="608" spans="1:5" ht="17" thickBot="1">
       <c r="A608" s="11">
         <v>44114</v>
       </c>
@@ -17937,7 +17937,7 @@
         <v>520452</v>
       </c>
     </row>
-    <row r="609" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="609" spans="1:5" ht="17" thickBot="1">
       <c r="A609" s="11">
         <v>44121</v>
       </c>
@@ -17955,7 +17955,7 @@
         <v>518763</v>
       </c>
     </row>
-    <row r="610" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="610" spans="1:5" ht="17" thickBot="1">
       <c r="A610" s="11">
         <v>44128</v>
       </c>
@@ -17973,7 +17973,7 @@
         <v>522653</v>
       </c>
     </row>
-    <row r="611" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="611" spans="1:5" ht="17" thickBot="1">
       <c r="A611" s="11">
         <v>44135</v>
       </c>
@@ -17991,7 +17991,7 @@
         <v>520778</v>
       </c>
     </row>
-    <row r="612" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="612" spans="1:5" ht="17" thickBot="1">
       <c r="A612" s="11">
         <v>44142</v>
       </c>
@@ -18009,7 +18009,7 @@
         <v>522028</v>
       </c>
     </row>
-    <row r="613" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="613" spans="1:5" ht="17" thickBot="1">
       <c r="A613" s="11">
         <v>44149</v>
       </c>
@@ -18027,7 +18027,7 @@
         <v>527462</v>
       </c>
     </row>
-    <row r="614" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="614" spans="1:5" ht="17" thickBot="1">
       <c r="A614" s="11">
         <v>44156</v>
       </c>
@@ -18045,7 +18045,7 @@
         <v>534607</v>
       </c>
     </row>
-    <row r="615" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="615" spans="1:5" ht="17" thickBot="1">
       <c r="A615" s="11">
         <v>44163</v>
       </c>
@@ -18063,7 +18063,7 @@
         <v>452792</v>
       </c>
     </row>
-    <row r="616" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="616" spans="1:5" ht="17" thickBot="1">
       <c r="A616" s="11">
         <v>44170</v>
       </c>
@@ -18081,7 +18081,7 @@
         <v>542203</v>
       </c>
     </row>
-    <row r="617" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="617" spans="1:5" ht="17" thickBot="1">
       <c r="A617" s="11">
         <v>44177</v>
       </c>
@@ -18099,7 +18099,7 @@
         <v>546209</v>
       </c>
     </row>
-    <row r="618" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="618" spans="1:5" ht="17" thickBot="1">
       <c r="A618" s="11">
         <v>44191</v>
       </c>
@@ -18117,7 +18117,7 @@
         <v>405111</v>
       </c>
     </row>
-    <row r="619" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="619" spans="1:5" ht="17" thickBot="1">
       <c r="A619" s="11">
         <v>44198</v>
       </c>
@@ -18135,7 +18135,7 @@
         <v>421991</v>
       </c>
     </row>
-    <row r="620" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="620" spans="1:5" ht="17" thickBot="1">
       <c r="A620" s="11">
         <v>44205</v>
       </c>
@@ -18153,7 +18153,7 @@
         <v>525253</v>
       </c>
     </row>
-    <row r="621" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="621" spans="1:5" ht="17" thickBot="1">
       <c r="A621" s="11">
         <v>44212</v>
       </c>
@@ -18171,7 +18171,7 @@
         <v>528547</v>
       </c>
     </row>
-    <row r="622" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="622" spans="1:5" ht="17" thickBot="1">
       <c r="A622" s="11">
         <v>44219</v>
       </c>
@@ -18189,7 +18189,7 @@
         <v>529030</v>
       </c>
     </row>
-    <row r="623" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="623" spans="1:5" ht="17" thickBot="1">
       <c r="A623" s="11">
         <v>44226</v>
       </c>
@@ -18207,7 +18207,7 @@
         <v>520693</v>
       </c>
     </row>
-    <row r="624" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="624" spans="1:5" ht="17" thickBot="1">
       <c r="A624" s="11">
         <v>44233</v>
       </c>
@@ -18225,7 +18225,7 @@
         <v>495815</v>
       </c>
     </row>
-    <row r="625" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="625" spans="1:5" ht="17" thickBot="1">
       <c r="A625" s="11">
         <v>44240</v>
       </c>
@@ -18243,7 +18243,7 @@
         <v>480483</v>
       </c>
     </row>
-    <row r="626" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="626" spans="1:5" ht="17" thickBot="1">
       <c r="A626" s="13">
         <v>44247</v>
       </c>
@@ -18261,7 +18261,7 @@
         <v>377904</v>
       </c>
     </row>
-    <row r="627" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="627" spans="1:5" ht="17" thickBot="1">
       <c r="A627" s="11">
         <v>44254</v>
       </c>
@@ -18279,7 +18279,7 @@
         <v>486429</v>
       </c>
     </row>
-    <row r="628" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="628" spans="1:5" ht="17" thickBot="1">
       <c r="A628" s="11">
         <v>44261</v>
       </c>
@@ -18297,7 +18297,7 @@
         <v>515135</v>
       </c>
     </row>
-    <row r="629" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="629" spans="1:5" ht="17" thickBot="1">
       <c r="A629" s="11">
         <v>44268</v>
       </c>
@@ -18315,7 +18315,7 @@
         <v>520736</v>
       </c>
     </row>
-    <row r="630" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="630" spans="1:5" ht="17" thickBot="1">
       <c r="A630" s="11">
         <v>44275</v>
       </c>
@@ -18333,7 +18333,7 @@
         <v>513325</v>
       </c>
     </row>
-    <row r="631" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="631" spans="1:5" ht="17" thickBot="1">
       <c r="A631" s="11">
         <v>44282</v>
       </c>
@@ -18351,7 +18351,7 @@
         <v>521731</v>
       </c>
     </row>
-    <row r="632" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="632" spans="1:5" ht="17" thickBot="1">
       <c r="A632" s="11">
         <v>44289</v>
       </c>
@@ -18369,7 +18369,7 @@
         <v>515562</v>
       </c>
     </row>
-    <row r="633" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="633" spans="1:5" ht="17" thickBot="1">
       <c r="A633" s="11">
         <v>44296</v>
       </c>
@@ -18387,7 +18387,7 @@
         <v>513724</v>
       </c>
     </row>
-    <row r="634" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="634" spans="1:5" ht="17" thickBot="1">
       <c r="A634" s="11">
         <v>44303</v>
       </c>
@@ -18405,7 +18405,7 @@
         <v>533217</v>
       </c>
     </row>
-    <row r="635" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="635" spans="1:5" ht="17" thickBot="1">
       <c r="A635" s="11">
         <v>44310</v>
       </c>
@@ -18423,7 +18423,7 @@
         <v>538184</v>
       </c>
     </row>
-    <row r="636" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="636" spans="1:5" ht="17" thickBot="1">
       <c r="A636" s="11">
         <v>44317</v>
       </c>
@@ -18441,7 +18441,7 @@
         <v>540667</v>
       </c>
     </row>
-    <row r="637" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="637" spans="1:5" ht="17" thickBot="1">
       <c r="A637" s="11">
         <v>44324</v>
       </c>
@@ -18459,7 +18459,7 @@
         <v>523309</v>
       </c>
     </row>
-    <row r="638" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="638" spans="1:5" ht="17" thickBot="1">
       <c r="A638" s="11">
         <v>44331</v>
       </c>
@@ -18477,7 +18477,7 @@
         <v>533872</v>
       </c>
     </row>
-    <row r="639" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="639" spans="1:5" ht="17" thickBot="1">
       <c r="A639" s="11">
         <v>44338</v>
       </c>
@@ -18495,7 +18495,7 @@
         <v>528774</v>
       </c>
     </row>
-    <row r="640" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="640" spans="1:5" ht="17" thickBot="1">
       <c r="A640" s="11">
         <v>44345</v>
       </c>
@@ -18513,7 +18513,7 @@
         <v>530225</v>
       </c>
     </row>
-    <row r="641" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="641" spans="1:5" ht="17" thickBot="1">
       <c r="A641" s="11">
         <v>44352</v>
       </c>
@@ -18531,7 +18531,7 @@
         <v>489144</v>
       </c>
     </row>
-    <row r="642" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="642" spans="1:5" ht="17" thickBot="1">
       <c r="A642" s="11">
         <v>44359</v>
       </c>
@@ -18564,7 +18564,7 @@
         <v>529635</v>
       </c>
     </row>
-    <row r="643" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="643" spans="1:5" ht="17" thickBot="1">
       <c r="A643" s="11">
         <v>44366</v>
       </c>
@@ -18582,7 +18582,7 @@
         <v>514112</v>
       </c>
     </row>
-    <row r="644" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="644" spans="1:5" ht="17" thickBot="1">
       <c r="A644" s="11">
         <v>44373</v>
       </c>
@@ -18600,7 +18600,7 @@
         <v>516167</v>
       </c>
     </row>
-    <row r="645" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="645" spans="1:5" ht="17" thickBot="1">
       <c r="A645" s="11">
         <v>44380</v>
       </c>
@@ -18618,7 +18618,7 @@
         <v>512919</v>
       </c>
     </row>
-    <row r="646" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="646" spans="1:5" ht="17" thickBot="1">
       <c r="A646" s="11">
         <v>44387</v>
       </c>
@@ -18636,7 +18636,7 @@
         <v>451825</v>
       </c>
     </row>
-    <row r="647" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="647" spans="1:5" ht="17" thickBot="1">
       <c r="A647" s="11">
         <v>44394</v>
       </c>
@@ -18654,7 +18654,7 @@
         <v>513255</v>
       </c>
     </row>
-    <row r="648" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="648" spans="1:5" ht="17" thickBot="1">
       <c r="A648" s="11">
         <v>44401</v>
       </c>
@@ -18672,7 +18672,7 @@
         <v>503219</v>
       </c>
     </row>
-    <row r="649" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="649" spans="1:5" ht="17" thickBot="1">
       <c r="A649" s="11">
         <v>44408</v>
       </c>
@@ -18690,7 +18690,7 @@
         <v>502540</v>
       </c>
     </row>
-    <row r="650" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="650" spans="1:5" ht="17" thickBot="1">
       <c r="A650" s="11">
         <v>44415</v>
       </c>
@@ -18708,7 +18708,7 @@
         <v>509607</v>
       </c>
     </row>
-    <row r="651" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="651" spans="1:5" ht="17" thickBot="1">
       <c r="A651" s="13">
         <v>44422</v>
       </c>
@@ -18726,7 +18726,7 @@
         <v>504810</v>
       </c>
     </row>
-    <row r="652" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="652" spans="1:5" ht="17" thickBot="1">
       <c r="A652" s="11">
         <v>44429</v>
       </c>
@@ -18744,7 +18744,7 @@
         <v>501273</v>
       </c>
     </row>
-    <row r="653" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="653" spans="1:5" ht="17" thickBot="1">
       <c r="A653" s="11">
         <v>44436</v>
       </c>
@@ -18762,7 +18762,7 @@
         <v>504417</v>
       </c>
     </row>
-    <row r="654" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="654" spans="1:5" ht="17" thickBot="1">
       <c r="A654" s="11">
         <v>44443</v>
       </c>
@@ -18780,7 +18780,7 @@
         <v>494415</v>
       </c>
     </row>
-    <row r="655" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="655" spans="1:5" ht="17" thickBot="1">
       <c r="A655" s="11">
         <v>44450</v>
       </c>
@@ -18798,7 +18798,7 @@
         <v>468610</v>
       </c>
     </row>
-    <row r="656" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="656" spans="1:5" ht="17" thickBot="1">
       <c r="A656" s="11">
         <v>44457</v>
       </c>
@@ -18816,7 +18816,7 @@
         <v>505622</v>
       </c>
     </row>
-    <row r="657" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="657" spans="1:5" ht="17" thickBot="1">
       <c r="A657" s="11">
         <v>44464</v>
       </c>
@@ -18834,7 +18834,7 @@
         <v>511713</v>
       </c>
     </row>
-    <row r="658" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="658" spans="1:5" ht="17" thickBot="1">
       <c r="A658" s="11">
         <v>44471</v>
       </c>
@@ -18852,7 +18852,7 @@
         <v>515849</v>
       </c>
     </row>
-    <row r="659" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="659" spans="1:5" ht="17" thickBot="1">
       <c r="A659" s="11">
         <v>44478</v>
       </c>
@@ -18870,7 +18870,7 @@
         <v>506642</v>
       </c>
     </row>
-    <row r="660" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="660" spans="1:5" ht="17" thickBot="1">
       <c r="A660" s="11">
         <v>44485</v>
       </c>
@@ -18888,7 +18888,7 @@
         <v>496983</v>
       </c>
     </row>
-    <row r="661" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="661" spans="1:5" ht="17" thickBot="1">
       <c r="A661" s="11">
         <v>44492</v>
       </c>
@@ -18906,7 +18906,7 @@
         <v>510762</v>
       </c>
     </row>
-    <row r="662" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="662" spans="1:5" ht="17" thickBot="1">
       <c r="A662" s="11">
         <v>44499</v>
       </c>
@@ -18924,7 +18924,7 @@
         <v>510141</v>
       </c>
     </row>
-    <row r="663" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="663" spans="1:5" ht="17" thickBot="1">
       <c r="A663" s="11">
         <v>44506</v>
       </c>
@@ -18942,7 +18942,7 @@
         <v>504111</v>
       </c>
     </row>
-    <row r="664" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="664" spans="1:5" ht="17" thickBot="1">
       <c r="A664" s="11">
         <v>44513</v>
       </c>
@@ -18960,7 +18960,7 @@
         <v>502613</v>
       </c>
     </row>
-    <row r="665" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="665" spans="1:5" ht="17" thickBot="1">
       <c r="A665" s="11">
         <v>44520</v>
       </c>
@@ -18978,7 +18978,7 @@
         <v>508309</v>
       </c>
     </row>
-    <row r="666" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="666" spans="1:5" ht="17" thickBot="1">
       <c r="A666" s="11">
         <v>44527</v>
       </c>
@@ -18996,7 +18996,7 @@
         <v>430793</v>
       </c>
     </row>
-    <row r="667" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="667" spans="1:5" ht="17" thickBot="1">
       <c r="A667" s="11">
         <v>44534</v>
       </c>
@@ -19014,7 +19014,7 @@
         <v>527406</v>
       </c>
     </row>
-    <row r="668" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="668" spans="1:5" ht="17" thickBot="1">
       <c r="A668" s="11">
         <v>44541</v>
       </c>
@@ -19032,7 +19032,7 @@
         <v>513366</v>
       </c>
     </row>
-    <row r="669" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="669" spans="1:5" ht="17" thickBot="1">
       <c r="A669" s="11">
         <v>44548</v>
       </c>
@@ -19050,7 +19050,7 @@
         <v>504099</v>
       </c>
     </row>
-    <row r="670" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="670" spans="1:5" ht="17" thickBot="1">
       <c r="A670" s="11">
         <v>44555</v>
       </c>
@@ -19068,7 +19068,7 @@
         <v>420373</v>
       </c>
     </row>
-    <row r="671" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="671" spans="1:5" ht="17" thickBot="1">
       <c r="A671" s="11">
         <v>44562</v>
       </c>
@@ -19086,7 +19086,7 @@
         <v>395371</v>
       </c>
     </row>
-    <row r="672" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="672" spans="1:5" ht="17" thickBot="1">
       <c r="A672" s="11">
         <v>44569</v>
       </c>
@@ -19104,7 +19104,7 @@
         <v>440761</v>
       </c>
     </row>
-    <row r="673" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="673" spans="1:5" ht="17" thickBot="1">
       <c r="A673" s="11">
         <v>44576</v>
       </c>
@@ -19122,7 +19122,7 @@
         <v>493617</v>
       </c>
     </row>
-    <row r="674" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="674" spans="1:5" ht="17" thickBot="1">
       <c r="A674" s="11">
         <v>44583</v>
       </c>
@@ -19140,7 +19140,7 @@
         <v>477462</v>
       </c>
     </row>
-    <row r="675" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="675" spans="1:5" ht="17" thickBot="1">
       <c r="A675" s="11">
         <v>44590</v>
       </c>
@@ -19158,7 +19158,7 @@
         <v>491868</v>
       </c>
     </row>
-    <row r="676" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="676" spans="1:5" ht="17" thickBot="1">
       <c r="A676" s="13">
         <v>44597</v>
       </c>
@@ -19176,7 +19176,7 @@
         <v>458152</v>
       </c>
     </row>
-    <row r="677" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="677" spans="1:5" ht="17" thickBot="1">
       <c r="A677" s="11">
         <v>44604</v>
       </c>
@@ -19194,7 +19194,7 @@
         <v>504482</v>
       </c>
     </row>
-    <row r="678" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="678" spans="1:5" ht="17" thickBot="1">
       <c r="A678" s="11">
         <v>44611</v>
       </c>
@@ -19212,7 +19212,7 @@
         <v>497822</v>
       </c>
     </row>
-    <row r="679" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="679" spans="1:5" ht="17" thickBot="1">
       <c r="A679" s="11">
         <v>44625</v>
       </c>
@@ -19230,7 +19230,7 @@
         <v>505177</v>
       </c>
     </row>
-    <row r="680" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="680" spans="1:5" ht="17" thickBot="1">
       <c r="A680" s="11">
         <v>44632</v>
       </c>
@@ -19248,7 +19248,7 @@
         <v>496134</v>
       </c>
     </row>
-    <row r="681" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="681" spans="1:5" ht="17" thickBot="1">
       <c r="A681" s="11">
         <v>44639</v>
       </c>
@@ -19266,7 +19266,7 @@
         <v>499362</v>
       </c>
     </row>
-    <row r="682" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="682" spans="1:5" ht="17" thickBot="1">
       <c r="A682" s="11">
         <v>44646</v>
       </c>
@@ -19284,7 +19284,7 @@
         <v>504817</v>
       </c>
     </row>
-    <row r="683" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="683" spans="1:5" ht="17" thickBot="1">
       <c r="A683" s="11">
         <v>44653</v>
       </c>
@@ -19302,7 +19302,7 @@
         <v>502194</v>
       </c>
     </row>
-    <row r="684" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="684" spans="1:5" ht="17" thickBot="1">
       <c r="A684" s="11">
         <v>44660</v>
       </c>
@@ -19320,7 +19320,7 @@
         <v>508343</v>
       </c>
     </row>
-    <row r="685" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="685" spans="1:5" ht="17" thickBot="1">
       <c r="A685" s="11">
         <v>44667</v>
       </c>
@@ -19338,7 +19338,7 @@
         <v>489801</v>
       </c>
     </row>
-    <row r="686" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="686" spans="1:5" ht="17" thickBot="1">
       <c r="A686" s="11">
         <v>44674</v>
       </c>
@@ -19356,7 +19356,7 @@
         <v>498011</v>
       </c>
     </row>
-    <row r="687" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="687" spans="1:5" ht="17" thickBot="1">
       <c r="A687" s="11">
         <v>44681</v>
       </c>
@@ -19374,7 +19374,7 @@
         <v>506699</v>
       </c>
     </row>
-    <row r="688" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="688" spans="1:5" ht="17" thickBot="1">
       <c r="A688" s="11">
         <v>44688</v>
       </c>
@@ -19392,7 +19392,7 @@
         <v>504927</v>
       </c>
     </row>
-    <row r="689" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="689" spans="1:5" ht="17" thickBot="1">
       <c r="A689" s="11">
         <v>44695</v>
       </c>
@@ -19410,7 +19410,7 @@
         <v>505120</v>
       </c>
     </row>
-    <row r="690" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="690" spans="1:5" ht="17" thickBot="1">
       <c r="A690" s="11">
         <v>44702</v>
       </c>
@@ -19428,7 +19428,7 @@
         <v>506976</v>
       </c>
     </row>
-    <row r="691" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="691" spans="1:5" ht="17" thickBot="1">
       <c r="A691" s="11">
         <v>44709</v>
       </c>
@@ -19446,7 +19446,7 @@
         <v>514277</v>
       </c>
     </row>
-    <row r="692" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="692" spans="1:5" ht="17" thickBot="1">
       <c r="A692" s="11">
         <v>44716</v>
       </c>
@@ -19464,7 +19464,7 @@
         <v>475513</v>
       </c>
     </row>
-    <row r="693" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="693" spans="1:5" ht="17" thickBot="1">
       <c r="A693" s="11">
         <v>44723</v>
       </c>
@@ -19482,7 +19482,7 @@
         <v>510295</v>
       </c>
     </row>
-    <row r="694" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="694" spans="1:5" ht="17" thickBot="1">
       <c r="A694" s="11">
         <v>44730</v>
       </c>
@@ -19500,7 +19500,7 @@
         <v>501207</v>
       </c>
     </row>
-    <row r="695" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="695" spans="1:5" ht="17" thickBot="1">
       <c r="A695" s="11">
         <v>44737</v>
       </c>
@@ -19518,7 +19518,7 @@
         <v>493374</v>
       </c>
     </row>
-    <row r="696" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="696" spans="1:5" ht="17" thickBot="1">
       <c r="A696" s="11">
         <v>44744</v>
       </c>
@@ -19536,7 +19536,7 @@
         <v>500285</v>
       </c>
     </row>
-    <row r="697" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="697" spans="1:5" ht="17" thickBot="1">
       <c r="A697" s="11">
         <v>44751</v>
       </c>
@@ -19554,7 +19554,7 @@
         <v>437600</v>
       </c>
     </row>
-    <row r="698" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="698" spans="1:5" ht="17" thickBot="1">
       <c r="A698" s="11">
         <v>44758</v>
       </c>
@@ -19572,7 +19572,7 @@
         <v>498899</v>
       </c>
     </row>
-    <row r="699" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="699" spans="1:5" ht="17" thickBot="1">
       <c r="A699" s="11">
         <v>44765</v>
       </c>
@@ -19590,7 +19590,7 @@
         <v>498901</v>
       </c>
     </row>
-    <row r="700" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="700" spans="1:5" ht="17" thickBot="1">
       <c r="A700" s="11">
         <v>44772</v>
       </c>
@@ -19608,7 +19608,7 @@
         <v>505409</v>
       </c>
     </row>
-    <row r="701" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="701" spans="1:5" ht="17" thickBot="1">
       <c r="A701" s="13">
         <v>44779</v>
       </c>
@@ -19626,7 +19626,7 @@
         <v>496526</v>
       </c>
     </row>
-    <row r="702" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="702" spans="1:5" ht="17" thickBot="1">
       <c r="A702" s="11">
         <v>44786</v>
       </c>
@@ -19644,7 +19644,7 @@
         <v>502775</v>
       </c>
     </row>
-    <row r="703" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="703" spans="1:5" ht="17" thickBot="1">
       <c r="A703" s="11">
         <v>44793</v>
       </c>
@@ -19662,7 +19662,7 @@
         <v>501548</v>
       </c>
     </row>
-    <row r="704" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="704" spans="1:5" ht="17" thickBot="1">
       <c r="A704" s="11">
         <v>44800</v>
       </c>
@@ -19680,7 +19680,7 @@
         <v>511574</v>
       </c>
     </row>
-    <row r="705" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="705" spans="1:5" ht="17" thickBot="1">
       <c r="A705" s="11">
         <v>44807</v>
       </c>
@@ -19698,7 +19698,7 @@
         <v>513087</v>
       </c>
     </row>
-    <row r="706" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="706" spans="1:5" ht="17" thickBot="1">
       <c r="A706" s="11">
         <v>44814</v>
       </c>
@@ -19731,7 +19731,7 @@
         <v>464261</v>
       </c>
     </row>
-    <row r="707" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="707" spans="1:5" ht="17" thickBot="1">
       <c r="A707" s="11">
         <v>44821</v>
       </c>
@@ -19749,7 +19749,7 @@
         <v>490654</v>
       </c>
     </row>
-    <row r="708" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="708" spans="1:5" ht="17" thickBot="1">
       <c r="A708" s="11">
         <v>44828</v>
       </c>
@@ -19767,7 +19767,7 @@
         <v>489111</v>
       </c>
     </row>
-    <row r="709" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="709" spans="1:5" ht="17" thickBot="1">
       <c r="A709" s="11">
         <v>44835</v>
       </c>
@@ -19785,7 +19785,7 @@
         <v>495868</v>
       </c>
     </row>
-    <row r="710" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="710" spans="1:5" ht="17" thickBot="1">
       <c r="A710" s="11">
         <v>44842</v>
       </c>
@@ -19803,7 +19803,7 @@
         <v>494413</v>
       </c>
     </row>
-    <row r="711" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="711" spans="1:5" ht="17" thickBot="1">
       <c r="A711" s="11">
         <v>44849</v>
       </c>
@@ -19821,7 +19821,7 @@
         <v>500304</v>
       </c>
     </row>
-    <row r="712" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="712" spans="1:5" ht="17" thickBot="1">
       <c r="A712" s="11">
         <v>44856</v>
       </c>
@@ -19839,7 +19839,7 @@
         <v>505322</v>
       </c>
     </row>
-    <row r="713" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="713" spans="1:5" ht="17" thickBot="1">
       <c r="A713" s="11">
         <v>44863</v>
       </c>
@@ -19857,7 +19857,7 @@
         <v>514457</v>
       </c>
     </row>
-    <row r="714" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="714" spans="1:5" ht="17" thickBot="1">
       <c r="A714" s="11">
         <v>44870</v>
       </c>
@@ -19875,7 +19875,7 @@
         <v>502106</v>
       </c>
     </row>
-    <row r="715" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="715" spans="1:5" ht="17" thickBot="1">
       <c r="A715" s="11">
         <v>44877</v>
       </c>
@@ -19893,7 +19893,7 @@
         <v>490350</v>
       </c>
     </row>
-    <row r="716" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="716" spans="1:5" ht="17" thickBot="1">
       <c r="A716" s="11">
         <v>44884</v>
       </c>
@@ -19911,7 +19911,7 @@
         <v>491794</v>
       </c>
     </row>
-    <row r="717" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="717" spans="1:5" ht="17" thickBot="1">
       <c r="A717" s="11">
         <v>44891</v>
       </c>
@@ -19929,7 +19929,7 @@
         <v>413305</v>
       </c>
     </row>
-    <row r="718" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="718" spans="1:5" ht="17" thickBot="1">
       <c r="A718" s="11">
         <v>44898</v>
       </c>
@@ -19947,7 +19947,7 @@
         <v>495472</v>
       </c>
     </row>
-    <row r="719" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="719" spans="1:5" ht="17" thickBot="1">
       <c r="A719" s="11">
         <v>44905</v>
       </c>
@@ -19965,7 +19965,7 @@
         <v>500310</v>
       </c>
     </row>
-    <row r="720" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="720" spans="1:5" ht="17" thickBot="1">
       <c r="A720" s="11">
         <v>44912</v>
       </c>
@@ -19983,7 +19983,7 @@
         <v>476232</v>
       </c>
     </row>
-    <row r="721" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="721" spans="1:5" ht="17" thickBot="1">
       <c r="A721" s="11">
         <v>44919</v>
       </c>
@@ -20001,7 +20001,7 @@
         <v>400289</v>
       </c>
     </row>
-    <row r="722" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="722" spans="1:5" ht="17" thickBot="1">
       <c r="A722" s="11">
         <v>44926</v>
       </c>
@@ -20019,7 +20019,7 @@
         <v>365553</v>
       </c>
     </row>
-    <row r="723" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="723" spans="1:5" ht="17" thickBot="1">
       <c r="A723" s="11">
         <v>44933</v>
       </c>
@@ -20037,7 +20037,7 @@
         <v>416489</v>
       </c>
     </row>
-    <row r="724" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="724" spans="1:5" ht="17" thickBot="1">
       <c r="A724" s="11">
         <v>44940</v>
       </c>
@@ -20055,7 +20055,7 @@
         <v>486000</v>
       </c>
     </row>
-    <row r="725" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="725" spans="1:5" ht="17" thickBot="1">
       <c r="A725" s="11">
         <v>44947</v>
       </c>
@@ -20073,7 +20073,7 @@
         <v>467485</v>
       </c>
     </row>
-    <row r="726" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="726" spans="1:5" ht="17" thickBot="1">
       <c r="A726" s="13">
         <v>44954</v>
       </c>
@@ -20091,7 +20091,7 @@
         <v>473650</v>
       </c>
     </row>
-    <row r="727" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="727" spans="1:5" ht="17" thickBot="1">
       <c r="A727" s="11">
         <v>44961</v>
       </c>
@@ -20109,7 +20109,7 @@
         <v>449586</v>
       </c>
     </row>
-    <row r="728" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="728" spans="1:5" ht="17" thickBot="1">
       <c r="A728" s="11">
         <v>44968</v>
       </c>
@@ -20127,7 +20127,7 @@
         <v>473972</v>
       </c>
     </row>
-    <row r="729" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="729" spans="1:5" ht="17" thickBot="1">
       <c r="A729" s="11">
         <v>44975</v>
       </c>
@@ -20145,7 +20145,7 @@
         <v>466932</v>
       </c>
     </row>
-    <row r="730" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="730" spans="1:5" ht="17" thickBot="1">
       <c r="A730" s="11">
         <v>44982</v>
       </c>
@@ -20163,7 +20163,7 @@
         <v>459233</v>
       </c>
     </row>
-    <row r="731" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="731" spans="1:5" ht="17" thickBot="1">
       <c r="A731" s="11">
         <v>44989</v>
       </c>
@@ -20181,7 +20181,7 @@
         <v>474191</v>
       </c>
     </row>
-    <row r="732" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="732" spans="1:5" ht="17" thickBot="1">
       <c r="A732" s="11">
         <v>44996</v>
       </c>
@@ -20199,7 +20199,7 @@
         <v>458629</v>
       </c>
     </row>
-    <row r="733" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="733" spans="1:5" ht="17" thickBot="1">
       <c r="A733" s="11">
         <v>45003</v>
       </c>
@@ -20217,7 +20217,7 @@
         <v>453500</v>
       </c>
     </row>
-    <row r="734" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="734" spans="1:5" ht="17" thickBot="1">
       <c r="A734" s="11">
         <v>45010</v>
       </c>
@@ -20235,7 +20235,7 @@
         <v>469958</v>
       </c>
     </row>
-    <row r="735" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="735" spans="1:5" ht="17" thickBot="1">
       <c r="A735" s="11">
         <v>45017</v>
       </c>
@@ -20253,7 +20253,7 @@
         <v>467430</v>
       </c>
     </row>
-    <row r="736" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="736" spans="1:5" ht="17" thickBot="1">
       <c r="A736" s="11">
         <v>45024</v>
       </c>
@@ -20271,7 +20271,7 @@
         <v>451336</v>
       </c>
     </row>
-    <row r="737" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="737" spans="1:5" ht="17" thickBot="1">
       <c r="A737" s="11">
         <v>45031</v>
       </c>
@@ -20289,7 +20289,7 @@
         <v>468197</v>
       </c>
     </row>
-    <row r="738" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="738" spans="1:5" ht="17" thickBot="1">
       <c r="A738" s="11">
         <v>45038</v>
       </c>
@@ -20307,7 +20307,7 @@
         <v>480457</v>
       </c>
     </row>
-    <row r="739" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="739" spans="1:5" ht="17" thickBot="1">
       <c r="A739" s="11">
         <v>45045</v>
       </c>
@@ -20325,7 +20325,7 @@
         <v>481960</v>
       </c>
     </row>
-    <row r="740" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="740" spans="1:5" ht="17" thickBot="1">
       <c r="A740" s="11">
         <v>45052</v>
       </c>
@@ -20343,7 +20343,7 @@
         <v>471859</v>
       </c>
     </row>
-    <row r="741" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="741" spans="1:5" ht="17" thickBot="1">
       <c r="A741" s="11">
         <v>45059</v>
       </c>
@@ -20361,7 +20361,7 @@
         <v>466381</v>
       </c>
     </row>
-    <row r="742" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="742" spans="1:5" ht="17" thickBot="1">
       <c r="A742" s="11">
         <v>45066</v>
       </c>
@@ -20379,7 +20379,7 @@
         <v>470694</v>
       </c>
     </row>
-    <row r="743" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="743" spans="1:5" ht="17" thickBot="1">
       <c r="A743" s="11">
         <v>45073</v>
       </c>
@@ -20397,7 +20397,7 @@
         <v>480998</v>
       </c>
     </row>
-    <row r="744" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="744" spans="1:5" ht="17" thickBot="1">
       <c r="A744" s="11">
         <v>45080</v>
       </c>
@@ -20415,7 +20415,7 @@
         <v>439601</v>
       </c>
     </row>
-    <row r="745" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="745" spans="1:5" ht="17" thickBot="1">
       <c r="A745" s="11">
         <v>45087</v>
       </c>
@@ -20433,7 +20433,7 @@
         <v>471141</v>
       </c>
     </row>
-    <row r="746" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="746" spans="1:5" ht="17" thickBot="1">
       <c r="A746" s="11">
         <v>45094</v>
       </c>
@@ -20451,7 +20451,7 @@
         <v>477126</v>
       </c>
     </row>
-    <row r="747" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="747" spans="1:5" ht="17" thickBot="1">
       <c r="A747" s="11">
         <v>45101</v>
       </c>
@@ -20469,7 +20469,7 @@
         <v>469453</v>
       </c>
     </row>
-    <row r="748" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="748" spans="1:5" ht="17" thickBot="1">
       <c r="A748" s="11">
         <v>45108</v>
       </c>
@@ -20487,7 +20487,7 @@
         <v>474443</v>
       </c>
     </row>
-    <row r="749" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="749" spans="1:5" ht="17" thickBot="1">
       <c r="A749" s="11">
         <v>45115</v>
       </c>
@@ -20505,7 +20505,7 @@
         <v>407843</v>
       </c>
     </row>
-    <row r="750" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="750" spans="1:5" ht="17" thickBot="1">
       <c r="A750" s="11">
         <v>45122</v>
       </c>
@@ -20523,7 +20523,7 @@
         <v>478153</v>
       </c>
     </row>
-    <row r="751" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="751" spans="1:5" ht="17" thickBot="1">
       <c r="A751" s="13">
         <v>45129</v>
       </c>
@@ -20541,7 +20541,7 @@
         <v>473736</v>
       </c>
     </row>
-    <row r="752" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="752" spans="1:5" ht="17" thickBot="1">
       <c r="A752" s="11">
         <v>45136</v>
       </c>
@@ -20559,7 +20559,7 @@
         <v>483481</v>
       </c>
     </row>
-    <row r="753" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="753" spans="1:5" ht="17" thickBot="1">
       <c r="A753" s="11">
         <v>45143</v>
       </c>
@@ -20577,7 +20577,7 @@
         <v>471938</v>
       </c>
     </row>
-    <row r="754" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="754" spans="1:5" ht="17" thickBot="1">
       <c r="A754" s="11">
         <v>45150</v>
       </c>
@@ -20595,7 +20595,7 @@
         <v>472498</v>
       </c>
     </row>
-    <row r="755" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="755" spans="1:5" ht="17" thickBot="1">
       <c r="A755" s="11">
         <v>45157</v>
       </c>
@@ -20613,7 +20613,7 @@
         <v>478853</v>
       </c>
     </row>
-    <row r="756" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="756" spans="1:5" ht="17" thickBot="1">
       <c r="A756" s="11">
         <v>45164</v>
       </c>
@@ -20631,7 +20631,7 @@
         <v>472525</v>
       </c>
     </row>
-    <row r="757" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="757" spans="1:5" ht="17" thickBot="1">
       <c r="A757" s="11">
         <v>45171</v>
       </c>
@@ -20649,7 +20649,7 @@
         <v>476851</v>
       </c>
     </row>
-    <row r="758" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="758" spans="1:5" ht="17" thickBot="1">
       <c r="A758" s="11">
         <v>45178</v>
       </c>
@@ -20667,7 +20667,7 @@
         <v>447345</v>
       </c>
     </row>
-    <row r="759" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="759" spans="1:5" ht="17" thickBot="1">
       <c r="A759" s="11">
         <v>45185</v>
       </c>
@@ -20685,7 +20685,7 @@
         <v>489790</v>
       </c>
     </row>
-    <row r="760" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="760" spans="1:5" ht="17" thickBot="1">
       <c r="A760" s="11">
         <v>45192</v>
       </c>
@@ -20703,7 +20703,7 @@
         <v>493323</v>
       </c>
     </row>
-    <row r="761" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="761" spans="1:5" ht="17" thickBot="1">
       <c r="A761" s="11">
         <v>45199</v>
       </c>
@@ -20721,7 +20721,7 @@
         <v>500154</v>
       </c>
     </row>
-    <row r="762" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="762" spans="1:5" ht="17" thickBot="1">
       <c r="A762" s="11">
         <v>45206</v>
       </c>
@@ -20739,7 +20739,7 @@
         <v>499217</v>
       </c>
     </row>
-    <row r="763" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="763" spans="1:5" ht="17" thickBot="1">
       <c r="A763" s="11">
         <v>45213</v>
       </c>
@@ -20757,7 +20757,7 @@
         <v>492781</v>
       </c>
     </row>
-    <row r="764" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="764" spans="1:5" ht="17" thickBot="1">
       <c r="A764" s="11">
         <v>45220</v>
       </c>
@@ -20775,7 +20775,7 @@
         <v>505985</v>
       </c>
     </row>
-    <row r="765" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="765" spans="1:5" ht="17" thickBot="1">
       <c r="A765" s="11">
         <v>45227</v>
       </c>
@@ -20793,7 +20793,7 @@
         <v>499389</v>
       </c>
     </row>
-    <row r="766" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="766" spans="1:5" ht="17" thickBot="1">
       <c r="A766" s="11">
         <v>45234</v>
       </c>
@@ -20811,7 +20811,7 @@
         <v>484757</v>
       </c>
     </row>
-    <row r="767" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="767" spans="1:5" ht="17" thickBot="1">
       <c r="A767" s="11">
         <v>45241</v>
       </c>
@@ -20829,7 +20829,7 @@
         <v>497348</v>
       </c>
     </row>
-    <row r="768" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="768" spans="1:5" ht="17" thickBot="1">
       <c r="A768" s="11">
         <v>45248</v>
       </c>
@@ -20847,7 +20847,7 @@
         <v>501416</v>
       </c>
     </row>
-    <row r="769" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="769" spans="1:5" ht="17" thickBot="1">
       <c r="A769" s="11">
         <v>45255</v>
       </c>
@@ -20865,7 +20865,7 @@
         <v>415332</v>
       </c>
     </row>
-    <row r="770" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="770" spans="1:5" ht="17" thickBot="1">
       <c r="A770" s="11">
         <v>45262</v>
       </c>
@@ -20898,7 +20898,7 @@
         <v>509626</v>
       </c>
     </row>
-    <row r="771" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="771" spans="1:5" ht="17" thickBot="1">
       <c r="A771" s="11">
         <v>45269</v>
       </c>
@@ -20916,7 +20916,7 @@
         <v>499094</v>
       </c>
     </row>
-    <row r="772" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="772" spans="1:5" ht="17" thickBot="1">
       <c r="A772" s="11">
         <v>45276</v>
       </c>
@@ -20934,7 +20934,7 @@
         <v>502583</v>
       </c>
     </row>
-    <row r="773" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="773" spans="1:5" ht="17" thickBot="1">
       <c r="A773" s="11">
         <v>45283</v>
       </c>
@@ -20952,7 +20952,7 @@
         <v>486787</v>
       </c>
     </row>
-    <row r="774" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="774" spans="1:5" ht="17" thickBot="1">
       <c r="A774" s="11">
         <v>45297</v>
       </c>
@@ -20970,7 +20970,7 @@
         <v>417257</v>
       </c>
     </row>
-    <row r="775" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="775" spans="1:5" ht="17" thickBot="1">
       <c r="A775" s="11">
         <v>45304</v>
       </c>
@@ -20988,7 +20988,7 @@
         <v>457453</v>
       </c>
     </row>
-    <row r="776" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="776" spans="1:5" ht="17" thickBot="1">
       <c r="A776" s="15">
         <v>45311</v>
       </c>
@@ -21006,7 +21006,7 @@
         <v>397553</v>
       </c>
     </row>
-    <row r="777" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="777" spans="1:5" ht="17" thickBot="1">
       <c r="A777" s="17">
         <v>45318</v>
       </c>
@@ -21024,7 +21024,7 @@
         <v>467222</v>
       </c>
     </row>
-    <row r="778" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="778" spans="1:5" ht="17" thickBot="1">
       <c r="A778" s="17">
         <v>45325</v>
       </c>
@@ -21042,7 +21042,7 @@
         <v>491697</v>
       </c>
     </row>
-    <row r="779" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="779" spans="1:5" ht="17" thickBot="1">
       <c r="A779" s="17">
         <v>45332</v>
       </c>
@@ -21060,7 +21060,7 @@
         <v>484840</v>
       </c>
     </row>
-    <row r="780" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="780" spans="1:5" ht="17" thickBot="1">
       <c r="A780" s="17">
         <v>45339</v>
       </c>
@@ -21078,7 +21078,7 @@
         <v>474226</v>
       </c>
     </row>
-    <row r="781" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="781" spans="1:5" ht="17" thickBot="1">
       <c r="A781" s="17">
         <v>45346</v>
       </c>
@@ -21096,7 +21096,7 @@
         <v>483656</v>
       </c>
     </row>
-    <row r="782" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="782" spans="1:5" ht="17" thickBot="1">
       <c r="A782" s="17">
         <v>45353</v>
       </c>
@@ -21114,7 +21114,7 @@
         <v>483138</v>
       </c>
     </row>
-    <row r="783" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="783" spans="1:5" ht="17" thickBot="1">
       <c r="A783" s="17">
         <v>45360</v>
       </c>
@@ -21132,7 +21132,7 @@
         <v>472662</v>
       </c>
     </row>
-    <row r="784" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="784" spans="1:5" ht="17" thickBot="1">
       <c r="A784" s="17">
         <v>45367</v>
       </c>
@@ -21150,7 +21150,7 @@
         <v>474596</v>
       </c>
     </row>
-    <row r="785" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="785" spans="1:5" ht="17" thickBot="1">
       <c r="A785" s="17">
         <v>45374</v>
       </c>
@@ -21168,7 +21168,7 @@
         <v>470593</v>
       </c>
     </row>
-    <row r="786" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="786" spans="1:5" ht="17" thickBot="1">
       <c r="A786" s="17">
         <v>45381</v>
       </c>
@@ -21186,7 +21186,7 @@
         <v>472651</v>
       </c>
     </row>
-    <row r="787" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="787" spans="1:5" ht="17" thickBot="1">
       <c r="A787" s="17">
         <v>45388</v>
       </c>
@@ -21204,7 +21204,7 @@
         <v>450142</v>
       </c>
     </row>
-    <row r="788" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="788" spans="1:5" ht="17" thickBot="1">
       <c r="A788" s="17">
         <v>45395</v>
       </c>
@@ -21222,7 +21222,7 @@
         <v>466463</v>
       </c>
     </row>
-    <row r="789" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="789" spans="1:5" ht="17" thickBot="1">
       <c r="A789" s="17">
         <v>45402</v>
       </c>
@@ -21240,7 +21240,7 @@
         <v>474544</v>
       </c>
     </row>
-    <row r="790" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="790" spans="1:5" ht="17" thickBot="1">
       <c r="A790" s="17">
         <v>45409</v>
       </c>
@@ -21258,7 +21258,7 @@
         <v>476302</v>
       </c>
     </row>
-    <row r="791" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="791" spans="1:5" ht="17" thickBot="1">
       <c r="A791" s="17">
         <v>45416</v>
       </c>
@@ -21276,7 +21276,7 @@
         <v>463106</v>
       </c>
     </row>
-    <row r="792" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="792" spans="1:5" ht="17" thickBot="1">
       <c r="A792" s="17">
         <v>45423</v>
       </c>
@@ -21294,7 +21294,7 @@
         <v>468748</v>
       </c>
     </row>
-    <row r="793" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="793" spans="1:5" ht="17" thickBot="1">
       <c r="A793" s="17">
         <v>45430</v>
       </c>
@@ -21312,7 +21312,7 @@
         <v>474886</v>
       </c>
     </row>
-    <row r="794" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="794" spans="1:5" ht="17" thickBot="1">
       <c r="A794" s="17">
         <v>45437</v>
       </c>
@@ -21330,7 +21330,7 @@
         <v>485232</v>
       </c>
     </row>
-    <row r="795" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="795" spans="1:5" ht="17" thickBot="1">
       <c r="A795" s="17">
         <v>45444</v>
       </c>
@@ -21348,7 +21348,7 @@
         <v>450077</v>
       </c>
     </row>
-    <row r="796" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="796" spans="1:5" ht="17" thickBot="1">
       <c r="A796" s="17">
         <v>45451</v>
       </c>
@@ -21366,7 +21366,7 @@
         <v>489916</v>
       </c>
     </row>
-    <row r="797" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="797" spans="1:5" ht="17" thickBot="1">
       <c r="A797" s="17">
         <v>45458</v>
       </c>
@@ -21384,7 +21384,7 @@
         <v>493138</v>
       </c>
     </row>
-    <row r="798" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="798" spans="1:5" ht="17" thickBot="1">
       <c r="A798" s="17">
         <v>45465</v>
       </c>
@@ -21402,7 +21402,7 @@
         <v>485557</v>
       </c>
     </row>
-    <row r="799" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="799" spans="1:5" ht="17" thickBot="1">
       <c r="A799" s="17">
         <v>45472</v>
       </c>
@@ -21420,7 +21420,7 @@
         <v>491899</v>
       </c>
     </row>
-    <row r="800" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="800" spans="1:5" ht="17" thickBot="1">
       <c r="A800" s="17">
         <v>45479</v>
       </c>
@@ -21438,7 +21438,7 @@
         <v>421817</v>
       </c>
     </row>
-    <row r="801" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="801" spans="1:5" ht="17" thickBot="1">
       <c r="A801" s="15">
         <v>45486</v>
       </c>
@@ -21456,7 +21456,7 @@
         <v>483806</v>
       </c>
     </row>
-    <row r="802" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="802" spans="1:5" ht="17" thickBot="1">
       <c r="A802" s="17">
         <v>45493</v>
       </c>
@@ -21474,7 +21474,7 @@
         <v>480083</v>
       </c>
     </row>
-    <row r="803" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="803" spans="1:5" ht="17" thickBot="1">
       <c r="A803" s="17">
         <v>45500</v>
       </c>
@@ -21492,7 +21492,7 @@
         <v>508496</v>
       </c>
     </row>
-    <row r="804" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="804" spans="1:5" ht="17" thickBot="1">
       <c r="A804" s="17">
         <v>45507</v>
       </c>
@@ -21510,7 +21510,7 @@
         <v>498807</v>
       </c>
     </row>
-    <row r="805" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="805" spans="1:5" ht="17" thickBot="1">
       <c r="A805" s="17">
         <v>45514</v>
       </c>
@@ -21528,7 +21528,7 @@
         <v>496509</v>
       </c>
     </row>
-    <row r="806" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="806" spans="1:5" ht="17" thickBot="1">
       <c r="A806" s="17">
         <v>45521</v>
       </c>
@@ -21546,7 +21546,7 @@
         <v>516819</v>
       </c>
     </row>
-    <row r="807" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="807" spans="1:5" ht="17" thickBot="1">
       <c r="A807" s="17">
         <v>45528</v>
       </c>
@@ -21564,7 +21564,7 @@
         <v>516807</v>
       </c>
     </row>
-    <row r="808" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="808" spans="1:5" ht="17" thickBot="1">
       <c r="A808" s="17">
         <v>45535</v>
       </c>
@@ -21582,7 +21582,7 @@
         <v>516632</v>
       </c>
     </row>
-    <row r="809" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="809" spans="1:5" ht="17" thickBot="1">
       <c r="A809" s="17">
         <v>45542</v>
       </c>
@@ -21600,7 +21600,7 @@
         <v>479179</v>
       </c>
     </row>
-    <row r="810" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="810" spans="1:5" ht="17" thickBot="1">
       <c r="A810" s="17">
         <v>45549</v>
       </c>
@@ -21618,7 +21618,7 @@
         <v>522557</v>
       </c>
     </row>
-    <row r="811" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="811" spans="1:5" ht="17" thickBot="1">
       <c r="A811" s="17">
         <v>45556</v>
       </c>
@@ -21636,7 +21636,7 @@
         <v>522112</v>
       </c>
     </row>
-    <row r="812" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="812" spans="1:5" ht="17" thickBot="1">
       <c r="A812" s="17">
         <v>45563</v>
       </c>
@@ -21654,7 +21654,7 @@
         <v>507537</v>
       </c>
     </row>
-    <row r="813" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="813" spans="1:5" ht="17" thickBot="1">
       <c r="A813" s="17">
         <v>45570</v>
       </c>
@@ -21672,7 +21672,7 @@
         <v>486187</v>
       </c>
     </row>
-    <row r="814" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="814" spans="1:5" ht="17" thickBot="1">
       <c r="A814" s="17">
         <v>45577</v>
       </c>
@@ -21690,7 +21690,7 @@
         <v>505033</v>
       </c>
     </row>
-    <row r="815" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="815" spans="1:5" ht="17" thickBot="1">
       <c r="A815" s="17">
         <v>45584</v>
       </c>
@@ -21708,7 +21708,7 @@
         <v>510730</v>
       </c>
     </row>
-    <row r="816" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="816" spans="1:5" ht="17" thickBot="1">
       <c r="A816" s="17">
         <v>45591</v>
       </c>
@@ -21726,7 +21726,7 @@
         <v>519415</v>
       </c>
     </row>
-    <row r="817" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="817" spans="1:5" ht="17" thickBot="1">
       <c r="A817" s="17">
         <v>45598</v>
       </c>
@@ -21744,7 +21744,7 @@
         <v>516743</v>
       </c>
     </row>
-    <row r="818" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="818" spans="1:5" ht="17" thickBot="1">
       <c r="A818" s="17">
         <v>45612</v>
       </c>
@@ -21762,7 +21762,7 @@
         <v>516886</v>
       </c>
     </row>
-    <row r="819" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="819" spans="1:5" ht="17" thickBot="1">
       <c r="A819" s="17">
         <v>45619</v>
       </c>
@@ -21780,7 +21780,7 @@
         <v>520798</v>
       </c>
     </row>
-    <row r="820" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="820" spans="1:5" ht="17" thickBot="1">
       <c r="A820" s="17">
         <v>45626</v>
       </c>
@@ -21798,7 +21798,7 @@
         <v>439362</v>
       </c>
     </row>
-    <row r="821" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="821" spans="1:5" ht="17" thickBot="1">
       <c r="A821" s="17">
         <v>45633</v>
       </c>
@@ -21816,7 +21816,7 @@
         <v>520894</v>
       </c>
     </row>
-    <row r="822" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="822" spans="1:5" ht="17" thickBot="1">
       <c r="A822" s="17">
         <v>45640</v>
       </c>
@@ -21834,7 +21834,7 @@
         <v>526166</v>
       </c>
     </row>
-    <row r="823" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="823" spans="1:5" ht="17" thickBot="1">
       <c r="A823" s="17">
         <v>45647</v>
       </c>
@@ -21852,7 +21852,7 @@
         <v>523912</v>
       </c>
     </row>
-    <row r="824" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="824" spans="1:5" ht="17" thickBot="1">
       <c r="A824" s="17">
         <v>45654</v>
       </c>
@@ -21870,7 +21870,7 @@
         <v>389700</v>
       </c>
     </row>
-    <row r="825" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="825" spans="1:5" ht="17" thickBot="1">
       <c r="A825" s="17">
         <v>45661</v>
       </c>
@@ -21888,7 +21888,7 @@
         <v>421410</v>
       </c>
     </row>
-    <row r="826" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="826" spans="1:5" ht="17" thickBot="1">
       <c r="A826" s="15">
         <v>45668</v>
       </c>
@@ -21906,7 +21906,7 @@
         <v>465390</v>
       </c>
     </row>
-    <row r="827" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="827" spans="1:5" ht="17" thickBot="1">
       <c r="A827" s="17">
         <v>45675</v>
       </c>
@@ -21924,7 +21924,7 @@
         <v>500160</v>
       </c>
     </row>
-    <row r="828" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="828" spans="1:5" ht="17" thickBot="1">
       <c r="A828" s="17">
         <v>45682</v>
       </c>
@@ -21942,7 +21942,7 @@
         <v>454797</v>
       </c>
     </row>
-    <row r="829" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="829" spans="1:5" ht="17" thickBot="1">
       <c r="A829" s="17">
         <v>45689</v>
       </c>
@@ -21960,7 +21960,7 @@
         <v>513622</v>
       </c>
     </row>
-    <row r="830" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="830" spans="1:5" ht="17" thickBot="1">
       <c r="A830" s="17">
         <v>45696</v>
       </c>
@@ -21978,7 +21978,7 @@
         <v>502449</v>
       </c>
     </row>
-    <row r="831" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="831" spans="1:5" ht="17" thickBot="1">
       <c r="A831" s="17">
         <v>45703</v>
       </c>
@@ -21996,7 +21996,7 @@
         <v>480740</v>
       </c>
     </row>
-    <row r="832" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="832" spans="1:5" ht="17" thickBot="1">
       <c r="A832" s="17">
         <v>45710</v>
       </c>
@@ -22014,7 +22014,7 @@
         <v>458513</v>
       </c>
     </row>
-    <row r="833" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="833" spans="1:5" ht="17" thickBot="1">
       <c r="A833" s="17">
         <v>45717</v>
       </c>
@@ -22032,7 +22032,7 @@
         <v>508531</v>
       </c>
     </row>
-    <row r="834" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="834" spans="1:5" ht="17" thickBot="1">
       <c r="A834" s="17">
         <v>45724</v>
       </c>
@@ -22065,7 +22065,7 @@
         <v>497412</v>
       </c>
     </row>
-    <row r="835" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="835" spans="1:5" ht="17" thickBot="1">
       <c r="A835" s="17">
         <v>45731</v>
       </c>
@@ -22083,7 +22083,7 @@
         <v>503473</v>
       </c>
     </row>
-    <row r="836" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="836" spans="1:5" ht="17" thickBot="1">
       <c r="A836" s="17">
         <v>45738</v>
       </c>
@@ -22101,7 +22101,7 @@
         <v>496214</v>
       </c>
     </row>
-    <row r="837" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="837" spans="1:5" ht="17" thickBot="1">
       <c r="A837" s="17">
         <v>45745</v>
       </c>
@@ -22119,7 +22119,7 @@
         <v>513553</v>
       </c>
     </row>
-    <row r="838" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="838" spans="1:5" ht="17" thickBot="1">
       <c r="A838" s="17">
         <v>45752</v>
       </c>
@@ -22137,7 +22137,7 @@
         <v>500584</v>
       </c>
     </row>
-    <row r="839" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="839" spans="1:5" ht="17" thickBot="1">
       <c r="A839" s="17">
         <v>45759</v>
       </c>
@@ -22155,7 +22155,7 @@
         <v>491908</v>
       </c>
     </row>
-    <row r="840" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="840" spans="1:5" ht="17" thickBot="1">
       <c r="A840" s="17">
         <v>45766</v>
       </c>
@@ -22173,7 +22173,7 @@
         <v>496053</v>
       </c>
     </row>
-    <row r="841" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="841" spans="1:5" ht="17" thickBot="1">
       <c r="A841" s="17">
         <v>45773</v>
       </c>
@@ -22191,7 +22191,7 @@
         <v>502105</v>
       </c>
     </row>
-    <row r="842" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="842" spans="1:5" ht="17" thickBot="1">
       <c r="A842" s="17">
         <v>45780</v>
       </c>
@@ -22209,7 +22209,7 @@
         <v>498693</v>
       </c>
     </row>
-    <row r="843" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="843" spans="1:5" ht="17" thickBot="1">
       <c r="A843" s="17">
         <v>45787</v>
       </c>
@@ -22227,7 +22227,7 @@
         <v>495552</v>
       </c>
     </row>
-    <row r="844" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="844" spans="1:5" ht="17" thickBot="1">
       <c r="A844" s="17">
         <v>45794</v>
       </c>
@@ -22245,7 +22245,7 @@
         <v>490775</v>
       </c>
     </row>
-    <row r="845" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="845" spans="1:5" ht="17" thickBot="1">
       <c r="A845" s="17">
         <v>45801</v>
       </c>
@@ -22263,7 +22263,7 @@
         <v>488709</v>
       </c>
     </row>
-    <row r="846" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="846" spans="1:5" ht="17" thickBot="1">
       <c r="A846" s="17">
         <v>45808</v>
       </c>
@@ -22281,7 +22281,7 @@
         <v>459884</v>
       </c>
     </row>
-    <row r="847" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="847" spans="1:5" ht="17" thickBot="1">
       <c r="A847" s="17">
         <v>45815</v>
       </c>
@@ -22299,7 +22299,7 @@
         <v>483807</v>
       </c>
     </row>
-    <row r="848" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="848" spans="1:5" ht="17" thickBot="1">
       <c r="A848" s="17">
         <v>45822</v>
       </c>
@@ -22317,7 +22317,7 @@
         <v>485810</v>
       </c>
     </row>
-    <row r="849" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="849" spans="1:5" ht="17" thickBot="1">
       <c r="A849" s="17">
         <v>45829</v>
       </c>
@@ -22335,7 +22335,7 @@
         <v>487328</v>
       </c>
     </row>
-    <row r="850" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="850" spans="1:5" ht="17" thickBot="1">
       <c r="A850" s="17">
         <v>45836</v>
       </c>
@@ -22353,7 +22353,7 @@
         <v>491424</v>
       </c>
     </row>
-    <row r="851" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="851" spans="1:5" ht="17" thickBot="1">
       <c r="A851" s="15">
         <v>45843</v>
       </c>
@@ -22371,7 +22371,7 @@
         <v>443049</v>
       </c>
     </row>
-    <row r="852" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="852" spans="1:5" ht="17" thickBot="1">
       <c r="A852" s="17">
         <v>45850</v>
       </c>
@@ -22389,7 +22389,7 @@
         <v>496188</v>
       </c>
     </row>
-    <row r="853" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="853" spans="1:5" ht="17" thickBot="1">
       <c r="A853" s="17">
         <v>45857</v>
       </c>
@@ -22407,7 +22407,7 @@
         <v>506882</v>
       </c>
     </row>
-    <row r="854" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="854" spans="1:5" ht="17" thickBot="1">
       <c r="A854" s="17">
         <v>45864</v>
       </c>
@@ -22425,7 +22425,7 @@
         <v>514279</v>
       </c>
     </row>
-    <row r="855" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="855" spans="1:5" ht="17" thickBot="1">
       <c r="A855" s="17">
         <v>45871</v>
       </c>
@@ -22443,7 +22443,7 @@
         <v>513529</v>
       </c>
     </row>
-    <row r="856" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="856" spans="1:5" ht="17" thickBot="1">
       <c r="A856" s="17">
         <v>45878</v>
       </c>
@@ -22461,7 +22461,7 @@
         <v>511194</v>
       </c>
     </row>
-    <row r="857" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="857" spans="1:5" ht="17" thickBot="1">
       <c r="A857" s="17">
         <v>45885</v>
       </c>
@@ -22479,7 +22479,7 @@
         <v>512970</v>
       </c>
     </row>
-    <row r="858" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="858" spans="1:5" ht="17" thickBot="1">
       <c r="A858" s="17">
         <v>45892</v>
       </c>
@@ -22497,7 +22497,7 @@
         <v>512333</v>
       </c>
     </row>
-    <row r="859" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="859" spans="1:5" ht="17" thickBot="1">
       <c r="A859" s="17">
         <v>45899</v>
       </c>
@@ -22515,7 +22515,7 @@
         <v>521502</v>
       </c>
     </row>
-    <row r="860" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="860" spans="1:5" ht="17" thickBot="1">
       <c r="A860" s="17">
         <v>45906</v>
       </c>
@@ -22533,7 +22533,7 @@
         <v>467880</v>
       </c>
     </row>
-    <row r="861" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="861" spans="1:5" ht="17" thickBot="1">
       <c r="A861" s="17">
         <v>45913</v>
       </c>
@@ -22551,7 +22551,7 @@
         <v>514167</v>
       </c>
     </row>
-    <row r="862" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="862" spans="1:5" ht="17" thickBot="1">
       <c r="A862" s="17">
         <v>45920</v>
       </c>
@@ -22569,7 +22569,7 @@
         <v>510677</v>
       </c>
     </row>
-    <row r="863" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="863" spans="1:5" ht="17" thickBot="1">
       <c r="A863" s="15">
         <v>45927</v>
       </c>
@@ -22587,7 +22587,7 @@
         <v>512642</v>
       </c>
     </row>
-    <row r="864" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="864" spans="1:5" ht="17" thickBot="1">
       <c r="A864" s="17">
         <v>45934</v>
       </c>
@@ -22605,7 +22605,7 @@
         <v>503538</v>
       </c>
     </row>
-    <row r="865" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="865" spans="1:5" ht="17" thickBot="1">
       <c r="A865" s="17">
         <v>45941</v>
       </c>
@@ -22623,7 +22623,7 @@
         <v>498462</v>
       </c>
     </row>
-    <row r="866" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="866" spans="1:5" ht="17" thickBot="1">
       <c r="A866" s="17">
         <v>45948</v>
       </c>
@@ -22641,7 +22641,7 @@
         <v>497854</v>
       </c>
     </row>
-    <row r="867" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="867" spans="1:5" ht="17" thickBot="1">
       <c r="A867" s="17">
         <v>45955</v>
       </c>
@@ -22659,7 +22659,7 @@
         <v>499688</v>
       </c>
     </row>
-    <row r="868" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="868" spans="1:5" ht="17" thickBot="1">
       <c r="A868" s="17">
         <v>45962</v>
       </c>
@@ -22677,7 +22677,7 @@
         <v>496928</v>
       </c>
     </row>
-    <row r="869" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="869" spans="1:5" ht="17" thickBot="1">
       <c r="A869" s="17">
         <v>45969</v>
       </c>
@@ -22695,7 +22695,7 @@
         <v>493493</v>
       </c>
     </row>
-    <row r="870" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="870" spans="1:5" ht="17" thickBot="1">
       <c r="A870" s="17">
         <v>45976</v>
       </c>
@@ -22713,7 +22713,7 @@
         <v>493880</v>
       </c>
     </row>
-    <row r="871" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="871" spans="1:5" ht="17" thickBot="1">
       <c r="A871" s="17">
         <v>45983</v>
       </c>
@@ -22731,7 +22731,7 @@
         <v>516110</v>
       </c>
     </row>
-    <row r="872" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="872" spans="1:5" ht="17" thickBot="1">
       <c r="A872" s="17">
         <v>45990</v>
       </c>
@@ -22749,7 +22749,7 @@
         <v>431435</v>
       </c>
     </row>
-    <row r="873" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="873" spans="1:5" ht="17" thickBot="1">
       <c r="A873" s="17">
         <v>45997</v>
       </c>
@@ -22767,7 +22767,7 @@
         <v>508999</v>
       </c>
     </row>
-    <row r="874" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="874" spans="1:5" ht="17" thickBot="1">
       <c r="A874" s="17">
         <v>46004</v>
       </c>
@@ -22785,7 +22785,7 @@
         <v>518904</v>
       </c>
     </row>
-    <row r="875" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="875" spans="1:5" ht="17" thickBot="1">
       <c r="A875" s="15">
         <v>46018</v>
       </c>
@@ -22803,7 +22803,7 @@
         <v>392295</v>
       </c>
     </row>
-    <row r="876" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="876" spans="1:5" ht="17" thickBot="1">
       <c r="A876" s="8">
         <v>46025</v>
       </c>
@@ -22821,7 +22821,7 @@
         <v>404293</v>
       </c>
     </row>
-    <row r="877" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="877" spans="1:5" ht="17" thickBot="1">
       <c r="A877" s="15">
         <v>46032</v>
       </c>
@@ -22839,7 +22839,7 @@
         <v>510457</v>
       </c>
     </row>
-    <row r="878" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="878" spans="1:5" ht="17" thickBot="1">
       <c r="A878" s="8">
         <v>46039</v>
       </c>
@@ -22872,7 +22872,7 @@
         <v>505385</v>
       </c>
     </row>
-    <row r="879" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="879" spans="1:5" ht="17" thickBot="1">
       <c r="A879" s="15">
         <v>46046</v>
       </c>
@@ -22905,7 +22905,7 @@
         <v>481708</v>
       </c>
     </row>
-    <row r="880" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="880" spans="1:5" ht="17" thickBot="1">
       <c r="A880" s="15">
         <v>46053</v>
       </c>
@@ -22938,7 +22938,7 @@
         <v>434361</v>
       </c>
     </row>
-    <row r="881" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="881" spans="1:5" ht="17" thickBot="1">
       <c r="A881" s="15">
         <v>46060</v>
       </c>
@@ -22956,7 +22956,7 @@
         <v>486854</v>
       </c>
     </row>
-    <row r="882" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="882" spans="1:5" ht="17" thickBot="1">
       <c r="A882" s="8">
         <v>46067</v>
       </c>
@@ -22989,7 +22989,7 @@
         <v>510399</v>
       </c>
     </row>
-    <row r="883" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="883" spans="1:5" ht="17" thickBot="1">
       <c r="A883" s="15">
         <v>46074</v>
       </c>
@@ -23022,7 +23022,7 @@
         <v>507712</v>
       </c>
     </row>
-    <row r="884" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="884" spans="1:5" ht="17" thickBot="1">
       <c r="A884" s="8">
         <v>46081</v>
       </c>
@@ -23040,7 +23040,7 @@
         <v>516729</v>
       </c>
     </row>
-    <row r="885" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="885" spans="1:5" ht="17" thickBot="1">
       <c r="A885" s="15">
         <v>46088</v>
       </c>
@@ -23058,7 +23058,7 @@
         <v>514996</v>
       </c>
     </row>
-    <row r="886" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="886" spans="1:5" ht="16">
       <c r="A886" s="8">
         <v>46102</v>
       </c>
@@ -23076,7 +23076,7 @@
         <v>502252</v>
       </c>
     </row>
-    <row r="887" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="887" spans="1:5" ht="16">
       <c r="A887" s="8">
         <v>46109</v>
       </c>
@@ -23094,7 +23094,7 @@
         <v>515921</v>
       </c>
     </row>
-    <row r="888" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="888" spans="1:5" ht="16">
       <c r="A888" s="8">
         <v>46116</v>
       </c>
@@ -23112,7 +23112,7 @@
         <v>501328</v>
       </c>
     </row>
-    <row r="889" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="889" spans="1:5" ht="16">
       <c r="A889" s="8">
         <v>46123</v>
       </c>
@@ -23130,7 +23130,7 @@
         <v>500040</v>
       </c>
     </row>
-    <row r="890" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="890" spans="1:5" ht="16">
       <c r="A890" s="8">
         <v>46130</v>
       </c>
@@ -23148,7 +23148,7 @@
         <v>508303</v>
       </c>
     </row>
-    <row r="891" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="891" spans="1:5" ht="16">
       <c r="A891" s="8">
         <v>46137</v>
       </c>
@@ -23166,7 +23166,7 @@
         <v>511616</v>
       </c>
     </row>
-    <row r="892" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="892" spans="1:5" ht="16">
       <c r="A892" s="8">
         <v>46144</v>
       </c>
@@ -23184,7 +23184,7 @@
         <v>518773</v>
       </c>
     </row>
-    <row r="893" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="893" spans="1:5" ht="16">
       <c r="A893" s="8">
         <v>46151</v>
       </c>
@@ -23217,7 +23217,7 @@
         <v>513755</v>
       </c>
     </row>
-    <row r="894" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="894" spans="1:5" ht="16">
       <c r="A894" s="8">
         <v>46158</v>
       </c>
@@ -23235,7 +23235,7 @@
         <v>511216</v>
       </c>
     </row>
-    <row r="895" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="895" spans="1:5" ht="16">
       <c r="A895" s="8">
         <v>46165</v>
       </c>
@@ -23253,7 +23253,7 @@
         <v>523574</v>
       </c>
     </row>
-    <row r="896" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="896" spans="1:5" ht="16">
       <c r="A896" s="8">
         <v>46172</v>
       </c>
@@ -23286,7 +23286,7 @@
         <v>492795</v>
       </c>
     </row>
-    <row r="897" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="897" spans="1:5" ht="16">
       <c r="A897" s="8">
         <v>46179</v>
       </c>
@@ -23304,7 +23304,7 @@
         <v>521804</v>
       </c>
     </row>
-    <row r="898" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="898" spans="1:5" ht="16">
       <c r="A898" s="8">
         <v>46186</v>
       </c>
@@ -23312,11 +23312,14 @@
         <v>46190</v>
       </c>
       <c r="C898" s="21">
-        <v>0.51388888888888884</v>
+        <v>0.68680555555555556</v>
       </c>
       <c r="D898" s="7" t="str">
         <f t="shared" si="17"/>
         <v>UTC-4</v>
+      </c>
+      <c r="E898" s="20">
+        <v>520406</v>
       </c>
     </row>
   </sheetData>
@@ -23332,7 +23335,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{300947AE-C9E8-48BA-99BA-AA00E1AFF02E}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -23343,12 +23346,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFF96248-4EFB-4252-A059-6D65AEEDC293}">
   <dimension ref="B2:C4"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15.6" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:3">
       <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
@@ -23356,7 +23359,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:3">
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
@@ -23364,7 +23367,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:3">
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>

--- a/data/freight/US Rail Traffic.xlsx
+++ b/data/freight/US Rail Traffic.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tommy/Desktop/Pycharm/FinancialData/data/freight/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7F58D89-9EED-7F4C-BBB2-83419F8101A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EA5BAF0-80D0-46E0-BC88-68E4305280C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22160" yWindow="600" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{55EF15CE-83DB-4E42-B75D-C3DAE3AA4C48}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{55EF15CE-83DB-4E42-B75D-C3DAE3AA4C48}"/>
   </bookViews>
   <sheets>
     <sheet name="USRT" sheetId="1" r:id="rId1"/>
@@ -91,7 +91,7 @@
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="166" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -268,9 +268,9 @@
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="쉼표" xfId="1" builtinId="3"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -288,7 +288,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -6537,9 +6537,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -6577,7 +6577,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -6683,7 +6683,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -6825,7 +6825,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -6833,18 +6833,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83FCC8DB-37A0-4531-B65E-34C65BAF4830}">
-  <dimension ref="A1:E898"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
+  <dimension ref="A1:E899"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.109375" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.33203125" style="21" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.83203125" style="20" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.1640625" style="6"/>
+    <col min="5" max="5" width="8.77734375" style="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -6861,7 +6861,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="16">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="7">
         <v>39823</v>
       </c>
@@ -6894,7 +6894,7 @@
         <v>474565</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="16">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="7">
         <v>39830</v>
       </c>
@@ -6912,7 +6912,7 @@
         <v>465386</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="16">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="7">
         <v>39837</v>
       </c>
@@ -6930,7 +6930,7 @@
         <v>462128</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="16">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="7">
         <v>39844</v>
       </c>
@@ -6948,7 +6948,7 @@
         <v>449966</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="16">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="7">
         <v>39851</v>
       </c>
@@ -6966,7 +6966,7 @@
         <v>455757</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="16">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="7">
         <v>39858</v>
       </c>
@@ -6984,7 +6984,7 @@
         <v>471961</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="16">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="7">
         <v>39865</v>
       </c>
@@ -7002,7 +7002,7 @@
         <v>446575</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="16">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="7">
         <v>39872</v>
       </c>
@@ -7020,7 +7020,7 @@
         <v>458242</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="16">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="7">
         <v>39879</v>
       </c>
@@ -7038,7 +7038,7 @@
         <v>455041</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="16">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="7">
         <v>39886</v>
       </c>
@@ -7056,7 +7056,7 @@
         <v>455686</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="16">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="7">
         <v>39893</v>
       </c>
@@ -7074,7 +7074,7 @@
         <v>459547</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="16">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="7">
         <v>39900</v>
       </c>
@@ -7092,7 +7092,7 @@
         <v>439844</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="16">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="7">
         <v>39907</v>
       </c>
@@ -7110,7 +7110,7 @@
         <v>447103</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="16">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" s="7">
         <v>39914</v>
       </c>
@@ -7128,7 +7128,7 @@
         <v>426107</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="16">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="7">
         <v>39921</v>
       </c>
@@ -7146,7 +7146,7 @@
         <v>438602</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="16">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" s="7">
         <v>39928</v>
       </c>
@@ -7164,7 +7164,7 @@
         <v>444794</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="16">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" s="7">
         <v>39935</v>
       </c>
@@ -7182,7 +7182,7 @@
         <v>442378</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="16">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" s="7">
         <v>39942</v>
       </c>
@@ -7200,7 +7200,7 @@
         <v>435052</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="16">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" s="7">
         <v>39949</v>
       </c>
@@ -7218,7 +7218,7 @@
         <v>438329</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="16">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" s="7">
         <v>39956</v>
       </c>
@@ -7236,7 +7236,7 @@
         <v>451355</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="16">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" s="7">
         <v>39963</v>
       </c>
@@ -7254,7 +7254,7 @@
         <v>401248</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="16">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" s="7">
         <v>39970</v>
       </c>
@@ -7272,7 +7272,7 @@
         <v>448743</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="16">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" s="7">
         <v>39977</v>
       </c>
@@ -7290,7 +7290,7 @@
         <v>451065</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="16">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" s="7">
         <v>39984</v>
       </c>
@@ -7308,7 +7308,7 @@
         <v>449103</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="16">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" s="7">
         <v>39991</v>
       </c>
@@ -7326,7 +7326,7 @@
         <v>444212</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="16">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" s="7">
         <v>39998</v>
       </c>
@@ -7344,7 +7344,7 @@
         <v>410661</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="16">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" s="7">
         <v>40005</v>
       </c>
@@ -7362,7 +7362,7 @@
         <v>439041</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="16">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" s="7">
         <v>40012</v>
       </c>
@@ -7380,7 +7380,7 @@
         <v>456926</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="16">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" s="7">
         <v>40019</v>
       </c>
@@ -7398,7 +7398,7 @@
         <v>467395</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="16">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" s="7">
         <v>40026</v>
       </c>
@@ -7416,7 +7416,7 @@
         <v>468150</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="16">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" s="7">
         <v>40033</v>
       </c>
@@ -7434,7 +7434,7 @@
         <v>469814</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="16">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" s="7">
         <v>40040</v>
       </c>
@@ -7452,7 +7452,7 @@
         <v>469727</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="16">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" s="7">
         <v>40047</v>
       </c>
@@ -7470,7 +7470,7 @@
         <v>472644</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="16">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" s="7">
         <v>40054</v>
       </c>
@@ -7488,7 +7488,7 @@
         <v>488273</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="16">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" s="7">
         <v>40061</v>
       </c>
@@ -7506,7 +7506,7 @@
         <v>486009</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="16">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" s="7">
         <v>40068</v>
       </c>
@@ -7524,7 +7524,7 @@
         <v>439238</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="16">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" s="7">
         <v>40075</v>
       </c>
@@ -7542,7 +7542,7 @@
         <v>487236</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="16">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" s="7">
         <v>40082</v>
       </c>
@@ -7560,7 +7560,7 @@
         <v>477434</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="16">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" s="7">
         <v>40089</v>
       </c>
@@ -7578,7 +7578,7 @@
         <v>484157</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="16">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" s="7">
         <v>40096</v>
       </c>
@@ -7596,7 +7596,7 @@
         <v>481944</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="16">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" s="7">
         <v>40103</v>
       </c>
@@ -7614,7 +7614,7 @@
         <v>481827</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="16">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" s="7">
         <v>40110</v>
       </c>
@@ -7632,7 +7632,7 @@
         <v>483850</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="16">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" s="7">
         <v>40117</v>
       </c>
@@ -7650,7 +7650,7 @@
         <v>479450</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="16">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" s="7">
         <v>40124</v>
       </c>
@@ -7668,7 +7668,7 @@
         <v>481493</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="16">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" s="7">
         <v>40131</v>
       </c>
@@ -7686,7 +7686,7 @@
         <v>489073</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="16">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" s="7">
         <v>40138</v>
       </c>
@@ -7704,7 +7704,7 @@
         <v>500284</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="16">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" s="7">
         <v>40145</v>
       </c>
@@ -7722,7 +7722,7 @@
         <v>412036</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="16">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" s="7">
         <v>40152</v>
       </c>
@@ -7740,7 +7740,7 @@
         <v>491440</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="16">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" s="7">
         <v>40159</v>
       </c>
@@ -7758,7 +7758,7 @@
         <v>464948</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="16">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" s="7">
         <v>40166</v>
       </c>
@@ -7776,7 +7776,7 @@
         <v>481426</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="16">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52" s="7">
         <v>40173</v>
       </c>
@@ -7794,7 +7794,7 @@
         <v>339702</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="16">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53" s="7">
         <v>40180</v>
       </c>
@@ -7812,7 +7812,7 @@
         <v>376455</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="16">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" s="7">
         <v>40187</v>
       </c>
@@ -7830,7 +7830,7 @@
         <v>433584</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="16">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55" s="7">
         <v>40194</v>
       </c>
@@ -7848,7 +7848,7 @@
         <v>465758</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="16">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56" s="7">
         <v>40201</v>
       </c>
@@ -7866,7 +7866,7 @@
         <v>478227</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="16">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57" s="7">
         <v>40208</v>
       </c>
@@ -7884,7 +7884,7 @@
         <v>482390</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="16">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58" s="7">
         <v>40215</v>
       </c>
@@ -7902,7 +7902,7 @@
         <v>469221</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="16">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59" s="7">
         <v>40222</v>
       </c>
@@ -7920,7 +7920,7 @@
         <v>450177</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="16">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60" s="7">
         <v>40229</v>
       </c>
@@ -7938,7 +7938,7 @@
         <v>474203</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="16">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61" s="7">
         <v>40236</v>
       </c>
@@ -7956,7 +7956,7 @@
         <v>496078</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="16">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62" s="7">
         <v>40243</v>
       </c>
@@ -7974,7 +7974,7 @@
         <v>497456</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="16">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63" s="7">
         <v>40250</v>
       </c>
@@ -7992,7 +7992,7 @@
         <v>491463</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="16">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64" s="7">
         <v>40257</v>
       </c>
@@ -8010,7 +8010,7 @@
         <v>488939</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="16">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A65" s="7">
         <v>40264</v>
       </c>
@@ -8028,7 +8028,7 @@
         <v>504028</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="16">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66" s="7">
         <v>40271</v>
       </c>
@@ -8061,7 +8061,7 @@
         <v>486474</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="16">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67" s="7">
         <v>40278</v>
       </c>
@@ -8079,7 +8079,7 @@
         <v>492044</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="16">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68" s="7">
         <v>40285</v>
       </c>
@@ -8097,7 +8097,7 @@
         <v>506502</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="16">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A69" s="7">
         <v>40292</v>
       </c>
@@ -8115,7 +8115,7 @@
         <v>510565</v>
       </c>
     </row>
-    <row r="70" spans="1:5" ht="16">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A70" s="7">
         <v>40299</v>
       </c>
@@ -8133,7 +8133,7 @@
         <v>508731</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="16">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A71" s="7">
         <v>40306</v>
       </c>
@@ -8151,7 +8151,7 @@
         <v>497714</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="16">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A72" s="7">
         <v>40313</v>
       </c>
@@ -8169,7 +8169,7 @@
         <v>508469</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="16">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A73" s="7">
         <v>40320</v>
       </c>
@@ -8187,7 +8187,7 @@
         <v>503232</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="16">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74" s="7">
         <v>40327</v>
       </c>
@@ -8205,7 +8205,7 @@
         <v>511776</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="16">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75" s="7">
         <v>40334</v>
       </c>
@@ -8223,7 +8223,7 @@
         <v>462009</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="16">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A76" s="7">
         <v>40341</v>
       </c>
@@ -8241,7 +8241,7 @@
         <v>512048</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="16">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A77" s="7">
         <v>40348</v>
       </c>
@@ -8259,7 +8259,7 @@
         <v>512898</v>
       </c>
     </row>
-    <row r="78" spans="1:5" ht="16">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A78" s="7">
         <v>40355</v>
       </c>
@@ -8277,7 +8277,7 @@
         <v>511945</v>
       </c>
     </row>
-    <row r="79" spans="1:5" ht="16">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A79" s="7">
         <v>40362</v>
       </c>
@@ -8295,7 +8295,7 @@
         <v>518063</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="16">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A80" s="7">
         <v>40369</v>
       </c>
@@ -8313,7 +8313,7 @@
         <v>445917</v>
       </c>
     </row>
-    <row r="81" spans="1:5" ht="16">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A81" s="7">
         <v>40376</v>
       </c>
@@ -8331,7 +8331,7 @@
         <v>509860</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="16">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A82" s="7">
         <v>40383</v>
       </c>
@@ -8349,7 +8349,7 @@
         <v>517297</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="16">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A83" s="7">
         <v>40390</v>
       </c>
@@ -8367,7 +8367,7 @@
         <v>533187</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="16">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A84" s="7">
         <v>40397</v>
       </c>
@@ -8385,7 +8385,7 @@
         <v>515715</v>
       </c>
     </row>
-    <row r="85" spans="1:5" ht="16">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A85" s="7">
         <v>40404</v>
       </c>
@@ -8403,7 +8403,7 @@
         <v>529715</v>
       </c>
     </row>
-    <row r="86" spans="1:5" ht="16">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A86" s="7">
         <v>40411</v>
       </c>
@@ -8421,7 +8421,7 @@
         <v>533038</v>
       </c>
     </row>
-    <row r="87" spans="1:5" ht="16">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A87" s="7">
         <v>40418</v>
       </c>
@@ -8439,7 +8439,7 @@
         <v>539552</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="16">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A88" s="7">
         <v>40425</v>
       </c>
@@ -8457,7 +8457,7 @@
         <v>542006</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="16">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A89" s="7">
         <v>40432</v>
       </c>
@@ -8475,7 +8475,7 @@
         <v>484380</v>
       </c>
     </row>
-    <row r="90" spans="1:5" ht="16">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A90" s="7">
         <v>40439</v>
       </c>
@@ -8493,7 +8493,7 @@
         <v>544692</v>
       </c>
     </row>
-    <row r="91" spans="1:5" ht="16">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A91" s="7">
         <v>40446</v>
       </c>
@@ -8511,7 +8511,7 @@
         <v>542075</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="16">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A92" s="7">
         <v>40453</v>
       </c>
@@ -8529,7 +8529,7 @@
         <v>539646</v>
       </c>
     </row>
-    <row r="93" spans="1:5" ht="16">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A93" s="7">
         <v>40460</v>
       </c>
@@ -8547,7 +8547,7 @@
         <v>533301</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="16">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A94" s="7">
         <v>40467</v>
       </c>
@@ -8565,7 +8565,7 @@
         <v>540844</v>
       </c>
     </row>
-    <row r="95" spans="1:5" ht="16">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A95" s="7">
         <v>40474</v>
       </c>
@@ -8583,7 +8583,7 @@
         <v>538461</v>
       </c>
     </row>
-    <row r="96" spans="1:5" ht="16">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A96" s="7">
         <v>40481</v>
       </c>
@@ -8601,7 +8601,7 @@
         <v>525601</v>
       </c>
     </row>
-    <row r="97" spans="1:5" ht="16">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A97" s="7">
         <v>40488</v>
       </c>
@@ -8619,7 +8619,7 @@
         <v>519134</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="16">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A98" s="7">
         <v>40495</v>
       </c>
@@ -8637,7 +8637,7 @@
         <v>530157</v>
       </c>
     </row>
-    <row r="99" spans="1:5" ht="16">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A99" s="7">
         <v>40502</v>
       </c>
@@ -8655,7 +8655,7 @@
         <v>533989</v>
       </c>
     </row>
-    <row r="100" spans="1:5" ht="16">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A100" s="7">
         <v>40509</v>
       </c>
@@ -8673,7 +8673,7 @@
         <v>437911</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="17" thickBot="1">
+    <row r="101" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A101" s="7">
         <v>40516</v>
       </c>
@@ -8691,7 +8691,7 @@
         <v>539405</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="17" thickBot="1">
+    <row r="102" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A102" s="11">
         <v>40523</v>
       </c>
@@ -8709,7 +8709,7 @@
         <v>520326</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="17" thickBot="1">
+    <row r="103" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A103" s="11">
         <v>40530</v>
       </c>
@@ -8727,7 +8727,7 @@
         <v>491896</v>
       </c>
     </row>
-    <row r="104" spans="1:5" ht="17" thickBot="1">
+    <row r="104" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A104" s="11">
         <v>40537</v>
       </c>
@@ -8745,7 +8745,7 @@
         <v>433347</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="17" thickBot="1">
+    <row r="105" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A105" s="11">
         <v>40544</v>
       </c>
@@ -8763,7 +8763,7 @@
         <v>406967</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="17" thickBot="1">
+    <row r="106" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A106" s="11">
         <v>40551</v>
       </c>
@@ -8781,7 +8781,7 @@
         <v>498773</v>
       </c>
     </row>
-    <row r="107" spans="1:5" ht="17" thickBot="1">
+    <row r="107" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A107" s="11">
         <v>40558</v>
       </c>
@@ -8799,7 +8799,7 @@
         <v>496473</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="17" thickBot="1">
+    <row r="108" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A108" s="11">
         <v>40565</v>
       </c>
@@ -8817,7 +8817,7 @@
         <v>496043</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="17" thickBot="1">
+    <row r="109" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A109" s="11">
         <v>40572</v>
       </c>
@@ -8835,7 +8835,7 @@
         <v>513889</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="17" thickBot="1">
+    <row r="110" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A110" s="11">
         <v>40579</v>
       </c>
@@ -8853,7 +8853,7 @@
         <v>465931</v>
       </c>
     </row>
-    <row r="111" spans="1:5" ht="17" thickBot="1">
+    <row r="111" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A111" s="11">
         <v>40586</v>
       </c>
@@ -8871,7 +8871,7 @@
         <v>502078</v>
       </c>
     </row>
-    <row r="112" spans="1:5" ht="17" thickBot="1">
+    <row r="112" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A112" s="11">
         <v>40593</v>
       </c>
@@ -8889,7 +8889,7 @@
         <v>530973</v>
       </c>
     </row>
-    <row r="113" spans="1:5" ht="17" thickBot="1">
+    <row r="113" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A113" s="11">
         <v>40600</v>
       </c>
@@ -8907,7 +8907,7 @@
         <v>516841</v>
       </c>
     </row>
-    <row r="114" spans="1:5" ht="17" thickBot="1">
+    <row r="114" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A114" s="11">
         <v>40607</v>
       </c>
@@ -8925,7 +8925,7 @@
         <v>515296</v>
       </c>
     </row>
-    <row r="115" spans="1:5" ht="17" thickBot="1">
+    <row r="115" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A115" s="11">
         <v>40614</v>
       </c>
@@ -8943,7 +8943,7 @@
         <v>508992</v>
       </c>
     </row>
-    <row r="116" spans="1:5" ht="17" thickBot="1">
+    <row r="116" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A116" s="11">
         <v>40621</v>
       </c>
@@ -8961,7 +8961,7 @@
         <v>516560</v>
       </c>
     </row>
-    <row r="117" spans="1:5" ht="17" thickBot="1">
+    <row r="117" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A117" s="11">
         <v>40628</v>
       </c>
@@ -8979,7 +8979,7 @@
         <v>522937</v>
       </c>
     </row>
-    <row r="118" spans="1:5" ht="17" thickBot="1">
+    <row r="118" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A118" s="11">
         <v>40635</v>
       </c>
@@ -8997,7 +8997,7 @@
         <v>540213</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="17" thickBot="1">
+    <row r="119" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A119" s="11">
         <v>40642</v>
       </c>
@@ -9015,7 +9015,7 @@
         <v>522511</v>
       </c>
     </row>
-    <row r="120" spans="1:5" ht="17" thickBot="1">
+    <row r="120" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A120" s="11">
         <v>40649</v>
       </c>
@@ -9033,7 +9033,7 @@
         <v>525886</v>
       </c>
     </row>
-    <row r="121" spans="1:5" ht="17" thickBot="1">
+    <row r="121" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A121" s="11">
         <v>40656</v>
       </c>
@@ -9051,7 +9051,7 @@
         <v>518374</v>
       </c>
     </row>
-    <row r="122" spans="1:5" ht="17" thickBot="1">
+    <row r="122" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A122" s="11">
         <v>40663</v>
       </c>
@@ -9069,7 +9069,7 @@
         <v>525024</v>
       </c>
     </row>
-    <row r="123" spans="1:5" ht="17" thickBot="1">
+    <row r="123" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A123" s="11">
         <v>40670</v>
       </c>
@@ -9087,7 +9087,7 @@
         <v>514038</v>
       </c>
     </row>
-    <row r="124" spans="1:5" ht="17" thickBot="1">
+    <row r="124" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A124" s="11">
         <v>40677</v>
       </c>
@@ -9105,7 +9105,7 @@
         <v>526146</v>
       </c>
     </row>
-    <row r="125" spans="1:5" ht="17" thickBot="1">
+    <row r="125" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A125" s="11">
         <v>40684</v>
       </c>
@@ -9123,7 +9123,7 @@
         <v>529383</v>
       </c>
     </row>
-    <row r="126" spans="1:5" ht="17" thickBot="1">
+    <row r="126" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A126" s="13">
         <v>40691</v>
       </c>
@@ -9141,7 +9141,7 @@
         <v>522717</v>
       </c>
     </row>
-    <row r="127" spans="1:5" ht="17" thickBot="1">
+    <row r="127" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A127" s="11">
         <v>40698</v>
       </c>
@@ -9159,7 +9159,7 @@
         <v>479149</v>
       </c>
     </row>
-    <row r="128" spans="1:5" ht="17" thickBot="1">
+    <row r="128" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A128" s="11">
         <v>40705</v>
       </c>
@@ -9177,7 +9177,7 @@
         <v>527603</v>
       </c>
     </row>
-    <row r="129" spans="1:5" ht="17" thickBot="1">
+    <row r="129" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A129" s="11">
         <v>40712</v>
       </c>
@@ -9195,7 +9195,7 @@
         <v>531992</v>
       </c>
     </row>
-    <row r="130" spans="1:5" ht="17" thickBot="1">
+    <row r="130" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A130" s="11">
         <v>40719</v>
       </c>
@@ -9228,7 +9228,7 @@
         <v>519337</v>
       </c>
     </row>
-    <row r="131" spans="1:5" ht="17" thickBot="1">
+    <row r="131" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A131" s="11">
         <v>40726</v>
       </c>
@@ -9246,7 +9246,7 @@
         <v>522931</v>
       </c>
     </row>
-    <row r="132" spans="1:5" ht="17" thickBot="1">
+    <row r="132" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A132" s="11">
         <v>40733</v>
       </c>
@@ -9264,7 +9264,7 @@
         <v>438193</v>
       </c>
     </row>
-    <row r="133" spans="1:5" ht="17" thickBot="1">
+    <row r="133" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A133" s="11">
         <v>40740</v>
       </c>
@@ -9282,7 +9282,7 @@
         <v>511711</v>
       </c>
     </row>
-    <row r="134" spans="1:5" ht="17" thickBot="1">
+    <row r="134" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A134" s="11">
         <v>40747</v>
       </c>
@@ -9300,7 +9300,7 @@
         <v>524090</v>
       </c>
     </row>
-    <row r="135" spans="1:5" ht="17" thickBot="1">
+    <row r="135" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A135" s="11">
         <v>40754</v>
       </c>
@@ -9318,7 +9318,7 @@
         <v>533337</v>
       </c>
     </row>
-    <row r="136" spans="1:5" ht="17" thickBot="1">
+    <row r="136" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A136" s="11">
         <v>40761</v>
       </c>
@@ -9336,7 +9336,7 @@
         <v>522889</v>
       </c>
     </row>
-    <row r="137" spans="1:5" ht="17" thickBot="1">
+    <row r="137" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A137" s="11">
         <v>40768</v>
       </c>
@@ -9354,7 +9354,7 @@
         <v>527864</v>
       </c>
     </row>
-    <row r="138" spans="1:5" ht="17" thickBot="1">
+    <row r="138" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A138" s="11">
         <v>40775</v>
       </c>
@@ -9372,7 +9372,7 @@
         <v>539201</v>
       </c>
     </row>
-    <row r="139" spans="1:5" ht="17" thickBot="1">
+    <row r="139" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A139" s="11">
         <v>40782</v>
       </c>
@@ -9390,7 +9390,7 @@
         <v>535994</v>
       </c>
     </row>
-    <row r="140" spans="1:5" ht="17" thickBot="1">
+    <row r="140" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A140" s="11">
         <v>40789</v>
       </c>
@@ -9408,7 +9408,7 @@
         <v>537201</v>
       </c>
     </row>
-    <row r="141" spans="1:5" ht="17" thickBot="1">
+    <row r="141" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A141" s="11">
         <v>40796</v>
       </c>
@@ -9426,7 +9426,7 @@
         <v>486472</v>
       </c>
     </row>
-    <row r="142" spans="1:5" ht="17" thickBot="1">
+    <row r="142" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A142" s="11">
         <v>40803</v>
       </c>
@@ -9444,7 +9444,7 @@
         <v>542164</v>
       </c>
     </row>
-    <row r="143" spans="1:5" ht="17" thickBot="1">
+    <row r="143" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A143" s="11">
         <v>40810</v>
       </c>
@@ -9462,7 +9462,7 @@
         <v>553535</v>
       </c>
     </row>
-    <row r="144" spans="1:5" ht="17" thickBot="1">
+    <row r="144" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A144" s="11">
         <v>40817</v>
       </c>
@@ -9480,7 +9480,7 @@
         <v>563034</v>
       </c>
     </row>
-    <row r="145" spans="1:5" ht="17" thickBot="1">
+    <row r="145" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A145" s="11">
         <v>40824</v>
       </c>
@@ -9498,7 +9498,7 @@
         <v>544499</v>
       </c>
     </row>
-    <row r="146" spans="1:5" ht="17" thickBot="1">
+    <row r="146" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A146" s="11">
         <v>40831</v>
       </c>
@@ -9516,7 +9516,7 @@
         <v>547752</v>
       </c>
     </row>
-    <row r="147" spans="1:5" ht="17" thickBot="1">
+    <row r="147" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A147" s="11">
         <v>40838</v>
       </c>
@@ -9534,7 +9534,7 @@
         <v>547268</v>
       </c>
     </row>
-    <row r="148" spans="1:5" ht="17" thickBot="1">
+    <row r="148" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A148" s="11">
         <v>40845</v>
       </c>
@@ -9552,7 +9552,7 @@
         <v>551674</v>
       </c>
     </row>
-    <row r="149" spans="1:5" ht="17" thickBot="1">
+    <row r="149" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A149" s="11">
         <v>40852</v>
       </c>
@@ -9570,7 +9570,7 @@
         <v>537645</v>
       </c>
     </row>
-    <row r="150" spans="1:5" ht="17" thickBot="1">
+    <row r="150" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A150" s="11">
         <v>40859</v>
       </c>
@@ -9588,7 +9588,7 @@
         <v>544563</v>
       </c>
     </row>
-    <row r="151" spans="1:5" ht="17" thickBot="1">
+    <row r="151" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A151" s="13">
         <v>40866</v>
       </c>
@@ -9606,7 +9606,7 @@
         <v>545153</v>
       </c>
     </row>
-    <row r="152" spans="1:5" ht="17" thickBot="1">
+    <row r="152" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A152" s="11">
         <v>40873</v>
       </c>
@@ -9624,7 +9624,7 @@
         <v>456170</v>
       </c>
     </row>
-    <row r="153" spans="1:5" ht="17" thickBot="1">
+    <row r="153" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A153" s="11">
         <v>40880</v>
       </c>
@@ -9642,7 +9642,7 @@
         <v>555353</v>
       </c>
     </row>
-    <row r="154" spans="1:5" ht="17" thickBot="1">
+    <row r="154" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A154" s="11">
         <v>40887</v>
       </c>
@@ -9660,7 +9660,7 @@
         <v>538299</v>
       </c>
     </row>
-    <row r="155" spans="1:5" ht="17" thickBot="1">
+    <row r="155" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A155" s="11">
         <v>40894</v>
       </c>
@@ -9678,7 +9678,7 @@
         <v>537699</v>
       </c>
     </row>
-    <row r="156" spans="1:5" ht="17" thickBot="1">
+    <row r="156" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A156" s="11">
         <v>40901</v>
       </c>
@@ -9696,7 +9696,7 @@
         <v>505089</v>
       </c>
     </row>
-    <row r="157" spans="1:5" ht="17" thickBot="1">
+    <row r="157" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A157" s="11">
         <v>40908</v>
       </c>
@@ -9714,7 +9714,7 @@
         <v>426883</v>
       </c>
     </row>
-    <row r="158" spans="1:5" ht="17" thickBot="1">
+    <row r="158" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A158" s="11">
         <v>40915</v>
       </c>
@@ -9732,7 +9732,7 @@
         <v>468674</v>
       </c>
     </row>
-    <row r="159" spans="1:5" ht="17" thickBot="1">
+    <row r="159" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A159" s="11">
         <v>40922</v>
       </c>
@@ -9750,7 +9750,7 @@
         <v>527651</v>
       </c>
     </row>
-    <row r="160" spans="1:5" ht="17" thickBot="1">
+    <row r="160" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A160" s="11">
         <v>40929</v>
       </c>
@@ -9768,7 +9768,7 @@
         <v>507440</v>
       </c>
     </row>
-    <row r="161" spans="1:5" ht="17" thickBot="1">
+    <row r="161" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A161" s="11">
         <v>40936</v>
       </c>
@@ -9786,7 +9786,7 @@
         <v>518682</v>
       </c>
     </row>
-    <row r="162" spans="1:5" ht="17" thickBot="1">
+    <row r="162" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A162" s="11">
         <v>40943</v>
       </c>
@@ -9804,7 +9804,7 @@
         <v>517136</v>
       </c>
     </row>
-    <row r="163" spans="1:5" ht="17" thickBot="1">
+    <row r="163" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A163" s="11">
         <v>40950</v>
       </c>
@@ -9822,7 +9822,7 @@
         <v>506708</v>
       </c>
     </row>
-    <row r="164" spans="1:5" ht="17" thickBot="1">
+    <row r="164" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A164" s="11">
         <v>40957</v>
       </c>
@@ -9840,7 +9840,7 @@
         <v>502992</v>
       </c>
     </row>
-    <row r="165" spans="1:5" ht="17" thickBot="1">
+    <row r="165" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A165" s="11">
         <v>40964</v>
       </c>
@@ -9858,7 +9858,7 @@
         <v>496046</v>
       </c>
     </row>
-    <row r="166" spans="1:5" ht="17" thickBot="1">
+    <row r="166" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A166" s="11">
         <v>40971</v>
       </c>
@@ -9876,7 +9876,7 @@
         <v>510568</v>
       </c>
     </row>
-    <row r="167" spans="1:5" ht="17" thickBot="1">
+    <row r="167" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A167" s="11">
         <v>40978</v>
       </c>
@@ -9894,7 +9894,7 @@
         <v>504767</v>
       </c>
     </row>
-    <row r="168" spans="1:5" ht="17" thickBot="1">
+    <row r="168" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A168" s="11">
         <v>40985</v>
       </c>
@@ -9912,7 +9912,7 @@
         <v>505558</v>
       </c>
     </row>
-    <row r="169" spans="1:5" ht="17" thickBot="1">
+    <row r="169" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A169" s="11">
         <v>40992</v>
       </c>
@@ -9930,7 +9930,7 @@
         <v>510794</v>
       </c>
     </row>
-    <row r="170" spans="1:5" ht="17" thickBot="1">
+    <row r="170" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A170" s="11">
         <v>40999</v>
       </c>
@@ -9948,7 +9948,7 @@
         <v>529734</v>
       </c>
     </row>
-    <row r="171" spans="1:5" ht="17" thickBot="1">
+    <row r="171" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A171" s="11">
         <v>41006</v>
       </c>
@@ -9966,7 +9966,7 @@
         <v>502127</v>
       </c>
     </row>
-    <row r="172" spans="1:5" ht="17" thickBot="1">
+    <row r="172" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A172" s="11">
         <v>41013</v>
       </c>
@@ -9984,7 +9984,7 @@
         <v>510946</v>
       </c>
     </row>
-    <row r="173" spans="1:5" ht="17" thickBot="1">
+    <row r="173" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A173" s="11">
         <v>41020</v>
       </c>
@@ -10002,7 +10002,7 @@
         <v>521538</v>
       </c>
     </row>
-    <row r="174" spans="1:5" ht="17" thickBot="1">
+    <row r="174" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A174" s="11">
         <v>41027</v>
       </c>
@@ -10020,7 +10020,7 @@
         <v>525445</v>
       </c>
     </row>
-    <row r="175" spans="1:5" ht="17" thickBot="1">
+    <row r="175" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A175" s="11">
         <v>41034</v>
       </c>
@@ -10038,7 +10038,7 @@
         <v>515167</v>
       </c>
     </row>
-    <row r="176" spans="1:5" ht="17" thickBot="1">
+    <row r="176" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A176" s="13">
         <v>41041</v>
       </c>
@@ -10056,7 +10056,7 @@
         <v>518043</v>
       </c>
     </row>
-    <row r="177" spans="1:5" ht="17" thickBot="1">
+    <row r="177" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A177" s="11">
         <v>41048</v>
       </c>
@@ -10074,7 +10074,7 @@
         <v>522229</v>
       </c>
     </row>
-    <row r="178" spans="1:5" ht="17" thickBot="1">
+    <row r="178" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A178" s="11">
         <v>41055</v>
       </c>
@@ -10092,7 +10092,7 @@
         <v>536107</v>
       </c>
     </row>
-    <row r="179" spans="1:5" ht="17" thickBot="1">
+    <row r="179" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A179" s="11">
         <v>41062</v>
       </c>
@@ -10110,7 +10110,7 @@
         <v>479118</v>
       </c>
     </row>
-    <row r="180" spans="1:5" ht="17" thickBot="1">
+    <row r="180" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A180" s="11">
         <v>41069</v>
       </c>
@@ -10128,7 +10128,7 @@
         <v>531835</v>
       </c>
     </row>
-    <row r="181" spans="1:5" ht="17" thickBot="1">
+    <row r="181" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A181" s="11">
         <v>41076</v>
       </c>
@@ -10146,7 +10146,7 @@
         <v>537011</v>
       </c>
     </row>
-    <row r="182" spans="1:5" ht="17" thickBot="1">
+    <row r="182" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A182" s="11">
         <v>41083</v>
       </c>
@@ -10164,7 +10164,7 @@
         <v>534858</v>
       </c>
     </row>
-    <row r="183" spans="1:5" ht="17" thickBot="1">
+    <row r="183" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A183" s="11">
         <v>41090</v>
       </c>
@@ -10182,7 +10182,7 @@
         <v>532131</v>
       </c>
     </row>
-    <row r="184" spans="1:5" ht="17" thickBot="1">
+    <row r="184" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A184" s="11">
         <v>41097</v>
       </c>
@@ -10200,7 +10200,7 @@
         <v>446518</v>
       </c>
     </row>
-    <row r="185" spans="1:5" ht="17" thickBot="1">
+    <row r="185" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A185" s="11">
         <v>41104</v>
       </c>
@@ -10218,7 +10218,7 @@
         <v>532071</v>
       </c>
     </row>
-    <row r="186" spans="1:5" ht="17" thickBot="1">
+    <row r="186" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A186" s="11">
         <v>41111</v>
       </c>
@@ -10236,7 +10236,7 @@
         <v>532729</v>
       </c>
     </row>
-    <row r="187" spans="1:5" ht="17" thickBot="1">
+    <row r="187" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A187" s="11">
         <v>41118</v>
       </c>
@@ -10254,7 +10254,7 @@
         <v>538486</v>
       </c>
     </row>
-    <row r="188" spans="1:5" ht="17" thickBot="1">
+    <row r="188" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A188" s="11">
         <v>41125</v>
       </c>
@@ -10272,7 +10272,7 @@
         <v>531490</v>
       </c>
     </row>
-    <row r="189" spans="1:5" ht="17" thickBot="1">
+    <row r="189" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A189" s="11">
         <v>41132</v>
       </c>
@@ -10290,7 +10290,7 @@
         <v>532202</v>
       </c>
     </row>
-    <row r="190" spans="1:5" ht="17" thickBot="1">
+    <row r="190" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A190" s="11">
         <v>41139</v>
       </c>
@@ -10308,7 +10308,7 @@
         <v>541140</v>
       </c>
     </row>
-    <row r="191" spans="1:5" ht="17" thickBot="1">
+    <row r="191" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A191" s="11">
         <v>41146</v>
       </c>
@@ -10326,7 +10326,7 @@
         <v>545406</v>
       </c>
     </row>
-    <row r="192" spans="1:5" ht="17" thickBot="1">
+    <row r="192" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A192" s="11">
         <v>41153</v>
       </c>
@@ -10344,7 +10344,7 @@
         <v>541845</v>
       </c>
     </row>
-    <row r="193" spans="1:5" ht="17" thickBot="1">
+    <row r="193" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A193" s="11">
         <v>41160</v>
       </c>
@@ -10362,7 +10362,7 @@
         <v>486818</v>
       </c>
     </row>
-    <row r="194" spans="1:5" ht="17" thickBot="1">
+    <row r="194" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A194" s="11">
         <v>41167</v>
       </c>
@@ -10395,7 +10395,7 @@
         <v>543250</v>
       </c>
     </row>
-    <row r="195" spans="1:5" ht="17" thickBot="1">
+    <row r="195" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A195" s="11">
         <v>41174</v>
       </c>
@@ -10413,7 +10413,7 @@
         <v>542897</v>
       </c>
     </row>
-    <row r="196" spans="1:5" ht="17" thickBot="1">
+    <row r="196" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A196" s="11">
         <v>41181</v>
       </c>
@@ -10431,7 +10431,7 @@
         <v>552468</v>
       </c>
     </row>
-    <row r="197" spans="1:5" ht="17" thickBot="1">
+    <row r="197" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A197" s="11">
         <v>41188</v>
       </c>
@@ -10449,7 +10449,7 @@
         <v>534553</v>
       </c>
     </row>
-    <row r="198" spans="1:5" ht="17" thickBot="1">
+    <row r="198" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A198" s="11">
         <v>41195</v>
       </c>
@@ -10467,7 +10467,7 @@
         <v>535915</v>
       </c>
     </row>
-    <row r="199" spans="1:5" ht="17" thickBot="1">
+    <row r="199" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A199" s="11">
         <v>41202</v>
       </c>
@@ -10485,7 +10485,7 @@
         <v>542674</v>
       </c>
     </row>
-    <row r="200" spans="1:5" ht="17" thickBot="1">
+    <row r="200" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A200" s="11">
         <v>41209</v>
       </c>
@@ -10503,7 +10503,7 @@
         <v>540290</v>
       </c>
     </row>
-    <row r="201" spans="1:5" ht="17" thickBot="1">
+    <row r="201" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A201" s="13">
         <v>41216</v>
       </c>
@@ -10521,7 +10521,7 @@
         <v>502697</v>
       </c>
     </row>
-    <row r="202" spans="1:5" ht="17" thickBot="1">
+    <row r="202" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A202" s="11">
         <v>41223</v>
       </c>
@@ -10539,7 +10539,7 @@
         <v>532945</v>
       </c>
     </row>
-    <row r="203" spans="1:5" ht="17" thickBot="1">
+    <row r="203" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A203" s="11">
         <v>41230</v>
       </c>
@@ -10557,7 +10557,7 @@
         <v>537832</v>
       </c>
     </row>
-    <row r="204" spans="1:5" ht="17" thickBot="1">
+    <row r="204" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A204" s="11">
         <v>41237</v>
       </c>
@@ -10575,7 +10575,7 @@
         <v>447469</v>
       </c>
     </row>
-    <row r="205" spans="1:5" ht="17" thickBot="1">
+    <row r="205" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A205" s="11">
         <v>41244</v>
       </c>
@@ -10593,7 +10593,7 @@
         <v>547119</v>
       </c>
     </row>
-    <row r="206" spans="1:5" ht="17" thickBot="1">
+    <row r="206" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A206" s="11">
         <v>41251</v>
       </c>
@@ -10611,7 +10611,7 @@
         <v>532304</v>
       </c>
     </row>
-    <row r="207" spans="1:5" ht="17" thickBot="1">
+    <row r="207" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A207" s="11">
         <v>41258</v>
       </c>
@@ -10629,7 +10629,7 @@
         <v>544625</v>
       </c>
     </row>
-    <row r="208" spans="1:5" ht="17" thickBot="1">
+    <row r="208" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A208" s="11">
         <v>41265</v>
       </c>
@@ -10647,7 +10647,7 @@
         <v>530342</v>
       </c>
     </row>
-    <row r="209" spans="1:5" ht="17" thickBot="1">
+    <row r="209" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A209" s="11">
         <v>41272</v>
       </c>
@@ -10665,7 +10665,7 @@
         <v>367721</v>
       </c>
     </row>
-    <row r="210" spans="1:5" ht="17" thickBot="1">
+    <row r="210" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A210" s="11">
         <v>41279</v>
       </c>
@@ -10683,7 +10683,7 @@
         <v>419999</v>
       </c>
     </row>
-    <row r="211" spans="1:5" ht="17" thickBot="1">
+    <row r="211" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A211" s="11">
         <v>41286</v>
       </c>
@@ -10701,7 +10701,7 @@
         <v>532789</v>
       </c>
     </row>
-    <row r="212" spans="1:5" ht="17" thickBot="1">
+    <row r="212" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A212" s="11">
         <v>41293</v>
       </c>
@@ -10719,7 +10719,7 @@
         <v>526887</v>
       </c>
     </row>
-    <row r="213" spans="1:5" ht="17" thickBot="1">
+    <row r="213" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A213" s="11">
         <v>41300</v>
       </c>
@@ -10737,7 +10737,7 @@
         <v>504628</v>
       </c>
     </row>
-    <row r="214" spans="1:5" ht="17" thickBot="1">
+    <row r="214" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A214" s="11">
         <v>41307</v>
       </c>
@@ -10755,7 +10755,7 @@
         <v>523931</v>
       </c>
     </row>
-    <row r="215" spans="1:5" ht="17" thickBot="1">
+    <row r="215" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A215" s="11">
         <v>41314</v>
       </c>
@@ -10773,7 +10773,7 @@
         <v>518048</v>
       </c>
     </row>
-    <row r="216" spans="1:5" ht="17" thickBot="1">
+    <row r="216" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A216" s="11">
         <v>41321</v>
       </c>
@@ -10791,7 +10791,7 @@
         <v>529674</v>
       </c>
     </row>
-    <row r="217" spans="1:5" ht="17" thickBot="1">
+    <row r="217" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A217" s="11">
         <v>41328</v>
       </c>
@@ -10809,7 +10809,7 @@
         <v>516142</v>
       </c>
     </row>
-    <row r="218" spans="1:5" ht="17" thickBot="1">
+    <row r="218" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A218" s="11">
         <v>41335</v>
       </c>
@@ -10827,7 +10827,7 @@
         <v>533057</v>
       </c>
     </row>
-    <row r="219" spans="1:5" ht="17" thickBot="1">
+    <row r="219" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A219" s="11">
         <v>41342</v>
       </c>
@@ -10845,7 +10845,7 @@
         <v>511872</v>
       </c>
     </row>
-    <row r="220" spans="1:5" ht="17" thickBot="1">
+    <row r="220" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A220" s="11">
         <v>41349</v>
       </c>
@@ -10863,7 +10863,7 @@
         <v>509430</v>
       </c>
     </row>
-    <row r="221" spans="1:5" ht="17" thickBot="1">
+    <row r="221" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A221" s="11">
         <v>41356</v>
       </c>
@@ -10881,7 +10881,7 @@
         <v>514379</v>
       </c>
     </row>
-    <row r="222" spans="1:5" ht="17" thickBot="1">
+    <row r="222" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A222" s="11">
         <v>41363</v>
       </c>
@@ -10899,7 +10899,7 @@
         <v>514954</v>
       </c>
     </row>
-    <row r="223" spans="1:5" ht="17" thickBot="1">
+    <row r="223" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A223" s="11">
         <v>41370</v>
       </c>
@@ -10917,7 +10917,7 @@
         <v>512396</v>
       </c>
     </row>
-    <row r="224" spans="1:5" ht="17" thickBot="1">
+    <row r="224" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A224" s="11">
         <v>41377</v>
       </c>
@@ -10935,7 +10935,7 @@
         <v>517662</v>
       </c>
     </row>
-    <row r="225" spans="1:5" ht="17" thickBot="1">
+    <row r="225" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A225" s="11">
         <v>41384</v>
       </c>
@@ -10953,7 +10953,7 @@
         <v>517360</v>
       </c>
     </row>
-    <row r="226" spans="1:5" ht="17" thickBot="1">
+    <row r="226" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A226" s="13">
         <v>41391</v>
       </c>
@@ -10971,7 +10971,7 @@
         <v>523207</v>
       </c>
     </row>
-    <row r="227" spans="1:5" ht="17" thickBot="1">
+    <row r="227" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A227" s="11">
         <v>41398</v>
       </c>
@@ -10989,7 +10989,7 @@
         <v>529594</v>
       </c>
     </row>
-    <row r="228" spans="1:5" ht="17" thickBot="1">
+    <row r="228" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A228" s="11">
         <v>41405</v>
       </c>
@@ -11007,7 +11007,7 @@
         <v>529252</v>
       </c>
     </row>
-    <row r="229" spans="1:5" ht="17" thickBot="1">
+    <row r="229" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A229" s="11">
         <v>41412</v>
       </c>
@@ -11025,7 +11025,7 @@
         <v>535835</v>
       </c>
     </row>
-    <row r="230" spans="1:5" ht="17" thickBot="1">
+    <row r="230" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A230" s="11">
         <v>41419</v>
       </c>
@@ -11043,7 +11043,7 @@
         <v>529937</v>
       </c>
     </row>
-    <row r="231" spans="1:5" ht="17" thickBot="1">
+    <row r="231" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A231" s="11">
         <v>41426</v>
       </c>
@@ -11061,7 +11061,7 @@
         <v>491082</v>
       </c>
     </row>
-    <row r="232" spans="1:5" ht="17" thickBot="1">
+    <row r="232" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A232" s="11">
         <v>41433</v>
       </c>
@@ -11079,7 +11079,7 @@
         <v>530890</v>
       </c>
     </row>
-    <row r="233" spans="1:5" ht="17" thickBot="1">
+    <row r="233" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A233" s="11">
         <v>41440</v>
       </c>
@@ -11097,7 +11097,7 @@
         <v>543145</v>
       </c>
     </row>
-    <row r="234" spans="1:5" ht="17" thickBot="1">
+    <row r="234" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A234" s="11">
         <v>41447</v>
       </c>
@@ -11115,7 +11115,7 @@
         <v>541031</v>
       </c>
     </row>
-    <row r="235" spans="1:5" ht="17" thickBot="1">
+    <row r="235" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A235" s="11">
         <v>41454</v>
       </c>
@@ -11133,7 +11133,7 @@
         <v>531040</v>
       </c>
     </row>
-    <row r="236" spans="1:5" ht="17" thickBot="1">
+    <row r="236" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A236" s="11">
         <v>41461</v>
       </c>
@@ -11151,7 +11151,7 @@
         <v>453493</v>
       </c>
     </row>
-    <row r="237" spans="1:5" ht="17" thickBot="1">
+    <row r="237" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A237" s="11">
         <v>41468</v>
       </c>
@@ -11169,7 +11169,7 @@
         <v>525333</v>
       </c>
     </row>
-    <row r="238" spans="1:5" ht="17" thickBot="1">
+    <row r="238" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A238" s="11">
         <v>41475</v>
       </c>
@@ -11187,7 +11187,7 @@
         <v>531357</v>
       </c>
     </row>
-    <row r="239" spans="1:5" ht="17" thickBot="1">
+    <row r="239" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A239" s="11">
         <v>41482</v>
       </c>
@@ -11205,7 +11205,7 @@
         <v>551911</v>
       </c>
     </row>
-    <row r="240" spans="1:5" ht="17" thickBot="1">
+    <row r="240" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A240" s="11">
         <v>41489</v>
       </c>
@@ -11223,7 +11223,7 @@
         <v>542396</v>
       </c>
     </row>
-    <row r="241" spans="1:5" ht="17" thickBot="1">
+    <row r="241" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A241" s="11">
         <v>41496</v>
       </c>
@@ -11241,7 +11241,7 @@
         <v>546772</v>
       </c>
     </row>
-    <row r="242" spans="1:5" ht="17" thickBot="1">
+    <row r="242" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A242" s="11">
         <v>41503</v>
       </c>
@@ -11259,7 +11259,7 @@
         <v>552359</v>
       </c>
     </row>
-    <row r="243" spans="1:5" ht="17" thickBot="1">
+    <row r="243" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A243" s="11">
         <v>41510</v>
       </c>
@@ -11277,7 +11277,7 @@
         <v>548969</v>
       </c>
     </row>
-    <row r="244" spans="1:5" ht="17" thickBot="1">
+    <row r="244" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A244" s="11">
         <v>41517</v>
       </c>
@@ -11295,7 +11295,7 @@
         <v>561698</v>
       </c>
     </row>
-    <row r="245" spans="1:5" ht="17" thickBot="1">
+    <row r="245" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A245" s="11">
         <v>41524</v>
       </c>
@@ -11313,7 +11313,7 @@
         <v>507493</v>
       </c>
     </row>
-    <row r="246" spans="1:5" ht="17" thickBot="1">
+    <row r="246" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A246" s="11">
         <v>41531</v>
       </c>
@@ -11331,7 +11331,7 @@
         <v>562094</v>
       </c>
     </row>
-    <row r="247" spans="1:5" ht="17" thickBot="1">
+    <row r="247" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A247" s="11">
         <v>41538</v>
       </c>
@@ -11349,7 +11349,7 @@
         <v>551057</v>
       </c>
     </row>
-    <row r="248" spans="1:5" ht="17" thickBot="1">
+    <row r="248" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A248" s="11">
         <v>41545</v>
       </c>
@@ -11367,7 +11367,7 @@
         <v>566662</v>
       </c>
     </row>
-    <row r="249" spans="1:5" ht="17" thickBot="1">
+    <row r="249" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A249" s="11">
         <v>41552</v>
       </c>
@@ -11385,7 +11385,7 @@
         <v>545708</v>
       </c>
     </row>
-    <row r="250" spans="1:5" ht="17" thickBot="1">
+    <row r="250" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A250" s="11">
         <v>41559</v>
       </c>
@@ -11403,7 +11403,7 @@
         <v>546211</v>
       </c>
     </row>
-    <row r="251" spans="1:5" ht="17" thickBot="1">
+    <row r="251" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A251" s="13">
         <v>41566</v>
       </c>
@@ -11421,7 +11421,7 @@
         <v>553943</v>
       </c>
     </row>
-    <row r="252" spans="1:5" ht="17" thickBot="1">
+    <row r="252" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A252" s="11">
         <v>41573</v>
       </c>
@@ -11439,7 +11439,7 @@
         <v>558686</v>
       </c>
     </row>
-    <row r="253" spans="1:5" ht="17" thickBot="1">
+    <row r="253" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A253" s="11">
         <v>41580</v>
       </c>
@@ -11457,7 +11457,7 @@
         <v>556662</v>
       </c>
     </row>
-    <row r="254" spans="1:5" ht="17" thickBot="1">
+    <row r="254" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A254" s="11">
         <v>41587</v>
       </c>
@@ -11475,7 +11475,7 @@
         <v>562840</v>
       </c>
     </row>
-    <row r="255" spans="1:5" ht="17" thickBot="1">
+    <row r="255" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A255" s="11">
         <v>41594</v>
       </c>
@@ -11493,7 +11493,7 @@
         <v>562206</v>
       </c>
     </row>
-    <row r="256" spans="1:5" ht="17" thickBot="1">
+    <row r="256" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A256" s="11">
         <v>41601</v>
       </c>
@@ -11511,7 +11511,7 @@
         <v>564340</v>
       </c>
     </row>
-    <row r="257" spans="1:5" ht="17" thickBot="1">
+    <row r="257" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A257" s="11">
         <v>41608</v>
       </c>
@@ -11529,7 +11529,7 @@
         <v>463516</v>
       </c>
     </row>
-    <row r="258" spans="1:5" ht="17" thickBot="1">
+    <row r="258" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A258" s="11">
         <v>41615</v>
       </c>
@@ -11562,7 +11562,7 @@
         <v>541978</v>
       </c>
     </row>
-    <row r="259" spans="1:5" ht="17" thickBot="1">
+    <row r="259" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A259" s="11">
         <v>41622</v>
       </c>
@@ -11580,7 +11580,7 @@
         <v>546825</v>
       </c>
     </row>
-    <row r="260" spans="1:5" ht="17" thickBot="1">
+    <row r="260" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A260" s="11">
         <v>41629</v>
       </c>
@@ -11598,7 +11598,7 @@
         <v>544984</v>
       </c>
     </row>
-    <row r="261" spans="1:5" ht="17" thickBot="1">
+    <row r="261" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A261" s="11">
         <v>41636</v>
       </c>
@@ -11616,7 +11616,7 @@
         <v>403329</v>
       </c>
     </row>
-    <row r="262" spans="1:5" ht="17" thickBot="1">
+    <row r="262" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A262" s="11">
         <v>41643</v>
       </c>
@@ -11634,7 +11634,7 @@
         <v>433724</v>
       </c>
     </row>
-    <row r="263" spans="1:5" ht="17" thickBot="1">
+    <row r="263" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A263" s="11">
         <v>41650</v>
       </c>
@@ -11652,7 +11652,7 @@
         <v>492836</v>
       </c>
     </row>
-    <row r="264" spans="1:5" ht="17" thickBot="1">
+    <row r="264" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A264" s="11">
         <v>41657</v>
       </c>
@@ -11670,7 +11670,7 @@
         <v>557253</v>
       </c>
     </row>
-    <row r="265" spans="1:5" ht="17" thickBot="1">
+    <row r="265" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A265" s="11">
         <v>41664</v>
       </c>
@@ -11688,7 +11688,7 @@
         <v>526644</v>
       </c>
     </row>
-    <row r="266" spans="1:5" ht="17" thickBot="1">
+    <row r="266" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A266" s="11">
         <v>41671</v>
       </c>
@@ -11706,7 +11706,7 @@
         <v>518012</v>
       </c>
     </row>
-    <row r="267" spans="1:5" ht="17" thickBot="1">
+    <row r="267" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A267" s="11">
         <v>41678</v>
       </c>
@@ -11724,7 +11724,7 @@
         <v>507368</v>
       </c>
     </row>
-    <row r="268" spans="1:5" ht="17" thickBot="1">
+    <row r="268" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A268" s="11">
         <v>41685</v>
       </c>
@@ -11742,7 +11742,7 @@
         <v>507257</v>
       </c>
     </row>
-    <row r="269" spans="1:5" ht="17" thickBot="1">
+    <row r="269" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A269" s="11">
         <v>41692</v>
       </c>
@@ -11760,7 +11760,7 @@
         <v>535036</v>
       </c>
     </row>
-    <row r="270" spans="1:5" ht="17" thickBot="1">
+    <row r="270" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A270" s="11">
         <v>41699</v>
       </c>
@@ -11778,7 +11778,7 @@
         <v>545004</v>
       </c>
     </row>
-    <row r="271" spans="1:5" ht="17" thickBot="1">
+    <row r="271" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A271" s="11">
         <v>41706</v>
       </c>
@@ -11796,7 +11796,7 @@
         <v>518495</v>
       </c>
     </row>
-    <row r="272" spans="1:5" ht="17" thickBot="1">
+    <row r="272" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A272" s="11">
         <v>41713</v>
       </c>
@@ -11814,7 +11814,7 @@
         <v>545366</v>
       </c>
     </row>
-    <row r="273" spans="1:5" ht="17" thickBot="1">
+    <row r="273" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A273" s="11">
         <v>41720</v>
       </c>
@@ -11832,7 +11832,7 @@
         <v>552238</v>
       </c>
     </row>
-    <row r="274" spans="1:5" ht="17" thickBot="1">
+    <row r="274" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A274" s="11">
         <v>41727</v>
       </c>
@@ -11850,7 +11850,7 @@
         <v>566505</v>
       </c>
     </row>
-    <row r="275" spans="1:5" ht="17" thickBot="1">
+    <row r="275" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A275" s="11">
         <v>41734</v>
       </c>
@@ -11868,7 +11868,7 @@
         <v>557123</v>
       </c>
     </row>
-    <row r="276" spans="1:5" ht="17" thickBot="1">
+    <row r="276" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A276" s="13">
         <v>41741</v>
       </c>
@@ -11886,7 +11886,7 @@
         <v>559676</v>
       </c>
     </row>
-    <row r="277" spans="1:5" ht="17" thickBot="1">
+    <row r="277" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A277" s="11">
         <v>41748</v>
       </c>
@@ -11904,7 +11904,7 @@
         <v>549826</v>
       </c>
     </row>
-    <row r="278" spans="1:5" ht="17" thickBot="1">
+    <row r="278" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A278" s="11">
         <v>41755</v>
       </c>
@@ -11922,7 +11922,7 @@
         <v>566336</v>
       </c>
     </row>
-    <row r="279" spans="1:5" ht="17" thickBot="1">
+    <row r="279" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A279" s="11">
         <v>41762</v>
       </c>
@@ -11940,7 +11940,7 @@
         <v>564801</v>
       </c>
     </row>
-    <row r="280" spans="1:5" ht="17" thickBot="1">
+    <row r="280" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A280" s="11">
         <v>41769</v>
       </c>
@@ -11958,7 +11958,7 @@
         <v>564096</v>
       </c>
     </row>
-    <row r="281" spans="1:5" ht="17" thickBot="1">
+    <row r="281" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A281" s="11">
         <v>41783</v>
       </c>
@@ -11976,7 +11976,7 @@
         <v>570380</v>
       </c>
     </row>
-    <row r="282" spans="1:5" ht="17" thickBot="1">
+    <row r="282" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A282" s="11">
         <v>41790</v>
       </c>
@@ -11994,7 +11994,7 @@
         <v>531725</v>
       </c>
     </row>
-    <row r="283" spans="1:5" ht="17" thickBot="1">
+    <row r="283" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A283" s="11">
         <v>41797</v>
       </c>
@@ -12012,7 +12012,7 @@
         <v>562747</v>
       </c>
     </row>
-    <row r="284" spans="1:5" ht="17" thickBot="1">
+    <row r="284" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A284" s="11">
         <v>41804</v>
       </c>
@@ -12030,7 +12030,7 @@
         <v>565375</v>
       </c>
     </row>
-    <row r="285" spans="1:5" ht="17" thickBot="1">
+    <row r="285" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A285" s="11">
         <v>41811</v>
       </c>
@@ -12048,7 +12048,7 @@
         <v>563695</v>
       </c>
     </row>
-    <row r="286" spans="1:5" ht="17" thickBot="1">
+    <row r="286" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A286" s="11">
         <v>41818</v>
       </c>
@@ -12066,7 +12066,7 @@
         <v>563223</v>
       </c>
     </row>
-    <row r="287" spans="1:5" ht="17" thickBot="1">
+    <row r="287" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A287" s="11">
         <v>41825</v>
       </c>
@@ -12084,7 +12084,7 @@
         <v>497828</v>
       </c>
     </row>
-    <row r="288" spans="1:5" ht="17" thickBot="1">
+    <row r="288" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A288" s="11">
         <v>41832</v>
       </c>
@@ -12102,7 +12102,7 @@
         <v>546863</v>
       </c>
     </row>
-    <row r="289" spans="1:5" ht="17" thickBot="1">
+    <row r="289" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A289" s="11">
         <v>41839</v>
       </c>
@@ -12120,7 +12120,7 @@
         <v>566931</v>
       </c>
     </row>
-    <row r="290" spans="1:5" ht="17" thickBot="1">
+    <row r="290" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A290" s="11">
         <v>41846</v>
       </c>
@@ -12138,7 +12138,7 @@
         <v>571797</v>
       </c>
     </row>
-    <row r="291" spans="1:5" ht="17" thickBot="1">
+    <row r="291" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A291" s="11">
         <v>41853</v>
       </c>
@@ -12156,7 +12156,7 @@
         <v>574552</v>
       </c>
     </row>
-    <row r="292" spans="1:5" ht="17" thickBot="1">
+    <row r="292" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A292" s="11">
         <v>41860</v>
       </c>
@@ -12174,7 +12174,7 @@
         <v>567908</v>
       </c>
     </row>
-    <row r="293" spans="1:5" ht="17" thickBot="1">
+    <row r="293" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A293" s="11">
         <v>41867</v>
       </c>
@@ -12192,7 +12192,7 @@
         <v>574592</v>
       </c>
     </row>
-    <row r="294" spans="1:5" ht="17" thickBot="1">
+    <row r="294" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A294" s="11">
         <v>41874</v>
       </c>
@@ -12210,7 +12210,7 @@
         <v>566266</v>
       </c>
     </row>
-    <row r="295" spans="1:5" ht="17" thickBot="1">
+    <row r="295" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A295" s="11">
         <v>41881</v>
       </c>
@@ -12228,7 +12228,7 @@
         <v>579209</v>
       </c>
     </row>
-    <row r="296" spans="1:5" ht="17" thickBot="1">
+    <row r="296" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A296" s="11">
         <v>41888</v>
       </c>
@@ -12246,7 +12246,7 @@
         <v>525144</v>
       </c>
     </row>
-    <row r="297" spans="1:5" ht="17" thickBot="1">
+    <row r="297" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A297" s="11">
         <v>41895</v>
       </c>
@@ -12264,7 +12264,7 @@
         <v>579440</v>
       </c>
     </row>
-    <row r="298" spans="1:5" ht="17" thickBot="1">
+    <row r="298" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A298" s="11">
         <v>41902</v>
       </c>
@@ -12282,7 +12282,7 @@
         <v>581955</v>
       </c>
     </row>
-    <row r="299" spans="1:5" ht="17" thickBot="1">
+    <row r="299" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A299" s="11">
         <v>41909</v>
       </c>
@@ -12300,7 +12300,7 @@
         <v>576934</v>
       </c>
     </row>
-    <row r="300" spans="1:5" ht="17" thickBot="1">
+    <row r="300" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A300" s="11">
         <v>41916</v>
       </c>
@@ -12318,7 +12318,7 @@
         <v>576356</v>
       </c>
     </row>
-    <row r="301" spans="1:5" ht="17" thickBot="1">
+    <row r="301" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A301" s="13">
         <v>41923</v>
       </c>
@@ -12336,7 +12336,7 @@
         <v>571812</v>
       </c>
     </row>
-    <row r="302" spans="1:5" ht="17" thickBot="1">
+    <row r="302" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A302" s="11">
         <v>41930</v>
       </c>
@@ -12354,7 +12354,7 @@
         <v>569684</v>
       </c>
     </row>
-    <row r="303" spans="1:5" ht="17" thickBot="1">
+    <row r="303" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A303" s="11">
         <v>41937</v>
       </c>
@@ -12372,7 +12372,7 @@
         <v>586115</v>
       </c>
     </row>
-    <row r="304" spans="1:5" ht="17" thickBot="1">
+    <row r="304" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A304" s="11">
         <v>41944</v>
       </c>
@@ -12390,7 +12390,7 @@
         <v>585208</v>
       </c>
     </row>
-    <row r="305" spans="1:5" ht="17" thickBot="1">
+    <row r="305" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A305" s="11">
         <v>41951</v>
       </c>
@@ -12408,7 +12408,7 @@
         <v>568807</v>
       </c>
     </row>
-    <row r="306" spans="1:5" ht="17" thickBot="1">
+    <row r="306" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A306" s="11">
         <v>41958</v>
       </c>
@@ -12426,7 +12426,7 @@
         <v>570350</v>
       </c>
     </row>
-    <row r="307" spans="1:5" ht="17" thickBot="1">
+    <row r="307" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A307" s="11">
         <v>41965</v>
       </c>
@@ -12444,7 +12444,7 @@
         <v>565185</v>
       </c>
     </row>
-    <row r="308" spans="1:5" ht="17" thickBot="1">
+    <row r="308" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A308" s="11">
         <v>41972</v>
       </c>
@@ -12462,7 +12462,7 @@
         <v>492532</v>
       </c>
     </row>
-    <row r="309" spans="1:5" ht="17" thickBot="1">
+    <row r="309" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A309" s="11">
         <v>41979</v>
       </c>
@@ -12480,7 +12480,7 @@
         <v>580108</v>
       </c>
     </row>
-    <row r="310" spans="1:5" ht="17" thickBot="1">
+    <row r="310" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A310" s="11">
         <v>41986</v>
       </c>
@@ -12498,7 +12498,7 @@
         <v>592608</v>
       </c>
     </row>
-    <row r="311" spans="1:5" ht="17" thickBot="1">
+    <row r="311" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A311" s="11">
         <v>41993</v>
       </c>
@@ -12516,7 +12516,7 @@
         <v>580559</v>
       </c>
     </row>
-    <row r="312" spans="1:5" ht="17" thickBot="1">
+    <row r="312" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A312" s="11">
         <v>42000</v>
       </c>
@@ -12534,7 +12534,7 @@
         <v>433338</v>
       </c>
     </row>
-    <row r="313" spans="1:5" ht="17" thickBot="1">
+    <row r="313" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A313" s="11">
         <v>42007</v>
       </c>
@@ -12552,7 +12552,7 @@
         <v>446201</v>
       </c>
     </row>
-    <row r="314" spans="1:5" ht="17" thickBot="1">
+    <row r="314" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A314" s="11">
         <v>42014</v>
       </c>
@@ -12570,7 +12570,7 @@
         <v>517520</v>
       </c>
     </row>
-    <row r="315" spans="1:5" ht="17" thickBot="1">
+    <row r="315" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A315" s="11">
         <v>42021</v>
       </c>
@@ -12588,7 +12588,7 @@
         <v>551856</v>
       </c>
     </row>
-    <row r="316" spans="1:5" ht="17" thickBot="1">
+    <row r="316" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A316" s="11">
         <v>42028</v>
       </c>
@@ -12606,7 +12606,7 @@
         <v>548055</v>
       </c>
     </row>
-    <row r="317" spans="1:5" ht="17" thickBot="1">
+    <row r="317" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A317" s="11">
         <v>42035</v>
       </c>
@@ -12624,7 +12624,7 @@
         <v>548478</v>
       </c>
     </row>
-    <row r="318" spans="1:5" ht="17" thickBot="1">
+    <row r="318" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A318" s="11">
         <v>42042</v>
       </c>
@@ -12642,7 +12642,7 @@
         <v>511563</v>
       </c>
     </row>
-    <row r="319" spans="1:5" ht="17" thickBot="1">
+    <row r="319" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A319" s="11">
         <v>42049</v>
       </c>
@@ -12660,7 +12660,7 @@
         <v>525224</v>
       </c>
     </row>
-    <row r="320" spans="1:5" ht="17" thickBot="1">
+    <row r="320" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A320" s="11">
         <v>42056</v>
       </c>
@@ -12678,7 +12678,7 @@
         <v>473161</v>
       </c>
     </row>
-    <row r="321" spans="1:5" ht="17" thickBot="1">
+    <row r="321" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A321" s="11">
         <v>42063</v>
       </c>
@@ -12696,7 +12696,7 @@
         <v>508658</v>
       </c>
     </row>
-    <row r="322" spans="1:5" ht="17" thickBot="1">
+    <row r="322" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A322" s="11">
         <v>42070</v>
       </c>
@@ -12729,7 +12729,7 @@
         <v>522382</v>
       </c>
     </row>
-    <row r="323" spans="1:5" ht="17" thickBot="1">
+    <row r="323" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A323" s="11">
         <v>42077</v>
       </c>
@@ -12747,7 +12747,7 @@
         <v>553031</v>
       </c>
     </row>
-    <row r="324" spans="1:5" ht="17" thickBot="1">
+    <row r="324" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A324" s="11">
         <v>42084</v>
       </c>
@@ -12765,7 +12765,7 @@
         <v>562472</v>
       </c>
     </row>
-    <row r="325" spans="1:5" ht="17" thickBot="1">
+    <row r="325" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A325" s="11">
         <v>42091</v>
       </c>
@@ -12783,7 +12783,7 @@
         <v>563280</v>
       </c>
     </row>
-    <row r="326" spans="1:5" ht="17" thickBot="1">
+    <row r="326" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A326" s="13">
         <v>42098</v>
       </c>
@@ -12801,7 +12801,7 @@
         <v>549021</v>
       </c>
     </row>
-    <row r="327" spans="1:5" ht="17" thickBot="1">
+    <row r="327" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A327" s="11">
         <v>42105</v>
       </c>
@@ -12819,7 +12819,7 @@
         <v>557812</v>
       </c>
     </row>
-    <row r="328" spans="1:5" ht="17" thickBot="1">
+    <row r="328" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A328" s="11">
         <v>42112</v>
       </c>
@@ -12837,7 +12837,7 @@
         <v>556432</v>
       </c>
     </row>
-    <row r="329" spans="1:5" ht="17" thickBot="1">
+    <row r="329" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A329" s="11">
         <v>42119</v>
       </c>
@@ -12855,7 +12855,7 @@
         <v>557306</v>
       </c>
     </row>
-    <row r="330" spans="1:5" ht="17" thickBot="1">
+    <row r="330" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A330" s="11">
         <v>42126</v>
       </c>
@@ -12873,7 +12873,7 @@
         <v>565787</v>
       </c>
     </row>
-    <row r="331" spans="1:5" ht="17" thickBot="1">
+    <row r="331" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A331" s="11">
         <v>42133</v>
       </c>
@@ -12891,7 +12891,7 @@
         <v>551034</v>
       </c>
     </row>
-    <row r="332" spans="1:5" ht="17" thickBot="1">
+    <row r="332" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A332" s="11">
         <v>42140</v>
       </c>
@@ -12909,7 +12909,7 @@
         <v>549199</v>
       </c>
     </row>
-    <row r="333" spans="1:5" ht="17" thickBot="1">
+    <row r="333" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A333" s="11">
         <v>42147</v>
       </c>
@@ -12927,7 +12927,7 @@
         <v>554477</v>
       </c>
     </row>
-    <row r="334" spans="1:5" ht="17" thickBot="1">
+    <row r="334" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A334" s="11">
         <v>42154</v>
       </c>
@@ -12945,7 +12945,7 @@
         <v>505543</v>
       </c>
     </row>
-    <row r="335" spans="1:5" ht="17" thickBot="1">
+    <row r="335" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A335" s="11">
         <v>42161</v>
       </c>
@@ -12963,7 +12963,7 @@
         <v>550037</v>
       </c>
     </row>
-    <row r="336" spans="1:5" ht="17" thickBot="1">
+    <row r="336" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A336" s="11">
         <v>42168</v>
       </c>
@@ -12981,7 +12981,7 @@
         <v>554461</v>
       </c>
     </row>
-    <row r="337" spans="1:5" ht="17" thickBot="1">
+    <row r="337" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A337" s="11">
         <v>42175</v>
       </c>
@@ -12999,7 +12999,7 @@
         <v>550839</v>
       </c>
     </row>
-    <row r="338" spans="1:5" ht="17" thickBot="1">
+    <row r="338" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A338" s="11">
         <v>42182</v>
       </c>
@@ -13017,7 +13017,7 @@
         <v>547969</v>
       </c>
     </row>
-    <row r="339" spans="1:5" ht="17" thickBot="1">
+    <row r="339" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A339" s="11">
         <v>42189</v>
       </c>
@@ -13035,7 +13035,7 @@
         <v>506284</v>
       </c>
     </row>
-    <row r="340" spans="1:5" ht="17" thickBot="1">
+    <row r="340" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A340" s="11">
         <v>42196</v>
       </c>
@@ -13053,7 +13053,7 @@
         <v>534097</v>
       </c>
     </row>
-    <row r="341" spans="1:5" ht="17" thickBot="1">
+    <row r="341" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A341" s="11">
         <v>42203</v>
       </c>
@@ -13071,7 +13071,7 @@
         <v>551181</v>
       </c>
     </row>
-    <row r="342" spans="1:5" ht="17" thickBot="1">
+    <row r="342" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A342" s="11">
         <v>42210</v>
       </c>
@@ -13089,7 +13089,7 @@
         <v>557612</v>
       </c>
     </row>
-    <row r="343" spans="1:5" ht="17" thickBot="1">
+    <row r="343" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A343" s="11">
         <v>42217</v>
       </c>
@@ -13107,7 +13107,7 @@
         <v>559125</v>
       </c>
     </row>
-    <row r="344" spans="1:5" ht="17" thickBot="1">
+    <row r="344" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A344" s="11">
         <v>42224</v>
       </c>
@@ -13125,7 +13125,7 @@
         <v>562884</v>
       </c>
     </row>
-    <row r="345" spans="1:5" ht="17" thickBot="1">
+    <row r="345" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A345" s="11">
         <v>42238</v>
       </c>
@@ -13143,7 +13143,7 @@
         <v>567943</v>
       </c>
     </row>
-    <row r="346" spans="1:5" ht="17" thickBot="1">
+    <row r="346" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A346" s="11">
         <v>42245</v>
       </c>
@@ -13161,7 +13161,7 @@
         <v>575323</v>
       </c>
     </row>
-    <row r="347" spans="1:5" ht="17" thickBot="1">
+    <row r="347" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A347" s="11">
         <v>42252</v>
       </c>
@@ -13179,7 +13179,7 @@
         <v>567206</v>
       </c>
     </row>
-    <row r="348" spans="1:5" ht="17" thickBot="1">
+    <row r="348" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A348" s="11">
         <v>42259</v>
       </c>
@@ -13197,7 +13197,7 @@
         <v>510797</v>
       </c>
     </row>
-    <row r="349" spans="1:5" ht="17" thickBot="1">
+    <row r="349" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A349" s="11">
         <v>42266</v>
       </c>
@@ -13215,7 +13215,7 @@
         <v>566734</v>
       </c>
     </row>
-    <row r="350" spans="1:5" ht="17" thickBot="1">
+    <row r="350" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A350" s="11">
         <v>42273</v>
       </c>
@@ -13233,7 +13233,7 @@
         <v>566700</v>
       </c>
     </row>
-    <row r="351" spans="1:5" ht="17" thickBot="1">
+    <row r="351" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A351" s="13">
         <v>42280</v>
       </c>
@@ -13251,7 +13251,7 @@
         <v>572293</v>
       </c>
     </row>
-    <row r="352" spans="1:5" ht="17" thickBot="1">
+    <row r="352" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A352" s="11">
         <v>42287</v>
       </c>
@@ -13269,7 +13269,7 @@
         <v>556233</v>
       </c>
     </row>
-    <row r="353" spans="1:5" ht="17" thickBot="1">
+    <row r="353" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A353" s="11">
         <v>42294</v>
       </c>
@@ -13287,7 +13287,7 @@
         <v>554696</v>
       </c>
     </row>
-    <row r="354" spans="1:5" ht="17" thickBot="1">
+    <row r="354" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A354" s="11">
         <v>42301</v>
       </c>
@@ -13305,7 +13305,7 @@
         <v>553144</v>
       </c>
     </row>
-    <row r="355" spans="1:5" ht="17" thickBot="1">
+    <row r="355" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A355" s="11">
         <v>42308</v>
       </c>
@@ -13323,7 +13323,7 @@
         <v>549707</v>
       </c>
     </row>
-    <row r="356" spans="1:5" ht="17" thickBot="1">
+    <row r="356" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A356" s="11">
         <v>42315</v>
       </c>
@@ -13341,7 +13341,7 @@
         <v>539165</v>
       </c>
     </row>
-    <row r="357" spans="1:5" ht="17" thickBot="1">
+    <row r="357" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A357" s="11">
         <v>42322</v>
       </c>
@@ -13359,7 +13359,7 @@
         <v>543681</v>
       </c>
     </row>
-    <row r="358" spans="1:5" ht="17" thickBot="1">
+    <row r="358" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A358" s="11">
         <v>42336</v>
       </c>
@@ -13377,7 +13377,7 @@
         <v>450389</v>
       </c>
     </row>
-    <row r="359" spans="1:5" ht="17" thickBot="1">
+    <row r="359" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A359" s="11">
         <v>42343</v>
       </c>
@@ -13395,7 +13395,7 @@
         <v>542050</v>
       </c>
     </row>
-    <row r="360" spans="1:5" ht="17" thickBot="1">
+    <row r="360" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A360" s="11">
         <v>42350</v>
       </c>
@@ -13413,7 +13413,7 @@
         <v>544975</v>
       </c>
     </row>
-    <row r="361" spans="1:5" ht="17" thickBot="1">
+    <row r="361" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A361" s="11">
         <v>42357</v>
       </c>
@@ -13431,7 +13431,7 @@
         <v>525555</v>
       </c>
     </row>
-    <row r="362" spans="1:5" ht="17" thickBot="1">
+    <row r="362" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A362" s="11">
         <v>42364</v>
       </c>
@@ -13449,7 +13449,7 @@
         <v>391107</v>
       </c>
     </row>
-    <row r="363" spans="1:5" ht="17" thickBot="1">
+    <row r="363" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A363" s="11">
         <v>42371</v>
       </c>
@@ -13467,7 +13467,7 @@
         <v>395663</v>
       </c>
     </row>
-    <row r="364" spans="1:5" ht="17" thickBot="1">
+    <row r="364" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A364" s="11">
         <v>42378</v>
       </c>
@@ -13485,7 +13485,7 @@
         <v>498160</v>
       </c>
     </row>
-    <row r="365" spans="1:5" ht="17" thickBot="1">
+    <row r="365" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A365" s="11">
         <v>42385</v>
       </c>
@@ -13503,7 +13503,7 @@
         <v>506433</v>
       </c>
     </row>
-    <row r="366" spans="1:5" ht="17" thickBot="1">
+    <row r="366" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A366" s="11">
         <v>42392</v>
       </c>
@@ -13521,7 +13521,7 @@
         <v>490324</v>
       </c>
     </row>
-    <row r="367" spans="1:5" ht="17" thickBot="1">
+    <row r="367" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A367" s="11">
         <v>42399</v>
       </c>
@@ -13539,7 +13539,7 @@
         <v>512746</v>
       </c>
     </row>
-    <row r="368" spans="1:5" ht="17" thickBot="1">
+    <row r="368" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A368" s="11">
         <v>42406</v>
       </c>
@@ -13557,7 +13557,7 @@
         <v>504510</v>
       </c>
     </row>
-    <row r="369" spans="1:5" ht="17" thickBot="1">
+    <row r="369" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A369" s="11">
         <v>42413</v>
       </c>
@@ -13575,7 +13575,7 @@
         <v>505148</v>
       </c>
     </row>
-    <row r="370" spans="1:5" ht="17" thickBot="1">
+    <row r="370" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A370" s="11">
         <v>42420</v>
       </c>
@@ -13593,7 +13593,7 @@
         <v>497210</v>
       </c>
     </row>
-    <row r="371" spans="1:5" ht="17" thickBot="1">
+    <row r="371" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A371" s="11">
         <v>42427</v>
       </c>
@@ -13611,7 +13611,7 @@
         <v>521300</v>
       </c>
     </row>
-    <row r="372" spans="1:5" ht="17" thickBot="1">
+    <row r="372" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A372" s="11">
         <v>42434</v>
       </c>
@@ -13629,7 +13629,7 @@
         <v>512202</v>
       </c>
     </row>
-    <row r="373" spans="1:5" ht="17" thickBot="1">
+    <row r="373" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A373" s="11">
         <v>42441</v>
       </c>
@@ -13647,7 +13647,7 @@
         <v>489177</v>
       </c>
     </row>
-    <row r="374" spans="1:5" ht="17" thickBot="1">
+    <row r="374" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A374" s="11">
         <v>42448</v>
       </c>
@@ -13665,7 +13665,7 @@
         <v>483463</v>
       </c>
     </row>
-    <row r="375" spans="1:5" ht="17" thickBot="1">
+    <row r="375" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A375" s="11">
         <v>42455</v>
       </c>
@@ -13683,7 +13683,7 @@
         <v>470271</v>
       </c>
     </row>
-    <row r="376" spans="1:5" ht="17" thickBot="1">
+    <row r="376" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A376" s="13">
         <v>42462</v>
       </c>
@@ -13701,7 +13701,7 @@
         <v>491979</v>
       </c>
     </row>
-    <row r="377" spans="1:5" ht="17" thickBot="1">
+    <row r="377" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A377" s="11">
         <v>42469</v>
       </c>
@@ -13719,7 +13719,7 @@
         <v>479059</v>
       </c>
     </row>
-    <row r="378" spans="1:5" ht="17" thickBot="1">
+    <row r="378" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A378" s="11">
         <v>42476</v>
       </c>
@@ -13737,7 +13737,7 @@
         <v>499779</v>
       </c>
     </row>
-    <row r="379" spans="1:5" ht="17" thickBot="1">
+    <row r="379" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A379" s="11">
         <v>42483</v>
       </c>
@@ -13755,7 +13755,7 @@
         <v>491946</v>
       </c>
     </row>
-    <row r="380" spans="1:5" ht="17" thickBot="1">
+    <row r="380" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A380" s="11">
         <v>42490</v>
       </c>
@@ -13773,7 +13773,7 @@
         <v>502045</v>
       </c>
     </row>
-    <row r="381" spans="1:5" ht="17" thickBot="1">
+    <row r="381" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A381" s="11">
         <v>42497</v>
       </c>
@@ -13791,7 +13791,7 @@
         <v>492923</v>
       </c>
     </row>
-    <row r="382" spans="1:5" ht="17" thickBot="1">
+    <row r="382" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A382" s="11">
         <v>42504</v>
       </c>
@@ -13809,7 +13809,7 @@
         <v>498379</v>
       </c>
     </row>
-    <row r="383" spans="1:5" ht="17" thickBot="1">
+    <row r="383" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A383" s="11">
         <v>42511</v>
       </c>
@@ -13827,7 +13827,7 @@
         <v>506983</v>
       </c>
     </row>
-    <row r="384" spans="1:5" ht="17" thickBot="1">
+    <row r="384" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A384" s="11">
         <v>42518</v>
       </c>
@@ -13845,7 +13845,7 @@
         <v>513917</v>
       </c>
     </row>
-    <row r="385" spans="1:5" ht="17" thickBot="1">
+    <row r="385" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A385" s="11">
         <v>42525</v>
       </c>
@@ -13863,7 +13863,7 @@
         <v>455346</v>
       </c>
     </row>
-    <row r="386" spans="1:5" ht="17" thickBot="1">
+    <row r="386" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A386" s="11">
         <v>42532</v>
       </c>
@@ -13896,7 +13896,7 @@
         <v>513471</v>
       </c>
     </row>
-    <row r="387" spans="1:5" ht="17" thickBot="1">
+    <row r="387" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A387" s="11">
         <v>42539</v>
       </c>
@@ -13914,7 +13914,7 @@
         <v>516096</v>
       </c>
     </row>
-    <row r="388" spans="1:5" ht="17" thickBot="1">
+    <row r="388" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A388" s="11">
         <v>42546</v>
       </c>
@@ -13932,7 +13932,7 @@
         <v>526161</v>
       </c>
     </row>
-    <row r="389" spans="1:5" ht="17" thickBot="1">
+    <row r="389" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A389" s="11">
         <v>42553</v>
       </c>
@@ -13950,7 +13950,7 @@
         <v>529191</v>
       </c>
     </row>
-    <row r="390" spans="1:5" ht="17" thickBot="1">
+    <row r="390" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A390" s="11">
         <v>42560</v>
       </c>
@@ -13968,7 +13968,7 @@
         <v>442113</v>
       </c>
     </row>
-    <row r="391" spans="1:5" ht="17" thickBot="1">
+    <row r="391" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A391" s="11">
         <v>42567</v>
       </c>
@@ -13986,7 +13986,7 @@
         <v>520222</v>
       </c>
     </row>
-    <row r="392" spans="1:5" ht="17" thickBot="1">
+    <row r="392" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A392" s="11">
         <v>42574</v>
       </c>
@@ -14004,7 +14004,7 @@
         <v>528070</v>
       </c>
     </row>
-    <row r="393" spans="1:5" ht="17" thickBot="1">
+    <row r="393" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A393" s="11">
         <v>42581</v>
       </c>
@@ -14022,7 +14022,7 @@
         <v>536916</v>
       </c>
     </row>
-    <row r="394" spans="1:5" ht="17" thickBot="1">
+    <row r="394" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A394" s="11">
         <v>42588</v>
       </c>
@@ -14040,7 +14040,7 @@
         <v>531595</v>
       </c>
     </row>
-    <row r="395" spans="1:5" ht="17" thickBot="1">
+    <row r="395" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A395" s="11">
         <v>42595</v>
       </c>
@@ -14058,7 +14058,7 @@
         <v>534533</v>
       </c>
     </row>
-    <row r="396" spans="1:5" ht="17" thickBot="1">
+    <row r="396" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A396" s="11">
         <v>42602</v>
       </c>
@@ -14076,7 +14076,7 @@
         <v>531484</v>
       </c>
     </row>
-    <row r="397" spans="1:5" ht="17" thickBot="1">
+    <row r="397" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A397" s="11">
         <v>42609</v>
       </c>
@@ -14094,7 +14094,7 @@
         <v>539657</v>
       </c>
     </row>
-    <row r="398" spans="1:5" ht="17" thickBot="1">
+    <row r="398" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A398" s="11">
         <v>42616</v>
       </c>
@@ -14112,7 +14112,7 @@
         <v>538826</v>
       </c>
     </row>
-    <row r="399" spans="1:5" ht="17" thickBot="1">
+    <row r="399" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A399" s="11">
         <v>42623</v>
       </c>
@@ -14130,7 +14130,7 @@
         <v>482894</v>
       </c>
     </row>
-    <row r="400" spans="1:5" ht="17" thickBot="1">
+    <row r="400" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A400" s="11">
         <v>42630</v>
       </c>
@@ -14148,7 +14148,7 @@
         <v>537904</v>
       </c>
     </row>
-    <row r="401" spans="1:5" ht="17" thickBot="1">
+    <row r="401" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A401" s="13">
         <v>42637</v>
       </c>
@@ -14166,7 +14166,7 @@
         <v>539609</v>
       </c>
     </row>
-    <row r="402" spans="1:5" ht="17" thickBot="1">
+    <row r="402" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A402" s="11">
         <v>42644</v>
       </c>
@@ -14184,7 +14184,7 @@
         <v>549171</v>
       </c>
     </row>
-    <row r="403" spans="1:5" ht="17" thickBot="1">
+    <row r="403" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A403" s="11">
         <v>42651</v>
       </c>
@@ -14202,7 +14202,7 @@
         <v>521789</v>
       </c>
     </row>
-    <row r="404" spans="1:5" ht="17" thickBot="1">
+    <row r="404" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A404" s="11">
         <v>42658</v>
       </c>
@@ -14220,7 +14220,7 @@
         <v>531936</v>
       </c>
     </row>
-    <row r="405" spans="1:5" ht="17" thickBot="1">
+    <row r="405" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A405" s="11">
         <v>42665</v>
       </c>
@@ -14238,7 +14238,7 @@
         <v>544092</v>
       </c>
     </row>
-    <row r="406" spans="1:5" ht="17" thickBot="1">
+    <row r="406" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A406" s="11">
         <v>42672</v>
       </c>
@@ -14256,7 +14256,7 @@
         <v>544997</v>
       </c>
     </row>
-    <row r="407" spans="1:5" ht="17" thickBot="1">
+    <row r="407" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A407" s="11">
         <v>42679</v>
       </c>
@@ -14274,7 +14274,7 @@
         <v>543377</v>
       </c>
     </row>
-    <row r="408" spans="1:5" ht="17" thickBot="1">
+    <row r="408" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A408" s="11">
         <v>42686</v>
       </c>
@@ -14292,7 +14292,7 @@
         <v>541127</v>
       </c>
     </row>
-    <row r="409" spans="1:5" ht="17" thickBot="1">
+    <row r="409" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A409" s="11">
         <v>42693</v>
       </c>
@@ -14310,7 +14310,7 @@
         <v>547804</v>
       </c>
     </row>
-    <row r="410" spans="1:5" ht="17" thickBot="1">
+    <row r="410" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A410" s="11">
         <v>42700</v>
       </c>
@@ -14328,7 +14328,7 @@
         <v>452759</v>
       </c>
     </row>
-    <row r="411" spans="1:5" ht="17" thickBot="1">
+    <row r="411" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A411" s="11">
         <v>42707</v>
       </c>
@@ -14346,7 +14346,7 @@
         <v>553130</v>
       </c>
     </row>
-    <row r="412" spans="1:5" ht="17" thickBot="1">
+    <row r="412" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A412" s="11">
         <v>42714</v>
       </c>
@@ -14364,7 +14364,7 @@
         <v>538932</v>
       </c>
     </row>
-    <row r="413" spans="1:5" ht="17" thickBot="1">
+    <row r="413" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A413" s="11">
         <v>42721</v>
       </c>
@@ -14382,7 +14382,7 @@
         <v>523949</v>
       </c>
     </row>
-    <row r="414" spans="1:5" ht="17" thickBot="1">
+    <row r="414" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A414" s="11">
         <v>42728</v>
       </c>
@@ -14400,7 +14400,7 @@
         <v>496633</v>
       </c>
     </row>
-    <row r="415" spans="1:5" ht="17" thickBot="1">
+    <row r="415" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A415" s="11">
         <v>42735</v>
       </c>
@@ -14418,7 +14418,7 @@
         <v>425998</v>
       </c>
     </row>
-    <row r="416" spans="1:5" ht="17" thickBot="1">
+    <row r="416" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A416" s="11">
         <v>42742</v>
       </c>
@@ -14436,7 +14436,7 @@
         <v>441417</v>
       </c>
     </row>
-    <row r="417" spans="1:5" ht="17" thickBot="1">
+    <row r="417" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A417" s="11">
         <v>42749</v>
       </c>
@@ -14454,7 +14454,7 @@
         <v>516229</v>
       </c>
     </row>
-    <row r="418" spans="1:5" ht="17" thickBot="1">
+    <row r="418" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A418" s="11">
         <v>42756</v>
       </c>
@@ -14472,7 +14472,7 @@
         <v>530299</v>
       </c>
     </row>
-    <row r="419" spans="1:5" ht="17" thickBot="1">
+    <row r="419" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A419" s="11">
         <v>42763</v>
       </c>
@@ -14490,7 +14490,7 @@
         <v>529696</v>
       </c>
     </row>
-    <row r="420" spans="1:5" ht="17" thickBot="1">
+    <row r="420" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A420" s="11">
         <v>42770</v>
       </c>
@@ -14508,7 +14508,7 @@
         <v>541474</v>
       </c>
     </row>
-    <row r="421" spans="1:5" ht="17" thickBot="1">
+    <row r="421" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A421" s="11">
         <v>42777</v>
       </c>
@@ -14526,7 +14526,7 @@
         <v>518431</v>
       </c>
     </row>
-    <row r="422" spans="1:5" ht="17" thickBot="1">
+    <row r="422" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A422" s="11">
         <v>42784</v>
       </c>
@@ -14544,7 +14544,7 @@
         <v>531123</v>
       </c>
     </row>
-    <row r="423" spans="1:5" ht="17" thickBot="1">
+    <row r="423" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A423" s="11">
         <v>42791</v>
       </c>
@@ -14562,7 +14562,7 @@
         <v>521451</v>
       </c>
     </row>
-    <row r="424" spans="1:5" ht="17" thickBot="1">
+    <row r="424" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A424" s="11">
         <v>42798</v>
       </c>
@@ -14580,7 +14580,7 @@
         <v>521607</v>
       </c>
     </row>
-    <row r="425" spans="1:5" ht="17" thickBot="1">
+    <row r="425" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A425" s="11">
         <v>42805</v>
       </c>
@@ -14598,7 +14598,7 @@
         <v>510638</v>
       </c>
     </row>
-    <row r="426" spans="1:5" ht="17" thickBot="1">
+    <row r="426" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A426" s="13">
         <v>42812</v>
       </c>
@@ -14616,7 +14616,7 @@
         <v>495281</v>
       </c>
     </row>
-    <row r="427" spans="1:5" ht="17" thickBot="1">
+    <row r="427" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A427" s="11">
         <v>42819</v>
       </c>
@@ -14634,7 +14634,7 @@
         <v>526471</v>
       </c>
     </row>
-    <row r="428" spans="1:5" ht="17" thickBot="1">
+    <row r="428" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A428" s="11">
         <v>42826</v>
       </c>
@@ -14652,7 +14652,7 @@
         <v>527665</v>
       </c>
     </row>
-    <row r="429" spans="1:5" ht="17" thickBot="1">
+    <row r="429" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A429" s="11">
         <v>42833</v>
       </c>
@@ -14670,7 +14670,7 @@
         <v>513022</v>
       </c>
     </row>
-    <row r="430" spans="1:5" ht="17" thickBot="1">
+    <row r="430" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A430" s="11">
         <v>42840</v>
       </c>
@@ -14688,7 +14688,7 @@
         <v>519318</v>
       </c>
     </row>
-    <row r="431" spans="1:5" ht="17" thickBot="1">
+    <row r="431" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A431" s="11">
         <v>42847</v>
       </c>
@@ -14706,7 +14706,7 @@
         <v>515131</v>
       </c>
     </row>
-    <row r="432" spans="1:5" ht="17" thickBot="1">
+    <row r="432" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A432" s="11">
         <v>42854</v>
       </c>
@@ -14724,7 +14724,7 @@
         <v>527830</v>
       </c>
     </row>
-    <row r="433" spans="1:5" ht="17" thickBot="1">
+    <row r="433" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A433" s="11">
         <v>42861</v>
       </c>
@@ -14742,7 +14742,7 @@
         <v>515305</v>
       </c>
     </row>
-    <row r="434" spans="1:5" ht="17" thickBot="1">
+    <row r="434" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A434" s="11">
         <v>42868</v>
       </c>
@@ -14760,7 +14760,7 @@
         <v>526970</v>
       </c>
     </row>
-    <row r="435" spans="1:5" ht="17" thickBot="1">
+    <row r="435" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A435" s="11">
         <v>42875</v>
       </c>
@@ -14778,7 +14778,7 @@
         <v>534922</v>
       </c>
     </row>
-    <row r="436" spans="1:5" ht="17" thickBot="1">
+    <row r="436" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A436" s="11">
         <v>42882</v>
       </c>
@@ -14796,7 +14796,7 @@
         <v>548103</v>
       </c>
     </row>
-    <row r="437" spans="1:5" ht="17" thickBot="1">
+    <row r="437" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A437" s="11">
         <v>42889</v>
       </c>
@@ -14814,7 +14814,7 @@
         <v>500192</v>
       </c>
     </row>
-    <row r="438" spans="1:5" ht="17" thickBot="1">
+    <row r="438" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A438" s="11">
         <v>42896</v>
       </c>
@@ -14832,7 +14832,7 @@
         <v>545317</v>
       </c>
     </row>
-    <row r="439" spans="1:5" ht="17" thickBot="1">
+    <row r="439" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A439" s="11">
         <v>42903</v>
       </c>
@@ -14850,7 +14850,7 @@
         <v>543179</v>
       </c>
     </row>
-    <row r="440" spans="1:5" ht="17" thickBot="1">
+    <row r="440" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A440" s="11">
         <v>42910</v>
       </c>
@@ -14868,7 +14868,7 @@
         <v>544694</v>
       </c>
     </row>
-    <row r="441" spans="1:5" ht="17" thickBot="1">
+    <row r="441" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A441" s="11">
         <v>42917</v>
       </c>
@@ -14886,7 +14886,7 @@
         <v>546361</v>
       </c>
     </row>
-    <row r="442" spans="1:5" ht="17" thickBot="1">
+    <row r="442" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A442" s="11">
         <v>42924</v>
       </c>
@@ -14904,7 +14904,7 @@
         <v>453080</v>
       </c>
     </row>
-    <row r="443" spans="1:5" ht="17" thickBot="1">
+    <row r="443" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A443" s="11">
         <v>42931</v>
       </c>
@@ -14922,7 +14922,7 @@
         <v>540005</v>
       </c>
     </row>
-    <row r="444" spans="1:5" ht="17" thickBot="1">
+    <row r="444" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A444" s="11">
         <v>42938</v>
       </c>
@@ -14940,7 +14940,7 @@
         <v>534152</v>
       </c>
     </row>
-    <row r="445" spans="1:5" ht="17" thickBot="1">
+    <row r="445" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A445" s="11">
         <v>42945</v>
       </c>
@@ -14958,7 +14958,7 @@
         <v>550356</v>
       </c>
     </row>
-    <row r="446" spans="1:5" ht="17" thickBot="1">
+    <row r="446" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A446" s="11">
         <v>42952</v>
       </c>
@@ -14976,7 +14976,7 @@
         <v>554822</v>
       </c>
     </row>
-    <row r="447" spans="1:5" ht="17" thickBot="1">
+    <row r="447" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A447" s="11">
         <v>42959</v>
       </c>
@@ -14994,7 +14994,7 @@
         <v>548790</v>
       </c>
     </row>
-    <row r="448" spans="1:5" ht="17" thickBot="1">
+    <row r="448" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A448" s="11">
         <v>42966</v>
       </c>
@@ -15012,7 +15012,7 @@
         <v>554021</v>
       </c>
     </row>
-    <row r="449" spans="1:5" ht="17" thickBot="1">
+    <row r="449" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A449" s="11">
         <v>42973</v>
       </c>
@@ -15030,7 +15030,7 @@
         <v>551776</v>
       </c>
     </row>
-    <row r="450" spans="1:5" ht="17" thickBot="1">
+    <row r="450" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A450" s="11">
         <v>42980</v>
       </c>
@@ -15063,7 +15063,7 @@
         <v>534140</v>
       </c>
     </row>
-    <row r="451" spans="1:5" ht="17" thickBot="1">
+    <row r="451" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A451" s="13">
         <v>42987</v>
       </c>
@@ -15081,7 +15081,7 @@
         <v>486474</v>
       </c>
     </row>
-    <row r="452" spans="1:5" ht="17" thickBot="1">
+    <row r="452" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A452" s="11">
         <v>42994</v>
       </c>
@@ -15099,7 +15099,7 @@
         <v>530774</v>
       </c>
     </row>
-    <row r="453" spans="1:5" ht="17" thickBot="1">
+    <row r="453" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A453" s="11">
         <v>43001</v>
       </c>
@@ -15117,7 +15117,7 @@
         <v>548204</v>
       </c>
     </row>
-    <row r="454" spans="1:5" ht="17" thickBot="1">
+    <row r="454" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A454" s="11">
         <v>43008</v>
       </c>
@@ -15135,7 +15135,7 @@
         <v>559555</v>
       </c>
     </row>
-    <row r="455" spans="1:5" ht="17" thickBot="1">
+    <row r="455" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A455" s="11">
         <v>43015</v>
       </c>
@@ -15153,7 +15153,7 @@
         <v>554826</v>
       </c>
     </row>
-    <row r="456" spans="1:5" ht="17" thickBot="1">
+    <row r="456" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A456" s="11">
         <v>43022</v>
       </c>
@@ -15171,7 +15171,7 @@
         <v>548264</v>
       </c>
     </row>
-    <row r="457" spans="1:5" ht="17" thickBot="1">
+    <row r="457" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A457" s="11">
         <v>43029</v>
       </c>
@@ -15189,7 +15189,7 @@
         <v>559989</v>
       </c>
     </row>
-    <row r="458" spans="1:5" ht="17" thickBot="1">
+    <row r="458" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A458" s="11">
         <v>43036</v>
       </c>
@@ -15207,7 +15207,7 @@
         <v>546582</v>
       </c>
     </row>
-    <row r="459" spans="1:5" ht="17" thickBot="1">
+    <row r="459" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A459" s="11">
         <v>43043</v>
       </c>
@@ -15225,7 +15225,7 @@
         <v>538739</v>
       </c>
     </row>
-    <row r="460" spans="1:5" ht="17" thickBot="1">
+    <row r="460" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A460" s="11">
         <v>43050</v>
       </c>
@@ -15243,7 +15243,7 @@
         <v>547480</v>
       </c>
     </row>
-    <row r="461" spans="1:5" ht="17" thickBot="1">
+    <row r="461" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A461" s="11">
         <v>43057</v>
       </c>
@@ -15261,7 +15261,7 @@
         <v>554066</v>
       </c>
     </row>
-    <row r="462" spans="1:5" ht="17" thickBot="1">
+    <row r="462" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A462" s="11">
         <v>43064</v>
       </c>
@@ -15279,7 +15279,7 @@
         <v>463602</v>
       </c>
     </row>
-    <row r="463" spans="1:5" ht="17" thickBot="1">
+    <row r="463" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A463" s="11">
         <v>43071</v>
       </c>
@@ -15297,7 +15297,7 @@
         <v>572794</v>
       </c>
     </row>
-    <row r="464" spans="1:5" ht="17" thickBot="1">
+    <row r="464" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A464" s="11">
         <v>43078</v>
       </c>
@@ -15315,7 +15315,7 @@
         <v>560756</v>
       </c>
     </row>
-    <row r="465" spans="1:5" ht="17" thickBot="1">
+    <row r="465" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A465" s="11">
         <v>43085</v>
       </c>
@@ -15333,7 +15333,7 @@
         <v>554779</v>
       </c>
     </row>
-    <row r="466" spans="1:5" ht="17" thickBot="1">
+    <row r="466" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A466" s="11">
         <v>43092</v>
       </c>
@@ -15351,7 +15351,7 @@
         <v>551566</v>
       </c>
     </row>
-    <row r="467" spans="1:5" ht="17" thickBot="1">
+    <row r="467" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A467" s="11">
         <v>43099</v>
       </c>
@@ -15369,7 +15369,7 @@
         <v>397032</v>
       </c>
     </row>
-    <row r="468" spans="1:5" ht="17" thickBot="1">
+    <row r="468" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A468" s="11">
         <v>43113</v>
       </c>
@@ -15387,7 +15387,7 @@
         <v>511937</v>
       </c>
     </row>
-    <row r="469" spans="1:5" ht="17" thickBot="1">
+    <row r="469" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A469" s="11">
         <v>43120</v>
       </c>
@@ -15405,7 +15405,7 @@
         <v>508239</v>
       </c>
     </row>
-    <row r="470" spans="1:5" ht="17" thickBot="1">
+    <row r="470" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A470" s="11">
         <v>43127</v>
       </c>
@@ -15423,7 +15423,7 @@
         <v>543515</v>
       </c>
     </row>
-    <row r="471" spans="1:5" ht="17" thickBot="1">
+    <row r="471" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A471" s="11">
         <v>43134</v>
       </c>
@@ -15441,7 +15441,7 @@
         <v>547993</v>
       </c>
     </row>
-    <row r="472" spans="1:5" ht="17" thickBot="1">
+    <row r="472" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A472" s="11">
         <v>43141</v>
       </c>
@@ -15459,7 +15459,7 @@
         <v>519545</v>
       </c>
     </row>
-    <row r="473" spans="1:5" ht="17" thickBot="1">
+    <row r="473" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A473" s="11">
         <v>43148</v>
       </c>
@@ -15477,7 +15477,7 @@
         <v>539963</v>
       </c>
     </row>
-    <row r="474" spans="1:5" ht="17" thickBot="1">
+    <row r="474" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A474" s="11">
         <v>43155</v>
       </c>
@@ -15495,7 +15495,7 @@
         <v>528440</v>
       </c>
     </row>
-    <row r="475" spans="1:5" ht="17" thickBot="1">
+    <row r="475" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A475" s="11">
         <v>43162</v>
       </c>
@@ -15513,7 +15513,7 @@
         <v>544194</v>
       </c>
     </row>
-    <row r="476" spans="1:5" ht="17" thickBot="1">
+    <row r="476" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A476" s="13">
         <v>43169</v>
       </c>
@@ -15531,7 +15531,7 @@
         <v>534282</v>
       </c>
     </row>
-    <row r="477" spans="1:5" ht="17" thickBot="1">
+    <row r="477" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A477" s="11">
         <v>43176</v>
       </c>
@@ -15549,7 +15549,7 @@
         <v>537338</v>
       </c>
     </row>
-    <row r="478" spans="1:5" ht="17" thickBot="1">
+    <row r="478" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A478" s="11">
         <v>43183</v>
       </c>
@@ -15567,7 +15567,7 @@
         <v>526521</v>
       </c>
     </row>
-    <row r="479" spans="1:5" ht="17" thickBot="1">
+    <row r="479" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A479" s="11">
         <v>43190</v>
       </c>
@@ -15585,7 +15585,7 @@
         <v>534751</v>
       </c>
     </row>
-    <row r="480" spans="1:5" ht="17" thickBot="1">
+    <row r="480" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A480" s="11">
         <v>43197</v>
       </c>
@@ -15603,7 +15603,7 @@
         <v>524905</v>
       </c>
     </row>
-    <row r="481" spans="1:5" ht="17" thickBot="1">
+    <row r="481" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A481" s="11">
         <v>43204</v>
       </c>
@@ -15621,7 +15621,7 @@
         <v>534198</v>
       </c>
     </row>
-    <row r="482" spans="1:5" ht="17" thickBot="1">
+    <row r="482" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A482" s="11">
         <v>43211</v>
       </c>
@@ -15639,7 +15639,7 @@
         <v>539425</v>
       </c>
     </row>
-    <row r="483" spans="1:5" ht="17" thickBot="1">
+    <row r="483" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A483" s="11">
         <v>43218</v>
       </c>
@@ -15657,7 +15657,7 @@
         <v>551498</v>
       </c>
     </row>
-    <row r="484" spans="1:5" ht="17" thickBot="1">
+    <row r="484" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A484" s="11">
         <v>43225</v>
       </c>
@@ -15675,7 +15675,7 @@
         <v>545937</v>
       </c>
     </row>
-    <row r="485" spans="1:5" ht="17" thickBot="1">
+    <row r="485" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A485" s="11">
         <v>43232</v>
       </c>
@@ -15693,7 +15693,7 @@
         <v>550029</v>
       </c>
     </row>
-    <row r="486" spans="1:5" ht="17" thickBot="1">
+    <row r="486" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A486" s="11">
         <v>43239</v>
       </c>
@@ -15711,7 +15711,7 @@
         <v>546415</v>
       </c>
     </row>
-    <row r="487" spans="1:5" ht="17" thickBot="1">
+    <row r="487" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A487" s="11">
         <v>43246</v>
       </c>
@@ -15729,7 +15729,7 @@
         <v>565502</v>
       </c>
     </row>
-    <row r="488" spans="1:5" ht="17" thickBot="1">
+    <row r="488" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A488" s="11">
         <v>43253</v>
       </c>
@@ -15747,7 +15747,7 @@
         <v>509740</v>
       </c>
     </row>
-    <row r="489" spans="1:5" ht="17" thickBot="1">
+    <row r="489" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A489" s="11">
         <v>43260</v>
       </c>
@@ -15765,7 +15765,7 @@
         <v>561061</v>
       </c>
     </row>
-    <row r="490" spans="1:5" ht="17" thickBot="1">
+    <row r="490" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A490" s="11">
         <v>43267</v>
       </c>
@@ -15783,7 +15783,7 @@
         <v>558098</v>
       </c>
     </row>
-    <row r="491" spans="1:5" ht="17" thickBot="1">
+    <row r="491" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A491" s="11">
         <v>43274</v>
       </c>
@@ -15801,7 +15801,7 @@
         <v>557340</v>
       </c>
     </row>
-    <row r="492" spans="1:5" ht="17" thickBot="1">
+    <row r="492" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A492" s="11">
         <v>43281</v>
       </c>
@@ -15819,7 +15819,7 @@
         <v>564243</v>
       </c>
     </row>
-    <row r="493" spans="1:5" ht="17" thickBot="1">
+    <row r="493" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A493" s="11">
         <v>43288</v>
       </c>
@@ -15837,7 +15837,7 @@
         <v>485193</v>
       </c>
     </row>
-    <row r="494" spans="1:5" ht="17" thickBot="1">
+    <row r="494" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A494" s="11">
         <v>43295</v>
       </c>
@@ -15855,7 +15855,7 @@
         <v>559064</v>
       </c>
     </row>
-    <row r="495" spans="1:5" ht="17" thickBot="1">
+    <row r="495" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A495" s="11">
         <v>43302</v>
       </c>
@@ -15873,7 +15873,7 @@
         <v>553024</v>
       </c>
     </row>
-    <row r="496" spans="1:5" ht="17" thickBot="1">
+    <row r="496" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A496" s="11">
         <v>43309</v>
       </c>
@@ -15891,7 +15891,7 @@
         <v>559154</v>
       </c>
     </row>
-    <row r="497" spans="1:5" ht="17" thickBot="1">
+    <row r="497" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A497" s="11">
         <v>43316</v>
       </c>
@@ -15909,7 +15909,7 @@
         <v>570995</v>
       </c>
     </row>
-    <row r="498" spans="1:5" ht="17" thickBot="1">
+    <row r="498" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A498" s="11">
         <v>43323</v>
       </c>
@@ -15927,7 +15927,7 @@
         <v>556887</v>
       </c>
     </row>
-    <row r="499" spans="1:5" ht="17" thickBot="1">
+    <row r="499" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A499" s="11">
         <v>43330</v>
       </c>
@@ -15945,7 +15945,7 @@
         <v>567477</v>
       </c>
     </row>
-    <row r="500" spans="1:5" ht="17" thickBot="1">
+    <row r="500" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A500" s="11">
         <v>43337</v>
       </c>
@@ -15963,7 +15963,7 @@
         <v>565706</v>
       </c>
     </row>
-    <row r="501" spans="1:5" ht="17" thickBot="1">
+    <row r="501" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A501" s="13">
         <v>43344</v>
       </c>
@@ -15981,7 +15981,7 @@
         <v>567881</v>
       </c>
     </row>
-    <row r="502" spans="1:5" ht="17" thickBot="1">
+    <row r="502" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A502" s="11">
         <v>43351</v>
       </c>
@@ -15999,7 +15999,7 @@
         <v>502208</v>
       </c>
     </row>
-    <row r="503" spans="1:5" ht="17" thickBot="1">
+    <row r="503" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A503" s="11">
         <v>43358</v>
       </c>
@@ -16017,7 +16017,7 @@
         <v>553003</v>
       </c>
     </row>
-    <row r="504" spans="1:5" ht="17" thickBot="1">
+    <row r="504" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A504" s="11">
         <v>43365</v>
       </c>
@@ -16035,7 +16035,7 @@
         <v>567078</v>
       </c>
     </row>
-    <row r="505" spans="1:5" ht="17" thickBot="1">
+    <row r="505" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A505" s="11">
         <v>43372</v>
       </c>
@@ -16053,7 +16053,7 @@
         <v>571922</v>
       </c>
     </row>
-    <row r="506" spans="1:5" ht="17" thickBot="1">
+    <row r="506" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A506" s="11">
         <v>43379</v>
       </c>
@@ -16071,7 +16071,7 @@
         <v>554238</v>
       </c>
     </row>
-    <row r="507" spans="1:5" ht="17" thickBot="1">
+    <row r="507" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A507" s="11">
         <v>43386</v>
       </c>
@@ -16089,7 +16089,7 @@
         <v>549757</v>
       </c>
     </row>
-    <row r="508" spans="1:5" ht="17" thickBot="1">
+    <row r="508" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A508" s="11">
         <v>43393</v>
       </c>
@@ -16107,7 +16107,7 @@
         <v>555106</v>
       </c>
     </row>
-    <row r="509" spans="1:5" ht="17" thickBot="1">
+    <row r="509" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A509" s="11">
         <v>43400</v>
       </c>
@@ -16125,7 +16125,7 @@
         <v>562804</v>
       </c>
     </row>
-    <row r="510" spans="1:5" ht="17" thickBot="1">
+    <row r="510" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A510" s="11">
         <v>43407</v>
       </c>
@@ -16143,7 +16143,7 @@
         <v>560046</v>
       </c>
     </row>
-    <row r="511" spans="1:5" ht="17" thickBot="1">
+    <row r="511" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A511" s="11">
         <v>43414</v>
       </c>
@@ -16161,7 +16161,7 @@
         <v>547236</v>
       </c>
     </row>
-    <row r="512" spans="1:5" ht="17" thickBot="1">
+    <row r="512" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A512" s="11">
         <v>43421</v>
       </c>
@@ -16179,7 +16179,7 @@
         <v>546541</v>
       </c>
     </row>
-    <row r="513" spans="1:5" ht="17" thickBot="1">
+    <row r="513" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A513" s="11">
         <v>43428</v>
       </c>
@@ -16197,7 +16197,7 @@
         <v>470851</v>
       </c>
     </row>
-    <row r="514" spans="1:5" ht="17" thickBot="1">
+    <row r="514" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A514" s="11">
         <v>43435</v>
       </c>
@@ -16230,7 +16230,7 @@
         <v>567282</v>
       </c>
     </row>
-    <row r="515" spans="1:5" ht="17" thickBot="1">
+    <row r="515" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A515" s="11">
         <v>43442</v>
       </c>
@@ -16248,7 +16248,7 @@
         <v>570225</v>
       </c>
     </row>
-    <row r="516" spans="1:5" ht="17" thickBot="1">
+    <row r="516" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A516" s="11">
         <v>43449</v>
       </c>
@@ -16266,7 +16266,7 @@
         <v>568941</v>
       </c>
     </row>
-    <row r="517" spans="1:5" ht="17" thickBot="1">
+    <row r="517" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A517" s="11">
         <v>43456</v>
       </c>
@@ -16284,7 +16284,7 @@
         <v>567252</v>
       </c>
     </row>
-    <row r="518" spans="1:5" ht="17" thickBot="1">
+    <row r="518" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A518" s="11">
         <v>43463</v>
       </c>
@@ -16302,7 +16302,7 @@
         <v>411676</v>
       </c>
     </row>
-    <row r="519" spans="1:5" ht="17" thickBot="1">
+    <row r="519" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A519" s="11">
         <v>43470</v>
       </c>
@@ -16320,7 +16320,7 @@
         <v>436103</v>
       </c>
     </row>
-    <row r="520" spans="1:5" ht="17" thickBot="1">
+    <row r="520" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A520" s="11">
         <v>43477</v>
       </c>
@@ -16338,7 +16338,7 @@
         <v>555127</v>
       </c>
     </row>
-    <row r="521" spans="1:5" ht="17" thickBot="1">
+    <row r="521" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A521" s="11">
         <v>43484</v>
       </c>
@@ -16356,7 +16356,7 @@
         <v>543111</v>
       </c>
     </row>
-    <row r="522" spans="1:5" ht="17" thickBot="1">
+    <row r="522" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A522" s="11">
         <v>43491</v>
       </c>
@@ -16374,7 +16374,7 @@
         <v>522026</v>
       </c>
     </row>
-    <row r="523" spans="1:5" ht="17" thickBot="1">
+    <row r="523" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A523" s="11">
         <v>43498</v>
       </c>
@@ -16392,7 +16392,7 @@
         <v>498288</v>
       </c>
     </row>
-    <row r="524" spans="1:5" ht="17" thickBot="1">
+    <row r="524" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A524" s="11">
         <v>43505</v>
       </c>
@@ -16410,7 +16410,7 @@
         <v>519779</v>
       </c>
     </row>
-    <row r="525" spans="1:5" ht="17" thickBot="1">
+    <row r="525" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A525" s="11">
         <v>43512</v>
       </c>
@@ -16428,7 +16428,7 @@
         <v>523915</v>
       </c>
     </row>
-    <row r="526" spans="1:5" ht="17" thickBot="1">
+    <row r="526" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A526" s="13">
         <v>43519</v>
       </c>
@@ -16446,7 +16446,7 @@
         <v>522630</v>
       </c>
     </row>
-    <row r="527" spans="1:5" ht="17" thickBot="1">
+    <row r="527" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A527" s="11">
         <v>43526</v>
       </c>
@@ -16464,7 +16464,7 @@
         <v>528153</v>
       </c>
     </row>
-    <row r="528" spans="1:5" ht="17" thickBot="1">
+    <row r="528" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A528" s="11">
         <v>43533</v>
       </c>
@@ -16482,7 +16482,7 @@
         <v>508958</v>
       </c>
     </row>
-    <row r="529" spans="1:5" ht="17" thickBot="1">
+    <row r="529" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A529" s="11">
         <v>43540</v>
       </c>
@@ -16500,7 +16500,7 @@
         <v>501001</v>
       </c>
     </row>
-    <row r="530" spans="1:5" ht="17" thickBot="1">
+    <row r="530" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A530" s="11">
         <v>43547</v>
       </c>
@@ -16518,7 +16518,7 @@
         <v>503017</v>
       </c>
     </row>
-    <row r="531" spans="1:5" ht="17" thickBot="1">
+    <row r="531" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A531" s="11">
         <v>43554</v>
       </c>
@@ -16536,7 +16536,7 @@
         <v>509958</v>
       </c>
     </row>
-    <row r="532" spans="1:5" ht="17" thickBot="1">
+    <row r="532" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A532" s="11">
         <v>43561</v>
       </c>
@@ -16554,7 +16554,7 @@
         <v>510192</v>
       </c>
     </row>
-    <row r="533" spans="1:5" ht="17" thickBot="1">
+    <row r="533" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A533" s="11">
         <v>43568</v>
       </c>
@@ -16572,7 +16572,7 @@
         <v>528167</v>
       </c>
     </row>
-    <row r="534" spans="1:5" ht="17" thickBot="1">
+    <row r="534" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A534" s="11">
         <v>43575</v>
       </c>
@@ -16590,7 +16590,7 @@
         <v>526141</v>
       </c>
     </row>
-    <row r="535" spans="1:5" ht="17" thickBot="1">
+    <row r="535" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A535" s="11">
         <v>43582</v>
       </c>
@@ -16608,7 +16608,7 @@
         <v>533190</v>
       </c>
     </row>
-    <row r="536" spans="1:5" ht="17" thickBot="1">
+    <row r="536" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A536" s="11">
         <v>43589</v>
       </c>
@@ -16626,7 +16626,7 @@
         <v>535089</v>
       </c>
     </row>
-    <row r="537" spans="1:5" ht="17" thickBot="1">
+    <row r="537" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A537" s="11">
         <v>43596</v>
       </c>
@@ -16644,7 +16644,7 @@
         <v>529263</v>
       </c>
     </row>
-    <row r="538" spans="1:5" ht="17" thickBot="1">
+    <row r="538" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A538" s="11">
         <v>43603</v>
       </c>
@@ -16662,7 +16662,7 @@
         <v>536358</v>
       </c>
     </row>
-    <row r="539" spans="1:5" ht="17" thickBot="1">
+    <row r="539" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A539" s="11">
         <v>43610</v>
       </c>
@@ -16680,7 +16680,7 @@
         <v>527966</v>
       </c>
     </row>
-    <row r="540" spans="1:5" ht="17" thickBot="1">
+    <row r="540" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A540" s="11">
         <v>43617</v>
       </c>
@@ -16698,7 +16698,7 @@
         <v>478679</v>
       </c>
     </row>
-    <row r="541" spans="1:5" ht="17" thickBot="1">
+    <row r="541" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A541" s="11">
         <v>43624</v>
       </c>
@@ -16716,7 +16716,7 @@
         <v>513099</v>
       </c>
     </row>
-    <row r="542" spans="1:5" ht="17" thickBot="1">
+    <row r="542" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A542" s="11">
         <v>43631</v>
       </c>
@@ -16734,7 +16734,7 @@
         <v>527989</v>
       </c>
     </row>
-    <row r="543" spans="1:5" ht="17" thickBot="1">
+    <row r="543" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A543" s="11">
         <v>43638</v>
       </c>
@@ -16752,7 +16752,7 @@
         <v>525116</v>
       </c>
     </row>
-    <row r="544" spans="1:5" ht="17" thickBot="1">
+    <row r="544" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A544" s="11">
         <v>43645</v>
       </c>
@@ -16770,7 +16770,7 @@
         <v>533164</v>
       </c>
     </row>
-    <row r="545" spans="1:5" ht="17" thickBot="1">
+    <row r="545" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A545" s="11">
         <v>43652</v>
       </c>
@@ -16788,7 +16788,7 @@
         <v>448459</v>
       </c>
     </row>
-    <row r="546" spans="1:5" ht="17" thickBot="1">
+    <row r="546" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A546" s="11">
         <v>43659</v>
       </c>
@@ -16806,7 +16806,7 @@
         <v>527908</v>
       </c>
     </row>
-    <row r="547" spans="1:5" ht="17" thickBot="1">
+    <row r="547" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A547" s="11">
         <v>43666</v>
       </c>
@@ -16824,7 +16824,7 @@
         <v>526010</v>
       </c>
     </row>
-    <row r="548" spans="1:5" ht="17" thickBot="1">
+    <row r="548" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A548" s="11">
         <v>43673</v>
       </c>
@@ -16842,7 +16842,7 @@
         <v>534498</v>
       </c>
     </row>
-    <row r="549" spans="1:5" ht="17" thickBot="1">
+    <row r="549" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A549" s="11">
         <v>43680</v>
       </c>
@@ -16860,7 +16860,7 @@
         <v>541558</v>
       </c>
     </row>
-    <row r="550" spans="1:5" ht="17" thickBot="1">
+    <row r="550" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A550" s="11">
         <v>43687</v>
       </c>
@@ -16878,7 +16878,7 @@
         <v>533190</v>
       </c>
     </row>
-    <row r="551" spans="1:5" ht="17" thickBot="1">
+    <row r="551" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A551" s="13">
         <v>43694</v>
       </c>
@@ -16896,7 +16896,7 @@
         <v>537617</v>
       </c>
     </row>
-    <row r="552" spans="1:5" ht="17" thickBot="1">
+    <row r="552" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A552" s="11">
         <v>43701</v>
       </c>
@@ -16914,7 +16914,7 @@
         <v>532483</v>
       </c>
     </row>
-    <row r="553" spans="1:5" ht="17" thickBot="1">
+    <row r="553" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A553" s="11">
         <v>43708</v>
       </c>
@@ -16932,7 +16932,7 @@
         <v>541945</v>
       </c>
     </row>
-    <row r="554" spans="1:5" ht="17" thickBot="1">
+    <row r="554" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A554" s="11">
         <v>43715</v>
       </c>
@@ -16950,7 +16950,7 @@
         <v>469285</v>
       </c>
     </row>
-    <row r="555" spans="1:5" ht="17" thickBot="1">
+    <row r="555" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A555" s="11">
         <v>43722</v>
       </c>
@@ -16968,7 +16968,7 @@
         <v>526734</v>
       </c>
     </row>
-    <row r="556" spans="1:5" ht="17" thickBot="1">
+    <row r="556" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A556" s="11">
         <v>43729</v>
       </c>
@@ -16986,7 +16986,7 @@
         <v>528670</v>
       </c>
     </row>
-    <row r="557" spans="1:5" ht="17" thickBot="1">
+    <row r="557" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A557" s="11">
         <v>43736</v>
       </c>
@@ -17004,7 +17004,7 @@
         <v>529336</v>
       </c>
     </row>
-    <row r="558" spans="1:5" ht="17" thickBot="1">
+    <row r="558" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A558" s="11">
         <v>43743</v>
       </c>
@@ -17022,7 +17022,7 @@
         <v>515061</v>
       </c>
     </row>
-    <row r="559" spans="1:5" ht="17" thickBot="1">
+    <row r="559" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A559" s="11">
         <v>43750</v>
       </c>
@@ -17040,7 +17040,7 @@
         <v>510820</v>
       </c>
     </row>
-    <row r="560" spans="1:5" ht="17" thickBot="1">
+    <row r="560" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A560" s="11">
         <v>43757</v>
       </c>
@@ -17058,7 +17058,7 @@
         <v>507381</v>
       </c>
     </row>
-    <row r="561" spans="1:5" ht="17" thickBot="1">
+    <row r="561" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A561" s="11">
         <v>43764</v>
       </c>
@@ -17076,7 +17076,7 @@
         <v>513147</v>
       </c>
     </row>
-    <row r="562" spans="1:5" ht="17" thickBot="1">
+    <row r="562" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A562" s="11">
         <v>43771</v>
       </c>
@@ -17094,7 +17094,7 @@
         <v>510012</v>
       </c>
     </row>
-    <row r="563" spans="1:5" ht="17" thickBot="1">
+    <row r="563" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A563" s="11">
         <v>43778</v>
       </c>
@@ -17112,7 +17112,7 @@
         <v>515269</v>
       </c>
     </row>
-    <row r="564" spans="1:5" ht="17" thickBot="1">
+    <row r="564" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A564" s="11">
         <v>43785</v>
       </c>
@@ -17130,7 +17130,7 @@
         <v>501249</v>
       </c>
     </row>
-    <row r="565" spans="1:5" ht="17" thickBot="1">
+    <row r="565" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A565" s="11">
         <v>43792</v>
       </c>
@@ -17148,7 +17148,7 @@
         <v>521927</v>
       </c>
     </row>
-    <row r="566" spans="1:5" ht="17" thickBot="1">
+    <row r="566" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A566" s="11">
         <v>43813</v>
       </c>
@@ -17166,7 +17166,7 @@
         <v>520589</v>
       </c>
     </row>
-    <row r="567" spans="1:5" ht="17" thickBot="1">
+    <row r="567" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A567" s="11">
         <v>43820</v>
       </c>
@@ -17184,7 +17184,7 @@
         <v>507589</v>
       </c>
     </row>
-    <row r="568" spans="1:5" ht="17" thickBot="1">
+    <row r="568" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A568" s="11">
         <v>43827</v>
       </c>
@@ -17202,7 +17202,7 @@
         <v>373728</v>
       </c>
     </row>
-    <row r="569" spans="1:5" ht="17" thickBot="1">
+    <row r="569" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A569" s="11">
         <v>43834</v>
       </c>
@@ -17220,7 +17220,7 @@
         <v>414014</v>
       </c>
     </row>
-    <row r="570" spans="1:5" ht="17" thickBot="1">
+    <row r="570" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A570" s="11">
         <v>43841</v>
       </c>
@@ -17238,7 +17238,7 @@
         <v>501624</v>
       </c>
     </row>
-    <row r="571" spans="1:5" ht="17" thickBot="1">
+    <row r="571" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A571" s="11">
         <v>43848</v>
       </c>
@@ -17256,7 +17256,7 @@
         <v>499732</v>
       </c>
     </row>
-    <row r="572" spans="1:5" ht="17" thickBot="1">
+    <row r="572" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A572" s="11">
         <v>43855</v>
       </c>
@@ -17274,7 +17274,7 @@
         <v>485282</v>
       </c>
     </row>
-    <row r="573" spans="1:5" ht="17" thickBot="1">
+    <row r="573" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A573" s="11">
         <v>43862</v>
       </c>
@@ -17292,7 +17292,7 @@
         <v>510161</v>
       </c>
     </row>
-    <row r="574" spans="1:5" ht="17" thickBot="1">
+    <row r="574" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A574" s="11">
         <v>43869</v>
       </c>
@@ -17310,7 +17310,7 @@
         <v>485329</v>
       </c>
     </row>
-    <row r="575" spans="1:5" ht="17" thickBot="1">
+    <row r="575" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A575" s="11">
         <v>43876</v>
       </c>
@@ -17328,7 +17328,7 @@
         <v>479137</v>
       </c>
     </row>
-    <row r="576" spans="1:5" ht="17" thickBot="1">
+    <row r="576" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A576" s="13">
         <v>43883</v>
       </c>
@@ -17346,7 +17346,7 @@
         <v>482690</v>
       </c>
     </row>
-    <row r="577" spans="1:5" ht="17" thickBot="1">
+    <row r="577" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A577" s="11">
         <v>43890</v>
       </c>
@@ -17364,7 +17364,7 @@
         <v>477611</v>
       </c>
     </row>
-    <row r="578" spans="1:5" ht="17" thickBot="1">
+    <row r="578" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A578" s="11">
         <v>43897</v>
       </c>
@@ -17397,7 +17397,7 @@
         <v>462303</v>
       </c>
     </row>
-    <row r="579" spans="1:5" ht="17" thickBot="1">
+    <row r="579" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A579" s="11">
         <v>43904</v>
       </c>
@@ -17415,7 +17415,7 @@
         <v>463017</v>
       </c>
     </row>
-    <row r="580" spans="1:5" ht="17" thickBot="1">
+    <row r="580" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A580" s="11">
         <v>43911</v>
       </c>
@@ -17433,7 +17433,7 @@
         <v>459966</v>
       </c>
     </row>
-    <row r="581" spans="1:5" ht="17" thickBot="1">
+    <row r="581" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A581" s="11">
         <v>43918</v>
       </c>
@@ -17451,7 +17451,7 @@
         <v>449767</v>
       </c>
     </row>
-    <row r="582" spans="1:5" ht="17" thickBot="1">
+    <row r="582" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A582" s="11">
         <v>43925</v>
       </c>
@@ -17469,7 +17469,7 @@
         <v>429095</v>
       </c>
     </row>
-    <row r="583" spans="1:5" ht="17" thickBot="1">
+    <row r="583" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A583" s="11">
         <v>43932</v>
       </c>
@@ -17487,7 +17487,7 @@
         <v>412503</v>
       </c>
     </row>
-    <row r="584" spans="1:5" ht="17" thickBot="1">
+    <row r="584" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A584" s="11">
         <v>43939</v>
       </c>
@@ -17505,7 +17505,7 @@
         <v>403283</v>
       </c>
     </row>
-    <row r="585" spans="1:5" ht="17" thickBot="1">
+    <row r="585" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A585" s="11">
         <v>43946</v>
       </c>
@@ -17523,7 +17523,7 @@
         <v>414123</v>
       </c>
     </row>
-    <row r="586" spans="1:5" ht="17" thickBot="1">
+    <row r="586" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A586" s="11">
         <v>43953</v>
       </c>
@@ -17541,7 +17541,7 @@
         <v>416954</v>
       </c>
     </row>
-    <row r="587" spans="1:5" ht="17" thickBot="1">
+    <row r="587" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A587" s="11">
         <v>43960</v>
       </c>
@@ -17559,7 +17559,7 @@
         <v>412549</v>
       </c>
     </row>
-    <row r="588" spans="1:5" ht="17" thickBot="1">
+    <row r="588" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A588" s="11">
         <v>43967</v>
       </c>
@@ -17577,7 +17577,7 @@
         <v>416115</v>
       </c>
     </row>
-    <row r="589" spans="1:5" ht="17" thickBot="1">
+    <row r="589" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A589" s="11">
         <v>43974</v>
       </c>
@@ -17595,7 +17595,7 @@
         <v>428715</v>
       </c>
     </row>
-    <row r="590" spans="1:5" ht="17" thickBot="1">
+    <row r="590" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A590" s="11">
         <v>43981</v>
       </c>
@@ -17613,7 +17613,7 @@
         <v>395714</v>
       </c>
     </row>
-    <row r="591" spans="1:5" ht="17" thickBot="1">
+    <row r="591" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A591" s="11">
         <v>43988</v>
       </c>
@@ -17631,7 +17631,7 @@
         <v>433171</v>
       </c>
     </row>
-    <row r="592" spans="1:5" ht="17" thickBot="1">
+    <row r="592" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A592" s="11">
         <v>43995</v>
       </c>
@@ -17649,7 +17649,7 @@
         <v>449291</v>
       </c>
     </row>
-    <row r="593" spans="1:5" ht="17" thickBot="1">
+    <row r="593" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A593" s="11">
         <v>44002</v>
       </c>
@@ -17667,7 +17667,7 @@
         <v>457278</v>
       </c>
     </row>
-    <row r="594" spans="1:5" ht="17" thickBot="1">
+    <row r="594" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A594" s="11">
         <v>44009</v>
       </c>
@@ -17685,7 +17685,7 @@
         <v>459449</v>
       </c>
     </row>
-    <row r="595" spans="1:5" ht="17" thickBot="1">
+    <row r="595" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A595" s="11">
         <v>44016</v>
       </c>
@@ -17703,7 +17703,7 @@
         <v>437989</v>
       </c>
     </row>
-    <row r="596" spans="1:5" ht="17" thickBot="1">
+    <row r="596" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A596" s="11">
         <v>44023</v>
       </c>
@@ -17721,7 +17721,7 @@
         <v>449092</v>
       </c>
     </row>
-    <row r="597" spans="1:5" ht="17" thickBot="1">
+    <row r="597" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A597" s="11">
         <v>44030</v>
       </c>
@@ -17739,7 +17739,7 @@
         <v>481597</v>
       </c>
     </row>
-    <row r="598" spans="1:5" ht="17" thickBot="1">
+    <row r="598" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A598" s="11">
         <v>44037</v>
       </c>
@@ -17757,7 +17757,7 @@
         <v>481331</v>
       </c>
     </row>
-    <row r="599" spans="1:5" ht="17" thickBot="1">
+    <row r="599" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A599" s="11">
         <v>44044</v>
       </c>
@@ -17775,7 +17775,7 @@
         <v>487968</v>
       </c>
     </row>
-    <row r="600" spans="1:5" ht="17" thickBot="1">
+    <row r="600" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A600" s="11">
         <v>44051</v>
       </c>
@@ -17793,7 +17793,7 @@
         <v>497397</v>
       </c>
     </row>
-    <row r="601" spans="1:5" ht="17" thickBot="1">
+    <row r="601" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A601" s="13">
         <v>44058</v>
       </c>
@@ -17811,7 +17811,7 @@
         <v>500563</v>
       </c>
     </row>
-    <row r="602" spans="1:5" ht="17" thickBot="1">
+    <row r="602" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A602" s="11">
         <v>44072</v>
       </c>
@@ -17829,7 +17829,7 @@
         <v>508307</v>
       </c>
     </row>
-    <row r="603" spans="1:5" ht="17" thickBot="1">
+    <row r="603" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A603" s="11">
         <v>44079</v>
       </c>
@@ -17847,7 +17847,7 @@
         <v>509637</v>
       </c>
     </row>
-    <row r="604" spans="1:5" ht="17" thickBot="1">
+    <row r="604" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A604" s="11">
         <v>44086</v>
       </c>
@@ -17865,7 +17865,7 @@
         <v>474785</v>
       </c>
     </row>
-    <row r="605" spans="1:5" ht="17" thickBot="1">
+    <row r="605" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A605" s="11">
         <v>44093</v>
       </c>
@@ -17883,7 +17883,7 @@
         <v>521956</v>
       </c>
     </row>
-    <row r="606" spans="1:5" ht="17" thickBot="1">
+    <row r="606" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A606" s="11">
         <v>44100</v>
       </c>
@@ -17901,7 +17901,7 @@
         <v>518290</v>
       </c>
     </row>
-    <row r="607" spans="1:5" ht="17" thickBot="1">
+    <row r="607" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A607" s="11">
         <v>44107</v>
       </c>
@@ -17919,7 +17919,7 @@
         <v>518761</v>
       </c>
     </row>
-    <row r="608" spans="1:5" ht="17" thickBot="1">
+    <row r="608" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A608" s="11">
         <v>44114</v>
       </c>
@@ -17937,7 +17937,7 @@
         <v>520452</v>
       </c>
     </row>
-    <row r="609" spans="1:5" ht="17" thickBot="1">
+    <row r="609" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A609" s="11">
         <v>44121</v>
       </c>
@@ -17955,7 +17955,7 @@
         <v>518763</v>
       </c>
     </row>
-    <row r="610" spans="1:5" ht="17" thickBot="1">
+    <row r="610" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A610" s="11">
         <v>44128</v>
       </c>
@@ -17973,7 +17973,7 @@
         <v>522653</v>
       </c>
     </row>
-    <row r="611" spans="1:5" ht="17" thickBot="1">
+    <row r="611" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A611" s="11">
         <v>44135</v>
       </c>
@@ -17991,7 +17991,7 @@
         <v>520778</v>
       </c>
     </row>
-    <row r="612" spans="1:5" ht="17" thickBot="1">
+    <row r="612" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A612" s="11">
         <v>44142</v>
       </c>
@@ -18009,7 +18009,7 @@
         <v>522028</v>
       </c>
     </row>
-    <row r="613" spans="1:5" ht="17" thickBot="1">
+    <row r="613" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A613" s="11">
         <v>44149</v>
       </c>
@@ -18027,7 +18027,7 @@
         <v>527462</v>
       </c>
     </row>
-    <row r="614" spans="1:5" ht="17" thickBot="1">
+    <row r="614" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A614" s="11">
         <v>44156</v>
       </c>
@@ -18045,7 +18045,7 @@
         <v>534607</v>
       </c>
     </row>
-    <row r="615" spans="1:5" ht="17" thickBot="1">
+    <row r="615" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A615" s="11">
         <v>44163</v>
       </c>
@@ -18063,7 +18063,7 @@
         <v>452792</v>
       </c>
     </row>
-    <row r="616" spans="1:5" ht="17" thickBot="1">
+    <row r="616" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A616" s="11">
         <v>44170</v>
       </c>
@@ -18081,7 +18081,7 @@
         <v>542203</v>
       </c>
     </row>
-    <row r="617" spans="1:5" ht="17" thickBot="1">
+    <row r="617" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A617" s="11">
         <v>44177</v>
       </c>
@@ -18099,7 +18099,7 @@
         <v>546209</v>
       </c>
     </row>
-    <row r="618" spans="1:5" ht="17" thickBot="1">
+    <row r="618" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A618" s="11">
         <v>44191</v>
       </c>
@@ -18117,7 +18117,7 @@
         <v>405111</v>
       </c>
     </row>
-    <row r="619" spans="1:5" ht="17" thickBot="1">
+    <row r="619" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A619" s="11">
         <v>44198</v>
       </c>
@@ -18135,7 +18135,7 @@
         <v>421991</v>
       </c>
     </row>
-    <row r="620" spans="1:5" ht="17" thickBot="1">
+    <row r="620" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A620" s="11">
         <v>44205</v>
       </c>
@@ -18153,7 +18153,7 @@
         <v>525253</v>
       </c>
     </row>
-    <row r="621" spans="1:5" ht="17" thickBot="1">
+    <row r="621" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A621" s="11">
         <v>44212</v>
       </c>
@@ -18171,7 +18171,7 @@
         <v>528547</v>
       </c>
     </row>
-    <row r="622" spans="1:5" ht="17" thickBot="1">
+    <row r="622" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A622" s="11">
         <v>44219</v>
       </c>
@@ -18189,7 +18189,7 @@
         <v>529030</v>
       </c>
     </row>
-    <row r="623" spans="1:5" ht="17" thickBot="1">
+    <row r="623" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A623" s="11">
         <v>44226</v>
       </c>
@@ -18207,7 +18207,7 @@
         <v>520693</v>
       </c>
     </row>
-    <row r="624" spans="1:5" ht="17" thickBot="1">
+    <row r="624" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A624" s="11">
         <v>44233</v>
       </c>
@@ -18225,7 +18225,7 @@
         <v>495815</v>
       </c>
     </row>
-    <row r="625" spans="1:5" ht="17" thickBot="1">
+    <row r="625" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A625" s="11">
         <v>44240</v>
       </c>
@@ -18243,7 +18243,7 @@
         <v>480483</v>
       </c>
     </row>
-    <row r="626" spans="1:5" ht="17" thickBot="1">
+    <row r="626" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A626" s="13">
         <v>44247</v>
       </c>
@@ -18261,7 +18261,7 @@
         <v>377904</v>
       </c>
     </row>
-    <row r="627" spans="1:5" ht="17" thickBot="1">
+    <row r="627" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A627" s="11">
         <v>44254</v>
       </c>
@@ -18279,7 +18279,7 @@
         <v>486429</v>
       </c>
     </row>
-    <row r="628" spans="1:5" ht="17" thickBot="1">
+    <row r="628" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A628" s="11">
         <v>44261</v>
       </c>
@@ -18297,7 +18297,7 @@
         <v>515135</v>
       </c>
     </row>
-    <row r="629" spans="1:5" ht="17" thickBot="1">
+    <row r="629" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A629" s="11">
         <v>44268</v>
       </c>
@@ -18315,7 +18315,7 @@
         <v>520736</v>
       </c>
     </row>
-    <row r="630" spans="1:5" ht="17" thickBot="1">
+    <row r="630" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A630" s="11">
         <v>44275</v>
       </c>
@@ -18333,7 +18333,7 @@
         <v>513325</v>
       </c>
     </row>
-    <row r="631" spans="1:5" ht="17" thickBot="1">
+    <row r="631" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A631" s="11">
         <v>44282</v>
       </c>
@@ -18351,7 +18351,7 @@
         <v>521731</v>
       </c>
     </row>
-    <row r="632" spans="1:5" ht="17" thickBot="1">
+    <row r="632" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A632" s="11">
         <v>44289</v>
       </c>
@@ -18369,7 +18369,7 @@
         <v>515562</v>
       </c>
     </row>
-    <row r="633" spans="1:5" ht="17" thickBot="1">
+    <row r="633" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A633" s="11">
         <v>44296</v>
       </c>
@@ -18387,7 +18387,7 @@
         <v>513724</v>
       </c>
     </row>
-    <row r="634" spans="1:5" ht="17" thickBot="1">
+    <row r="634" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A634" s="11">
         <v>44303</v>
       </c>
@@ -18405,7 +18405,7 @@
         <v>533217</v>
       </c>
     </row>
-    <row r="635" spans="1:5" ht="17" thickBot="1">
+    <row r="635" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A635" s="11">
         <v>44310</v>
       </c>
@@ -18423,7 +18423,7 @@
         <v>538184</v>
       </c>
     </row>
-    <row r="636" spans="1:5" ht="17" thickBot="1">
+    <row r="636" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A636" s="11">
         <v>44317</v>
       </c>
@@ -18441,7 +18441,7 @@
         <v>540667</v>
       </c>
     </row>
-    <row r="637" spans="1:5" ht="17" thickBot="1">
+    <row r="637" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A637" s="11">
         <v>44324</v>
       </c>
@@ -18459,7 +18459,7 @@
         <v>523309</v>
       </c>
     </row>
-    <row r="638" spans="1:5" ht="17" thickBot="1">
+    <row r="638" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A638" s="11">
         <v>44331</v>
       </c>
@@ -18477,7 +18477,7 @@
         <v>533872</v>
       </c>
     </row>
-    <row r="639" spans="1:5" ht="17" thickBot="1">
+    <row r="639" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A639" s="11">
         <v>44338</v>
       </c>
@@ -18495,7 +18495,7 @@
         <v>528774</v>
       </c>
     </row>
-    <row r="640" spans="1:5" ht="17" thickBot="1">
+    <row r="640" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A640" s="11">
         <v>44345</v>
       </c>
@@ -18513,7 +18513,7 @@
         <v>530225</v>
       </c>
     </row>
-    <row r="641" spans="1:5" ht="17" thickBot="1">
+    <row r="641" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A641" s="11">
         <v>44352</v>
       </c>
@@ -18531,7 +18531,7 @@
         <v>489144</v>
       </c>
     </row>
-    <row r="642" spans="1:5" ht="17" thickBot="1">
+    <row r="642" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A642" s="11">
         <v>44359</v>
       </c>
@@ -18564,7 +18564,7 @@
         <v>529635</v>
       </c>
     </row>
-    <row r="643" spans="1:5" ht="17" thickBot="1">
+    <row r="643" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A643" s="11">
         <v>44366</v>
       </c>
@@ -18582,7 +18582,7 @@
         <v>514112</v>
       </c>
     </row>
-    <row r="644" spans="1:5" ht="17" thickBot="1">
+    <row r="644" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A644" s="11">
         <v>44373</v>
       </c>
@@ -18600,7 +18600,7 @@
         <v>516167</v>
       </c>
     </row>
-    <row r="645" spans="1:5" ht="17" thickBot="1">
+    <row r="645" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A645" s="11">
         <v>44380</v>
       </c>
@@ -18618,7 +18618,7 @@
         <v>512919</v>
       </c>
     </row>
-    <row r="646" spans="1:5" ht="17" thickBot="1">
+    <row r="646" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A646" s="11">
         <v>44387</v>
       </c>
@@ -18636,7 +18636,7 @@
         <v>451825</v>
       </c>
     </row>
-    <row r="647" spans="1:5" ht="17" thickBot="1">
+    <row r="647" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A647" s="11">
         <v>44394</v>
       </c>
@@ -18654,7 +18654,7 @@
         <v>513255</v>
       </c>
     </row>
-    <row r="648" spans="1:5" ht="17" thickBot="1">
+    <row r="648" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A648" s="11">
         <v>44401</v>
       </c>
@@ -18672,7 +18672,7 @@
         <v>503219</v>
       </c>
     </row>
-    <row r="649" spans="1:5" ht="17" thickBot="1">
+    <row r="649" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A649" s="11">
         <v>44408</v>
       </c>
@@ -18690,7 +18690,7 @@
         <v>502540</v>
       </c>
     </row>
-    <row r="650" spans="1:5" ht="17" thickBot="1">
+    <row r="650" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A650" s="11">
         <v>44415</v>
       </c>
@@ -18708,7 +18708,7 @@
         <v>509607</v>
       </c>
     </row>
-    <row r="651" spans="1:5" ht="17" thickBot="1">
+    <row r="651" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A651" s="13">
         <v>44422</v>
       </c>
@@ -18726,7 +18726,7 @@
         <v>504810</v>
       </c>
     </row>
-    <row r="652" spans="1:5" ht="17" thickBot="1">
+    <row r="652" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A652" s="11">
         <v>44429</v>
       </c>
@@ -18744,7 +18744,7 @@
         <v>501273</v>
       </c>
     </row>
-    <row r="653" spans="1:5" ht="17" thickBot="1">
+    <row r="653" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A653" s="11">
         <v>44436</v>
       </c>
@@ -18762,7 +18762,7 @@
         <v>504417</v>
       </c>
     </row>
-    <row r="654" spans="1:5" ht="17" thickBot="1">
+    <row r="654" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A654" s="11">
         <v>44443</v>
       </c>
@@ -18780,7 +18780,7 @@
         <v>494415</v>
       </c>
     </row>
-    <row r="655" spans="1:5" ht="17" thickBot="1">
+    <row r="655" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A655" s="11">
         <v>44450</v>
       </c>
@@ -18798,7 +18798,7 @@
         <v>468610</v>
       </c>
     </row>
-    <row r="656" spans="1:5" ht="17" thickBot="1">
+    <row r="656" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A656" s="11">
         <v>44457</v>
       </c>
@@ -18816,7 +18816,7 @@
         <v>505622</v>
       </c>
     </row>
-    <row r="657" spans="1:5" ht="17" thickBot="1">
+    <row r="657" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A657" s="11">
         <v>44464</v>
       </c>
@@ -18834,7 +18834,7 @@
         <v>511713</v>
       </c>
     </row>
-    <row r="658" spans="1:5" ht="17" thickBot="1">
+    <row r="658" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A658" s="11">
         <v>44471</v>
       </c>
@@ -18852,7 +18852,7 @@
         <v>515849</v>
       </c>
     </row>
-    <row r="659" spans="1:5" ht="17" thickBot="1">
+    <row r="659" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A659" s="11">
         <v>44478</v>
       </c>
@@ -18870,7 +18870,7 @@
         <v>506642</v>
       </c>
     </row>
-    <row r="660" spans="1:5" ht="17" thickBot="1">
+    <row r="660" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A660" s="11">
         <v>44485</v>
       </c>
@@ -18888,7 +18888,7 @@
         <v>496983</v>
       </c>
     </row>
-    <row r="661" spans="1:5" ht="17" thickBot="1">
+    <row r="661" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A661" s="11">
         <v>44492</v>
       </c>
@@ -18906,7 +18906,7 @@
         <v>510762</v>
       </c>
     </row>
-    <row r="662" spans="1:5" ht="17" thickBot="1">
+    <row r="662" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A662" s="11">
         <v>44499</v>
       </c>
@@ -18924,7 +18924,7 @@
         <v>510141</v>
       </c>
     </row>
-    <row r="663" spans="1:5" ht="17" thickBot="1">
+    <row r="663" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A663" s="11">
         <v>44506</v>
       </c>
@@ -18942,7 +18942,7 @@
         <v>504111</v>
       </c>
     </row>
-    <row r="664" spans="1:5" ht="17" thickBot="1">
+    <row r="664" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A664" s="11">
         <v>44513</v>
       </c>
@@ -18960,7 +18960,7 @@
         <v>502613</v>
       </c>
     </row>
-    <row r="665" spans="1:5" ht="17" thickBot="1">
+    <row r="665" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A665" s="11">
         <v>44520</v>
       </c>
@@ -18978,7 +18978,7 @@
         <v>508309</v>
       </c>
     </row>
-    <row r="666" spans="1:5" ht="17" thickBot="1">
+    <row r="666" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A666" s="11">
         <v>44527</v>
       </c>
@@ -18996,7 +18996,7 @@
         <v>430793</v>
       </c>
     </row>
-    <row r="667" spans="1:5" ht="17" thickBot="1">
+    <row r="667" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A667" s="11">
         <v>44534</v>
       </c>
@@ -19014,7 +19014,7 @@
         <v>527406</v>
       </c>
     </row>
-    <row r="668" spans="1:5" ht="17" thickBot="1">
+    <row r="668" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A668" s="11">
         <v>44541</v>
       </c>
@@ -19032,7 +19032,7 @@
         <v>513366</v>
       </c>
     </row>
-    <row r="669" spans="1:5" ht="17" thickBot="1">
+    <row r="669" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A669" s="11">
         <v>44548</v>
       </c>
@@ -19050,7 +19050,7 @@
         <v>504099</v>
       </c>
     </row>
-    <row r="670" spans="1:5" ht="17" thickBot="1">
+    <row r="670" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A670" s="11">
         <v>44555</v>
       </c>
@@ -19068,7 +19068,7 @@
         <v>420373</v>
       </c>
     </row>
-    <row r="671" spans="1:5" ht="17" thickBot="1">
+    <row r="671" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A671" s="11">
         <v>44562</v>
       </c>
@@ -19086,7 +19086,7 @@
         <v>395371</v>
       </c>
     </row>
-    <row r="672" spans="1:5" ht="17" thickBot="1">
+    <row r="672" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A672" s="11">
         <v>44569</v>
       </c>
@@ -19104,7 +19104,7 @@
         <v>440761</v>
       </c>
     </row>
-    <row r="673" spans="1:5" ht="17" thickBot="1">
+    <row r="673" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A673" s="11">
         <v>44576</v>
       </c>
@@ -19122,7 +19122,7 @@
         <v>493617</v>
       </c>
     </row>
-    <row r="674" spans="1:5" ht="17" thickBot="1">
+    <row r="674" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A674" s="11">
         <v>44583</v>
       </c>
@@ -19140,7 +19140,7 @@
         <v>477462</v>
       </c>
     </row>
-    <row r="675" spans="1:5" ht="17" thickBot="1">
+    <row r="675" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A675" s="11">
         <v>44590</v>
       </c>
@@ -19158,7 +19158,7 @@
         <v>491868</v>
       </c>
     </row>
-    <row r="676" spans="1:5" ht="17" thickBot="1">
+    <row r="676" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A676" s="13">
         <v>44597</v>
       </c>
@@ -19176,7 +19176,7 @@
         <v>458152</v>
       </c>
     </row>
-    <row r="677" spans="1:5" ht="17" thickBot="1">
+    <row r="677" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A677" s="11">
         <v>44604</v>
       </c>
@@ -19194,7 +19194,7 @@
         <v>504482</v>
       </c>
     </row>
-    <row r="678" spans="1:5" ht="17" thickBot="1">
+    <row r="678" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A678" s="11">
         <v>44611</v>
       </c>
@@ -19212,7 +19212,7 @@
         <v>497822</v>
       </c>
     </row>
-    <row r="679" spans="1:5" ht="17" thickBot="1">
+    <row r="679" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A679" s="11">
         <v>44625</v>
       </c>
@@ -19230,7 +19230,7 @@
         <v>505177</v>
       </c>
     </row>
-    <row r="680" spans="1:5" ht="17" thickBot="1">
+    <row r="680" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A680" s="11">
         <v>44632</v>
       </c>
@@ -19248,7 +19248,7 @@
         <v>496134</v>
       </c>
     </row>
-    <row r="681" spans="1:5" ht="17" thickBot="1">
+    <row r="681" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A681" s="11">
         <v>44639</v>
       </c>
@@ -19266,7 +19266,7 @@
         <v>499362</v>
       </c>
     </row>
-    <row r="682" spans="1:5" ht="17" thickBot="1">
+    <row r="682" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A682" s="11">
         <v>44646</v>
       </c>
@@ -19284,7 +19284,7 @@
         <v>504817</v>
       </c>
     </row>
-    <row r="683" spans="1:5" ht="17" thickBot="1">
+    <row r="683" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A683" s="11">
         <v>44653</v>
       </c>
@@ -19302,7 +19302,7 @@
         <v>502194</v>
       </c>
     </row>
-    <row r="684" spans="1:5" ht="17" thickBot="1">
+    <row r="684" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A684" s="11">
         <v>44660</v>
       </c>
@@ -19320,7 +19320,7 @@
         <v>508343</v>
       </c>
     </row>
-    <row r="685" spans="1:5" ht="17" thickBot="1">
+    <row r="685" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A685" s="11">
         <v>44667</v>
       </c>
@@ -19338,7 +19338,7 @@
         <v>489801</v>
       </c>
     </row>
-    <row r="686" spans="1:5" ht="17" thickBot="1">
+    <row r="686" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A686" s="11">
         <v>44674</v>
       </c>
@@ -19356,7 +19356,7 @@
         <v>498011</v>
       </c>
     </row>
-    <row r="687" spans="1:5" ht="17" thickBot="1">
+    <row r="687" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A687" s="11">
         <v>44681</v>
       </c>
@@ -19374,7 +19374,7 @@
         <v>506699</v>
       </c>
     </row>
-    <row r="688" spans="1:5" ht="17" thickBot="1">
+    <row r="688" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A688" s="11">
         <v>44688</v>
       </c>
@@ -19392,7 +19392,7 @@
         <v>504927</v>
       </c>
     </row>
-    <row r="689" spans="1:5" ht="17" thickBot="1">
+    <row r="689" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A689" s="11">
         <v>44695</v>
       </c>
@@ -19410,7 +19410,7 @@
         <v>505120</v>
       </c>
     </row>
-    <row r="690" spans="1:5" ht="17" thickBot="1">
+    <row r="690" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A690" s="11">
         <v>44702</v>
       </c>
@@ -19428,7 +19428,7 @@
         <v>506976</v>
       </c>
     </row>
-    <row r="691" spans="1:5" ht="17" thickBot="1">
+    <row r="691" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A691" s="11">
         <v>44709</v>
       </c>
@@ -19446,7 +19446,7 @@
         <v>514277</v>
       </c>
     </row>
-    <row r="692" spans="1:5" ht="17" thickBot="1">
+    <row r="692" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A692" s="11">
         <v>44716</v>
       </c>
@@ -19464,7 +19464,7 @@
         <v>475513</v>
       </c>
     </row>
-    <row r="693" spans="1:5" ht="17" thickBot="1">
+    <row r="693" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A693" s="11">
         <v>44723</v>
       </c>
@@ -19482,7 +19482,7 @@
         <v>510295</v>
       </c>
     </row>
-    <row r="694" spans="1:5" ht="17" thickBot="1">
+    <row r="694" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A694" s="11">
         <v>44730</v>
       </c>
@@ -19500,7 +19500,7 @@
         <v>501207</v>
       </c>
     </row>
-    <row r="695" spans="1:5" ht="17" thickBot="1">
+    <row r="695" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A695" s="11">
         <v>44737</v>
       </c>
@@ -19518,7 +19518,7 @@
         <v>493374</v>
       </c>
     </row>
-    <row r="696" spans="1:5" ht="17" thickBot="1">
+    <row r="696" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A696" s="11">
         <v>44744</v>
       </c>
@@ -19536,7 +19536,7 @@
         <v>500285</v>
       </c>
     </row>
-    <row r="697" spans="1:5" ht="17" thickBot="1">
+    <row r="697" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A697" s="11">
         <v>44751</v>
       </c>
@@ -19554,7 +19554,7 @@
         <v>437600</v>
       </c>
     </row>
-    <row r="698" spans="1:5" ht="17" thickBot="1">
+    <row r="698" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A698" s="11">
         <v>44758</v>
       </c>
@@ -19572,7 +19572,7 @@
         <v>498899</v>
       </c>
     </row>
-    <row r="699" spans="1:5" ht="17" thickBot="1">
+    <row r="699" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A699" s="11">
         <v>44765</v>
       </c>
@@ -19590,7 +19590,7 @@
         <v>498901</v>
       </c>
     </row>
-    <row r="700" spans="1:5" ht="17" thickBot="1">
+    <row r="700" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A700" s="11">
         <v>44772</v>
       </c>
@@ -19608,7 +19608,7 @@
         <v>505409</v>
       </c>
     </row>
-    <row r="701" spans="1:5" ht="17" thickBot="1">
+    <row r="701" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A701" s="13">
         <v>44779</v>
       </c>
@@ -19626,7 +19626,7 @@
         <v>496526</v>
       </c>
     </row>
-    <row r="702" spans="1:5" ht="17" thickBot="1">
+    <row r="702" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A702" s="11">
         <v>44786</v>
       </c>
@@ -19644,7 +19644,7 @@
         <v>502775</v>
       </c>
     </row>
-    <row r="703" spans="1:5" ht="17" thickBot="1">
+    <row r="703" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A703" s="11">
         <v>44793</v>
       </c>
@@ -19662,7 +19662,7 @@
         <v>501548</v>
       </c>
     </row>
-    <row r="704" spans="1:5" ht="17" thickBot="1">
+    <row r="704" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A704" s="11">
         <v>44800</v>
       </c>
@@ -19680,7 +19680,7 @@
         <v>511574</v>
       </c>
     </row>
-    <row r="705" spans="1:5" ht="17" thickBot="1">
+    <row r="705" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A705" s="11">
         <v>44807</v>
       </c>
@@ -19698,7 +19698,7 @@
         <v>513087</v>
       </c>
     </row>
-    <row r="706" spans="1:5" ht="17" thickBot="1">
+    <row r="706" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A706" s="11">
         <v>44814</v>
       </c>
@@ -19731,7 +19731,7 @@
         <v>464261</v>
       </c>
     </row>
-    <row r="707" spans="1:5" ht="17" thickBot="1">
+    <row r="707" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A707" s="11">
         <v>44821</v>
       </c>
@@ -19749,7 +19749,7 @@
         <v>490654</v>
       </c>
     </row>
-    <row r="708" spans="1:5" ht="17" thickBot="1">
+    <row r="708" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A708" s="11">
         <v>44828</v>
       </c>
@@ -19767,7 +19767,7 @@
         <v>489111</v>
       </c>
     </row>
-    <row r="709" spans="1:5" ht="17" thickBot="1">
+    <row r="709" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A709" s="11">
         <v>44835</v>
       </c>
@@ -19785,7 +19785,7 @@
         <v>495868</v>
       </c>
     </row>
-    <row r="710" spans="1:5" ht="17" thickBot="1">
+    <row r="710" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A710" s="11">
         <v>44842</v>
       </c>
@@ -19803,7 +19803,7 @@
         <v>494413</v>
       </c>
     </row>
-    <row r="711" spans="1:5" ht="17" thickBot="1">
+    <row r="711" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A711" s="11">
         <v>44849</v>
       </c>
@@ -19821,7 +19821,7 @@
         <v>500304</v>
       </c>
     </row>
-    <row r="712" spans="1:5" ht="17" thickBot="1">
+    <row r="712" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A712" s="11">
         <v>44856</v>
       </c>
@@ -19839,7 +19839,7 @@
         <v>505322</v>
       </c>
     </row>
-    <row r="713" spans="1:5" ht="17" thickBot="1">
+    <row r="713" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A713" s="11">
         <v>44863</v>
       </c>
@@ -19857,7 +19857,7 @@
         <v>514457</v>
       </c>
     </row>
-    <row r="714" spans="1:5" ht="17" thickBot="1">
+    <row r="714" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A714" s="11">
         <v>44870</v>
       </c>
@@ -19875,7 +19875,7 @@
         <v>502106</v>
       </c>
     </row>
-    <row r="715" spans="1:5" ht="17" thickBot="1">
+    <row r="715" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A715" s="11">
         <v>44877</v>
       </c>
@@ -19893,7 +19893,7 @@
         <v>490350</v>
       </c>
     </row>
-    <row r="716" spans="1:5" ht="17" thickBot="1">
+    <row r="716" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A716" s="11">
         <v>44884</v>
       </c>
@@ -19911,7 +19911,7 @@
         <v>491794</v>
       </c>
     </row>
-    <row r="717" spans="1:5" ht="17" thickBot="1">
+    <row r="717" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A717" s="11">
         <v>44891</v>
       </c>
@@ -19929,7 +19929,7 @@
         <v>413305</v>
       </c>
     </row>
-    <row r="718" spans="1:5" ht="17" thickBot="1">
+    <row r="718" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A718" s="11">
         <v>44898</v>
       </c>
@@ -19947,7 +19947,7 @@
         <v>495472</v>
       </c>
     </row>
-    <row r="719" spans="1:5" ht="17" thickBot="1">
+    <row r="719" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A719" s="11">
         <v>44905</v>
       </c>
@@ -19965,7 +19965,7 @@
         <v>500310</v>
       </c>
     </row>
-    <row r="720" spans="1:5" ht="17" thickBot="1">
+    <row r="720" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A720" s="11">
         <v>44912</v>
       </c>
@@ -19983,7 +19983,7 @@
         <v>476232</v>
       </c>
     </row>
-    <row r="721" spans="1:5" ht="17" thickBot="1">
+    <row r="721" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A721" s="11">
         <v>44919</v>
       </c>
@@ -20001,7 +20001,7 @@
         <v>400289</v>
       </c>
     </row>
-    <row r="722" spans="1:5" ht="17" thickBot="1">
+    <row r="722" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A722" s="11">
         <v>44926</v>
       </c>
@@ -20019,7 +20019,7 @@
         <v>365553</v>
       </c>
     </row>
-    <row r="723" spans="1:5" ht="17" thickBot="1">
+    <row r="723" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A723" s="11">
         <v>44933</v>
       </c>
@@ -20037,7 +20037,7 @@
         <v>416489</v>
       </c>
     </row>
-    <row r="724" spans="1:5" ht="17" thickBot="1">
+    <row r="724" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A724" s="11">
         <v>44940</v>
       </c>
@@ -20055,7 +20055,7 @@
         <v>486000</v>
       </c>
     </row>
-    <row r="725" spans="1:5" ht="17" thickBot="1">
+    <row r="725" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A725" s="11">
         <v>44947</v>
       </c>
@@ -20073,7 +20073,7 @@
         <v>467485</v>
       </c>
     </row>
-    <row r="726" spans="1:5" ht="17" thickBot="1">
+    <row r="726" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A726" s="13">
         <v>44954</v>
       </c>
@@ -20091,7 +20091,7 @@
         <v>473650</v>
       </c>
     </row>
-    <row r="727" spans="1:5" ht="17" thickBot="1">
+    <row r="727" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A727" s="11">
         <v>44961</v>
       </c>
@@ -20109,7 +20109,7 @@
         <v>449586</v>
       </c>
     </row>
-    <row r="728" spans="1:5" ht="17" thickBot="1">
+    <row r="728" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A728" s="11">
         <v>44968</v>
       </c>
@@ -20127,7 +20127,7 @@
         <v>473972</v>
       </c>
     </row>
-    <row r="729" spans="1:5" ht="17" thickBot="1">
+    <row r="729" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A729" s="11">
         <v>44975</v>
       </c>
@@ -20145,7 +20145,7 @@
         <v>466932</v>
       </c>
     </row>
-    <row r="730" spans="1:5" ht="17" thickBot="1">
+    <row r="730" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A730" s="11">
         <v>44982</v>
       </c>
@@ -20163,7 +20163,7 @@
         <v>459233</v>
       </c>
     </row>
-    <row r="731" spans="1:5" ht="17" thickBot="1">
+    <row r="731" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A731" s="11">
         <v>44989</v>
       </c>
@@ -20181,7 +20181,7 @@
         <v>474191</v>
       </c>
     </row>
-    <row r="732" spans="1:5" ht="17" thickBot="1">
+    <row r="732" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A732" s="11">
         <v>44996</v>
       </c>
@@ -20199,7 +20199,7 @@
         <v>458629</v>
       </c>
     </row>
-    <row r="733" spans="1:5" ht="17" thickBot="1">
+    <row r="733" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A733" s="11">
         <v>45003</v>
       </c>
@@ -20217,7 +20217,7 @@
         <v>453500</v>
       </c>
     </row>
-    <row r="734" spans="1:5" ht="17" thickBot="1">
+    <row r="734" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A734" s="11">
         <v>45010</v>
       </c>
@@ -20235,7 +20235,7 @@
         <v>469958</v>
       </c>
     </row>
-    <row r="735" spans="1:5" ht="17" thickBot="1">
+    <row r="735" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A735" s="11">
         <v>45017</v>
       </c>
@@ -20253,7 +20253,7 @@
         <v>467430</v>
       </c>
     </row>
-    <row r="736" spans="1:5" ht="17" thickBot="1">
+    <row r="736" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A736" s="11">
         <v>45024</v>
       </c>
@@ -20271,7 +20271,7 @@
         <v>451336</v>
       </c>
     </row>
-    <row r="737" spans="1:5" ht="17" thickBot="1">
+    <row r="737" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A737" s="11">
         <v>45031</v>
       </c>
@@ -20289,7 +20289,7 @@
         <v>468197</v>
       </c>
     </row>
-    <row r="738" spans="1:5" ht="17" thickBot="1">
+    <row r="738" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A738" s="11">
         <v>45038</v>
       </c>
@@ -20307,7 +20307,7 @@
         <v>480457</v>
       </c>
     </row>
-    <row r="739" spans="1:5" ht="17" thickBot="1">
+    <row r="739" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A739" s="11">
         <v>45045</v>
       </c>
@@ -20325,7 +20325,7 @@
         <v>481960</v>
       </c>
     </row>
-    <row r="740" spans="1:5" ht="17" thickBot="1">
+    <row r="740" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A740" s="11">
         <v>45052</v>
       </c>
@@ -20343,7 +20343,7 @@
         <v>471859</v>
       </c>
     </row>
-    <row r="741" spans="1:5" ht="17" thickBot="1">
+    <row r="741" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A741" s="11">
         <v>45059</v>
       </c>
@@ -20361,7 +20361,7 @@
         <v>466381</v>
       </c>
     </row>
-    <row r="742" spans="1:5" ht="17" thickBot="1">
+    <row r="742" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A742" s="11">
         <v>45066</v>
       </c>
@@ -20379,7 +20379,7 @@
         <v>470694</v>
       </c>
     </row>
-    <row r="743" spans="1:5" ht="17" thickBot="1">
+    <row r="743" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A743" s="11">
         <v>45073</v>
       </c>
@@ -20397,7 +20397,7 @@
         <v>480998</v>
       </c>
     </row>
-    <row r="744" spans="1:5" ht="17" thickBot="1">
+    <row r="744" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A744" s="11">
         <v>45080</v>
       </c>
@@ -20415,7 +20415,7 @@
         <v>439601</v>
       </c>
     </row>
-    <row r="745" spans="1:5" ht="17" thickBot="1">
+    <row r="745" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A745" s="11">
         <v>45087</v>
       </c>
@@ -20433,7 +20433,7 @@
         <v>471141</v>
       </c>
     </row>
-    <row r="746" spans="1:5" ht="17" thickBot="1">
+    <row r="746" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A746" s="11">
         <v>45094</v>
       </c>
@@ -20451,7 +20451,7 @@
         <v>477126</v>
       </c>
     </row>
-    <row r="747" spans="1:5" ht="17" thickBot="1">
+    <row r="747" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A747" s="11">
         <v>45101</v>
       </c>
@@ -20469,7 +20469,7 @@
         <v>469453</v>
       </c>
     </row>
-    <row r="748" spans="1:5" ht="17" thickBot="1">
+    <row r="748" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A748" s="11">
         <v>45108</v>
       </c>
@@ -20487,7 +20487,7 @@
         <v>474443</v>
       </c>
     </row>
-    <row r="749" spans="1:5" ht="17" thickBot="1">
+    <row r="749" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A749" s="11">
         <v>45115</v>
       </c>
@@ -20505,7 +20505,7 @@
         <v>407843</v>
       </c>
     </row>
-    <row r="750" spans="1:5" ht="17" thickBot="1">
+    <row r="750" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A750" s="11">
         <v>45122</v>
       </c>
@@ -20523,7 +20523,7 @@
         <v>478153</v>
       </c>
     </row>
-    <row r="751" spans="1:5" ht="17" thickBot="1">
+    <row r="751" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A751" s="13">
         <v>45129</v>
       </c>
@@ -20541,7 +20541,7 @@
         <v>473736</v>
       </c>
     </row>
-    <row r="752" spans="1:5" ht="17" thickBot="1">
+    <row r="752" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A752" s="11">
         <v>45136</v>
       </c>
@@ -20559,7 +20559,7 @@
         <v>483481</v>
       </c>
     </row>
-    <row r="753" spans="1:5" ht="17" thickBot="1">
+    <row r="753" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A753" s="11">
         <v>45143</v>
       </c>
@@ -20577,7 +20577,7 @@
         <v>471938</v>
       </c>
     </row>
-    <row r="754" spans="1:5" ht="17" thickBot="1">
+    <row r="754" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A754" s="11">
         <v>45150</v>
       </c>
@@ -20595,7 +20595,7 @@
         <v>472498</v>
       </c>
     </row>
-    <row r="755" spans="1:5" ht="17" thickBot="1">
+    <row r="755" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A755" s="11">
         <v>45157</v>
       </c>
@@ -20613,7 +20613,7 @@
         <v>478853</v>
       </c>
     </row>
-    <row r="756" spans="1:5" ht="17" thickBot="1">
+    <row r="756" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A756" s="11">
         <v>45164</v>
       </c>
@@ -20631,7 +20631,7 @@
         <v>472525</v>
       </c>
     </row>
-    <row r="757" spans="1:5" ht="17" thickBot="1">
+    <row r="757" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A757" s="11">
         <v>45171</v>
       </c>
@@ -20649,7 +20649,7 @@
         <v>476851</v>
       </c>
     </row>
-    <row r="758" spans="1:5" ht="17" thickBot="1">
+    <row r="758" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A758" s="11">
         <v>45178</v>
       </c>
@@ -20667,7 +20667,7 @@
         <v>447345</v>
       </c>
     </row>
-    <row r="759" spans="1:5" ht="17" thickBot="1">
+    <row r="759" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A759" s="11">
         <v>45185</v>
       </c>
@@ -20685,7 +20685,7 @@
         <v>489790</v>
       </c>
     </row>
-    <row r="760" spans="1:5" ht="17" thickBot="1">
+    <row r="760" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A760" s="11">
         <v>45192</v>
       </c>
@@ -20703,7 +20703,7 @@
         <v>493323</v>
       </c>
     </row>
-    <row r="761" spans="1:5" ht="17" thickBot="1">
+    <row r="761" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A761" s="11">
         <v>45199</v>
       </c>
@@ -20721,7 +20721,7 @@
         <v>500154</v>
       </c>
     </row>
-    <row r="762" spans="1:5" ht="17" thickBot="1">
+    <row r="762" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A762" s="11">
         <v>45206</v>
       </c>
@@ -20739,7 +20739,7 @@
         <v>499217</v>
       </c>
     </row>
-    <row r="763" spans="1:5" ht="17" thickBot="1">
+    <row r="763" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A763" s="11">
         <v>45213</v>
       </c>
@@ -20757,7 +20757,7 @@
         <v>492781</v>
       </c>
     </row>
-    <row r="764" spans="1:5" ht="17" thickBot="1">
+    <row r="764" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A764" s="11">
         <v>45220</v>
       </c>
@@ -20775,7 +20775,7 @@
         <v>505985</v>
       </c>
     </row>
-    <row r="765" spans="1:5" ht="17" thickBot="1">
+    <row r="765" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A765" s="11">
         <v>45227</v>
       </c>
@@ -20793,7 +20793,7 @@
         <v>499389</v>
       </c>
     </row>
-    <row r="766" spans="1:5" ht="17" thickBot="1">
+    <row r="766" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A766" s="11">
         <v>45234</v>
       </c>
@@ -20811,7 +20811,7 @@
         <v>484757</v>
       </c>
     </row>
-    <row r="767" spans="1:5" ht="17" thickBot="1">
+    <row r="767" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A767" s="11">
         <v>45241</v>
       </c>
@@ -20829,7 +20829,7 @@
         <v>497348</v>
       </c>
     </row>
-    <row r="768" spans="1:5" ht="17" thickBot="1">
+    <row r="768" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A768" s="11">
         <v>45248</v>
       </c>
@@ -20847,7 +20847,7 @@
         <v>501416</v>
       </c>
     </row>
-    <row r="769" spans="1:5" ht="17" thickBot="1">
+    <row r="769" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A769" s="11">
         <v>45255</v>
       </c>
@@ -20865,7 +20865,7 @@
         <v>415332</v>
       </c>
     </row>
-    <row r="770" spans="1:5" ht="17" thickBot="1">
+    <row r="770" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A770" s="11">
         <v>45262</v>
       </c>
@@ -20898,7 +20898,7 @@
         <v>509626</v>
       </c>
     </row>
-    <row r="771" spans="1:5" ht="17" thickBot="1">
+    <row r="771" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A771" s="11">
         <v>45269</v>
       </c>
@@ -20916,7 +20916,7 @@
         <v>499094</v>
       </c>
     </row>
-    <row r="772" spans="1:5" ht="17" thickBot="1">
+    <row r="772" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A772" s="11">
         <v>45276</v>
       </c>
@@ -20934,7 +20934,7 @@
         <v>502583</v>
       </c>
     </row>
-    <row r="773" spans="1:5" ht="17" thickBot="1">
+    <row r="773" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A773" s="11">
         <v>45283</v>
       </c>
@@ -20952,7 +20952,7 @@
         <v>486787</v>
       </c>
     </row>
-    <row r="774" spans="1:5" ht="17" thickBot="1">
+    <row r="774" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A774" s="11">
         <v>45297</v>
       </c>
@@ -20970,7 +20970,7 @@
         <v>417257</v>
       </c>
     </row>
-    <row r="775" spans="1:5" ht="17" thickBot="1">
+    <row r="775" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A775" s="11">
         <v>45304</v>
       </c>
@@ -20988,7 +20988,7 @@
         <v>457453</v>
       </c>
     </row>
-    <row r="776" spans="1:5" ht="17" thickBot="1">
+    <row r="776" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A776" s="15">
         <v>45311</v>
       </c>
@@ -21006,7 +21006,7 @@
         <v>397553</v>
       </c>
     </row>
-    <row r="777" spans="1:5" ht="17" thickBot="1">
+    <row r="777" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A777" s="17">
         <v>45318</v>
       </c>
@@ -21024,7 +21024,7 @@
         <v>467222</v>
       </c>
     </row>
-    <row r="778" spans="1:5" ht="17" thickBot="1">
+    <row r="778" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A778" s="17">
         <v>45325</v>
       </c>
@@ -21042,7 +21042,7 @@
         <v>491697</v>
       </c>
     </row>
-    <row r="779" spans="1:5" ht="17" thickBot="1">
+    <row r="779" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A779" s="17">
         <v>45332</v>
       </c>
@@ -21060,7 +21060,7 @@
         <v>484840</v>
       </c>
     </row>
-    <row r="780" spans="1:5" ht="17" thickBot="1">
+    <row r="780" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A780" s="17">
         <v>45339</v>
       </c>
@@ -21078,7 +21078,7 @@
         <v>474226</v>
       </c>
     </row>
-    <row r="781" spans="1:5" ht="17" thickBot="1">
+    <row r="781" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A781" s="17">
         <v>45346</v>
       </c>
@@ -21096,7 +21096,7 @@
         <v>483656</v>
       </c>
     </row>
-    <row r="782" spans="1:5" ht="17" thickBot="1">
+    <row r="782" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A782" s="17">
         <v>45353</v>
       </c>
@@ -21114,7 +21114,7 @@
         <v>483138</v>
       </c>
     </row>
-    <row r="783" spans="1:5" ht="17" thickBot="1">
+    <row r="783" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A783" s="17">
         <v>45360</v>
       </c>
@@ -21132,7 +21132,7 @@
         <v>472662</v>
       </c>
     </row>
-    <row r="784" spans="1:5" ht="17" thickBot="1">
+    <row r="784" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A784" s="17">
         <v>45367</v>
       </c>
@@ -21150,7 +21150,7 @@
         <v>474596</v>
       </c>
     </row>
-    <row r="785" spans="1:5" ht="17" thickBot="1">
+    <row r="785" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A785" s="17">
         <v>45374</v>
       </c>
@@ -21168,7 +21168,7 @@
         <v>470593</v>
       </c>
     </row>
-    <row r="786" spans="1:5" ht="17" thickBot="1">
+    <row r="786" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A786" s="17">
         <v>45381</v>
       </c>
@@ -21186,7 +21186,7 @@
         <v>472651</v>
       </c>
     </row>
-    <row r="787" spans="1:5" ht="17" thickBot="1">
+    <row r="787" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A787" s="17">
         <v>45388</v>
       </c>
@@ -21204,7 +21204,7 @@
         <v>450142</v>
       </c>
     </row>
-    <row r="788" spans="1:5" ht="17" thickBot="1">
+    <row r="788" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A788" s="17">
         <v>45395</v>
       </c>
@@ -21222,7 +21222,7 @@
         <v>466463</v>
       </c>
     </row>
-    <row r="789" spans="1:5" ht="17" thickBot="1">
+    <row r="789" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A789" s="17">
         <v>45402</v>
       </c>
@@ -21240,7 +21240,7 @@
         <v>474544</v>
       </c>
     </row>
-    <row r="790" spans="1:5" ht="17" thickBot="1">
+    <row r="790" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A790" s="17">
         <v>45409</v>
       </c>
@@ -21258,7 +21258,7 @@
         <v>476302</v>
       </c>
     </row>
-    <row r="791" spans="1:5" ht="17" thickBot="1">
+    <row r="791" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A791" s="17">
         <v>45416</v>
       </c>
@@ -21276,7 +21276,7 @@
         <v>463106</v>
       </c>
     </row>
-    <row r="792" spans="1:5" ht="17" thickBot="1">
+    <row r="792" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A792" s="17">
         <v>45423</v>
       </c>
@@ -21294,7 +21294,7 @@
         <v>468748</v>
       </c>
     </row>
-    <row r="793" spans="1:5" ht="17" thickBot="1">
+    <row r="793" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A793" s="17">
         <v>45430</v>
       </c>
@@ -21312,7 +21312,7 @@
         <v>474886</v>
       </c>
     </row>
-    <row r="794" spans="1:5" ht="17" thickBot="1">
+    <row r="794" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A794" s="17">
         <v>45437</v>
       </c>
@@ -21330,7 +21330,7 @@
         <v>485232</v>
       </c>
     </row>
-    <row r="795" spans="1:5" ht="17" thickBot="1">
+    <row r="795" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A795" s="17">
         <v>45444</v>
       </c>
@@ -21348,7 +21348,7 @@
         <v>450077</v>
       </c>
     </row>
-    <row r="796" spans="1:5" ht="17" thickBot="1">
+    <row r="796" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A796" s="17">
         <v>45451</v>
       </c>
@@ -21366,7 +21366,7 @@
         <v>489916</v>
       </c>
     </row>
-    <row r="797" spans="1:5" ht="17" thickBot="1">
+    <row r="797" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A797" s="17">
         <v>45458</v>
       </c>
@@ -21384,7 +21384,7 @@
         <v>493138</v>
       </c>
     </row>
-    <row r="798" spans="1:5" ht="17" thickBot="1">
+    <row r="798" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A798" s="17">
         <v>45465</v>
       </c>
@@ -21402,7 +21402,7 @@
         <v>485557</v>
       </c>
     </row>
-    <row r="799" spans="1:5" ht="17" thickBot="1">
+    <row r="799" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A799" s="17">
         <v>45472</v>
       </c>
@@ -21420,7 +21420,7 @@
         <v>491899</v>
       </c>
     </row>
-    <row r="800" spans="1:5" ht="17" thickBot="1">
+    <row r="800" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A800" s="17">
         <v>45479</v>
       </c>
@@ -21438,7 +21438,7 @@
         <v>421817</v>
       </c>
     </row>
-    <row r="801" spans="1:5" ht="17" thickBot="1">
+    <row r="801" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A801" s="15">
         <v>45486</v>
       </c>
@@ -21456,7 +21456,7 @@
         <v>483806</v>
       </c>
     </row>
-    <row r="802" spans="1:5" ht="17" thickBot="1">
+    <row r="802" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A802" s="17">
         <v>45493</v>
       </c>
@@ -21474,7 +21474,7 @@
         <v>480083</v>
       </c>
     </row>
-    <row r="803" spans="1:5" ht="17" thickBot="1">
+    <row r="803" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A803" s="17">
         <v>45500</v>
       </c>
@@ -21492,7 +21492,7 @@
         <v>508496</v>
       </c>
     </row>
-    <row r="804" spans="1:5" ht="17" thickBot="1">
+    <row r="804" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A804" s="17">
         <v>45507</v>
       </c>
@@ -21510,7 +21510,7 @@
         <v>498807</v>
       </c>
     </row>
-    <row r="805" spans="1:5" ht="17" thickBot="1">
+    <row r="805" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A805" s="17">
         <v>45514</v>
       </c>
@@ -21528,7 +21528,7 @@
         <v>496509</v>
       </c>
     </row>
-    <row r="806" spans="1:5" ht="17" thickBot="1">
+    <row r="806" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A806" s="17">
         <v>45521</v>
       </c>
@@ -21546,7 +21546,7 @@
         <v>516819</v>
       </c>
     </row>
-    <row r="807" spans="1:5" ht="17" thickBot="1">
+    <row r="807" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A807" s="17">
         <v>45528</v>
       </c>
@@ -21564,7 +21564,7 @@
         <v>516807</v>
       </c>
     </row>
-    <row r="808" spans="1:5" ht="17" thickBot="1">
+    <row r="808" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A808" s="17">
         <v>45535</v>
       </c>
@@ -21582,7 +21582,7 @@
         <v>516632</v>
       </c>
     </row>
-    <row r="809" spans="1:5" ht="17" thickBot="1">
+    <row r="809" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A809" s="17">
         <v>45542</v>
       </c>
@@ -21600,7 +21600,7 @@
         <v>479179</v>
       </c>
     </row>
-    <row r="810" spans="1:5" ht="17" thickBot="1">
+    <row r="810" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A810" s="17">
         <v>45549</v>
       </c>
@@ -21618,7 +21618,7 @@
         <v>522557</v>
       </c>
     </row>
-    <row r="811" spans="1:5" ht="17" thickBot="1">
+    <row r="811" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A811" s="17">
         <v>45556</v>
       </c>
@@ -21636,7 +21636,7 @@
         <v>522112</v>
       </c>
     </row>
-    <row r="812" spans="1:5" ht="17" thickBot="1">
+    <row r="812" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A812" s="17">
         <v>45563</v>
       </c>
@@ -21654,7 +21654,7 @@
         <v>507537</v>
       </c>
     </row>
-    <row r="813" spans="1:5" ht="17" thickBot="1">
+    <row r="813" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A813" s="17">
         <v>45570</v>
       </c>
@@ -21672,7 +21672,7 @@
         <v>486187</v>
       </c>
     </row>
-    <row r="814" spans="1:5" ht="17" thickBot="1">
+    <row r="814" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A814" s="17">
         <v>45577</v>
       </c>
@@ -21690,7 +21690,7 @@
         <v>505033</v>
       </c>
     </row>
-    <row r="815" spans="1:5" ht="17" thickBot="1">
+    <row r="815" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A815" s="17">
         <v>45584</v>
       </c>
@@ -21708,7 +21708,7 @@
         <v>510730</v>
       </c>
     </row>
-    <row r="816" spans="1:5" ht="17" thickBot="1">
+    <row r="816" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A816" s="17">
         <v>45591</v>
       </c>
@@ -21726,7 +21726,7 @@
         <v>519415</v>
       </c>
     </row>
-    <row r="817" spans="1:5" ht="17" thickBot="1">
+    <row r="817" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A817" s="17">
         <v>45598</v>
       </c>
@@ -21744,7 +21744,7 @@
         <v>516743</v>
       </c>
     </row>
-    <row r="818" spans="1:5" ht="17" thickBot="1">
+    <row r="818" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A818" s="17">
         <v>45612</v>
       </c>
@@ -21762,7 +21762,7 @@
         <v>516886</v>
       </c>
     </row>
-    <row r="819" spans="1:5" ht="17" thickBot="1">
+    <row r="819" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A819" s="17">
         <v>45619</v>
       </c>
@@ -21780,7 +21780,7 @@
         <v>520798</v>
       </c>
     </row>
-    <row r="820" spans="1:5" ht="17" thickBot="1">
+    <row r="820" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A820" s="17">
         <v>45626</v>
       </c>
@@ -21798,7 +21798,7 @@
         <v>439362</v>
       </c>
     </row>
-    <row r="821" spans="1:5" ht="17" thickBot="1">
+    <row r="821" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A821" s="17">
         <v>45633</v>
       </c>
@@ -21816,7 +21816,7 @@
         <v>520894</v>
       </c>
     </row>
-    <row r="822" spans="1:5" ht="17" thickBot="1">
+    <row r="822" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A822" s="17">
         <v>45640</v>
       </c>
@@ -21834,7 +21834,7 @@
         <v>526166</v>
       </c>
     </row>
-    <row r="823" spans="1:5" ht="17" thickBot="1">
+    <row r="823" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A823" s="17">
         <v>45647</v>
       </c>
@@ -21852,7 +21852,7 @@
         <v>523912</v>
       </c>
     </row>
-    <row r="824" spans="1:5" ht="17" thickBot="1">
+    <row r="824" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A824" s="17">
         <v>45654</v>
       </c>
@@ -21870,7 +21870,7 @@
         <v>389700</v>
       </c>
     </row>
-    <row r="825" spans="1:5" ht="17" thickBot="1">
+    <row r="825" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A825" s="17">
         <v>45661</v>
       </c>
@@ -21888,7 +21888,7 @@
         <v>421410</v>
       </c>
     </row>
-    <row r="826" spans="1:5" ht="17" thickBot="1">
+    <row r="826" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A826" s="15">
         <v>45668</v>
       </c>
@@ -21906,7 +21906,7 @@
         <v>465390</v>
       </c>
     </row>
-    <row r="827" spans="1:5" ht="17" thickBot="1">
+    <row r="827" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A827" s="17">
         <v>45675</v>
       </c>
@@ -21924,7 +21924,7 @@
         <v>500160</v>
       </c>
     </row>
-    <row r="828" spans="1:5" ht="17" thickBot="1">
+    <row r="828" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A828" s="17">
         <v>45682</v>
       </c>
@@ -21942,7 +21942,7 @@
         <v>454797</v>
       </c>
     </row>
-    <row r="829" spans="1:5" ht="17" thickBot="1">
+    <row r="829" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A829" s="17">
         <v>45689</v>
       </c>
@@ -21960,7 +21960,7 @@
         <v>513622</v>
       </c>
     </row>
-    <row r="830" spans="1:5" ht="17" thickBot="1">
+    <row r="830" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A830" s="17">
         <v>45696</v>
       </c>
@@ -21978,7 +21978,7 @@
         <v>502449</v>
       </c>
     </row>
-    <row r="831" spans="1:5" ht="17" thickBot="1">
+    <row r="831" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A831" s="17">
         <v>45703</v>
       </c>
@@ -21996,7 +21996,7 @@
         <v>480740</v>
       </c>
     </row>
-    <row r="832" spans="1:5" ht="17" thickBot="1">
+    <row r="832" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A832" s="17">
         <v>45710</v>
       </c>
@@ -22014,7 +22014,7 @@
         <v>458513</v>
       </c>
     </row>
-    <row r="833" spans="1:5" ht="17" thickBot="1">
+    <row r="833" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A833" s="17">
         <v>45717</v>
       </c>
@@ -22032,7 +22032,7 @@
         <v>508531</v>
       </c>
     </row>
-    <row r="834" spans="1:5" ht="17" thickBot="1">
+    <row r="834" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A834" s="17">
         <v>45724</v>
       </c>
@@ -22065,7 +22065,7 @@
         <v>497412</v>
       </c>
     </row>
-    <row r="835" spans="1:5" ht="17" thickBot="1">
+    <row r="835" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A835" s="17">
         <v>45731</v>
       </c>
@@ -22083,7 +22083,7 @@
         <v>503473</v>
       </c>
     </row>
-    <row r="836" spans="1:5" ht="17" thickBot="1">
+    <row r="836" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A836" s="17">
         <v>45738</v>
       </c>
@@ -22101,7 +22101,7 @@
         <v>496214</v>
       </c>
     </row>
-    <row r="837" spans="1:5" ht="17" thickBot="1">
+    <row r="837" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A837" s="17">
         <v>45745</v>
       </c>
@@ -22119,7 +22119,7 @@
         <v>513553</v>
       </c>
     </row>
-    <row r="838" spans="1:5" ht="17" thickBot="1">
+    <row r="838" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A838" s="17">
         <v>45752</v>
       </c>
@@ -22137,7 +22137,7 @@
         <v>500584</v>
       </c>
     </row>
-    <row r="839" spans="1:5" ht="17" thickBot="1">
+    <row r="839" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A839" s="17">
         <v>45759</v>
       </c>
@@ -22155,7 +22155,7 @@
         <v>491908</v>
       </c>
     </row>
-    <row r="840" spans="1:5" ht="17" thickBot="1">
+    <row r="840" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A840" s="17">
         <v>45766</v>
       </c>
@@ -22173,7 +22173,7 @@
         <v>496053</v>
       </c>
     </row>
-    <row r="841" spans="1:5" ht="17" thickBot="1">
+    <row r="841" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A841" s="17">
         <v>45773</v>
       </c>
@@ -22191,7 +22191,7 @@
         <v>502105</v>
       </c>
     </row>
-    <row r="842" spans="1:5" ht="17" thickBot="1">
+    <row r="842" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A842" s="17">
         <v>45780</v>
       </c>
@@ -22209,7 +22209,7 @@
         <v>498693</v>
       </c>
     </row>
-    <row r="843" spans="1:5" ht="17" thickBot="1">
+    <row r="843" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A843" s="17">
         <v>45787</v>
       </c>
@@ -22227,7 +22227,7 @@
         <v>495552</v>
       </c>
     </row>
-    <row r="844" spans="1:5" ht="17" thickBot="1">
+    <row r="844" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A844" s="17">
         <v>45794</v>
       </c>
@@ -22245,7 +22245,7 @@
         <v>490775</v>
       </c>
     </row>
-    <row r="845" spans="1:5" ht="17" thickBot="1">
+    <row r="845" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A845" s="17">
         <v>45801</v>
       </c>
@@ -22263,7 +22263,7 @@
         <v>488709</v>
       </c>
     </row>
-    <row r="846" spans="1:5" ht="17" thickBot="1">
+    <row r="846" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A846" s="17">
         <v>45808</v>
       </c>
@@ -22281,7 +22281,7 @@
         <v>459884</v>
       </c>
     </row>
-    <row r="847" spans="1:5" ht="17" thickBot="1">
+    <row r="847" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A847" s="17">
         <v>45815</v>
       </c>
@@ -22299,7 +22299,7 @@
         <v>483807</v>
       </c>
     </row>
-    <row r="848" spans="1:5" ht="17" thickBot="1">
+    <row r="848" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A848" s="17">
         <v>45822</v>
       </c>
@@ -22317,7 +22317,7 @@
         <v>485810</v>
       </c>
     </row>
-    <row r="849" spans="1:5" ht="17" thickBot="1">
+    <row r="849" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A849" s="17">
         <v>45829</v>
       </c>
@@ -22335,7 +22335,7 @@
         <v>487328</v>
       </c>
     </row>
-    <row r="850" spans="1:5" ht="17" thickBot="1">
+    <row r="850" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A850" s="17">
         <v>45836</v>
       </c>
@@ -22353,7 +22353,7 @@
         <v>491424</v>
       </c>
     </row>
-    <row r="851" spans="1:5" ht="17" thickBot="1">
+    <row r="851" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A851" s="15">
         <v>45843</v>
       </c>
@@ -22371,7 +22371,7 @@
         <v>443049</v>
       </c>
     </row>
-    <row r="852" spans="1:5" ht="17" thickBot="1">
+    <row r="852" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A852" s="17">
         <v>45850</v>
       </c>
@@ -22389,7 +22389,7 @@
         <v>496188</v>
       </c>
     </row>
-    <row r="853" spans="1:5" ht="17" thickBot="1">
+    <row r="853" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A853" s="17">
         <v>45857</v>
       </c>
@@ -22407,7 +22407,7 @@
         <v>506882</v>
       </c>
     </row>
-    <row r="854" spans="1:5" ht="17" thickBot="1">
+    <row r="854" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A854" s="17">
         <v>45864</v>
       </c>
@@ -22425,7 +22425,7 @@
         <v>514279</v>
       </c>
     </row>
-    <row r="855" spans="1:5" ht="17" thickBot="1">
+    <row r="855" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A855" s="17">
         <v>45871</v>
       </c>
@@ -22443,7 +22443,7 @@
         <v>513529</v>
       </c>
     </row>
-    <row r="856" spans="1:5" ht="17" thickBot="1">
+    <row r="856" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A856" s="17">
         <v>45878</v>
       </c>
@@ -22461,7 +22461,7 @@
         <v>511194</v>
       </c>
     </row>
-    <row r="857" spans="1:5" ht="17" thickBot="1">
+    <row r="857" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A857" s="17">
         <v>45885</v>
       </c>
@@ -22479,7 +22479,7 @@
         <v>512970</v>
       </c>
     </row>
-    <row r="858" spans="1:5" ht="17" thickBot="1">
+    <row r="858" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A858" s="17">
         <v>45892</v>
       </c>
@@ -22497,7 +22497,7 @@
         <v>512333</v>
       </c>
     </row>
-    <row r="859" spans="1:5" ht="17" thickBot="1">
+    <row r="859" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A859" s="17">
         <v>45899</v>
       </c>
@@ -22515,7 +22515,7 @@
         <v>521502</v>
       </c>
     </row>
-    <row r="860" spans="1:5" ht="17" thickBot="1">
+    <row r="860" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A860" s="17">
         <v>45906</v>
       </c>
@@ -22533,7 +22533,7 @@
         <v>467880</v>
       </c>
     </row>
-    <row r="861" spans="1:5" ht="17" thickBot="1">
+    <row r="861" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A861" s="17">
         <v>45913</v>
       </c>
@@ -22551,7 +22551,7 @@
         <v>514167</v>
       </c>
     </row>
-    <row r="862" spans="1:5" ht="17" thickBot="1">
+    <row r="862" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A862" s="17">
         <v>45920</v>
       </c>
@@ -22569,7 +22569,7 @@
         <v>510677</v>
       </c>
     </row>
-    <row r="863" spans="1:5" ht="17" thickBot="1">
+    <row r="863" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A863" s="15">
         <v>45927</v>
       </c>
@@ -22587,7 +22587,7 @@
         <v>512642</v>
       </c>
     </row>
-    <row r="864" spans="1:5" ht="17" thickBot="1">
+    <row r="864" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A864" s="17">
         <v>45934</v>
       </c>
@@ -22605,7 +22605,7 @@
         <v>503538</v>
       </c>
     </row>
-    <row r="865" spans="1:5" ht="17" thickBot="1">
+    <row r="865" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A865" s="17">
         <v>45941</v>
       </c>
@@ -22623,7 +22623,7 @@
         <v>498462</v>
       </c>
     </row>
-    <row r="866" spans="1:5" ht="17" thickBot="1">
+    <row r="866" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A866" s="17">
         <v>45948</v>
       </c>
@@ -22641,7 +22641,7 @@
         <v>497854</v>
       </c>
     </row>
-    <row r="867" spans="1:5" ht="17" thickBot="1">
+    <row r="867" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A867" s="17">
         <v>45955</v>
       </c>
@@ -22659,7 +22659,7 @@
         <v>499688</v>
       </c>
     </row>
-    <row r="868" spans="1:5" ht="17" thickBot="1">
+    <row r="868" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A868" s="17">
         <v>45962</v>
       </c>
@@ -22677,7 +22677,7 @@
         <v>496928</v>
       </c>
     </row>
-    <row r="869" spans="1:5" ht="17" thickBot="1">
+    <row r="869" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A869" s="17">
         <v>45969</v>
       </c>
@@ -22695,7 +22695,7 @@
         <v>493493</v>
       </c>
     </row>
-    <row r="870" spans="1:5" ht="17" thickBot="1">
+    <row r="870" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A870" s="17">
         <v>45976</v>
       </c>
@@ -22713,7 +22713,7 @@
         <v>493880</v>
       </c>
     </row>
-    <row r="871" spans="1:5" ht="17" thickBot="1">
+    <row r="871" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A871" s="17">
         <v>45983</v>
       </c>
@@ -22731,7 +22731,7 @@
         <v>516110</v>
       </c>
     </row>
-    <row r="872" spans="1:5" ht="17" thickBot="1">
+    <row r="872" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A872" s="17">
         <v>45990</v>
       </c>
@@ -22749,7 +22749,7 @@
         <v>431435</v>
       </c>
     </row>
-    <row r="873" spans="1:5" ht="17" thickBot="1">
+    <row r="873" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A873" s="17">
         <v>45997</v>
       </c>
@@ -22767,7 +22767,7 @@
         <v>508999</v>
       </c>
     </row>
-    <row r="874" spans="1:5" ht="17" thickBot="1">
+    <row r="874" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A874" s="17">
         <v>46004</v>
       </c>
@@ -22785,7 +22785,7 @@
         <v>518904</v>
       </c>
     </row>
-    <row r="875" spans="1:5" ht="17" thickBot="1">
+    <row r="875" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A875" s="15">
         <v>46018</v>
       </c>
@@ -22803,7 +22803,7 @@
         <v>392295</v>
       </c>
     </row>
-    <row r="876" spans="1:5" ht="17" thickBot="1">
+    <row r="876" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A876" s="8">
         <v>46025</v>
       </c>
@@ -22821,7 +22821,7 @@
         <v>404293</v>
       </c>
     </row>
-    <row r="877" spans="1:5" ht="17" thickBot="1">
+    <row r="877" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A877" s="15">
         <v>46032</v>
       </c>
@@ -22839,7 +22839,7 @@
         <v>510457</v>
       </c>
     </row>
-    <row r="878" spans="1:5" ht="17" thickBot="1">
+    <row r="878" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A878" s="8">
         <v>46039</v>
       </c>
@@ -22872,7 +22872,7 @@
         <v>505385</v>
       </c>
     </row>
-    <row r="879" spans="1:5" ht="17" thickBot="1">
+    <row r="879" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A879" s="15">
         <v>46046</v>
       </c>
@@ -22905,7 +22905,7 @@
         <v>481708</v>
       </c>
     </row>
-    <row r="880" spans="1:5" ht="17" thickBot="1">
+    <row r="880" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A880" s="15">
         <v>46053</v>
       </c>
@@ -22938,7 +22938,7 @@
         <v>434361</v>
       </c>
     </row>
-    <row r="881" spans="1:5" ht="17" thickBot="1">
+    <row r="881" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A881" s="15">
         <v>46060</v>
       </c>
@@ -22956,7 +22956,7 @@
         <v>486854</v>
       </c>
     </row>
-    <row r="882" spans="1:5" ht="17" thickBot="1">
+    <row r="882" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A882" s="8">
         <v>46067</v>
       </c>
@@ -22989,7 +22989,7 @@
         <v>510399</v>
       </c>
     </row>
-    <row r="883" spans="1:5" ht="17" thickBot="1">
+    <row r="883" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A883" s="15">
         <v>46074</v>
       </c>
@@ -23022,7 +23022,7 @@
         <v>507712</v>
       </c>
     </row>
-    <row r="884" spans="1:5" ht="17" thickBot="1">
+    <row r="884" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A884" s="8">
         <v>46081</v>
       </c>
@@ -23040,7 +23040,7 @@
         <v>516729</v>
       </c>
     </row>
-    <row r="885" spans="1:5" ht="17" thickBot="1">
+    <row r="885" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A885" s="15">
         <v>46088</v>
       </c>
@@ -23058,7 +23058,7 @@
         <v>514996</v>
       </c>
     </row>
-    <row r="886" spans="1:5" ht="16">
+    <row r="886" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A886" s="8">
         <v>46102</v>
       </c>
@@ -23076,7 +23076,7 @@
         <v>502252</v>
       </c>
     </row>
-    <row r="887" spans="1:5" ht="16">
+    <row r="887" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A887" s="8">
         <v>46109</v>
       </c>
@@ -23094,7 +23094,7 @@
         <v>515921</v>
       </c>
     </row>
-    <row r="888" spans="1:5" ht="16">
+    <row r="888" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A888" s="8">
         <v>46116</v>
       </c>
@@ -23112,7 +23112,7 @@
         <v>501328</v>
       </c>
     </row>
-    <row r="889" spans="1:5" ht="16">
+    <row r="889" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A889" s="8">
         <v>46123</v>
       </c>
@@ -23130,7 +23130,7 @@
         <v>500040</v>
       </c>
     </row>
-    <row r="890" spans="1:5" ht="16">
+    <row r="890" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A890" s="8">
         <v>46130</v>
       </c>
@@ -23148,7 +23148,7 @@
         <v>508303</v>
       </c>
     </row>
-    <row r="891" spans="1:5" ht="16">
+    <row r="891" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A891" s="8">
         <v>46137</v>
       </c>
@@ -23166,7 +23166,7 @@
         <v>511616</v>
       </c>
     </row>
-    <row r="892" spans="1:5" ht="16">
+    <row r="892" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A892" s="8">
         <v>46144</v>
       </c>
@@ -23184,7 +23184,7 @@
         <v>518773</v>
       </c>
     </row>
-    <row r="893" spans="1:5" ht="16">
+    <row r="893" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A893" s="8">
         <v>46151</v>
       </c>
@@ -23217,7 +23217,7 @@
         <v>513755</v>
       </c>
     </row>
-    <row r="894" spans="1:5" ht="16">
+    <row r="894" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A894" s="8">
         <v>46158</v>
       </c>
@@ -23235,7 +23235,7 @@
         <v>511216</v>
       </c>
     </row>
-    <row r="895" spans="1:5" ht="16">
+    <row r="895" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A895" s="8">
         <v>46165</v>
       </c>
@@ -23253,7 +23253,7 @@
         <v>523574</v>
       </c>
     </row>
-    <row r="896" spans="1:5" ht="16">
+    <row r="896" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A896" s="8">
         <v>46172</v>
       </c>
@@ -23286,7 +23286,7 @@
         <v>492795</v>
       </c>
     </row>
-    <row r="897" spans="1:5" ht="16">
+    <row r="897" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A897" s="8">
         <v>46179</v>
       </c>
@@ -23304,7 +23304,7 @@
         <v>521804</v>
       </c>
     </row>
-    <row r="898" spans="1:5" ht="16">
+    <row r="898" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A898" s="8">
         <v>46186</v>
       </c>
@@ -23320,6 +23320,36 @@
       </c>
       <c r="E898" s="20">
         <v>520406</v>
+      </c>
+    </row>
+    <row r="899" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A899" s="8">
+        <v>46193</v>
+      </c>
+      <c r="B899" s="8">
+        <v>46197</v>
+      </c>
+      <c r="C899" s="21">
+        <v>0.87291666666666601</v>
+      </c>
+      <c r="D899" s="7" t="str">
+        <f t="shared" ref="D899" si="18">IF(
+ AND(
+  A899 &gt;= IF(
+         YEAR(A899)&gt;=2007,
+         DATE(YEAR(A899),3,14)-WEEKDAY(DATE(YEAR(A899),3,14),1)+1 + TIME(2,0,0),
+         DATE(YEAR(A899),4,7)-WEEKDAY(DATE(YEAR(A899),4,7),1)+1 + TIME(2,0,0)
+       ),
+  A899 &lt;  IF(
+         YEAR(A899)&gt;=2007,
+         DATE(YEAR(A899),11,7)-WEEKDAY(DATE(YEAR(A899),11,7),1)+1 + TIME(2,0,0),
+         DATE(YEAR(A899),10,31)-WEEKDAY(DATE(YEAR(A899),10,31),1) + TIME(2,0,0)
+       )
+ ),
+ "UTC-4",
+ "UTC-5"
+)</f>
+        <v>UTC-4</v>
       </c>
     </row>
   </sheetData>
@@ -23335,7 +23365,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{300947AE-C9E8-48BA-99BA-AA00E1AFF02E}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="15.6" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -23346,12 +23376,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFF96248-4EFB-4252-A059-6D65AEEDC293}">
   <dimension ref="B2:C4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="15.6" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
@@ -23359,7 +23389,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="2:3">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
@@ -23367,7 +23397,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="2:3">
+    <row r="4" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>

--- a/data/freight/US Rail Traffic.xlsx
+++ b/data/freight/US Rail Traffic.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\freight\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tommy/Desktop/Pycharm/FinancialData/data/freight/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EA5BAF0-80D0-46E0-BC88-68E4305280C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D4F01BB-B885-8349-8636-EEC74B12800D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{55EF15CE-83DB-4E42-B75D-C3DAE3AA4C48}"/>
+    <workbookView xWindow="22160" yWindow="600" windowWidth="29040" windowHeight="15720" xr2:uid="{55EF15CE-83DB-4E42-B75D-C3DAE3AA4C48}"/>
   </bookViews>
   <sheets>
     <sheet name="USRT" sheetId="1" r:id="rId1"/>
@@ -91,7 +91,7 @@
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="166" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -268,9 +268,9 @@
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="쉼표" xfId="1" builtinId="3"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -288,7 +288,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -6537,9 +6537,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -6577,7 +6577,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -6683,7 +6683,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -6825,7 +6825,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -6834,17 +6834,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83FCC8DB-37A0-4531-B65E-34C65BAF4830}">
   <dimension ref="A1:E899"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.33203125" style="21" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.77734375" style="20" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="6"/>
+    <col min="5" max="5" width="8.83203125" style="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.1640625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -6861,7 +6861,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" ht="16">
       <c r="A2" s="7">
         <v>39823</v>
       </c>
@@ -6872,7 +6872,7 @@
         <v>0.5</v>
       </c>
       <c r="D2" s="7" t="str">
-        <f t="shared" ref="D2:D65" si="0">IF(
+        <f>IF(
  AND(
   A2 &gt;= IF(
          YEAR(A2)&gt;=2007,
@@ -6894,7 +6894,7 @@
         <v>474565</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="16">
       <c r="A3" s="7">
         <v>39830</v>
       </c>
@@ -6905,14 +6905,29 @@
         <v>0.5</v>
       </c>
       <c r="D3" s="7" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="D2:D65" si="0">IF(
+ AND(
+  A3 &gt;= IF(
+         YEAR(A3)&gt;=2007,
+         DATE(YEAR(A3),3,14)-WEEKDAY(DATE(YEAR(A3),3,14),1)+1 + TIME(2,0,0),
+         DATE(YEAR(A3),4,7)-WEEKDAY(DATE(YEAR(A3),4,7),1)+1 + TIME(2,0,0)
+       ),
+  A3 &lt;  IF(
+         YEAR(A3)&gt;=2007,
+         DATE(YEAR(A3),11,7)-WEEKDAY(DATE(YEAR(A3),11,7),1)+1 + TIME(2,0,0),
+         DATE(YEAR(A3),10,31)-WEEKDAY(DATE(YEAR(A3),10,31),1) + TIME(2,0,0)
+       )
+ ),
+ "UTC-4",
+ "UTC-5"
+)</f>
         <v>UTC-5</v>
       </c>
       <c r="E3" s="10">
         <v>465386</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" ht="16">
       <c r="A4" s="7">
         <v>39837</v>
       </c>
@@ -6930,7 +6945,7 @@
         <v>462128</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="16">
       <c r="A5" s="7">
         <v>39844</v>
       </c>
@@ -6948,7 +6963,7 @@
         <v>449966</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="16">
       <c r="A6" s="7">
         <v>39851</v>
       </c>
@@ -6966,7 +6981,7 @@
         <v>455757</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" ht="16">
       <c r="A7" s="7">
         <v>39858</v>
       </c>
@@ -6984,7 +6999,7 @@
         <v>471961</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" ht="16">
       <c r="A8" s="7">
         <v>39865</v>
       </c>
@@ -7002,7 +7017,7 @@
         <v>446575</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" ht="16">
       <c r="A9" s="7">
         <v>39872</v>
       </c>
@@ -7020,7 +7035,7 @@
         <v>458242</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" ht="16">
       <c r="A10" s="7">
         <v>39879</v>
       </c>
@@ -7038,7 +7053,7 @@
         <v>455041</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" ht="16">
       <c r="A11" s="7">
         <v>39886</v>
       </c>
@@ -7056,7 +7071,7 @@
         <v>455686</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" ht="16">
       <c r="A12" s="7">
         <v>39893</v>
       </c>
@@ -7074,7 +7089,7 @@
         <v>459547</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" ht="16">
       <c r="A13" s="7">
         <v>39900</v>
       </c>
@@ -7092,7 +7107,7 @@
         <v>439844</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" ht="16">
       <c r="A14" s="7">
         <v>39907</v>
       </c>
@@ -7110,7 +7125,7 @@
         <v>447103</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" ht="16">
       <c r="A15" s="7">
         <v>39914</v>
       </c>
@@ -7128,7 +7143,7 @@
         <v>426107</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" ht="16">
       <c r="A16" s="7">
         <v>39921</v>
       </c>
@@ -7146,7 +7161,7 @@
         <v>438602</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" ht="16">
       <c r="A17" s="7">
         <v>39928</v>
       </c>
@@ -7164,7 +7179,7 @@
         <v>444794</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" ht="16">
       <c r="A18" s="7">
         <v>39935</v>
       </c>
@@ -7182,7 +7197,7 @@
         <v>442378</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" ht="16">
       <c r="A19" s="7">
         <v>39942</v>
       </c>
@@ -7200,7 +7215,7 @@
         <v>435052</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" ht="16">
       <c r="A20" s="7">
         <v>39949</v>
       </c>
@@ -7218,7 +7233,7 @@
         <v>438329</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" ht="16">
       <c r="A21" s="7">
         <v>39956</v>
       </c>
@@ -7236,7 +7251,7 @@
         <v>451355</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" ht="16">
       <c r="A22" s="7">
         <v>39963</v>
       </c>
@@ -7254,7 +7269,7 @@
         <v>401248</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" ht="16">
       <c r="A23" s="7">
         <v>39970</v>
       </c>
@@ -7272,7 +7287,7 @@
         <v>448743</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" ht="16">
       <c r="A24" s="7">
         <v>39977</v>
       </c>
@@ -7290,7 +7305,7 @@
         <v>451065</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" ht="16">
       <c r="A25" s="7">
         <v>39984</v>
       </c>
@@ -7308,7 +7323,7 @@
         <v>449103</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5" ht="16">
       <c r="A26" s="7">
         <v>39991</v>
       </c>
@@ -7326,7 +7341,7 @@
         <v>444212</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" ht="16">
       <c r="A27" s="7">
         <v>39998</v>
       </c>
@@ -7344,7 +7359,7 @@
         <v>410661</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5" ht="16">
       <c r="A28" s="7">
         <v>40005</v>
       </c>
@@ -7362,7 +7377,7 @@
         <v>439041</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5" ht="16">
       <c r="A29" s="7">
         <v>40012</v>
       </c>
@@ -7380,7 +7395,7 @@
         <v>456926</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:5" ht="16">
       <c r="A30" s="7">
         <v>40019</v>
       </c>
@@ -7398,7 +7413,7 @@
         <v>467395</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:5" ht="16">
       <c r="A31" s="7">
         <v>40026</v>
       </c>
@@ -7416,7 +7431,7 @@
         <v>468150</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:5" ht="16">
       <c r="A32" s="7">
         <v>40033</v>
       </c>
@@ -7434,7 +7449,7 @@
         <v>469814</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:5" ht="16">
       <c r="A33" s="7">
         <v>40040</v>
       </c>
@@ -7452,7 +7467,7 @@
         <v>469727</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:5" ht="16">
       <c r="A34" s="7">
         <v>40047</v>
       </c>
@@ -7470,7 +7485,7 @@
         <v>472644</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:5" ht="16">
       <c r="A35" s="7">
         <v>40054</v>
       </c>
@@ -7488,7 +7503,7 @@
         <v>488273</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:5" ht="16">
       <c r="A36" s="7">
         <v>40061</v>
       </c>
@@ -7506,7 +7521,7 @@
         <v>486009</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:5" ht="16">
       <c r="A37" s="7">
         <v>40068</v>
       </c>
@@ -7524,7 +7539,7 @@
         <v>439238</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:5" ht="16">
       <c r="A38" s="7">
         <v>40075</v>
       </c>
@@ -7542,7 +7557,7 @@
         <v>487236</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:5" ht="16">
       <c r="A39" s="7">
         <v>40082</v>
       </c>
@@ -7560,7 +7575,7 @@
         <v>477434</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:5" ht="16">
       <c r="A40" s="7">
         <v>40089</v>
       </c>
@@ -7578,7 +7593,7 @@
         <v>484157</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:5" ht="16">
       <c r="A41" s="7">
         <v>40096</v>
       </c>
@@ -7596,7 +7611,7 @@
         <v>481944</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:5" ht="16">
       <c r="A42" s="7">
         <v>40103</v>
       </c>
@@ -7614,7 +7629,7 @@
         <v>481827</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:5" ht="16">
       <c r="A43" s="7">
         <v>40110</v>
       </c>
@@ -7632,7 +7647,7 @@
         <v>483850</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:5" ht="16">
       <c r="A44" s="7">
         <v>40117</v>
       </c>
@@ -7650,7 +7665,7 @@
         <v>479450</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:5" ht="16">
       <c r="A45" s="7">
         <v>40124</v>
       </c>
@@ -7668,7 +7683,7 @@
         <v>481493</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:5" ht="16">
       <c r="A46" s="7">
         <v>40131</v>
       </c>
@@ -7686,7 +7701,7 @@
         <v>489073</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:5" ht="16">
       <c r="A47" s="7">
         <v>40138</v>
       </c>
@@ -7704,7 +7719,7 @@
         <v>500284</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:5" ht="16">
       <c r="A48" s="7">
         <v>40145</v>
       </c>
@@ -7722,7 +7737,7 @@
         <v>412036</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:5" ht="16">
       <c r="A49" s="7">
         <v>40152</v>
       </c>
@@ -7740,7 +7755,7 @@
         <v>491440</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:5" ht="16">
       <c r="A50" s="7">
         <v>40159</v>
       </c>
@@ -7758,7 +7773,7 @@
         <v>464948</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:5" ht="16">
       <c r="A51" s="7">
         <v>40166</v>
       </c>
@@ -7776,7 +7791,7 @@
         <v>481426</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:5" ht="16">
       <c r="A52" s="7">
         <v>40173</v>
       </c>
@@ -7794,7 +7809,7 @@
         <v>339702</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:5" ht="16">
       <c r="A53" s="7">
         <v>40180</v>
       </c>
@@ -7812,7 +7827,7 @@
         <v>376455</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:5" ht="16">
       <c r="A54" s="7">
         <v>40187</v>
       </c>
@@ -7830,7 +7845,7 @@
         <v>433584</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:5" ht="16">
       <c r="A55" s="7">
         <v>40194</v>
       </c>
@@ -7848,7 +7863,7 @@
         <v>465758</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:5" ht="16">
       <c r="A56" s="7">
         <v>40201</v>
       </c>
@@ -7866,7 +7881,7 @@
         <v>478227</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:5" ht="16">
       <c r="A57" s="7">
         <v>40208</v>
       </c>
@@ -7884,7 +7899,7 @@
         <v>482390</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:5" ht="16">
       <c r="A58" s="7">
         <v>40215</v>
       </c>
@@ -7902,7 +7917,7 @@
         <v>469221</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:5" ht="16">
       <c r="A59" s="7">
         <v>40222</v>
       </c>
@@ -7920,7 +7935,7 @@
         <v>450177</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:5" ht="16">
       <c r="A60" s="7">
         <v>40229</v>
       </c>
@@ -7938,7 +7953,7 @@
         <v>474203</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:5" ht="16">
       <c r="A61" s="7">
         <v>40236</v>
       </c>
@@ -7956,7 +7971,7 @@
         <v>496078</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:5" ht="16">
       <c r="A62" s="7">
         <v>40243</v>
       </c>
@@ -7974,7 +7989,7 @@
         <v>497456</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:5" ht="16">
       <c r="A63" s="7">
         <v>40250</v>
       </c>
@@ -7992,7 +8007,7 @@
         <v>491463</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:5" ht="16">
       <c r="A64" s="7">
         <v>40257</v>
       </c>
@@ -8010,7 +8025,7 @@
         <v>488939</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:5" ht="16">
       <c r="A65" s="7">
         <v>40264</v>
       </c>
@@ -8028,7 +8043,7 @@
         <v>504028</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:5" ht="16">
       <c r="A66" s="7">
         <v>40271</v>
       </c>
@@ -8061,7 +8076,7 @@
         <v>486474</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:5" ht="16">
       <c r="A67" s="7">
         <v>40278</v>
       </c>
@@ -8079,7 +8094,7 @@
         <v>492044</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:5" ht="16">
       <c r="A68" s="7">
         <v>40285</v>
       </c>
@@ -8097,7 +8112,7 @@
         <v>506502</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:5" ht="16">
       <c r="A69" s="7">
         <v>40292</v>
       </c>
@@ -8115,7 +8130,7 @@
         <v>510565</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:5" ht="16">
       <c r="A70" s="7">
         <v>40299</v>
       </c>
@@ -8133,7 +8148,7 @@
         <v>508731</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:5" ht="16">
       <c r="A71" s="7">
         <v>40306</v>
       </c>
@@ -8151,7 +8166,7 @@
         <v>497714</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:5" ht="16">
       <c r="A72" s="7">
         <v>40313</v>
       </c>
@@ -8169,7 +8184,7 @@
         <v>508469</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:5" ht="16">
       <c r="A73" s="7">
         <v>40320</v>
       </c>
@@ -8187,7 +8202,7 @@
         <v>503232</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:5" ht="16">
       <c r="A74" s="7">
         <v>40327</v>
       </c>
@@ -8205,7 +8220,7 @@
         <v>511776</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:5" ht="16">
       <c r="A75" s="7">
         <v>40334</v>
       </c>
@@ -8223,7 +8238,7 @@
         <v>462009</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:5" ht="16">
       <c r="A76" s="7">
         <v>40341</v>
       </c>
@@ -8241,7 +8256,7 @@
         <v>512048</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:5" ht="16">
       <c r="A77" s="7">
         <v>40348</v>
       </c>
@@ -8259,7 +8274,7 @@
         <v>512898</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:5" ht="16">
       <c r="A78" s="7">
         <v>40355</v>
       </c>
@@ -8277,7 +8292,7 @@
         <v>511945</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:5" ht="16">
       <c r="A79" s="7">
         <v>40362</v>
       </c>
@@ -8295,7 +8310,7 @@
         <v>518063</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:5" ht="16">
       <c r="A80" s="7">
         <v>40369</v>
       </c>
@@ -8313,7 +8328,7 @@
         <v>445917</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:5" ht="16">
       <c r="A81" s="7">
         <v>40376</v>
       </c>
@@ -8331,7 +8346,7 @@
         <v>509860</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:5" ht="16">
       <c r="A82" s="7">
         <v>40383</v>
       </c>
@@ -8349,7 +8364,7 @@
         <v>517297</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:5" ht="16">
       <c r="A83" s="7">
         <v>40390</v>
       </c>
@@ -8367,7 +8382,7 @@
         <v>533187</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:5" ht="16">
       <c r="A84" s="7">
         <v>40397</v>
       </c>
@@ -8385,7 +8400,7 @@
         <v>515715</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:5" ht="16">
       <c r="A85" s="7">
         <v>40404</v>
       </c>
@@ -8403,7 +8418,7 @@
         <v>529715</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:5" ht="16">
       <c r="A86" s="7">
         <v>40411</v>
       </c>
@@ -8421,7 +8436,7 @@
         <v>533038</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:5" ht="16">
       <c r="A87" s="7">
         <v>40418</v>
       </c>
@@ -8439,7 +8454,7 @@
         <v>539552</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:5" ht="16">
       <c r="A88" s="7">
         <v>40425</v>
       </c>
@@ -8457,7 +8472,7 @@
         <v>542006</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:5" ht="16">
       <c r="A89" s="7">
         <v>40432</v>
       </c>
@@ -8475,7 +8490,7 @@
         <v>484380</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:5" ht="16">
       <c r="A90" s="7">
         <v>40439</v>
       </c>
@@ -8493,7 +8508,7 @@
         <v>544692</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:5" ht="16">
       <c r="A91" s="7">
         <v>40446</v>
       </c>
@@ -8511,7 +8526,7 @@
         <v>542075</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:5" ht="16">
       <c r="A92" s="7">
         <v>40453</v>
       </c>
@@ -8529,7 +8544,7 @@
         <v>539646</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:5" ht="16">
       <c r="A93" s="7">
         <v>40460</v>
       </c>
@@ -8547,7 +8562,7 @@
         <v>533301</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:5" ht="16">
       <c r="A94" s="7">
         <v>40467</v>
       </c>
@@ -8565,7 +8580,7 @@
         <v>540844</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:5" ht="16">
       <c r="A95" s="7">
         <v>40474</v>
       </c>
@@ -8583,7 +8598,7 @@
         <v>538461</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:5" ht="16">
       <c r="A96" s="7">
         <v>40481</v>
       </c>
@@ -8601,7 +8616,7 @@
         <v>525601</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:5" ht="16">
       <c r="A97" s="7">
         <v>40488</v>
       </c>
@@ -8619,7 +8634,7 @@
         <v>519134</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:5" ht="16">
       <c r="A98" s="7">
         <v>40495</v>
       </c>
@@ -8637,7 +8652,7 @@
         <v>530157</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:5" ht="16">
       <c r="A99" s="7">
         <v>40502</v>
       </c>
@@ -8655,7 +8670,7 @@
         <v>533989</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:5" ht="16">
       <c r="A100" s="7">
         <v>40509</v>
       </c>
@@ -8673,7 +8688,7 @@
         <v>437911</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:5" ht="17" thickBot="1">
       <c r="A101" s="7">
         <v>40516</v>
       </c>
@@ -8691,7 +8706,7 @@
         <v>539405</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:5" ht="17" thickBot="1">
       <c r="A102" s="11">
         <v>40523</v>
       </c>
@@ -8709,7 +8724,7 @@
         <v>520326</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:5" ht="17" thickBot="1">
       <c r="A103" s="11">
         <v>40530</v>
       </c>
@@ -8727,7 +8742,7 @@
         <v>491896</v>
       </c>
     </row>
-    <row r="104" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:5" ht="17" thickBot="1">
       <c r="A104" s="11">
         <v>40537</v>
       </c>
@@ -8745,7 +8760,7 @@
         <v>433347</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:5" ht="17" thickBot="1">
       <c r="A105" s="11">
         <v>40544</v>
       </c>
@@ -8763,7 +8778,7 @@
         <v>406967</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:5" ht="17" thickBot="1">
       <c r="A106" s="11">
         <v>40551</v>
       </c>
@@ -8781,7 +8796,7 @@
         <v>498773</v>
       </c>
     </row>
-    <row r="107" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:5" ht="17" thickBot="1">
       <c r="A107" s="11">
         <v>40558</v>
       </c>
@@ -8799,7 +8814,7 @@
         <v>496473</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:5" ht="17" thickBot="1">
       <c r="A108" s="11">
         <v>40565</v>
       </c>
@@ -8817,7 +8832,7 @@
         <v>496043</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:5" ht="17" thickBot="1">
       <c r="A109" s="11">
         <v>40572</v>
       </c>
@@ -8835,7 +8850,7 @@
         <v>513889</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:5" ht="17" thickBot="1">
       <c r="A110" s="11">
         <v>40579</v>
       </c>
@@ -8853,7 +8868,7 @@
         <v>465931</v>
       </c>
     </row>
-    <row r="111" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:5" ht="17" thickBot="1">
       <c r="A111" s="11">
         <v>40586</v>
       </c>
@@ -8871,7 +8886,7 @@
         <v>502078</v>
       </c>
     </row>
-    <row r="112" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:5" ht="17" thickBot="1">
       <c r="A112" s="11">
         <v>40593</v>
       </c>
@@ -8889,7 +8904,7 @@
         <v>530973</v>
       </c>
     </row>
-    <row r="113" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:5" ht="17" thickBot="1">
       <c r="A113" s="11">
         <v>40600</v>
       </c>
@@ -8907,7 +8922,7 @@
         <v>516841</v>
       </c>
     </row>
-    <row r="114" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:5" ht="17" thickBot="1">
       <c r="A114" s="11">
         <v>40607</v>
       </c>
@@ -8925,7 +8940,7 @@
         <v>515296</v>
       </c>
     </row>
-    <row r="115" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:5" ht="17" thickBot="1">
       <c r="A115" s="11">
         <v>40614</v>
       </c>
@@ -8943,7 +8958,7 @@
         <v>508992</v>
       </c>
     </row>
-    <row r="116" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:5" ht="17" thickBot="1">
       <c r="A116" s="11">
         <v>40621</v>
       </c>
@@ -8961,7 +8976,7 @@
         <v>516560</v>
       </c>
     </row>
-    <row r="117" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:5" ht="17" thickBot="1">
       <c r="A117" s="11">
         <v>40628</v>
       </c>
@@ -8979,7 +8994,7 @@
         <v>522937</v>
       </c>
     </row>
-    <row r="118" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:5" ht="17" thickBot="1">
       <c r="A118" s="11">
         <v>40635</v>
       </c>
@@ -8997,7 +9012,7 @@
         <v>540213</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:5" ht="17" thickBot="1">
       <c r="A119" s="11">
         <v>40642</v>
       </c>
@@ -9015,7 +9030,7 @@
         <v>522511</v>
       </c>
     </row>
-    <row r="120" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:5" ht="17" thickBot="1">
       <c r="A120" s="11">
         <v>40649</v>
       </c>
@@ -9033,7 +9048,7 @@
         <v>525886</v>
       </c>
     </row>
-    <row r="121" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:5" ht="17" thickBot="1">
       <c r="A121" s="11">
         <v>40656</v>
       </c>
@@ -9051,7 +9066,7 @@
         <v>518374</v>
       </c>
     </row>
-    <row r="122" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:5" ht="17" thickBot="1">
       <c r="A122" s="11">
         <v>40663</v>
       </c>
@@ -9069,7 +9084,7 @@
         <v>525024</v>
       </c>
     </row>
-    <row r="123" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:5" ht="17" thickBot="1">
       <c r="A123" s="11">
         <v>40670</v>
       </c>
@@ -9087,7 +9102,7 @@
         <v>514038</v>
       </c>
     </row>
-    <row r="124" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:5" ht="17" thickBot="1">
       <c r="A124" s="11">
         <v>40677</v>
       </c>
@@ -9105,7 +9120,7 @@
         <v>526146</v>
       </c>
     </row>
-    <row r="125" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:5" ht="17" thickBot="1">
       <c r="A125" s="11">
         <v>40684</v>
       </c>
@@ -9123,7 +9138,7 @@
         <v>529383</v>
       </c>
     </row>
-    <row r="126" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:5" ht="17" thickBot="1">
       <c r="A126" s="13">
         <v>40691</v>
       </c>
@@ -9141,7 +9156,7 @@
         <v>522717</v>
       </c>
     </row>
-    <row r="127" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:5" ht="17" thickBot="1">
       <c r="A127" s="11">
         <v>40698</v>
       </c>
@@ -9159,7 +9174,7 @@
         <v>479149</v>
       </c>
     </row>
-    <row r="128" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:5" ht="17" thickBot="1">
       <c r="A128" s="11">
         <v>40705</v>
       </c>
@@ -9177,7 +9192,7 @@
         <v>527603</v>
       </c>
     </row>
-    <row r="129" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:5" ht="17" thickBot="1">
       <c r="A129" s="11">
         <v>40712</v>
       </c>
@@ -9195,7 +9210,7 @@
         <v>531992</v>
       </c>
     </row>
-    <row r="130" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:5" ht="17" thickBot="1">
       <c r="A130" s="11">
         <v>40719</v>
       </c>
@@ -9228,7 +9243,7 @@
         <v>519337</v>
       </c>
     </row>
-    <row r="131" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:5" ht="17" thickBot="1">
       <c r="A131" s="11">
         <v>40726</v>
       </c>
@@ -9246,7 +9261,7 @@
         <v>522931</v>
       </c>
     </row>
-    <row r="132" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:5" ht="17" thickBot="1">
       <c r="A132" s="11">
         <v>40733</v>
       </c>
@@ -9264,7 +9279,7 @@
         <v>438193</v>
       </c>
     </row>
-    <row r="133" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:5" ht="17" thickBot="1">
       <c r="A133" s="11">
         <v>40740</v>
       </c>
@@ -9282,7 +9297,7 @@
         <v>511711</v>
       </c>
     </row>
-    <row r="134" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:5" ht="17" thickBot="1">
       <c r="A134" s="11">
         <v>40747</v>
       </c>
@@ -9300,7 +9315,7 @@
         <v>524090</v>
       </c>
     </row>
-    <row r="135" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:5" ht="17" thickBot="1">
       <c r="A135" s="11">
         <v>40754</v>
       </c>
@@ -9318,7 +9333,7 @@
         <v>533337</v>
       </c>
     </row>
-    <row r="136" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:5" ht="17" thickBot="1">
       <c r="A136" s="11">
         <v>40761</v>
       </c>
@@ -9336,7 +9351,7 @@
         <v>522889</v>
       </c>
     </row>
-    <row r="137" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:5" ht="17" thickBot="1">
       <c r="A137" s="11">
         <v>40768</v>
       </c>
@@ -9354,7 +9369,7 @@
         <v>527864</v>
       </c>
     </row>
-    <row r="138" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:5" ht="17" thickBot="1">
       <c r="A138" s="11">
         <v>40775</v>
       </c>
@@ -9372,7 +9387,7 @@
         <v>539201</v>
       </c>
     </row>
-    <row r="139" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:5" ht="17" thickBot="1">
       <c r="A139" s="11">
         <v>40782</v>
       </c>
@@ -9390,7 +9405,7 @@
         <v>535994</v>
       </c>
     </row>
-    <row r="140" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:5" ht="17" thickBot="1">
       <c r="A140" s="11">
         <v>40789</v>
       </c>
@@ -9408,7 +9423,7 @@
         <v>537201</v>
       </c>
     </row>
-    <row r="141" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:5" ht="17" thickBot="1">
       <c r="A141" s="11">
         <v>40796</v>
       </c>
@@ -9426,7 +9441,7 @@
         <v>486472</v>
       </c>
     </row>
-    <row r="142" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:5" ht="17" thickBot="1">
       <c r="A142" s="11">
         <v>40803</v>
       </c>
@@ -9444,7 +9459,7 @@
         <v>542164</v>
       </c>
     </row>
-    <row r="143" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:5" ht="17" thickBot="1">
       <c r="A143" s="11">
         <v>40810</v>
       </c>
@@ -9462,7 +9477,7 @@
         <v>553535</v>
       </c>
     </row>
-    <row r="144" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:5" ht="17" thickBot="1">
       <c r="A144" s="11">
         <v>40817</v>
       </c>
@@ -9480,7 +9495,7 @@
         <v>563034</v>
       </c>
     </row>
-    <row r="145" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="145" spans="1:5" ht="17" thickBot="1">
       <c r="A145" s="11">
         <v>40824</v>
       </c>
@@ -9498,7 +9513,7 @@
         <v>544499</v>
       </c>
     </row>
-    <row r="146" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="146" spans="1:5" ht="17" thickBot="1">
       <c r="A146" s="11">
         <v>40831</v>
       </c>
@@ -9516,7 +9531,7 @@
         <v>547752</v>
       </c>
     </row>
-    <row r="147" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:5" ht="17" thickBot="1">
       <c r="A147" s="11">
         <v>40838</v>
       </c>
@@ -9534,7 +9549,7 @@
         <v>547268</v>
       </c>
     </row>
-    <row r="148" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="148" spans="1:5" ht="17" thickBot="1">
       <c r="A148" s="11">
         <v>40845</v>
       </c>
@@ -9552,7 +9567,7 @@
         <v>551674</v>
       </c>
     </row>
-    <row r="149" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:5" ht="17" thickBot="1">
       <c r="A149" s="11">
         <v>40852</v>
       </c>
@@ -9570,7 +9585,7 @@
         <v>537645</v>
       </c>
     </row>
-    <row r="150" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:5" ht="17" thickBot="1">
       <c r="A150" s="11">
         <v>40859</v>
       </c>
@@ -9588,7 +9603,7 @@
         <v>544563</v>
       </c>
     </row>
-    <row r="151" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:5" ht="17" thickBot="1">
       <c r="A151" s="13">
         <v>40866</v>
       </c>
@@ -9606,7 +9621,7 @@
         <v>545153</v>
       </c>
     </row>
-    <row r="152" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:5" ht="17" thickBot="1">
       <c r="A152" s="11">
         <v>40873</v>
       </c>
@@ -9624,7 +9639,7 @@
         <v>456170</v>
       </c>
     </row>
-    <row r="153" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:5" ht="17" thickBot="1">
       <c r="A153" s="11">
         <v>40880</v>
       </c>
@@ -9642,7 +9657,7 @@
         <v>555353</v>
       </c>
     </row>
-    <row r="154" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:5" ht="17" thickBot="1">
       <c r="A154" s="11">
         <v>40887</v>
       </c>
@@ -9660,7 +9675,7 @@
         <v>538299</v>
       </c>
     </row>
-    <row r="155" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:5" ht="17" thickBot="1">
       <c r="A155" s="11">
         <v>40894</v>
       </c>
@@ -9678,7 +9693,7 @@
         <v>537699</v>
       </c>
     </row>
-    <row r="156" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:5" ht="17" thickBot="1">
       <c r="A156" s="11">
         <v>40901</v>
       </c>
@@ -9696,7 +9711,7 @@
         <v>505089</v>
       </c>
     </row>
-    <row r="157" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="157" spans="1:5" ht="17" thickBot="1">
       <c r="A157" s="11">
         <v>40908</v>
       </c>
@@ -9714,7 +9729,7 @@
         <v>426883</v>
       </c>
     </row>
-    <row r="158" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="158" spans="1:5" ht="17" thickBot="1">
       <c r="A158" s="11">
         <v>40915</v>
       </c>
@@ -9732,7 +9747,7 @@
         <v>468674</v>
       </c>
     </row>
-    <row r="159" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="159" spans="1:5" ht="17" thickBot="1">
       <c r="A159" s="11">
         <v>40922</v>
       </c>
@@ -9750,7 +9765,7 @@
         <v>527651</v>
       </c>
     </row>
-    <row r="160" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="160" spans="1:5" ht="17" thickBot="1">
       <c r="A160" s="11">
         <v>40929</v>
       </c>
@@ -9768,7 +9783,7 @@
         <v>507440</v>
       </c>
     </row>
-    <row r="161" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="161" spans="1:5" ht="17" thickBot="1">
       <c r="A161" s="11">
         <v>40936</v>
       </c>
@@ -9786,7 +9801,7 @@
         <v>518682</v>
       </c>
     </row>
-    <row r="162" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:5" ht="17" thickBot="1">
       <c r="A162" s="11">
         <v>40943</v>
       </c>
@@ -9804,7 +9819,7 @@
         <v>517136</v>
       </c>
     </row>
-    <row r="163" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="163" spans="1:5" ht="17" thickBot="1">
       <c r="A163" s="11">
         <v>40950</v>
       </c>
@@ -9822,7 +9837,7 @@
         <v>506708</v>
       </c>
     </row>
-    <row r="164" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="164" spans="1:5" ht="17" thickBot="1">
       <c r="A164" s="11">
         <v>40957</v>
       </c>
@@ -9840,7 +9855,7 @@
         <v>502992</v>
       </c>
     </row>
-    <row r="165" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="165" spans="1:5" ht="17" thickBot="1">
       <c r="A165" s="11">
         <v>40964</v>
       </c>
@@ -9858,7 +9873,7 @@
         <v>496046</v>
       </c>
     </row>
-    <row r="166" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="166" spans="1:5" ht="17" thickBot="1">
       <c r="A166" s="11">
         <v>40971</v>
       </c>
@@ -9876,7 +9891,7 @@
         <v>510568</v>
       </c>
     </row>
-    <row r="167" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="167" spans="1:5" ht="17" thickBot="1">
       <c r="A167" s="11">
         <v>40978</v>
       </c>
@@ -9894,7 +9909,7 @@
         <v>504767</v>
       </c>
     </row>
-    <row r="168" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="168" spans="1:5" ht="17" thickBot="1">
       <c r="A168" s="11">
         <v>40985</v>
       </c>
@@ -9912,7 +9927,7 @@
         <v>505558</v>
       </c>
     </row>
-    <row r="169" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="169" spans="1:5" ht="17" thickBot="1">
       <c r="A169" s="11">
         <v>40992</v>
       </c>
@@ -9930,7 +9945,7 @@
         <v>510794</v>
       </c>
     </row>
-    <row r="170" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="170" spans="1:5" ht="17" thickBot="1">
       <c r="A170" s="11">
         <v>40999</v>
       </c>
@@ -9948,7 +9963,7 @@
         <v>529734</v>
       </c>
     </row>
-    <row r="171" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="171" spans="1:5" ht="17" thickBot="1">
       <c r="A171" s="11">
         <v>41006</v>
       </c>
@@ -9966,7 +9981,7 @@
         <v>502127</v>
       </c>
     </row>
-    <row r="172" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="172" spans="1:5" ht="17" thickBot="1">
       <c r="A172" s="11">
         <v>41013</v>
       </c>
@@ -9984,7 +9999,7 @@
         <v>510946</v>
       </c>
     </row>
-    <row r="173" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="173" spans="1:5" ht="17" thickBot="1">
       <c r="A173" s="11">
         <v>41020</v>
       </c>
@@ -10002,7 +10017,7 @@
         <v>521538</v>
       </c>
     </row>
-    <row r="174" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="174" spans="1:5" ht="17" thickBot="1">
       <c r="A174" s="11">
         <v>41027</v>
       </c>
@@ -10020,7 +10035,7 @@
         <v>525445</v>
       </c>
     </row>
-    <row r="175" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="175" spans="1:5" ht="17" thickBot="1">
       <c r="A175" s="11">
         <v>41034</v>
       </c>
@@ -10038,7 +10053,7 @@
         <v>515167</v>
       </c>
     </row>
-    <row r="176" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="176" spans="1:5" ht="17" thickBot="1">
       <c r="A176" s="13">
         <v>41041</v>
       </c>
@@ -10056,7 +10071,7 @@
         <v>518043</v>
       </c>
     </row>
-    <row r="177" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="177" spans="1:5" ht="17" thickBot="1">
       <c r="A177" s="11">
         <v>41048</v>
       </c>
@@ -10074,7 +10089,7 @@
         <v>522229</v>
       </c>
     </row>
-    <row r="178" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="178" spans="1:5" ht="17" thickBot="1">
       <c r="A178" s="11">
         <v>41055</v>
       </c>
@@ -10092,7 +10107,7 @@
         <v>536107</v>
       </c>
     </row>
-    <row r="179" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="179" spans="1:5" ht="17" thickBot="1">
       <c r="A179" s="11">
         <v>41062</v>
       </c>
@@ -10110,7 +10125,7 @@
         <v>479118</v>
       </c>
     </row>
-    <row r="180" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="180" spans="1:5" ht="17" thickBot="1">
       <c r="A180" s="11">
         <v>41069</v>
       </c>
@@ -10128,7 +10143,7 @@
         <v>531835</v>
       </c>
     </row>
-    <row r="181" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="181" spans="1:5" ht="17" thickBot="1">
       <c r="A181" s="11">
         <v>41076</v>
       </c>
@@ -10146,7 +10161,7 @@
         <v>537011</v>
       </c>
     </row>
-    <row r="182" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="182" spans="1:5" ht="17" thickBot="1">
       <c r="A182" s="11">
         <v>41083</v>
       </c>
@@ -10164,7 +10179,7 @@
         <v>534858</v>
       </c>
     </row>
-    <row r="183" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="183" spans="1:5" ht="17" thickBot="1">
       <c r="A183" s="11">
         <v>41090</v>
       </c>
@@ -10182,7 +10197,7 @@
         <v>532131</v>
       </c>
     </row>
-    <row r="184" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="184" spans="1:5" ht="17" thickBot="1">
       <c r="A184" s="11">
         <v>41097</v>
       </c>
@@ -10200,7 +10215,7 @@
         <v>446518</v>
       </c>
     </row>
-    <row r="185" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="185" spans="1:5" ht="17" thickBot="1">
       <c r="A185" s="11">
         <v>41104</v>
       </c>
@@ -10218,7 +10233,7 @@
         <v>532071</v>
       </c>
     </row>
-    <row r="186" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="186" spans="1:5" ht="17" thickBot="1">
       <c r="A186" s="11">
         <v>41111</v>
       </c>
@@ -10236,7 +10251,7 @@
         <v>532729</v>
       </c>
     </row>
-    <row r="187" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="187" spans="1:5" ht="17" thickBot="1">
       <c r="A187" s="11">
         <v>41118</v>
       </c>
@@ -10254,7 +10269,7 @@
         <v>538486</v>
       </c>
     </row>
-    <row r="188" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="188" spans="1:5" ht="17" thickBot="1">
       <c r="A188" s="11">
         <v>41125</v>
       </c>
@@ -10272,7 +10287,7 @@
         <v>531490</v>
       </c>
     </row>
-    <row r="189" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="189" spans="1:5" ht="17" thickBot="1">
       <c r="A189" s="11">
         <v>41132</v>
       </c>
@@ -10290,7 +10305,7 @@
         <v>532202</v>
       </c>
     </row>
-    <row r="190" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="190" spans="1:5" ht="17" thickBot="1">
       <c r="A190" s="11">
         <v>41139</v>
       </c>
@@ -10308,7 +10323,7 @@
         <v>541140</v>
       </c>
     </row>
-    <row r="191" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="191" spans="1:5" ht="17" thickBot="1">
       <c r="A191" s="11">
         <v>41146</v>
       </c>
@@ -10326,7 +10341,7 @@
         <v>545406</v>
       </c>
     </row>
-    <row r="192" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="192" spans="1:5" ht="17" thickBot="1">
       <c r="A192" s="11">
         <v>41153</v>
       </c>
@@ -10344,7 +10359,7 @@
         <v>541845</v>
       </c>
     </row>
-    <row r="193" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="193" spans="1:5" ht="17" thickBot="1">
       <c r="A193" s="11">
         <v>41160</v>
       </c>
@@ -10362,7 +10377,7 @@
         <v>486818</v>
       </c>
     </row>
-    <row r="194" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="194" spans="1:5" ht="17" thickBot="1">
       <c r="A194" s="11">
         <v>41167</v>
       </c>
@@ -10395,7 +10410,7 @@
         <v>543250</v>
       </c>
     </row>
-    <row r="195" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="195" spans="1:5" ht="17" thickBot="1">
       <c r="A195" s="11">
         <v>41174</v>
       </c>
@@ -10413,7 +10428,7 @@
         <v>542897</v>
       </c>
     </row>
-    <row r="196" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="196" spans="1:5" ht="17" thickBot="1">
       <c r="A196" s="11">
         <v>41181</v>
       </c>
@@ -10431,7 +10446,7 @@
         <v>552468</v>
       </c>
     </row>
-    <row r="197" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="197" spans="1:5" ht="17" thickBot="1">
       <c r="A197" s="11">
         <v>41188</v>
       </c>
@@ -10449,7 +10464,7 @@
         <v>534553</v>
       </c>
     </row>
-    <row r="198" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="198" spans="1:5" ht="17" thickBot="1">
       <c r="A198" s="11">
         <v>41195</v>
       </c>
@@ -10467,7 +10482,7 @@
         <v>535915</v>
       </c>
     </row>
-    <row r="199" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="199" spans="1:5" ht="17" thickBot="1">
       <c r="A199" s="11">
         <v>41202</v>
       </c>
@@ -10485,7 +10500,7 @@
         <v>542674</v>
       </c>
     </row>
-    <row r="200" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="200" spans="1:5" ht="17" thickBot="1">
       <c r="A200" s="11">
         <v>41209</v>
       </c>
@@ -10503,7 +10518,7 @@
         <v>540290</v>
       </c>
     </row>
-    <row r="201" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="201" spans="1:5" ht="17" thickBot="1">
       <c r="A201" s="13">
         <v>41216</v>
       </c>
@@ -10521,7 +10536,7 @@
         <v>502697</v>
       </c>
     </row>
-    <row r="202" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="202" spans="1:5" ht="17" thickBot="1">
       <c r="A202" s="11">
         <v>41223</v>
       </c>
@@ -10539,7 +10554,7 @@
         <v>532945</v>
       </c>
     </row>
-    <row r="203" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="203" spans="1:5" ht="17" thickBot="1">
       <c r="A203" s="11">
         <v>41230</v>
       </c>
@@ -10557,7 +10572,7 @@
         <v>537832</v>
       </c>
     </row>
-    <row r="204" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="204" spans="1:5" ht="17" thickBot="1">
       <c r="A204" s="11">
         <v>41237</v>
       </c>
@@ -10575,7 +10590,7 @@
         <v>447469</v>
       </c>
     </row>
-    <row r="205" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="205" spans="1:5" ht="17" thickBot="1">
       <c r="A205" s="11">
         <v>41244</v>
       </c>
@@ -10593,7 +10608,7 @@
         <v>547119</v>
       </c>
     </row>
-    <row r="206" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="206" spans="1:5" ht="17" thickBot="1">
       <c r="A206" s="11">
         <v>41251</v>
       </c>
@@ -10611,7 +10626,7 @@
         <v>532304</v>
       </c>
     </row>
-    <row r="207" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="207" spans="1:5" ht="17" thickBot="1">
       <c r="A207" s="11">
         <v>41258</v>
       </c>
@@ -10629,7 +10644,7 @@
         <v>544625</v>
       </c>
     </row>
-    <row r="208" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="208" spans="1:5" ht="17" thickBot="1">
       <c r="A208" s="11">
         <v>41265</v>
       </c>
@@ -10647,7 +10662,7 @@
         <v>530342</v>
       </c>
     </row>
-    <row r="209" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="209" spans="1:5" ht="17" thickBot="1">
       <c r="A209" s="11">
         <v>41272</v>
       </c>
@@ -10665,7 +10680,7 @@
         <v>367721</v>
       </c>
     </row>
-    <row r="210" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="210" spans="1:5" ht="17" thickBot="1">
       <c r="A210" s="11">
         <v>41279</v>
       </c>
@@ -10683,7 +10698,7 @@
         <v>419999</v>
       </c>
     </row>
-    <row r="211" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="211" spans="1:5" ht="17" thickBot="1">
       <c r="A211" s="11">
         <v>41286</v>
       </c>
@@ -10701,7 +10716,7 @@
         <v>532789</v>
       </c>
     </row>
-    <row r="212" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="212" spans="1:5" ht="17" thickBot="1">
       <c r="A212" s="11">
         <v>41293</v>
       </c>
@@ -10719,7 +10734,7 @@
         <v>526887</v>
       </c>
     </row>
-    <row r="213" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="213" spans="1:5" ht="17" thickBot="1">
       <c r="A213" s="11">
         <v>41300</v>
       </c>
@@ -10737,7 +10752,7 @@
         <v>504628</v>
       </c>
     </row>
-    <row r="214" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="214" spans="1:5" ht="17" thickBot="1">
       <c r="A214" s="11">
         <v>41307</v>
       </c>
@@ -10755,7 +10770,7 @@
         <v>523931</v>
       </c>
     </row>
-    <row r="215" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="215" spans="1:5" ht="17" thickBot="1">
       <c r="A215" s="11">
         <v>41314</v>
       </c>
@@ -10773,7 +10788,7 @@
         <v>518048</v>
       </c>
     </row>
-    <row r="216" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="216" spans="1:5" ht="17" thickBot="1">
       <c r="A216" s="11">
         <v>41321</v>
       </c>
@@ -10791,7 +10806,7 @@
         <v>529674</v>
       </c>
     </row>
-    <row r="217" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="217" spans="1:5" ht="17" thickBot="1">
       <c r="A217" s="11">
         <v>41328</v>
       </c>
@@ -10809,7 +10824,7 @@
         <v>516142</v>
       </c>
     </row>
-    <row r="218" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="218" spans="1:5" ht="17" thickBot="1">
       <c r="A218" s="11">
         <v>41335</v>
       </c>
@@ -10827,7 +10842,7 @@
         <v>533057</v>
       </c>
     </row>
-    <row r="219" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="219" spans="1:5" ht="17" thickBot="1">
       <c r="A219" s="11">
         <v>41342</v>
       </c>
@@ -10845,7 +10860,7 @@
         <v>511872</v>
       </c>
     </row>
-    <row r="220" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="220" spans="1:5" ht="17" thickBot="1">
       <c r="A220" s="11">
         <v>41349</v>
       </c>
@@ -10863,7 +10878,7 @@
         <v>509430</v>
       </c>
     </row>
-    <row r="221" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="221" spans="1:5" ht="17" thickBot="1">
       <c r="A221" s="11">
         <v>41356</v>
       </c>
@@ -10881,7 +10896,7 @@
         <v>514379</v>
       </c>
     </row>
-    <row r="222" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="222" spans="1:5" ht="17" thickBot="1">
       <c r="A222" s="11">
         <v>41363</v>
       </c>
@@ -10899,7 +10914,7 @@
         <v>514954</v>
       </c>
     </row>
-    <row r="223" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="223" spans="1:5" ht="17" thickBot="1">
       <c r="A223" s="11">
         <v>41370</v>
       </c>
@@ -10917,7 +10932,7 @@
         <v>512396</v>
       </c>
     </row>
-    <row r="224" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="224" spans="1:5" ht="17" thickBot="1">
       <c r="A224" s="11">
         <v>41377</v>
       </c>
@@ -10935,7 +10950,7 @@
         <v>517662</v>
       </c>
     </row>
-    <row r="225" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="225" spans="1:5" ht="17" thickBot="1">
       <c r="A225" s="11">
         <v>41384</v>
       </c>
@@ -10953,7 +10968,7 @@
         <v>517360</v>
       </c>
     </row>
-    <row r="226" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="226" spans="1:5" ht="17" thickBot="1">
       <c r="A226" s="13">
         <v>41391</v>
       </c>
@@ -10971,7 +10986,7 @@
         <v>523207</v>
       </c>
     </row>
-    <row r="227" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="227" spans="1:5" ht="17" thickBot="1">
       <c r="A227" s="11">
         <v>41398</v>
       </c>
@@ -10989,7 +11004,7 @@
         <v>529594</v>
       </c>
     </row>
-    <row r="228" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="228" spans="1:5" ht="17" thickBot="1">
       <c r="A228" s="11">
         <v>41405</v>
       </c>
@@ -11007,7 +11022,7 @@
         <v>529252</v>
       </c>
     </row>
-    <row r="229" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="229" spans="1:5" ht="17" thickBot="1">
       <c r="A229" s="11">
         <v>41412</v>
       </c>
@@ -11025,7 +11040,7 @@
         <v>535835</v>
       </c>
     </row>
-    <row r="230" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="230" spans="1:5" ht="17" thickBot="1">
       <c r="A230" s="11">
         <v>41419</v>
       </c>
@@ -11043,7 +11058,7 @@
         <v>529937</v>
       </c>
     </row>
-    <row r="231" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="231" spans="1:5" ht="17" thickBot="1">
       <c r="A231" s="11">
         <v>41426</v>
       </c>
@@ -11061,7 +11076,7 @@
         <v>491082</v>
       </c>
     </row>
-    <row r="232" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="232" spans="1:5" ht="17" thickBot="1">
       <c r="A232" s="11">
         <v>41433</v>
       </c>
@@ -11079,7 +11094,7 @@
         <v>530890</v>
       </c>
     </row>
-    <row r="233" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="233" spans="1:5" ht="17" thickBot="1">
       <c r="A233" s="11">
         <v>41440</v>
       </c>
@@ -11097,7 +11112,7 @@
         <v>543145</v>
       </c>
     </row>
-    <row r="234" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="234" spans="1:5" ht="17" thickBot="1">
       <c r="A234" s="11">
         <v>41447</v>
       </c>
@@ -11115,7 +11130,7 @@
         <v>541031</v>
       </c>
     </row>
-    <row r="235" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="235" spans="1:5" ht="17" thickBot="1">
       <c r="A235" s="11">
         <v>41454</v>
       </c>
@@ -11133,7 +11148,7 @@
         <v>531040</v>
       </c>
     </row>
-    <row r="236" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="236" spans="1:5" ht="17" thickBot="1">
       <c r="A236" s="11">
         <v>41461</v>
       </c>
@@ -11151,7 +11166,7 @@
         <v>453493</v>
       </c>
     </row>
-    <row r="237" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="237" spans="1:5" ht="17" thickBot="1">
       <c r="A237" s="11">
         <v>41468</v>
       </c>
@@ -11169,7 +11184,7 @@
         <v>525333</v>
       </c>
     </row>
-    <row r="238" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="238" spans="1:5" ht="17" thickBot="1">
       <c r="A238" s="11">
         <v>41475</v>
       </c>
@@ -11187,7 +11202,7 @@
         <v>531357</v>
       </c>
     </row>
-    <row r="239" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="239" spans="1:5" ht="17" thickBot="1">
       <c r="A239" s="11">
         <v>41482</v>
       </c>
@@ -11205,7 +11220,7 @@
         <v>551911</v>
       </c>
     </row>
-    <row r="240" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="240" spans="1:5" ht="17" thickBot="1">
       <c r="A240" s="11">
         <v>41489</v>
       </c>
@@ -11223,7 +11238,7 @@
         <v>542396</v>
       </c>
     </row>
-    <row r="241" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="241" spans="1:5" ht="17" thickBot="1">
       <c r="A241" s="11">
         <v>41496</v>
       </c>
@@ -11241,7 +11256,7 @@
         <v>546772</v>
       </c>
     </row>
-    <row r="242" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="242" spans="1:5" ht="17" thickBot="1">
       <c r="A242" s="11">
         <v>41503</v>
       </c>
@@ -11259,7 +11274,7 @@
         <v>552359</v>
       </c>
     </row>
-    <row r="243" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="243" spans="1:5" ht="17" thickBot="1">
       <c r="A243" s="11">
         <v>41510</v>
       </c>
@@ -11277,7 +11292,7 @@
         <v>548969</v>
       </c>
     </row>
-    <row r="244" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="244" spans="1:5" ht="17" thickBot="1">
       <c r="A244" s="11">
         <v>41517</v>
       </c>
@@ -11295,7 +11310,7 @@
         <v>561698</v>
       </c>
     </row>
-    <row r="245" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="245" spans="1:5" ht="17" thickBot="1">
       <c r="A245" s="11">
         <v>41524</v>
       </c>
@@ -11313,7 +11328,7 @@
         <v>507493</v>
       </c>
     </row>
-    <row r="246" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="246" spans="1:5" ht="17" thickBot="1">
       <c r="A246" s="11">
         <v>41531</v>
       </c>
@@ -11331,7 +11346,7 @@
         <v>562094</v>
       </c>
     </row>
-    <row r="247" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="247" spans="1:5" ht="17" thickBot="1">
       <c r="A247" s="11">
         <v>41538</v>
       </c>
@@ -11349,7 +11364,7 @@
         <v>551057</v>
       </c>
     </row>
-    <row r="248" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="248" spans="1:5" ht="17" thickBot="1">
       <c r="A248" s="11">
         <v>41545</v>
       </c>
@@ -11367,7 +11382,7 @@
         <v>566662</v>
       </c>
     </row>
-    <row r="249" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="249" spans="1:5" ht="17" thickBot="1">
       <c r="A249" s="11">
         <v>41552</v>
       </c>
@@ -11385,7 +11400,7 @@
         <v>545708</v>
       </c>
     </row>
-    <row r="250" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="250" spans="1:5" ht="17" thickBot="1">
       <c r="A250" s="11">
         <v>41559</v>
       </c>
@@ -11403,7 +11418,7 @@
         <v>546211</v>
       </c>
     </row>
-    <row r="251" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="251" spans="1:5" ht="17" thickBot="1">
       <c r="A251" s="13">
         <v>41566</v>
       </c>
@@ -11421,7 +11436,7 @@
         <v>553943</v>
       </c>
     </row>
-    <row r="252" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="252" spans="1:5" ht="17" thickBot="1">
       <c r="A252" s="11">
         <v>41573</v>
       </c>
@@ -11439,7 +11454,7 @@
         <v>558686</v>
       </c>
     </row>
-    <row r="253" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="253" spans="1:5" ht="17" thickBot="1">
       <c r="A253" s="11">
         <v>41580</v>
       </c>
@@ -11457,7 +11472,7 @@
         <v>556662</v>
       </c>
     </row>
-    <row r="254" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="254" spans="1:5" ht="17" thickBot="1">
       <c r="A254" s="11">
         <v>41587</v>
       </c>
@@ -11475,7 +11490,7 @@
         <v>562840</v>
       </c>
     </row>
-    <row r="255" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="255" spans="1:5" ht="17" thickBot="1">
       <c r="A255" s="11">
         <v>41594</v>
       </c>
@@ -11493,7 +11508,7 @@
         <v>562206</v>
       </c>
     </row>
-    <row r="256" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="256" spans="1:5" ht="17" thickBot="1">
       <c r="A256" s="11">
         <v>41601</v>
       </c>
@@ -11511,7 +11526,7 @@
         <v>564340</v>
       </c>
     </row>
-    <row r="257" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="257" spans="1:5" ht="17" thickBot="1">
       <c r="A257" s="11">
         <v>41608</v>
       </c>
@@ -11529,7 +11544,7 @@
         <v>463516</v>
       </c>
     </row>
-    <row r="258" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="258" spans="1:5" ht="17" thickBot="1">
       <c r="A258" s="11">
         <v>41615</v>
       </c>
@@ -11562,7 +11577,7 @@
         <v>541978</v>
       </c>
     </row>
-    <row r="259" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="259" spans="1:5" ht="17" thickBot="1">
       <c r="A259" s="11">
         <v>41622</v>
       </c>
@@ -11580,7 +11595,7 @@
         <v>546825</v>
       </c>
     </row>
-    <row r="260" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="260" spans="1:5" ht="17" thickBot="1">
       <c r="A260" s="11">
         <v>41629</v>
       </c>
@@ -11598,7 +11613,7 @@
         <v>544984</v>
       </c>
     </row>
-    <row r="261" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="261" spans="1:5" ht="17" thickBot="1">
       <c r="A261" s="11">
         <v>41636</v>
       </c>
@@ -11616,7 +11631,7 @@
         <v>403329</v>
       </c>
     </row>
-    <row r="262" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="262" spans="1:5" ht="17" thickBot="1">
       <c r="A262" s="11">
         <v>41643</v>
       </c>
@@ -11634,7 +11649,7 @@
         <v>433724</v>
       </c>
     </row>
-    <row r="263" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="263" spans="1:5" ht="17" thickBot="1">
       <c r="A263" s="11">
         <v>41650</v>
       </c>
@@ -11652,7 +11667,7 @@
         <v>492836</v>
       </c>
     </row>
-    <row r="264" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="264" spans="1:5" ht="17" thickBot="1">
       <c r="A264" s="11">
         <v>41657</v>
       </c>
@@ -11670,7 +11685,7 @@
         <v>557253</v>
       </c>
     </row>
-    <row r="265" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="265" spans="1:5" ht="17" thickBot="1">
       <c r="A265" s="11">
         <v>41664</v>
       </c>
@@ -11688,7 +11703,7 @@
         <v>526644</v>
       </c>
     </row>
-    <row r="266" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="266" spans="1:5" ht="17" thickBot="1">
       <c r="A266" s="11">
         <v>41671</v>
       </c>
@@ -11706,7 +11721,7 @@
         <v>518012</v>
       </c>
     </row>
-    <row r="267" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="267" spans="1:5" ht="17" thickBot="1">
       <c r="A267" s="11">
         <v>41678</v>
       </c>
@@ -11724,7 +11739,7 @@
         <v>507368</v>
       </c>
     </row>
-    <row r="268" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="268" spans="1:5" ht="17" thickBot="1">
       <c r="A268" s="11">
         <v>41685</v>
       </c>
@@ -11742,7 +11757,7 @@
         <v>507257</v>
       </c>
     </row>
-    <row r="269" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="269" spans="1:5" ht="17" thickBot="1">
       <c r="A269" s="11">
         <v>41692</v>
       </c>
@@ -11760,7 +11775,7 @@
         <v>535036</v>
       </c>
     </row>
-    <row r="270" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="270" spans="1:5" ht="17" thickBot="1">
       <c r="A270" s="11">
         <v>41699</v>
       </c>
@@ -11778,7 +11793,7 @@
         <v>545004</v>
       </c>
     </row>
-    <row r="271" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="271" spans="1:5" ht="17" thickBot="1">
       <c r="A271" s="11">
         <v>41706</v>
       </c>
@@ -11796,7 +11811,7 @@
         <v>518495</v>
       </c>
     </row>
-    <row r="272" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="272" spans="1:5" ht="17" thickBot="1">
       <c r="A272" s="11">
         <v>41713</v>
       </c>
@@ -11814,7 +11829,7 @@
         <v>545366</v>
       </c>
     </row>
-    <row r="273" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="273" spans="1:5" ht="17" thickBot="1">
       <c r="A273" s="11">
         <v>41720</v>
       </c>
@@ -11832,7 +11847,7 @@
         <v>552238</v>
       </c>
     </row>
-    <row r="274" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="274" spans="1:5" ht="17" thickBot="1">
       <c r="A274" s="11">
         <v>41727</v>
       </c>
@@ -11850,7 +11865,7 @@
         <v>566505</v>
       </c>
     </row>
-    <row r="275" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="275" spans="1:5" ht="17" thickBot="1">
       <c r="A275" s="11">
         <v>41734</v>
       </c>
@@ -11868,7 +11883,7 @@
         <v>557123</v>
       </c>
     </row>
-    <row r="276" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="276" spans="1:5" ht="17" thickBot="1">
       <c r="A276" s="13">
         <v>41741</v>
       </c>
@@ -11886,7 +11901,7 @@
         <v>559676</v>
       </c>
     </row>
-    <row r="277" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="277" spans="1:5" ht="17" thickBot="1">
       <c r="A277" s="11">
         <v>41748</v>
       </c>
@@ -11904,7 +11919,7 @@
         <v>549826</v>
       </c>
     </row>
-    <row r="278" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="278" spans="1:5" ht="17" thickBot="1">
       <c r="A278" s="11">
         <v>41755</v>
       </c>
@@ -11922,7 +11937,7 @@
         <v>566336</v>
       </c>
     </row>
-    <row r="279" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="279" spans="1:5" ht="17" thickBot="1">
       <c r="A279" s="11">
         <v>41762</v>
       </c>
@@ -11940,7 +11955,7 @@
         <v>564801</v>
       </c>
     </row>
-    <row r="280" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="280" spans="1:5" ht="17" thickBot="1">
       <c r="A280" s="11">
         <v>41769</v>
       </c>
@@ -11958,7 +11973,7 @@
         <v>564096</v>
       </c>
     </row>
-    <row r="281" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="281" spans="1:5" ht="17" thickBot="1">
       <c r="A281" s="11">
         <v>41783</v>
       </c>
@@ -11976,7 +11991,7 @@
         <v>570380</v>
       </c>
     </row>
-    <row r="282" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="282" spans="1:5" ht="17" thickBot="1">
       <c r="A282" s="11">
         <v>41790</v>
       </c>
@@ -11994,7 +12009,7 @@
         <v>531725</v>
       </c>
     </row>
-    <row r="283" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="283" spans="1:5" ht="17" thickBot="1">
       <c r="A283" s="11">
         <v>41797</v>
       </c>
@@ -12012,7 +12027,7 @@
         <v>562747</v>
       </c>
     </row>
-    <row r="284" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="284" spans="1:5" ht="17" thickBot="1">
       <c r="A284" s="11">
         <v>41804</v>
       </c>
@@ -12030,7 +12045,7 @@
         <v>565375</v>
       </c>
     </row>
-    <row r="285" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="285" spans="1:5" ht="17" thickBot="1">
       <c r="A285" s="11">
         <v>41811</v>
       </c>
@@ -12048,7 +12063,7 @@
         <v>563695</v>
       </c>
     </row>
-    <row r="286" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="286" spans="1:5" ht="17" thickBot="1">
       <c r="A286" s="11">
         <v>41818</v>
       </c>
@@ -12066,7 +12081,7 @@
         <v>563223</v>
       </c>
     </row>
-    <row r="287" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="287" spans="1:5" ht="17" thickBot="1">
       <c r="A287" s="11">
         <v>41825</v>
       </c>
@@ -12084,7 +12099,7 @@
         <v>497828</v>
       </c>
     </row>
-    <row r="288" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="288" spans="1:5" ht="17" thickBot="1">
       <c r="A288" s="11">
         <v>41832</v>
       </c>
@@ -12102,7 +12117,7 @@
         <v>546863</v>
       </c>
     </row>
-    <row r="289" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="289" spans="1:5" ht="17" thickBot="1">
       <c r="A289" s="11">
         <v>41839</v>
       </c>
@@ -12120,7 +12135,7 @@
         <v>566931</v>
       </c>
     </row>
-    <row r="290" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="290" spans="1:5" ht="17" thickBot="1">
       <c r="A290" s="11">
         <v>41846</v>
       </c>
@@ -12138,7 +12153,7 @@
         <v>571797</v>
       </c>
     </row>
-    <row r="291" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="291" spans="1:5" ht="17" thickBot="1">
       <c r="A291" s="11">
         <v>41853</v>
       </c>
@@ -12156,7 +12171,7 @@
         <v>574552</v>
       </c>
     </row>
-    <row r="292" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="292" spans="1:5" ht="17" thickBot="1">
       <c r="A292" s="11">
         <v>41860</v>
       </c>
@@ -12174,7 +12189,7 @@
         <v>567908</v>
       </c>
     </row>
-    <row r="293" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="293" spans="1:5" ht="17" thickBot="1">
       <c r="A293" s="11">
         <v>41867</v>
       </c>
@@ -12192,7 +12207,7 @@
         <v>574592</v>
       </c>
     </row>
-    <row r="294" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="294" spans="1:5" ht="17" thickBot="1">
       <c r="A294" s="11">
         <v>41874</v>
       </c>
@@ -12210,7 +12225,7 @@
         <v>566266</v>
       </c>
     </row>
-    <row r="295" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="295" spans="1:5" ht="17" thickBot="1">
       <c r="A295" s="11">
         <v>41881</v>
       </c>
@@ -12228,7 +12243,7 @@
         <v>579209</v>
       </c>
     </row>
-    <row r="296" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="296" spans="1:5" ht="17" thickBot="1">
       <c r="A296" s="11">
         <v>41888</v>
       </c>
@@ -12246,7 +12261,7 @@
         <v>525144</v>
       </c>
     </row>
-    <row r="297" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="297" spans="1:5" ht="17" thickBot="1">
       <c r="A297" s="11">
         <v>41895</v>
       </c>
@@ -12264,7 +12279,7 @@
         <v>579440</v>
       </c>
     </row>
-    <row r="298" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="298" spans="1:5" ht="17" thickBot="1">
       <c r="A298" s="11">
         <v>41902</v>
       </c>
@@ -12282,7 +12297,7 @@
         <v>581955</v>
       </c>
     </row>
-    <row r="299" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="299" spans="1:5" ht="17" thickBot="1">
       <c r="A299" s="11">
         <v>41909</v>
       </c>
@@ -12300,7 +12315,7 @@
         <v>576934</v>
       </c>
     </row>
-    <row r="300" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="300" spans="1:5" ht="17" thickBot="1">
       <c r="A300" s="11">
         <v>41916</v>
       </c>
@@ -12318,7 +12333,7 @@
         <v>576356</v>
       </c>
     </row>
-    <row r="301" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="301" spans="1:5" ht="17" thickBot="1">
       <c r="A301" s="13">
         <v>41923</v>
       </c>
@@ -12336,7 +12351,7 @@
         <v>571812</v>
       </c>
     </row>
-    <row r="302" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="302" spans="1:5" ht="17" thickBot="1">
       <c r="A302" s="11">
         <v>41930</v>
       </c>
@@ -12354,7 +12369,7 @@
         <v>569684</v>
       </c>
     </row>
-    <row r="303" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="303" spans="1:5" ht="17" thickBot="1">
       <c r="A303" s="11">
         <v>41937</v>
       </c>
@@ -12372,7 +12387,7 @@
         <v>586115</v>
       </c>
     </row>
-    <row r="304" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="304" spans="1:5" ht="17" thickBot="1">
       <c r="A304" s="11">
         <v>41944</v>
       </c>
@@ -12390,7 +12405,7 @@
         <v>585208</v>
       </c>
     </row>
-    <row r="305" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="305" spans="1:5" ht="17" thickBot="1">
       <c r="A305" s="11">
         <v>41951</v>
       </c>
@@ -12408,7 +12423,7 @@
         <v>568807</v>
       </c>
     </row>
-    <row r="306" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="306" spans="1:5" ht="17" thickBot="1">
       <c r="A306" s="11">
         <v>41958</v>
       </c>
@@ -12426,7 +12441,7 @@
         <v>570350</v>
       </c>
     </row>
-    <row r="307" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="307" spans="1:5" ht="17" thickBot="1">
       <c r="A307" s="11">
         <v>41965</v>
       </c>
@@ -12444,7 +12459,7 @@
         <v>565185</v>
       </c>
     </row>
-    <row r="308" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="308" spans="1:5" ht="17" thickBot="1">
       <c r="A308" s="11">
         <v>41972</v>
       </c>
@@ -12462,7 +12477,7 @@
         <v>492532</v>
       </c>
     </row>
-    <row r="309" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="309" spans="1:5" ht="17" thickBot="1">
       <c r="A309" s="11">
         <v>41979</v>
       </c>
@@ -12480,7 +12495,7 @@
         <v>580108</v>
       </c>
     </row>
-    <row r="310" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="310" spans="1:5" ht="17" thickBot="1">
       <c r="A310" s="11">
         <v>41986</v>
       </c>
@@ -12498,7 +12513,7 @@
         <v>592608</v>
       </c>
     </row>
-    <row r="311" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="311" spans="1:5" ht="17" thickBot="1">
       <c r="A311" s="11">
         <v>41993</v>
       </c>
@@ -12516,7 +12531,7 @@
         <v>580559</v>
       </c>
     </row>
-    <row r="312" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="312" spans="1:5" ht="17" thickBot="1">
       <c r="A312" s="11">
         <v>42000</v>
       </c>
@@ -12534,7 +12549,7 @@
         <v>433338</v>
       </c>
     </row>
-    <row r="313" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="313" spans="1:5" ht="17" thickBot="1">
       <c r="A313" s="11">
         <v>42007</v>
       </c>
@@ -12552,7 +12567,7 @@
         <v>446201</v>
       </c>
     </row>
-    <row r="314" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="314" spans="1:5" ht="17" thickBot="1">
       <c r="A314" s="11">
         <v>42014</v>
       </c>
@@ -12570,7 +12585,7 @@
         <v>517520</v>
       </c>
     </row>
-    <row r="315" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="315" spans="1:5" ht="17" thickBot="1">
       <c r="A315" s="11">
         <v>42021</v>
       </c>
@@ -12588,7 +12603,7 @@
         <v>551856</v>
       </c>
     </row>
-    <row r="316" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="316" spans="1:5" ht="17" thickBot="1">
       <c r="A316" s="11">
         <v>42028</v>
       </c>
@@ -12606,7 +12621,7 @@
         <v>548055</v>
       </c>
     </row>
-    <row r="317" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="317" spans="1:5" ht="17" thickBot="1">
       <c r="A317" s="11">
         <v>42035</v>
       </c>
@@ -12624,7 +12639,7 @@
         <v>548478</v>
       </c>
     </row>
-    <row r="318" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="318" spans="1:5" ht="17" thickBot="1">
       <c r="A318" s="11">
         <v>42042</v>
       </c>
@@ -12642,7 +12657,7 @@
         <v>511563</v>
       </c>
     </row>
-    <row r="319" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="319" spans="1:5" ht="17" thickBot="1">
       <c r="A319" s="11">
         <v>42049</v>
       </c>
@@ -12660,7 +12675,7 @@
         <v>525224</v>
       </c>
     </row>
-    <row r="320" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="320" spans="1:5" ht="17" thickBot="1">
       <c r="A320" s="11">
         <v>42056</v>
       </c>
@@ -12678,7 +12693,7 @@
         <v>473161</v>
       </c>
     </row>
-    <row r="321" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="321" spans="1:5" ht="17" thickBot="1">
       <c r="A321" s="11">
         <v>42063</v>
       </c>
@@ -12696,7 +12711,7 @@
         <v>508658</v>
       </c>
     </row>
-    <row r="322" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="322" spans="1:5" ht="17" thickBot="1">
       <c r="A322" s="11">
         <v>42070</v>
       </c>
@@ -12729,7 +12744,7 @@
         <v>522382</v>
       </c>
     </row>
-    <row r="323" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="323" spans="1:5" ht="17" thickBot="1">
       <c r="A323" s="11">
         <v>42077</v>
       </c>
@@ -12747,7 +12762,7 @@
         <v>553031</v>
       </c>
     </row>
-    <row r="324" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="324" spans="1:5" ht="17" thickBot="1">
       <c r="A324" s="11">
         <v>42084</v>
       </c>
@@ -12765,7 +12780,7 @@
         <v>562472</v>
       </c>
     </row>
-    <row r="325" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="325" spans="1:5" ht="17" thickBot="1">
       <c r="A325" s="11">
         <v>42091</v>
       </c>
@@ -12783,7 +12798,7 @@
         <v>563280</v>
       </c>
     </row>
-    <row r="326" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="326" spans="1:5" ht="17" thickBot="1">
       <c r="A326" s="13">
         <v>42098</v>
       </c>
@@ -12801,7 +12816,7 @@
         <v>549021</v>
       </c>
     </row>
-    <row r="327" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="327" spans="1:5" ht="17" thickBot="1">
       <c r="A327" s="11">
         <v>42105</v>
       </c>
@@ -12819,7 +12834,7 @@
         <v>557812</v>
       </c>
     </row>
-    <row r="328" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="328" spans="1:5" ht="17" thickBot="1">
       <c r="A328" s="11">
         <v>42112</v>
       </c>
@@ -12837,7 +12852,7 @@
         <v>556432</v>
       </c>
     </row>
-    <row r="329" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="329" spans="1:5" ht="17" thickBot="1">
       <c r="A329" s="11">
         <v>42119</v>
       </c>
@@ -12855,7 +12870,7 @@
         <v>557306</v>
       </c>
     </row>
-    <row r="330" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="330" spans="1:5" ht="17" thickBot="1">
       <c r="A330" s="11">
         <v>42126</v>
       </c>
@@ -12873,7 +12888,7 @@
         <v>565787</v>
       </c>
     </row>
-    <row r="331" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="331" spans="1:5" ht="17" thickBot="1">
       <c r="A331" s="11">
         <v>42133</v>
       </c>
@@ -12891,7 +12906,7 @@
         <v>551034</v>
       </c>
     </row>
-    <row r="332" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="332" spans="1:5" ht="17" thickBot="1">
       <c r="A332" s="11">
         <v>42140</v>
       </c>
@@ -12909,7 +12924,7 @@
         <v>549199</v>
       </c>
     </row>
-    <row r="333" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="333" spans="1:5" ht="17" thickBot="1">
       <c r="A333" s="11">
         <v>42147</v>
       </c>
@@ -12927,7 +12942,7 @@
         <v>554477</v>
       </c>
     </row>
-    <row r="334" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="334" spans="1:5" ht="17" thickBot="1">
       <c r="A334" s="11">
         <v>42154</v>
       </c>
@@ -12945,7 +12960,7 @@
         <v>505543</v>
       </c>
     </row>
-    <row r="335" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="335" spans="1:5" ht="17" thickBot="1">
       <c r="A335" s="11">
         <v>42161</v>
       </c>
@@ -12963,7 +12978,7 @@
         <v>550037</v>
       </c>
     </row>
-    <row r="336" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="336" spans="1:5" ht="17" thickBot="1">
       <c r="A336" s="11">
         <v>42168</v>
       </c>
@@ -12981,7 +12996,7 @@
         <v>554461</v>
       </c>
     </row>
-    <row r="337" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="337" spans="1:5" ht="17" thickBot="1">
       <c r="A337" s="11">
         <v>42175</v>
       </c>
@@ -12999,7 +13014,7 @@
         <v>550839</v>
       </c>
     </row>
-    <row r="338" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="338" spans="1:5" ht="17" thickBot="1">
       <c r="A338" s="11">
         <v>42182</v>
       </c>
@@ -13017,7 +13032,7 @@
         <v>547969</v>
       </c>
     </row>
-    <row r="339" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="339" spans="1:5" ht="17" thickBot="1">
       <c r="A339" s="11">
         <v>42189</v>
       </c>
@@ -13035,7 +13050,7 @@
         <v>506284</v>
       </c>
     </row>
-    <row r="340" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="340" spans="1:5" ht="17" thickBot="1">
       <c r="A340" s="11">
         <v>42196</v>
       </c>
@@ -13053,7 +13068,7 @@
         <v>534097</v>
       </c>
     </row>
-    <row r="341" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="341" spans="1:5" ht="17" thickBot="1">
       <c r="A341" s="11">
         <v>42203</v>
       </c>
@@ -13071,7 +13086,7 @@
         <v>551181</v>
       </c>
     </row>
-    <row r="342" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="342" spans="1:5" ht="17" thickBot="1">
       <c r="A342" s="11">
         <v>42210</v>
       </c>
@@ -13089,7 +13104,7 @@
         <v>557612</v>
       </c>
     </row>
-    <row r="343" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="343" spans="1:5" ht="17" thickBot="1">
       <c r="A343" s="11">
         <v>42217</v>
       </c>
@@ -13107,7 +13122,7 @@
         <v>559125</v>
       </c>
     </row>
-    <row r="344" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="344" spans="1:5" ht="17" thickBot="1">
       <c r="A344" s="11">
         <v>42224</v>
       </c>
@@ -13125,7 +13140,7 @@
         <v>562884</v>
       </c>
     </row>
-    <row r="345" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="345" spans="1:5" ht="17" thickBot="1">
       <c r="A345" s="11">
         <v>42238</v>
       </c>
@@ -13143,7 +13158,7 @@
         <v>567943</v>
       </c>
     </row>
-    <row r="346" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="346" spans="1:5" ht="17" thickBot="1">
       <c r="A346" s="11">
         <v>42245</v>
       </c>
@@ -13161,7 +13176,7 @@
         <v>575323</v>
       </c>
     </row>
-    <row r="347" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="347" spans="1:5" ht="17" thickBot="1">
       <c r="A347" s="11">
         <v>42252</v>
       </c>
@@ -13179,7 +13194,7 @@
         <v>567206</v>
       </c>
     </row>
-    <row r="348" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="348" spans="1:5" ht="17" thickBot="1">
       <c r="A348" s="11">
         <v>42259</v>
       </c>
@@ -13197,7 +13212,7 @@
         <v>510797</v>
       </c>
     </row>
-    <row r="349" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="349" spans="1:5" ht="17" thickBot="1">
       <c r="A349" s="11">
         <v>42266</v>
       </c>
@@ -13215,7 +13230,7 @@
         <v>566734</v>
       </c>
     </row>
-    <row r="350" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="350" spans="1:5" ht="17" thickBot="1">
       <c r="A350" s="11">
         <v>42273</v>
       </c>
@@ -13233,7 +13248,7 @@
         <v>566700</v>
       </c>
     </row>
-    <row r="351" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="351" spans="1:5" ht="17" thickBot="1">
       <c r="A351" s="13">
         <v>42280</v>
       </c>
@@ -13251,7 +13266,7 @@
         <v>572293</v>
       </c>
     </row>
-    <row r="352" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="352" spans="1:5" ht="17" thickBot="1">
       <c r="A352" s="11">
         <v>42287</v>
       </c>
@@ -13269,7 +13284,7 @@
         <v>556233</v>
       </c>
     </row>
-    <row r="353" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="353" spans="1:5" ht="17" thickBot="1">
       <c r="A353" s="11">
         <v>42294</v>
       </c>
@@ -13287,7 +13302,7 @@
         <v>554696</v>
       </c>
     </row>
-    <row r="354" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="354" spans="1:5" ht="17" thickBot="1">
       <c r="A354" s="11">
         <v>42301</v>
       </c>
@@ -13305,7 +13320,7 @@
         <v>553144</v>
       </c>
     </row>
-    <row r="355" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="355" spans="1:5" ht="17" thickBot="1">
       <c r="A355" s="11">
         <v>42308</v>
       </c>
@@ -13323,7 +13338,7 @@
         <v>549707</v>
       </c>
     </row>
-    <row r="356" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="356" spans="1:5" ht="17" thickBot="1">
       <c r="A356" s="11">
         <v>42315</v>
       </c>
@@ -13341,7 +13356,7 @@
         <v>539165</v>
       </c>
     </row>
-    <row r="357" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="357" spans="1:5" ht="17" thickBot="1">
       <c r="A357" s="11">
         <v>42322</v>
       </c>
@@ -13359,7 +13374,7 @@
         <v>543681</v>
       </c>
     </row>
-    <row r="358" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="358" spans="1:5" ht="17" thickBot="1">
       <c r="A358" s="11">
         <v>42336</v>
       </c>
@@ -13377,7 +13392,7 @@
         <v>450389</v>
       </c>
     </row>
-    <row r="359" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="359" spans="1:5" ht="17" thickBot="1">
       <c r="A359" s="11">
         <v>42343</v>
       </c>
@@ -13395,7 +13410,7 @@
         <v>542050</v>
       </c>
     </row>
-    <row r="360" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="360" spans="1:5" ht="17" thickBot="1">
       <c r="A360" s="11">
         <v>42350</v>
       </c>
@@ -13413,7 +13428,7 @@
         <v>544975</v>
       </c>
     </row>
-    <row r="361" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="361" spans="1:5" ht="17" thickBot="1">
       <c r="A361" s="11">
         <v>42357</v>
       </c>
@@ -13431,7 +13446,7 @@
         <v>525555</v>
       </c>
     </row>
-    <row r="362" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="362" spans="1:5" ht="17" thickBot="1">
       <c r="A362" s="11">
         <v>42364</v>
       </c>
@@ -13449,7 +13464,7 @@
         <v>391107</v>
       </c>
     </row>
-    <row r="363" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="363" spans="1:5" ht="17" thickBot="1">
       <c r="A363" s="11">
         <v>42371</v>
       </c>
@@ -13467,7 +13482,7 @@
         <v>395663</v>
       </c>
     </row>
-    <row r="364" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="364" spans="1:5" ht="17" thickBot="1">
       <c r="A364" s="11">
         <v>42378</v>
       </c>
@@ -13485,7 +13500,7 @@
         <v>498160</v>
       </c>
     </row>
-    <row r="365" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="365" spans="1:5" ht="17" thickBot="1">
       <c r="A365" s="11">
         <v>42385</v>
       </c>
@@ -13503,7 +13518,7 @@
         <v>506433</v>
       </c>
     </row>
-    <row r="366" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="366" spans="1:5" ht="17" thickBot="1">
       <c r="A366" s="11">
         <v>42392</v>
       </c>
@@ -13521,7 +13536,7 @@
         <v>490324</v>
       </c>
     </row>
-    <row r="367" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="367" spans="1:5" ht="17" thickBot="1">
       <c r="A367" s="11">
         <v>42399</v>
       </c>
@@ -13539,7 +13554,7 @@
         <v>512746</v>
       </c>
     </row>
-    <row r="368" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="368" spans="1:5" ht="17" thickBot="1">
       <c r="A368" s="11">
         <v>42406</v>
       </c>
@@ -13557,7 +13572,7 @@
         <v>504510</v>
       </c>
     </row>
-    <row r="369" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="369" spans="1:5" ht="17" thickBot="1">
       <c r="A369" s="11">
         <v>42413</v>
       </c>
@@ -13575,7 +13590,7 @@
         <v>505148</v>
       </c>
     </row>
-    <row r="370" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="370" spans="1:5" ht="17" thickBot="1">
       <c r="A370" s="11">
         <v>42420</v>
       </c>
@@ -13593,7 +13608,7 @@
         <v>497210</v>
       </c>
     </row>
-    <row r="371" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="371" spans="1:5" ht="17" thickBot="1">
       <c r="A371" s="11">
         <v>42427</v>
       </c>
@@ -13611,7 +13626,7 @@
         <v>521300</v>
       </c>
     </row>
-    <row r="372" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="372" spans="1:5" ht="17" thickBot="1">
       <c r="A372" s="11">
         <v>42434</v>
       </c>
@@ -13629,7 +13644,7 @@
         <v>512202</v>
       </c>
     </row>
-    <row r="373" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="373" spans="1:5" ht="17" thickBot="1">
       <c r="A373" s="11">
         <v>42441</v>
       </c>
@@ -13647,7 +13662,7 @@
         <v>489177</v>
       </c>
     </row>
-    <row r="374" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="374" spans="1:5" ht="17" thickBot="1">
       <c r="A374" s="11">
         <v>42448</v>
       </c>
@@ -13665,7 +13680,7 @@
         <v>483463</v>
       </c>
     </row>
-    <row r="375" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="375" spans="1:5" ht="17" thickBot="1">
       <c r="A375" s="11">
         <v>42455</v>
       </c>
@@ -13683,7 +13698,7 @@
         <v>470271</v>
       </c>
     </row>
-    <row r="376" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="376" spans="1:5" ht="17" thickBot="1">
       <c r="A376" s="13">
         <v>42462</v>
       </c>
@@ -13701,7 +13716,7 @@
         <v>491979</v>
       </c>
     </row>
-    <row r="377" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="377" spans="1:5" ht="17" thickBot="1">
       <c r="A377" s="11">
         <v>42469</v>
       </c>
@@ -13719,7 +13734,7 @@
         <v>479059</v>
       </c>
     </row>
-    <row r="378" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="378" spans="1:5" ht="17" thickBot="1">
       <c r="A378" s="11">
         <v>42476</v>
       </c>
@@ -13737,7 +13752,7 @@
         <v>499779</v>
       </c>
     </row>
-    <row r="379" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="379" spans="1:5" ht="17" thickBot="1">
       <c r="A379" s="11">
         <v>42483</v>
       </c>
@@ -13755,7 +13770,7 @@
         <v>491946</v>
       </c>
     </row>
-    <row r="380" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="380" spans="1:5" ht="17" thickBot="1">
       <c r="A380" s="11">
         <v>42490</v>
       </c>
@@ -13773,7 +13788,7 @@
         <v>502045</v>
       </c>
     </row>
-    <row r="381" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="381" spans="1:5" ht="17" thickBot="1">
       <c r="A381" s="11">
         <v>42497</v>
       </c>
@@ -13791,7 +13806,7 @@
         <v>492923</v>
       </c>
     </row>
-    <row r="382" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="382" spans="1:5" ht="17" thickBot="1">
       <c r="A382" s="11">
         <v>42504</v>
       </c>
@@ -13809,7 +13824,7 @@
         <v>498379</v>
       </c>
     </row>
-    <row r="383" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="383" spans="1:5" ht="17" thickBot="1">
       <c r="A383" s="11">
         <v>42511</v>
       </c>
@@ -13827,7 +13842,7 @@
         <v>506983</v>
       </c>
     </row>
-    <row r="384" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="384" spans="1:5" ht="17" thickBot="1">
       <c r="A384" s="11">
         <v>42518</v>
       </c>
@@ -13845,7 +13860,7 @@
         <v>513917</v>
       </c>
     </row>
-    <row r="385" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="385" spans="1:5" ht="17" thickBot="1">
       <c r="A385" s="11">
         <v>42525</v>
       </c>
@@ -13863,7 +13878,7 @@
         <v>455346</v>
       </c>
     </row>
-    <row r="386" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="386" spans="1:5" ht="17" thickBot="1">
       <c r="A386" s="11">
         <v>42532</v>
       </c>
@@ -13896,7 +13911,7 @@
         <v>513471</v>
       </c>
     </row>
-    <row r="387" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="387" spans="1:5" ht="17" thickBot="1">
       <c r="A387" s="11">
         <v>42539</v>
       </c>
@@ -13914,7 +13929,7 @@
         <v>516096</v>
       </c>
     </row>
-    <row r="388" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="388" spans="1:5" ht="17" thickBot="1">
       <c r="A388" s="11">
         <v>42546</v>
       </c>
@@ -13932,7 +13947,7 @@
         <v>526161</v>
       </c>
     </row>
-    <row r="389" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="389" spans="1:5" ht="17" thickBot="1">
       <c r="A389" s="11">
         <v>42553</v>
       </c>
@@ -13950,7 +13965,7 @@
         <v>529191</v>
       </c>
     </row>
-    <row r="390" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="390" spans="1:5" ht="17" thickBot="1">
       <c r="A390" s="11">
         <v>42560</v>
       </c>
@@ -13968,7 +13983,7 @@
         <v>442113</v>
       </c>
     </row>
-    <row r="391" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="391" spans="1:5" ht="17" thickBot="1">
       <c r="A391" s="11">
         <v>42567</v>
       </c>
@@ -13986,7 +14001,7 @@
         <v>520222</v>
       </c>
     </row>
-    <row r="392" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="392" spans="1:5" ht="17" thickBot="1">
       <c r="A392" s="11">
         <v>42574</v>
       </c>
@@ -14004,7 +14019,7 @@
         <v>528070</v>
       </c>
     </row>
-    <row r="393" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="393" spans="1:5" ht="17" thickBot="1">
       <c r="A393" s="11">
         <v>42581</v>
       </c>
@@ -14022,7 +14037,7 @@
         <v>536916</v>
       </c>
     </row>
-    <row r="394" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="394" spans="1:5" ht="17" thickBot="1">
       <c r="A394" s="11">
         <v>42588</v>
       </c>
@@ -14040,7 +14055,7 @@
         <v>531595</v>
       </c>
     </row>
-    <row r="395" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="395" spans="1:5" ht="17" thickBot="1">
       <c r="A395" s="11">
         <v>42595</v>
       </c>
@@ -14058,7 +14073,7 @@
         <v>534533</v>
       </c>
     </row>
-    <row r="396" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="396" spans="1:5" ht="17" thickBot="1">
       <c r="A396" s="11">
         <v>42602</v>
       </c>
@@ -14076,7 +14091,7 @@
         <v>531484</v>
       </c>
     </row>
-    <row r="397" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="397" spans="1:5" ht="17" thickBot="1">
       <c r="A397" s="11">
         <v>42609</v>
       </c>
@@ -14094,7 +14109,7 @@
         <v>539657</v>
       </c>
     </row>
-    <row r="398" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="398" spans="1:5" ht="17" thickBot="1">
       <c r="A398" s="11">
         <v>42616</v>
       </c>
@@ -14112,7 +14127,7 @@
         <v>538826</v>
       </c>
     </row>
-    <row r="399" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="399" spans="1:5" ht="17" thickBot="1">
       <c r="A399" s="11">
         <v>42623</v>
       </c>
@@ -14130,7 +14145,7 @@
         <v>482894</v>
       </c>
     </row>
-    <row r="400" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="400" spans="1:5" ht="17" thickBot="1">
       <c r="A400" s="11">
         <v>42630</v>
       </c>
@@ -14148,7 +14163,7 @@
         <v>537904</v>
       </c>
     </row>
-    <row r="401" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="401" spans="1:5" ht="17" thickBot="1">
       <c r="A401" s="13">
         <v>42637</v>
       </c>
@@ -14166,7 +14181,7 @@
         <v>539609</v>
       </c>
     </row>
-    <row r="402" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="402" spans="1:5" ht="17" thickBot="1">
       <c r="A402" s="11">
         <v>42644</v>
       </c>
@@ -14184,7 +14199,7 @@
         <v>549171</v>
       </c>
     </row>
-    <row r="403" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="403" spans="1:5" ht="17" thickBot="1">
       <c r="A403" s="11">
         <v>42651</v>
       </c>
@@ -14202,7 +14217,7 @@
         <v>521789</v>
       </c>
     </row>
-    <row r="404" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="404" spans="1:5" ht="17" thickBot="1">
       <c r="A404" s="11">
         <v>42658</v>
       </c>
@@ -14220,7 +14235,7 @@
         <v>531936</v>
       </c>
     </row>
-    <row r="405" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="405" spans="1:5" ht="17" thickBot="1">
       <c r="A405" s="11">
         <v>42665</v>
       </c>
@@ -14238,7 +14253,7 @@
         <v>544092</v>
       </c>
     </row>
-    <row r="406" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="406" spans="1:5" ht="17" thickBot="1">
       <c r="A406" s="11">
         <v>42672</v>
       </c>
@@ -14256,7 +14271,7 @@
         <v>544997</v>
       </c>
     </row>
-    <row r="407" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="407" spans="1:5" ht="17" thickBot="1">
       <c r="A407" s="11">
         <v>42679</v>
       </c>
@@ -14274,7 +14289,7 @@
         <v>543377</v>
       </c>
     </row>
-    <row r="408" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="408" spans="1:5" ht="17" thickBot="1">
       <c r="A408" s="11">
         <v>42686</v>
       </c>
@@ -14292,7 +14307,7 @@
         <v>541127</v>
       </c>
     </row>
-    <row r="409" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="409" spans="1:5" ht="17" thickBot="1">
       <c r="A409" s="11">
         <v>42693</v>
       </c>
@@ -14310,7 +14325,7 @@
         <v>547804</v>
       </c>
     </row>
-    <row r="410" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="410" spans="1:5" ht="17" thickBot="1">
       <c r="A410" s="11">
         <v>42700</v>
       </c>
@@ -14328,7 +14343,7 @@
         <v>452759</v>
       </c>
     </row>
-    <row r="411" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="411" spans="1:5" ht="17" thickBot="1">
       <c r="A411" s="11">
         <v>42707</v>
       </c>
@@ -14346,7 +14361,7 @@
         <v>553130</v>
       </c>
     </row>
-    <row r="412" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="412" spans="1:5" ht="17" thickBot="1">
       <c r="A412" s="11">
         <v>42714</v>
       </c>
@@ -14364,7 +14379,7 @@
         <v>538932</v>
       </c>
     </row>
-    <row r="413" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="413" spans="1:5" ht="17" thickBot="1">
       <c r="A413" s="11">
         <v>42721</v>
       </c>
@@ -14382,7 +14397,7 @@
         <v>523949</v>
       </c>
     </row>
-    <row r="414" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="414" spans="1:5" ht="17" thickBot="1">
       <c r="A414" s="11">
         <v>42728</v>
       </c>
@@ -14400,7 +14415,7 @@
         <v>496633</v>
       </c>
     </row>
-    <row r="415" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="415" spans="1:5" ht="17" thickBot="1">
       <c r="A415" s="11">
         <v>42735</v>
       </c>
@@ -14418,7 +14433,7 @@
         <v>425998</v>
       </c>
     </row>
-    <row r="416" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="416" spans="1:5" ht="17" thickBot="1">
       <c r="A416" s="11">
         <v>42742</v>
       </c>
@@ -14436,7 +14451,7 @@
         <v>441417</v>
       </c>
     </row>
-    <row r="417" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="417" spans="1:5" ht="17" thickBot="1">
       <c r="A417" s="11">
         <v>42749</v>
       </c>
@@ -14454,7 +14469,7 @@
         <v>516229</v>
       </c>
     </row>
-    <row r="418" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="418" spans="1:5" ht="17" thickBot="1">
       <c r="A418" s="11">
         <v>42756</v>
       </c>
@@ -14472,7 +14487,7 @@
         <v>530299</v>
       </c>
     </row>
-    <row r="419" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="419" spans="1:5" ht="17" thickBot="1">
       <c r="A419" s="11">
         <v>42763</v>
       </c>
@@ -14490,7 +14505,7 @@
         <v>529696</v>
       </c>
     </row>
-    <row r="420" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="420" spans="1:5" ht="17" thickBot="1">
       <c r="A420" s="11">
         <v>42770</v>
       </c>
@@ -14508,7 +14523,7 @@
         <v>541474</v>
       </c>
     </row>
-    <row r="421" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="421" spans="1:5" ht="17" thickBot="1">
       <c r="A421" s="11">
         <v>42777</v>
       </c>
@@ -14526,7 +14541,7 @@
         <v>518431</v>
       </c>
     </row>
-    <row r="422" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="422" spans="1:5" ht="17" thickBot="1">
       <c r="A422" s="11">
         <v>42784</v>
       </c>
@@ -14544,7 +14559,7 @@
         <v>531123</v>
       </c>
     </row>
-    <row r="423" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="423" spans="1:5" ht="17" thickBot="1">
       <c r="A423" s="11">
         <v>42791</v>
       </c>
@@ -14562,7 +14577,7 @@
         <v>521451</v>
       </c>
     </row>
-    <row r="424" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="424" spans="1:5" ht="17" thickBot="1">
       <c r="A424" s="11">
         <v>42798</v>
       </c>
@@ -14580,7 +14595,7 @@
         <v>521607</v>
       </c>
     </row>
-    <row r="425" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="425" spans="1:5" ht="17" thickBot="1">
       <c r="A425" s="11">
         <v>42805</v>
       </c>
@@ -14598,7 +14613,7 @@
         <v>510638</v>
       </c>
     </row>
-    <row r="426" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="426" spans="1:5" ht="17" thickBot="1">
       <c r="A426" s="13">
         <v>42812</v>
       </c>
@@ -14616,7 +14631,7 @@
         <v>495281</v>
       </c>
     </row>
-    <row r="427" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="427" spans="1:5" ht="17" thickBot="1">
       <c r="A427" s="11">
         <v>42819</v>
       </c>
@@ -14634,7 +14649,7 @@
         <v>526471</v>
       </c>
     </row>
-    <row r="428" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="428" spans="1:5" ht="17" thickBot="1">
       <c r="A428" s="11">
         <v>42826</v>
       </c>
@@ -14652,7 +14667,7 @@
         <v>527665</v>
       </c>
     </row>
-    <row r="429" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="429" spans="1:5" ht="17" thickBot="1">
       <c r="A429" s="11">
         <v>42833</v>
       </c>
@@ -14670,7 +14685,7 @@
         <v>513022</v>
       </c>
     </row>
-    <row r="430" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="430" spans="1:5" ht="17" thickBot="1">
       <c r="A430" s="11">
         <v>42840</v>
       </c>
@@ -14688,7 +14703,7 @@
         <v>519318</v>
       </c>
     </row>
-    <row r="431" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="431" spans="1:5" ht="17" thickBot="1">
       <c r="A431" s="11">
         <v>42847</v>
       </c>
@@ -14706,7 +14721,7 @@
         <v>515131</v>
       </c>
     </row>
-    <row r="432" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="432" spans="1:5" ht="17" thickBot="1">
       <c r="A432" s="11">
         <v>42854</v>
       </c>
@@ -14724,7 +14739,7 @@
         <v>527830</v>
       </c>
     </row>
-    <row r="433" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="433" spans="1:5" ht="17" thickBot="1">
       <c r="A433" s="11">
         <v>42861</v>
       </c>
@@ -14742,7 +14757,7 @@
         <v>515305</v>
       </c>
     </row>
-    <row r="434" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="434" spans="1:5" ht="17" thickBot="1">
       <c r="A434" s="11">
         <v>42868</v>
       </c>
@@ -14760,7 +14775,7 @@
         <v>526970</v>
       </c>
     </row>
-    <row r="435" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="435" spans="1:5" ht="17" thickBot="1">
       <c r="A435" s="11">
         <v>42875</v>
       </c>
@@ -14778,7 +14793,7 @@
         <v>534922</v>
       </c>
     </row>
-    <row r="436" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="436" spans="1:5" ht="17" thickBot="1">
       <c r="A436" s="11">
         <v>42882</v>
       </c>
@@ -14796,7 +14811,7 @@
         <v>548103</v>
       </c>
     </row>
-    <row r="437" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="437" spans="1:5" ht="17" thickBot="1">
       <c r="A437" s="11">
         <v>42889</v>
       </c>
@@ -14814,7 +14829,7 @@
         <v>500192</v>
       </c>
     </row>
-    <row r="438" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="438" spans="1:5" ht="17" thickBot="1">
       <c r="A438" s="11">
         <v>42896</v>
       </c>
@@ -14832,7 +14847,7 @@
         <v>545317</v>
       </c>
     </row>
-    <row r="439" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="439" spans="1:5" ht="17" thickBot="1">
       <c r="A439" s="11">
         <v>42903</v>
       </c>
@@ -14850,7 +14865,7 @@
         <v>543179</v>
       </c>
     </row>
-    <row r="440" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="440" spans="1:5" ht="17" thickBot="1">
       <c r="A440" s="11">
         <v>42910</v>
       </c>
@@ -14868,7 +14883,7 @@
         <v>544694</v>
       </c>
     </row>
-    <row r="441" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="441" spans="1:5" ht="17" thickBot="1">
       <c r="A441" s="11">
         <v>42917</v>
       </c>
@@ -14886,7 +14901,7 @@
         <v>546361</v>
       </c>
     </row>
-    <row r="442" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="442" spans="1:5" ht="17" thickBot="1">
       <c r="A442" s="11">
         <v>42924</v>
       </c>
@@ -14904,7 +14919,7 @@
         <v>453080</v>
       </c>
     </row>
-    <row r="443" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="443" spans="1:5" ht="17" thickBot="1">
       <c r="A443" s="11">
         <v>42931</v>
       </c>
@@ -14922,7 +14937,7 @@
         <v>540005</v>
       </c>
     </row>
-    <row r="444" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="444" spans="1:5" ht="17" thickBot="1">
       <c r="A444" s="11">
         <v>42938</v>
       </c>
@@ -14940,7 +14955,7 @@
         <v>534152</v>
       </c>
     </row>
-    <row r="445" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="445" spans="1:5" ht="17" thickBot="1">
       <c r="A445" s="11">
         <v>42945</v>
       </c>
@@ -14958,7 +14973,7 @@
         <v>550356</v>
       </c>
     </row>
-    <row r="446" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="446" spans="1:5" ht="17" thickBot="1">
       <c r="A446" s="11">
         <v>42952</v>
       </c>
@@ -14976,7 +14991,7 @@
         <v>554822</v>
       </c>
     </row>
-    <row r="447" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="447" spans="1:5" ht="17" thickBot="1">
       <c r="A447" s="11">
         <v>42959</v>
       </c>
@@ -14994,7 +15009,7 @@
         <v>548790</v>
       </c>
     </row>
-    <row r="448" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="448" spans="1:5" ht="17" thickBot="1">
       <c r="A448" s="11">
         <v>42966</v>
       </c>
@@ -15012,7 +15027,7 @@
         <v>554021</v>
       </c>
     </row>
-    <row r="449" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="449" spans="1:5" ht="17" thickBot="1">
       <c r="A449" s="11">
         <v>42973</v>
       </c>
@@ -15030,7 +15045,7 @@
         <v>551776</v>
       </c>
     </row>
-    <row r="450" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="450" spans="1:5" ht="17" thickBot="1">
       <c r="A450" s="11">
         <v>42980</v>
       </c>
@@ -15063,7 +15078,7 @@
         <v>534140</v>
       </c>
     </row>
-    <row r="451" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="451" spans="1:5" ht="17" thickBot="1">
       <c r="A451" s="13">
         <v>42987</v>
       </c>
@@ -15081,7 +15096,7 @@
         <v>486474</v>
       </c>
     </row>
-    <row r="452" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="452" spans="1:5" ht="17" thickBot="1">
       <c r="A452" s="11">
         <v>42994</v>
       </c>
@@ -15099,7 +15114,7 @@
         <v>530774</v>
       </c>
     </row>
-    <row r="453" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="453" spans="1:5" ht="17" thickBot="1">
       <c r="A453" s="11">
         <v>43001</v>
       </c>
@@ -15117,7 +15132,7 @@
         <v>548204</v>
       </c>
     </row>
-    <row r="454" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="454" spans="1:5" ht="17" thickBot="1">
       <c r="A454" s="11">
         <v>43008</v>
       </c>
@@ -15135,7 +15150,7 @@
         <v>559555</v>
       </c>
     </row>
-    <row r="455" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="455" spans="1:5" ht="17" thickBot="1">
       <c r="A455" s="11">
         <v>43015</v>
       </c>
@@ -15153,7 +15168,7 @@
         <v>554826</v>
       </c>
     </row>
-    <row r="456" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="456" spans="1:5" ht="17" thickBot="1">
       <c r="A456" s="11">
         <v>43022</v>
       </c>
@@ -15171,7 +15186,7 @@
         <v>548264</v>
       </c>
     </row>
-    <row r="457" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="457" spans="1:5" ht="17" thickBot="1">
       <c r="A457" s="11">
         <v>43029</v>
       </c>
@@ -15189,7 +15204,7 @@
         <v>559989</v>
       </c>
     </row>
-    <row r="458" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="458" spans="1:5" ht="17" thickBot="1">
       <c r="A458" s="11">
         <v>43036</v>
       </c>
@@ -15207,7 +15222,7 @@
         <v>546582</v>
       </c>
     </row>
-    <row r="459" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="459" spans="1:5" ht="17" thickBot="1">
       <c r="A459" s="11">
         <v>43043</v>
       </c>
@@ -15225,7 +15240,7 @@
         <v>538739</v>
       </c>
     </row>
-    <row r="460" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="460" spans="1:5" ht="17" thickBot="1">
       <c r="A460" s="11">
         <v>43050</v>
       </c>
@@ -15243,7 +15258,7 @@
         <v>547480</v>
       </c>
     </row>
-    <row r="461" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="461" spans="1:5" ht="17" thickBot="1">
       <c r="A461" s="11">
         <v>43057</v>
       </c>
@@ -15261,7 +15276,7 @@
         <v>554066</v>
       </c>
     </row>
-    <row r="462" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="462" spans="1:5" ht="17" thickBot="1">
       <c r="A462" s="11">
         <v>43064</v>
       </c>
@@ -15279,7 +15294,7 @@
         <v>463602</v>
       </c>
     </row>
-    <row r="463" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="463" spans="1:5" ht="17" thickBot="1">
       <c r="A463" s="11">
         <v>43071</v>
       </c>
@@ -15297,7 +15312,7 @@
         <v>572794</v>
       </c>
     </row>
-    <row r="464" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="464" spans="1:5" ht="17" thickBot="1">
       <c r="A464" s="11">
         <v>43078</v>
       </c>
@@ -15315,7 +15330,7 @@
         <v>560756</v>
       </c>
     </row>
-    <row r="465" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="465" spans="1:5" ht="17" thickBot="1">
       <c r="A465" s="11">
         <v>43085</v>
       </c>
@@ -15333,7 +15348,7 @@
         <v>554779</v>
       </c>
     </row>
-    <row r="466" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="466" spans="1:5" ht="17" thickBot="1">
       <c r="A466" s="11">
         <v>43092</v>
       </c>
@@ -15351,7 +15366,7 @@
         <v>551566</v>
       </c>
     </row>
-    <row r="467" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="467" spans="1:5" ht="17" thickBot="1">
       <c r="A467" s="11">
         <v>43099</v>
       </c>
@@ -15369,7 +15384,7 @@
         <v>397032</v>
       </c>
     </row>
-    <row r="468" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="468" spans="1:5" ht="17" thickBot="1">
       <c r="A468" s="11">
         <v>43113</v>
       </c>
@@ -15387,7 +15402,7 @@
         <v>511937</v>
       </c>
     </row>
-    <row r="469" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="469" spans="1:5" ht="17" thickBot="1">
       <c r="A469" s="11">
         <v>43120</v>
       </c>
@@ -15405,7 +15420,7 @@
         <v>508239</v>
       </c>
     </row>
-    <row r="470" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="470" spans="1:5" ht="17" thickBot="1">
       <c r="A470" s="11">
         <v>43127</v>
       </c>
@@ -15423,7 +15438,7 @@
         <v>543515</v>
       </c>
     </row>
-    <row r="471" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="471" spans="1:5" ht="17" thickBot="1">
       <c r="A471" s="11">
         <v>43134</v>
       </c>
@@ -15441,7 +15456,7 @@
         <v>547993</v>
       </c>
     </row>
-    <row r="472" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="472" spans="1:5" ht="17" thickBot="1">
       <c r="A472" s="11">
         <v>43141</v>
       </c>
@@ -15459,7 +15474,7 @@
         <v>519545</v>
       </c>
     </row>
-    <row r="473" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="473" spans="1:5" ht="17" thickBot="1">
       <c r="A473" s="11">
         <v>43148</v>
       </c>
@@ -15477,7 +15492,7 @@
         <v>539963</v>
       </c>
     </row>
-    <row r="474" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="474" spans="1:5" ht="17" thickBot="1">
       <c r="A474" s="11">
         <v>43155</v>
       </c>
@@ -15495,7 +15510,7 @@
         <v>528440</v>
       </c>
     </row>
-    <row r="475" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="475" spans="1:5" ht="17" thickBot="1">
       <c r="A475" s="11">
         <v>43162</v>
       </c>
@@ -15513,7 +15528,7 @@
         <v>544194</v>
       </c>
     </row>
-    <row r="476" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="476" spans="1:5" ht="17" thickBot="1">
       <c r="A476" s="13">
         <v>43169</v>
       </c>
@@ -15531,7 +15546,7 @@
         <v>534282</v>
       </c>
     </row>
-    <row r="477" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="477" spans="1:5" ht="17" thickBot="1">
       <c r="A477" s="11">
         <v>43176</v>
       </c>
@@ -15549,7 +15564,7 @@
         <v>537338</v>
       </c>
     </row>
-    <row r="478" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="478" spans="1:5" ht="17" thickBot="1">
       <c r="A478" s="11">
         <v>43183</v>
       </c>
@@ -15567,7 +15582,7 @@
         <v>526521</v>
       </c>
     </row>
-    <row r="479" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="479" spans="1:5" ht="17" thickBot="1">
       <c r="A479" s="11">
         <v>43190</v>
       </c>
@@ -15585,7 +15600,7 @@
         <v>534751</v>
       </c>
     </row>
-    <row r="480" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="480" spans="1:5" ht="17" thickBot="1">
       <c r="A480" s="11">
         <v>43197</v>
       </c>
@@ -15603,7 +15618,7 @@
         <v>524905</v>
       </c>
     </row>
-    <row r="481" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="481" spans="1:5" ht="17" thickBot="1">
       <c r="A481" s="11">
         <v>43204</v>
       </c>
@@ -15621,7 +15636,7 @@
         <v>534198</v>
       </c>
     </row>
-    <row r="482" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="482" spans="1:5" ht="17" thickBot="1">
       <c r="A482" s="11">
         <v>43211</v>
       </c>
@@ -15639,7 +15654,7 @@
         <v>539425</v>
       </c>
     </row>
-    <row r="483" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="483" spans="1:5" ht="17" thickBot="1">
       <c r="A483" s="11">
         <v>43218</v>
       </c>
@@ -15657,7 +15672,7 @@
         <v>551498</v>
       </c>
     </row>
-    <row r="484" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="484" spans="1:5" ht="17" thickBot="1">
       <c r="A484" s="11">
         <v>43225</v>
       </c>
@@ -15675,7 +15690,7 @@
         <v>545937</v>
       </c>
     </row>
-    <row r="485" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="485" spans="1:5" ht="17" thickBot="1">
       <c r="A485" s="11">
         <v>43232</v>
       </c>
@@ -15693,7 +15708,7 @@
         <v>550029</v>
       </c>
     </row>
-    <row r="486" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="486" spans="1:5" ht="17" thickBot="1">
       <c r="A486" s="11">
         <v>43239</v>
       </c>
@@ -15711,7 +15726,7 @@
         <v>546415</v>
       </c>
     </row>
-    <row r="487" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="487" spans="1:5" ht="17" thickBot="1">
       <c r="A487" s="11">
         <v>43246</v>
       </c>
@@ -15729,7 +15744,7 @@
         <v>565502</v>
       </c>
     </row>
-    <row r="488" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="488" spans="1:5" ht="17" thickBot="1">
       <c r="A488" s="11">
         <v>43253</v>
       </c>
@@ -15747,7 +15762,7 @@
         <v>509740</v>
       </c>
     </row>
-    <row r="489" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="489" spans="1:5" ht="17" thickBot="1">
       <c r="A489" s="11">
         <v>43260</v>
       </c>
@@ -15765,7 +15780,7 @@
         <v>561061</v>
       </c>
     </row>
-    <row r="490" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="490" spans="1:5" ht="17" thickBot="1">
       <c r="A490" s="11">
         <v>43267</v>
       </c>
@@ -15783,7 +15798,7 @@
         <v>558098</v>
       </c>
     </row>
-    <row r="491" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="491" spans="1:5" ht="17" thickBot="1">
       <c r="A491" s="11">
         <v>43274</v>
       </c>
@@ -15801,7 +15816,7 @@
         <v>557340</v>
       </c>
     </row>
-    <row r="492" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="492" spans="1:5" ht="17" thickBot="1">
       <c r="A492" s="11">
         <v>43281</v>
       </c>
@@ -15819,7 +15834,7 @@
         <v>564243</v>
       </c>
     </row>
-    <row r="493" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="493" spans="1:5" ht="17" thickBot="1">
       <c r="A493" s="11">
         <v>43288</v>
       </c>
@@ -15837,7 +15852,7 @@
         <v>485193</v>
       </c>
     </row>
-    <row r="494" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="494" spans="1:5" ht="17" thickBot="1">
       <c r="A494" s="11">
         <v>43295</v>
       </c>
@@ -15855,7 +15870,7 @@
         <v>559064</v>
       </c>
     </row>
-    <row r="495" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="495" spans="1:5" ht="17" thickBot="1">
       <c r="A495" s="11">
         <v>43302</v>
       </c>
@@ -15873,7 +15888,7 @@
         <v>553024</v>
       </c>
     </row>
-    <row r="496" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="496" spans="1:5" ht="17" thickBot="1">
       <c r="A496" s="11">
         <v>43309</v>
       </c>
@@ -15891,7 +15906,7 @@
         <v>559154</v>
       </c>
     </row>
-    <row r="497" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="497" spans="1:5" ht="17" thickBot="1">
       <c r="A497" s="11">
         <v>43316</v>
       </c>
@@ -15909,7 +15924,7 @@
         <v>570995</v>
       </c>
     </row>
-    <row r="498" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="498" spans="1:5" ht="17" thickBot="1">
       <c r="A498" s="11">
         <v>43323</v>
       </c>
@@ -15927,7 +15942,7 @@
         <v>556887</v>
       </c>
     </row>
-    <row r="499" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="499" spans="1:5" ht="17" thickBot="1">
       <c r="A499" s="11">
         <v>43330</v>
       </c>
@@ -15945,7 +15960,7 @@
         <v>567477</v>
       </c>
     </row>
-    <row r="500" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="500" spans="1:5" ht="17" thickBot="1">
       <c r="A500" s="11">
         <v>43337</v>
       </c>
@@ -15963,7 +15978,7 @@
         <v>565706</v>
       </c>
     </row>
-    <row r="501" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="501" spans="1:5" ht="17" thickBot="1">
       <c r="A501" s="13">
         <v>43344</v>
       </c>
@@ -15981,7 +15996,7 @@
         <v>567881</v>
       </c>
     </row>
-    <row r="502" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="502" spans="1:5" ht="17" thickBot="1">
       <c r="A502" s="11">
         <v>43351</v>
       </c>
@@ -15999,7 +16014,7 @@
         <v>502208</v>
       </c>
     </row>
-    <row r="503" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="503" spans="1:5" ht="17" thickBot="1">
       <c r="A503" s="11">
         <v>43358</v>
       </c>
@@ -16017,7 +16032,7 @@
         <v>553003</v>
       </c>
     </row>
-    <row r="504" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="504" spans="1:5" ht="17" thickBot="1">
       <c r="A504" s="11">
         <v>43365</v>
       </c>
@@ -16035,7 +16050,7 @@
         <v>567078</v>
       </c>
     </row>
-    <row r="505" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="505" spans="1:5" ht="17" thickBot="1">
       <c r="A505" s="11">
         <v>43372</v>
       </c>
@@ -16053,7 +16068,7 @@
         <v>571922</v>
       </c>
     </row>
-    <row r="506" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="506" spans="1:5" ht="17" thickBot="1">
       <c r="A506" s="11">
         <v>43379</v>
       </c>
@@ -16071,7 +16086,7 @@
         <v>554238</v>
       </c>
     </row>
-    <row r="507" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="507" spans="1:5" ht="17" thickBot="1">
       <c r="A507" s="11">
         <v>43386</v>
       </c>
@@ -16089,7 +16104,7 @@
         <v>549757</v>
       </c>
     </row>
-    <row r="508" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="508" spans="1:5" ht="17" thickBot="1">
       <c r="A508" s="11">
         <v>43393</v>
       </c>
@@ -16107,7 +16122,7 @@
         <v>555106</v>
       </c>
     </row>
-    <row r="509" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="509" spans="1:5" ht="17" thickBot="1">
       <c r="A509" s="11">
         <v>43400</v>
       </c>
@@ -16125,7 +16140,7 @@
         <v>562804</v>
       </c>
     </row>
-    <row r="510" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="510" spans="1:5" ht="17" thickBot="1">
       <c r="A510" s="11">
         <v>43407</v>
       </c>
@@ -16143,7 +16158,7 @@
         <v>560046</v>
       </c>
     </row>
-    <row r="511" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="511" spans="1:5" ht="17" thickBot="1">
       <c r="A511" s="11">
         <v>43414</v>
       </c>
@@ -16161,7 +16176,7 @@
         <v>547236</v>
       </c>
     </row>
-    <row r="512" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="512" spans="1:5" ht="17" thickBot="1">
       <c r="A512" s="11">
         <v>43421</v>
       </c>
@@ -16179,7 +16194,7 @@
         <v>546541</v>
       </c>
     </row>
-    <row r="513" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="513" spans="1:5" ht="17" thickBot="1">
       <c r="A513" s="11">
         <v>43428</v>
       </c>
@@ -16197,7 +16212,7 @@
         <v>470851</v>
       </c>
     </row>
-    <row r="514" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="514" spans="1:5" ht="17" thickBot="1">
       <c r="A514" s="11">
         <v>43435</v>
       </c>
@@ -16230,7 +16245,7 @@
         <v>567282</v>
       </c>
     </row>
-    <row r="515" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="515" spans="1:5" ht="17" thickBot="1">
       <c r="A515" s="11">
         <v>43442</v>
       </c>
@@ -16248,7 +16263,7 @@
         <v>570225</v>
       </c>
     </row>
-    <row r="516" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="516" spans="1:5" ht="17" thickBot="1">
       <c r="A516" s="11">
         <v>43449</v>
       </c>
@@ -16266,7 +16281,7 @@
         <v>568941</v>
       </c>
     </row>
-    <row r="517" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="517" spans="1:5" ht="17" thickBot="1">
       <c r="A517" s="11">
         <v>43456</v>
       </c>
@@ -16284,7 +16299,7 @@
         <v>567252</v>
       </c>
     </row>
-    <row r="518" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="518" spans="1:5" ht="17" thickBot="1">
       <c r="A518" s="11">
         <v>43463</v>
       </c>
@@ -16302,7 +16317,7 @@
         <v>411676</v>
       </c>
     </row>
-    <row r="519" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="519" spans="1:5" ht="17" thickBot="1">
       <c r="A519" s="11">
         <v>43470</v>
       </c>
@@ -16320,7 +16335,7 @@
         <v>436103</v>
       </c>
     </row>
-    <row r="520" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="520" spans="1:5" ht="17" thickBot="1">
       <c r="A520" s="11">
         <v>43477</v>
       </c>
@@ -16338,7 +16353,7 @@
         <v>555127</v>
       </c>
     </row>
-    <row r="521" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="521" spans="1:5" ht="17" thickBot="1">
       <c r="A521" s="11">
         <v>43484</v>
       </c>
@@ -16356,7 +16371,7 @@
         <v>543111</v>
       </c>
     </row>
-    <row r="522" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="522" spans="1:5" ht="17" thickBot="1">
       <c r="A522" s="11">
         <v>43491</v>
       </c>
@@ -16374,7 +16389,7 @@
         <v>522026</v>
       </c>
     </row>
-    <row r="523" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="523" spans="1:5" ht="17" thickBot="1">
       <c r="A523" s="11">
         <v>43498</v>
       </c>
@@ -16392,7 +16407,7 @@
         <v>498288</v>
       </c>
     </row>
-    <row r="524" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="524" spans="1:5" ht="17" thickBot="1">
       <c r="A524" s="11">
         <v>43505</v>
       </c>
@@ -16410,7 +16425,7 @@
         <v>519779</v>
       </c>
     </row>
-    <row r="525" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="525" spans="1:5" ht="17" thickBot="1">
       <c r="A525" s="11">
         <v>43512</v>
       </c>
@@ -16428,7 +16443,7 @@
         <v>523915</v>
       </c>
     </row>
-    <row r="526" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="526" spans="1:5" ht="17" thickBot="1">
       <c r="A526" s="13">
         <v>43519</v>
       </c>
@@ -16446,7 +16461,7 @@
         <v>522630</v>
       </c>
     </row>
-    <row r="527" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="527" spans="1:5" ht="17" thickBot="1">
       <c r="A527" s="11">
         <v>43526</v>
       </c>
@@ -16464,7 +16479,7 @@
         <v>528153</v>
       </c>
     </row>
-    <row r="528" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="528" spans="1:5" ht="17" thickBot="1">
       <c r="A528" s="11">
         <v>43533</v>
       </c>
@@ -16482,7 +16497,7 @@
         <v>508958</v>
       </c>
     </row>
-    <row r="529" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="529" spans="1:5" ht="17" thickBot="1">
       <c r="A529" s="11">
         <v>43540</v>
       </c>
@@ -16500,7 +16515,7 @@
         <v>501001</v>
       </c>
     </row>
-    <row r="530" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="530" spans="1:5" ht="17" thickBot="1">
       <c r="A530" s="11">
         <v>43547</v>
       </c>
@@ -16518,7 +16533,7 @@
         <v>503017</v>
       </c>
     </row>
-    <row r="531" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="531" spans="1:5" ht="17" thickBot="1">
       <c r="A531" s="11">
         <v>43554</v>
       </c>
@@ -16536,7 +16551,7 @@
         <v>509958</v>
       </c>
     </row>
-    <row r="532" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="532" spans="1:5" ht="17" thickBot="1">
       <c r="A532" s="11">
         <v>43561</v>
       </c>
@@ -16554,7 +16569,7 @@
         <v>510192</v>
       </c>
     </row>
-    <row r="533" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="533" spans="1:5" ht="17" thickBot="1">
       <c r="A533" s="11">
         <v>43568</v>
       </c>
@@ -16572,7 +16587,7 @@
         <v>528167</v>
       </c>
     </row>
-    <row r="534" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="534" spans="1:5" ht="17" thickBot="1">
       <c r="A534" s="11">
         <v>43575</v>
       </c>
@@ -16590,7 +16605,7 @@
         <v>526141</v>
       </c>
     </row>
-    <row r="535" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="535" spans="1:5" ht="17" thickBot="1">
       <c r="A535" s="11">
         <v>43582</v>
       </c>
@@ -16608,7 +16623,7 @@
         <v>533190</v>
       </c>
     </row>
-    <row r="536" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="536" spans="1:5" ht="17" thickBot="1">
       <c r="A536" s="11">
         <v>43589</v>
       </c>
@@ -16626,7 +16641,7 @@
         <v>535089</v>
       </c>
     </row>
-    <row r="537" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="537" spans="1:5" ht="17" thickBot="1">
       <c r="A537" s="11">
         <v>43596</v>
       </c>
@@ -16644,7 +16659,7 @@
         <v>529263</v>
       </c>
     </row>
-    <row r="538" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="538" spans="1:5" ht="17" thickBot="1">
       <c r="A538" s="11">
         <v>43603</v>
       </c>
@@ -16662,7 +16677,7 @@
         <v>536358</v>
       </c>
     </row>
-    <row r="539" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="539" spans="1:5" ht="17" thickBot="1">
       <c r="A539" s="11">
         <v>43610</v>
       </c>
@@ -16680,7 +16695,7 @@
         <v>527966</v>
       </c>
     </row>
-    <row r="540" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="540" spans="1:5" ht="17" thickBot="1">
       <c r="A540" s="11">
         <v>43617</v>
       </c>
@@ -16698,7 +16713,7 @@
         <v>478679</v>
       </c>
     </row>
-    <row r="541" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="541" spans="1:5" ht="17" thickBot="1">
       <c r="A541" s="11">
         <v>43624</v>
       </c>
@@ -16716,7 +16731,7 @@
         <v>513099</v>
       </c>
     </row>
-    <row r="542" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="542" spans="1:5" ht="17" thickBot="1">
       <c r="A542" s="11">
         <v>43631</v>
       </c>
@@ -16734,7 +16749,7 @@
         <v>527989</v>
       </c>
     </row>
-    <row r="543" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="543" spans="1:5" ht="17" thickBot="1">
       <c r="A543" s="11">
         <v>43638</v>
       </c>
@@ -16752,7 +16767,7 @@
         <v>525116</v>
       </c>
     </row>
-    <row r="544" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="544" spans="1:5" ht="17" thickBot="1">
       <c r="A544" s="11">
         <v>43645</v>
       </c>
@@ -16770,7 +16785,7 @@
         <v>533164</v>
       </c>
     </row>
-    <row r="545" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="545" spans="1:5" ht="17" thickBot="1">
       <c r="A545" s="11">
         <v>43652</v>
       </c>
@@ -16788,7 +16803,7 @@
         <v>448459</v>
       </c>
     </row>
-    <row r="546" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="546" spans="1:5" ht="17" thickBot="1">
       <c r="A546" s="11">
         <v>43659</v>
       </c>
@@ -16806,7 +16821,7 @@
         <v>527908</v>
       </c>
     </row>
-    <row r="547" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="547" spans="1:5" ht="17" thickBot="1">
       <c r="A547" s="11">
         <v>43666</v>
       </c>
@@ -16824,7 +16839,7 @@
         <v>526010</v>
       </c>
     </row>
-    <row r="548" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="548" spans="1:5" ht="17" thickBot="1">
       <c r="A548" s="11">
         <v>43673</v>
       </c>
@@ -16842,7 +16857,7 @@
         <v>534498</v>
       </c>
     </row>
-    <row r="549" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="549" spans="1:5" ht="17" thickBot="1">
       <c r="A549" s="11">
         <v>43680</v>
       </c>
@@ -16860,7 +16875,7 @@
         <v>541558</v>
       </c>
     </row>
-    <row r="550" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="550" spans="1:5" ht="17" thickBot="1">
       <c r="A550" s="11">
         <v>43687</v>
       </c>
@@ -16878,7 +16893,7 @@
         <v>533190</v>
       </c>
     </row>
-    <row r="551" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="551" spans="1:5" ht="17" thickBot="1">
       <c r="A551" s="13">
         <v>43694</v>
       </c>
@@ -16896,7 +16911,7 @@
         <v>537617</v>
       </c>
     </row>
-    <row r="552" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="552" spans="1:5" ht="17" thickBot="1">
       <c r="A552" s="11">
         <v>43701</v>
       </c>
@@ -16914,7 +16929,7 @@
         <v>532483</v>
       </c>
     </row>
-    <row r="553" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="553" spans="1:5" ht="17" thickBot="1">
       <c r="A553" s="11">
         <v>43708</v>
       </c>
@@ -16932,7 +16947,7 @@
         <v>541945</v>
       </c>
     </row>
-    <row r="554" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="554" spans="1:5" ht="17" thickBot="1">
       <c r="A554" s="11">
         <v>43715</v>
       </c>
@@ -16950,7 +16965,7 @@
         <v>469285</v>
       </c>
     </row>
-    <row r="555" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="555" spans="1:5" ht="17" thickBot="1">
       <c r="A555" s="11">
         <v>43722</v>
       </c>
@@ -16968,7 +16983,7 @@
         <v>526734</v>
       </c>
     </row>
-    <row r="556" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="556" spans="1:5" ht="17" thickBot="1">
       <c r="A556" s="11">
         <v>43729</v>
       </c>
@@ -16986,7 +17001,7 @@
         <v>528670</v>
       </c>
     </row>
-    <row r="557" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="557" spans="1:5" ht="17" thickBot="1">
       <c r="A557" s="11">
         <v>43736</v>
       </c>
@@ -17004,7 +17019,7 @@
         <v>529336</v>
       </c>
     </row>
-    <row r="558" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="558" spans="1:5" ht="17" thickBot="1">
       <c r="A558" s="11">
         <v>43743</v>
       </c>
@@ -17022,7 +17037,7 @@
         <v>515061</v>
       </c>
     </row>
-    <row r="559" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="559" spans="1:5" ht="17" thickBot="1">
       <c r="A559" s="11">
         <v>43750</v>
       </c>
@@ -17040,7 +17055,7 @@
         <v>510820</v>
       </c>
     </row>
-    <row r="560" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="560" spans="1:5" ht="17" thickBot="1">
       <c r="A560" s="11">
         <v>43757</v>
       </c>
@@ -17058,7 +17073,7 @@
         <v>507381</v>
       </c>
     </row>
-    <row r="561" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="561" spans="1:5" ht="17" thickBot="1">
       <c r="A561" s="11">
         <v>43764</v>
       </c>
@@ -17076,7 +17091,7 @@
         <v>513147</v>
       </c>
     </row>
-    <row r="562" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="562" spans="1:5" ht="17" thickBot="1">
       <c r="A562" s="11">
         <v>43771</v>
       </c>
@@ -17094,7 +17109,7 @@
         <v>510012</v>
       </c>
     </row>
-    <row r="563" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="563" spans="1:5" ht="17" thickBot="1">
       <c r="A563" s="11">
         <v>43778</v>
       </c>
@@ -17112,7 +17127,7 @@
         <v>515269</v>
       </c>
     </row>
-    <row r="564" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="564" spans="1:5" ht="17" thickBot="1">
       <c r="A564" s="11">
         <v>43785</v>
       </c>
@@ -17130,7 +17145,7 @@
         <v>501249</v>
       </c>
     </row>
-    <row r="565" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="565" spans="1:5" ht="17" thickBot="1">
       <c r="A565" s="11">
         <v>43792</v>
       </c>
@@ -17148,7 +17163,7 @@
         <v>521927</v>
       </c>
     </row>
-    <row r="566" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="566" spans="1:5" ht="17" thickBot="1">
       <c r="A566" s="11">
         <v>43813</v>
       </c>
@@ -17166,7 +17181,7 @@
         <v>520589</v>
       </c>
     </row>
-    <row r="567" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="567" spans="1:5" ht="17" thickBot="1">
       <c r="A567" s="11">
         <v>43820</v>
       </c>
@@ -17184,7 +17199,7 @@
         <v>507589</v>
       </c>
     </row>
-    <row r="568" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="568" spans="1:5" ht="17" thickBot="1">
       <c r="A568" s="11">
         <v>43827</v>
       </c>
@@ -17202,7 +17217,7 @@
         <v>373728</v>
       </c>
     </row>
-    <row r="569" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="569" spans="1:5" ht="17" thickBot="1">
       <c r="A569" s="11">
         <v>43834</v>
       </c>
@@ -17220,7 +17235,7 @@
         <v>414014</v>
       </c>
     </row>
-    <row r="570" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="570" spans="1:5" ht="17" thickBot="1">
       <c r="A570" s="11">
         <v>43841</v>
       </c>
@@ -17238,7 +17253,7 @@
         <v>501624</v>
       </c>
     </row>
-    <row r="571" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="571" spans="1:5" ht="17" thickBot="1">
       <c r="A571" s="11">
         <v>43848</v>
       </c>
@@ -17256,7 +17271,7 @@
         <v>499732</v>
       </c>
     </row>
-    <row r="572" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="572" spans="1:5" ht="17" thickBot="1">
       <c r="A572" s="11">
         <v>43855</v>
       </c>
@@ -17274,7 +17289,7 @@
         <v>485282</v>
       </c>
     </row>
-    <row r="573" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="573" spans="1:5" ht="17" thickBot="1">
       <c r="A573" s="11">
         <v>43862</v>
       </c>
@@ -17292,7 +17307,7 @@
         <v>510161</v>
       </c>
     </row>
-    <row r="574" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="574" spans="1:5" ht="17" thickBot="1">
       <c r="A574" s="11">
         <v>43869</v>
       </c>
@@ -17310,7 +17325,7 @@
         <v>485329</v>
       </c>
     </row>
-    <row r="575" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="575" spans="1:5" ht="17" thickBot="1">
       <c r="A575" s="11">
         <v>43876</v>
       </c>
@@ -17328,7 +17343,7 @@
         <v>479137</v>
       </c>
     </row>
-    <row r="576" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="576" spans="1:5" ht="17" thickBot="1">
       <c r="A576" s="13">
         <v>43883</v>
       </c>
@@ -17346,7 +17361,7 @@
         <v>482690</v>
       </c>
     </row>
-    <row r="577" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="577" spans="1:5" ht="17" thickBot="1">
       <c r="A577" s="11">
         <v>43890</v>
       </c>
@@ -17364,7 +17379,7 @@
         <v>477611</v>
       </c>
     </row>
-    <row r="578" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="578" spans="1:5" ht="17" thickBot="1">
       <c r="A578" s="11">
         <v>43897</v>
       </c>
@@ -17397,7 +17412,7 @@
         <v>462303</v>
       </c>
     </row>
-    <row r="579" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="579" spans="1:5" ht="17" thickBot="1">
       <c r="A579" s="11">
         <v>43904</v>
       </c>
@@ -17415,7 +17430,7 @@
         <v>463017</v>
       </c>
     </row>
-    <row r="580" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="580" spans="1:5" ht="17" thickBot="1">
       <c r="A580" s="11">
         <v>43911</v>
       </c>
@@ -17433,7 +17448,7 @@
         <v>459966</v>
       </c>
     </row>
-    <row r="581" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="581" spans="1:5" ht="17" thickBot="1">
       <c r="A581" s="11">
         <v>43918</v>
       </c>
@@ -17451,7 +17466,7 @@
         <v>449767</v>
       </c>
     </row>
-    <row r="582" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="582" spans="1:5" ht="17" thickBot="1">
       <c r="A582" s="11">
         <v>43925</v>
       </c>
@@ -17469,7 +17484,7 @@
         <v>429095</v>
       </c>
     </row>
-    <row r="583" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="583" spans="1:5" ht="17" thickBot="1">
       <c r="A583" s="11">
         <v>43932</v>
       </c>
@@ -17487,7 +17502,7 @@
         <v>412503</v>
       </c>
     </row>
-    <row r="584" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="584" spans="1:5" ht="17" thickBot="1">
       <c r="A584" s="11">
         <v>43939</v>
       </c>
@@ -17505,7 +17520,7 @@
         <v>403283</v>
       </c>
     </row>
-    <row r="585" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="585" spans="1:5" ht="17" thickBot="1">
       <c r="A585" s="11">
         <v>43946</v>
       </c>
@@ -17523,7 +17538,7 @@
         <v>414123</v>
       </c>
     </row>
-    <row r="586" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="586" spans="1:5" ht="17" thickBot="1">
       <c r="A586" s="11">
         <v>43953</v>
       </c>
@@ -17541,7 +17556,7 @@
         <v>416954</v>
       </c>
     </row>
-    <row r="587" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="587" spans="1:5" ht="17" thickBot="1">
       <c r="A587" s="11">
         <v>43960</v>
       </c>
@@ -17559,7 +17574,7 @@
         <v>412549</v>
       </c>
     </row>
-    <row r="588" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="588" spans="1:5" ht="17" thickBot="1">
       <c r="A588" s="11">
         <v>43967</v>
       </c>
@@ -17577,7 +17592,7 @@
         <v>416115</v>
       </c>
     </row>
-    <row r="589" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="589" spans="1:5" ht="17" thickBot="1">
       <c r="A589" s="11">
         <v>43974</v>
       </c>
@@ -17595,7 +17610,7 @@
         <v>428715</v>
       </c>
     </row>
-    <row r="590" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="590" spans="1:5" ht="17" thickBot="1">
       <c r="A590" s="11">
         <v>43981</v>
       </c>
@@ -17613,7 +17628,7 @@
         <v>395714</v>
       </c>
     </row>
-    <row r="591" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="591" spans="1:5" ht="17" thickBot="1">
       <c r="A591" s="11">
         <v>43988</v>
       </c>
@@ -17631,7 +17646,7 @@
         <v>433171</v>
       </c>
     </row>
-    <row r="592" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="592" spans="1:5" ht="17" thickBot="1">
       <c r="A592" s="11">
         <v>43995</v>
       </c>
@@ -17649,7 +17664,7 @@
         <v>449291</v>
       </c>
     </row>
-    <row r="593" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="593" spans="1:5" ht="17" thickBot="1">
       <c r="A593" s="11">
         <v>44002</v>
       </c>
@@ -17667,7 +17682,7 @@
         <v>457278</v>
       </c>
     </row>
-    <row r="594" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="594" spans="1:5" ht="17" thickBot="1">
       <c r="A594" s="11">
         <v>44009</v>
       </c>
@@ -17685,7 +17700,7 @@
         <v>459449</v>
       </c>
     </row>
-    <row r="595" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="595" spans="1:5" ht="17" thickBot="1">
       <c r="A595" s="11">
         <v>44016</v>
       </c>
@@ -17703,7 +17718,7 @@
         <v>437989</v>
       </c>
     </row>
-    <row r="596" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="596" spans="1:5" ht="17" thickBot="1">
       <c r="A596" s="11">
         <v>44023</v>
       </c>
@@ -17721,7 +17736,7 @@
         <v>449092</v>
       </c>
     </row>
-    <row r="597" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="597" spans="1:5" ht="17" thickBot="1">
       <c r="A597" s="11">
         <v>44030</v>
       </c>
@@ -17739,7 +17754,7 @@
         <v>481597</v>
       </c>
     </row>
-    <row r="598" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="598" spans="1:5" ht="17" thickBot="1">
       <c r="A598" s="11">
         <v>44037</v>
       </c>
@@ -17757,7 +17772,7 @@
         <v>481331</v>
       </c>
     </row>
-    <row r="599" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="599" spans="1:5" ht="17" thickBot="1">
       <c r="A599" s="11">
         <v>44044</v>
       </c>
@@ -17775,7 +17790,7 @@
         <v>487968</v>
       </c>
     </row>
-    <row r="600" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="600" spans="1:5" ht="17" thickBot="1">
       <c r="A600" s="11">
         <v>44051</v>
       </c>
@@ -17793,7 +17808,7 @@
         <v>497397</v>
       </c>
     </row>
-    <row r="601" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="601" spans="1:5" ht="17" thickBot="1">
       <c r="A601" s="13">
         <v>44058</v>
       </c>
@@ -17811,7 +17826,7 @@
         <v>500563</v>
       </c>
     </row>
-    <row r="602" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="602" spans="1:5" ht="17" thickBot="1">
       <c r="A602" s="11">
         <v>44072</v>
       </c>
@@ -17829,7 +17844,7 @@
         <v>508307</v>
       </c>
     </row>
-    <row r="603" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="603" spans="1:5" ht="17" thickBot="1">
       <c r="A603" s="11">
         <v>44079</v>
       </c>
@@ -17847,7 +17862,7 @@
         <v>509637</v>
       </c>
     </row>
-    <row r="604" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="604" spans="1:5" ht="17" thickBot="1">
       <c r="A604" s="11">
         <v>44086</v>
       </c>
@@ -17865,7 +17880,7 @@
         <v>474785</v>
       </c>
     </row>
-    <row r="605" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="605" spans="1:5" ht="17" thickBot="1">
       <c r="A605" s="11">
         <v>44093</v>
       </c>
@@ -17883,7 +17898,7 @@
         <v>521956</v>
       </c>
     </row>
-    <row r="606" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="606" spans="1:5" ht="17" thickBot="1">
       <c r="A606" s="11">
         <v>44100</v>
       </c>
@@ -17901,7 +17916,7 @@
         <v>518290</v>
       </c>
     </row>
-    <row r="607" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="607" spans="1:5" ht="17" thickBot="1">
       <c r="A607" s="11">
         <v>44107</v>
       </c>
@@ -17919,7 +17934,7 @@
         <v>518761</v>
       </c>
     </row>
-    <row r="608" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="608" spans="1:5" ht="17" thickBot="1">
       <c r="A608" s="11">
         <v>44114</v>
       </c>
@@ -17937,7 +17952,7 @@
         <v>520452</v>
       </c>
     </row>
-    <row r="609" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="609" spans="1:5" ht="17" thickBot="1">
       <c r="A609" s="11">
         <v>44121</v>
       </c>
@@ -17955,7 +17970,7 @@
         <v>518763</v>
       </c>
     </row>
-    <row r="610" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="610" spans="1:5" ht="17" thickBot="1">
       <c r="A610" s="11">
         <v>44128</v>
       </c>
@@ -17973,7 +17988,7 @@
         <v>522653</v>
       </c>
     </row>
-    <row r="611" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="611" spans="1:5" ht="17" thickBot="1">
       <c r="A611" s="11">
         <v>44135</v>
       </c>
@@ -17991,7 +18006,7 @@
         <v>520778</v>
       </c>
     </row>
-    <row r="612" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="612" spans="1:5" ht="17" thickBot="1">
       <c r="A612" s="11">
         <v>44142</v>
       </c>
@@ -18009,7 +18024,7 @@
         <v>522028</v>
       </c>
     </row>
-    <row r="613" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="613" spans="1:5" ht="17" thickBot="1">
       <c r="A613" s="11">
         <v>44149</v>
       </c>
@@ -18027,7 +18042,7 @@
         <v>527462</v>
       </c>
     </row>
-    <row r="614" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="614" spans="1:5" ht="17" thickBot="1">
       <c r="A614" s="11">
         <v>44156</v>
       </c>
@@ -18045,7 +18060,7 @@
         <v>534607</v>
       </c>
     </row>
-    <row r="615" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="615" spans="1:5" ht="17" thickBot="1">
       <c r="A615" s="11">
         <v>44163</v>
       </c>
@@ -18063,7 +18078,7 @@
         <v>452792</v>
       </c>
     </row>
-    <row r="616" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="616" spans="1:5" ht="17" thickBot="1">
       <c r="A616" s="11">
         <v>44170</v>
       </c>
@@ -18081,7 +18096,7 @@
         <v>542203</v>
       </c>
     </row>
-    <row r="617" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="617" spans="1:5" ht="17" thickBot="1">
       <c r="A617" s="11">
         <v>44177</v>
       </c>
@@ -18099,7 +18114,7 @@
         <v>546209</v>
       </c>
     </row>
-    <row r="618" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="618" spans="1:5" ht="17" thickBot="1">
       <c r="A618" s="11">
         <v>44191</v>
       </c>
@@ -18117,7 +18132,7 @@
         <v>405111</v>
       </c>
     </row>
-    <row r="619" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="619" spans="1:5" ht="17" thickBot="1">
       <c r="A619" s="11">
         <v>44198</v>
       </c>
@@ -18135,7 +18150,7 @@
         <v>421991</v>
       </c>
     </row>
-    <row r="620" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="620" spans="1:5" ht="17" thickBot="1">
       <c r="A620" s="11">
         <v>44205</v>
       </c>
@@ -18153,7 +18168,7 @@
         <v>525253</v>
       </c>
     </row>
-    <row r="621" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="621" spans="1:5" ht="17" thickBot="1">
       <c r="A621" s="11">
         <v>44212</v>
       </c>
@@ -18171,7 +18186,7 @@
         <v>528547</v>
       </c>
     </row>
-    <row r="622" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="622" spans="1:5" ht="17" thickBot="1">
       <c r="A622" s="11">
         <v>44219</v>
       </c>
@@ -18189,7 +18204,7 @@
         <v>529030</v>
       </c>
     </row>
-    <row r="623" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="623" spans="1:5" ht="17" thickBot="1">
       <c r="A623" s="11">
         <v>44226</v>
       </c>
@@ -18207,7 +18222,7 @@
         <v>520693</v>
       </c>
     </row>
-    <row r="624" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="624" spans="1:5" ht="17" thickBot="1">
       <c r="A624" s="11">
         <v>44233</v>
       </c>
@@ -18225,7 +18240,7 @@
         <v>495815</v>
       </c>
     </row>
-    <row r="625" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="625" spans="1:5" ht="17" thickBot="1">
       <c r="A625" s="11">
         <v>44240</v>
       </c>
@@ -18243,7 +18258,7 @@
         <v>480483</v>
       </c>
     </row>
-    <row r="626" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="626" spans="1:5" ht="17" thickBot="1">
       <c r="A626" s="13">
         <v>44247</v>
       </c>
@@ -18261,7 +18276,7 @@
         <v>377904</v>
       </c>
     </row>
-    <row r="627" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="627" spans="1:5" ht="17" thickBot="1">
       <c r="A627" s="11">
         <v>44254</v>
       </c>
@@ -18279,7 +18294,7 @@
         <v>486429</v>
       </c>
     </row>
-    <row r="628" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="628" spans="1:5" ht="17" thickBot="1">
       <c r="A628" s="11">
         <v>44261</v>
       </c>
@@ -18297,7 +18312,7 @@
         <v>515135</v>
       </c>
     </row>
-    <row r="629" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="629" spans="1:5" ht="17" thickBot="1">
       <c r="A629" s="11">
         <v>44268</v>
       </c>
@@ -18315,7 +18330,7 @@
         <v>520736</v>
       </c>
     </row>
-    <row r="630" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="630" spans="1:5" ht="17" thickBot="1">
       <c r="A630" s="11">
         <v>44275</v>
       </c>
@@ -18333,7 +18348,7 @@
         <v>513325</v>
       </c>
     </row>
-    <row r="631" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="631" spans="1:5" ht="17" thickBot="1">
       <c r="A631" s="11">
         <v>44282</v>
       </c>
@@ -18351,7 +18366,7 @@
         <v>521731</v>
       </c>
     </row>
-    <row r="632" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="632" spans="1:5" ht="17" thickBot="1">
       <c r="A632" s="11">
         <v>44289</v>
       </c>
@@ -18369,7 +18384,7 @@
         <v>515562</v>
       </c>
     </row>
-    <row r="633" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="633" spans="1:5" ht="17" thickBot="1">
       <c r="A633" s="11">
         <v>44296</v>
       </c>
@@ -18387,7 +18402,7 @@
         <v>513724</v>
       </c>
     </row>
-    <row r="634" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="634" spans="1:5" ht="17" thickBot="1">
       <c r="A634" s="11">
         <v>44303</v>
       </c>
@@ -18405,7 +18420,7 @@
         <v>533217</v>
       </c>
     </row>
-    <row r="635" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="635" spans="1:5" ht="17" thickBot="1">
       <c r="A635" s="11">
         <v>44310</v>
       </c>
@@ -18423,7 +18438,7 @@
         <v>538184</v>
       </c>
     </row>
-    <row r="636" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="636" spans="1:5" ht="17" thickBot="1">
       <c r="A636" s="11">
         <v>44317</v>
       </c>
@@ -18441,7 +18456,7 @@
         <v>540667</v>
       </c>
     </row>
-    <row r="637" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="637" spans="1:5" ht="17" thickBot="1">
       <c r="A637" s="11">
         <v>44324</v>
       </c>
@@ -18459,7 +18474,7 @@
         <v>523309</v>
       </c>
     </row>
-    <row r="638" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="638" spans="1:5" ht="17" thickBot="1">
       <c r="A638" s="11">
         <v>44331</v>
       </c>
@@ -18477,7 +18492,7 @@
         <v>533872</v>
       </c>
     </row>
-    <row r="639" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="639" spans="1:5" ht="17" thickBot="1">
       <c r="A639" s="11">
         <v>44338</v>
       </c>
@@ -18495,7 +18510,7 @@
         <v>528774</v>
       </c>
     </row>
-    <row r="640" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="640" spans="1:5" ht="17" thickBot="1">
       <c r="A640" s="11">
         <v>44345</v>
       </c>
@@ -18513,7 +18528,7 @@
         <v>530225</v>
       </c>
     </row>
-    <row r="641" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="641" spans="1:5" ht="17" thickBot="1">
       <c r="A641" s="11">
         <v>44352</v>
       </c>
@@ -18531,7 +18546,7 @@
         <v>489144</v>
       </c>
     </row>
-    <row r="642" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="642" spans="1:5" ht="17" thickBot="1">
       <c r="A642" s="11">
         <v>44359</v>
       </c>
@@ -18564,7 +18579,7 @@
         <v>529635</v>
       </c>
     </row>
-    <row r="643" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="643" spans="1:5" ht="17" thickBot="1">
       <c r="A643" s="11">
         <v>44366</v>
       </c>
@@ -18582,7 +18597,7 @@
         <v>514112</v>
       </c>
     </row>
-    <row r="644" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="644" spans="1:5" ht="17" thickBot="1">
       <c r="A644" s="11">
         <v>44373</v>
       </c>
@@ -18600,7 +18615,7 @@
         <v>516167</v>
       </c>
     </row>
-    <row r="645" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="645" spans="1:5" ht="17" thickBot="1">
       <c r="A645" s="11">
         <v>44380</v>
       </c>
@@ -18618,7 +18633,7 @@
         <v>512919</v>
       </c>
     </row>
-    <row r="646" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="646" spans="1:5" ht="17" thickBot="1">
       <c r="A646" s="11">
         <v>44387</v>
       </c>
@@ -18636,7 +18651,7 @@
         <v>451825</v>
       </c>
     </row>
-    <row r="647" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="647" spans="1:5" ht="17" thickBot="1">
       <c r="A647" s="11">
         <v>44394</v>
       </c>
@@ -18654,7 +18669,7 @@
         <v>513255</v>
       </c>
     </row>
-    <row r="648" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="648" spans="1:5" ht="17" thickBot="1">
       <c r="A648" s="11">
         <v>44401</v>
       </c>
@@ -18672,7 +18687,7 @@
         <v>503219</v>
       </c>
     </row>
-    <row r="649" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="649" spans="1:5" ht="17" thickBot="1">
       <c r="A649" s="11">
         <v>44408</v>
       </c>
@@ -18690,7 +18705,7 @@
         <v>502540</v>
       </c>
     </row>
-    <row r="650" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="650" spans="1:5" ht="17" thickBot="1">
       <c r="A650" s="11">
         <v>44415</v>
       </c>
@@ -18708,7 +18723,7 @@
         <v>509607</v>
       </c>
     </row>
-    <row r="651" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="651" spans="1:5" ht="17" thickBot="1">
       <c r="A651" s="13">
         <v>44422</v>
       </c>
@@ -18726,7 +18741,7 @@
         <v>504810</v>
       </c>
     </row>
-    <row r="652" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="652" spans="1:5" ht="17" thickBot="1">
       <c r="A652" s="11">
         <v>44429</v>
       </c>
@@ -18744,7 +18759,7 @@
         <v>501273</v>
       </c>
     </row>
-    <row r="653" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="653" spans="1:5" ht="17" thickBot="1">
       <c r="A653" s="11">
         <v>44436</v>
       </c>
@@ -18762,7 +18777,7 @@
         <v>504417</v>
       </c>
     </row>
-    <row r="654" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="654" spans="1:5" ht="17" thickBot="1">
       <c r="A654" s="11">
         <v>44443</v>
       </c>
@@ -18780,7 +18795,7 @@
         <v>494415</v>
       </c>
     </row>
-    <row r="655" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="655" spans="1:5" ht="17" thickBot="1">
       <c r="A655" s="11">
         <v>44450</v>
       </c>
@@ -18798,7 +18813,7 @@
         <v>468610</v>
       </c>
     </row>
-    <row r="656" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="656" spans="1:5" ht="17" thickBot="1">
       <c r="A656" s="11">
         <v>44457</v>
       </c>
@@ -18816,7 +18831,7 @@
         <v>505622</v>
       </c>
     </row>
-    <row r="657" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="657" spans="1:5" ht="17" thickBot="1">
       <c r="A657" s="11">
         <v>44464</v>
       </c>
@@ -18834,7 +18849,7 @@
         <v>511713</v>
       </c>
     </row>
-    <row r="658" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="658" spans="1:5" ht="17" thickBot="1">
       <c r="A658" s="11">
         <v>44471</v>
       </c>
@@ -18852,7 +18867,7 @@
         <v>515849</v>
       </c>
     </row>
-    <row r="659" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="659" spans="1:5" ht="17" thickBot="1">
       <c r="A659" s="11">
         <v>44478</v>
       </c>
@@ -18870,7 +18885,7 @@
         <v>506642</v>
       </c>
     </row>
-    <row r="660" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="660" spans="1:5" ht="17" thickBot="1">
       <c r="A660" s="11">
         <v>44485</v>
       </c>
@@ -18888,7 +18903,7 @@
         <v>496983</v>
       </c>
     </row>
-    <row r="661" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="661" spans="1:5" ht="17" thickBot="1">
       <c r="A661" s="11">
         <v>44492</v>
       </c>
@@ -18906,7 +18921,7 @@
         <v>510762</v>
       </c>
     </row>
-    <row r="662" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="662" spans="1:5" ht="17" thickBot="1">
       <c r="A662" s="11">
         <v>44499</v>
       </c>
@@ -18924,7 +18939,7 @@
         <v>510141</v>
       </c>
     </row>
-    <row r="663" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="663" spans="1:5" ht="17" thickBot="1">
       <c r="A663" s="11">
         <v>44506</v>
       </c>
@@ -18942,7 +18957,7 @@
         <v>504111</v>
       </c>
     </row>
-    <row r="664" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="664" spans="1:5" ht="17" thickBot="1">
       <c r="A664" s="11">
         <v>44513</v>
       </c>
@@ -18960,7 +18975,7 @@
         <v>502613</v>
       </c>
     </row>
-    <row r="665" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="665" spans="1:5" ht="17" thickBot="1">
       <c r="A665" s="11">
         <v>44520</v>
       </c>
@@ -18978,7 +18993,7 @@
         <v>508309</v>
       </c>
     </row>
-    <row r="666" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="666" spans="1:5" ht="17" thickBot="1">
       <c r="A666" s="11">
         <v>44527</v>
       </c>
@@ -18996,7 +19011,7 @@
         <v>430793</v>
       </c>
     </row>
-    <row r="667" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="667" spans="1:5" ht="17" thickBot="1">
       <c r="A667" s="11">
         <v>44534</v>
       </c>
@@ -19014,7 +19029,7 @@
         <v>527406</v>
       </c>
     </row>
-    <row r="668" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="668" spans="1:5" ht="17" thickBot="1">
       <c r="A668" s="11">
         <v>44541</v>
       </c>
@@ -19032,7 +19047,7 @@
         <v>513366</v>
       </c>
     </row>
-    <row r="669" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="669" spans="1:5" ht="17" thickBot="1">
       <c r="A669" s="11">
         <v>44548</v>
       </c>
@@ -19050,7 +19065,7 @@
         <v>504099</v>
       </c>
     </row>
-    <row r="670" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="670" spans="1:5" ht="17" thickBot="1">
       <c r="A670" s="11">
         <v>44555</v>
       </c>
@@ -19068,7 +19083,7 @@
         <v>420373</v>
       </c>
     </row>
-    <row r="671" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="671" spans="1:5" ht="17" thickBot="1">
       <c r="A671" s="11">
         <v>44562</v>
       </c>
@@ -19086,7 +19101,7 @@
         <v>395371</v>
       </c>
     </row>
-    <row r="672" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="672" spans="1:5" ht="17" thickBot="1">
       <c r="A672" s="11">
         <v>44569</v>
       </c>
@@ -19104,7 +19119,7 @@
         <v>440761</v>
       </c>
     </row>
-    <row r="673" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="673" spans="1:5" ht="17" thickBot="1">
       <c r="A673" s="11">
         <v>44576</v>
       </c>
@@ -19122,7 +19137,7 @@
         <v>493617</v>
       </c>
     </row>
-    <row r="674" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="674" spans="1:5" ht="17" thickBot="1">
       <c r="A674" s="11">
         <v>44583</v>
       </c>
@@ -19140,7 +19155,7 @@
         <v>477462</v>
       </c>
     </row>
-    <row r="675" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="675" spans="1:5" ht="17" thickBot="1">
       <c r="A675" s="11">
         <v>44590</v>
       </c>
@@ -19158,7 +19173,7 @@
         <v>491868</v>
       </c>
     </row>
-    <row r="676" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="676" spans="1:5" ht="17" thickBot="1">
       <c r="A676" s="13">
         <v>44597</v>
       </c>
@@ -19176,7 +19191,7 @@
         <v>458152</v>
       </c>
     </row>
-    <row r="677" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="677" spans="1:5" ht="17" thickBot="1">
       <c r="A677" s="11">
         <v>44604</v>
       </c>
@@ -19194,7 +19209,7 @@
         <v>504482</v>
       </c>
     </row>
-    <row r="678" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="678" spans="1:5" ht="17" thickBot="1">
       <c r="A678" s="11">
         <v>44611</v>
       </c>
@@ -19212,7 +19227,7 @@
         <v>497822</v>
       </c>
     </row>
-    <row r="679" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="679" spans="1:5" ht="17" thickBot="1">
       <c r="A679" s="11">
         <v>44625</v>
       </c>
@@ -19230,7 +19245,7 @@
         <v>505177</v>
       </c>
     </row>
-    <row r="680" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="680" spans="1:5" ht="17" thickBot="1">
       <c r="A680" s="11">
         <v>44632</v>
       </c>
@@ -19248,7 +19263,7 @@
         <v>496134</v>
       </c>
     </row>
-    <row r="681" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="681" spans="1:5" ht="17" thickBot="1">
       <c r="A681" s="11">
         <v>44639</v>
       </c>
@@ -19266,7 +19281,7 @@
         <v>499362</v>
       </c>
     </row>
-    <row r="682" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="682" spans="1:5" ht="17" thickBot="1">
       <c r="A682" s="11">
         <v>44646</v>
       </c>
@@ -19284,7 +19299,7 @@
         <v>504817</v>
       </c>
     </row>
-    <row r="683" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="683" spans="1:5" ht="17" thickBot="1">
       <c r="A683" s="11">
         <v>44653</v>
       </c>
@@ -19302,7 +19317,7 @@
         <v>502194</v>
       </c>
     </row>
-    <row r="684" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="684" spans="1:5" ht="17" thickBot="1">
       <c r="A684" s="11">
         <v>44660</v>
       </c>
@@ -19320,7 +19335,7 @@
         <v>508343</v>
       </c>
     </row>
-    <row r="685" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="685" spans="1:5" ht="17" thickBot="1">
       <c r="A685" s="11">
         <v>44667</v>
       </c>
@@ -19338,7 +19353,7 @@
         <v>489801</v>
       </c>
     </row>
-    <row r="686" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="686" spans="1:5" ht="17" thickBot="1">
       <c r="A686" s="11">
         <v>44674</v>
       </c>
@@ -19356,7 +19371,7 @@
         <v>498011</v>
       </c>
     </row>
-    <row r="687" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="687" spans="1:5" ht="17" thickBot="1">
       <c r="A687" s="11">
         <v>44681</v>
       </c>
@@ -19374,7 +19389,7 @@
         <v>506699</v>
       </c>
     </row>
-    <row r="688" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="688" spans="1:5" ht="17" thickBot="1">
       <c r="A688" s="11">
         <v>44688</v>
       </c>
@@ -19392,7 +19407,7 @@
         <v>504927</v>
       </c>
     </row>
-    <row r="689" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="689" spans="1:5" ht="17" thickBot="1">
       <c r="A689" s="11">
         <v>44695</v>
       </c>
@@ -19410,7 +19425,7 @@
         <v>505120</v>
       </c>
     </row>
-    <row r="690" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="690" spans="1:5" ht="17" thickBot="1">
       <c r="A690" s="11">
         <v>44702</v>
       </c>
@@ -19428,7 +19443,7 @@
         <v>506976</v>
       </c>
     </row>
-    <row r="691" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="691" spans="1:5" ht="17" thickBot="1">
       <c r="A691" s="11">
         <v>44709</v>
       </c>
@@ -19446,7 +19461,7 @@
         <v>514277</v>
       </c>
     </row>
-    <row r="692" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="692" spans="1:5" ht="17" thickBot="1">
       <c r="A692" s="11">
         <v>44716</v>
       </c>
@@ -19464,7 +19479,7 @@
         <v>475513</v>
       </c>
     </row>
-    <row r="693" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="693" spans="1:5" ht="17" thickBot="1">
       <c r="A693" s="11">
         <v>44723</v>
       </c>
@@ -19482,7 +19497,7 @@
         <v>510295</v>
       </c>
     </row>
-    <row r="694" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="694" spans="1:5" ht="17" thickBot="1">
       <c r="A694" s="11">
         <v>44730</v>
       </c>
@@ -19500,7 +19515,7 @@
         <v>501207</v>
       </c>
     </row>
-    <row r="695" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="695" spans="1:5" ht="17" thickBot="1">
       <c r="A695" s="11">
         <v>44737</v>
       </c>
@@ -19518,7 +19533,7 @@
         <v>493374</v>
       </c>
     </row>
-    <row r="696" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="696" spans="1:5" ht="17" thickBot="1">
       <c r="A696" s="11">
         <v>44744</v>
       </c>
@@ -19536,7 +19551,7 @@
         <v>500285</v>
       </c>
     </row>
-    <row r="697" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="697" spans="1:5" ht="17" thickBot="1">
       <c r="A697" s="11">
         <v>44751</v>
       </c>
@@ -19554,7 +19569,7 @@
         <v>437600</v>
       </c>
     </row>
-    <row r="698" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="698" spans="1:5" ht="17" thickBot="1">
       <c r="A698" s="11">
         <v>44758</v>
       </c>
@@ -19572,7 +19587,7 @@
         <v>498899</v>
       </c>
     </row>
-    <row r="699" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="699" spans="1:5" ht="17" thickBot="1">
       <c r="A699" s="11">
         <v>44765</v>
       </c>
@@ -19590,7 +19605,7 @@
         <v>498901</v>
       </c>
     </row>
-    <row r="700" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="700" spans="1:5" ht="17" thickBot="1">
       <c r="A700" s="11">
         <v>44772</v>
       </c>
@@ -19608,7 +19623,7 @@
         <v>505409</v>
       </c>
     </row>
-    <row r="701" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="701" spans="1:5" ht="17" thickBot="1">
       <c r="A701" s="13">
         <v>44779</v>
       </c>
@@ -19626,7 +19641,7 @@
         <v>496526</v>
       </c>
     </row>
-    <row r="702" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="702" spans="1:5" ht="17" thickBot="1">
       <c r="A702" s="11">
         <v>44786</v>
       </c>
@@ -19644,7 +19659,7 @@
         <v>502775</v>
       </c>
     </row>
-    <row r="703" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="703" spans="1:5" ht="17" thickBot="1">
       <c r="A703" s="11">
         <v>44793</v>
       </c>
@@ -19662,7 +19677,7 @@
         <v>501548</v>
       </c>
     </row>
-    <row r="704" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="704" spans="1:5" ht="17" thickBot="1">
       <c r="A704" s="11">
         <v>44800</v>
       </c>
@@ -19680,7 +19695,7 @@
         <v>511574</v>
       </c>
     </row>
-    <row r="705" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="705" spans="1:5" ht="17" thickBot="1">
       <c r="A705" s="11">
         <v>44807</v>
       </c>
@@ -19698,7 +19713,7 @@
         <v>513087</v>
       </c>
     </row>
-    <row r="706" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="706" spans="1:5" ht="17" thickBot="1">
       <c r="A706" s="11">
         <v>44814</v>
       </c>
@@ -19731,7 +19746,7 @@
         <v>464261</v>
       </c>
     </row>
-    <row r="707" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="707" spans="1:5" ht="17" thickBot="1">
       <c r="A707" s="11">
         <v>44821</v>
       </c>
@@ -19749,7 +19764,7 @@
         <v>490654</v>
       </c>
     </row>
-    <row r="708" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="708" spans="1:5" ht="17" thickBot="1">
       <c r="A708" s="11">
         <v>44828</v>
       </c>
@@ -19767,7 +19782,7 @@
         <v>489111</v>
       </c>
     </row>
-    <row r="709" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="709" spans="1:5" ht="17" thickBot="1">
       <c r="A709" s="11">
         <v>44835</v>
       </c>
@@ -19785,7 +19800,7 @@
         <v>495868</v>
       </c>
     </row>
-    <row r="710" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="710" spans="1:5" ht="17" thickBot="1">
       <c r="A710" s="11">
         <v>44842</v>
       </c>
@@ -19803,7 +19818,7 @@
         <v>494413</v>
       </c>
     </row>
-    <row r="711" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="711" spans="1:5" ht="17" thickBot="1">
       <c r="A711" s="11">
         <v>44849</v>
       </c>
@@ -19821,7 +19836,7 @@
         <v>500304</v>
       </c>
     </row>
-    <row r="712" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="712" spans="1:5" ht="17" thickBot="1">
       <c r="A712" s="11">
         <v>44856</v>
       </c>
@@ -19839,7 +19854,7 @@
         <v>505322</v>
       </c>
     </row>
-    <row r="713" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="713" spans="1:5" ht="17" thickBot="1">
       <c r="A713" s="11">
         <v>44863</v>
       </c>
@@ -19857,7 +19872,7 @@
         <v>514457</v>
       </c>
     </row>
-    <row r="714" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="714" spans="1:5" ht="17" thickBot="1">
       <c r="A714" s="11">
         <v>44870</v>
       </c>
@@ -19875,7 +19890,7 @@
         <v>502106</v>
       </c>
     </row>
-    <row r="715" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="715" spans="1:5" ht="17" thickBot="1">
       <c r="A715" s="11">
         <v>44877</v>
       </c>
@@ -19893,7 +19908,7 @@
         <v>490350</v>
       </c>
     </row>
-    <row r="716" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="716" spans="1:5" ht="17" thickBot="1">
       <c r="A716" s="11">
         <v>44884</v>
       </c>
@@ -19911,7 +19926,7 @@
         <v>491794</v>
       </c>
     </row>
-    <row r="717" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="717" spans="1:5" ht="17" thickBot="1">
       <c r="A717" s="11">
         <v>44891</v>
       </c>
@@ -19929,7 +19944,7 @@
         <v>413305</v>
       </c>
     </row>
-    <row r="718" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="718" spans="1:5" ht="17" thickBot="1">
       <c r="A718" s="11">
         <v>44898</v>
       </c>
@@ -19947,7 +19962,7 @@
         <v>495472</v>
       </c>
     </row>
-    <row r="719" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="719" spans="1:5" ht="17" thickBot="1">
       <c r="A719" s="11">
         <v>44905</v>
       </c>
@@ -19965,7 +19980,7 @@
         <v>500310</v>
       </c>
     </row>
-    <row r="720" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="720" spans="1:5" ht="17" thickBot="1">
       <c r="A720" s="11">
         <v>44912</v>
       </c>
@@ -19983,7 +19998,7 @@
         <v>476232</v>
       </c>
     </row>
-    <row r="721" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="721" spans="1:5" ht="17" thickBot="1">
       <c r="A721" s="11">
         <v>44919</v>
       </c>
@@ -20001,7 +20016,7 @@
         <v>400289</v>
       </c>
     </row>
-    <row r="722" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="722" spans="1:5" ht="17" thickBot="1">
       <c r="A722" s="11">
         <v>44926</v>
       </c>
@@ -20019,7 +20034,7 @@
         <v>365553</v>
       </c>
     </row>
-    <row r="723" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="723" spans="1:5" ht="17" thickBot="1">
       <c r="A723" s="11">
         <v>44933</v>
       </c>
@@ -20037,7 +20052,7 @@
         <v>416489</v>
       </c>
     </row>
-    <row r="724" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="724" spans="1:5" ht="17" thickBot="1">
       <c r="A724" s="11">
         <v>44940</v>
       </c>
@@ -20055,7 +20070,7 @@
         <v>486000</v>
       </c>
     </row>
-    <row r="725" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="725" spans="1:5" ht="17" thickBot="1">
       <c r="A725" s="11">
         <v>44947</v>
       </c>
@@ -20073,7 +20088,7 @@
         <v>467485</v>
       </c>
     </row>
-    <row r="726" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="726" spans="1:5" ht="17" thickBot="1">
       <c r="A726" s="13">
         <v>44954</v>
       </c>
@@ -20091,7 +20106,7 @@
         <v>473650</v>
       </c>
     </row>
-    <row r="727" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="727" spans="1:5" ht="17" thickBot="1">
       <c r="A727" s="11">
         <v>44961</v>
       </c>
@@ -20109,7 +20124,7 @@
         <v>449586</v>
       </c>
     </row>
-    <row r="728" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="728" spans="1:5" ht="17" thickBot="1">
       <c r="A728" s="11">
         <v>44968</v>
       </c>
@@ -20127,7 +20142,7 @@
         <v>473972</v>
       </c>
     </row>
-    <row r="729" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="729" spans="1:5" ht="17" thickBot="1">
       <c r="A729" s="11">
         <v>44975</v>
       </c>
@@ -20145,7 +20160,7 @@
         <v>466932</v>
       </c>
     </row>
-    <row r="730" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="730" spans="1:5" ht="17" thickBot="1">
       <c r="A730" s="11">
         <v>44982</v>
       </c>
@@ -20163,7 +20178,7 @@
         <v>459233</v>
       </c>
     </row>
-    <row r="731" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="731" spans="1:5" ht="17" thickBot="1">
       <c r="A731" s="11">
         <v>44989</v>
       </c>
@@ -20181,7 +20196,7 @@
         <v>474191</v>
       </c>
     </row>
-    <row r="732" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="732" spans="1:5" ht="17" thickBot="1">
       <c r="A732" s="11">
         <v>44996</v>
       </c>
@@ -20199,7 +20214,7 @@
         <v>458629</v>
       </c>
     </row>
-    <row r="733" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="733" spans="1:5" ht="17" thickBot="1">
       <c r="A733" s="11">
         <v>45003</v>
       </c>
@@ -20217,7 +20232,7 @@
         <v>453500</v>
       </c>
     </row>
-    <row r="734" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="734" spans="1:5" ht="17" thickBot="1">
       <c r="A734" s="11">
         <v>45010</v>
       </c>
@@ -20235,7 +20250,7 @@
         <v>469958</v>
       </c>
     </row>
-    <row r="735" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="735" spans="1:5" ht="17" thickBot="1">
       <c r="A735" s="11">
         <v>45017</v>
       </c>
@@ -20253,7 +20268,7 @@
         <v>467430</v>
       </c>
     </row>
-    <row r="736" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="736" spans="1:5" ht="17" thickBot="1">
       <c r="A736" s="11">
         <v>45024</v>
       </c>
@@ -20271,7 +20286,7 @@
         <v>451336</v>
       </c>
     </row>
-    <row r="737" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="737" spans="1:5" ht="17" thickBot="1">
       <c r="A737" s="11">
         <v>45031</v>
       </c>
@@ -20289,7 +20304,7 @@
         <v>468197</v>
       </c>
     </row>
-    <row r="738" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="738" spans="1:5" ht="17" thickBot="1">
       <c r="A738" s="11">
         <v>45038</v>
       </c>
@@ -20307,7 +20322,7 @@
         <v>480457</v>
       </c>
     </row>
-    <row r="739" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="739" spans="1:5" ht="17" thickBot="1">
       <c r="A739" s="11">
         <v>45045</v>
       </c>
@@ -20325,7 +20340,7 @@
         <v>481960</v>
       </c>
     </row>
-    <row r="740" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="740" spans="1:5" ht="17" thickBot="1">
       <c r="A740" s="11">
         <v>45052</v>
       </c>
@@ -20343,7 +20358,7 @@
         <v>471859</v>
       </c>
     </row>
-    <row r="741" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="741" spans="1:5" ht="17" thickBot="1">
       <c r="A741" s="11">
         <v>45059</v>
       </c>
@@ -20361,7 +20376,7 @@
         <v>466381</v>
       </c>
     </row>
-    <row r="742" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="742" spans="1:5" ht="17" thickBot="1">
       <c r="A742" s="11">
         <v>45066</v>
       </c>
@@ -20379,7 +20394,7 @@
         <v>470694</v>
       </c>
     </row>
-    <row r="743" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="743" spans="1:5" ht="17" thickBot="1">
       <c r="A743" s="11">
         <v>45073</v>
       </c>
@@ -20397,7 +20412,7 @@
         <v>480998</v>
       </c>
     </row>
-    <row r="744" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="744" spans="1:5" ht="17" thickBot="1">
       <c r="A744" s="11">
         <v>45080</v>
       </c>
@@ -20415,7 +20430,7 @@
         <v>439601</v>
       </c>
     </row>
-    <row r="745" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="745" spans="1:5" ht="17" thickBot="1">
       <c r="A745" s="11">
         <v>45087</v>
       </c>
@@ -20433,7 +20448,7 @@
         <v>471141</v>
       </c>
     </row>
-    <row r="746" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="746" spans="1:5" ht="17" thickBot="1">
       <c r="A746" s="11">
         <v>45094</v>
       </c>
@@ -20451,7 +20466,7 @@
         <v>477126</v>
       </c>
     </row>
-    <row r="747" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="747" spans="1:5" ht="17" thickBot="1">
       <c r="A747" s="11">
         <v>45101</v>
       </c>
@@ -20469,7 +20484,7 @@
         <v>469453</v>
       </c>
     </row>
-    <row r="748" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="748" spans="1:5" ht="17" thickBot="1">
       <c r="A748" s="11">
         <v>45108</v>
       </c>
@@ -20487,7 +20502,7 @@
         <v>474443</v>
       </c>
     </row>
-    <row r="749" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="749" spans="1:5" ht="17" thickBot="1">
       <c r="A749" s="11">
         <v>45115</v>
       </c>
@@ -20505,7 +20520,7 @@
         <v>407843</v>
       </c>
     </row>
-    <row r="750" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="750" spans="1:5" ht="17" thickBot="1">
       <c r="A750" s="11">
         <v>45122</v>
       </c>
@@ -20523,7 +20538,7 @@
         <v>478153</v>
       </c>
     </row>
-    <row r="751" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="751" spans="1:5" ht="17" thickBot="1">
       <c r="A751" s="13">
         <v>45129</v>
       </c>
@@ -20541,7 +20556,7 @@
         <v>473736</v>
       </c>
     </row>
-    <row r="752" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="752" spans="1:5" ht="17" thickBot="1">
       <c r="A752" s="11">
         <v>45136</v>
       </c>
@@ -20559,7 +20574,7 @@
         <v>483481</v>
       </c>
     </row>
-    <row r="753" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="753" spans="1:5" ht="17" thickBot="1">
       <c r="A753" s="11">
         <v>45143</v>
       </c>
@@ -20577,7 +20592,7 @@
         <v>471938</v>
       </c>
     </row>
-    <row r="754" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="754" spans="1:5" ht="17" thickBot="1">
       <c r="A754" s="11">
         <v>45150</v>
       </c>
@@ -20595,7 +20610,7 @@
         <v>472498</v>
       </c>
     </row>
-    <row r="755" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="755" spans="1:5" ht="17" thickBot="1">
       <c r="A755" s="11">
         <v>45157</v>
       </c>
@@ -20613,7 +20628,7 @@
         <v>478853</v>
       </c>
     </row>
-    <row r="756" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="756" spans="1:5" ht="17" thickBot="1">
       <c r="A756" s="11">
         <v>45164</v>
       </c>
@@ -20631,7 +20646,7 @@
         <v>472525</v>
       </c>
     </row>
-    <row r="757" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="757" spans="1:5" ht="17" thickBot="1">
       <c r="A757" s="11">
         <v>45171</v>
       </c>
@@ -20649,7 +20664,7 @@
         <v>476851</v>
       </c>
     </row>
-    <row r="758" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="758" spans="1:5" ht="17" thickBot="1">
       <c r="A758" s="11">
         <v>45178</v>
       </c>
@@ -20667,7 +20682,7 @@
         <v>447345</v>
       </c>
     </row>
-    <row r="759" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="759" spans="1:5" ht="17" thickBot="1">
       <c r="A759" s="11">
         <v>45185</v>
       </c>
@@ -20685,7 +20700,7 @@
         <v>489790</v>
       </c>
     </row>
-    <row r="760" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="760" spans="1:5" ht="17" thickBot="1">
       <c r="A760" s="11">
         <v>45192</v>
       </c>
@@ -20703,7 +20718,7 @@
         <v>493323</v>
       </c>
     </row>
-    <row r="761" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="761" spans="1:5" ht="17" thickBot="1">
       <c r="A761" s="11">
         <v>45199</v>
       </c>
@@ -20721,7 +20736,7 @@
         <v>500154</v>
       </c>
     </row>
-    <row r="762" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="762" spans="1:5" ht="17" thickBot="1">
       <c r="A762" s="11">
         <v>45206</v>
       </c>
@@ -20739,7 +20754,7 @@
         <v>499217</v>
       </c>
     </row>
-    <row r="763" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="763" spans="1:5" ht="17" thickBot="1">
       <c r="A763" s="11">
         <v>45213</v>
       </c>
@@ -20757,7 +20772,7 @@
         <v>492781</v>
       </c>
     </row>
-    <row r="764" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="764" spans="1:5" ht="17" thickBot="1">
       <c r="A764" s="11">
         <v>45220</v>
       </c>
@@ -20775,7 +20790,7 @@
         <v>505985</v>
       </c>
     </row>
-    <row r="765" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="765" spans="1:5" ht="17" thickBot="1">
       <c r="A765" s="11">
         <v>45227</v>
       </c>
@@ -20793,7 +20808,7 @@
         <v>499389</v>
       </c>
     </row>
-    <row r="766" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="766" spans="1:5" ht="17" thickBot="1">
       <c r="A766" s="11">
         <v>45234</v>
       </c>
@@ -20811,7 +20826,7 @@
         <v>484757</v>
       </c>
     </row>
-    <row r="767" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="767" spans="1:5" ht="17" thickBot="1">
       <c r="A767" s="11">
         <v>45241</v>
       </c>
@@ -20829,7 +20844,7 @@
         <v>497348</v>
       </c>
     </row>
-    <row r="768" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="768" spans="1:5" ht="17" thickBot="1">
       <c r="A768" s="11">
         <v>45248</v>
       </c>
@@ -20847,7 +20862,7 @@
         <v>501416</v>
       </c>
     </row>
-    <row r="769" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="769" spans="1:5" ht="17" thickBot="1">
       <c r="A769" s="11">
         <v>45255</v>
       </c>
@@ -20865,7 +20880,7 @@
         <v>415332</v>
       </c>
     </row>
-    <row r="770" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="770" spans="1:5" ht="17" thickBot="1">
       <c r="A770" s="11">
         <v>45262</v>
       </c>
@@ -20898,7 +20913,7 @@
         <v>509626</v>
       </c>
     </row>
-    <row r="771" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="771" spans="1:5" ht="17" thickBot="1">
       <c r="A771" s="11">
         <v>45269</v>
       </c>
@@ -20916,7 +20931,7 @@
         <v>499094</v>
       </c>
     </row>
-    <row r="772" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="772" spans="1:5" ht="17" thickBot="1">
       <c r="A772" s="11">
         <v>45276</v>
       </c>
@@ -20934,7 +20949,7 @@
         <v>502583</v>
       </c>
     </row>
-    <row r="773" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="773" spans="1:5" ht="17" thickBot="1">
       <c r="A773" s="11">
         <v>45283</v>
       </c>
@@ -20952,7 +20967,7 @@
         <v>486787</v>
       </c>
     </row>
-    <row r="774" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="774" spans="1:5" ht="17" thickBot="1">
       <c r="A774" s="11">
         <v>45297</v>
       </c>
@@ -20970,7 +20985,7 @@
         <v>417257</v>
       </c>
     </row>
-    <row r="775" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="775" spans="1:5" ht="17" thickBot="1">
       <c r="A775" s="11">
         <v>45304</v>
       </c>
@@ -20988,7 +21003,7 @@
         <v>457453</v>
       </c>
     </row>
-    <row r="776" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="776" spans="1:5" ht="17" thickBot="1">
       <c r="A776" s="15">
         <v>45311</v>
       </c>
@@ -21006,7 +21021,7 @@
         <v>397553</v>
       </c>
     </row>
-    <row r="777" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="777" spans="1:5" ht="17" thickBot="1">
       <c r="A777" s="17">
         <v>45318</v>
       </c>
@@ -21024,7 +21039,7 @@
         <v>467222</v>
       </c>
     </row>
-    <row r="778" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="778" spans="1:5" ht="17" thickBot="1">
       <c r="A778" s="17">
         <v>45325</v>
       </c>
@@ -21042,7 +21057,7 @@
         <v>491697</v>
       </c>
     </row>
-    <row r="779" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="779" spans="1:5" ht="17" thickBot="1">
       <c r="A779" s="17">
         <v>45332</v>
       </c>
@@ -21060,7 +21075,7 @@
         <v>484840</v>
       </c>
     </row>
-    <row r="780" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="780" spans="1:5" ht="17" thickBot="1">
       <c r="A780" s="17">
         <v>45339</v>
       </c>
@@ -21078,7 +21093,7 @@
         <v>474226</v>
       </c>
     </row>
-    <row r="781" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="781" spans="1:5" ht="17" thickBot="1">
       <c r="A781" s="17">
         <v>45346</v>
       </c>
@@ -21096,7 +21111,7 @@
         <v>483656</v>
       </c>
     </row>
-    <row r="782" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="782" spans="1:5" ht="17" thickBot="1">
       <c r="A782" s="17">
         <v>45353</v>
       </c>
@@ -21114,7 +21129,7 @@
         <v>483138</v>
       </c>
     </row>
-    <row r="783" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="783" spans="1:5" ht="17" thickBot="1">
       <c r="A783" s="17">
         <v>45360</v>
       </c>
@@ -21132,7 +21147,7 @@
         <v>472662</v>
       </c>
     </row>
-    <row r="784" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="784" spans="1:5" ht="17" thickBot="1">
       <c r="A784" s="17">
         <v>45367</v>
       </c>
@@ -21150,7 +21165,7 @@
         <v>474596</v>
       </c>
     </row>
-    <row r="785" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="785" spans="1:5" ht="17" thickBot="1">
       <c r="A785" s="17">
         <v>45374</v>
       </c>
@@ -21168,7 +21183,7 @@
         <v>470593</v>
       </c>
     </row>
-    <row r="786" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="786" spans="1:5" ht="17" thickBot="1">
       <c r="A786" s="17">
         <v>45381</v>
       </c>
@@ -21186,7 +21201,7 @@
         <v>472651</v>
       </c>
     </row>
-    <row r="787" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="787" spans="1:5" ht="17" thickBot="1">
       <c r="A787" s="17">
         <v>45388</v>
       </c>
@@ -21204,7 +21219,7 @@
         <v>450142</v>
       </c>
     </row>
-    <row r="788" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="788" spans="1:5" ht="17" thickBot="1">
       <c r="A788" s="17">
         <v>45395</v>
       </c>
@@ -21222,7 +21237,7 @@
         <v>466463</v>
       </c>
     </row>
-    <row r="789" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="789" spans="1:5" ht="17" thickBot="1">
       <c r="A789" s="17">
         <v>45402</v>
       </c>
@@ -21240,7 +21255,7 @@
         <v>474544</v>
       </c>
     </row>
-    <row r="790" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="790" spans="1:5" ht="17" thickBot="1">
       <c r="A790" s="17">
         <v>45409</v>
       </c>
@@ -21258,7 +21273,7 @@
         <v>476302</v>
       </c>
     </row>
-    <row r="791" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="791" spans="1:5" ht="17" thickBot="1">
       <c r="A791" s="17">
         <v>45416</v>
       </c>
@@ -21276,7 +21291,7 @@
         <v>463106</v>
       </c>
     </row>
-    <row r="792" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="792" spans="1:5" ht="17" thickBot="1">
       <c r="A792" s="17">
         <v>45423</v>
       </c>
@@ -21294,7 +21309,7 @@
         <v>468748</v>
       </c>
     </row>
-    <row r="793" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="793" spans="1:5" ht="17" thickBot="1">
       <c r="A793" s="17">
         <v>45430</v>
       </c>
@@ -21312,7 +21327,7 @@
         <v>474886</v>
       </c>
     </row>
-    <row r="794" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="794" spans="1:5" ht="17" thickBot="1">
       <c r="A794" s="17">
         <v>45437</v>
       </c>
@@ -21330,7 +21345,7 @@
         <v>485232</v>
       </c>
     </row>
-    <row r="795" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="795" spans="1:5" ht="17" thickBot="1">
       <c r="A795" s="17">
         <v>45444</v>
       </c>
@@ -21348,7 +21363,7 @@
         <v>450077</v>
       </c>
     </row>
-    <row r="796" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="796" spans="1:5" ht="17" thickBot="1">
       <c r="A796" s="17">
         <v>45451</v>
       </c>
@@ -21366,7 +21381,7 @@
         <v>489916</v>
       </c>
     </row>
-    <row r="797" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="797" spans="1:5" ht="17" thickBot="1">
       <c r="A797" s="17">
         <v>45458</v>
       </c>
@@ -21384,7 +21399,7 @@
         <v>493138</v>
       </c>
     </row>
-    <row r="798" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="798" spans="1:5" ht="17" thickBot="1">
       <c r="A798" s="17">
         <v>45465</v>
       </c>
@@ -21402,7 +21417,7 @@
         <v>485557</v>
       </c>
     </row>
-    <row r="799" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="799" spans="1:5" ht="17" thickBot="1">
       <c r="A799" s="17">
         <v>45472</v>
       </c>
@@ -21420,7 +21435,7 @@
         <v>491899</v>
       </c>
     </row>
-    <row r="800" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="800" spans="1:5" ht="17" thickBot="1">
       <c r="A800" s="17">
         <v>45479</v>
       </c>
@@ -21438,7 +21453,7 @@
         <v>421817</v>
       </c>
     </row>
-    <row r="801" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="801" spans="1:5" ht="17" thickBot="1">
       <c r="A801" s="15">
         <v>45486</v>
       </c>
@@ -21456,7 +21471,7 @@
         <v>483806</v>
       </c>
     </row>
-    <row r="802" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="802" spans="1:5" ht="17" thickBot="1">
       <c r="A802" s="17">
         <v>45493</v>
       </c>
@@ -21474,7 +21489,7 @@
         <v>480083</v>
       </c>
     </row>
-    <row r="803" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="803" spans="1:5" ht="17" thickBot="1">
       <c r="A803" s="17">
         <v>45500</v>
       </c>
@@ -21492,7 +21507,7 @@
         <v>508496</v>
       </c>
     </row>
-    <row r="804" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="804" spans="1:5" ht="17" thickBot="1">
       <c r="A804" s="17">
         <v>45507</v>
       </c>
@@ -21510,7 +21525,7 @@
         <v>498807</v>
       </c>
     </row>
-    <row r="805" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="805" spans="1:5" ht="17" thickBot="1">
       <c r="A805" s="17">
         <v>45514</v>
       </c>
@@ -21528,7 +21543,7 @@
         <v>496509</v>
       </c>
     </row>
-    <row r="806" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="806" spans="1:5" ht="17" thickBot="1">
       <c r="A806" s="17">
         <v>45521</v>
       </c>
@@ -21546,7 +21561,7 @@
         <v>516819</v>
       </c>
     </row>
-    <row r="807" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="807" spans="1:5" ht="17" thickBot="1">
       <c r="A807" s="17">
         <v>45528</v>
       </c>
@@ -21564,7 +21579,7 @@
         <v>516807</v>
       </c>
     </row>
-    <row r="808" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="808" spans="1:5" ht="17" thickBot="1">
       <c r="A808" s="17">
         <v>45535</v>
       </c>
@@ -21582,7 +21597,7 @@
         <v>516632</v>
       </c>
     </row>
-    <row r="809" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="809" spans="1:5" ht="17" thickBot="1">
       <c r="A809" s="17">
         <v>45542</v>
       </c>
@@ -21600,7 +21615,7 @@
         <v>479179</v>
       </c>
     </row>
-    <row r="810" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="810" spans="1:5" ht="17" thickBot="1">
       <c r="A810" s="17">
         <v>45549</v>
       </c>
@@ -21618,7 +21633,7 @@
         <v>522557</v>
       </c>
     </row>
-    <row r="811" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="811" spans="1:5" ht="17" thickBot="1">
       <c r="A811" s="17">
         <v>45556</v>
       </c>
@@ -21636,7 +21651,7 @@
         <v>522112</v>
       </c>
     </row>
-    <row r="812" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="812" spans="1:5" ht="17" thickBot="1">
       <c r="A812" s="17">
         <v>45563</v>
       </c>
@@ -21654,7 +21669,7 @@
         <v>507537</v>
       </c>
     </row>
-    <row r="813" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="813" spans="1:5" ht="17" thickBot="1">
       <c r="A813" s="17">
         <v>45570</v>
       </c>
@@ -21672,7 +21687,7 @@
         <v>486187</v>
       </c>
     </row>
-    <row r="814" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="814" spans="1:5" ht="17" thickBot="1">
       <c r="A814" s="17">
         <v>45577</v>
       </c>
@@ -21690,7 +21705,7 @@
         <v>505033</v>
       </c>
     </row>
-    <row r="815" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="815" spans="1:5" ht="17" thickBot="1">
       <c r="A815" s="17">
         <v>45584</v>
       </c>
@@ -21708,7 +21723,7 @@
         <v>510730</v>
       </c>
     </row>
-    <row r="816" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="816" spans="1:5" ht="17" thickBot="1">
       <c r="A816" s="17">
         <v>45591</v>
       </c>
@@ -21726,7 +21741,7 @@
         <v>519415</v>
       </c>
     </row>
-    <row r="817" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="817" spans="1:5" ht="17" thickBot="1">
       <c r="A817" s="17">
         <v>45598</v>
       </c>
@@ -21744,7 +21759,7 @@
         <v>516743</v>
       </c>
     </row>
-    <row r="818" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="818" spans="1:5" ht="17" thickBot="1">
       <c r="A818" s="17">
         <v>45612</v>
       </c>
@@ -21762,7 +21777,7 @@
         <v>516886</v>
       </c>
     </row>
-    <row r="819" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="819" spans="1:5" ht="17" thickBot="1">
       <c r="A819" s="17">
         <v>45619</v>
       </c>
@@ -21780,7 +21795,7 @@
         <v>520798</v>
       </c>
     </row>
-    <row r="820" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="820" spans="1:5" ht="17" thickBot="1">
       <c r="A820" s="17">
         <v>45626</v>
       </c>
@@ -21798,7 +21813,7 @@
         <v>439362</v>
       </c>
     </row>
-    <row r="821" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="821" spans="1:5" ht="17" thickBot="1">
       <c r="A821" s="17">
         <v>45633</v>
       </c>
@@ -21816,7 +21831,7 @@
         <v>520894</v>
       </c>
     </row>
-    <row r="822" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="822" spans="1:5" ht="17" thickBot="1">
       <c r="A822" s="17">
         <v>45640</v>
       </c>
@@ -21834,7 +21849,7 @@
         <v>526166</v>
       </c>
     </row>
-    <row r="823" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="823" spans="1:5" ht="17" thickBot="1">
       <c r="A823" s="17">
         <v>45647</v>
       </c>
@@ -21852,7 +21867,7 @@
         <v>523912</v>
       </c>
     </row>
-    <row r="824" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="824" spans="1:5" ht="17" thickBot="1">
       <c r="A824" s="17">
         <v>45654</v>
       </c>
@@ -21870,7 +21885,7 @@
         <v>389700</v>
       </c>
     </row>
-    <row r="825" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="825" spans="1:5" ht="17" thickBot="1">
       <c r="A825" s="17">
         <v>45661</v>
       </c>
@@ -21888,7 +21903,7 @@
         <v>421410</v>
       </c>
     </row>
-    <row r="826" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="826" spans="1:5" ht="17" thickBot="1">
       <c r="A826" s="15">
         <v>45668</v>
       </c>
@@ -21906,7 +21921,7 @@
         <v>465390</v>
       </c>
     </row>
-    <row r="827" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="827" spans="1:5" ht="17" thickBot="1">
       <c r="A827" s="17">
         <v>45675</v>
       </c>
@@ -21924,7 +21939,7 @@
         <v>500160</v>
       </c>
     </row>
-    <row r="828" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="828" spans="1:5" ht="17" thickBot="1">
       <c r="A828" s="17">
         <v>45682</v>
       </c>
@@ -21942,7 +21957,7 @@
         <v>454797</v>
       </c>
     </row>
-    <row r="829" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="829" spans="1:5" ht="17" thickBot="1">
       <c r="A829" s="17">
         <v>45689</v>
       </c>
@@ -21960,7 +21975,7 @@
         <v>513622</v>
       </c>
     </row>
-    <row r="830" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="830" spans="1:5" ht="17" thickBot="1">
       <c r="A830" s="17">
         <v>45696</v>
       </c>
@@ -21978,7 +21993,7 @@
         <v>502449</v>
       </c>
     </row>
-    <row r="831" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="831" spans="1:5" ht="17" thickBot="1">
       <c r="A831" s="17">
         <v>45703</v>
       </c>
@@ -21996,7 +22011,7 @@
         <v>480740</v>
       </c>
     </row>
-    <row r="832" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="832" spans="1:5" ht="17" thickBot="1">
       <c r="A832" s="17">
         <v>45710</v>
       </c>
@@ -22014,7 +22029,7 @@
         <v>458513</v>
       </c>
     </row>
-    <row r="833" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="833" spans="1:5" ht="17" thickBot="1">
       <c r="A833" s="17">
         <v>45717</v>
       </c>
@@ -22032,7 +22047,7 @@
         <v>508531</v>
       </c>
     </row>
-    <row r="834" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="834" spans="1:5" ht="17" thickBot="1">
       <c r="A834" s="17">
         <v>45724</v>
       </c>
@@ -22065,7 +22080,7 @@
         <v>497412</v>
       </c>
     </row>
-    <row r="835" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="835" spans="1:5" ht="17" thickBot="1">
       <c r="A835" s="17">
         <v>45731</v>
       </c>
@@ -22083,7 +22098,7 @@
         <v>503473</v>
       </c>
     </row>
-    <row r="836" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="836" spans="1:5" ht="17" thickBot="1">
       <c r="A836" s="17">
         <v>45738</v>
       </c>
@@ -22101,7 +22116,7 @@
         <v>496214</v>
       </c>
     </row>
-    <row r="837" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="837" spans="1:5" ht="17" thickBot="1">
       <c r="A837" s="17">
         <v>45745</v>
       </c>
@@ -22119,7 +22134,7 @@
         <v>513553</v>
       </c>
     </row>
-    <row r="838" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="838" spans="1:5" ht="17" thickBot="1">
       <c r="A838" s="17">
         <v>45752</v>
       </c>
@@ -22137,7 +22152,7 @@
         <v>500584</v>
       </c>
     </row>
-    <row r="839" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="839" spans="1:5" ht="17" thickBot="1">
       <c r="A839" s="17">
         <v>45759</v>
       </c>
@@ -22155,7 +22170,7 @@
         <v>491908</v>
       </c>
     </row>
-    <row r="840" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="840" spans="1:5" ht="17" thickBot="1">
       <c r="A840" s="17">
         <v>45766</v>
       </c>
@@ -22173,7 +22188,7 @@
         <v>496053</v>
       </c>
     </row>
-    <row r="841" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="841" spans="1:5" ht="17" thickBot="1">
       <c r="A841" s="17">
         <v>45773</v>
       </c>
@@ -22191,7 +22206,7 @@
         <v>502105</v>
       </c>
     </row>
-    <row r="842" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="842" spans="1:5" ht="17" thickBot="1">
       <c r="A842" s="17">
         <v>45780</v>
       </c>
@@ -22209,7 +22224,7 @@
         <v>498693</v>
       </c>
     </row>
-    <row r="843" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="843" spans="1:5" ht="17" thickBot="1">
       <c r="A843" s="17">
         <v>45787</v>
       </c>
@@ -22227,7 +22242,7 @@
         <v>495552</v>
       </c>
     </row>
-    <row r="844" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="844" spans="1:5" ht="17" thickBot="1">
       <c r="A844" s="17">
         <v>45794</v>
       </c>
@@ -22245,7 +22260,7 @@
         <v>490775</v>
       </c>
     </row>
-    <row r="845" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="845" spans="1:5" ht="17" thickBot="1">
       <c r="A845" s="17">
         <v>45801</v>
       </c>
@@ -22263,7 +22278,7 @@
         <v>488709</v>
       </c>
     </row>
-    <row r="846" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="846" spans="1:5" ht="17" thickBot="1">
       <c r="A846" s="17">
         <v>45808</v>
       </c>
@@ -22281,7 +22296,7 @@
         <v>459884</v>
       </c>
     </row>
-    <row r="847" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="847" spans="1:5" ht="17" thickBot="1">
       <c r="A847" s="17">
         <v>45815</v>
       </c>
@@ -22299,7 +22314,7 @@
         <v>483807</v>
       </c>
     </row>
-    <row r="848" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="848" spans="1:5" ht="17" thickBot="1">
       <c r="A848" s="17">
         <v>45822</v>
       </c>
@@ -22317,7 +22332,7 @@
         <v>485810</v>
       </c>
     </row>
-    <row r="849" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="849" spans="1:5" ht="17" thickBot="1">
       <c r="A849" s="17">
         <v>45829</v>
       </c>
@@ -22335,7 +22350,7 @@
         <v>487328</v>
       </c>
     </row>
-    <row r="850" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="850" spans="1:5" ht="17" thickBot="1">
       <c r="A850" s="17">
         <v>45836</v>
       </c>
@@ -22353,7 +22368,7 @@
         <v>491424</v>
       </c>
     </row>
-    <row r="851" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="851" spans="1:5" ht="17" thickBot="1">
       <c r="A851" s="15">
         <v>45843</v>
       </c>
@@ -22371,7 +22386,7 @@
         <v>443049</v>
       </c>
     </row>
-    <row r="852" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="852" spans="1:5" ht="17" thickBot="1">
       <c r="A852" s="17">
         <v>45850</v>
       </c>
@@ -22389,7 +22404,7 @@
         <v>496188</v>
       </c>
     </row>
-    <row r="853" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="853" spans="1:5" ht="17" thickBot="1">
       <c r="A853" s="17">
         <v>45857</v>
       </c>
@@ -22407,7 +22422,7 @@
         <v>506882</v>
       </c>
     </row>
-    <row r="854" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="854" spans="1:5" ht="17" thickBot="1">
       <c r="A854" s="17">
         <v>45864</v>
       </c>
@@ -22425,7 +22440,7 @@
         <v>514279</v>
       </c>
     </row>
-    <row r="855" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="855" spans="1:5" ht="17" thickBot="1">
       <c r="A855" s="17">
         <v>45871</v>
       </c>
@@ -22443,7 +22458,7 @@
         <v>513529</v>
       </c>
     </row>
-    <row r="856" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="856" spans="1:5" ht="17" thickBot="1">
       <c r="A856" s="17">
         <v>45878</v>
       </c>
@@ -22461,7 +22476,7 @@
         <v>511194</v>
       </c>
     </row>
-    <row r="857" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="857" spans="1:5" ht="17" thickBot="1">
       <c r="A857" s="17">
         <v>45885</v>
       </c>
@@ -22479,7 +22494,7 @@
         <v>512970</v>
       </c>
     </row>
-    <row r="858" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="858" spans="1:5" ht="17" thickBot="1">
       <c r="A858" s="17">
         <v>45892</v>
       </c>
@@ -22497,7 +22512,7 @@
         <v>512333</v>
       </c>
     </row>
-    <row r="859" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="859" spans="1:5" ht="17" thickBot="1">
       <c r="A859" s="17">
         <v>45899</v>
       </c>
@@ -22515,7 +22530,7 @@
         <v>521502</v>
       </c>
     </row>
-    <row r="860" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="860" spans="1:5" ht="17" thickBot="1">
       <c r="A860" s="17">
         <v>45906</v>
       </c>
@@ -22533,7 +22548,7 @@
         <v>467880</v>
       </c>
     </row>
-    <row r="861" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="861" spans="1:5" ht="17" thickBot="1">
       <c r="A861" s="17">
         <v>45913</v>
       </c>
@@ -22551,7 +22566,7 @@
         <v>514167</v>
       </c>
     </row>
-    <row r="862" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="862" spans="1:5" ht="17" thickBot="1">
       <c r="A862" s="17">
         <v>45920</v>
       </c>
@@ -22569,7 +22584,7 @@
         <v>510677</v>
       </c>
     </row>
-    <row r="863" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="863" spans="1:5" ht="17" thickBot="1">
       <c r="A863" s="15">
         <v>45927</v>
       </c>
@@ -22587,7 +22602,7 @@
         <v>512642</v>
       </c>
     </row>
-    <row r="864" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="864" spans="1:5" ht="17" thickBot="1">
       <c r="A864" s="17">
         <v>45934</v>
       </c>
@@ -22605,7 +22620,7 @@
         <v>503538</v>
       </c>
     </row>
-    <row r="865" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="865" spans="1:5" ht="17" thickBot="1">
       <c r="A865" s="17">
         <v>45941</v>
       </c>
@@ -22623,7 +22638,7 @@
         <v>498462</v>
       </c>
     </row>
-    <row r="866" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="866" spans="1:5" ht="17" thickBot="1">
       <c r="A866" s="17">
         <v>45948</v>
       </c>
@@ -22641,7 +22656,7 @@
         <v>497854</v>
       </c>
     </row>
-    <row r="867" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="867" spans="1:5" ht="17" thickBot="1">
       <c r="A867" s="17">
         <v>45955</v>
       </c>
@@ -22659,7 +22674,7 @@
         <v>499688</v>
       </c>
     </row>
-    <row r="868" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="868" spans="1:5" ht="17" thickBot="1">
       <c r="A868" s="17">
         <v>45962</v>
       </c>
@@ -22677,7 +22692,7 @@
         <v>496928</v>
       </c>
     </row>
-    <row r="869" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="869" spans="1:5" ht="17" thickBot="1">
       <c r="A869" s="17">
         <v>45969</v>
       </c>
@@ -22695,7 +22710,7 @@
         <v>493493</v>
       </c>
     </row>
-    <row r="870" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="870" spans="1:5" ht="17" thickBot="1">
       <c r="A870" s="17">
         <v>45976</v>
       </c>
@@ -22713,7 +22728,7 @@
         <v>493880</v>
       </c>
     </row>
-    <row r="871" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="871" spans="1:5" ht="17" thickBot="1">
       <c r="A871" s="17">
         <v>45983</v>
       </c>
@@ -22731,7 +22746,7 @@
         <v>516110</v>
       </c>
     </row>
-    <row r="872" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="872" spans="1:5" ht="17" thickBot="1">
       <c r="A872" s="17">
         <v>45990</v>
       </c>
@@ -22749,7 +22764,7 @@
         <v>431435</v>
       </c>
     </row>
-    <row r="873" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="873" spans="1:5" ht="17" thickBot="1">
       <c r="A873" s="17">
         <v>45997</v>
       </c>
@@ -22767,7 +22782,7 @@
         <v>508999</v>
       </c>
     </row>
-    <row r="874" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="874" spans="1:5" ht="17" thickBot="1">
       <c r="A874" s="17">
         <v>46004</v>
       </c>
@@ -22785,7 +22800,7 @@
         <v>518904</v>
       </c>
     </row>
-    <row r="875" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="875" spans="1:5" ht="17" thickBot="1">
       <c r="A875" s="15">
         <v>46018</v>
       </c>
@@ -22803,7 +22818,7 @@
         <v>392295</v>
       </c>
     </row>
-    <row r="876" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="876" spans="1:5" ht="17" thickBot="1">
       <c r="A876" s="8">
         <v>46025</v>
       </c>
@@ -22821,7 +22836,7 @@
         <v>404293</v>
       </c>
     </row>
-    <row r="877" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="877" spans="1:5" ht="17" thickBot="1">
       <c r="A877" s="15">
         <v>46032</v>
       </c>
@@ -22839,7 +22854,7 @@
         <v>510457</v>
       </c>
     </row>
-    <row r="878" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="878" spans="1:5" ht="17" thickBot="1">
       <c r="A878" s="8">
         <v>46039</v>
       </c>
@@ -22872,7 +22887,7 @@
         <v>505385</v>
       </c>
     </row>
-    <row r="879" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="879" spans="1:5" ht="17" thickBot="1">
       <c r="A879" s="15">
         <v>46046</v>
       </c>
@@ -22905,7 +22920,7 @@
         <v>481708</v>
       </c>
     </row>
-    <row r="880" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="880" spans="1:5" ht="17" thickBot="1">
       <c r="A880" s="15">
         <v>46053</v>
       </c>
@@ -22938,7 +22953,7 @@
         <v>434361</v>
       </c>
     </row>
-    <row r="881" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="881" spans="1:5" ht="17" thickBot="1">
       <c r="A881" s="15">
         <v>46060</v>
       </c>
@@ -22956,7 +22971,7 @@
         <v>486854</v>
       </c>
     </row>
-    <row r="882" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="882" spans="1:5" ht="17" thickBot="1">
       <c r="A882" s="8">
         <v>46067</v>
       </c>
@@ -22989,7 +23004,7 @@
         <v>510399</v>
       </c>
     </row>
-    <row r="883" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="883" spans="1:5" ht="17" thickBot="1">
       <c r="A883" s="15">
         <v>46074</v>
       </c>
@@ -23022,7 +23037,7 @@
         <v>507712</v>
       </c>
     </row>
-    <row r="884" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="884" spans="1:5" ht="17" thickBot="1">
       <c r="A884" s="8">
         <v>46081</v>
       </c>
@@ -23040,7 +23055,7 @@
         <v>516729</v>
       </c>
     </row>
-    <row r="885" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="885" spans="1:5" ht="17" thickBot="1">
       <c r="A885" s="15">
         <v>46088</v>
       </c>
@@ -23058,7 +23073,7 @@
         <v>514996</v>
       </c>
     </row>
-    <row r="886" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="886" spans="1:5" ht="16">
       <c r="A886" s="8">
         <v>46102</v>
       </c>
@@ -23076,7 +23091,7 @@
         <v>502252</v>
       </c>
     </row>
-    <row r="887" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="887" spans="1:5" ht="16">
       <c r="A887" s="8">
         <v>46109</v>
       </c>
@@ -23094,7 +23109,7 @@
         <v>515921</v>
       </c>
     </row>
-    <row r="888" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="888" spans="1:5" ht="16">
       <c r="A888" s="8">
         <v>46116</v>
       </c>
@@ -23112,7 +23127,7 @@
         <v>501328</v>
       </c>
     </row>
-    <row r="889" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="889" spans="1:5" ht="16">
       <c r="A889" s="8">
         <v>46123</v>
       </c>
@@ -23130,7 +23145,7 @@
         <v>500040</v>
       </c>
     </row>
-    <row r="890" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="890" spans="1:5" ht="16">
       <c r="A890" s="8">
         <v>46130</v>
       </c>
@@ -23148,7 +23163,7 @@
         <v>508303</v>
       </c>
     </row>
-    <row r="891" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="891" spans="1:5" ht="16">
       <c r="A891" s="8">
         <v>46137</v>
       </c>
@@ -23166,7 +23181,7 @@
         <v>511616</v>
       </c>
     </row>
-    <row r="892" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="892" spans="1:5" ht="16">
       <c r="A892" s="8">
         <v>46144</v>
       </c>
@@ -23184,7 +23199,7 @@
         <v>518773</v>
       </c>
     </row>
-    <row r="893" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="893" spans="1:5" ht="16">
       <c r="A893" s="8">
         <v>46151</v>
       </c>
@@ -23217,7 +23232,7 @@
         <v>513755</v>
       </c>
     </row>
-    <row r="894" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="894" spans="1:5" ht="16">
       <c r="A894" s="8">
         <v>46158</v>
       </c>
@@ -23235,7 +23250,7 @@
         <v>511216</v>
       </c>
     </row>
-    <row r="895" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="895" spans="1:5" ht="16">
       <c r="A895" s="8">
         <v>46165</v>
       </c>
@@ -23253,7 +23268,7 @@
         <v>523574</v>
       </c>
     </row>
-    <row r="896" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="896" spans="1:5" ht="16">
       <c r="A896" s="8">
         <v>46172</v>
       </c>
@@ -23286,7 +23301,7 @@
         <v>492795</v>
       </c>
     </row>
-    <row r="897" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="897" spans="1:5" ht="16">
       <c r="A897" s="8">
         <v>46179</v>
       </c>
@@ -23304,7 +23319,7 @@
         <v>521804</v>
       </c>
     </row>
-    <row r="898" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="898" spans="1:5" ht="16">
       <c r="A898" s="8">
         <v>46186</v>
       </c>
@@ -23322,7 +23337,7 @@
         <v>520406</v>
       </c>
     </row>
-    <row r="899" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="899" spans="1:5" ht="16">
       <c r="A899" s="8">
         <v>46193</v>
       </c>
@@ -23365,7 +23380,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{300947AE-C9E8-48BA-99BA-AA00E1AFF02E}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="15.6" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -23376,12 +23391,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFF96248-4EFB-4252-A059-6D65AEEDC293}">
   <dimension ref="B2:C4"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="15.6" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:3">
       <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
@@ -23389,7 +23404,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:3">
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
@@ -23397,7 +23412,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:3">
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>

--- a/data/freight/US Rail Traffic.xlsx
+++ b/data/freight/US Rail Traffic.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tommy/Desktop/Pycharm/FinancialData/data/freight/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D4F01BB-B885-8349-8636-EEC74B12800D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CB49217-E88F-44A8-905E-08B6AABE2CE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22160" yWindow="600" windowWidth="29040" windowHeight="15720" xr2:uid="{55EF15CE-83DB-4E42-B75D-C3DAE3AA4C48}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{55EF15CE-83DB-4E42-B75D-C3DAE3AA4C48}"/>
   </bookViews>
   <sheets>
     <sheet name="USRT" sheetId="1" r:id="rId1"/>
@@ -91,7 +91,7 @@
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="166" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -268,9 +268,9 @@
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="쉼표" xfId="1" builtinId="3"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -288,7 +288,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -6537,9 +6537,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -6577,7 +6577,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -6683,7 +6683,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -6825,7 +6825,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -6834,17 +6834,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83FCC8DB-37A0-4531-B65E-34C65BAF4830}">
   <dimension ref="A1:E899"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.109375" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.33203125" style="21" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.83203125" style="20" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.1640625" style="6"/>
+    <col min="5" max="5" width="8.77734375" style="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -6861,7 +6861,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="16">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="7">
         <v>39823</v>
       </c>
@@ -6894,7 +6894,7 @@
         <v>474565</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="16">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="7">
         <v>39830</v>
       </c>
@@ -6905,7 +6905,7 @@
         <v>0.5</v>
       </c>
       <c r="D3" s="7" t="str">
-        <f t="shared" ref="D2:D65" si="0">IF(
+        <f t="shared" ref="D3:D65" si="0">IF(
  AND(
   A3 &gt;= IF(
          YEAR(A3)&gt;=2007,
@@ -6927,7 +6927,7 @@
         <v>465386</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="16">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="7">
         <v>39837</v>
       </c>
@@ -6945,7 +6945,7 @@
         <v>462128</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="16">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="7">
         <v>39844</v>
       </c>
@@ -6963,7 +6963,7 @@
         <v>449966</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="16">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="7">
         <v>39851</v>
       </c>
@@ -6981,7 +6981,7 @@
         <v>455757</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="16">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="7">
         <v>39858</v>
       </c>
@@ -6999,7 +6999,7 @@
         <v>471961</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="16">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="7">
         <v>39865</v>
       </c>
@@ -7017,7 +7017,7 @@
         <v>446575</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="16">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="7">
         <v>39872</v>
       </c>
@@ -7035,7 +7035,7 @@
         <v>458242</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="16">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="7">
         <v>39879</v>
       </c>
@@ -7053,7 +7053,7 @@
         <v>455041</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="16">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="7">
         <v>39886</v>
       </c>
@@ -7071,7 +7071,7 @@
         <v>455686</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="16">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="7">
         <v>39893</v>
       </c>
@@ -7089,7 +7089,7 @@
         <v>459547</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="16">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="7">
         <v>39900</v>
       </c>
@@ -7107,7 +7107,7 @@
         <v>439844</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="16">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="7">
         <v>39907</v>
       </c>
@@ -7125,7 +7125,7 @@
         <v>447103</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="16">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" s="7">
         <v>39914</v>
       </c>
@@ -7143,7 +7143,7 @@
         <v>426107</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="16">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="7">
         <v>39921</v>
       </c>
@@ -7161,7 +7161,7 @@
         <v>438602</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="16">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" s="7">
         <v>39928</v>
       </c>
@@ -7179,7 +7179,7 @@
         <v>444794</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="16">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" s="7">
         <v>39935</v>
       </c>
@@ -7197,7 +7197,7 @@
         <v>442378</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="16">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" s="7">
         <v>39942</v>
       </c>
@@ -7215,7 +7215,7 @@
         <v>435052</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="16">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" s="7">
         <v>39949</v>
       </c>
@@ -7233,7 +7233,7 @@
         <v>438329</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="16">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" s="7">
         <v>39956</v>
       </c>
@@ -7251,7 +7251,7 @@
         <v>451355</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="16">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" s="7">
         <v>39963</v>
       </c>
@@ -7269,7 +7269,7 @@
         <v>401248</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="16">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" s="7">
         <v>39970</v>
       </c>
@@ -7287,7 +7287,7 @@
         <v>448743</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="16">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" s="7">
         <v>39977</v>
       </c>
@@ -7305,7 +7305,7 @@
         <v>451065</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="16">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" s="7">
         <v>39984</v>
       </c>
@@ -7323,7 +7323,7 @@
         <v>449103</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="16">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" s="7">
         <v>39991</v>
       </c>
@@ -7341,7 +7341,7 @@
         <v>444212</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="16">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" s="7">
         <v>39998</v>
       </c>
@@ -7359,7 +7359,7 @@
         <v>410661</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="16">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" s="7">
         <v>40005</v>
       </c>
@@ -7377,7 +7377,7 @@
         <v>439041</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="16">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" s="7">
         <v>40012</v>
       </c>
@@ -7395,7 +7395,7 @@
         <v>456926</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="16">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" s="7">
         <v>40019</v>
       </c>
@@ -7413,7 +7413,7 @@
         <v>467395</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="16">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" s="7">
         <v>40026</v>
       </c>
@@ -7431,7 +7431,7 @@
         <v>468150</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="16">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" s="7">
         <v>40033</v>
       </c>
@@ -7449,7 +7449,7 @@
         <v>469814</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="16">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" s="7">
         <v>40040</v>
       </c>
@@ -7467,7 +7467,7 @@
         <v>469727</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="16">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" s="7">
         <v>40047</v>
       </c>
@@ -7485,7 +7485,7 @@
         <v>472644</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="16">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" s="7">
         <v>40054</v>
       </c>
@@ -7503,7 +7503,7 @@
         <v>488273</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="16">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" s="7">
         <v>40061</v>
       </c>
@@ -7521,7 +7521,7 @@
         <v>486009</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="16">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" s="7">
         <v>40068</v>
       </c>
@@ -7539,7 +7539,7 @@
         <v>439238</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="16">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" s="7">
         <v>40075</v>
       </c>
@@ -7557,7 +7557,7 @@
         <v>487236</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="16">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" s="7">
         <v>40082</v>
       </c>
@@ -7575,7 +7575,7 @@
         <v>477434</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="16">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" s="7">
         <v>40089</v>
       </c>
@@ -7593,7 +7593,7 @@
         <v>484157</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="16">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" s="7">
         <v>40096</v>
       </c>
@@ -7611,7 +7611,7 @@
         <v>481944</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="16">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" s="7">
         <v>40103</v>
       </c>
@@ -7629,7 +7629,7 @@
         <v>481827</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="16">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" s="7">
         <v>40110</v>
       </c>
@@ -7647,7 +7647,7 @@
         <v>483850</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="16">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" s="7">
         <v>40117</v>
       </c>
@@ -7665,7 +7665,7 @@
         <v>479450</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="16">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" s="7">
         <v>40124</v>
       </c>
@@ -7683,7 +7683,7 @@
         <v>481493</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="16">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" s="7">
         <v>40131</v>
       </c>
@@ -7701,7 +7701,7 @@
         <v>489073</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="16">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" s="7">
         <v>40138</v>
       </c>
@@ -7719,7 +7719,7 @@
         <v>500284</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="16">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" s="7">
         <v>40145</v>
       </c>
@@ -7737,7 +7737,7 @@
         <v>412036</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="16">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" s="7">
         <v>40152</v>
       </c>
@@ -7755,7 +7755,7 @@
         <v>491440</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="16">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" s="7">
         <v>40159</v>
       </c>
@@ -7773,7 +7773,7 @@
         <v>464948</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="16">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" s="7">
         <v>40166</v>
       </c>
@@ -7791,7 +7791,7 @@
         <v>481426</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="16">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52" s="7">
         <v>40173</v>
       </c>
@@ -7809,7 +7809,7 @@
         <v>339702</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="16">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53" s="7">
         <v>40180</v>
       </c>
@@ -7827,7 +7827,7 @@
         <v>376455</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="16">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" s="7">
         <v>40187</v>
       </c>
@@ -7845,7 +7845,7 @@
         <v>433584</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="16">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55" s="7">
         <v>40194</v>
       </c>
@@ -7863,7 +7863,7 @@
         <v>465758</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="16">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56" s="7">
         <v>40201</v>
       </c>
@@ -7881,7 +7881,7 @@
         <v>478227</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="16">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57" s="7">
         <v>40208</v>
       </c>
@@ -7899,7 +7899,7 @@
         <v>482390</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="16">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58" s="7">
         <v>40215</v>
       </c>
@@ -7917,7 +7917,7 @@
         <v>469221</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="16">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59" s="7">
         <v>40222</v>
       </c>
@@ -7935,7 +7935,7 @@
         <v>450177</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="16">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60" s="7">
         <v>40229</v>
       </c>
@@ -7953,7 +7953,7 @@
         <v>474203</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="16">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61" s="7">
         <v>40236</v>
       </c>
@@ -7971,7 +7971,7 @@
         <v>496078</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="16">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62" s="7">
         <v>40243</v>
       </c>
@@ -7989,7 +7989,7 @@
         <v>497456</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="16">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63" s="7">
         <v>40250</v>
       </c>
@@ -8007,7 +8007,7 @@
         <v>491463</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="16">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64" s="7">
         <v>40257</v>
       </c>
@@ -8025,7 +8025,7 @@
         <v>488939</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="16">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A65" s="7">
         <v>40264</v>
       </c>
@@ -8043,7 +8043,7 @@
         <v>504028</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="16">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66" s="7">
         <v>40271</v>
       </c>
@@ -8076,7 +8076,7 @@
         <v>486474</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="16">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67" s="7">
         <v>40278</v>
       </c>
@@ -8094,7 +8094,7 @@
         <v>492044</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="16">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68" s="7">
         <v>40285</v>
       </c>
@@ -8112,7 +8112,7 @@
         <v>506502</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="16">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A69" s="7">
         <v>40292</v>
       </c>
@@ -8130,7 +8130,7 @@
         <v>510565</v>
       </c>
     </row>
-    <row r="70" spans="1:5" ht="16">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A70" s="7">
         <v>40299</v>
       </c>
@@ -8148,7 +8148,7 @@
         <v>508731</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="16">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A71" s="7">
         <v>40306</v>
       </c>
@@ -8166,7 +8166,7 @@
         <v>497714</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="16">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A72" s="7">
         <v>40313</v>
       </c>
@@ -8184,7 +8184,7 @@
         <v>508469</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="16">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A73" s="7">
         <v>40320</v>
       </c>
@@ -8202,7 +8202,7 @@
         <v>503232</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="16">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74" s="7">
         <v>40327</v>
       </c>
@@ -8220,7 +8220,7 @@
         <v>511776</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="16">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75" s="7">
         <v>40334</v>
       </c>
@@ -8238,7 +8238,7 @@
         <v>462009</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="16">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A76" s="7">
         <v>40341</v>
       </c>
@@ -8256,7 +8256,7 @@
         <v>512048</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="16">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A77" s="7">
         <v>40348</v>
       </c>
@@ -8274,7 +8274,7 @@
         <v>512898</v>
       </c>
     </row>
-    <row r="78" spans="1:5" ht="16">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A78" s="7">
         <v>40355</v>
       </c>
@@ -8292,7 +8292,7 @@
         <v>511945</v>
       </c>
     </row>
-    <row r="79" spans="1:5" ht="16">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A79" s="7">
         <v>40362</v>
       </c>
@@ -8310,7 +8310,7 @@
         <v>518063</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="16">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A80" s="7">
         <v>40369</v>
       </c>
@@ -8328,7 +8328,7 @@
         <v>445917</v>
       </c>
     </row>
-    <row r="81" spans="1:5" ht="16">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A81" s="7">
         <v>40376</v>
       </c>
@@ -8346,7 +8346,7 @@
         <v>509860</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="16">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A82" s="7">
         <v>40383</v>
       </c>
@@ -8364,7 +8364,7 @@
         <v>517297</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="16">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A83" s="7">
         <v>40390</v>
       </c>
@@ -8382,7 +8382,7 @@
         <v>533187</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="16">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A84" s="7">
         <v>40397</v>
       </c>
@@ -8400,7 +8400,7 @@
         <v>515715</v>
       </c>
     </row>
-    <row r="85" spans="1:5" ht="16">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A85" s="7">
         <v>40404</v>
       </c>
@@ -8418,7 +8418,7 @@
         <v>529715</v>
       </c>
     </row>
-    <row r="86" spans="1:5" ht="16">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A86" s="7">
         <v>40411</v>
       </c>
@@ -8436,7 +8436,7 @@
         <v>533038</v>
       </c>
     </row>
-    <row r="87" spans="1:5" ht="16">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A87" s="7">
         <v>40418</v>
       </c>
@@ -8454,7 +8454,7 @@
         <v>539552</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="16">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A88" s="7">
         <v>40425</v>
       </c>
@@ -8472,7 +8472,7 @@
         <v>542006</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="16">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A89" s="7">
         <v>40432</v>
       </c>
@@ -8490,7 +8490,7 @@
         <v>484380</v>
       </c>
     </row>
-    <row r="90" spans="1:5" ht="16">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A90" s="7">
         <v>40439</v>
       </c>
@@ -8508,7 +8508,7 @@
         <v>544692</v>
       </c>
     </row>
-    <row r="91" spans="1:5" ht="16">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A91" s="7">
         <v>40446</v>
       </c>
@@ -8526,7 +8526,7 @@
         <v>542075</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="16">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A92" s="7">
         <v>40453</v>
       </c>
@@ -8544,7 +8544,7 @@
         <v>539646</v>
       </c>
     </row>
-    <row r="93" spans="1:5" ht="16">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A93" s="7">
         <v>40460</v>
       </c>
@@ -8562,7 +8562,7 @@
         <v>533301</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="16">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A94" s="7">
         <v>40467</v>
       </c>
@@ -8580,7 +8580,7 @@
         <v>540844</v>
       </c>
     </row>
-    <row r="95" spans="1:5" ht="16">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A95" s="7">
         <v>40474</v>
       </c>
@@ -8598,7 +8598,7 @@
         <v>538461</v>
       </c>
     </row>
-    <row r="96" spans="1:5" ht="16">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A96" s="7">
         <v>40481</v>
       </c>
@@ -8616,7 +8616,7 @@
         <v>525601</v>
       </c>
     </row>
-    <row r="97" spans="1:5" ht="16">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A97" s="7">
         <v>40488</v>
       </c>
@@ -8634,7 +8634,7 @@
         <v>519134</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="16">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A98" s="7">
         <v>40495</v>
       </c>
@@ -8652,7 +8652,7 @@
         <v>530157</v>
       </c>
     </row>
-    <row r="99" spans="1:5" ht="16">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A99" s="7">
         <v>40502</v>
       </c>
@@ -8670,7 +8670,7 @@
         <v>533989</v>
       </c>
     </row>
-    <row r="100" spans="1:5" ht="16">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A100" s="7">
         <v>40509</v>
       </c>
@@ -8688,7 +8688,7 @@
         <v>437911</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="17" thickBot="1">
+    <row r="101" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A101" s="7">
         <v>40516</v>
       </c>
@@ -8706,7 +8706,7 @@
         <v>539405</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="17" thickBot="1">
+    <row r="102" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A102" s="11">
         <v>40523</v>
       </c>
@@ -8724,7 +8724,7 @@
         <v>520326</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="17" thickBot="1">
+    <row r="103" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A103" s="11">
         <v>40530</v>
       </c>
@@ -8742,7 +8742,7 @@
         <v>491896</v>
       </c>
     </row>
-    <row r="104" spans="1:5" ht="17" thickBot="1">
+    <row r="104" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A104" s="11">
         <v>40537</v>
       </c>
@@ -8760,7 +8760,7 @@
         <v>433347</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="17" thickBot="1">
+    <row r="105" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A105" s="11">
         <v>40544</v>
       </c>
@@ -8778,7 +8778,7 @@
         <v>406967</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="17" thickBot="1">
+    <row r="106" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A106" s="11">
         <v>40551</v>
       </c>
@@ -8796,7 +8796,7 @@
         <v>498773</v>
       </c>
     </row>
-    <row r="107" spans="1:5" ht="17" thickBot="1">
+    <row r="107" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A107" s="11">
         <v>40558</v>
       </c>
@@ -8814,7 +8814,7 @@
         <v>496473</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="17" thickBot="1">
+    <row r="108" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A108" s="11">
         <v>40565</v>
       </c>
@@ -8832,7 +8832,7 @@
         <v>496043</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="17" thickBot="1">
+    <row r="109" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A109" s="11">
         <v>40572</v>
       </c>
@@ -8850,7 +8850,7 @@
         <v>513889</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="17" thickBot="1">
+    <row r="110" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A110" s="11">
         <v>40579</v>
       </c>
@@ -8868,7 +8868,7 @@
         <v>465931</v>
       </c>
     </row>
-    <row r="111" spans="1:5" ht="17" thickBot="1">
+    <row r="111" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A111" s="11">
         <v>40586</v>
       </c>
@@ -8886,7 +8886,7 @@
         <v>502078</v>
       </c>
     </row>
-    <row r="112" spans="1:5" ht="17" thickBot="1">
+    <row r="112" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A112" s="11">
         <v>40593</v>
       </c>
@@ -8904,7 +8904,7 @@
         <v>530973</v>
       </c>
     </row>
-    <row r="113" spans="1:5" ht="17" thickBot="1">
+    <row r="113" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A113" s="11">
         <v>40600</v>
       </c>
@@ -8922,7 +8922,7 @@
         <v>516841</v>
       </c>
     </row>
-    <row r="114" spans="1:5" ht="17" thickBot="1">
+    <row r="114" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A114" s="11">
         <v>40607</v>
       </c>
@@ -8940,7 +8940,7 @@
         <v>515296</v>
       </c>
     </row>
-    <row r="115" spans="1:5" ht="17" thickBot="1">
+    <row r="115" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A115" s="11">
         <v>40614</v>
       </c>
@@ -8958,7 +8958,7 @@
         <v>508992</v>
       </c>
     </row>
-    <row r="116" spans="1:5" ht="17" thickBot="1">
+    <row r="116" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A116" s="11">
         <v>40621</v>
       </c>
@@ -8976,7 +8976,7 @@
         <v>516560</v>
       </c>
     </row>
-    <row r="117" spans="1:5" ht="17" thickBot="1">
+    <row r="117" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A117" s="11">
         <v>40628</v>
       </c>
@@ -8994,7 +8994,7 @@
         <v>522937</v>
       </c>
     </row>
-    <row r="118" spans="1:5" ht="17" thickBot="1">
+    <row r="118" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A118" s="11">
         <v>40635</v>
       </c>
@@ -9012,7 +9012,7 @@
         <v>540213</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="17" thickBot="1">
+    <row r="119" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A119" s="11">
         <v>40642</v>
       </c>
@@ -9030,7 +9030,7 @@
         <v>522511</v>
       </c>
     </row>
-    <row r="120" spans="1:5" ht="17" thickBot="1">
+    <row r="120" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A120" s="11">
         <v>40649</v>
       </c>
@@ -9048,7 +9048,7 @@
         <v>525886</v>
       </c>
     </row>
-    <row r="121" spans="1:5" ht="17" thickBot="1">
+    <row r="121" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A121" s="11">
         <v>40656</v>
       </c>
@@ -9066,7 +9066,7 @@
         <v>518374</v>
       </c>
     </row>
-    <row r="122" spans="1:5" ht="17" thickBot="1">
+    <row r="122" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A122" s="11">
         <v>40663</v>
       </c>
@@ -9084,7 +9084,7 @@
         <v>525024</v>
       </c>
     </row>
-    <row r="123" spans="1:5" ht="17" thickBot="1">
+    <row r="123" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A123" s="11">
         <v>40670</v>
       </c>
@@ -9102,7 +9102,7 @@
         <v>514038</v>
       </c>
     </row>
-    <row r="124" spans="1:5" ht="17" thickBot="1">
+    <row r="124" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A124" s="11">
         <v>40677</v>
       </c>
@@ -9120,7 +9120,7 @@
         <v>526146</v>
       </c>
     </row>
-    <row r="125" spans="1:5" ht="17" thickBot="1">
+    <row r="125" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A125" s="11">
         <v>40684</v>
       </c>
@@ -9138,7 +9138,7 @@
         <v>529383</v>
       </c>
     </row>
-    <row r="126" spans="1:5" ht="17" thickBot="1">
+    <row r="126" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A126" s="13">
         <v>40691</v>
       </c>
@@ -9156,7 +9156,7 @@
         <v>522717</v>
       </c>
     </row>
-    <row r="127" spans="1:5" ht="17" thickBot="1">
+    <row r="127" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A127" s="11">
         <v>40698</v>
       </c>
@@ -9174,7 +9174,7 @@
         <v>479149</v>
       </c>
     </row>
-    <row r="128" spans="1:5" ht="17" thickBot="1">
+    <row r="128" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A128" s="11">
         <v>40705</v>
       </c>
@@ -9192,7 +9192,7 @@
         <v>527603</v>
       </c>
     </row>
-    <row r="129" spans="1:5" ht="17" thickBot="1">
+    <row r="129" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A129" s="11">
         <v>40712</v>
       </c>
@@ -9210,7 +9210,7 @@
         <v>531992</v>
       </c>
     </row>
-    <row r="130" spans="1:5" ht="17" thickBot="1">
+    <row r="130" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A130" s="11">
         <v>40719</v>
       </c>
@@ -9243,7 +9243,7 @@
         <v>519337</v>
       </c>
     </row>
-    <row r="131" spans="1:5" ht="17" thickBot="1">
+    <row r="131" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A131" s="11">
         <v>40726</v>
       </c>
@@ -9261,7 +9261,7 @@
         <v>522931</v>
       </c>
     </row>
-    <row r="132" spans="1:5" ht="17" thickBot="1">
+    <row r="132" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A132" s="11">
         <v>40733</v>
       </c>
@@ -9279,7 +9279,7 @@
         <v>438193</v>
       </c>
     </row>
-    <row r="133" spans="1:5" ht="17" thickBot="1">
+    <row r="133" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A133" s="11">
         <v>40740</v>
       </c>
@@ -9297,7 +9297,7 @@
         <v>511711</v>
       </c>
     </row>
-    <row r="134" spans="1:5" ht="17" thickBot="1">
+    <row r="134" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A134" s="11">
         <v>40747</v>
       </c>
@@ -9315,7 +9315,7 @@
         <v>524090</v>
       </c>
     </row>
-    <row r="135" spans="1:5" ht="17" thickBot="1">
+    <row r="135" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A135" s="11">
         <v>40754</v>
       </c>
@@ -9333,7 +9333,7 @@
         <v>533337</v>
       </c>
     </row>
-    <row r="136" spans="1:5" ht="17" thickBot="1">
+    <row r="136" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A136" s="11">
         <v>40761</v>
       </c>
@@ -9351,7 +9351,7 @@
         <v>522889</v>
       </c>
     </row>
-    <row r="137" spans="1:5" ht="17" thickBot="1">
+    <row r="137" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A137" s="11">
         <v>40768</v>
       </c>
@@ -9369,7 +9369,7 @@
         <v>527864</v>
       </c>
     </row>
-    <row r="138" spans="1:5" ht="17" thickBot="1">
+    <row r="138" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A138" s="11">
         <v>40775</v>
       </c>
@@ -9387,7 +9387,7 @@
         <v>539201</v>
       </c>
     </row>
-    <row r="139" spans="1:5" ht="17" thickBot="1">
+    <row r="139" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A139" s="11">
         <v>40782</v>
       </c>
@@ -9405,7 +9405,7 @@
         <v>535994</v>
       </c>
     </row>
-    <row r="140" spans="1:5" ht="17" thickBot="1">
+    <row r="140" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A140" s="11">
         <v>40789</v>
       </c>
@@ -9423,7 +9423,7 @@
         <v>537201</v>
       </c>
     </row>
-    <row r="141" spans="1:5" ht="17" thickBot="1">
+    <row r="141" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A141" s="11">
         <v>40796</v>
       </c>
@@ -9441,7 +9441,7 @@
         <v>486472</v>
       </c>
     </row>
-    <row r="142" spans="1:5" ht="17" thickBot="1">
+    <row r="142" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A142" s="11">
         <v>40803</v>
       </c>
@@ -9459,7 +9459,7 @@
         <v>542164</v>
       </c>
     </row>
-    <row r="143" spans="1:5" ht="17" thickBot="1">
+    <row r="143" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A143" s="11">
         <v>40810</v>
       </c>
@@ -9477,7 +9477,7 @@
         <v>553535</v>
       </c>
     </row>
-    <row r="144" spans="1:5" ht="17" thickBot="1">
+    <row r="144" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A144" s="11">
         <v>40817</v>
       </c>
@@ -9495,7 +9495,7 @@
         <v>563034</v>
       </c>
     </row>
-    <row r="145" spans="1:5" ht="17" thickBot="1">
+    <row r="145" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A145" s="11">
         <v>40824</v>
       </c>
@@ -9513,7 +9513,7 @@
         <v>544499</v>
       </c>
     </row>
-    <row r="146" spans="1:5" ht="17" thickBot="1">
+    <row r="146" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A146" s="11">
         <v>40831</v>
       </c>
@@ -9531,7 +9531,7 @@
         <v>547752</v>
       </c>
     </row>
-    <row r="147" spans="1:5" ht="17" thickBot="1">
+    <row r="147" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A147" s="11">
         <v>40838</v>
       </c>
@@ -9549,7 +9549,7 @@
         <v>547268</v>
       </c>
     </row>
-    <row r="148" spans="1:5" ht="17" thickBot="1">
+    <row r="148" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A148" s="11">
         <v>40845</v>
       </c>
@@ -9567,7 +9567,7 @@
         <v>551674</v>
       </c>
     </row>
-    <row r="149" spans="1:5" ht="17" thickBot="1">
+    <row r="149" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A149" s="11">
         <v>40852</v>
       </c>
@@ -9585,7 +9585,7 @@
         <v>537645</v>
       </c>
     </row>
-    <row r="150" spans="1:5" ht="17" thickBot="1">
+    <row r="150" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A150" s="11">
         <v>40859</v>
       </c>
@@ -9603,7 +9603,7 @@
         <v>544563</v>
       </c>
     </row>
-    <row r="151" spans="1:5" ht="17" thickBot="1">
+    <row r="151" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A151" s="13">
         <v>40866</v>
       </c>
@@ -9621,7 +9621,7 @@
         <v>545153</v>
       </c>
     </row>
-    <row r="152" spans="1:5" ht="17" thickBot="1">
+    <row r="152" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A152" s="11">
         <v>40873</v>
       </c>
@@ -9639,7 +9639,7 @@
         <v>456170</v>
       </c>
     </row>
-    <row r="153" spans="1:5" ht="17" thickBot="1">
+    <row r="153" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A153" s="11">
         <v>40880</v>
       </c>
@@ -9657,7 +9657,7 @@
         <v>555353</v>
       </c>
     </row>
-    <row r="154" spans="1:5" ht="17" thickBot="1">
+    <row r="154" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A154" s="11">
         <v>40887</v>
       </c>
@@ -9675,7 +9675,7 @@
         <v>538299</v>
       </c>
     </row>
-    <row r="155" spans="1:5" ht="17" thickBot="1">
+    <row r="155" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A155" s="11">
         <v>40894</v>
       </c>
@@ -9693,7 +9693,7 @@
         <v>537699</v>
       </c>
     </row>
-    <row r="156" spans="1:5" ht="17" thickBot="1">
+    <row r="156" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A156" s="11">
         <v>40901</v>
       </c>
@@ -9711,7 +9711,7 @@
         <v>505089</v>
       </c>
     </row>
-    <row r="157" spans="1:5" ht="17" thickBot="1">
+    <row r="157" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A157" s="11">
         <v>40908</v>
       </c>
@@ -9729,7 +9729,7 @@
         <v>426883</v>
       </c>
     </row>
-    <row r="158" spans="1:5" ht="17" thickBot="1">
+    <row r="158" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A158" s="11">
         <v>40915</v>
       </c>
@@ -9747,7 +9747,7 @@
         <v>468674</v>
       </c>
     </row>
-    <row r="159" spans="1:5" ht="17" thickBot="1">
+    <row r="159" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A159" s="11">
         <v>40922</v>
       </c>
@@ -9765,7 +9765,7 @@
         <v>527651</v>
       </c>
     </row>
-    <row r="160" spans="1:5" ht="17" thickBot="1">
+    <row r="160" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A160" s="11">
         <v>40929</v>
       </c>
@@ -9783,7 +9783,7 @@
         <v>507440</v>
       </c>
     </row>
-    <row r="161" spans="1:5" ht="17" thickBot="1">
+    <row r="161" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A161" s="11">
         <v>40936</v>
       </c>
@@ -9801,7 +9801,7 @@
         <v>518682</v>
       </c>
     </row>
-    <row r="162" spans="1:5" ht="17" thickBot="1">
+    <row r="162" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A162" s="11">
         <v>40943</v>
       </c>
@@ -9819,7 +9819,7 @@
         <v>517136</v>
       </c>
     </row>
-    <row r="163" spans="1:5" ht="17" thickBot="1">
+    <row r="163" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A163" s="11">
         <v>40950</v>
       </c>
@@ -9837,7 +9837,7 @@
         <v>506708</v>
       </c>
     </row>
-    <row r="164" spans="1:5" ht="17" thickBot="1">
+    <row r="164" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A164" s="11">
         <v>40957</v>
       </c>
@@ -9855,7 +9855,7 @@
         <v>502992</v>
       </c>
     </row>
-    <row r="165" spans="1:5" ht="17" thickBot="1">
+    <row r="165" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A165" s="11">
         <v>40964</v>
       </c>
@@ -9873,7 +9873,7 @@
         <v>496046</v>
       </c>
     </row>
-    <row r="166" spans="1:5" ht="17" thickBot="1">
+    <row r="166" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A166" s="11">
         <v>40971</v>
       </c>
@@ -9891,7 +9891,7 @@
         <v>510568</v>
       </c>
     </row>
-    <row r="167" spans="1:5" ht="17" thickBot="1">
+    <row r="167" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A167" s="11">
         <v>40978</v>
       </c>
@@ -9909,7 +9909,7 @@
         <v>504767</v>
       </c>
     </row>
-    <row r="168" spans="1:5" ht="17" thickBot="1">
+    <row r="168" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A168" s="11">
         <v>40985</v>
       </c>
@@ -9927,7 +9927,7 @@
         <v>505558</v>
       </c>
     </row>
-    <row r="169" spans="1:5" ht="17" thickBot="1">
+    <row r="169" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A169" s="11">
         <v>40992</v>
       </c>
@@ -9945,7 +9945,7 @@
         <v>510794</v>
       </c>
     </row>
-    <row r="170" spans="1:5" ht="17" thickBot="1">
+    <row r="170" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A170" s="11">
         <v>40999</v>
       </c>
@@ -9963,7 +9963,7 @@
         <v>529734</v>
       </c>
     </row>
-    <row r="171" spans="1:5" ht="17" thickBot="1">
+    <row r="171" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A171" s="11">
         <v>41006</v>
       </c>
@@ -9981,7 +9981,7 @@
         <v>502127</v>
       </c>
     </row>
-    <row r="172" spans="1:5" ht="17" thickBot="1">
+    <row r="172" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A172" s="11">
         <v>41013</v>
       </c>
@@ -9999,7 +9999,7 @@
         <v>510946</v>
       </c>
     </row>
-    <row r="173" spans="1:5" ht="17" thickBot="1">
+    <row r="173" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A173" s="11">
         <v>41020</v>
       </c>
@@ -10017,7 +10017,7 @@
         <v>521538</v>
       </c>
     </row>
-    <row r="174" spans="1:5" ht="17" thickBot="1">
+    <row r="174" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A174" s="11">
         <v>41027</v>
       </c>
@@ -10035,7 +10035,7 @@
         <v>525445</v>
       </c>
     </row>
-    <row r="175" spans="1:5" ht="17" thickBot="1">
+    <row r="175" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A175" s="11">
         <v>41034</v>
       </c>
@@ -10053,7 +10053,7 @@
         <v>515167</v>
       </c>
     </row>
-    <row r="176" spans="1:5" ht="17" thickBot="1">
+    <row r="176" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A176" s="13">
         <v>41041</v>
       </c>
@@ -10071,7 +10071,7 @@
         <v>518043</v>
       </c>
     </row>
-    <row r="177" spans="1:5" ht="17" thickBot="1">
+    <row r="177" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A177" s="11">
         <v>41048</v>
       </c>
@@ -10089,7 +10089,7 @@
         <v>522229</v>
       </c>
     </row>
-    <row r="178" spans="1:5" ht="17" thickBot="1">
+    <row r="178" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A178" s="11">
         <v>41055</v>
       </c>
@@ -10107,7 +10107,7 @@
         <v>536107</v>
       </c>
     </row>
-    <row r="179" spans="1:5" ht="17" thickBot="1">
+    <row r="179" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A179" s="11">
         <v>41062</v>
       </c>
@@ -10125,7 +10125,7 @@
         <v>479118</v>
       </c>
     </row>
-    <row r="180" spans="1:5" ht="17" thickBot="1">
+    <row r="180" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A180" s="11">
         <v>41069</v>
       </c>
@@ -10143,7 +10143,7 @@
         <v>531835</v>
       </c>
     </row>
-    <row r="181" spans="1:5" ht="17" thickBot="1">
+    <row r="181" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A181" s="11">
         <v>41076</v>
       </c>
@@ -10161,7 +10161,7 @@
         <v>537011</v>
       </c>
     </row>
-    <row r="182" spans="1:5" ht="17" thickBot="1">
+    <row r="182" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A182" s="11">
         <v>41083</v>
       </c>
@@ -10179,7 +10179,7 @@
         <v>534858</v>
       </c>
     </row>
-    <row r="183" spans="1:5" ht="17" thickBot="1">
+    <row r="183" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A183" s="11">
         <v>41090</v>
       </c>
@@ -10197,7 +10197,7 @@
         <v>532131</v>
       </c>
     </row>
-    <row r="184" spans="1:5" ht="17" thickBot="1">
+    <row r="184" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A184" s="11">
         <v>41097</v>
       </c>
@@ -10215,7 +10215,7 @@
         <v>446518</v>
       </c>
     </row>
-    <row r="185" spans="1:5" ht="17" thickBot="1">
+    <row r="185" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A185" s="11">
         <v>41104</v>
       </c>
@@ -10233,7 +10233,7 @@
         <v>532071</v>
       </c>
     </row>
-    <row r="186" spans="1:5" ht="17" thickBot="1">
+    <row r="186" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A186" s="11">
         <v>41111</v>
       </c>
@@ -10251,7 +10251,7 @@
         <v>532729</v>
       </c>
     </row>
-    <row r="187" spans="1:5" ht="17" thickBot="1">
+    <row r="187" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A187" s="11">
         <v>41118</v>
       </c>
@@ -10269,7 +10269,7 @@
         <v>538486</v>
       </c>
     </row>
-    <row r="188" spans="1:5" ht="17" thickBot="1">
+    <row r="188" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A188" s="11">
         <v>41125</v>
       </c>
@@ -10287,7 +10287,7 @@
         <v>531490</v>
       </c>
     </row>
-    <row r="189" spans="1:5" ht="17" thickBot="1">
+    <row r="189" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A189" s="11">
         <v>41132</v>
       </c>
@@ -10305,7 +10305,7 @@
         <v>532202</v>
       </c>
     </row>
-    <row r="190" spans="1:5" ht="17" thickBot="1">
+    <row r="190" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A190" s="11">
         <v>41139</v>
       </c>
@@ -10323,7 +10323,7 @@
         <v>541140</v>
       </c>
     </row>
-    <row r="191" spans="1:5" ht="17" thickBot="1">
+    <row r="191" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A191" s="11">
         <v>41146</v>
       </c>
@@ -10341,7 +10341,7 @@
         <v>545406</v>
       </c>
     </row>
-    <row r="192" spans="1:5" ht="17" thickBot="1">
+    <row r="192" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A192" s="11">
         <v>41153</v>
       </c>
@@ -10359,7 +10359,7 @@
         <v>541845</v>
       </c>
     </row>
-    <row r="193" spans="1:5" ht="17" thickBot="1">
+    <row r="193" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A193" s="11">
         <v>41160</v>
       </c>
@@ -10377,7 +10377,7 @@
         <v>486818</v>
       </c>
     </row>
-    <row r="194" spans="1:5" ht="17" thickBot="1">
+    <row r="194" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A194" s="11">
         <v>41167</v>
       </c>
@@ -10410,7 +10410,7 @@
         <v>543250</v>
       </c>
     </row>
-    <row r="195" spans="1:5" ht="17" thickBot="1">
+    <row r="195" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A195" s="11">
         <v>41174</v>
       </c>
@@ -10428,7 +10428,7 @@
         <v>542897</v>
       </c>
     </row>
-    <row r="196" spans="1:5" ht="17" thickBot="1">
+    <row r="196" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A196" s="11">
         <v>41181</v>
       </c>
@@ -10446,7 +10446,7 @@
         <v>552468</v>
       </c>
     </row>
-    <row r="197" spans="1:5" ht="17" thickBot="1">
+    <row r="197" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A197" s="11">
         <v>41188</v>
       </c>
@@ -10464,7 +10464,7 @@
         <v>534553</v>
       </c>
     </row>
-    <row r="198" spans="1:5" ht="17" thickBot="1">
+    <row r="198" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A198" s="11">
         <v>41195</v>
       </c>
@@ -10482,7 +10482,7 @@
         <v>535915</v>
       </c>
     </row>
-    <row r="199" spans="1:5" ht="17" thickBot="1">
+    <row r="199" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A199" s="11">
         <v>41202</v>
       </c>
@@ -10500,7 +10500,7 @@
         <v>542674</v>
       </c>
     </row>
-    <row r="200" spans="1:5" ht="17" thickBot="1">
+    <row r="200" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A200" s="11">
         <v>41209</v>
       </c>
@@ -10518,7 +10518,7 @@
         <v>540290</v>
       </c>
     </row>
-    <row r="201" spans="1:5" ht="17" thickBot="1">
+    <row r="201" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A201" s="13">
         <v>41216</v>
       </c>
@@ -10536,7 +10536,7 @@
         <v>502697</v>
       </c>
     </row>
-    <row r="202" spans="1:5" ht="17" thickBot="1">
+    <row r="202" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A202" s="11">
         <v>41223</v>
       </c>
@@ -10554,7 +10554,7 @@
         <v>532945</v>
       </c>
     </row>
-    <row r="203" spans="1:5" ht="17" thickBot="1">
+    <row r="203" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A203" s="11">
         <v>41230</v>
       </c>
@@ -10572,7 +10572,7 @@
         <v>537832</v>
       </c>
     </row>
-    <row r="204" spans="1:5" ht="17" thickBot="1">
+    <row r="204" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A204" s="11">
         <v>41237</v>
       </c>
@@ -10590,7 +10590,7 @@
         <v>447469</v>
       </c>
     </row>
-    <row r="205" spans="1:5" ht="17" thickBot="1">
+    <row r="205" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A205" s="11">
         <v>41244</v>
       </c>
@@ -10608,7 +10608,7 @@
         <v>547119</v>
       </c>
     </row>
-    <row r="206" spans="1:5" ht="17" thickBot="1">
+    <row r="206" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A206" s="11">
         <v>41251</v>
       </c>
@@ -10626,7 +10626,7 @@
         <v>532304</v>
       </c>
     </row>
-    <row r="207" spans="1:5" ht="17" thickBot="1">
+    <row r="207" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A207" s="11">
         <v>41258</v>
       </c>
@@ -10644,7 +10644,7 @@
         <v>544625</v>
       </c>
     </row>
-    <row r="208" spans="1:5" ht="17" thickBot="1">
+    <row r="208" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A208" s="11">
         <v>41265</v>
       </c>
@@ -10662,7 +10662,7 @@
         <v>530342</v>
       </c>
     </row>
-    <row r="209" spans="1:5" ht="17" thickBot="1">
+    <row r="209" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A209" s="11">
         <v>41272</v>
       </c>
@@ -10680,7 +10680,7 @@
         <v>367721</v>
       </c>
     </row>
-    <row r="210" spans="1:5" ht="17" thickBot="1">
+    <row r="210" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A210" s="11">
         <v>41279</v>
       </c>
@@ -10698,7 +10698,7 @@
         <v>419999</v>
       </c>
     </row>
-    <row r="211" spans="1:5" ht="17" thickBot="1">
+    <row r="211" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A211" s="11">
         <v>41286</v>
       </c>
@@ -10716,7 +10716,7 @@
         <v>532789</v>
       </c>
     </row>
-    <row r="212" spans="1:5" ht="17" thickBot="1">
+    <row r="212" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A212" s="11">
         <v>41293</v>
       </c>
@@ -10734,7 +10734,7 @@
         <v>526887</v>
       </c>
     </row>
-    <row r="213" spans="1:5" ht="17" thickBot="1">
+    <row r="213" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A213" s="11">
         <v>41300</v>
       </c>
@@ -10752,7 +10752,7 @@
         <v>504628</v>
       </c>
     </row>
-    <row r="214" spans="1:5" ht="17" thickBot="1">
+    <row r="214" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A214" s="11">
         <v>41307</v>
       </c>
@@ -10770,7 +10770,7 @@
         <v>523931</v>
       </c>
     </row>
-    <row r="215" spans="1:5" ht="17" thickBot="1">
+    <row r="215" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A215" s="11">
         <v>41314</v>
       </c>
@@ -10788,7 +10788,7 @@
         <v>518048</v>
       </c>
     </row>
-    <row r="216" spans="1:5" ht="17" thickBot="1">
+    <row r="216" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A216" s="11">
         <v>41321</v>
       </c>
@@ -10806,7 +10806,7 @@
         <v>529674</v>
       </c>
     </row>
-    <row r="217" spans="1:5" ht="17" thickBot="1">
+    <row r="217" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A217" s="11">
         <v>41328</v>
       </c>
@@ -10824,7 +10824,7 @@
         <v>516142</v>
       </c>
     </row>
-    <row r="218" spans="1:5" ht="17" thickBot="1">
+    <row r="218" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A218" s="11">
         <v>41335</v>
       </c>
@@ -10842,7 +10842,7 @@
         <v>533057</v>
       </c>
     </row>
-    <row r="219" spans="1:5" ht="17" thickBot="1">
+    <row r="219" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A219" s="11">
         <v>41342</v>
       </c>
@@ -10860,7 +10860,7 @@
         <v>511872</v>
       </c>
     </row>
-    <row r="220" spans="1:5" ht="17" thickBot="1">
+    <row r="220" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A220" s="11">
         <v>41349</v>
       </c>
@@ -10878,7 +10878,7 @@
         <v>509430</v>
       </c>
     </row>
-    <row r="221" spans="1:5" ht="17" thickBot="1">
+    <row r="221" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A221" s="11">
         <v>41356</v>
       </c>
@@ -10896,7 +10896,7 @@
         <v>514379</v>
       </c>
     </row>
-    <row r="222" spans="1:5" ht="17" thickBot="1">
+    <row r="222" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A222" s="11">
         <v>41363</v>
       </c>
@@ -10914,7 +10914,7 @@
         <v>514954</v>
       </c>
     </row>
-    <row r="223" spans="1:5" ht="17" thickBot="1">
+    <row r="223" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A223" s="11">
         <v>41370</v>
       </c>
@@ -10932,7 +10932,7 @@
         <v>512396</v>
       </c>
     </row>
-    <row r="224" spans="1:5" ht="17" thickBot="1">
+    <row r="224" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A224" s="11">
         <v>41377</v>
       </c>
@@ -10950,7 +10950,7 @@
         <v>517662</v>
       </c>
     </row>
-    <row r="225" spans="1:5" ht="17" thickBot="1">
+    <row r="225" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A225" s="11">
         <v>41384</v>
       </c>
@@ -10968,7 +10968,7 @@
         <v>517360</v>
       </c>
     </row>
-    <row r="226" spans="1:5" ht="17" thickBot="1">
+    <row r="226" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A226" s="13">
         <v>41391</v>
       </c>
@@ -10986,7 +10986,7 @@
         <v>523207</v>
       </c>
     </row>
-    <row r="227" spans="1:5" ht="17" thickBot="1">
+    <row r="227" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A227" s="11">
         <v>41398</v>
       </c>
@@ -11004,7 +11004,7 @@
         <v>529594</v>
       </c>
     </row>
-    <row r="228" spans="1:5" ht="17" thickBot="1">
+    <row r="228" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A228" s="11">
         <v>41405</v>
       </c>
@@ -11022,7 +11022,7 @@
         <v>529252</v>
       </c>
     </row>
-    <row r="229" spans="1:5" ht="17" thickBot="1">
+    <row r="229" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A229" s="11">
         <v>41412</v>
       </c>
@@ -11040,7 +11040,7 @@
         <v>535835</v>
       </c>
     </row>
-    <row r="230" spans="1:5" ht="17" thickBot="1">
+    <row r="230" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A230" s="11">
         <v>41419</v>
       </c>
@@ -11058,7 +11058,7 @@
         <v>529937</v>
       </c>
     </row>
-    <row r="231" spans="1:5" ht="17" thickBot="1">
+    <row r="231" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A231" s="11">
         <v>41426</v>
       </c>
@@ -11076,7 +11076,7 @@
         <v>491082</v>
       </c>
     </row>
-    <row r="232" spans="1:5" ht="17" thickBot="1">
+    <row r="232" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A232" s="11">
         <v>41433</v>
       </c>
@@ -11094,7 +11094,7 @@
         <v>530890</v>
       </c>
     </row>
-    <row r="233" spans="1:5" ht="17" thickBot="1">
+    <row r="233" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A233" s="11">
         <v>41440</v>
       </c>
@@ -11112,7 +11112,7 @@
         <v>543145</v>
       </c>
     </row>
-    <row r="234" spans="1:5" ht="17" thickBot="1">
+    <row r="234" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A234" s="11">
         <v>41447</v>
       </c>
@@ -11130,7 +11130,7 @@
         <v>541031</v>
       </c>
     </row>
-    <row r="235" spans="1:5" ht="17" thickBot="1">
+    <row r="235" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A235" s="11">
         <v>41454</v>
       </c>
@@ -11148,7 +11148,7 @@
         <v>531040</v>
       </c>
     </row>
-    <row r="236" spans="1:5" ht="17" thickBot="1">
+    <row r="236" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A236" s="11">
         <v>41461</v>
       </c>
@@ -11166,7 +11166,7 @@
         <v>453493</v>
       </c>
     </row>
-    <row r="237" spans="1:5" ht="17" thickBot="1">
+    <row r="237" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A237" s="11">
         <v>41468</v>
       </c>
@@ -11184,7 +11184,7 @@
         <v>525333</v>
       </c>
     </row>
-    <row r="238" spans="1:5" ht="17" thickBot="1">
+    <row r="238" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A238" s="11">
         <v>41475</v>
       </c>
@@ -11202,7 +11202,7 @@
         <v>531357</v>
       </c>
     </row>
-    <row r="239" spans="1:5" ht="17" thickBot="1">
+    <row r="239" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A239" s="11">
         <v>41482</v>
       </c>
@@ -11220,7 +11220,7 @@
         <v>551911</v>
       </c>
     </row>
-    <row r="240" spans="1:5" ht="17" thickBot="1">
+    <row r="240" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A240" s="11">
         <v>41489</v>
       </c>
@@ -11238,7 +11238,7 @@
         <v>542396</v>
       </c>
     </row>
-    <row r="241" spans="1:5" ht="17" thickBot="1">
+    <row r="241" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A241" s="11">
         <v>41496</v>
       </c>
@@ -11256,7 +11256,7 @@
         <v>546772</v>
       </c>
     </row>
-    <row r="242" spans="1:5" ht="17" thickBot="1">
+    <row r="242" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A242" s="11">
         <v>41503</v>
       </c>
@@ -11274,7 +11274,7 @@
         <v>552359</v>
       </c>
     </row>
-    <row r="243" spans="1:5" ht="17" thickBot="1">
+    <row r="243" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A243" s="11">
         <v>41510</v>
       </c>
@@ -11292,7 +11292,7 @@
         <v>548969</v>
       </c>
     </row>
-    <row r="244" spans="1:5" ht="17" thickBot="1">
+    <row r="244" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A244" s="11">
         <v>41517</v>
       </c>
@@ -11310,7 +11310,7 @@
         <v>561698</v>
       </c>
     </row>
-    <row r="245" spans="1:5" ht="17" thickBot="1">
+    <row r="245" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A245" s="11">
         <v>41524</v>
       </c>
@@ -11328,7 +11328,7 @@
         <v>507493</v>
       </c>
     </row>
-    <row r="246" spans="1:5" ht="17" thickBot="1">
+    <row r="246" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A246" s="11">
         <v>41531</v>
       </c>
@@ -11346,7 +11346,7 @@
         <v>562094</v>
       </c>
     </row>
-    <row r="247" spans="1:5" ht="17" thickBot="1">
+    <row r="247" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A247" s="11">
         <v>41538</v>
       </c>
@@ -11364,7 +11364,7 @@
         <v>551057</v>
       </c>
     </row>
-    <row r="248" spans="1:5" ht="17" thickBot="1">
+    <row r="248" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A248" s="11">
         <v>41545</v>
       </c>
@@ -11382,7 +11382,7 @@
         <v>566662</v>
       </c>
     </row>
-    <row r="249" spans="1:5" ht="17" thickBot="1">
+    <row r="249" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A249" s="11">
         <v>41552</v>
       </c>
@@ -11400,7 +11400,7 @@
         <v>545708</v>
       </c>
     </row>
-    <row r="250" spans="1:5" ht="17" thickBot="1">
+    <row r="250" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A250" s="11">
         <v>41559</v>
       </c>
@@ -11418,7 +11418,7 @@
         <v>546211</v>
       </c>
     </row>
-    <row r="251" spans="1:5" ht="17" thickBot="1">
+    <row r="251" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A251" s="13">
         <v>41566</v>
       </c>
@@ -11436,7 +11436,7 @@
         <v>553943</v>
       </c>
     </row>
-    <row r="252" spans="1:5" ht="17" thickBot="1">
+    <row r="252" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A252" s="11">
         <v>41573</v>
       </c>
@@ -11454,7 +11454,7 @@
         <v>558686</v>
       </c>
     </row>
-    <row r="253" spans="1:5" ht="17" thickBot="1">
+    <row r="253" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A253" s="11">
         <v>41580</v>
       </c>
@@ -11472,7 +11472,7 @@
         <v>556662</v>
       </c>
     </row>
-    <row r="254" spans="1:5" ht="17" thickBot="1">
+    <row r="254" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A254" s="11">
         <v>41587</v>
       </c>
@@ -11490,7 +11490,7 @@
         <v>562840</v>
       </c>
     </row>
-    <row r="255" spans="1:5" ht="17" thickBot="1">
+    <row r="255" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A255" s="11">
         <v>41594</v>
       </c>
@@ -11508,7 +11508,7 @@
         <v>562206</v>
       </c>
     </row>
-    <row r="256" spans="1:5" ht="17" thickBot="1">
+    <row r="256" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A256" s="11">
         <v>41601</v>
       </c>
@@ -11526,7 +11526,7 @@
         <v>564340</v>
       </c>
     </row>
-    <row r="257" spans="1:5" ht="17" thickBot="1">
+    <row r="257" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A257" s="11">
         <v>41608</v>
       </c>
@@ -11544,7 +11544,7 @@
         <v>463516</v>
       </c>
     </row>
-    <row r="258" spans="1:5" ht="17" thickBot="1">
+    <row r="258" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A258" s="11">
         <v>41615</v>
       </c>
@@ -11577,7 +11577,7 @@
         <v>541978</v>
       </c>
     </row>
-    <row r="259" spans="1:5" ht="17" thickBot="1">
+    <row r="259" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A259" s="11">
         <v>41622</v>
       </c>
@@ -11595,7 +11595,7 @@
         <v>546825</v>
       </c>
     </row>
-    <row r="260" spans="1:5" ht="17" thickBot="1">
+    <row r="260" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A260" s="11">
         <v>41629</v>
       </c>
@@ -11613,7 +11613,7 @@
         <v>544984</v>
       </c>
     </row>
-    <row r="261" spans="1:5" ht="17" thickBot="1">
+    <row r="261" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A261" s="11">
         <v>41636</v>
       </c>
@@ -11631,7 +11631,7 @@
         <v>403329</v>
       </c>
     </row>
-    <row r="262" spans="1:5" ht="17" thickBot="1">
+    <row r="262" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A262" s="11">
         <v>41643</v>
       </c>
@@ -11649,7 +11649,7 @@
         <v>433724</v>
       </c>
     </row>
-    <row r="263" spans="1:5" ht="17" thickBot="1">
+    <row r="263" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A263" s="11">
         <v>41650</v>
       </c>
@@ -11667,7 +11667,7 @@
         <v>492836</v>
       </c>
     </row>
-    <row r="264" spans="1:5" ht="17" thickBot="1">
+    <row r="264" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A264" s="11">
         <v>41657</v>
       </c>
@@ -11685,7 +11685,7 @@
         <v>557253</v>
       </c>
     </row>
-    <row r="265" spans="1:5" ht="17" thickBot="1">
+    <row r="265" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A265" s="11">
         <v>41664</v>
       </c>
@@ -11703,7 +11703,7 @@
         <v>526644</v>
       </c>
     </row>
-    <row r="266" spans="1:5" ht="17" thickBot="1">
+    <row r="266" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A266" s="11">
         <v>41671</v>
       </c>
@@ -11721,7 +11721,7 @@
         <v>518012</v>
       </c>
     </row>
-    <row r="267" spans="1:5" ht="17" thickBot="1">
+    <row r="267" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A267" s="11">
         <v>41678</v>
       </c>
@@ -11739,7 +11739,7 @@
         <v>507368</v>
       </c>
     </row>
-    <row r="268" spans="1:5" ht="17" thickBot="1">
+    <row r="268" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A268" s="11">
         <v>41685</v>
       </c>
@@ -11757,7 +11757,7 @@
         <v>507257</v>
       </c>
     </row>
-    <row r="269" spans="1:5" ht="17" thickBot="1">
+    <row r="269" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A269" s="11">
         <v>41692</v>
       </c>
@@ -11775,7 +11775,7 @@
         <v>535036</v>
       </c>
     </row>
-    <row r="270" spans="1:5" ht="17" thickBot="1">
+    <row r="270" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A270" s="11">
         <v>41699</v>
       </c>
@@ -11793,7 +11793,7 @@
         <v>545004</v>
       </c>
     </row>
-    <row r="271" spans="1:5" ht="17" thickBot="1">
+    <row r="271" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A271" s="11">
         <v>41706</v>
       </c>
@@ -11811,7 +11811,7 @@
         <v>518495</v>
       </c>
     </row>
-    <row r="272" spans="1:5" ht="17" thickBot="1">
+    <row r="272" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A272" s="11">
         <v>41713</v>
       </c>
@@ -11829,7 +11829,7 @@
         <v>545366</v>
       </c>
     </row>
-    <row r="273" spans="1:5" ht="17" thickBot="1">
+    <row r="273" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A273" s="11">
         <v>41720</v>
       </c>
@@ -11847,7 +11847,7 @@
         <v>552238</v>
       </c>
     </row>
-    <row r="274" spans="1:5" ht="17" thickBot="1">
+    <row r="274" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A274" s="11">
         <v>41727</v>
       </c>
@@ -11865,7 +11865,7 @@
         <v>566505</v>
       </c>
     </row>
-    <row r="275" spans="1:5" ht="17" thickBot="1">
+    <row r="275" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A275" s="11">
         <v>41734</v>
       </c>
@@ -11883,7 +11883,7 @@
         <v>557123</v>
       </c>
     </row>
-    <row r="276" spans="1:5" ht="17" thickBot="1">
+    <row r="276" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A276" s="13">
         <v>41741</v>
       </c>
@@ -11901,7 +11901,7 @@
         <v>559676</v>
       </c>
     </row>
-    <row r="277" spans="1:5" ht="17" thickBot="1">
+    <row r="277" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A277" s="11">
         <v>41748</v>
       </c>
@@ -11919,7 +11919,7 @@
         <v>549826</v>
       </c>
     </row>
-    <row r="278" spans="1:5" ht="17" thickBot="1">
+    <row r="278" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A278" s="11">
         <v>41755</v>
       </c>
@@ -11937,7 +11937,7 @@
         <v>566336</v>
       </c>
     </row>
-    <row r="279" spans="1:5" ht="17" thickBot="1">
+    <row r="279" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A279" s="11">
         <v>41762</v>
       </c>
@@ -11955,7 +11955,7 @@
         <v>564801</v>
       </c>
     </row>
-    <row r="280" spans="1:5" ht="17" thickBot="1">
+    <row r="280" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A280" s="11">
         <v>41769</v>
       </c>
@@ -11973,7 +11973,7 @@
         <v>564096</v>
       </c>
     </row>
-    <row r="281" spans="1:5" ht="17" thickBot="1">
+    <row r="281" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A281" s="11">
         <v>41783</v>
       </c>
@@ -11991,7 +11991,7 @@
         <v>570380</v>
       </c>
     </row>
-    <row r="282" spans="1:5" ht="17" thickBot="1">
+    <row r="282" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A282" s="11">
         <v>41790</v>
       </c>
@@ -12009,7 +12009,7 @@
         <v>531725</v>
       </c>
     </row>
-    <row r="283" spans="1:5" ht="17" thickBot="1">
+    <row r="283" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A283" s="11">
         <v>41797</v>
       </c>
@@ -12027,7 +12027,7 @@
         <v>562747</v>
       </c>
     </row>
-    <row r="284" spans="1:5" ht="17" thickBot="1">
+    <row r="284" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A284" s="11">
         <v>41804</v>
       </c>
@@ -12045,7 +12045,7 @@
         <v>565375</v>
       </c>
     </row>
-    <row r="285" spans="1:5" ht="17" thickBot="1">
+    <row r="285" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A285" s="11">
         <v>41811</v>
       </c>
@@ -12063,7 +12063,7 @@
         <v>563695</v>
       </c>
     </row>
-    <row r="286" spans="1:5" ht="17" thickBot="1">
+    <row r="286" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A286" s="11">
         <v>41818</v>
       </c>
@@ -12081,7 +12081,7 @@
         <v>563223</v>
       </c>
     </row>
-    <row r="287" spans="1:5" ht="17" thickBot="1">
+    <row r="287" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A287" s="11">
         <v>41825</v>
       </c>
@@ -12099,7 +12099,7 @@
         <v>497828</v>
       </c>
     </row>
-    <row r="288" spans="1:5" ht="17" thickBot="1">
+    <row r="288" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A288" s="11">
         <v>41832</v>
       </c>
@@ -12117,7 +12117,7 @@
         <v>546863</v>
       </c>
     </row>
-    <row r="289" spans="1:5" ht="17" thickBot="1">
+    <row r="289" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A289" s="11">
         <v>41839</v>
       </c>
@@ -12135,7 +12135,7 @@
         <v>566931</v>
       </c>
     </row>
-    <row r="290" spans="1:5" ht="17" thickBot="1">
+    <row r="290" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A290" s="11">
         <v>41846</v>
       </c>
@@ -12153,7 +12153,7 @@
         <v>571797</v>
       </c>
     </row>
-    <row r="291" spans="1:5" ht="17" thickBot="1">
+    <row r="291" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A291" s="11">
         <v>41853</v>
       </c>
@@ -12171,7 +12171,7 @@
         <v>574552</v>
       </c>
     </row>
-    <row r="292" spans="1:5" ht="17" thickBot="1">
+    <row r="292" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A292" s="11">
         <v>41860</v>
       </c>
@@ -12189,7 +12189,7 @@
         <v>567908</v>
       </c>
     </row>
-    <row r="293" spans="1:5" ht="17" thickBot="1">
+    <row r="293" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A293" s="11">
         <v>41867</v>
       </c>
@@ -12207,7 +12207,7 @@
         <v>574592</v>
       </c>
     </row>
-    <row r="294" spans="1:5" ht="17" thickBot="1">
+    <row r="294" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A294" s="11">
         <v>41874</v>
       </c>
@@ -12225,7 +12225,7 @@
         <v>566266</v>
       </c>
     </row>
-    <row r="295" spans="1:5" ht="17" thickBot="1">
+    <row r="295" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A295" s="11">
         <v>41881</v>
       </c>
@@ -12243,7 +12243,7 @@
         <v>579209</v>
       </c>
     </row>
-    <row r="296" spans="1:5" ht="17" thickBot="1">
+    <row r="296" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A296" s="11">
         <v>41888</v>
       </c>
@@ -12261,7 +12261,7 @@
         <v>525144</v>
       </c>
     </row>
-    <row r="297" spans="1:5" ht="17" thickBot="1">
+    <row r="297" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A297" s="11">
         <v>41895</v>
       </c>
@@ -12279,7 +12279,7 @@
         <v>579440</v>
       </c>
     </row>
-    <row r="298" spans="1:5" ht="17" thickBot="1">
+    <row r="298" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A298" s="11">
         <v>41902</v>
       </c>
@@ -12297,7 +12297,7 @@
         <v>581955</v>
       </c>
     </row>
-    <row r="299" spans="1:5" ht="17" thickBot="1">
+    <row r="299" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A299" s="11">
         <v>41909</v>
       </c>
@@ -12315,7 +12315,7 @@
         <v>576934</v>
       </c>
     </row>
-    <row r="300" spans="1:5" ht="17" thickBot="1">
+    <row r="300" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A300" s="11">
         <v>41916</v>
       </c>
@@ -12333,7 +12333,7 @@
         <v>576356</v>
       </c>
     </row>
-    <row r="301" spans="1:5" ht="17" thickBot="1">
+    <row r="301" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A301" s="13">
         <v>41923</v>
       </c>
@@ -12351,7 +12351,7 @@
         <v>571812</v>
       </c>
     </row>
-    <row r="302" spans="1:5" ht="17" thickBot="1">
+    <row r="302" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A302" s="11">
         <v>41930</v>
       </c>
@@ -12369,7 +12369,7 @@
         <v>569684</v>
       </c>
     </row>
-    <row r="303" spans="1:5" ht="17" thickBot="1">
+    <row r="303" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A303" s="11">
         <v>41937</v>
       </c>
@@ -12387,7 +12387,7 @@
         <v>586115</v>
       </c>
     </row>
-    <row r="304" spans="1:5" ht="17" thickBot="1">
+    <row r="304" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A304" s="11">
         <v>41944</v>
       </c>
@@ -12405,7 +12405,7 @@
         <v>585208</v>
       </c>
     </row>
-    <row r="305" spans="1:5" ht="17" thickBot="1">
+    <row r="305" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A305" s="11">
         <v>41951</v>
       </c>
@@ -12423,7 +12423,7 @@
         <v>568807</v>
       </c>
     </row>
-    <row r="306" spans="1:5" ht="17" thickBot="1">
+    <row r="306" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A306" s="11">
         <v>41958</v>
       </c>
@@ -12441,7 +12441,7 @@
         <v>570350</v>
       </c>
     </row>
-    <row r="307" spans="1:5" ht="17" thickBot="1">
+    <row r="307" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A307" s="11">
         <v>41965</v>
       </c>
@@ -12459,7 +12459,7 @@
         <v>565185</v>
       </c>
     </row>
-    <row r="308" spans="1:5" ht="17" thickBot="1">
+    <row r="308" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A308" s="11">
         <v>41972</v>
       </c>
@@ -12477,7 +12477,7 @@
         <v>492532</v>
       </c>
     </row>
-    <row r="309" spans="1:5" ht="17" thickBot="1">
+    <row r="309" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A309" s="11">
         <v>41979</v>
       </c>
@@ -12495,7 +12495,7 @@
         <v>580108</v>
       </c>
     </row>
-    <row r="310" spans="1:5" ht="17" thickBot="1">
+    <row r="310" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A310" s="11">
         <v>41986</v>
       </c>
@@ -12513,7 +12513,7 @@
         <v>592608</v>
       </c>
     </row>
-    <row r="311" spans="1:5" ht="17" thickBot="1">
+    <row r="311" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A311" s="11">
         <v>41993</v>
       </c>
@@ -12531,7 +12531,7 @@
         <v>580559</v>
       </c>
     </row>
-    <row r="312" spans="1:5" ht="17" thickBot="1">
+    <row r="312" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A312" s="11">
         <v>42000</v>
       </c>
@@ -12549,7 +12549,7 @@
         <v>433338</v>
       </c>
     </row>
-    <row r="313" spans="1:5" ht="17" thickBot="1">
+    <row r="313" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A313" s="11">
         <v>42007</v>
       </c>
@@ -12567,7 +12567,7 @@
         <v>446201</v>
       </c>
     </row>
-    <row r="314" spans="1:5" ht="17" thickBot="1">
+    <row r="314" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A314" s="11">
         <v>42014</v>
       </c>
@@ -12585,7 +12585,7 @@
         <v>517520</v>
       </c>
     </row>
-    <row r="315" spans="1:5" ht="17" thickBot="1">
+    <row r="315" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A315" s="11">
         <v>42021</v>
       </c>
@@ -12603,7 +12603,7 @@
         <v>551856</v>
       </c>
     </row>
-    <row r="316" spans="1:5" ht="17" thickBot="1">
+    <row r="316" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A316" s="11">
         <v>42028</v>
       </c>
@@ -12621,7 +12621,7 @@
         <v>548055</v>
       </c>
     </row>
-    <row r="317" spans="1:5" ht="17" thickBot="1">
+    <row r="317" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A317" s="11">
         <v>42035</v>
       </c>
@@ -12639,7 +12639,7 @@
         <v>548478</v>
       </c>
     </row>
-    <row r="318" spans="1:5" ht="17" thickBot="1">
+    <row r="318" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A318" s="11">
         <v>42042</v>
       </c>
@@ -12657,7 +12657,7 @@
         <v>511563</v>
       </c>
     </row>
-    <row r="319" spans="1:5" ht="17" thickBot="1">
+    <row r="319" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A319" s="11">
         <v>42049</v>
       </c>
@@ -12675,7 +12675,7 @@
         <v>525224</v>
       </c>
     </row>
-    <row r="320" spans="1:5" ht="17" thickBot="1">
+    <row r="320" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A320" s="11">
         <v>42056</v>
       </c>
@@ -12693,7 +12693,7 @@
         <v>473161</v>
       </c>
     </row>
-    <row r="321" spans="1:5" ht="17" thickBot="1">
+    <row r="321" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A321" s="11">
         <v>42063</v>
       </c>
@@ -12711,7 +12711,7 @@
         <v>508658</v>
       </c>
     </row>
-    <row r="322" spans="1:5" ht="17" thickBot="1">
+    <row r="322" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A322" s="11">
         <v>42070</v>
       </c>
@@ -12744,7 +12744,7 @@
         <v>522382</v>
       </c>
     </row>
-    <row r="323" spans="1:5" ht="17" thickBot="1">
+    <row r="323" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A323" s="11">
         <v>42077</v>
       </c>
@@ -12762,7 +12762,7 @@
         <v>553031</v>
       </c>
     </row>
-    <row r="324" spans="1:5" ht="17" thickBot="1">
+    <row r="324" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A324" s="11">
         <v>42084</v>
       </c>
@@ -12780,7 +12780,7 @@
         <v>562472</v>
       </c>
     </row>
-    <row r="325" spans="1:5" ht="17" thickBot="1">
+    <row r="325" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A325" s="11">
         <v>42091</v>
       </c>
@@ -12798,7 +12798,7 @@
         <v>563280</v>
       </c>
     </row>
-    <row r="326" spans="1:5" ht="17" thickBot="1">
+    <row r="326" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A326" s="13">
         <v>42098</v>
       </c>
@@ -12816,7 +12816,7 @@
         <v>549021</v>
       </c>
     </row>
-    <row r="327" spans="1:5" ht="17" thickBot="1">
+    <row r="327" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A327" s="11">
         <v>42105</v>
       </c>
@@ -12834,7 +12834,7 @@
         <v>557812</v>
       </c>
     </row>
-    <row r="328" spans="1:5" ht="17" thickBot="1">
+    <row r="328" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A328" s="11">
         <v>42112</v>
       </c>
@@ -12852,7 +12852,7 @@
         <v>556432</v>
       </c>
     </row>
-    <row r="329" spans="1:5" ht="17" thickBot="1">
+    <row r="329" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A329" s="11">
         <v>42119</v>
       </c>
@@ -12870,7 +12870,7 @@
         <v>557306</v>
       </c>
     </row>
-    <row r="330" spans="1:5" ht="17" thickBot="1">
+    <row r="330" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A330" s="11">
         <v>42126</v>
       </c>
@@ -12888,7 +12888,7 @@
         <v>565787</v>
       </c>
     </row>
-    <row r="331" spans="1:5" ht="17" thickBot="1">
+    <row r="331" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A331" s="11">
         <v>42133</v>
       </c>
@@ -12906,7 +12906,7 @@
         <v>551034</v>
       </c>
     </row>
-    <row r="332" spans="1:5" ht="17" thickBot="1">
+    <row r="332" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A332" s="11">
         <v>42140</v>
       </c>
@@ -12924,7 +12924,7 @@
         <v>549199</v>
       </c>
     </row>
-    <row r="333" spans="1:5" ht="17" thickBot="1">
+    <row r="333" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A333" s="11">
         <v>42147</v>
       </c>
@@ -12942,7 +12942,7 @@
         <v>554477</v>
       </c>
     </row>
-    <row r="334" spans="1:5" ht="17" thickBot="1">
+    <row r="334" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A334" s="11">
         <v>42154</v>
       </c>
@@ -12960,7 +12960,7 @@
         <v>505543</v>
       </c>
     </row>
-    <row r="335" spans="1:5" ht="17" thickBot="1">
+    <row r="335" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A335" s="11">
         <v>42161</v>
       </c>
@@ -12978,7 +12978,7 @@
         <v>550037</v>
       </c>
     </row>
-    <row r="336" spans="1:5" ht="17" thickBot="1">
+    <row r="336" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A336" s="11">
         <v>42168</v>
       </c>
@@ -12996,7 +12996,7 @@
         <v>554461</v>
       </c>
     </row>
-    <row r="337" spans="1:5" ht="17" thickBot="1">
+    <row r="337" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A337" s="11">
         <v>42175</v>
       </c>
@@ -13014,7 +13014,7 @@
         <v>550839</v>
       </c>
     </row>
-    <row r="338" spans="1:5" ht="17" thickBot="1">
+    <row r="338" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A338" s="11">
         <v>42182</v>
       </c>
@@ -13032,7 +13032,7 @@
         <v>547969</v>
       </c>
     </row>
-    <row r="339" spans="1:5" ht="17" thickBot="1">
+    <row r="339" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A339" s="11">
         <v>42189</v>
       </c>
@@ -13050,7 +13050,7 @@
         <v>506284</v>
       </c>
     </row>
-    <row r="340" spans="1:5" ht="17" thickBot="1">
+    <row r="340" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A340" s="11">
         <v>42196</v>
       </c>
@@ -13068,7 +13068,7 @@
         <v>534097</v>
       </c>
     </row>
-    <row r="341" spans="1:5" ht="17" thickBot="1">
+    <row r="341" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A341" s="11">
         <v>42203</v>
       </c>
@@ -13086,7 +13086,7 @@
         <v>551181</v>
       </c>
     </row>
-    <row r="342" spans="1:5" ht="17" thickBot="1">
+    <row r="342" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A342" s="11">
         <v>42210</v>
       </c>
@@ -13104,7 +13104,7 @@
         <v>557612</v>
       </c>
     </row>
-    <row r="343" spans="1:5" ht="17" thickBot="1">
+    <row r="343" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A343" s="11">
         <v>42217</v>
       </c>
@@ -13122,7 +13122,7 @@
         <v>559125</v>
       </c>
     </row>
-    <row r="344" spans="1:5" ht="17" thickBot="1">
+    <row r="344" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A344" s="11">
         <v>42224</v>
       </c>
@@ -13140,7 +13140,7 @@
         <v>562884</v>
       </c>
     </row>
-    <row r="345" spans="1:5" ht="17" thickBot="1">
+    <row r="345" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A345" s="11">
         <v>42238</v>
       </c>
@@ -13158,7 +13158,7 @@
         <v>567943</v>
       </c>
     </row>
-    <row r="346" spans="1:5" ht="17" thickBot="1">
+    <row r="346" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A346" s="11">
         <v>42245</v>
       </c>
@@ -13176,7 +13176,7 @@
         <v>575323</v>
       </c>
     </row>
-    <row r="347" spans="1:5" ht="17" thickBot="1">
+    <row r="347" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A347" s="11">
         <v>42252</v>
       </c>
@@ -13194,7 +13194,7 @@
         <v>567206</v>
       </c>
     </row>
-    <row r="348" spans="1:5" ht="17" thickBot="1">
+    <row r="348" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A348" s="11">
         <v>42259</v>
       </c>
@@ -13212,7 +13212,7 @@
         <v>510797</v>
       </c>
     </row>
-    <row r="349" spans="1:5" ht="17" thickBot="1">
+    <row r="349" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A349" s="11">
         <v>42266</v>
       </c>
@@ -13230,7 +13230,7 @@
         <v>566734</v>
       </c>
     </row>
-    <row r="350" spans="1:5" ht="17" thickBot="1">
+    <row r="350" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A350" s="11">
         <v>42273</v>
       </c>
@@ -13248,7 +13248,7 @@
         <v>566700</v>
       </c>
     </row>
-    <row r="351" spans="1:5" ht="17" thickBot="1">
+    <row r="351" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A351" s="13">
         <v>42280</v>
       </c>
@@ -13266,7 +13266,7 @@
         <v>572293</v>
       </c>
     </row>
-    <row r="352" spans="1:5" ht="17" thickBot="1">
+    <row r="352" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A352" s="11">
         <v>42287</v>
       </c>
@@ -13284,7 +13284,7 @@
         <v>556233</v>
       </c>
     </row>
-    <row r="353" spans="1:5" ht="17" thickBot="1">
+    <row r="353" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A353" s="11">
         <v>42294</v>
       </c>
@@ -13302,7 +13302,7 @@
         <v>554696</v>
       </c>
     </row>
-    <row r="354" spans="1:5" ht="17" thickBot="1">
+    <row r="354" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A354" s="11">
         <v>42301</v>
       </c>
@@ -13320,7 +13320,7 @@
         <v>553144</v>
       </c>
     </row>
-    <row r="355" spans="1:5" ht="17" thickBot="1">
+    <row r="355" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A355" s="11">
         <v>42308</v>
       </c>
@@ -13338,7 +13338,7 @@
         <v>549707</v>
       </c>
     </row>
-    <row r="356" spans="1:5" ht="17" thickBot="1">
+    <row r="356" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A356" s="11">
         <v>42315</v>
       </c>
@@ -13356,7 +13356,7 @@
         <v>539165</v>
       </c>
     </row>
-    <row r="357" spans="1:5" ht="17" thickBot="1">
+    <row r="357" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A357" s="11">
         <v>42322</v>
       </c>
@@ -13374,7 +13374,7 @@
         <v>543681</v>
       </c>
     </row>
-    <row r="358" spans="1:5" ht="17" thickBot="1">
+    <row r="358" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A358" s="11">
         <v>42336</v>
       </c>
@@ -13392,7 +13392,7 @@
         <v>450389</v>
       </c>
     </row>
-    <row r="359" spans="1:5" ht="17" thickBot="1">
+    <row r="359" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A359" s="11">
         <v>42343</v>
       </c>
@@ -13410,7 +13410,7 @@
         <v>542050</v>
       </c>
     </row>
-    <row r="360" spans="1:5" ht="17" thickBot="1">
+    <row r="360" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A360" s="11">
         <v>42350</v>
       </c>
@@ -13428,7 +13428,7 @@
         <v>544975</v>
       </c>
     </row>
-    <row r="361" spans="1:5" ht="17" thickBot="1">
+    <row r="361" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A361" s="11">
         <v>42357</v>
       </c>
@@ -13446,7 +13446,7 @@
         <v>525555</v>
       </c>
     </row>
-    <row r="362" spans="1:5" ht="17" thickBot="1">
+    <row r="362" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A362" s="11">
         <v>42364</v>
       </c>
@@ -13464,7 +13464,7 @@
         <v>391107</v>
       </c>
     </row>
-    <row r="363" spans="1:5" ht="17" thickBot="1">
+    <row r="363" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A363" s="11">
         <v>42371</v>
       </c>
@@ -13482,7 +13482,7 @@
         <v>395663</v>
       </c>
     </row>
-    <row r="364" spans="1:5" ht="17" thickBot="1">
+    <row r="364" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A364" s="11">
         <v>42378</v>
       </c>
@@ -13500,7 +13500,7 @@
         <v>498160</v>
       </c>
     </row>
-    <row r="365" spans="1:5" ht="17" thickBot="1">
+    <row r="365" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A365" s="11">
         <v>42385</v>
       </c>
@@ -13518,7 +13518,7 @@
         <v>506433</v>
       </c>
     </row>
-    <row r="366" spans="1:5" ht="17" thickBot="1">
+    <row r="366" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A366" s="11">
         <v>42392</v>
       </c>
@@ -13536,7 +13536,7 @@
         <v>490324</v>
       </c>
     </row>
-    <row r="367" spans="1:5" ht="17" thickBot="1">
+    <row r="367" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A367" s="11">
         <v>42399</v>
       </c>
@@ -13554,7 +13554,7 @@
         <v>512746</v>
       </c>
     </row>
-    <row r="368" spans="1:5" ht="17" thickBot="1">
+    <row r="368" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A368" s="11">
         <v>42406</v>
       </c>
@@ -13572,7 +13572,7 @@
         <v>504510</v>
       </c>
     </row>
-    <row r="369" spans="1:5" ht="17" thickBot="1">
+    <row r="369" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A369" s="11">
         <v>42413</v>
       </c>
@@ -13590,7 +13590,7 @@
         <v>505148</v>
       </c>
     </row>
-    <row r="370" spans="1:5" ht="17" thickBot="1">
+    <row r="370" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A370" s="11">
         <v>42420</v>
       </c>
@@ -13608,7 +13608,7 @@
         <v>497210</v>
       </c>
     </row>
-    <row r="371" spans="1:5" ht="17" thickBot="1">
+    <row r="371" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A371" s="11">
         <v>42427</v>
       </c>
@@ -13626,7 +13626,7 @@
         <v>521300</v>
       </c>
     </row>
-    <row r="372" spans="1:5" ht="17" thickBot="1">
+    <row r="372" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A372" s="11">
         <v>42434</v>
       </c>
@@ -13644,7 +13644,7 @@
         <v>512202</v>
       </c>
     </row>
-    <row r="373" spans="1:5" ht="17" thickBot="1">
+    <row r="373" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A373" s="11">
         <v>42441</v>
       </c>
@@ -13662,7 +13662,7 @@
         <v>489177</v>
       </c>
     </row>
-    <row r="374" spans="1:5" ht="17" thickBot="1">
+    <row r="374" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A374" s="11">
         <v>42448</v>
       </c>
@@ -13680,7 +13680,7 @@
         <v>483463</v>
       </c>
     </row>
-    <row r="375" spans="1:5" ht="17" thickBot="1">
+    <row r="375" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A375" s="11">
         <v>42455</v>
       </c>
@@ -13698,7 +13698,7 @@
         <v>470271</v>
       </c>
     </row>
-    <row r="376" spans="1:5" ht="17" thickBot="1">
+    <row r="376" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A376" s="13">
         <v>42462</v>
       </c>
@@ -13716,7 +13716,7 @@
         <v>491979</v>
       </c>
     </row>
-    <row r="377" spans="1:5" ht="17" thickBot="1">
+    <row r="377" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A377" s="11">
         <v>42469</v>
       </c>
@@ -13734,7 +13734,7 @@
         <v>479059</v>
       </c>
     </row>
-    <row r="378" spans="1:5" ht="17" thickBot="1">
+    <row r="378" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A378" s="11">
         <v>42476</v>
       </c>
@@ -13752,7 +13752,7 @@
         <v>499779</v>
       </c>
     </row>
-    <row r="379" spans="1:5" ht="17" thickBot="1">
+    <row r="379" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A379" s="11">
         <v>42483</v>
       </c>
@@ -13770,7 +13770,7 @@
         <v>491946</v>
       </c>
     </row>
-    <row r="380" spans="1:5" ht="17" thickBot="1">
+    <row r="380" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A380" s="11">
         <v>42490</v>
       </c>
@@ -13788,7 +13788,7 @@
         <v>502045</v>
       </c>
     </row>
-    <row r="381" spans="1:5" ht="17" thickBot="1">
+    <row r="381" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A381" s="11">
         <v>42497</v>
       </c>
@@ -13806,7 +13806,7 @@
         <v>492923</v>
       </c>
     </row>
-    <row r="382" spans="1:5" ht="17" thickBot="1">
+    <row r="382" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A382" s="11">
         <v>42504</v>
       </c>
@@ -13824,7 +13824,7 @@
         <v>498379</v>
       </c>
     </row>
-    <row r="383" spans="1:5" ht="17" thickBot="1">
+    <row r="383" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A383" s="11">
         <v>42511</v>
       </c>
@@ -13842,7 +13842,7 @@
         <v>506983</v>
       </c>
     </row>
-    <row r="384" spans="1:5" ht="17" thickBot="1">
+    <row r="384" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A384" s="11">
         <v>42518</v>
       </c>
@@ -13860,7 +13860,7 @@
         <v>513917</v>
       </c>
     </row>
-    <row r="385" spans="1:5" ht="17" thickBot="1">
+    <row r="385" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A385" s="11">
         <v>42525</v>
       </c>
@@ -13878,7 +13878,7 @@
         <v>455346</v>
       </c>
     </row>
-    <row r="386" spans="1:5" ht="17" thickBot="1">
+    <row r="386" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A386" s="11">
         <v>42532</v>
       </c>
@@ -13911,7 +13911,7 @@
         <v>513471</v>
       </c>
     </row>
-    <row r="387" spans="1:5" ht="17" thickBot="1">
+    <row r="387" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A387" s="11">
         <v>42539</v>
       </c>
@@ -13929,7 +13929,7 @@
         <v>516096</v>
       </c>
     </row>
-    <row r="388" spans="1:5" ht="17" thickBot="1">
+    <row r="388" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A388" s="11">
         <v>42546</v>
       </c>
@@ -13947,7 +13947,7 @@
         <v>526161</v>
       </c>
     </row>
-    <row r="389" spans="1:5" ht="17" thickBot="1">
+    <row r="389" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A389" s="11">
         <v>42553</v>
       </c>
@@ -13965,7 +13965,7 @@
         <v>529191</v>
       </c>
     </row>
-    <row r="390" spans="1:5" ht="17" thickBot="1">
+    <row r="390" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A390" s="11">
         <v>42560</v>
       </c>
@@ -13983,7 +13983,7 @@
         <v>442113</v>
       </c>
     </row>
-    <row r="391" spans="1:5" ht="17" thickBot="1">
+    <row r="391" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A391" s="11">
         <v>42567</v>
       </c>
@@ -14001,7 +14001,7 @@
         <v>520222</v>
       </c>
     </row>
-    <row r="392" spans="1:5" ht="17" thickBot="1">
+    <row r="392" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A392" s="11">
         <v>42574</v>
       </c>
@@ -14019,7 +14019,7 @@
         <v>528070</v>
       </c>
     </row>
-    <row r="393" spans="1:5" ht="17" thickBot="1">
+    <row r="393" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A393" s="11">
         <v>42581</v>
       </c>
@@ -14037,7 +14037,7 @@
         <v>536916</v>
       </c>
     </row>
-    <row r="394" spans="1:5" ht="17" thickBot="1">
+    <row r="394" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A394" s="11">
         <v>42588</v>
       </c>
@@ -14055,7 +14055,7 @@
         <v>531595</v>
       </c>
     </row>
-    <row r="395" spans="1:5" ht="17" thickBot="1">
+    <row r="395" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A395" s="11">
         <v>42595</v>
       </c>
@@ -14073,7 +14073,7 @@
         <v>534533</v>
       </c>
     </row>
-    <row r="396" spans="1:5" ht="17" thickBot="1">
+    <row r="396" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A396" s="11">
         <v>42602</v>
       </c>
@@ -14091,7 +14091,7 @@
         <v>531484</v>
       </c>
     </row>
-    <row r="397" spans="1:5" ht="17" thickBot="1">
+    <row r="397" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A397" s="11">
         <v>42609</v>
       </c>
@@ -14109,7 +14109,7 @@
         <v>539657</v>
       </c>
     </row>
-    <row r="398" spans="1:5" ht="17" thickBot="1">
+    <row r="398" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A398" s="11">
         <v>42616</v>
       </c>
@@ -14127,7 +14127,7 @@
         <v>538826</v>
       </c>
     </row>
-    <row r="399" spans="1:5" ht="17" thickBot="1">
+    <row r="399" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A399" s="11">
         <v>42623</v>
       </c>
@@ -14145,7 +14145,7 @@
         <v>482894</v>
       </c>
     </row>
-    <row r="400" spans="1:5" ht="17" thickBot="1">
+    <row r="400" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A400" s="11">
         <v>42630</v>
       </c>
@@ -14163,7 +14163,7 @@
         <v>537904</v>
       </c>
     </row>
-    <row r="401" spans="1:5" ht="17" thickBot="1">
+    <row r="401" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A401" s="13">
         <v>42637</v>
       </c>
@@ -14181,7 +14181,7 @@
         <v>539609</v>
       </c>
     </row>
-    <row r="402" spans="1:5" ht="17" thickBot="1">
+    <row r="402" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A402" s="11">
         <v>42644</v>
       </c>
@@ -14199,7 +14199,7 @@
         <v>549171</v>
       </c>
     </row>
-    <row r="403" spans="1:5" ht="17" thickBot="1">
+    <row r="403" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A403" s="11">
         <v>42651</v>
       </c>
@@ -14217,7 +14217,7 @@
         <v>521789</v>
       </c>
     </row>
-    <row r="404" spans="1:5" ht="17" thickBot="1">
+    <row r="404" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A404" s="11">
         <v>42658</v>
       </c>
@@ -14235,7 +14235,7 @@
         <v>531936</v>
       </c>
     </row>
-    <row r="405" spans="1:5" ht="17" thickBot="1">
+    <row r="405" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A405" s="11">
         <v>42665</v>
       </c>
@@ -14253,7 +14253,7 @@
         <v>544092</v>
       </c>
     </row>
-    <row r="406" spans="1:5" ht="17" thickBot="1">
+    <row r="406" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A406" s="11">
         <v>42672</v>
       </c>
@@ -14271,7 +14271,7 @@
         <v>544997</v>
       </c>
     </row>
-    <row r="407" spans="1:5" ht="17" thickBot="1">
+    <row r="407" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A407" s="11">
         <v>42679</v>
       </c>
@@ -14289,7 +14289,7 @@
         <v>543377</v>
       </c>
     </row>
-    <row r="408" spans="1:5" ht="17" thickBot="1">
+    <row r="408" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A408" s="11">
         <v>42686</v>
       </c>
@@ -14307,7 +14307,7 @@
         <v>541127</v>
       </c>
     </row>
-    <row r="409" spans="1:5" ht="17" thickBot="1">
+    <row r="409" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A409" s="11">
         <v>42693</v>
       </c>
@@ -14325,7 +14325,7 @@
         <v>547804</v>
       </c>
     </row>
-    <row r="410" spans="1:5" ht="17" thickBot="1">
+    <row r="410" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A410" s="11">
         <v>42700</v>
       </c>
@@ -14343,7 +14343,7 @@
         <v>452759</v>
       </c>
     </row>
-    <row r="411" spans="1:5" ht="17" thickBot="1">
+    <row r="411" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A411" s="11">
         <v>42707</v>
       </c>
@@ -14361,7 +14361,7 @@
         <v>553130</v>
       </c>
     </row>
-    <row r="412" spans="1:5" ht="17" thickBot="1">
+    <row r="412" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A412" s="11">
         <v>42714</v>
       </c>
@@ -14379,7 +14379,7 @@
         <v>538932</v>
       </c>
     </row>
-    <row r="413" spans="1:5" ht="17" thickBot="1">
+    <row r="413" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A413" s="11">
         <v>42721</v>
       </c>
@@ -14397,7 +14397,7 @@
         <v>523949</v>
       </c>
     </row>
-    <row r="414" spans="1:5" ht="17" thickBot="1">
+    <row r="414" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A414" s="11">
         <v>42728</v>
       </c>
@@ -14415,7 +14415,7 @@
         <v>496633</v>
       </c>
     </row>
-    <row r="415" spans="1:5" ht="17" thickBot="1">
+    <row r="415" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A415" s="11">
         <v>42735</v>
       </c>
@@ -14433,7 +14433,7 @@
         <v>425998</v>
       </c>
     </row>
-    <row r="416" spans="1:5" ht="17" thickBot="1">
+    <row r="416" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A416" s="11">
         <v>42742</v>
       </c>
@@ -14451,7 +14451,7 @@
         <v>441417</v>
       </c>
     </row>
-    <row r="417" spans="1:5" ht="17" thickBot="1">
+    <row r="417" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A417" s="11">
         <v>42749</v>
       </c>
@@ -14469,7 +14469,7 @@
         <v>516229</v>
       </c>
     </row>
-    <row r="418" spans="1:5" ht="17" thickBot="1">
+    <row r="418" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A418" s="11">
         <v>42756</v>
       </c>
@@ -14487,7 +14487,7 @@
         <v>530299</v>
       </c>
     </row>
-    <row r="419" spans="1:5" ht="17" thickBot="1">
+    <row r="419" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A419" s="11">
         <v>42763</v>
       </c>
@@ -14505,7 +14505,7 @@
         <v>529696</v>
       </c>
     </row>
-    <row r="420" spans="1:5" ht="17" thickBot="1">
+    <row r="420" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A420" s="11">
         <v>42770</v>
       </c>
@@ -14523,7 +14523,7 @@
         <v>541474</v>
       </c>
     </row>
-    <row r="421" spans="1:5" ht="17" thickBot="1">
+    <row r="421" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A421" s="11">
         <v>42777</v>
       </c>
@@ -14541,7 +14541,7 @@
         <v>518431</v>
       </c>
     </row>
-    <row r="422" spans="1:5" ht="17" thickBot="1">
+    <row r="422" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A422" s="11">
         <v>42784</v>
       </c>
@@ -14559,7 +14559,7 @@
         <v>531123</v>
       </c>
     </row>
-    <row r="423" spans="1:5" ht="17" thickBot="1">
+    <row r="423" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A423" s="11">
         <v>42791</v>
       </c>
@@ -14577,7 +14577,7 @@
         <v>521451</v>
       </c>
     </row>
-    <row r="424" spans="1:5" ht="17" thickBot="1">
+    <row r="424" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A424" s="11">
         <v>42798</v>
       </c>
@@ -14595,7 +14595,7 @@
         <v>521607</v>
       </c>
     </row>
-    <row r="425" spans="1:5" ht="17" thickBot="1">
+    <row r="425" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A425" s="11">
         <v>42805</v>
       </c>
@@ -14613,7 +14613,7 @@
         <v>510638</v>
       </c>
     </row>
-    <row r="426" spans="1:5" ht="17" thickBot="1">
+    <row r="426" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A426" s="13">
         <v>42812</v>
       </c>
@@ -14631,7 +14631,7 @@
         <v>495281</v>
       </c>
     </row>
-    <row r="427" spans="1:5" ht="17" thickBot="1">
+    <row r="427" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A427" s="11">
         <v>42819</v>
       </c>
@@ -14649,7 +14649,7 @@
         <v>526471</v>
       </c>
     </row>
-    <row r="428" spans="1:5" ht="17" thickBot="1">
+    <row r="428" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A428" s="11">
         <v>42826</v>
       </c>
@@ -14667,7 +14667,7 @@
         <v>527665</v>
       </c>
     </row>
-    <row r="429" spans="1:5" ht="17" thickBot="1">
+    <row r="429" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A429" s="11">
         <v>42833</v>
       </c>
@@ -14685,7 +14685,7 @@
         <v>513022</v>
       </c>
     </row>
-    <row r="430" spans="1:5" ht="17" thickBot="1">
+    <row r="430" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A430" s="11">
         <v>42840</v>
       </c>
@@ -14703,7 +14703,7 @@
         <v>519318</v>
       </c>
     </row>
-    <row r="431" spans="1:5" ht="17" thickBot="1">
+    <row r="431" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A431" s="11">
         <v>42847</v>
       </c>
@@ -14721,7 +14721,7 @@
         <v>515131</v>
       </c>
     </row>
-    <row r="432" spans="1:5" ht="17" thickBot="1">
+    <row r="432" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A432" s="11">
         <v>42854</v>
       </c>
@@ -14739,7 +14739,7 @@
         <v>527830</v>
       </c>
     </row>
-    <row r="433" spans="1:5" ht="17" thickBot="1">
+    <row r="433" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A433" s="11">
         <v>42861</v>
       </c>
@@ -14757,7 +14757,7 @@
         <v>515305</v>
       </c>
     </row>
-    <row r="434" spans="1:5" ht="17" thickBot="1">
+    <row r="434" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A434" s="11">
         <v>42868</v>
       </c>
@@ -14775,7 +14775,7 @@
         <v>526970</v>
       </c>
     </row>
-    <row r="435" spans="1:5" ht="17" thickBot="1">
+    <row r="435" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A435" s="11">
         <v>42875</v>
       </c>
@@ -14793,7 +14793,7 @@
         <v>534922</v>
       </c>
     </row>
-    <row r="436" spans="1:5" ht="17" thickBot="1">
+    <row r="436" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A436" s="11">
         <v>42882</v>
       </c>
@@ -14811,7 +14811,7 @@
         <v>548103</v>
       </c>
     </row>
-    <row r="437" spans="1:5" ht="17" thickBot="1">
+    <row r="437" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A437" s="11">
         <v>42889</v>
       </c>
@@ -14829,7 +14829,7 @@
         <v>500192</v>
       </c>
     </row>
-    <row r="438" spans="1:5" ht="17" thickBot="1">
+    <row r="438" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A438" s="11">
         <v>42896</v>
       </c>
@@ -14847,7 +14847,7 @@
         <v>545317</v>
       </c>
     </row>
-    <row r="439" spans="1:5" ht="17" thickBot="1">
+    <row r="439" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A439" s="11">
         <v>42903</v>
       </c>
@@ -14865,7 +14865,7 @@
         <v>543179</v>
       </c>
     </row>
-    <row r="440" spans="1:5" ht="17" thickBot="1">
+    <row r="440" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A440" s="11">
         <v>42910</v>
       </c>
@@ -14883,7 +14883,7 @@
         <v>544694</v>
       </c>
     </row>
-    <row r="441" spans="1:5" ht="17" thickBot="1">
+    <row r="441" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A441" s="11">
         <v>42917</v>
       </c>
@@ -14901,7 +14901,7 @@
         <v>546361</v>
       </c>
     </row>
-    <row r="442" spans="1:5" ht="17" thickBot="1">
+    <row r="442" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A442" s="11">
         <v>42924</v>
       </c>
@@ -14919,7 +14919,7 @@
         <v>453080</v>
       </c>
     </row>
-    <row r="443" spans="1:5" ht="17" thickBot="1">
+    <row r="443" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A443" s="11">
         <v>42931</v>
       </c>
@@ -14937,7 +14937,7 @@
         <v>540005</v>
       </c>
     </row>
-    <row r="444" spans="1:5" ht="17" thickBot="1">
+    <row r="444" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A444" s="11">
         <v>42938</v>
       </c>
@@ -14955,7 +14955,7 @@
         <v>534152</v>
       </c>
     </row>
-    <row r="445" spans="1:5" ht="17" thickBot="1">
+    <row r="445" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A445" s="11">
         <v>42945</v>
       </c>
@@ -14973,7 +14973,7 @@
         <v>550356</v>
       </c>
     </row>
-    <row r="446" spans="1:5" ht="17" thickBot="1">
+    <row r="446" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A446" s="11">
         <v>42952</v>
       </c>
@@ -14991,7 +14991,7 @@
         <v>554822</v>
       </c>
     </row>
-    <row r="447" spans="1:5" ht="17" thickBot="1">
+    <row r="447" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A447" s="11">
         <v>42959</v>
       </c>
@@ -15009,7 +15009,7 @@
         <v>548790</v>
       </c>
     </row>
-    <row r="448" spans="1:5" ht="17" thickBot="1">
+    <row r="448" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A448" s="11">
         <v>42966</v>
       </c>
@@ -15027,7 +15027,7 @@
         <v>554021</v>
       </c>
     </row>
-    <row r="449" spans="1:5" ht="17" thickBot="1">
+    <row r="449" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A449" s="11">
         <v>42973</v>
       </c>
@@ -15045,7 +15045,7 @@
         <v>551776</v>
       </c>
     </row>
-    <row r="450" spans="1:5" ht="17" thickBot="1">
+    <row r="450" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A450" s="11">
         <v>42980</v>
       </c>
@@ -15078,7 +15078,7 @@
         <v>534140</v>
       </c>
     </row>
-    <row r="451" spans="1:5" ht="17" thickBot="1">
+    <row r="451" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A451" s="13">
         <v>42987</v>
       </c>
@@ -15096,7 +15096,7 @@
         <v>486474</v>
       </c>
     </row>
-    <row r="452" spans="1:5" ht="17" thickBot="1">
+    <row r="452" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A452" s="11">
         <v>42994</v>
       </c>
@@ -15114,7 +15114,7 @@
         <v>530774</v>
       </c>
     </row>
-    <row r="453" spans="1:5" ht="17" thickBot="1">
+    <row r="453" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A453" s="11">
         <v>43001</v>
       </c>
@@ -15132,7 +15132,7 @@
         <v>548204</v>
       </c>
     </row>
-    <row r="454" spans="1:5" ht="17" thickBot="1">
+    <row r="454" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A454" s="11">
         <v>43008</v>
       </c>
@@ -15150,7 +15150,7 @@
         <v>559555</v>
       </c>
     </row>
-    <row r="455" spans="1:5" ht="17" thickBot="1">
+    <row r="455" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A455" s="11">
         <v>43015</v>
       </c>
@@ -15168,7 +15168,7 @@
         <v>554826</v>
       </c>
     </row>
-    <row r="456" spans="1:5" ht="17" thickBot="1">
+    <row r="456" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A456" s="11">
         <v>43022</v>
       </c>
@@ -15186,7 +15186,7 @@
         <v>548264</v>
       </c>
     </row>
-    <row r="457" spans="1:5" ht="17" thickBot="1">
+    <row r="457" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A457" s="11">
         <v>43029</v>
       </c>
@@ -15204,7 +15204,7 @@
         <v>559989</v>
       </c>
     </row>
-    <row r="458" spans="1:5" ht="17" thickBot="1">
+    <row r="458" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A458" s="11">
         <v>43036</v>
       </c>
@@ -15222,7 +15222,7 @@
         <v>546582</v>
       </c>
     </row>
-    <row r="459" spans="1:5" ht="17" thickBot="1">
+    <row r="459" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A459" s="11">
         <v>43043</v>
       </c>
@@ -15240,7 +15240,7 @@
         <v>538739</v>
       </c>
     </row>
-    <row r="460" spans="1:5" ht="17" thickBot="1">
+    <row r="460" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A460" s="11">
         <v>43050</v>
       </c>
@@ -15258,7 +15258,7 @@
         <v>547480</v>
       </c>
     </row>
-    <row r="461" spans="1:5" ht="17" thickBot="1">
+    <row r="461" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A461" s="11">
         <v>43057</v>
       </c>
@@ -15276,7 +15276,7 @@
         <v>554066</v>
       </c>
     </row>
-    <row r="462" spans="1:5" ht="17" thickBot="1">
+    <row r="462" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A462" s="11">
         <v>43064</v>
       </c>
@@ -15294,7 +15294,7 @@
         <v>463602</v>
       </c>
     </row>
-    <row r="463" spans="1:5" ht="17" thickBot="1">
+    <row r="463" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A463" s="11">
         <v>43071</v>
       </c>
@@ -15312,7 +15312,7 @@
         <v>572794</v>
       </c>
     </row>
-    <row r="464" spans="1:5" ht="17" thickBot="1">
+    <row r="464" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A464" s="11">
         <v>43078</v>
       </c>
@@ -15330,7 +15330,7 @@
         <v>560756</v>
       </c>
     </row>
-    <row r="465" spans="1:5" ht="17" thickBot="1">
+    <row r="465" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A465" s="11">
         <v>43085</v>
       </c>
@@ -15348,7 +15348,7 @@
         <v>554779</v>
       </c>
     </row>
-    <row r="466" spans="1:5" ht="17" thickBot="1">
+    <row r="466" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A466" s="11">
         <v>43092</v>
       </c>
@@ -15366,7 +15366,7 @@
         <v>551566</v>
       </c>
     </row>
-    <row r="467" spans="1:5" ht="17" thickBot="1">
+    <row r="467" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A467" s="11">
         <v>43099</v>
       </c>
@@ -15384,7 +15384,7 @@
         <v>397032</v>
       </c>
     </row>
-    <row r="468" spans="1:5" ht="17" thickBot="1">
+    <row r="468" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A468" s="11">
         <v>43113</v>
       </c>
@@ -15402,7 +15402,7 @@
         <v>511937</v>
       </c>
     </row>
-    <row r="469" spans="1:5" ht="17" thickBot="1">
+    <row r="469" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A469" s="11">
         <v>43120</v>
       </c>
@@ -15420,7 +15420,7 @@
         <v>508239</v>
       </c>
     </row>
-    <row r="470" spans="1:5" ht="17" thickBot="1">
+    <row r="470" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A470" s="11">
         <v>43127</v>
       </c>
@@ -15438,7 +15438,7 @@
         <v>543515</v>
       </c>
     </row>
-    <row r="471" spans="1:5" ht="17" thickBot="1">
+    <row r="471" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A471" s="11">
         <v>43134</v>
       </c>
@@ -15456,7 +15456,7 @@
         <v>547993</v>
       </c>
     </row>
-    <row r="472" spans="1:5" ht="17" thickBot="1">
+    <row r="472" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A472" s="11">
         <v>43141</v>
       </c>
@@ -15474,7 +15474,7 @@
         <v>519545</v>
       </c>
     </row>
-    <row r="473" spans="1:5" ht="17" thickBot="1">
+    <row r="473" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A473" s="11">
         <v>43148</v>
       </c>
@@ -15492,7 +15492,7 @@
         <v>539963</v>
       </c>
     </row>
-    <row r="474" spans="1:5" ht="17" thickBot="1">
+    <row r="474" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A474" s="11">
         <v>43155</v>
       </c>
@@ -15510,7 +15510,7 @@
         <v>528440</v>
       </c>
     </row>
-    <row r="475" spans="1:5" ht="17" thickBot="1">
+    <row r="475" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A475" s="11">
         <v>43162</v>
       </c>
@@ -15528,7 +15528,7 @@
         <v>544194</v>
       </c>
     </row>
-    <row r="476" spans="1:5" ht="17" thickBot="1">
+    <row r="476" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A476" s="13">
         <v>43169</v>
       </c>
@@ -15546,7 +15546,7 @@
         <v>534282</v>
       </c>
     </row>
-    <row r="477" spans="1:5" ht="17" thickBot="1">
+    <row r="477" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A477" s="11">
         <v>43176</v>
       </c>
@@ -15564,7 +15564,7 @@
         <v>537338</v>
       </c>
     </row>
-    <row r="478" spans="1:5" ht="17" thickBot="1">
+    <row r="478" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A478" s="11">
         <v>43183</v>
       </c>
@@ -15582,7 +15582,7 @@
         <v>526521</v>
       </c>
     </row>
-    <row r="479" spans="1:5" ht="17" thickBot="1">
+    <row r="479" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A479" s="11">
         <v>43190</v>
       </c>
@@ -15600,7 +15600,7 @@
         <v>534751</v>
       </c>
     </row>
-    <row r="480" spans="1:5" ht="17" thickBot="1">
+    <row r="480" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A480" s="11">
         <v>43197</v>
       </c>
@@ -15618,7 +15618,7 @@
         <v>524905</v>
       </c>
     </row>
-    <row r="481" spans="1:5" ht="17" thickBot="1">
+    <row r="481" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A481" s="11">
         <v>43204</v>
       </c>
@@ -15636,7 +15636,7 @@
         <v>534198</v>
       </c>
     </row>
-    <row r="482" spans="1:5" ht="17" thickBot="1">
+    <row r="482" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A482" s="11">
         <v>43211</v>
       </c>
@@ -15654,7 +15654,7 @@
         <v>539425</v>
       </c>
     </row>
-    <row r="483" spans="1:5" ht="17" thickBot="1">
+    <row r="483" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A483" s="11">
         <v>43218</v>
       </c>
@@ -15672,7 +15672,7 @@
         <v>551498</v>
       </c>
     </row>
-    <row r="484" spans="1:5" ht="17" thickBot="1">
+    <row r="484" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A484" s="11">
         <v>43225</v>
       </c>
@@ -15690,7 +15690,7 @@
         <v>545937</v>
       </c>
     </row>
-    <row r="485" spans="1:5" ht="17" thickBot="1">
+    <row r="485" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A485" s="11">
         <v>43232</v>
       </c>
@@ -15708,7 +15708,7 @@
         <v>550029</v>
       </c>
     </row>
-    <row r="486" spans="1:5" ht="17" thickBot="1">
+    <row r="486" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A486" s="11">
         <v>43239</v>
       </c>
@@ -15726,7 +15726,7 @@
         <v>546415</v>
       </c>
     </row>
-    <row r="487" spans="1:5" ht="17" thickBot="1">
+    <row r="487" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A487" s="11">
         <v>43246</v>
       </c>
@@ -15744,7 +15744,7 @@
         <v>565502</v>
       </c>
     </row>
-    <row r="488" spans="1:5" ht="17" thickBot="1">
+    <row r="488" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A488" s="11">
         <v>43253</v>
       </c>
@@ -15762,7 +15762,7 @@
         <v>509740</v>
       </c>
     </row>
-    <row r="489" spans="1:5" ht="17" thickBot="1">
+    <row r="489" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A489" s="11">
         <v>43260</v>
       </c>
@@ -15780,7 +15780,7 @@
         <v>561061</v>
       </c>
     </row>
-    <row r="490" spans="1:5" ht="17" thickBot="1">
+    <row r="490" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A490" s="11">
         <v>43267</v>
       </c>
@@ -15798,7 +15798,7 @@
         <v>558098</v>
       </c>
     </row>
-    <row r="491" spans="1:5" ht="17" thickBot="1">
+    <row r="491" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A491" s="11">
         <v>43274</v>
       </c>
@@ -15816,7 +15816,7 @@
         <v>557340</v>
       </c>
     </row>
-    <row r="492" spans="1:5" ht="17" thickBot="1">
+    <row r="492" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A492" s="11">
         <v>43281</v>
       </c>
@@ -15834,7 +15834,7 @@
         <v>564243</v>
       </c>
     </row>
-    <row r="493" spans="1:5" ht="17" thickBot="1">
+    <row r="493" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A493" s="11">
         <v>43288</v>
       </c>
@@ -15852,7 +15852,7 @@
         <v>485193</v>
       </c>
     </row>
-    <row r="494" spans="1:5" ht="17" thickBot="1">
+    <row r="494" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A494" s="11">
         <v>43295</v>
       </c>
@@ -15870,7 +15870,7 @@
         <v>559064</v>
       </c>
     </row>
-    <row r="495" spans="1:5" ht="17" thickBot="1">
+    <row r="495" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A495" s="11">
         <v>43302</v>
       </c>
@@ -15888,7 +15888,7 @@
         <v>553024</v>
       </c>
     </row>
-    <row r="496" spans="1:5" ht="17" thickBot="1">
+    <row r="496" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A496" s="11">
         <v>43309</v>
       </c>
@@ -15906,7 +15906,7 @@
         <v>559154</v>
       </c>
     </row>
-    <row r="497" spans="1:5" ht="17" thickBot="1">
+    <row r="497" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A497" s="11">
         <v>43316</v>
       </c>
@@ -15924,7 +15924,7 @@
         <v>570995</v>
       </c>
     </row>
-    <row r="498" spans="1:5" ht="17" thickBot="1">
+    <row r="498" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A498" s="11">
         <v>43323</v>
       </c>
@@ -15942,7 +15942,7 @@
         <v>556887</v>
       </c>
     </row>
-    <row r="499" spans="1:5" ht="17" thickBot="1">
+    <row r="499" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A499" s="11">
         <v>43330</v>
       </c>
@@ -15960,7 +15960,7 @@
         <v>567477</v>
       </c>
     </row>
-    <row r="500" spans="1:5" ht="17" thickBot="1">
+    <row r="500" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A500" s="11">
         <v>43337</v>
       </c>
@@ -15978,7 +15978,7 @@
         <v>565706</v>
       </c>
     </row>
-    <row r="501" spans="1:5" ht="17" thickBot="1">
+    <row r="501" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A501" s="13">
         <v>43344</v>
       </c>
@@ -15996,7 +15996,7 @@
         <v>567881</v>
       </c>
     </row>
-    <row r="502" spans="1:5" ht="17" thickBot="1">
+    <row r="502" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A502" s="11">
         <v>43351</v>
       </c>
@@ -16014,7 +16014,7 @@
         <v>502208</v>
       </c>
     </row>
-    <row r="503" spans="1:5" ht="17" thickBot="1">
+    <row r="503" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A503" s="11">
         <v>43358</v>
       </c>
@@ -16032,7 +16032,7 @@
         <v>553003</v>
       </c>
     </row>
-    <row r="504" spans="1:5" ht="17" thickBot="1">
+    <row r="504" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A504" s="11">
         <v>43365</v>
       </c>
@@ -16050,7 +16050,7 @@
         <v>567078</v>
       </c>
     </row>
-    <row r="505" spans="1:5" ht="17" thickBot="1">
+    <row r="505" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A505" s="11">
         <v>43372</v>
       </c>
@@ -16068,7 +16068,7 @@
         <v>571922</v>
       </c>
     </row>
-    <row r="506" spans="1:5" ht="17" thickBot="1">
+    <row r="506" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A506" s="11">
         <v>43379</v>
       </c>
@@ -16086,7 +16086,7 @@
         <v>554238</v>
       </c>
     </row>
-    <row r="507" spans="1:5" ht="17" thickBot="1">
+    <row r="507" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A507" s="11">
         <v>43386</v>
       </c>
@@ -16104,7 +16104,7 @@
         <v>549757</v>
       </c>
     </row>
-    <row r="508" spans="1:5" ht="17" thickBot="1">
+    <row r="508" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A508" s="11">
         <v>43393</v>
       </c>
@@ -16122,7 +16122,7 @@
         <v>555106</v>
       </c>
     </row>
-    <row r="509" spans="1:5" ht="17" thickBot="1">
+    <row r="509" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A509" s="11">
         <v>43400</v>
       </c>
@@ -16140,7 +16140,7 @@
         <v>562804</v>
       </c>
     </row>
-    <row r="510" spans="1:5" ht="17" thickBot="1">
+    <row r="510" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A510" s="11">
         <v>43407</v>
       </c>
@@ -16158,7 +16158,7 @@
         <v>560046</v>
       </c>
     </row>
-    <row r="511" spans="1:5" ht="17" thickBot="1">
+    <row r="511" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A511" s="11">
         <v>43414</v>
       </c>
@@ -16176,7 +16176,7 @@
         <v>547236</v>
       </c>
     </row>
-    <row r="512" spans="1:5" ht="17" thickBot="1">
+    <row r="512" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A512" s="11">
         <v>43421</v>
       </c>
@@ -16194,7 +16194,7 @@
         <v>546541</v>
       </c>
     </row>
-    <row r="513" spans="1:5" ht="17" thickBot="1">
+    <row r="513" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A513" s="11">
         <v>43428</v>
       </c>
@@ -16212,7 +16212,7 @@
         <v>470851</v>
       </c>
     </row>
-    <row r="514" spans="1:5" ht="17" thickBot="1">
+    <row r="514" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A514" s="11">
         <v>43435</v>
       </c>
@@ -16245,7 +16245,7 @@
         <v>567282</v>
       </c>
     </row>
-    <row r="515" spans="1:5" ht="17" thickBot="1">
+    <row r="515" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A515" s="11">
         <v>43442</v>
       </c>
@@ -16263,7 +16263,7 @@
         <v>570225</v>
       </c>
     </row>
-    <row r="516" spans="1:5" ht="17" thickBot="1">
+    <row r="516" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A516" s="11">
         <v>43449</v>
       </c>
@@ -16281,7 +16281,7 @@
         <v>568941</v>
       </c>
     </row>
-    <row r="517" spans="1:5" ht="17" thickBot="1">
+    <row r="517" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A517" s="11">
         <v>43456</v>
       </c>
@@ -16299,7 +16299,7 @@
         <v>567252</v>
       </c>
     </row>
-    <row r="518" spans="1:5" ht="17" thickBot="1">
+    <row r="518" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A518" s="11">
         <v>43463</v>
       </c>
@@ -16317,7 +16317,7 @@
         <v>411676</v>
       </c>
     </row>
-    <row r="519" spans="1:5" ht="17" thickBot="1">
+    <row r="519" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A519" s="11">
         <v>43470</v>
       </c>
@@ -16335,7 +16335,7 @@
         <v>436103</v>
       </c>
     </row>
-    <row r="520" spans="1:5" ht="17" thickBot="1">
+    <row r="520" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A520" s="11">
         <v>43477</v>
       </c>
@@ -16353,7 +16353,7 @@
         <v>555127</v>
       </c>
     </row>
-    <row r="521" spans="1:5" ht="17" thickBot="1">
+    <row r="521" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A521" s="11">
         <v>43484</v>
       </c>
@@ -16371,7 +16371,7 @@
         <v>543111</v>
       </c>
     </row>
-    <row r="522" spans="1:5" ht="17" thickBot="1">
+    <row r="522" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A522" s="11">
         <v>43491</v>
       </c>
@@ -16389,7 +16389,7 @@
         <v>522026</v>
       </c>
     </row>
-    <row r="523" spans="1:5" ht="17" thickBot="1">
+    <row r="523" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A523" s="11">
         <v>43498</v>
       </c>
@@ -16407,7 +16407,7 @@
         <v>498288</v>
       </c>
     </row>
-    <row r="524" spans="1:5" ht="17" thickBot="1">
+    <row r="524" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A524" s="11">
         <v>43505</v>
       </c>
@@ -16425,7 +16425,7 @@
         <v>519779</v>
       </c>
     </row>
-    <row r="525" spans="1:5" ht="17" thickBot="1">
+    <row r="525" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A525" s="11">
         <v>43512</v>
       </c>
@@ -16443,7 +16443,7 @@
         <v>523915</v>
       </c>
     </row>
-    <row r="526" spans="1:5" ht="17" thickBot="1">
+    <row r="526" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A526" s="13">
         <v>43519</v>
       </c>
@@ -16461,7 +16461,7 @@
         <v>522630</v>
       </c>
     </row>
-    <row r="527" spans="1:5" ht="17" thickBot="1">
+    <row r="527" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A527" s="11">
         <v>43526</v>
       </c>
@@ -16479,7 +16479,7 @@
         <v>528153</v>
       </c>
     </row>
-    <row r="528" spans="1:5" ht="17" thickBot="1">
+    <row r="528" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A528" s="11">
         <v>43533</v>
       </c>
@@ -16497,7 +16497,7 @@
         <v>508958</v>
       </c>
     </row>
-    <row r="529" spans="1:5" ht="17" thickBot="1">
+    <row r="529" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A529" s="11">
         <v>43540</v>
       </c>
@@ -16515,7 +16515,7 @@
         <v>501001</v>
       </c>
     </row>
-    <row r="530" spans="1:5" ht="17" thickBot="1">
+    <row r="530" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A530" s="11">
         <v>43547</v>
       </c>
@@ -16533,7 +16533,7 @@
         <v>503017</v>
       </c>
     </row>
-    <row r="531" spans="1:5" ht="17" thickBot="1">
+    <row r="531" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A531" s="11">
         <v>43554</v>
       </c>
@@ -16551,7 +16551,7 @@
         <v>509958</v>
       </c>
     </row>
-    <row r="532" spans="1:5" ht="17" thickBot="1">
+    <row r="532" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A532" s="11">
         <v>43561</v>
       </c>
@@ -16569,7 +16569,7 @@
         <v>510192</v>
       </c>
     </row>
-    <row r="533" spans="1:5" ht="17" thickBot="1">
+    <row r="533" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A533" s="11">
         <v>43568</v>
       </c>
@@ -16587,7 +16587,7 @@
         <v>528167</v>
       </c>
     </row>
-    <row r="534" spans="1:5" ht="17" thickBot="1">
+    <row r="534" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A534" s="11">
         <v>43575</v>
       </c>
@@ -16605,7 +16605,7 @@
         <v>526141</v>
       </c>
     </row>
-    <row r="535" spans="1:5" ht="17" thickBot="1">
+    <row r="535" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A535" s="11">
         <v>43582</v>
       </c>
@@ -16623,7 +16623,7 @@
         <v>533190</v>
       </c>
     </row>
-    <row r="536" spans="1:5" ht="17" thickBot="1">
+    <row r="536" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A536" s="11">
         <v>43589</v>
       </c>
@@ -16641,7 +16641,7 @@
         <v>535089</v>
       </c>
     </row>
-    <row r="537" spans="1:5" ht="17" thickBot="1">
+    <row r="537" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A537" s="11">
         <v>43596</v>
       </c>
@@ -16659,7 +16659,7 @@
         <v>529263</v>
       </c>
     </row>
-    <row r="538" spans="1:5" ht="17" thickBot="1">
+    <row r="538" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A538" s="11">
         <v>43603</v>
       </c>
@@ -16677,7 +16677,7 @@
         <v>536358</v>
       </c>
     </row>
-    <row r="539" spans="1:5" ht="17" thickBot="1">
+    <row r="539" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A539" s="11">
         <v>43610</v>
       </c>
@@ -16695,7 +16695,7 @@
         <v>527966</v>
       </c>
     </row>
-    <row r="540" spans="1:5" ht="17" thickBot="1">
+    <row r="540" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A540" s="11">
         <v>43617</v>
       </c>
@@ -16713,7 +16713,7 @@
         <v>478679</v>
       </c>
     </row>
-    <row r="541" spans="1:5" ht="17" thickBot="1">
+    <row r="541" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A541" s="11">
         <v>43624</v>
       </c>
@@ -16731,7 +16731,7 @@
         <v>513099</v>
       </c>
     </row>
-    <row r="542" spans="1:5" ht="17" thickBot="1">
+    <row r="542" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A542" s="11">
         <v>43631</v>
       </c>
@@ -16749,7 +16749,7 @@
         <v>527989</v>
       </c>
     </row>
-    <row r="543" spans="1:5" ht="17" thickBot="1">
+    <row r="543" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A543" s="11">
         <v>43638</v>
       </c>
@@ -16767,7 +16767,7 @@
         <v>525116</v>
       </c>
     </row>
-    <row r="544" spans="1:5" ht="17" thickBot="1">
+    <row r="544" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A544" s="11">
         <v>43645</v>
       </c>
@@ -16785,7 +16785,7 @@
         <v>533164</v>
       </c>
     </row>
-    <row r="545" spans="1:5" ht="17" thickBot="1">
+    <row r="545" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A545" s="11">
         <v>43652</v>
       </c>
@@ -16803,7 +16803,7 @@
         <v>448459</v>
       </c>
     </row>
-    <row r="546" spans="1:5" ht="17" thickBot="1">
+    <row r="546" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A546" s="11">
         <v>43659</v>
       </c>
@@ -16821,7 +16821,7 @@
         <v>527908</v>
       </c>
     </row>
-    <row r="547" spans="1:5" ht="17" thickBot="1">
+    <row r="547" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A547" s="11">
         <v>43666</v>
       </c>
@@ -16839,7 +16839,7 @@
         <v>526010</v>
       </c>
     </row>
-    <row r="548" spans="1:5" ht="17" thickBot="1">
+    <row r="548" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A548" s="11">
         <v>43673</v>
       </c>
@@ -16857,7 +16857,7 @@
         <v>534498</v>
       </c>
     </row>
-    <row r="549" spans="1:5" ht="17" thickBot="1">
+    <row r="549" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A549" s="11">
         <v>43680</v>
       </c>
@@ -16875,7 +16875,7 @@
         <v>541558</v>
       </c>
     </row>
-    <row r="550" spans="1:5" ht="17" thickBot="1">
+    <row r="550" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A550" s="11">
         <v>43687</v>
       </c>
@@ -16893,7 +16893,7 @@
         <v>533190</v>
       </c>
     </row>
-    <row r="551" spans="1:5" ht="17" thickBot="1">
+    <row r="551" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A551" s="13">
         <v>43694</v>
       </c>
@@ -16911,7 +16911,7 @@
         <v>537617</v>
       </c>
     </row>
-    <row r="552" spans="1:5" ht="17" thickBot="1">
+    <row r="552" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A552" s="11">
         <v>43701</v>
       </c>
@@ -16929,7 +16929,7 @@
         <v>532483</v>
       </c>
     </row>
-    <row r="553" spans="1:5" ht="17" thickBot="1">
+    <row r="553" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A553" s="11">
         <v>43708</v>
       </c>
@@ -16947,7 +16947,7 @@
         <v>541945</v>
       </c>
     </row>
-    <row r="554" spans="1:5" ht="17" thickBot="1">
+    <row r="554" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A554" s="11">
         <v>43715</v>
       </c>
@@ -16965,7 +16965,7 @@
         <v>469285</v>
       </c>
     </row>
-    <row r="555" spans="1:5" ht="17" thickBot="1">
+    <row r="555" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A555" s="11">
         <v>43722</v>
       </c>
@@ -16983,7 +16983,7 @@
         <v>526734</v>
       </c>
     </row>
-    <row r="556" spans="1:5" ht="17" thickBot="1">
+    <row r="556" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A556" s="11">
         <v>43729</v>
       </c>
@@ -17001,7 +17001,7 @@
         <v>528670</v>
       </c>
     </row>
-    <row r="557" spans="1:5" ht="17" thickBot="1">
+    <row r="557" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A557" s="11">
         <v>43736</v>
       </c>
@@ -17019,7 +17019,7 @@
         <v>529336</v>
       </c>
     </row>
-    <row r="558" spans="1:5" ht="17" thickBot="1">
+    <row r="558" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A558" s="11">
         <v>43743</v>
       </c>
@@ -17037,7 +17037,7 @@
         <v>515061</v>
       </c>
     </row>
-    <row r="559" spans="1:5" ht="17" thickBot="1">
+    <row r="559" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A559" s="11">
         <v>43750</v>
       </c>
@@ -17055,7 +17055,7 @@
         <v>510820</v>
       </c>
     </row>
-    <row r="560" spans="1:5" ht="17" thickBot="1">
+    <row r="560" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A560" s="11">
         <v>43757</v>
       </c>
@@ -17073,7 +17073,7 @@
         <v>507381</v>
       </c>
     </row>
-    <row r="561" spans="1:5" ht="17" thickBot="1">
+    <row r="561" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A561" s="11">
         <v>43764</v>
       </c>
@@ -17091,7 +17091,7 @@
         <v>513147</v>
       </c>
     </row>
-    <row r="562" spans="1:5" ht="17" thickBot="1">
+    <row r="562" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A562" s="11">
         <v>43771</v>
       </c>
@@ -17109,7 +17109,7 @@
         <v>510012</v>
       </c>
     </row>
-    <row r="563" spans="1:5" ht="17" thickBot="1">
+    <row r="563" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A563" s="11">
         <v>43778</v>
       </c>
@@ -17127,7 +17127,7 @@
         <v>515269</v>
       </c>
     </row>
-    <row r="564" spans="1:5" ht="17" thickBot="1">
+    <row r="564" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A564" s="11">
         <v>43785</v>
       </c>
@@ -17145,7 +17145,7 @@
         <v>501249</v>
       </c>
     </row>
-    <row r="565" spans="1:5" ht="17" thickBot="1">
+    <row r="565" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A565" s="11">
         <v>43792</v>
       </c>
@@ -17163,7 +17163,7 @@
         <v>521927</v>
       </c>
     </row>
-    <row r="566" spans="1:5" ht="17" thickBot="1">
+    <row r="566" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A566" s="11">
         <v>43813</v>
       </c>
@@ -17181,7 +17181,7 @@
         <v>520589</v>
       </c>
     </row>
-    <row r="567" spans="1:5" ht="17" thickBot="1">
+    <row r="567" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A567" s="11">
         <v>43820</v>
       </c>
@@ -17199,7 +17199,7 @@
         <v>507589</v>
       </c>
     </row>
-    <row r="568" spans="1:5" ht="17" thickBot="1">
+    <row r="568" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A568" s="11">
         <v>43827</v>
       </c>
@@ -17217,7 +17217,7 @@
         <v>373728</v>
       </c>
     </row>
-    <row r="569" spans="1:5" ht="17" thickBot="1">
+    <row r="569" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A569" s="11">
         <v>43834</v>
       </c>
@@ -17235,7 +17235,7 @@
         <v>414014</v>
       </c>
     </row>
-    <row r="570" spans="1:5" ht="17" thickBot="1">
+    <row r="570" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A570" s="11">
         <v>43841</v>
       </c>
@@ -17253,7 +17253,7 @@
         <v>501624</v>
       </c>
     </row>
-    <row r="571" spans="1:5" ht="17" thickBot="1">
+    <row r="571" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A571" s="11">
         <v>43848</v>
       </c>
@@ -17271,7 +17271,7 @@
         <v>499732</v>
       </c>
     </row>
-    <row r="572" spans="1:5" ht="17" thickBot="1">
+    <row r="572" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A572" s="11">
         <v>43855</v>
       </c>
@@ -17289,7 +17289,7 @@
         <v>485282</v>
       </c>
     </row>
-    <row r="573" spans="1:5" ht="17" thickBot="1">
+    <row r="573" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A573" s="11">
         <v>43862</v>
       </c>
@@ -17307,7 +17307,7 @@
         <v>510161</v>
       </c>
     </row>
-    <row r="574" spans="1:5" ht="17" thickBot="1">
+    <row r="574" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A574" s="11">
         <v>43869</v>
       </c>
@@ -17325,7 +17325,7 @@
         <v>485329</v>
       </c>
     </row>
-    <row r="575" spans="1:5" ht="17" thickBot="1">
+    <row r="575" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A575" s="11">
         <v>43876</v>
       </c>
@@ -17343,7 +17343,7 @@
         <v>479137</v>
       </c>
     </row>
-    <row r="576" spans="1:5" ht="17" thickBot="1">
+    <row r="576" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A576" s="13">
         <v>43883</v>
       </c>
@@ -17361,7 +17361,7 @@
         <v>482690</v>
       </c>
     </row>
-    <row r="577" spans="1:5" ht="17" thickBot="1">
+    <row r="577" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A577" s="11">
         <v>43890</v>
       </c>
@@ -17379,7 +17379,7 @@
         <v>477611</v>
       </c>
     </row>
-    <row r="578" spans="1:5" ht="17" thickBot="1">
+    <row r="578" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A578" s="11">
         <v>43897</v>
       </c>
@@ -17412,7 +17412,7 @@
         <v>462303</v>
       </c>
     </row>
-    <row r="579" spans="1:5" ht="17" thickBot="1">
+    <row r="579" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A579" s="11">
         <v>43904</v>
       </c>
@@ -17430,7 +17430,7 @@
         <v>463017</v>
       </c>
     </row>
-    <row r="580" spans="1:5" ht="17" thickBot="1">
+    <row r="580" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A580" s="11">
         <v>43911</v>
       </c>
@@ -17448,7 +17448,7 @@
         <v>459966</v>
       </c>
     </row>
-    <row r="581" spans="1:5" ht="17" thickBot="1">
+    <row r="581" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A581" s="11">
         <v>43918</v>
       </c>
@@ -17466,7 +17466,7 @@
         <v>449767</v>
       </c>
     </row>
-    <row r="582" spans="1:5" ht="17" thickBot="1">
+    <row r="582" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A582" s="11">
         <v>43925</v>
       </c>
@@ -17484,7 +17484,7 @@
         <v>429095</v>
       </c>
     </row>
-    <row r="583" spans="1:5" ht="17" thickBot="1">
+    <row r="583" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A583" s="11">
         <v>43932</v>
       </c>
@@ -17502,7 +17502,7 @@
         <v>412503</v>
       </c>
     </row>
-    <row r="584" spans="1:5" ht="17" thickBot="1">
+    <row r="584" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A584" s="11">
         <v>43939</v>
       </c>
@@ -17520,7 +17520,7 @@
         <v>403283</v>
       </c>
     </row>
-    <row r="585" spans="1:5" ht="17" thickBot="1">
+    <row r="585" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A585" s="11">
         <v>43946</v>
       </c>
@@ -17538,7 +17538,7 @@
         <v>414123</v>
       </c>
     </row>
-    <row r="586" spans="1:5" ht="17" thickBot="1">
+    <row r="586" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A586" s="11">
         <v>43953</v>
       </c>
@@ -17556,7 +17556,7 @@
         <v>416954</v>
       </c>
     </row>
-    <row r="587" spans="1:5" ht="17" thickBot="1">
+    <row r="587" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A587" s="11">
         <v>43960</v>
       </c>
@@ -17574,7 +17574,7 @@
         <v>412549</v>
       </c>
     </row>
-    <row r="588" spans="1:5" ht="17" thickBot="1">
+    <row r="588" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A588" s="11">
         <v>43967</v>
       </c>
@@ -17592,7 +17592,7 @@
         <v>416115</v>
       </c>
     </row>
-    <row r="589" spans="1:5" ht="17" thickBot="1">
+    <row r="589" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A589" s="11">
         <v>43974</v>
       </c>
@@ -17610,7 +17610,7 @@
         <v>428715</v>
       </c>
     </row>
-    <row r="590" spans="1:5" ht="17" thickBot="1">
+    <row r="590" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A590" s="11">
         <v>43981</v>
       </c>
@@ -17628,7 +17628,7 @@
         <v>395714</v>
       </c>
     </row>
-    <row r="591" spans="1:5" ht="17" thickBot="1">
+    <row r="591" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A591" s="11">
         <v>43988</v>
       </c>
@@ -17646,7 +17646,7 @@
         <v>433171</v>
       </c>
     </row>
-    <row r="592" spans="1:5" ht="17" thickBot="1">
+    <row r="592" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A592" s="11">
         <v>43995</v>
       </c>
@@ -17664,7 +17664,7 @@
         <v>449291</v>
       </c>
     </row>
-    <row r="593" spans="1:5" ht="17" thickBot="1">
+    <row r="593" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A593" s="11">
         <v>44002</v>
       </c>
@@ -17682,7 +17682,7 @@
         <v>457278</v>
       </c>
     </row>
-    <row r="594" spans="1:5" ht="17" thickBot="1">
+    <row r="594" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A594" s="11">
         <v>44009</v>
       </c>
@@ -17700,7 +17700,7 @@
         <v>459449</v>
       </c>
     </row>
-    <row r="595" spans="1:5" ht="17" thickBot="1">
+    <row r="595" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A595" s="11">
         <v>44016</v>
       </c>
@@ -17718,7 +17718,7 @@
         <v>437989</v>
       </c>
     </row>
-    <row r="596" spans="1:5" ht="17" thickBot="1">
+    <row r="596" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A596" s="11">
         <v>44023</v>
       </c>
@@ -17736,7 +17736,7 @@
         <v>449092</v>
       </c>
     </row>
-    <row r="597" spans="1:5" ht="17" thickBot="1">
+    <row r="597" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A597" s="11">
         <v>44030</v>
       </c>
@@ -17754,7 +17754,7 @@
         <v>481597</v>
       </c>
     </row>
-    <row r="598" spans="1:5" ht="17" thickBot="1">
+    <row r="598" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A598" s="11">
         <v>44037</v>
       </c>
@@ -17772,7 +17772,7 @@
         <v>481331</v>
       </c>
     </row>
-    <row r="599" spans="1:5" ht="17" thickBot="1">
+    <row r="599" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A599" s="11">
         <v>44044</v>
       </c>
@@ -17790,7 +17790,7 @@
         <v>487968</v>
       </c>
     </row>
-    <row r="600" spans="1:5" ht="17" thickBot="1">
+    <row r="600" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A600" s="11">
         <v>44051</v>
       </c>
@@ -17808,7 +17808,7 @@
         <v>497397</v>
       </c>
     </row>
-    <row r="601" spans="1:5" ht="17" thickBot="1">
+    <row r="601" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A601" s="13">
         <v>44058</v>
       </c>
@@ -17826,7 +17826,7 @@
         <v>500563</v>
       </c>
     </row>
-    <row r="602" spans="1:5" ht="17" thickBot="1">
+    <row r="602" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A602" s="11">
         <v>44072</v>
       </c>
@@ -17844,7 +17844,7 @@
         <v>508307</v>
       </c>
     </row>
-    <row r="603" spans="1:5" ht="17" thickBot="1">
+    <row r="603" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A603" s="11">
         <v>44079</v>
       </c>
@@ -17862,7 +17862,7 @@
         <v>509637</v>
       </c>
     </row>
-    <row r="604" spans="1:5" ht="17" thickBot="1">
+    <row r="604" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A604" s="11">
         <v>44086</v>
       </c>
@@ -17880,7 +17880,7 @@
         <v>474785</v>
       </c>
     </row>
-    <row r="605" spans="1:5" ht="17" thickBot="1">
+    <row r="605" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A605" s="11">
         <v>44093</v>
       </c>
@@ -17898,7 +17898,7 @@
         <v>521956</v>
       </c>
     </row>
-    <row r="606" spans="1:5" ht="17" thickBot="1">
+    <row r="606" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A606" s="11">
         <v>44100</v>
       </c>
@@ -17916,7 +17916,7 @@
         <v>518290</v>
       </c>
     </row>
-    <row r="607" spans="1:5" ht="17" thickBot="1">
+    <row r="607" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A607" s="11">
         <v>44107</v>
       </c>
@@ -17934,7 +17934,7 @@
         <v>518761</v>
       </c>
     </row>
-    <row r="608" spans="1:5" ht="17" thickBot="1">
+    <row r="608" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A608" s="11">
         <v>44114</v>
       </c>
@@ -17952,7 +17952,7 @@
         <v>520452</v>
       </c>
     </row>
-    <row r="609" spans="1:5" ht="17" thickBot="1">
+    <row r="609" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A609" s="11">
         <v>44121</v>
       </c>
@@ -17970,7 +17970,7 @@
         <v>518763</v>
       </c>
     </row>
-    <row r="610" spans="1:5" ht="17" thickBot="1">
+    <row r="610" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A610" s="11">
         <v>44128</v>
       </c>
@@ -17988,7 +17988,7 @@
         <v>522653</v>
       </c>
     </row>
-    <row r="611" spans="1:5" ht="17" thickBot="1">
+    <row r="611" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A611" s="11">
         <v>44135</v>
       </c>
@@ -18006,7 +18006,7 @@
         <v>520778</v>
       </c>
     </row>
-    <row r="612" spans="1:5" ht="17" thickBot="1">
+    <row r="612" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A612" s="11">
         <v>44142</v>
       </c>
@@ -18024,7 +18024,7 @@
         <v>522028</v>
       </c>
     </row>
-    <row r="613" spans="1:5" ht="17" thickBot="1">
+    <row r="613" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A613" s="11">
         <v>44149</v>
       </c>
@@ -18042,7 +18042,7 @@
         <v>527462</v>
       </c>
     </row>
-    <row r="614" spans="1:5" ht="17" thickBot="1">
+    <row r="614" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A614" s="11">
         <v>44156</v>
       </c>
@@ -18060,7 +18060,7 @@
         <v>534607</v>
       </c>
     </row>
-    <row r="615" spans="1:5" ht="17" thickBot="1">
+    <row r="615" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A615" s="11">
         <v>44163</v>
       </c>
@@ -18078,7 +18078,7 @@
         <v>452792</v>
       </c>
     </row>
-    <row r="616" spans="1:5" ht="17" thickBot="1">
+    <row r="616" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A616" s="11">
         <v>44170</v>
       </c>
@@ -18096,7 +18096,7 @@
         <v>542203</v>
       </c>
     </row>
-    <row r="617" spans="1:5" ht="17" thickBot="1">
+    <row r="617" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A617" s="11">
         <v>44177</v>
       </c>
@@ -18114,7 +18114,7 @@
         <v>546209</v>
       </c>
     </row>
-    <row r="618" spans="1:5" ht="17" thickBot="1">
+    <row r="618" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A618" s="11">
         <v>44191</v>
       </c>
@@ -18132,7 +18132,7 @@
         <v>405111</v>
       </c>
     </row>
-    <row r="619" spans="1:5" ht="17" thickBot="1">
+    <row r="619" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A619" s="11">
         <v>44198</v>
       </c>
@@ -18150,7 +18150,7 @@
         <v>421991</v>
       </c>
     </row>
-    <row r="620" spans="1:5" ht="17" thickBot="1">
+    <row r="620" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A620" s="11">
         <v>44205</v>
       </c>
@@ -18168,7 +18168,7 @@
         <v>525253</v>
       </c>
     </row>
-    <row r="621" spans="1:5" ht="17" thickBot="1">
+    <row r="621" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A621" s="11">
         <v>44212</v>
       </c>
@@ -18186,7 +18186,7 @@
         <v>528547</v>
       </c>
     </row>
-    <row r="622" spans="1:5" ht="17" thickBot="1">
+    <row r="622" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A622" s="11">
         <v>44219</v>
       </c>
@@ -18204,7 +18204,7 @@
         <v>529030</v>
       </c>
     </row>
-    <row r="623" spans="1:5" ht="17" thickBot="1">
+    <row r="623" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A623" s="11">
         <v>44226</v>
       </c>
@@ -18222,7 +18222,7 @@
         <v>520693</v>
       </c>
     </row>
-    <row r="624" spans="1:5" ht="17" thickBot="1">
+    <row r="624" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A624" s="11">
         <v>44233</v>
       </c>
@@ -18240,7 +18240,7 @@
         <v>495815</v>
       </c>
     </row>
-    <row r="625" spans="1:5" ht="17" thickBot="1">
+    <row r="625" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A625" s="11">
         <v>44240</v>
       </c>
@@ -18258,7 +18258,7 @@
         <v>480483</v>
       </c>
     </row>
-    <row r="626" spans="1:5" ht="17" thickBot="1">
+    <row r="626" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A626" s="13">
         <v>44247</v>
       </c>
@@ -18276,7 +18276,7 @@
         <v>377904</v>
       </c>
     </row>
-    <row r="627" spans="1:5" ht="17" thickBot="1">
+    <row r="627" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A627" s="11">
         <v>44254</v>
       </c>
@@ -18294,7 +18294,7 @@
         <v>486429</v>
       </c>
     </row>
-    <row r="628" spans="1:5" ht="17" thickBot="1">
+    <row r="628" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A628" s="11">
         <v>44261</v>
       </c>
@@ -18312,7 +18312,7 @@
         <v>515135</v>
       </c>
     </row>
-    <row r="629" spans="1:5" ht="17" thickBot="1">
+    <row r="629" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A629" s="11">
         <v>44268</v>
       </c>
@@ -18330,7 +18330,7 @@
         <v>520736</v>
       </c>
     </row>
-    <row r="630" spans="1:5" ht="17" thickBot="1">
+    <row r="630" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A630" s="11">
         <v>44275</v>
       </c>
@@ -18348,7 +18348,7 @@
         <v>513325</v>
       </c>
     </row>
-    <row r="631" spans="1:5" ht="17" thickBot="1">
+    <row r="631" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A631" s="11">
         <v>44282</v>
       </c>
@@ -18366,7 +18366,7 @@
         <v>521731</v>
       </c>
     </row>
-    <row r="632" spans="1:5" ht="17" thickBot="1">
+    <row r="632" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A632" s="11">
         <v>44289</v>
       </c>
@@ -18384,7 +18384,7 @@
         <v>515562</v>
       </c>
     </row>
-    <row r="633" spans="1:5" ht="17" thickBot="1">
+    <row r="633" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A633" s="11">
         <v>44296</v>
       </c>
@@ -18402,7 +18402,7 @@
         <v>513724</v>
       </c>
     </row>
-    <row r="634" spans="1:5" ht="17" thickBot="1">
+    <row r="634" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A634" s="11">
         <v>44303</v>
       </c>
@@ -18420,7 +18420,7 @@
         <v>533217</v>
       </c>
     </row>
-    <row r="635" spans="1:5" ht="17" thickBot="1">
+    <row r="635" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A635" s="11">
         <v>44310</v>
       </c>
@@ -18438,7 +18438,7 @@
         <v>538184</v>
       </c>
     </row>
-    <row r="636" spans="1:5" ht="17" thickBot="1">
+    <row r="636" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A636" s="11">
         <v>44317</v>
       </c>
@@ -18456,7 +18456,7 @@
         <v>540667</v>
       </c>
     </row>
-    <row r="637" spans="1:5" ht="17" thickBot="1">
+    <row r="637" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A637" s="11">
         <v>44324</v>
       </c>
@@ -18474,7 +18474,7 @@
         <v>523309</v>
       </c>
     </row>
-    <row r="638" spans="1:5" ht="17" thickBot="1">
+    <row r="638" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A638" s="11">
         <v>44331</v>
       </c>
@@ -18492,7 +18492,7 @@
         <v>533872</v>
       </c>
     </row>
-    <row r="639" spans="1:5" ht="17" thickBot="1">
+    <row r="639" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A639" s="11">
         <v>44338</v>
       </c>
@@ -18510,7 +18510,7 @@
         <v>528774</v>
       </c>
     </row>
-    <row r="640" spans="1:5" ht="17" thickBot="1">
+    <row r="640" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A640" s="11">
         <v>44345</v>
       </c>
@@ -18528,7 +18528,7 @@
         <v>530225</v>
       </c>
     </row>
-    <row r="641" spans="1:5" ht="17" thickBot="1">
+    <row r="641" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A641" s="11">
         <v>44352</v>
       </c>
@@ -18546,7 +18546,7 @@
         <v>489144</v>
       </c>
     </row>
-    <row r="642" spans="1:5" ht="17" thickBot="1">
+    <row r="642" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A642" s="11">
         <v>44359</v>
       </c>
@@ -18579,7 +18579,7 @@
         <v>529635</v>
       </c>
     </row>
-    <row r="643" spans="1:5" ht="17" thickBot="1">
+    <row r="643" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A643" s="11">
         <v>44366</v>
       </c>
@@ -18597,7 +18597,7 @@
         <v>514112</v>
       </c>
     </row>
-    <row r="644" spans="1:5" ht="17" thickBot="1">
+    <row r="644" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A644" s="11">
         <v>44373</v>
       </c>
@@ -18615,7 +18615,7 @@
         <v>516167</v>
       </c>
     </row>
-    <row r="645" spans="1:5" ht="17" thickBot="1">
+    <row r="645" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A645" s="11">
         <v>44380</v>
       </c>
@@ -18633,7 +18633,7 @@
         <v>512919</v>
       </c>
     </row>
-    <row r="646" spans="1:5" ht="17" thickBot="1">
+    <row r="646" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A646" s="11">
         <v>44387</v>
       </c>
@@ -18651,7 +18651,7 @@
         <v>451825</v>
       </c>
     </row>
-    <row r="647" spans="1:5" ht="17" thickBot="1">
+    <row r="647" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A647" s="11">
         <v>44394</v>
       </c>
@@ -18669,7 +18669,7 @@
         <v>513255</v>
       </c>
     </row>
-    <row r="648" spans="1:5" ht="17" thickBot="1">
+    <row r="648" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A648" s="11">
         <v>44401</v>
       </c>
@@ -18687,7 +18687,7 @@
         <v>503219</v>
       </c>
     </row>
-    <row r="649" spans="1:5" ht="17" thickBot="1">
+    <row r="649" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A649" s="11">
         <v>44408</v>
       </c>
@@ -18705,7 +18705,7 @@
         <v>502540</v>
       </c>
     </row>
-    <row r="650" spans="1:5" ht="17" thickBot="1">
+    <row r="650" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A650" s="11">
         <v>44415</v>
       </c>
@@ -18723,7 +18723,7 @@
         <v>509607</v>
       </c>
     </row>
-    <row r="651" spans="1:5" ht="17" thickBot="1">
+    <row r="651" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A651" s="13">
         <v>44422</v>
       </c>
@@ -18741,7 +18741,7 @@
         <v>504810</v>
       </c>
     </row>
-    <row r="652" spans="1:5" ht="17" thickBot="1">
+    <row r="652" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A652" s="11">
         <v>44429</v>
       </c>
@@ -18759,7 +18759,7 @@
         <v>501273</v>
       </c>
     </row>
-    <row r="653" spans="1:5" ht="17" thickBot="1">
+    <row r="653" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A653" s="11">
         <v>44436</v>
       </c>
@@ -18777,7 +18777,7 @@
         <v>504417</v>
       </c>
     </row>
-    <row r="654" spans="1:5" ht="17" thickBot="1">
+    <row r="654" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A654" s="11">
         <v>44443</v>
       </c>
@@ -18795,7 +18795,7 @@
         <v>494415</v>
       </c>
     </row>
-    <row r="655" spans="1:5" ht="17" thickBot="1">
+    <row r="655" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A655" s="11">
         <v>44450</v>
       </c>
@@ -18813,7 +18813,7 @@
         <v>468610</v>
       </c>
     </row>
-    <row r="656" spans="1:5" ht="17" thickBot="1">
+    <row r="656" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A656" s="11">
         <v>44457</v>
       </c>
@@ -18831,7 +18831,7 @@
         <v>505622</v>
       </c>
     </row>
-    <row r="657" spans="1:5" ht="17" thickBot="1">
+    <row r="657" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A657" s="11">
         <v>44464</v>
       </c>
@@ -18849,7 +18849,7 @@
         <v>511713</v>
       </c>
     </row>
-    <row r="658" spans="1:5" ht="17" thickBot="1">
+    <row r="658" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A658" s="11">
         <v>44471</v>
       </c>
@@ -18867,7 +18867,7 @@
         <v>515849</v>
       </c>
     </row>
-    <row r="659" spans="1:5" ht="17" thickBot="1">
+    <row r="659" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A659" s="11">
         <v>44478</v>
       </c>
@@ -18885,7 +18885,7 @@
         <v>506642</v>
       </c>
     </row>
-    <row r="660" spans="1:5" ht="17" thickBot="1">
+    <row r="660" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A660" s="11">
         <v>44485</v>
       </c>
@@ -18903,7 +18903,7 @@
         <v>496983</v>
       </c>
     </row>
-    <row r="661" spans="1:5" ht="17" thickBot="1">
+    <row r="661" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A661" s="11">
         <v>44492</v>
       </c>
@@ -18921,7 +18921,7 @@
         <v>510762</v>
       </c>
     </row>
-    <row r="662" spans="1:5" ht="17" thickBot="1">
+    <row r="662" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A662" s="11">
         <v>44499</v>
       </c>
@@ -18939,7 +18939,7 @@
         <v>510141</v>
       </c>
     </row>
-    <row r="663" spans="1:5" ht="17" thickBot="1">
+    <row r="663" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A663" s="11">
         <v>44506</v>
       </c>
@@ -18957,7 +18957,7 @@
         <v>504111</v>
       </c>
     </row>
-    <row r="664" spans="1:5" ht="17" thickBot="1">
+    <row r="664" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A664" s="11">
         <v>44513</v>
       </c>
@@ -18975,7 +18975,7 @@
         <v>502613</v>
       </c>
     </row>
-    <row r="665" spans="1:5" ht="17" thickBot="1">
+    <row r="665" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A665" s="11">
         <v>44520</v>
       </c>
@@ -18993,7 +18993,7 @@
         <v>508309</v>
       </c>
     </row>
-    <row r="666" spans="1:5" ht="17" thickBot="1">
+    <row r="666" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A666" s="11">
         <v>44527</v>
       </c>
@@ -19011,7 +19011,7 @@
         <v>430793</v>
       </c>
     </row>
-    <row r="667" spans="1:5" ht="17" thickBot="1">
+    <row r="667" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A667" s="11">
         <v>44534</v>
       </c>
@@ -19029,7 +19029,7 @@
         <v>527406</v>
       </c>
     </row>
-    <row r="668" spans="1:5" ht="17" thickBot="1">
+    <row r="668" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A668" s="11">
         <v>44541</v>
       </c>
@@ -19047,7 +19047,7 @@
         <v>513366</v>
       </c>
     </row>
-    <row r="669" spans="1:5" ht="17" thickBot="1">
+    <row r="669" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A669" s="11">
         <v>44548</v>
       </c>
@@ -19065,7 +19065,7 @@
         <v>504099</v>
       </c>
     </row>
-    <row r="670" spans="1:5" ht="17" thickBot="1">
+    <row r="670" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A670" s="11">
         <v>44555</v>
       </c>
@@ -19083,7 +19083,7 @@
         <v>420373</v>
       </c>
     </row>
-    <row r="671" spans="1:5" ht="17" thickBot="1">
+    <row r="671" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A671" s="11">
         <v>44562</v>
       </c>
@@ -19101,7 +19101,7 @@
         <v>395371</v>
       </c>
     </row>
-    <row r="672" spans="1:5" ht="17" thickBot="1">
+    <row r="672" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A672" s="11">
         <v>44569</v>
       </c>
@@ -19119,7 +19119,7 @@
         <v>440761</v>
       </c>
     </row>
-    <row r="673" spans="1:5" ht="17" thickBot="1">
+    <row r="673" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A673" s="11">
         <v>44576</v>
       </c>
@@ -19137,7 +19137,7 @@
         <v>493617</v>
       </c>
     </row>
-    <row r="674" spans="1:5" ht="17" thickBot="1">
+    <row r="674" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A674" s="11">
         <v>44583</v>
       </c>
@@ -19155,7 +19155,7 @@
         <v>477462</v>
       </c>
     </row>
-    <row r="675" spans="1:5" ht="17" thickBot="1">
+    <row r="675" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A675" s="11">
         <v>44590</v>
       </c>
@@ -19173,7 +19173,7 @@
         <v>491868</v>
       </c>
     </row>
-    <row r="676" spans="1:5" ht="17" thickBot="1">
+    <row r="676" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A676" s="13">
         <v>44597</v>
       </c>
@@ -19191,7 +19191,7 @@
         <v>458152</v>
       </c>
     </row>
-    <row r="677" spans="1:5" ht="17" thickBot="1">
+    <row r="677" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A677" s="11">
         <v>44604</v>
       </c>
@@ -19209,7 +19209,7 @@
         <v>504482</v>
       </c>
     </row>
-    <row r="678" spans="1:5" ht="17" thickBot="1">
+    <row r="678" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A678" s="11">
         <v>44611</v>
       </c>
@@ -19227,7 +19227,7 @@
         <v>497822</v>
       </c>
     </row>
-    <row r="679" spans="1:5" ht="17" thickBot="1">
+    <row r="679" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A679" s="11">
         <v>44625</v>
       </c>
@@ -19245,7 +19245,7 @@
         <v>505177</v>
       </c>
     </row>
-    <row r="680" spans="1:5" ht="17" thickBot="1">
+    <row r="680" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A680" s="11">
         <v>44632</v>
       </c>
@@ -19263,7 +19263,7 @@
         <v>496134</v>
       </c>
     </row>
-    <row r="681" spans="1:5" ht="17" thickBot="1">
+    <row r="681" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A681" s="11">
         <v>44639</v>
       </c>
@@ -19281,7 +19281,7 @@
         <v>499362</v>
       </c>
     </row>
-    <row r="682" spans="1:5" ht="17" thickBot="1">
+    <row r="682" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A682" s="11">
         <v>44646</v>
       </c>
@@ -19299,7 +19299,7 @@
         <v>504817</v>
       </c>
     </row>
-    <row r="683" spans="1:5" ht="17" thickBot="1">
+    <row r="683" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A683" s="11">
         <v>44653</v>
       </c>
@@ -19317,7 +19317,7 @@
         <v>502194</v>
       </c>
     </row>
-    <row r="684" spans="1:5" ht="17" thickBot="1">
+    <row r="684" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A684" s="11">
         <v>44660</v>
       </c>
@@ -19335,7 +19335,7 @@
         <v>508343</v>
       </c>
     </row>
-    <row r="685" spans="1:5" ht="17" thickBot="1">
+    <row r="685" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A685" s="11">
         <v>44667</v>
       </c>
@@ -19353,7 +19353,7 @@
         <v>489801</v>
       </c>
     </row>
-    <row r="686" spans="1:5" ht="17" thickBot="1">
+    <row r="686" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A686" s="11">
         <v>44674</v>
       </c>
@@ -19371,7 +19371,7 @@
         <v>498011</v>
       </c>
     </row>
-    <row r="687" spans="1:5" ht="17" thickBot="1">
+    <row r="687" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A687" s="11">
         <v>44681</v>
       </c>
@@ -19389,7 +19389,7 @@
         <v>506699</v>
       </c>
     </row>
-    <row r="688" spans="1:5" ht="17" thickBot="1">
+    <row r="688" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A688" s="11">
         <v>44688</v>
       </c>
@@ -19407,7 +19407,7 @@
         <v>504927</v>
       </c>
     </row>
-    <row r="689" spans="1:5" ht="17" thickBot="1">
+    <row r="689" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A689" s="11">
         <v>44695</v>
       </c>
@@ -19425,7 +19425,7 @@
         <v>505120</v>
       </c>
     </row>
-    <row r="690" spans="1:5" ht="17" thickBot="1">
+    <row r="690" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A690" s="11">
         <v>44702</v>
       </c>
@@ -19443,7 +19443,7 @@
         <v>506976</v>
       </c>
     </row>
-    <row r="691" spans="1:5" ht="17" thickBot="1">
+    <row r="691" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A691" s="11">
         <v>44709</v>
       </c>
@@ -19461,7 +19461,7 @@
         <v>514277</v>
       </c>
     </row>
-    <row r="692" spans="1:5" ht="17" thickBot="1">
+    <row r="692" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A692" s="11">
         <v>44716</v>
       </c>
@@ -19479,7 +19479,7 @@
         <v>475513</v>
       </c>
     </row>
-    <row r="693" spans="1:5" ht="17" thickBot="1">
+    <row r="693" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A693" s="11">
         <v>44723</v>
       </c>
@@ -19497,7 +19497,7 @@
         <v>510295</v>
       </c>
     </row>
-    <row r="694" spans="1:5" ht="17" thickBot="1">
+    <row r="694" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A694" s="11">
         <v>44730</v>
       </c>
@@ -19515,7 +19515,7 @@
         <v>501207</v>
       </c>
     </row>
-    <row r="695" spans="1:5" ht="17" thickBot="1">
+    <row r="695" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A695" s="11">
         <v>44737</v>
       </c>
@@ -19533,7 +19533,7 @@
         <v>493374</v>
       </c>
     </row>
-    <row r="696" spans="1:5" ht="17" thickBot="1">
+    <row r="696" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A696" s="11">
         <v>44744</v>
       </c>
@@ -19551,7 +19551,7 @@
         <v>500285</v>
       </c>
     </row>
-    <row r="697" spans="1:5" ht="17" thickBot="1">
+    <row r="697" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A697" s="11">
         <v>44751</v>
       </c>
@@ -19569,7 +19569,7 @@
         <v>437600</v>
       </c>
     </row>
-    <row r="698" spans="1:5" ht="17" thickBot="1">
+    <row r="698" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A698" s="11">
         <v>44758</v>
       </c>
@@ -19587,7 +19587,7 @@
         <v>498899</v>
       </c>
     </row>
-    <row r="699" spans="1:5" ht="17" thickBot="1">
+    <row r="699" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A699" s="11">
         <v>44765</v>
       </c>
@@ -19605,7 +19605,7 @@
         <v>498901</v>
       </c>
     </row>
-    <row r="700" spans="1:5" ht="17" thickBot="1">
+    <row r="700" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A700" s="11">
         <v>44772</v>
       </c>
@@ -19623,7 +19623,7 @@
         <v>505409</v>
       </c>
     </row>
-    <row r="701" spans="1:5" ht="17" thickBot="1">
+    <row r="701" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A701" s="13">
         <v>44779</v>
       </c>
@@ -19641,7 +19641,7 @@
         <v>496526</v>
       </c>
     </row>
-    <row r="702" spans="1:5" ht="17" thickBot="1">
+    <row r="702" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A702" s="11">
         <v>44786</v>
       </c>
@@ -19659,7 +19659,7 @@
         <v>502775</v>
       </c>
     </row>
-    <row r="703" spans="1:5" ht="17" thickBot="1">
+    <row r="703" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A703" s="11">
         <v>44793</v>
       </c>
@@ -19677,7 +19677,7 @@
         <v>501548</v>
       </c>
     </row>
-    <row r="704" spans="1:5" ht="17" thickBot="1">
+    <row r="704" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A704" s="11">
         <v>44800</v>
       </c>
@@ -19695,7 +19695,7 @@
         <v>511574</v>
       </c>
     </row>
-    <row r="705" spans="1:5" ht="17" thickBot="1">
+    <row r="705" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A705" s="11">
         <v>44807</v>
       </c>
@@ -19713,7 +19713,7 @@
         <v>513087</v>
       </c>
     </row>
-    <row r="706" spans="1:5" ht="17" thickBot="1">
+    <row r="706" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A706" s="11">
         <v>44814</v>
       </c>
@@ -19746,7 +19746,7 @@
         <v>464261</v>
       </c>
     </row>
-    <row r="707" spans="1:5" ht="17" thickBot="1">
+    <row r="707" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A707" s="11">
         <v>44821</v>
       </c>
@@ -19764,7 +19764,7 @@
         <v>490654</v>
       </c>
     </row>
-    <row r="708" spans="1:5" ht="17" thickBot="1">
+    <row r="708" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A708" s="11">
         <v>44828</v>
       </c>
@@ -19782,7 +19782,7 @@
         <v>489111</v>
       </c>
     </row>
-    <row r="709" spans="1:5" ht="17" thickBot="1">
+    <row r="709" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A709" s="11">
         <v>44835</v>
       </c>
@@ -19800,7 +19800,7 @@
         <v>495868</v>
       </c>
     </row>
-    <row r="710" spans="1:5" ht="17" thickBot="1">
+    <row r="710" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A710" s="11">
         <v>44842</v>
       </c>
@@ -19818,7 +19818,7 @@
         <v>494413</v>
       </c>
     </row>
-    <row r="711" spans="1:5" ht="17" thickBot="1">
+    <row r="711" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A711" s="11">
         <v>44849</v>
       </c>
@@ -19836,7 +19836,7 @@
         <v>500304</v>
       </c>
     </row>
-    <row r="712" spans="1:5" ht="17" thickBot="1">
+    <row r="712" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A712" s="11">
         <v>44856</v>
       </c>
@@ -19854,7 +19854,7 @@
         <v>505322</v>
       </c>
     </row>
-    <row r="713" spans="1:5" ht="17" thickBot="1">
+    <row r="713" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A713" s="11">
         <v>44863</v>
       </c>
@@ -19872,7 +19872,7 @@
         <v>514457</v>
       </c>
     </row>
-    <row r="714" spans="1:5" ht="17" thickBot="1">
+    <row r="714" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A714" s="11">
         <v>44870</v>
       </c>
@@ -19890,7 +19890,7 @@
         <v>502106</v>
       </c>
     </row>
-    <row r="715" spans="1:5" ht="17" thickBot="1">
+    <row r="715" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A715" s="11">
         <v>44877</v>
       </c>
@@ -19908,7 +19908,7 @@
         <v>490350</v>
       </c>
     </row>
-    <row r="716" spans="1:5" ht="17" thickBot="1">
+    <row r="716" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A716" s="11">
         <v>44884</v>
       </c>
@@ -19926,7 +19926,7 @@
         <v>491794</v>
       </c>
     </row>
-    <row r="717" spans="1:5" ht="17" thickBot="1">
+    <row r="717" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A717" s="11">
         <v>44891</v>
       </c>
@@ -19944,7 +19944,7 @@
         <v>413305</v>
       </c>
     </row>
-    <row r="718" spans="1:5" ht="17" thickBot="1">
+    <row r="718" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A718" s="11">
         <v>44898</v>
       </c>
@@ -19962,7 +19962,7 @@
         <v>495472</v>
       </c>
     </row>
-    <row r="719" spans="1:5" ht="17" thickBot="1">
+    <row r="719" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A719" s="11">
         <v>44905</v>
       </c>
@@ -19980,7 +19980,7 @@
         <v>500310</v>
       </c>
     </row>
-    <row r="720" spans="1:5" ht="17" thickBot="1">
+    <row r="720" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A720" s="11">
         <v>44912</v>
       </c>
@@ -19998,7 +19998,7 @@
         <v>476232</v>
       </c>
     </row>
-    <row r="721" spans="1:5" ht="17" thickBot="1">
+    <row r="721" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A721" s="11">
         <v>44919</v>
       </c>
@@ -20016,7 +20016,7 @@
         <v>400289</v>
       </c>
     </row>
-    <row r="722" spans="1:5" ht="17" thickBot="1">
+    <row r="722" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A722" s="11">
         <v>44926</v>
       </c>
@@ -20034,7 +20034,7 @@
         <v>365553</v>
       </c>
     </row>
-    <row r="723" spans="1:5" ht="17" thickBot="1">
+    <row r="723" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A723" s="11">
         <v>44933</v>
       </c>
@@ -20052,7 +20052,7 @@
         <v>416489</v>
       </c>
     </row>
-    <row r="724" spans="1:5" ht="17" thickBot="1">
+    <row r="724" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A724" s="11">
         <v>44940</v>
       </c>
@@ -20070,7 +20070,7 @@
         <v>486000</v>
       </c>
     </row>
-    <row r="725" spans="1:5" ht="17" thickBot="1">
+    <row r="725" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A725" s="11">
         <v>44947</v>
       </c>
@@ -20088,7 +20088,7 @@
         <v>467485</v>
       </c>
     </row>
-    <row r="726" spans="1:5" ht="17" thickBot="1">
+    <row r="726" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A726" s="13">
         <v>44954</v>
       </c>
@@ -20106,7 +20106,7 @@
         <v>473650</v>
       </c>
     </row>
-    <row r="727" spans="1:5" ht="17" thickBot="1">
+    <row r="727" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A727" s="11">
         <v>44961</v>
       </c>
@@ -20124,7 +20124,7 @@
         <v>449586</v>
       </c>
     </row>
-    <row r="728" spans="1:5" ht="17" thickBot="1">
+    <row r="728" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A728" s="11">
         <v>44968</v>
       </c>
@@ -20142,7 +20142,7 @@
         <v>473972</v>
       </c>
     </row>
-    <row r="729" spans="1:5" ht="17" thickBot="1">
+    <row r="729" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A729" s="11">
         <v>44975</v>
       </c>
@@ -20160,7 +20160,7 @@
         <v>466932</v>
       </c>
     </row>
-    <row r="730" spans="1:5" ht="17" thickBot="1">
+    <row r="730" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A730" s="11">
         <v>44982</v>
       </c>
@@ -20178,7 +20178,7 @@
         <v>459233</v>
       </c>
     </row>
-    <row r="731" spans="1:5" ht="17" thickBot="1">
+    <row r="731" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A731" s="11">
         <v>44989</v>
       </c>
@@ -20196,7 +20196,7 @@
         <v>474191</v>
       </c>
     </row>
-    <row r="732" spans="1:5" ht="17" thickBot="1">
+    <row r="732" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A732" s="11">
         <v>44996</v>
       </c>
@@ -20214,7 +20214,7 @@
         <v>458629</v>
       </c>
     </row>
-    <row r="733" spans="1:5" ht="17" thickBot="1">
+    <row r="733" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A733" s="11">
         <v>45003</v>
       </c>
@@ -20232,7 +20232,7 @@
         <v>453500</v>
       </c>
     </row>
-    <row r="734" spans="1:5" ht="17" thickBot="1">
+    <row r="734" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A734" s="11">
         <v>45010</v>
       </c>
@@ -20250,7 +20250,7 @@
         <v>469958</v>
       </c>
     </row>
-    <row r="735" spans="1:5" ht="17" thickBot="1">
+    <row r="735" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A735" s="11">
         <v>45017</v>
       </c>
@@ -20268,7 +20268,7 @@
         <v>467430</v>
       </c>
     </row>
-    <row r="736" spans="1:5" ht="17" thickBot="1">
+    <row r="736" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A736" s="11">
         <v>45024</v>
       </c>
@@ -20286,7 +20286,7 @@
         <v>451336</v>
       </c>
     </row>
-    <row r="737" spans="1:5" ht="17" thickBot="1">
+    <row r="737" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A737" s="11">
         <v>45031</v>
       </c>
@@ -20304,7 +20304,7 @@
         <v>468197</v>
       </c>
     </row>
-    <row r="738" spans="1:5" ht="17" thickBot="1">
+    <row r="738" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A738" s="11">
         <v>45038</v>
       </c>
@@ -20322,7 +20322,7 @@
         <v>480457</v>
       </c>
     </row>
-    <row r="739" spans="1:5" ht="17" thickBot="1">
+    <row r="739" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A739" s="11">
         <v>45045</v>
       </c>
@@ -20340,7 +20340,7 @@
         <v>481960</v>
       </c>
     </row>
-    <row r="740" spans="1:5" ht="17" thickBot="1">
+    <row r="740" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A740" s="11">
         <v>45052</v>
       </c>
@@ -20358,7 +20358,7 @@
         <v>471859</v>
       </c>
     </row>
-    <row r="741" spans="1:5" ht="17" thickBot="1">
+    <row r="741" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A741" s="11">
         <v>45059</v>
       </c>
@@ -20376,7 +20376,7 @@
         <v>466381</v>
       </c>
     </row>
-    <row r="742" spans="1:5" ht="17" thickBot="1">
+    <row r="742" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A742" s="11">
         <v>45066</v>
       </c>
@@ -20394,7 +20394,7 @@
         <v>470694</v>
       </c>
     </row>
-    <row r="743" spans="1:5" ht="17" thickBot="1">
+    <row r="743" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A743" s="11">
         <v>45073</v>
       </c>
@@ -20412,7 +20412,7 @@
         <v>480998</v>
       </c>
     </row>
-    <row r="744" spans="1:5" ht="17" thickBot="1">
+    <row r="744" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A744" s="11">
         <v>45080</v>
       </c>
@@ -20430,7 +20430,7 @@
         <v>439601</v>
       </c>
     </row>
-    <row r="745" spans="1:5" ht="17" thickBot="1">
+    <row r="745" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A745" s="11">
         <v>45087</v>
       </c>
@@ -20448,7 +20448,7 @@
         <v>471141</v>
       </c>
     </row>
-    <row r="746" spans="1:5" ht="17" thickBot="1">
+    <row r="746" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A746" s="11">
         <v>45094</v>
       </c>
@@ -20466,7 +20466,7 @@
         <v>477126</v>
       </c>
     </row>
-    <row r="747" spans="1:5" ht="17" thickBot="1">
+    <row r="747" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A747" s="11">
         <v>45101</v>
       </c>
@@ -20484,7 +20484,7 @@
         <v>469453</v>
       </c>
     </row>
-    <row r="748" spans="1:5" ht="17" thickBot="1">
+    <row r="748" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A748" s="11">
         <v>45108</v>
       </c>
@@ -20502,7 +20502,7 @@
         <v>474443</v>
       </c>
     </row>
-    <row r="749" spans="1:5" ht="17" thickBot="1">
+    <row r="749" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A749" s="11">
         <v>45115</v>
       </c>
@@ -20520,7 +20520,7 @@
         <v>407843</v>
       </c>
     </row>
-    <row r="750" spans="1:5" ht="17" thickBot="1">
+    <row r="750" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A750" s="11">
         <v>45122</v>
       </c>
@@ -20538,7 +20538,7 @@
         <v>478153</v>
       </c>
     </row>
-    <row r="751" spans="1:5" ht="17" thickBot="1">
+    <row r="751" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A751" s="13">
         <v>45129</v>
       </c>
@@ -20556,7 +20556,7 @@
         <v>473736</v>
       </c>
     </row>
-    <row r="752" spans="1:5" ht="17" thickBot="1">
+    <row r="752" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A752" s="11">
         <v>45136</v>
       </c>
@@ -20574,7 +20574,7 @@
         <v>483481</v>
       </c>
     </row>
-    <row r="753" spans="1:5" ht="17" thickBot="1">
+    <row r="753" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A753" s="11">
         <v>45143</v>
       </c>
@@ -20592,7 +20592,7 @@
         <v>471938</v>
       </c>
     </row>
-    <row r="754" spans="1:5" ht="17" thickBot="1">
+    <row r="754" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A754" s="11">
         <v>45150</v>
       </c>
@@ -20610,7 +20610,7 @@
         <v>472498</v>
       </c>
     </row>
-    <row r="755" spans="1:5" ht="17" thickBot="1">
+    <row r="755" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A755" s="11">
         <v>45157</v>
       </c>
@@ -20628,7 +20628,7 @@
         <v>478853</v>
       </c>
     </row>
-    <row r="756" spans="1:5" ht="17" thickBot="1">
+    <row r="756" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A756" s="11">
         <v>45164</v>
       </c>
@@ -20646,7 +20646,7 @@
         <v>472525</v>
       </c>
     </row>
-    <row r="757" spans="1:5" ht="17" thickBot="1">
+    <row r="757" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A757" s="11">
         <v>45171</v>
       </c>
@@ -20664,7 +20664,7 @@
         <v>476851</v>
       </c>
     </row>
-    <row r="758" spans="1:5" ht="17" thickBot="1">
+    <row r="758" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A758" s="11">
         <v>45178</v>
       </c>
@@ -20682,7 +20682,7 @@
         <v>447345</v>
       </c>
     </row>
-    <row r="759" spans="1:5" ht="17" thickBot="1">
+    <row r="759" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A759" s="11">
         <v>45185</v>
       </c>
@@ -20700,7 +20700,7 @@
         <v>489790</v>
       </c>
     </row>
-    <row r="760" spans="1:5" ht="17" thickBot="1">
+    <row r="760" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A760" s="11">
         <v>45192</v>
       </c>
@@ -20718,7 +20718,7 @@
         <v>493323</v>
       </c>
     </row>
-    <row r="761" spans="1:5" ht="17" thickBot="1">
+    <row r="761" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A761" s="11">
         <v>45199</v>
       </c>
@@ -20736,7 +20736,7 @@
         <v>500154</v>
       </c>
     </row>
-    <row r="762" spans="1:5" ht="17" thickBot="1">
+    <row r="762" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A762" s="11">
         <v>45206</v>
       </c>
@@ -20754,7 +20754,7 @@
         <v>499217</v>
       </c>
     </row>
-    <row r="763" spans="1:5" ht="17" thickBot="1">
+    <row r="763" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A763" s="11">
         <v>45213</v>
       </c>
@@ -20772,7 +20772,7 @@
         <v>492781</v>
       </c>
     </row>
-    <row r="764" spans="1:5" ht="17" thickBot="1">
+    <row r="764" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A764" s="11">
         <v>45220</v>
       </c>
@@ -20790,7 +20790,7 @@
         <v>505985</v>
       </c>
     </row>
-    <row r="765" spans="1:5" ht="17" thickBot="1">
+    <row r="765" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A765" s="11">
         <v>45227</v>
       </c>
@@ -20808,7 +20808,7 @@
         <v>499389</v>
       </c>
     </row>
-    <row r="766" spans="1:5" ht="17" thickBot="1">
+    <row r="766" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A766" s="11">
         <v>45234</v>
       </c>
@@ -20826,7 +20826,7 @@
         <v>484757</v>
       </c>
     </row>
-    <row r="767" spans="1:5" ht="17" thickBot="1">
+    <row r="767" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A767" s="11">
         <v>45241</v>
       </c>
@@ -20844,7 +20844,7 @@
         <v>497348</v>
       </c>
     </row>
-    <row r="768" spans="1:5" ht="17" thickBot="1">
+    <row r="768" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A768" s="11">
         <v>45248</v>
       </c>
@@ -20862,7 +20862,7 @@
         <v>501416</v>
       </c>
     </row>
-    <row r="769" spans="1:5" ht="17" thickBot="1">
+    <row r="769" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A769" s="11">
         <v>45255</v>
       </c>
@@ -20880,7 +20880,7 @@
         <v>415332</v>
       </c>
     </row>
-    <row r="770" spans="1:5" ht="17" thickBot="1">
+    <row r="770" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A770" s="11">
         <v>45262</v>
       </c>
@@ -20913,7 +20913,7 @@
         <v>509626</v>
       </c>
     </row>
-    <row r="771" spans="1:5" ht="17" thickBot="1">
+    <row r="771" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A771" s="11">
         <v>45269</v>
       </c>
@@ -20931,7 +20931,7 @@
         <v>499094</v>
       </c>
     </row>
-    <row r="772" spans="1:5" ht="17" thickBot="1">
+    <row r="772" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A772" s="11">
         <v>45276</v>
       </c>
@@ -20949,7 +20949,7 @@
         <v>502583</v>
       </c>
     </row>
-    <row r="773" spans="1:5" ht="17" thickBot="1">
+    <row r="773" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A773" s="11">
         <v>45283</v>
       </c>
@@ -20967,7 +20967,7 @@
         <v>486787</v>
       </c>
     </row>
-    <row r="774" spans="1:5" ht="17" thickBot="1">
+    <row r="774" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A774" s="11">
         <v>45297</v>
       </c>
@@ -20985,7 +20985,7 @@
         <v>417257</v>
       </c>
     </row>
-    <row r="775" spans="1:5" ht="17" thickBot="1">
+    <row r="775" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A775" s="11">
         <v>45304</v>
       </c>
@@ -21003,7 +21003,7 @@
         <v>457453</v>
       </c>
     </row>
-    <row r="776" spans="1:5" ht="17" thickBot="1">
+    <row r="776" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A776" s="15">
         <v>45311</v>
       </c>
@@ -21021,7 +21021,7 @@
         <v>397553</v>
       </c>
     </row>
-    <row r="777" spans="1:5" ht="17" thickBot="1">
+    <row r="777" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A777" s="17">
         <v>45318</v>
       </c>
@@ -21039,7 +21039,7 @@
         <v>467222</v>
       </c>
     </row>
-    <row r="778" spans="1:5" ht="17" thickBot="1">
+    <row r="778" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A778" s="17">
         <v>45325</v>
       </c>
@@ -21057,7 +21057,7 @@
         <v>491697</v>
       </c>
     </row>
-    <row r="779" spans="1:5" ht="17" thickBot="1">
+    <row r="779" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A779" s="17">
         <v>45332</v>
       </c>
@@ -21075,7 +21075,7 @@
         <v>484840</v>
       </c>
     </row>
-    <row r="780" spans="1:5" ht="17" thickBot="1">
+    <row r="780" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A780" s="17">
         <v>45339</v>
       </c>
@@ -21093,7 +21093,7 @@
         <v>474226</v>
       </c>
     </row>
-    <row r="781" spans="1:5" ht="17" thickBot="1">
+    <row r="781" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A781" s="17">
         <v>45346</v>
       </c>
@@ -21111,7 +21111,7 @@
         <v>483656</v>
       </c>
     </row>
-    <row r="782" spans="1:5" ht="17" thickBot="1">
+    <row r="782" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A782" s="17">
         <v>45353</v>
       </c>
@@ -21129,7 +21129,7 @@
         <v>483138</v>
       </c>
     </row>
-    <row r="783" spans="1:5" ht="17" thickBot="1">
+    <row r="783" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A783" s="17">
         <v>45360</v>
       </c>
@@ -21147,7 +21147,7 @@
         <v>472662</v>
       </c>
     </row>
-    <row r="784" spans="1:5" ht="17" thickBot="1">
+    <row r="784" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A784" s="17">
         <v>45367</v>
       </c>
@@ -21165,7 +21165,7 @@
         <v>474596</v>
       </c>
     </row>
-    <row r="785" spans="1:5" ht="17" thickBot="1">
+    <row r="785" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A785" s="17">
         <v>45374</v>
       </c>
@@ -21183,7 +21183,7 @@
         <v>470593</v>
       </c>
     </row>
-    <row r="786" spans="1:5" ht="17" thickBot="1">
+    <row r="786" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A786" s="17">
         <v>45381</v>
       </c>
@@ -21201,7 +21201,7 @@
         <v>472651</v>
       </c>
     </row>
-    <row r="787" spans="1:5" ht="17" thickBot="1">
+    <row r="787" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A787" s="17">
         <v>45388</v>
       </c>
@@ -21219,7 +21219,7 @@
         <v>450142</v>
       </c>
     </row>
-    <row r="788" spans="1:5" ht="17" thickBot="1">
+    <row r="788" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A788" s="17">
         <v>45395</v>
       </c>
@@ -21237,7 +21237,7 @@
         <v>466463</v>
       </c>
     </row>
-    <row r="789" spans="1:5" ht="17" thickBot="1">
+    <row r="789" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A789" s="17">
         <v>45402</v>
       </c>
@@ -21255,7 +21255,7 @@
         <v>474544</v>
       </c>
     </row>
-    <row r="790" spans="1:5" ht="17" thickBot="1">
+    <row r="790" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A790" s="17">
         <v>45409</v>
       </c>
@@ -21273,7 +21273,7 @@
         <v>476302</v>
       </c>
     </row>
-    <row r="791" spans="1:5" ht="17" thickBot="1">
+    <row r="791" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A791" s="17">
         <v>45416</v>
       </c>
@@ -21291,7 +21291,7 @@
         <v>463106</v>
       </c>
     </row>
-    <row r="792" spans="1:5" ht="17" thickBot="1">
+    <row r="792" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A792" s="17">
         <v>45423</v>
       </c>
@@ -21309,7 +21309,7 @@
         <v>468748</v>
       </c>
     </row>
-    <row r="793" spans="1:5" ht="17" thickBot="1">
+    <row r="793" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A793" s="17">
         <v>45430</v>
       </c>
@@ -21327,7 +21327,7 @@
         <v>474886</v>
       </c>
     </row>
-    <row r="794" spans="1:5" ht="17" thickBot="1">
+    <row r="794" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A794" s="17">
         <v>45437</v>
       </c>
@@ -21345,7 +21345,7 @@
         <v>485232</v>
       </c>
     </row>
-    <row r="795" spans="1:5" ht="17" thickBot="1">
+    <row r="795" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A795" s="17">
         <v>45444</v>
       </c>
@@ -21363,7 +21363,7 @@
         <v>450077</v>
       </c>
     </row>
-    <row r="796" spans="1:5" ht="17" thickBot="1">
+    <row r="796" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A796" s="17">
         <v>45451</v>
       </c>
@@ -21381,7 +21381,7 @@
         <v>489916</v>
       </c>
     </row>
-    <row r="797" spans="1:5" ht="17" thickBot="1">
+    <row r="797" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A797" s="17">
         <v>45458</v>
       </c>
@@ -21399,7 +21399,7 @@
         <v>493138</v>
       </c>
     </row>
-    <row r="798" spans="1:5" ht="17" thickBot="1">
+    <row r="798" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A798" s="17">
         <v>45465</v>
       </c>
@@ -21417,7 +21417,7 @@
         <v>485557</v>
       </c>
     </row>
-    <row r="799" spans="1:5" ht="17" thickBot="1">
+    <row r="799" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A799" s="17">
         <v>45472</v>
       </c>
@@ -21435,7 +21435,7 @@
         <v>491899</v>
       </c>
     </row>
-    <row r="800" spans="1:5" ht="17" thickBot="1">
+    <row r="800" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A800" s="17">
         <v>45479</v>
       </c>
@@ -21453,7 +21453,7 @@
         <v>421817</v>
       </c>
     </row>
-    <row r="801" spans="1:5" ht="17" thickBot="1">
+    <row r="801" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A801" s="15">
         <v>45486</v>
       </c>
@@ -21471,7 +21471,7 @@
         <v>483806</v>
       </c>
     </row>
-    <row r="802" spans="1:5" ht="17" thickBot="1">
+    <row r="802" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A802" s="17">
         <v>45493</v>
       </c>
@@ -21489,7 +21489,7 @@
         <v>480083</v>
       </c>
     </row>
-    <row r="803" spans="1:5" ht="17" thickBot="1">
+    <row r="803" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A803" s="17">
         <v>45500</v>
       </c>
@@ -21507,7 +21507,7 @@
         <v>508496</v>
       </c>
     </row>
-    <row r="804" spans="1:5" ht="17" thickBot="1">
+    <row r="804" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A804" s="17">
         <v>45507</v>
       </c>
@@ -21525,7 +21525,7 @@
         <v>498807</v>
       </c>
     </row>
-    <row r="805" spans="1:5" ht="17" thickBot="1">
+    <row r="805" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A805" s="17">
         <v>45514</v>
       </c>
@@ -21543,7 +21543,7 @@
         <v>496509</v>
       </c>
     </row>
-    <row r="806" spans="1:5" ht="17" thickBot="1">
+    <row r="806" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A806" s="17">
         <v>45521</v>
       </c>
@@ -21561,7 +21561,7 @@
         <v>516819</v>
       </c>
     </row>
-    <row r="807" spans="1:5" ht="17" thickBot="1">
+    <row r="807" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A807" s="17">
         <v>45528</v>
       </c>
@@ -21579,7 +21579,7 @@
         <v>516807</v>
       </c>
     </row>
-    <row r="808" spans="1:5" ht="17" thickBot="1">
+    <row r="808" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A808" s="17">
         <v>45535</v>
       </c>
@@ -21597,7 +21597,7 @@
         <v>516632</v>
       </c>
     </row>
-    <row r="809" spans="1:5" ht="17" thickBot="1">
+    <row r="809" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A809" s="17">
         <v>45542</v>
       </c>
@@ -21615,7 +21615,7 @@
         <v>479179</v>
       </c>
     </row>
-    <row r="810" spans="1:5" ht="17" thickBot="1">
+    <row r="810" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A810" s="17">
         <v>45549</v>
       </c>
@@ -21633,7 +21633,7 @@
         <v>522557</v>
       </c>
     </row>
-    <row r="811" spans="1:5" ht="17" thickBot="1">
+    <row r="811" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A811" s="17">
         <v>45556</v>
       </c>
@@ -21651,7 +21651,7 @@
         <v>522112</v>
       </c>
     </row>
-    <row r="812" spans="1:5" ht="17" thickBot="1">
+    <row r="812" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A812" s="17">
         <v>45563</v>
       </c>
@@ -21669,7 +21669,7 @@
         <v>507537</v>
       </c>
     </row>
-    <row r="813" spans="1:5" ht="17" thickBot="1">
+    <row r="813" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A813" s="17">
         <v>45570</v>
       </c>
@@ -21687,7 +21687,7 @@
         <v>486187</v>
       </c>
     </row>
-    <row r="814" spans="1:5" ht="17" thickBot="1">
+    <row r="814" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A814" s="17">
         <v>45577</v>
       </c>
@@ -21705,7 +21705,7 @@
         <v>505033</v>
       </c>
     </row>
-    <row r="815" spans="1:5" ht="17" thickBot="1">
+    <row r="815" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A815" s="17">
         <v>45584</v>
       </c>
@@ -21723,7 +21723,7 @@
         <v>510730</v>
       </c>
     </row>
-    <row r="816" spans="1:5" ht="17" thickBot="1">
+    <row r="816" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A816" s="17">
         <v>45591</v>
       </c>
@@ -21741,7 +21741,7 @@
         <v>519415</v>
       </c>
     </row>
-    <row r="817" spans="1:5" ht="17" thickBot="1">
+    <row r="817" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A817" s="17">
         <v>45598</v>
       </c>
@@ -21759,7 +21759,7 @@
         <v>516743</v>
       </c>
     </row>
-    <row r="818" spans="1:5" ht="17" thickBot="1">
+    <row r="818" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A818" s="17">
         <v>45612</v>
       </c>
@@ -21777,7 +21777,7 @@
         <v>516886</v>
       </c>
     </row>
-    <row r="819" spans="1:5" ht="17" thickBot="1">
+    <row r="819" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A819" s="17">
         <v>45619</v>
       </c>
@@ -21795,7 +21795,7 @@
         <v>520798</v>
       </c>
     </row>
-    <row r="820" spans="1:5" ht="17" thickBot="1">
+    <row r="820" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A820" s="17">
         <v>45626</v>
       </c>
@@ -21813,7 +21813,7 @@
         <v>439362</v>
       </c>
     </row>
-    <row r="821" spans="1:5" ht="17" thickBot="1">
+    <row r="821" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A821" s="17">
         <v>45633</v>
       </c>
@@ -21831,7 +21831,7 @@
         <v>520894</v>
       </c>
     </row>
-    <row r="822" spans="1:5" ht="17" thickBot="1">
+    <row r="822" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A822" s="17">
         <v>45640</v>
       </c>
@@ -21849,7 +21849,7 @@
         <v>526166</v>
       </c>
     </row>
-    <row r="823" spans="1:5" ht="17" thickBot="1">
+    <row r="823" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A823" s="17">
         <v>45647</v>
       </c>
@@ -21867,7 +21867,7 @@
         <v>523912</v>
       </c>
     </row>
-    <row r="824" spans="1:5" ht="17" thickBot="1">
+    <row r="824" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A824" s="17">
         <v>45654</v>
       </c>
@@ -21885,7 +21885,7 @@
         <v>389700</v>
       </c>
     </row>
-    <row r="825" spans="1:5" ht="17" thickBot="1">
+    <row r="825" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A825" s="17">
         <v>45661</v>
       </c>
@@ -21903,7 +21903,7 @@
         <v>421410</v>
       </c>
     </row>
-    <row r="826" spans="1:5" ht="17" thickBot="1">
+    <row r="826" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A826" s="15">
         <v>45668</v>
       </c>
@@ -21921,7 +21921,7 @@
         <v>465390</v>
       </c>
     </row>
-    <row r="827" spans="1:5" ht="17" thickBot="1">
+    <row r="827" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A827" s="17">
         <v>45675</v>
       </c>
@@ -21939,7 +21939,7 @@
         <v>500160</v>
       </c>
     </row>
-    <row r="828" spans="1:5" ht="17" thickBot="1">
+    <row r="828" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A828" s="17">
         <v>45682</v>
       </c>
@@ -21957,7 +21957,7 @@
         <v>454797</v>
       </c>
     </row>
-    <row r="829" spans="1:5" ht="17" thickBot="1">
+    <row r="829" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A829" s="17">
         <v>45689</v>
       </c>
@@ -21975,7 +21975,7 @@
         <v>513622</v>
       </c>
     </row>
-    <row r="830" spans="1:5" ht="17" thickBot="1">
+    <row r="830" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A830" s="17">
         <v>45696</v>
       </c>
@@ -21993,7 +21993,7 @@
         <v>502449</v>
       </c>
     </row>
-    <row r="831" spans="1:5" ht="17" thickBot="1">
+    <row r="831" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A831" s="17">
         <v>45703</v>
       </c>
@@ -22011,7 +22011,7 @@
         <v>480740</v>
       </c>
     </row>
-    <row r="832" spans="1:5" ht="17" thickBot="1">
+    <row r="832" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A832" s="17">
         <v>45710</v>
       </c>
@@ -22029,7 +22029,7 @@
         <v>458513</v>
       </c>
     </row>
-    <row r="833" spans="1:5" ht="17" thickBot="1">
+    <row r="833" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A833" s="17">
         <v>45717</v>
       </c>
@@ -22047,7 +22047,7 @@
         <v>508531</v>
       </c>
     </row>
-    <row r="834" spans="1:5" ht="17" thickBot="1">
+    <row r="834" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A834" s="17">
         <v>45724</v>
       </c>
@@ -22080,7 +22080,7 @@
         <v>497412</v>
       </c>
     </row>
-    <row r="835" spans="1:5" ht="17" thickBot="1">
+    <row r="835" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A835" s="17">
         <v>45731</v>
       </c>
@@ -22098,7 +22098,7 @@
         <v>503473</v>
       </c>
     </row>
-    <row r="836" spans="1:5" ht="17" thickBot="1">
+    <row r="836" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A836" s="17">
         <v>45738</v>
       </c>
@@ -22116,7 +22116,7 @@
         <v>496214</v>
       </c>
     </row>
-    <row r="837" spans="1:5" ht="17" thickBot="1">
+    <row r="837" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A837" s="17">
         <v>45745</v>
       </c>
@@ -22134,7 +22134,7 @@
         <v>513553</v>
       </c>
     </row>
-    <row r="838" spans="1:5" ht="17" thickBot="1">
+    <row r="838" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A838" s="17">
         <v>45752</v>
       </c>
@@ -22152,7 +22152,7 @@
         <v>500584</v>
       </c>
     </row>
-    <row r="839" spans="1:5" ht="17" thickBot="1">
+    <row r="839" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A839" s="17">
         <v>45759</v>
       </c>
@@ -22170,7 +22170,7 @@
         <v>491908</v>
       </c>
     </row>
-    <row r="840" spans="1:5" ht="17" thickBot="1">
+    <row r="840" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A840" s="17">
         <v>45766</v>
       </c>
@@ -22188,7 +22188,7 @@
         <v>496053</v>
       </c>
     </row>
-    <row r="841" spans="1:5" ht="17" thickBot="1">
+    <row r="841" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A841" s="17">
         <v>45773</v>
       </c>
@@ -22206,7 +22206,7 @@
         <v>502105</v>
       </c>
     </row>
-    <row r="842" spans="1:5" ht="17" thickBot="1">
+    <row r="842" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A842" s="17">
         <v>45780</v>
       </c>
@@ -22224,7 +22224,7 @@
         <v>498693</v>
       </c>
     </row>
-    <row r="843" spans="1:5" ht="17" thickBot="1">
+    <row r="843" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A843" s="17">
         <v>45787</v>
       </c>
@@ -22242,7 +22242,7 @@
         <v>495552</v>
       </c>
     </row>
-    <row r="844" spans="1:5" ht="17" thickBot="1">
+    <row r="844" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A844" s="17">
         <v>45794</v>
       </c>
@@ -22260,7 +22260,7 @@
         <v>490775</v>
       </c>
     </row>
-    <row r="845" spans="1:5" ht="17" thickBot="1">
+    <row r="845" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A845" s="17">
         <v>45801</v>
       </c>
@@ -22278,7 +22278,7 @@
         <v>488709</v>
       </c>
     </row>
-    <row r="846" spans="1:5" ht="17" thickBot="1">
+    <row r="846" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A846" s="17">
         <v>45808</v>
       </c>
@@ -22296,7 +22296,7 @@
         <v>459884</v>
       </c>
     </row>
-    <row r="847" spans="1:5" ht="17" thickBot="1">
+    <row r="847" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A847" s="17">
         <v>45815</v>
       </c>
@@ -22314,7 +22314,7 @@
         <v>483807</v>
       </c>
     </row>
-    <row r="848" spans="1:5" ht="17" thickBot="1">
+    <row r="848" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A848" s="17">
         <v>45822</v>
       </c>
@@ -22332,7 +22332,7 @@
         <v>485810</v>
       </c>
     </row>
-    <row r="849" spans="1:5" ht="17" thickBot="1">
+    <row r="849" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A849" s="17">
         <v>45829</v>
       </c>
@@ -22350,7 +22350,7 @@
         <v>487328</v>
       </c>
     </row>
-    <row r="850" spans="1:5" ht="17" thickBot="1">
+    <row r="850" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A850" s="17">
         <v>45836</v>
       </c>
@@ -22368,7 +22368,7 @@
         <v>491424</v>
       </c>
     </row>
-    <row r="851" spans="1:5" ht="17" thickBot="1">
+    <row r="851" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A851" s="15">
         <v>45843</v>
       </c>
@@ -22386,7 +22386,7 @@
         <v>443049</v>
       </c>
     </row>
-    <row r="852" spans="1:5" ht="17" thickBot="1">
+    <row r="852" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A852" s="17">
         <v>45850</v>
       </c>
@@ -22404,7 +22404,7 @@
         <v>496188</v>
       </c>
     </row>
-    <row r="853" spans="1:5" ht="17" thickBot="1">
+    <row r="853" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A853" s="17">
         <v>45857</v>
       </c>
@@ -22422,7 +22422,7 @@
         <v>506882</v>
       </c>
     </row>
-    <row r="854" spans="1:5" ht="17" thickBot="1">
+    <row r="854" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A854" s="17">
         <v>45864</v>
       </c>
@@ -22440,7 +22440,7 @@
         <v>514279</v>
       </c>
     </row>
-    <row r="855" spans="1:5" ht="17" thickBot="1">
+    <row r="855" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A855" s="17">
         <v>45871</v>
       </c>
@@ -22458,7 +22458,7 @@
         <v>513529</v>
       </c>
     </row>
-    <row r="856" spans="1:5" ht="17" thickBot="1">
+    <row r="856" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A856" s="17">
         <v>45878</v>
       </c>
@@ -22476,7 +22476,7 @@
         <v>511194</v>
       </c>
     </row>
-    <row r="857" spans="1:5" ht="17" thickBot="1">
+    <row r="857" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A857" s="17">
         <v>45885</v>
       </c>
@@ -22494,7 +22494,7 @@
         <v>512970</v>
       </c>
     </row>
-    <row r="858" spans="1:5" ht="17" thickBot="1">
+    <row r="858" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A858" s="17">
         <v>45892</v>
       </c>
@@ -22512,7 +22512,7 @@
         <v>512333</v>
       </c>
     </row>
-    <row r="859" spans="1:5" ht="17" thickBot="1">
+    <row r="859" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A859" s="17">
         <v>45899</v>
       </c>
@@ -22530,7 +22530,7 @@
         <v>521502</v>
       </c>
     </row>
-    <row r="860" spans="1:5" ht="17" thickBot="1">
+    <row r="860" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A860" s="17">
         <v>45906</v>
       </c>
@@ -22548,7 +22548,7 @@
         <v>467880</v>
       </c>
     </row>
-    <row r="861" spans="1:5" ht="17" thickBot="1">
+    <row r="861" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A861" s="17">
         <v>45913</v>
       </c>
@@ -22566,7 +22566,7 @@
         <v>514167</v>
       </c>
     </row>
-    <row r="862" spans="1:5" ht="17" thickBot="1">
+    <row r="862" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A862" s="17">
         <v>45920</v>
       </c>
@@ -22584,7 +22584,7 @@
         <v>510677</v>
       </c>
     </row>
-    <row r="863" spans="1:5" ht="17" thickBot="1">
+    <row r="863" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A863" s="15">
         <v>45927</v>
       </c>
@@ -22602,7 +22602,7 @@
         <v>512642</v>
       </c>
     </row>
-    <row r="864" spans="1:5" ht="17" thickBot="1">
+    <row r="864" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A864" s="17">
         <v>45934</v>
       </c>
@@ -22620,7 +22620,7 @@
         <v>503538</v>
       </c>
     </row>
-    <row r="865" spans="1:5" ht="17" thickBot="1">
+    <row r="865" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A865" s="17">
         <v>45941</v>
       </c>
@@ -22638,7 +22638,7 @@
         <v>498462</v>
       </c>
     </row>
-    <row r="866" spans="1:5" ht="17" thickBot="1">
+    <row r="866" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A866" s="17">
         <v>45948</v>
       </c>
@@ -22656,7 +22656,7 @@
         <v>497854</v>
       </c>
     </row>
-    <row r="867" spans="1:5" ht="17" thickBot="1">
+    <row r="867" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A867" s="17">
         <v>45955</v>
       </c>
@@ -22674,7 +22674,7 @@
         <v>499688</v>
       </c>
     </row>
-    <row r="868" spans="1:5" ht="17" thickBot="1">
+    <row r="868" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A868" s="17">
         <v>45962</v>
       </c>
@@ -22692,7 +22692,7 @@
         <v>496928</v>
       </c>
     </row>
-    <row r="869" spans="1:5" ht="17" thickBot="1">
+    <row r="869" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A869" s="17">
         <v>45969</v>
       </c>
@@ -22710,7 +22710,7 @@
         <v>493493</v>
       </c>
     </row>
-    <row r="870" spans="1:5" ht="17" thickBot="1">
+    <row r="870" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A870" s="17">
         <v>45976</v>
       </c>
@@ -22728,7 +22728,7 @@
         <v>493880</v>
       </c>
     </row>
-    <row r="871" spans="1:5" ht="17" thickBot="1">
+    <row r="871" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A871" s="17">
         <v>45983</v>
       </c>
@@ -22746,7 +22746,7 @@
         <v>516110</v>
       </c>
     </row>
-    <row r="872" spans="1:5" ht="17" thickBot="1">
+    <row r="872" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A872" s="17">
         <v>45990</v>
       </c>
@@ -22764,7 +22764,7 @@
         <v>431435</v>
       </c>
     </row>
-    <row r="873" spans="1:5" ht="17" thickBot="1">
+    <row r="873" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A873" s="17">
         <v>45997</v>
       </c>
@@ -22782,7 +22782,7 @@
         <v>508999</v>
       </c>
     </row>
-    <row r="874" spans="1:5" ht="17" thickBot="1">
+    <row r="874" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A874" s="17">
         <v>46004</v>
       </c>
@@ -22800,7 +22800,7 @@
         <v>518904</v>
       </c>
     </row>
-    <row r="875" spans="1:5" ht="17" thickBot="1">
+    <row r="875" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A875" s="15">
         <v>46018</v>
       </c>
@@ -22818,7 +22818,7 @@
         <v>392295</v>
       </c>
     </row>
-    <row r="876" spans="1:5" ht="17" thickBot="1">
+    <row r="876" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A876" s="8">
         <v>46025</v>
       </c>
@@ -22836,7 +22836,7 @@
         <v>404293</v>
       </c>
     </row>
-    <row r="877" spans="1:5" ht="17" thickBot="1">
+    <row r="877" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A877" s="15">
         <v>46032</v>
       </c>
@@ -22854,7 +22854,7 @@
         <v>510457</v>
       </c>
     </row>
-    <row r="878" spans="1:5" ht="17" thickBot="1">
+    <row r="878" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A878" s="8">
         <v>46039</v>
       </c>
@@ -22887,7 +22887,7 @@
         <v>505385</v>
       </c>
     </row>
-    <row r="879" spans="1:5" ht="17" thickBot="1">
+    <row r="879" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A879" s="15">
         <v>46046</v>
       </c>
@@ -22920,7 +22920,7 @@
         <v>481708</v>
       </c>
     </row>
-    <row r="880" spans="1:5" ht="17" thickBot="1">
+    <row r="880" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A880" s="15">
         <v>46053</v>
       </c>
@@ -22953,7 +22953,7 @@
         <v>434361</v>
       </c>
     </row>
-    <row r="881" spans="1:5" ht="17" thickBot="1">
+    <row r="881" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A881" s="15">
         <v>46060</v>
       </c>
@@ -22971,7 +22971,7 @@
         <v>486854</v>
       </c>
     </row>
-    <row r="882" spans="1:5" ht="17" thickBot="1">
+    <row r="882" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A882" s="8">
         <v>46067</v>
       </c>
@@ -23004,7 +23004,7 @@
         <v>510399</v>
       </c>
     </row>
-    <row r="883" spans="1:5" ht="17" thickBot="1">
+    <row r="883" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A883" s="15">
         <v>46074</v>
       </c>
@@ -23037,7 +23037,7 @@
         <v>507712</v>
       </c>
     </row>
-    <row r="884" spans="1:5" ht="17" thickBot="1">
+    <row r="884" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A884" s="8">
         <v>46081</v>
       </c>
@@ -23055,7 +23055,7 @@
         <v>516729</v>
       </c>
     </row>
-    <row r="885" spans="1:5" ht="17" thickBot="1">
+    <row r="885" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A885" s="15">
         <v>46088</v>
       </c>
@@ -23073,7 +23073,7 @@
         <v>514996</v>
       </c>
     </row>
-    <row r="886" spans="1:5" ht="16">
+    <row r="886" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A886" s="8">
         <v>46102</v>
       </c>
@@ -23091,7 +23091,7 @@
         <v>502252</v>
       </c>
     </row>
-    <row r="887" spans="1:5" ht="16">
+    <row r="887" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A887" s="8">
         <v>46109</v>
       </c>
@@ -23109,7 +23109,7 @@
         <v>515921</v>
       </c>
     </row>
-    <row r="888" spans="1:5" ht="16">
+    <row r="888" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A888" s="8">
         <v>46116</v>
       </c>
@@ -23127,7 +23127,7 @@
         <v>501328</v>
       </c>
     </row>
-    <row r="889" spans="1:5" ht="16">
+    <row r="889" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A889" s="8">
         <v>46123</v>
       </c>
@@ -23145,7 +23145,7 @@
         <v>500040</v>
       </c>
     </row>
-    <row r="890" spans="1:5" ht="16">
+    <row r="890" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A890" s="8">
         <v>46130</v>
       </c>
@@ -23163,7 +23163,7 @@
         <v>508303</v>
       </c>
     </row>
-    <row r="891" spans="1:5" ht="16">
+    <row r="891" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A891" s="8">
         <v>46137</v>
       </c>
@@ -23181,7 +23181,7 @@
         <v>511616</v>
       </c>
     </row>
-    <row r="892" spans="1:5" ht="16">
+    <row r="892" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A892" s="8">
         <v>46144</v>
       </c>
@@ -23199,7 +23199,7 @@
         <v>518773</v>
       </c>
     </row>
-    <row r="893" spans="1:5" ht="16">
+    <row r="893" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A893" s="8">
         <v>46151</v>
       </c>
@@ -23232,7 +23232,7 @@
         <v>513755</v>
       </c>
     </row>
-    <row r="894" spans="1:5" ht="16">
+    <row r="894" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A894" s="8">
         <v>46158</v>
       </c>
@@ -23250,7 +23250,7 @@
         <v>511216</v>
       </c>
     </row>
-    <row r="895" spans="1:5" ht="16">
+    <row r="895" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A895" s="8">
         <v>46165</v>
       </c>
@@ -23268,7 +23268,7 @@
         <v>523574</v>
       </c>
     </row>
-    <row r="896" spans="1:5" ht="16">
+    <row r="896" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A896" s="8">
         <v>46172</v>
       </c>
@@ -23301,7 +23301,7 @@
         <v>492795</v>
       </c>
     </row>
-    <row r="897" spans="1:5" ht="16">
+    <row r="897" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A897" s="8">
         <v>46179</v>
       </c>
@@ -23319,7 +23319,7 @@
         <v>521804</v>
       </c>
     </row>
-    <row r="898" spans="1:5" ht="16">
+    <row r="898" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A898" s="8">
         <v>46186</v>
       </c>
@@ -23337,7 +23337,7 @@
         <v>520406</v>
       </c>
     </row>
-    <row r="899" spans="1:5" ht="16">
+    <row r="899" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A899" s="8">
         <v>46193</v>
       </c>
@@ -23345,7 +23345,7 @@
         <v>46197</v>
       </c>
       <c r="C899" s="21">
-        <v>0.87291666666666601</v>
+        <v>0.50138888888888888</v>
       </c>
       <c r="D899" s="7" t="str">
         <f t="shared" ref="D899" si="18">IF(
@@ -23366,6 +23366,9 @@
 )</f>
         <v>UTC-4</v>
       </c>
+      <c r="E899" s="20">
+        <v>521998</v>
+      </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E876">
@@ -23380,7 +23383,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{300947AE-C9E8-48BA-99BA-AA00E1AFF02E}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="15.6" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -23391,12 +23394,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFF96248-4EFB-4252-A059-6D65AEEDC293}">
   <dimension ref="B2:C4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="15.6" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
@@ -23404,7 +23407,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="2:3">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
@@ -23412,7 +23415,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="2:3">
+    <row r="4" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>

--- a/data/freight/US Rail Traffic.xlsx
+++ b/data/freight/US Rail Traffic.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CB49217-E88F-44A8-905E-08B6AABE2CE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6914BA7-DAC9-46C5-94B5-90C10012C56A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{55EF15CE-83DB-4E42-B75D-C3DAE3AA4C48}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{55EF15CE-83DB-4E42-B75D-C3DAE3AA4C48}"/>
   </bookViews>
   <sheets>
     <sheet name="USRT" sheetId="1" r:id="rId1"/>
@@ -6833,7 +6833,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83FCC8DB-37A0-4531-B65E-34C65BAF4830}">
-  <dimension ref="A1:E899"/>
+  <dimension ref="A1:E900"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="8" bestFit="1" customWidth="1"/>
@@ -23348,7 +23348,7 @@
         <v>0.50138888888888888</v>
       </c>
       <c r="D899" s="7" t="str">
-        <f t="shared" ref="D899" si="18">IF(
+        <f t="shared" ref="D899:D900" si="18">IF(
  AND(
   A899 &gt;= IF(
          YEAR(A899)&gt;=2007,
@@ -23368,6 +23368,21 @@
       </c>
       <c r="E899" s="20">
         <v>521998</v>
+      </c>
+    </row>
+    <row r="900" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A900" s="8">
+        <v>46200</v>
+      </c>
+      <c r="B900" s="8">
+        <v>46204</v>
+      </c>
+      <c r="C900" s="21">
+        <v>0.50069444444444444</v>
+      </c>
+      <c r="D900" s="7" t="str">
+        <f t="shared" si="18"/>
+        <v>UTC-4</v>
       </c>
     </row>
   </sheetData>
